--- a/data/teams/leagues/Averages_Spain_Segunda_División_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Spain_Segunda_División_2025-2026.xlsx
@@ -137,7 +137,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="AveragesTable" displayName="AveragesTable" ref="A1:EC23" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="AveragesTable_Spain_Segu" displayName="AveragesTable_Spain_Segu" ref="A1:EC23" headerRowCount="1">
   <autoFilter ref="A1:EC23"/>
   <tableColumns count="133">
     <tableColumn id="1" name="team_name"/>

--- a/data/teams/leagues/Averages_Spain_Segunda_División_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Spain_Segunda_División_2025-2026.xlsx
@@ -1379,10 +1379,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2" t="n">
         <v>7</v>
@@ -1391,49 +1391,49 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="G2" t="n">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="H2" t="n">
-        <v>93.33</v>
+        <v>91.43000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.17</v>
+        <v>-0.14</v>
       </c>
       <c r="J2" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="K2" t="n">
-        <v>5.17</v>
+        <v>5</v>
       </c>
       <c r="L2" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="M2" t="n">
-        <v>49</v>
+        <v>48.86</v>
       </c>
       <c r="N2" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="O2" t="n">
-        <v>2.67</v>
+        <v>2.43</v>
       </c>
       <c r="P2" t="n">
-        <v>10</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="Q2" t="n">
-        <v>9.83</v>
+        <v>9.57</v>
       </c>
       <c r="R2" t="n">
-        <v>6.83</v>
+        <v>7.14</v>
       </c>
       <c r="S2" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="T2" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -1445,28 +1445,28 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>45.67</v>
+        <v>43.86</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="Z2" t="n">
-        <v>15.5</v>
+        <v>15.71</v>
       </c>
       <c r="AA2" t="n">
-        <v>10.67</v>
+        <v>10.71</v>
       </c>
       <c r="AB2" t="n">
-        <v>4.83</v>
+        <v>5</v>
       </c>
       <c r="AC2" t="n">
-        <v>25.33</v>
+        <v>24.86</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AF2" t="n">
         <v>0.43</v>
@@ -1550,70 +1550,70 @@
         <v>2.43</v>
       </c>
       <c r="BG2" t="n">
-        <v>3.31</v>
+        <v>3.14</v>
       </c>
       <c r="BH2" t="n">
-        <v>10.85</v>
+        <v>10.5</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.31</v>
+        <v>3.14</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="BL2" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="BN2" t="n">
-        <v>2.31</v>
+        <v>2.21</v>
       </c>
       <c r="BO2" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="BP2" t="n">
-        <v>5.54</v>
+        <v>5.21</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.23</v>
+        <v>5.21</v>
       </c>
       <c r="BR2" t="n">
-        <v>76.92</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="BS2" t="n">
-        <v>69.23</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="BT2" t="n">
-        <v>61.54</v>
+        <v>57.14</v>
       </c>
       <c r="BU2" t="n">
-        <v>46.15</v>
+        <v>42.86</v>
       </c>
       <c r="BV2" t="n">
-        <v>38.46</v>
+        <v>35.71</v>
       </c>
       <c r="BW2" t="n">
-        <v>15.38</v>
+        <v>14.29</v>
       </c>
       <c r="BX2" t="n">
-        <v>61.54</v>
+        <v>57.14</v>
       </c>
       <c r="BY2" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="BZ2" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.31</v>
+        <v>3.32</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.56</v>
+        <v>3.57</v>
       </c>
       <c r="CC2" t="n">
         <v>3.77</v>
@@ -1625,7 +1625,7 @@
         <v>1.37</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.69</v>
+        <v>2.68</v>
       </c>
       <c r="CG2" t="n">
         <v>2.92</v>
@@ -1634,19 +1634,19 @@
         <v>1.42</v>
       </c>
       <c r="CI2" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="CJ2" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="CL2" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="CN2" t="n">
         <v>1.89</v>
@@ -1655,28 +1655,28 @@
         <v>1.27</v>
       </c>
       <c r="CP2" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CQ2" t="n">
-        <v>3.23</v>
+        <v>3.21</v>
       </c>
       <c r="CR2" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CS2" t="n">
-        <v>2.83</v>
+        <v>2.82</v>
       </c>
       <c r="CT2" t="n">
-        <v>3.05</v>
+        <v>3.08</v>
       </c>
       <c r="CU2" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="CV2" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="CW2" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CX2" t="n">
         <v>1.51</v>
@@ -1685,7 +1685,7 @@
         <v>1.86</v>
       </c>
       <c r="CZ2" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="DA2" t="n">
         <v>1.95</v>
@@ -1694,85 +1694,85 @@
         <v>1.29</v>
       </c>
       <c r="DC2" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="DD2" t="n">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="DH2" t="n">
-        <v>89.08</v>
+        <v>88.43000000000001</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.69</v>
+        <v>2.58</v>
       </c>
       <c r="DK2" t="n">
-        <v>4.7</v>
+        <v>4.65</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="DM2" t="n">
-        <v>44.69</v>
+        <v>44.93</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.85</v>
+        <v>0.78</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.54</v>
+        <v>2.43</v>
       </c>
       <c r="DP2" t="n">
-        <v>11.31</v>
+        <v>11.14</v>
       </c>
       <c r="DQ2" t="n">
-        <v>11.46</v>
+        <v>11.22</v>
       </c>
       <c r="DR2" t="n">
-        <v>8.23</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>44.08</v>
+        <v>43.28</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.31</v>
+        <v>0.28</v>
       </c>
       <c r="DX2" t="n">
-        <v>13.54</v>
+        <v>13.78</v>
       </c>
       <c r="DY2" t="n">
-        <v>8.460000000000001</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="DZ2" t="n">
-        <v>5.08</v>
+        <v>5.14</v>
       </c>
       <c r="EA2" t="n">
-        <v>24.15</v>
+        <v>24</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -2588,94 +2588,94 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D5" t="n">
         <v>7</v>
       </c>
       <c r="E5" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="F5" t="n">
-        <v>2.83</v>
+        <v>2.71</v>
       </c>
       <c r="G5" t="n">
-        <v>3.83</v>
+        <v>4</v>
       </c>
       <c r="H5" t="n">
-        <v>107.33</v>
+        <v>108.14</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>4</v>
+        <v>3.86</v>
       </c>
       <c r="K5" t="n">
-        <v>7.33</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="M5" t="n">
-        <v>68.83</v>
+        <v>68.43000000000001</v>
       </c>
       <c r="N5" t="n">
         <v>1</v>
       </c>
       <c r="O5" t="n">
-        <v>3.5</v>
+        <v>4.29</v>
       </c>
       <c r="P5" t="n">
-        <v>13.67</v>
+        <v>13</v>
       </c>
       <c r="Q5" t="n">
-        <v>15.83</v>
+        <v>15.29</v>
       </c>
       <c r="R5" t="n">
-        <v>5</v>
+        <v>5.14</v>
       </c>
       <c r="S5" t="n">
-        <v>1.33</v>
+        <v>1.71</v>
       </c>
       <c r="T5" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="U5" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="V5" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>59.83</v>
+        <v>60.57</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="Z5" t="n">
-        <v>15.5</v>
+        <v>16.57</v>
       </c>
       <c r="AA5" t="n">
-        <v>10.17</v>
+        <v>10.86</v>
       </c>
       <c r="AB5" t="n">
-        <v>5.33</v>
+        <v>5.71</v>
       </c>
       <c r="AC5" t="n">
-        <v>18.83</v>
+        <v>18</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="AE5" t="n">
-        <v>3.33</v>
+        <v>3.29</v>
       </c>
       <c r="AF5" t="n">
         <v>0.14</v>
@@ -2759,70 +2759,70 @@
         <v>2.29</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.31</v>
+        <v>2.79</v>
       </c>
       <c r="BH5" t="n">
-        <v>10.31</v>
+        <v>10.64</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.31</v>
+        <v>2.79</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.77</v>
+        <v>1</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.38</v>
+        <v>0.57</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.15</v>
+        <v>1.57</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="BP5" t="n">
-        <v>5.31</v>
+        <v>5.57</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5</v>
+        <v>5.07</v>
       </c>
       <c r="BR5" t="n">
-        <v>84.62</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BS5" t="n">
-        <v>53.85</v>
+        <v>57.14</v>
       </c>
       <c r="BT5" t="n">
-        <v>46.15</v>
+        <v>50</v>
       </c>
       <c r="BU5" t="n">
-        <v>30.77</v>
+        <v>35.71</v>
       </c>
       <c r="BV5" t="n">
-        <v>7.69</v>
+        <v>14.29</v>
       </c>
       <c r="BW5" t="n">
-        <v>7.69</v>
+        <v>14.29</v>
       </c>
       <c r="BX5" t="n">
-        <v>53.85</v>
+        <v>57.14</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.74</v>
+        <v>1.68</v>
       </c>
       <c r="BZ5" t="n">
-        <v>1.74</v>
+        <v>1.68</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.48</v>
+        <v>3.61</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.76</v>
+        <v>3.89</v>
       </c>
       <c r="CC5" t="n">
         <v>2.86</v>
@@ -2834,19 +2834,19 @@
         <v>1.33</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.57</v>
+        <v>2.56</v>
       </c>
       <c r="CG5" t="n">
-        <v>3.09</v>
+        <v>3.1</v>
       </c>
       <c r="CH5" t="n">
         <v>1.48</v>
       </c>
       <c r="CI5" t="n">
-        <v>2.16</v>
+        <v>2.13</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="CK5" t="n">
         <v>1.53</v>
@@ -2867,25 +2867,25 @@
         <v>1.74</v>
       </c>
       <c r="CQ5" t="n">
-        <v>2.83</v>
+        <v>2.82</v>
       </c>
       <c r="CR5" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CS5" t="n">
-        <v>2.78</v>
+        <v>2.75</v>
       </c>
       <c r="CT5" t="n">
-        <v>3.12</v>
+        <v>3.14</v>
       </c>
       <c r="CU5" t="n">
         <v>1.49</v>
       </c>
       <c r="CV5" t="n">
-        <v>2.29</v>
+        <v>2.26</v>
       </c>
       <c r="CW5" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="CX5" t="n">
         <v>1.55</v>
@@ -2903,85 +2903,85 @@
         <v>1.24</v>
       </c>
       <c r="DC5" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="DD5" t="n">
-        <v>2.93</v>
+        <v>2.91</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DF5" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="DG5" t="n">
-        <v>3</v>
+        <v>3.14</v>
       </c>
       <c r="DH5" t="n">
-        <v>100.69</v>
+        <v>101.57</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DJ5" t="n">
-        <v>3.23</v>
+        <v>3.22</v>
       </c>
       <c r="DK5" t="n">
-        <v>6.31</v>
+        <v>6.86</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.61</v>
+        <v>0.64</v>
       </c>
       <c r="DM5" t="n">
-        <v>59.84</v>
+        <v>60.28</v>
       </c>
       <c r="DN5" t="n">
         <v>1</v>
       </c>
       <c r="DO5" t="n">
-        <v>3.31</v>
+        <v>3.72</v>
       </c>
       <c r="DP5" t="n">
-        <v>13.23</v>
+        <v>12.93</v>
       </c>
       <c r="DQ5" t="n">
-        <v>15.15</v>
+        <v>14.93</v>
       </c>
       <c r="DR5" t="n">
-        <v>5.85</v>
+        <v>5.86</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.15</v>
+        <v>0.22</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.15</v>
+        <v>0.22</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>55.61</v>
+        <v>56.28</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.31</v>
+        <v>0.28</v>
       </c>
       <c r="DX5" t="n">
-        <v>13.46</v>
+        <v>14.14</v>
       </c>
       <c r="DY5" t="n">
-        <v>8.69</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="DZ5" t="n">
-        <v>4.77</v>
+        <v>5</v>
       </c>
       <c r="EA5" t="n">
-        <v>19.08</v>
+        <v>18.64</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="EC5" t="n">
-        <v>2.77</v>
+        <v>2.79</v>
       </c>
     </row>
     <row r="6">
@@ -5006,13 +5006,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C11" t="n">
         <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -5096,139 +5096,139 @@
         <v>2</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AG11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>95.38</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>40.38</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>14.62</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>15.25</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>6.88</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>55.38</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>14.88</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>10.12</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>17.12</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="BN11" t="n">
         <v>1.71</v>
       </c>
-      <c r="AH11" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>93.43000000000001</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>3.43</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>4.14</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>40.71</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>15.57</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>16.14</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>6.14</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>53.71</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>14.57</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>10</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>4.57</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>16.57</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="BH11" t="n">
-        <v>9.619999999999999</v>
-      </c>
-      <c r="BI11" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="BJ11" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="BK11" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="BL11" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="BM11" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="BN11" t="n">
-        <v>1.77</v>
-      </c>
       <c r="BO11" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.46</v>
+        <v>4.21</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.08</v>
+        <v>5.07</v>
       </c>
       <c r="BR11" t="n">
-        <v>84.62</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BS11" t="n">
-        <v>84.62</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="BT11" t="n">
-        <v>61.54</v>
+        <v>57.14</v>
       </c>
       <c r="BU11" t="n">
-        <v>30.77</v>
+        <v>28.57</v>
       </c>
       <c r="BV11" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BW11" t="n">
         <v>0</v>
       </c>
       <c r="BX11" t="n">
-        <v>69.23</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="BY11" t="n">
         <v>2.14</v>
@@ -5237,169 +5237,169 @@
         <v>2.17</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.22</v>
+        <v>3.23</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.41</v>
+        <v>3.43</v>
       </c>
       <c r="CC11" t="n">
-        <v>3.83</v>
+        <v>3.72</v>
       </c>
       <c r="CD11" t="n">
-        <v>4.06</v>
+        <v>3.98</v>
       </c>
       <c r="CE11" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CF11" t="n">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="CG11" t="n">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="CH11" t="n">
         <v>1.35</v>
       </c>
       <c r="CI11" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="CJ11" t="n">
         <v>1.87</v>
       </c>
-      <c r="CJ11" t="n">
+      <c r="CK11" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="CL11" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="CM11" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="CN11" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="CO11" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="CP11" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="CQ11" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="CR11" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="CS11" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="CT11" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="CU11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="CV11" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="CW11" t="n">
         <v>1.89</v>
       </c>
-      <c r="CK11" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="CL11" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="CM11" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="CN11" t="n">
+      <c r="CX11" t="n">
         <v>1.69</v>
       </c>
-      <c r="CO11" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="CP11" t="n">
+      <c r="CY11" t="n">
         <v>2.11</v>
       </c>
-      <c r="CQ11" t="n">
-        <v>3.73</v>
-      </c>
-      <c r="CR11" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="CS11" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="CT11" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="CU11" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="CV11" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="CW11" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="CX11" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="CY11" t="n">
+      <c r="CZ11" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="DA11" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="DB11" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="DC11" t="n">
         <v>2.14</v>
       </c>
-      <c r="CZ11" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="DA11" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="DB11" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="DC11" t="n">
-        <v>2.17</v>
-      </c>
       <c r="DD11" t="n">
-        <v>3.91</v>
+        <v>3.84</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="DG11" t="n">
-        <v>3.23</v>
+        <v>3.15</v>
       </c>
       <c r="DH11" t="n">
-        <v>93.84999999999999</v>
+        <v>94.93000000000001</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.15</v>
+        <v>0.22</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.85</v>
+        <v>2.71</v>
       </c>
       <c r="DK11" t="n">
-        <v>5.08</v>
+        <v>4.86</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DM11" t="n">
-        <v>43.69</v>
+        <v>43.29</v>
       </c>
       <c r="DN11" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="DO11" t="n">
-        <v>1.84</v>
+        <v>1.71</v>
       </c>
       <c r="DP11" t="n">
-        <v>14.92</v>
+        <v>14.43</v>
       </c>
       <c r="DQ11" t="n">
-        <v>15.92</v>
+        <v>15.43</v>
       </c>
       <c r="DR11" t="n">
-        <v>7</v>
+        <v>7.36</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>55.61</v>
+        <v>56.43</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DX11" t="n">
-        <v>14.15</v>
+        <v>14.36</v>
       </c>
       <c r="DY11" t="n">
-        <v>9.390000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="DZ11" t="n">
-        <v>4.77</v>
+        <v>4.86</v>
       </c>
       <c r="EA11" t="n">
-        <v>17.23</v>
+        <v>17.5</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.61</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="12">
@@ -5409,13 +5409,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C12" t="n">
         <v>7</v>
       </c>
       <c r="D12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E12" t="n">
         <v>0.29</v>
@@ -5502,136 +5502,136 @@
         <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AH12" t="n">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AI12" t="n">
-        <v>91.5</v>
+        <v>90.29000000000001</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.67</v>
+        <v>3</v>
       </c>
       <c r="AL12" t="n">
-        <v>2</v>
+        <v>2.29</v>
       </c>
       <c r="AM12" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>35.57</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>13.86</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>15</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>9</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>45.57</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>10.14</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>6.71</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>22.57</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>8.789999999999999</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="BK12" t="n">
         <v>0.5</v>
       </c>
-      <c r="AN12" t="n">
-        <v>37</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>13.33</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>16.17</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>9.33</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>45</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>9.67</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>3.17</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>22.67</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="BH12" t="n">
-        <v>8.619999999999999</v>
-      </c>
-      <c r="BI12" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="BJ12" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="BK12" t="n">
-        <v>0.54</v>
-      </c>
       <c r="BL12" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.62</v>
+        <v>0.71</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="BP12" t="n">
-        <v>3.54</v>
+        <v>3.71</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.08</v>
+        <v>5.07</v>
       </c>
       <c r="BR12" t="n">
-        <v>76.92</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="BS12" t="n">
-        <v>69.23</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BT12" t="n">
-        <v>53.85</v>
+        <v>57.14</v>
       </c>
       <c r="BU12" t="n">
-        <v>30.77</v>
+        <v>35.71</v>
       </c>
       <c r="BV12" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BW12" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BX12" t="n">
-        <v>53.85</v>
+        <v>57.14</v>
       </c>
       <c r="BY12" t="n">
         <v>2.13</v>
@@ -5640,73 +5640,73 @@
         <v>2.32</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.24</v>
+        <v>3.3</v>
       </c>
       <c r="CC12" t="n">
-        <v>3.57</v>
+        <v>3.61</v>
       </c>
       <c r="CD12" t="n">
-        <v>3.98</v>
+        <v>4</v>
       </c>
       <c r="CE12" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CF12" t="n">
-        <v>3.24</v>
+        <v>3.18</v>
       </c>
       <c r="CG12" t="n">
-        <v>2.56</v>
+        <v>2.61</v>
       </c>
       <c r="CH12" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="CI12" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="CJ12" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="CK12" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="CL12" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="CM12" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="CN12" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="CO12" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="CP12" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="CQ12" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="CR12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="CS12" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="CT12" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="CU12" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="CV12" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="CW12" t="n">
         <v>1.99</v>
-      </c>
-      <c r="CK12" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="CL12" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="CM12" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="CN12" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="CO12" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="CP12" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="CQ12" t="n">
-        <v>4.12</v>
-      </c>
-      <c r="CR12" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="CS12" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="CT12" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="CU12" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="CV12" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="CW12" t="n">
-        <v>2.02</v>
       </c>
       <c r="CX12" t="n">
         <v>1.69</v>
@@ -5721,55 +5721,55 @@
         <v>1.72</v>
       </c>
       <c r="DB12" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="DC12" t="n">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="DD12" t="n">
-        <v>4.46</v>
+        <v>4.34</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="DH12" t="n">
-        <v>91.77</v>
+        <v>91.15000000000001</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.15</v>
+        <v>2.36</v>
       </c>
       <c r="DK12" t="n">
         <v>4.08</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="DM12" t="n">
-        <v>40.93</v>
+        <v>39.93</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.62</v>
+        <v>0.72</v>
       </c>
       <c r="DO12" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="DP12" t="n">
-        <v>13</v>
+        <v>13.28</v>
       </c>
       <c r="DQ12" t="n">
-        <v>15.92</v>
+        <v>15.36</v>
       </c>
       <c r="DR12" t="n">
-        <v>8.23</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="DS12" t="n">
         <v>0</v>
@@ -5781,28 +5781,28 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>48.54</v>
+        <v>48.57</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="DX12" t="n">
-        <v>12.16</v>
+        <v>12.22</v>
       </c>
       <c r="DY12" t="n">
-        <v>8.85</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="DZ12" t="n">
-        <v>3.31</v>
+        <v>3.43</v>
       </c>
       <c r="EA12" t="n">
-        <v>22.47</v>
+        <v>22.43</v>
       </c>
       <c r="EB12" t="n">
         <v>1.3</v>
       </c>
       <c r="EC12" t="n">
-        <v>1.77</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -7021,94 +7021,94 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D16" t="n">
         <v>6</v>
       </c>
       <c r="E16" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="F16" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="G16" t="n">
-        <v>4.71</v>
+        <v>4.38</v>
       </c>
       <c r="H16" t="n">
-        <v>105.86</v>
+        <v>102.25</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>2.29</v>
+        <v>2.5</v>
       </c>
       <c r="K16" t="n">
-        <v>8</v>
+        <v>7.88</v>
       </c>
       <c r="L16" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="M16" t="n">
-        <v>51.14</v>
+        <v>49.88</v>
       </c>
       <c r="N16" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="O16" t="n">
-        <v>3.29</v>
+        <v>3.5</v>
       </c>
       <c r="P16" t="n">
-        <v>13</v>
+        <v>12.38</v>
       </c>
       <c r="Q16" t="n">
-        <v>13.71</v>
+        <v>14.12</v>
       </c>
       <c r="R16" t="n">
-        <v>7</v>
+        <v>7.38</v>
       </c>
       <c r="S16" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="T16" t="n">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="U16" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="V16" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>55.86</v>
+        <v>55.25</v>
       </c>
       <c r="Y16" t="n">
         <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>16.43</v>
+        <v>16</v>
       </c>
       <c r="AA16" t="n">
-        <v>10.29</v>
+        <v>10</v>
       </c>
       <c r="AB16" t="n">
-        <v>6.14</v>
+        <v>6</v>
       </c>
       <c r="AC16" t="n">
-        <v>19.14</v>
+        <v>19</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.84</v>
+        <v>1.79</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.29</v>
+        <v>2.5</v>
       </c>
       <c r="AF16" t="n">
         <v>0</v>
@@ -7192,70 +7192,70 @@
         <v>2.83</v>
       </c>
       <c r="BG16" t="n">
-        <v>3.85</v>
+        <v>3.86</v>
       </c>
       <c r="BH16" t="n">
-        <v>11.69</v>
+        <v>11.64</v>
       </c>
       <c r="BI16" t="n">
-        <v>3.85</v>
+        <v>3.86</v>
       </c>
       <c r="BJ16" t="n">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="BL16" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="BM16" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="BN16" t="n">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="BP16" t="n">
-        <v>5.85</v>
+        <v>5.86</v>
       </c>
       <c r="BQ16" t="n">
-        <v>5.85</v>
+        <v>5.79</v>
       </c>
       <c r="BR16" t="n">
         <v>100</v>
       </c>
       <c r="BS16" t="n">
-        <v>92.31</v>
+        <v>92.86</v>
       </c>
       <c r="BT16" t="n">
-        <v>92.31</v>
+        <v>92.86</v>
       </c>
       <c r="BU16" t="n">
-        <v>61.54</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="BV16" t="n">
-        <v>30.77</v>
+        <v>28.57</v>
       </c>
       <c r="BW16" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BX16" t="n">
-        <v>84.62</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BY16" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="BZ16" t="n">
         <v>1.81</v>
       </c>
       <c r="CA16" t="n">
-        <v>3.7</v>
+        <v>3.71</v>
       </c>
       <c r="CB16" t="n">
-        <v>3.87</v>
+        <v>3.88</v>
       </c>
       <c r="CC16" t="n">
         <v>3.18</v>
@@ -7270,7 +7270,7 @@
         <v>2.43</v>
       </c>
       <c r="CG16" t="n">
-        <v>3.11</v>
+        <v>3.12</v>
       </c>
       <c r="CH16" t="n">
         <v>1.49</v>
@@ -7282,7 +7282,7 @@
         <v>1.64</v>
       </c>
       <c r="CK16" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CL16" t="n">
         <v>1.87</v>
@@ -7303,7 +7303,7 @@
         <v>2.66</v>
       </c>
       <c r="CR16" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CS16" t="n">
         <v>2.6</v>
@@ -7342,79 +7342,79 @@
         <v>2.76</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="DG16" t="n">
-        <v>3.77</v>
+        <v>3.65</v>
       </c>
       <c r="DH16" t="n">
-        <v>99</v>
+        <v>97.43000000000001</v>
       </c>
       <c r="DI16" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="DJ16" t="n">
-        <v>2.77</v>
+        <v>2.86</v>
       </c>
       <c r="DK16" t="n">
-        <v>6.54</v>
+        <v>6.57</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="DM16" t="n">
-        <v>44</v>
+        <v>43.79</v>
       </c>
       <c r="DN16" t="n">
         <v>0.92</v>
       </c>
       <c r="DO16" t="n">
-        <v>2.77</v>
+        <v>2.93</v>
       </c>
       <c r="DP16" t="n">
-        <v>13.31</v>
+        <v>12.93</v>
       </c>
       <c r="DQ16" t="n">
-        <v>14.92</v>
+        <v>15.07</v>
       </c>
       <c r="DR16" t="n">
-        <v>7.54</v>
+        <v>7.72</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>53.39</v>
+        <v>53.21</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DX16" t="n">
-        <v>14.31</v>
+        <v>14.21</v>
       </c>
       <c r="DY16" t="n">
-        <v>8.619999999999999</v>
+        <v>8.57</v>
       </c>
       <c r="DZ16" t="n">
-        <v>5.69</v>
+        <v>5.64</v>
       </c>
       <c r="EA16" t="n">
         <v>18</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="EC16" t="n">
-        <v>2.54</v>
+        <v>2.64</v>
       </c>
     </row>
     <row r="17">
@@ -7424,13 +7424,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C17" t="n">
         <v>7</v>
       </c>
       <c r="D17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E17" t="n">
         <v>0.14</v>
@@ -7517,136 +7517,136 @@
         <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.67</v>
+        <v>2.43</v>
       </c>
       <c r="AI17" t="n">
-        <v>90.17</v>
+        <v>87</v>
       </c>
       <c r="AJ17" t="n">
         <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>3</v>
+        <v>2.71</v>
       </c>
       <c r="AL17" t="n">
-        <v>3.83</v>
+        <v>3.43</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AN17" t="n">
-        <v>28.33</v>
+        <v>27.14</v>
       </c>
       <c r="AO17" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AQ17" t="n">
-        <v>17.17</v>
+        <v>16.57</v>
       </c>
       <c r="AR17" t="n">
-        <v>14.17</v>
+        <v>13.43</v>
       </c>
       <c r="AS17" t="n">
+        <v>8.710000000000001</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>43.86</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>11.29</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>6.86</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>4.43</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>23.43</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="BH17" t="n">
         <v>9</v>
       </c>
-      <c r="AT17" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>45.33</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>10</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>6.33</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>3.67</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>22.67</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>3</v>
-      </c>
-      <c r="BG17" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="BH17" t="n">
-        <v>8.539999999999999</v>
-      </c>
       <c r="BI17" t="n">
-        <v>2.85</v>
+        <v>3.29</v>
       </c>
       <c r="BJ17" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.31</v>
+        <v>0.36</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.85</v>
+        <v>1.07</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.54</v>
+        <v>0.71</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.38</v>
+        <v>1.79</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="BP17" t="n">
-        <v>3.92</v>
+        <v>4.29</v>
       </c>
       <c r="BQ17" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="BR17" t="n">
         <v>100</v>
       </c>
       <c r="BS17" t="n">
-        <v>69.23</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BT17" t="n">
-        <v>53.85</v>
+        <v>57.14</v>
       </c>
       <c r="BU17" t="n">
-        <v>23.08</v>
+        <v>28.57</v>
       </c>
       <c r="BV17" t="n">
-        <v>15.38</v>
+        <v>21.43</v>
       </c>
       <c r="BW17" t="n">
-        <v>15.38</v>
+        <v>21.43</v>
       </c>
       <c r="BX17" t="n">
-        <v>53.85</v>
+        <v>57.14</v>
       </c>
       <c r="BY17" t="n">
         <v>3.21</v>
@@ -7655,28 +7655,28 @@
         <v>3.5</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.37</v>
+        <v>3.5</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.6</v>
+        <v>3.74</v>
       </c>
       <c r="CC17" t="n">
-        <v>5.12</v>
+        <v>5.67</v>
       </c>
       <c r="CD17" t="n">
-        <v>6.4</v>
+        <v>6.87</v>
       </c>
       <c r="CE17" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="CF17" t="n">
-        <v>3.1</v>
+        <v>3.04</v>
       </c>
       <c r="CG17" t="n">
-        <v>2.69</v>
+        <v>2.73</v>
       </c>
       <c r="CH17" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="CI17" t="n">
         <v>1.81</v>
@@ -7685,37 +7685,37 @@
         <v>1.96</v>
       </c>
       <c r="CK17" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CL17" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="CN17" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CO17" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="CP17" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="CQ17" t="n">
-        <v>3.73</v>
+        <v>3.65</v>
       </c>
       <c r="CR17" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CS17" t="n">
-        <v>3.11</v>
+        <v>3.05</v>
       </c>
       <c r="CT17" t="n">
-        <v>2.73</v>
+        <v>2.78</v>
       </c>
       <c r="CU17" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="CV17" t="n">
         <v>1.86</v>
@@ -7724,100 +7724,100 @@
         <v>2.02</v>
       </c>
       <c r="CX17" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CY17" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="CZ17" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="DA17" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="DB17" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="DC17" t="n">
-        <v>2.23</v>
+        <v>2.19</v>
       </c>
       <c r="DD17" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.92</v>
+        <v>1.78</v>
       </c>
       <c r="DG17" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="DH17" t="n">
-        <v>83.62</v>
+        <v>82.5</v>
       </c>
       <c r="DI17" t="n">
         <v>0</v>
       </c>
       <c r="DJ17" t="n">
-        <v>3.08</v>
+        <v>2.92</v>
       </c>
       <c r="DK17" t="n">
-        <v>3.31</v>
+        <v>3.14</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DM17" t="n">
-        <v>30.07</v>
+        <v>29.36</v>
       </c>
       <c r="DN17" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="DO17" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="DP17" t="n">
-        <v>18.77</v>
+        <v>18.36</v>
       </c>
       <c r="DQ17" t="n">
-        <v>13.92</v>
+        <v>13.57</v>
       </c>
       <c r="DR17" t="n">
-        <v>8.539999999999999</v>
+        <v>8.43</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>44.69</v>
+        <v>44</v>
       </c>
       <c r="DW17" t="n">
         <v>0</v>
       </c>
       <c r="DX17" t="n">
-        <v>10.16</v>
+        <v>10.79</v>
       </c>
       <c r="DY17" t="n">
-        <v>6.38</v>
+        <v>6.64</v>
       </c>
       <c r="DZ17" t="n">
-        <v>3.77</v>
+        <v>4.15</v>
       </c>
       <c r="EA17" t="n">
-        <v>21.46</v>
+        <v>21.93</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="EC17" t="n">
-        <v>3.08</v>
+        <v>2.92</v>
       </c>
     </row>
     <row r="18">
@@ -7827,10 +7827,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C18" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D18" t="n">
         <v>6</v>
@@ -7839,82 +7839,82 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="G18" t="n">
-        <v>4.43</v>
+        <v>4.75</v>
       </c>
       <c r="H18" t="n">
-        <v>118.86</v>
+        <v>119.12</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="K18" t="n">
-        <v>6.43</v>
+        <v>6.88</v>
       </c>
       <c r="L18" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="M18" t="n">
-        <v>69.86</v>
+        <v>69.62</v>
       </c>
       <c r="N18" t="n">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="O18" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="P18" t="n">
-        <v>17</v>
+        <v>17.75</v>
       </c>
       <c r="Q18" t="n">
-        <v>13.14</v>
+        <v>13</v>
       </c>
       <c r="R18" t="n">
-        <v>5.57</v>
+        <v>5.62</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
       </c>
       <c r="T18" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="U18" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="V18" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>55.71</v>
+        <v>55.88</v>
       </c>
       <c r="Y18" t="n">
         <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>16.14</v>
+        <v>16.88</v>
       </c>
       <c r="AA18" t="n">
-        <v>10.43</v>
+        <v>11.38</v>
       </c>
       <c r="AB18" t="n">
-        <v>5.71</v>
+        <v>5.5</v>
       </c>
       <c r="AC18" t="n">
-        <v>29.57</v>
+        <v>28.25</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="AF18" t="n">
         <v>0</v>
@@ -7998,70 +7998,70 @@
         <v>3.33</v>
       </c>
       <c r="BG18" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="BH18" t="n">
-        <v>8.539999999999999</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="BI18" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="BL18" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="BO18" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="BP18" t="n">
-        <v>3.31</v>
+        <v>3.29</v>
       </c>
       <c r="BQ18" t="n">
-        <v>5.23</v>
+        <v>5.43</v>
       </c>
       <c r="BR18" t="n">
-        <v>84.62</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BS18" t="n">
-        <v>61.54</v>
+        <v>57.14</v>
       </c>
       <c r="BT18" t="n">
-        <v>30.77</v>
+        <v>28.57</v>
       </c>
       <c r="BU18" t="n">
-        <v>15.38</v>
+        <v>14.29</v>
       </c>
       <c r="BV18" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BW18" t="n">
         <v>0</v>
       </c>
       <c r="BX18" t="n">
-        <v>46.15</v>
+        <v>42.86</v>
       </c>
       <c r="BY18" t="n">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="BZ18" t="n">
-        <v>1.93</v>
+        <v>2.01</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.33</v>
+        <v>3.3</v>
       </c>
       <c r="CB18" t="n">
-        <v>3.44</v>
+        <v>3.41</v>
       </c>
       <c r="CC18" t="n">
         <v>2.88</v>
@@ -8073,154 +8073,154 @@
         <v>1.41</v>
       </c>
       <c r="CF18" t="n">
-        <v>2.94</v>
+        <v>2.95</v>
       </c>
       <c r="CG18" t="n">
-        <v>2.76</v>
+        <v>2.73</v>
       </c>
       <c r="CH18" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CI18" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CJ18" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CK18" t="n">
         <v>1.62</v>
       </c>
       <c r="CL18" t="n">
-        <v>2.08</v>
+        <v>2.13</v>
       </c>
       <c r="CM18" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="CN18" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="CO18" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="CP18" t="n">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="CQ18" t="n">
-        <v>3.72</v>
+        <v>3.79</v>
       </c>
       <c r="CR18" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="CS18" t="n">
         <v>3.09</v>
       </c>
       <c r="CT18" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="CU18" t="n">
         <v>1.4</v>
       </c>
       <c r="CV18" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="CW18" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CX18" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="CY18" t="n">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="CZ18" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="DA18" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="DB18" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="DC18" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="DD18" t="n">
-        <v>3.9</v>
+        <v>3.99</v>
       </c>
       <c r="DE18" t="n">
         <v>0</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="DG18" t="n">
-        <v>3.62</v>
+        <v>3.86</v>
       </c>
       <c r="DH18" t="n">
-        <v>113.46</v>
+        <v>114</v>
       </c>
       <c r="DI18" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DJ18" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="DK18" t="n">
-        <v>6</v>
+        <v>6.29</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="DM18" t="n">
-        <v>57.62</v>
+        <v>58.35</v>
       </c>
       <c r="DN18" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="DO18" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="DP18" t="n">
-        <v>17.92</v>
+        <v>18.29</v>
       </c>
       <c r="DQ18" t="n">
-        <v>13.77</v>
+        <v>13.64</v>
       </c>
       <c r="DR18" t="n">
-        <v>6.92</v>
+        <v>6.85</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DT18" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DU18" t="n">
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>53.15</v>
+        <v>53.43</v>
       </c>
       <c r="DW18" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DX18" t="n">
-        <v>14.23</v>
+        <v>14.79</v>
       </c>
       <c r="DY18" t="n">
-        <v>9.460000000000001</v>
+        <v>10.07</v>
       </c>
       <c r="DZ18" t="n">
-        <v>4.77</v>
+        <v>4.72</v>
       </c>
       <c r="EA18" t="n">
-        <v>26.23</v>
+        <v>25.71</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="EC18" t="n">
-        <v>2.77</v>
+        <v>2.79</v>
       </c>
     </row>
     <row r="19">
@@ -9842,13 +9842,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C23" t="n">
         <v>7</v>
       </c>
       <c r="D23" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E23" t="n">
         <v>0.14</v>
@@ -9935,49 +9935,49 @@
         <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AH23" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AI23" t="n">
-        <v>91.5</v>
+        <v>89.14</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AK23" t="n">
         <v>2</v>
       </c>
       <c r="AL23" t="n">
-        <v>4.33</v>
+        <v>3.86</v>
       </c>
       <c r="AM23" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AN23" t="n">
-        <v>36.67</v>
+        <v>33.43</v>
       </c>
       <c r="AO23" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="AP23" t="n">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="AQ23" t="n">
-        <v>12.33</v>
+        <v>12.29</v>
       </c>
       <c r="AR23" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AS23" t="n">
-        <v>8.17</v>
+        <v>9</v>
       </c>
       <c r="AT23" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AU23" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="AV23" t="n">
         <v>0</v>
@@ -9989,22 +9989,22 @@
         <v>0</v>
       </c>
       <c r="AY23" t="n">
-        <v>59.67</v>
+        <v>57.29</v>
       </c>
       <c r="AZ23" t="n">
         <v>0</v>
       </c>
       <c r="BA23" t="n">
-        <v>10</v>
+        <v>10.14</v>
       </c>
       <c r="BB23" t="n">
-        <v>7.17</v>
+        <v>7.14</v>
       </c>
       <c r="BC23" t="n">
-        <v>2.83</v>
+        <v>3</v>
       </c>
       <c r="BD23" t="n">
-        <v>18.17</v>
+        <v>17.43</v>
       </c>
       <c r="BE23" t="n">
         <v>1.1</v>
@@ -10013,49 +10013,49 @@
         <v>2</v>
       </c>
       <c r="BG23" t="n">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="BH23" t="n">
-        <v>7.62</v>
+        <v>7.86</v>
       </c>
       <c r="BI23" t="n">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="BJ23" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="BK23" t="n">
-        <v>0.31</v>
+        <v>0.36</v>
       </c>
       <c r="BL23" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="BM23" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="BN23" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="BO23" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="BP23" t="n">
-        <v>3.62</v>
+        <v>3.57</v>
       </c>
       <c r="BQ23" t="n">
-        <v>4</v>
+        <v>4.29</v>
       </c>
       <c r="BR23" t="n">
-        <v>76.92</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="BS23" t="n">
-        <v>46.15</v>
+        <v>42.86</v>
       </c>
       <c r="BT23" t="n">
-        <v>30.77</v>
+        <v>28.57</v>
       </c>
       <c r="BU23" t="n">
-        <v>23.08</v>
+        <v>21.43</v>
       </c>
       <c r="BV23" t="n">
         <v>0</v>
@@ -10064,7 +10064,7 @@
         <v>0</v>
       </c>
       <c r="BX23" t="n">
-        <v>46.15</v>
+        <v>42.86</v>
       </c>
       <c r="BY23" t="n">
         <v>1.85</v>
@@ -10073,16 +10073,16 @@
         <v>1.92</v>
       </c>
       <c r="CA23" t="n">
-        <v>3.19</v>
+        <v>3.16</v>
       </c>
       <c r="CB23" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="CC23" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="CD23" t="n">
         <v>3.32</v>
-      </c>
-      <c r="CC23" t="n">
-        <v>3.06</v>
-      </c>
-      <c r="CD23" t="n">
-        <v>3.33</v>
       </c>
       <c r="CE23" t="n">
         <v>1.47</v>
@@ -10091,46 +10091,46 @@
         <v>3.24</v>
       </c>
       <c r="CG23" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="CH23" t="n">
         <v>1.32</v>
       </c>
       <c r="CI23" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CJ23" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="CK23" t="n">
         <v>1.69</v>
       </c>
       <c r="CL23" t="n">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
       <c r="CM23" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CN23" t="n">
         <v>1.67</v>
       </c>
       <c r="CO23" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CP23" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="CQ23" t="n">
-        <v>4.19</v>
+        <v>4.23</v>
       </c>
       <c r="CR23" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="CS23" t="n">
         <v>3.18</v>
       </c>
       <c r="CT23" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="CU23" t="n">
         <v>1.37</v>
@@ -10142,67 +10142,67 @@
         <v>2.06</v>
       </c>
       <c r="CX23" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CY23" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="CZ23" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="DA23" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="DB23" t="n">
         <v>1.45</v>
       </c>
       <c r="DC23" t="n">
-        <v>2.41</v>
+        <v>2.43</v>
       </c>
       <c r="DD23" t="n">
-        <v>4.58</v>
+        <v>4.63</v>
       </c>
       <c r="DE23" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DF23" t="n">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
       <c r="DG23" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="DH23" t="n">
-        <v>95.84999999999999</v>
+        <v>94.36</v>
       </c>
       <c r="DI23" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DJ23" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="DK23" t="n">
-        <v>4.23</v>
+        <v>4</v>
       </c>
       <c r="DL23" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DM23" t="n">
-        <v>38.62</v>
+        <v>36.86</v>
       </c>
       <c r="DN23" t="n">
-        <v>0.39</v>
+        <v>0.43</v>
       </c>
       <c r="DO23" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="DP23" t="n">
-        <v>13</v>
+        <v>12.93</v>
       </c>
       <c r="DQ23" t="n">
-        <v>18.23</v>
+        <v>18.57</v>
       </c>
       <c r="DR23" t="n">
-        <v>7.08</v>
+        <v>7.57</v>
       </c>
       <c r="DS23" t="n">
         <v>0</v>
@@ -10214,28 +10214,28 @@
         <v>0</v>
       </c>
       <c r="DV23" t="n">
-        <v>57.46</v>
+        <v>56.43</v>
       </c>
       <c r="DW23" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DX23" t="n">
-        <v>11.54</v>
+        <v>11.5</v>
       </c>
       <c r="DY23" t="n">
-        <v>7.69</v>
+        <v>7.64</v>
       </c>
       <c r="DZ23" t="n">
-        <v>3.84</v>
+        <v>3.86</v>
       </c>
       <c r="EA23" t="n">
-        <v>18.92</v>
+        <v>18.5</v>
       </c>
       <c r="EB23" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="EC23" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Spain_Segunda_División_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Spain_Segunda_División_2025-2026.xlsx
@@ -1782,94 +1782,94 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D3" t="n">
         <v>6</v>
       </c>
       <c r="E3" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="F3" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="G3" t="n">
-        <v>3.17</v>
+        <v>3.57</v>
       </c>
       <c r="H3" t="n">
-        <v>97.5</v>
+        <v>95.86</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="K3" t="n">
-        <v>7.33</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="L3" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="M3" t="n">
-        <v>51.17</v>
+        <v>51.29</v>
       </c>
       <c r="N3" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="O3" t="n">
-        <v>4</v>
+        <v>4.43</v>
       </c>
       <c r="P3" t="n">
-        <v>13.83</v>
+        <v>13.71</v>
       </c>
       <c r="Q3" t="n">
-        <v>10.33</v>
+        <v>10.29</v>
       </c>
       <c r="R3" t="n">
-        <v>8</v>
+        <v>7.57</v>
       </c>
       <c r="S3" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="T3" t="n">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="U3" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="V3" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>54.17</v>
+        <v>54.86</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="Z3" t="n">
-        <v>19.67</v>
+        <v>19.14</v>
       </c>
       <c r="AA3" t="n">
-        <v>11.67</v>
+        <v>11</v>
       </c>
       <c r="AB3" t="n">
-        <v>8</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="AC3" t="n">
-        <v>16.83</v>
+        <v>16.71</v>
       </c>
       <c r="AD3" t="n">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.33</v>
+        <v>2.43</v>
       </c>
       <c r="AF3" t="n">
         <v>0</v>
@@ -1953,70 +1953,70 @@
         <v>3.17</v>
       </c>
       <c r="BG3" t="n">
-        <v>3.42</v>
+        <v>3.38</v>
       </c>
       <c r="BH3" t="n">
-        <v>9.5</v>
+        <v>10.15</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.42</v>
+        <v>3.38</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="BL3" t="n">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="BM3" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="BN3" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="BP3" t="n">
-        <v>4.17</v>
+        <v>4.62</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5.25</v>
+        <v>5.46</v>
       </c>
       <c r="BR3" t="n">
         <v>100</v>
       </c>
       <c r="BS3" t="n">
-        <v>75</v>
+        <v>76.92</v>
       </c>
       <c r="BT3" t="n">
-        <v>58.33</v>
+        <v>61.54</v>
       </c>
       <c r="BU3" t="n">
-        <v>50</v>
+        <v>46.15</v>
       </c>
       <c r="BV3" t="n">
-        <v>25</v>
+        <v>23.08</v>
       </c>
       <c r="BW3" t="n">
-        <v>16.67</v>
+        <v>15.38</v>
       </c>
       <c r="BX3" t="n">
-        <v>75</v>
+        <v>69.23</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="BZ3" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.49</v>
+        <v>3.51</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.69</v>
+        <v>3.72</v>
       </c>
       <c r="CC3" t="n">
         <v>2.68</v>
@@ -2037,31 +2037,31 @@
         <v>1.46</v>
       </c>
       <c r="CI3" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="CJ3" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="CL3" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CO3" t="n">
         <v>1.23</v>
       </c>
       <c r="CP3" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CQ3" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="CR3" t="n">
         <v>1.38</v>
@@ -2070,16 +2070,16 @@
         <v>2.81</v>
       </c>
       <c r="CT3" t="n">
-        <v>3.15</v>
+        <v>3.16</v>
       </c>
       <c r="CU3" t="n">
         <v>1.47</v>
       </c>
       <c r="CV3" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="CW3" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CX3" t="n">
         <v>1.54</v>
@@ -2088,7 +2088,7 @@
         <v>1.9</v>
       </c>
       <c r="CZ3" t="n">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="DA3" t="n">
         <v>1.91</v>
@@ -2106,13 +2106,13 @@
         <v>0.08</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="DG3" t="n">
-        <v>2.67</v>
+        <v>2.92</v>
       </c>
       <c r="DH3" t="n">
-        <v>100</v>
+        <v>98.92</v>
       </c>
       <c r="DI3" t="n">
         <v>0</v>
@@ -2121,61 +2121,61 @@
         <v>3</v>
       </c>
       <c r="DK3" t="n">
-        <v>5.42</v>
+        <v>6</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.34</v>
+        <v>0.31</v>
       </c>
       <c r="DM3" t="n">
-        <v>46.84</v>
+        <v>47.23</v>
       </c>
       <c r="DN3" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="DO3" t="n">
-        <v>2.66</v>
+        <v>3</v>
       </c>
       <c r="DP3" t="n">
-        <v>13.83</v>
+        <v>13.77</v>
       </c>
       <c r="DQ3" t="n">
-        <v>13.08</v>
+        <v>12.85</v>
       </c>
       <c r="DR3" t="n">
-        <v>7.75</v>
+        <v>7.54</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>53.67</v>
+        <v>54.08</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="DX3" t="n">
-        <v>16.42</v>
+        <v>16.38</v>
       </c>
       <c r="DY3" t="n">
-        <v>10.75</v>
+        <v>10.46</v>
       </c>
       <c r="DZ3" t="n">
-        <v>5.66</v>
+        <v>5.92</v>
       </c>
       <c r="EA3" t="n">
-        <v>19</v>
+        <v>18.77</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
     </row>
     <row r="4">
@@ -2185,13 +2185,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C4" t="n">
         <v>7</v>
       </c>
       <c r="D4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E4" t="n">
         <v>0.14</v>
@@ -2275,139 +2275,139 @@
         <v>3</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AI4" t="n">
-        <v>88.33</v>
+        <v>85.14</v>
       </c>
       <c r="AJ4" t="n">
         <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="AL4" t="n">
-        <v>3.83</v>
+        <v>3.86</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AN4" t="n">
-        <v>40.5</v>
+        <v>39.43</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="AP4" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ4" t="n">
-        <v>14</v>
+        <v>13.71</v>
       </c>
       <c r="AR4" t="n">
-        <v>12.5</v>
+        <v>13.57</v>
       </c>
       <c r="AS4" t="n">
-        <v>9.17</v>
+        <v>9.43</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="AX4" t="n">
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>45.33</v>
+        <v>46.14</v>
       </c>
       <c r="AZ4" t="n">
         <v>0</v>
       </c>
       <c r="BA4" t="n">
-        <v>9.33</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="BB4" t="n">
-        <v>6.33</v>
+        <v>5.71</v>
       </c>
       <c r="BC4" t="n">
-        <v>3</v>
+        <v>3.14</v>
       </c>
       <c r="BD4" t="n">
-        <v>23.33</v>
+        <v>22.43</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="BF4" t="n">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="BH4" t="n">
-        <v>7.46</v>
+        <v>7.71</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.54</v>
+        <v>0.64</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="BP4" t="n">
-        <v>3.77</v>
+        <v>3.86</v>
       </c>
       <c r="BQ4" t="n">
-        <v>3.69</v>
+        <v>3.86</v>
       </c>
       <c r="BR4" t="n">
-        <v>76.92</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="BS4" t="n">
-        <v>61.54</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="BT4" t="n">
-        <v>53.85</v>
+        <v>50</v>
       </c>
       <c r="BU4" t="n">
-        <v>23.08</v>
+        <v>21.43</v>
       </c>
       <c r="BV4" t="n">
-        <v>15.38</v>
+        <v>14.29</v>
       </c>
       <c r="BW4" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BX4" t="n">
-        <v>61.54</v>
+        <v>57.14</v>
       </c>
       <c r="BY4" t="n">
         <v>2.28</v>
@@ -2419,19 +2419,19 @@
         <v>3.01</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.1</v>
+        <v>3.09</v>
       </c>
       <c r="CC4" t="n">
-        <v>3.77</v>
+        <v>3.58</v>
       </c>
       <c r="CD4" t="n">
-        <v>4.14</v>
+        <v>3.91</v>
       </c>
       <c r="CE4" t="n">
         <v>1.55</v>
       </c>
       <c r="CF4" t="n">
-        <v>3.48</v>
+        <v>3.49</v>
       </c>
       <c r="CG4" t="n">
         <v>2.36</v>
@@ -2446,16 +2446,16 @@
         <v>2.16</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CL4" t="n">
         <v>2.4</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CO4" t="n">
         <v>1.5</v>
@@ -2464,7 +2464,7 @@
         <v>2.54</v>
       </c>
       <c r="CQ4" t="n">
-        <v>4.85</v>
+        <v>4.9</v>
       </c>
       <c r="CR4" t="n">
         <v>1.6</v>
@@ -2473,7 +2473,7 @@
         <v>3.39</v>
       </c>
       <c r="CT4" t="n">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="CU4" t="n">
         <v>1.33</v>
@@ -2482,7 +2482,7 @@
         <v>1.68</v>
       </c>
       <c r="CW4" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="CX4" t="n">
         <v>1.8</v>
@@ -2497,88 +2497,88 @@
         <v>1.61</v>
       </c>
       <c r="DB4" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="DC4" t="n">
-        <v>2.73</v>
+        <v>2.74</v>
       </c>
       <c r="DD4" t="n">
-        <v>5.47</v>
+        <v>5.53</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="DG4" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="DH4" t="n">
-        <v>90.61</v>
+        <v>88.86</v>
       </c>
       <c r="DI4" t="n">
         <v>0</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.77</v>
+        <v>2.64</v>
       </c>
       <c r="DK4" t="n">
-        <v>3.61</v>
+        <v>3.64</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DM4" t="n">
-        <v>42.92</v>
+        <v>42.22</v>
       </c>
       <c r="DN4" t="n">
         <v>1.08</v>
       </c>
       <c r="DO4" t="n">
-        <v>1.84</v>
+        <v>1.78</v>
       </c>
       <c r="DP4" t="n">
-        <v>13.69</v>
+        <v>13.57</v>
       </c>
       <c r="DQ4" t="n">
-        <v>13.61</v>
+        <v>14.07</v>
       </c>
       <c r="DR4" t="n">
-        <v>8.619999999999999</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.38</v>
+        <v>0.43</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.38</v>
+        <v>0.43</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>47.46</v>
+        <v>47.72</v>
       </c>
       <c r="DW4" t="n">
         <v>0</v>
       </c>
       <c r="DX4" t="n">
-        <v>10</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="DY4" t="n">
-        <v>6.92</v>
+        <v>6.57</v>
       </c>
       <c r="DZ4" t="n">
-        <v>3.08</v>
+        <v>3.14</v>
       </c>
       <c r="EA4" t="n">
-        <v>25</v>
+        <v>24.43</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.77</v>
+        <v>2.64</v>
       </c>
     </row>
     <row r="5">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D6" t="n">
         <v>7</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="F6" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>3.6</v>
+        <v>3.67</v>
       </c>
       <c r="H6" t="n">
-        <v>109.2</v>
+        <v>109.83</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="J6" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="K6" t="n">
-        <v>5.8</v>
+        <v>5.83</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="M6" t="n">
-        <v>59</v>
+        <v>61.5</v>
       </c>
       <c r="N6" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="O6" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="P6" t="n">
-        <v>13.8</v>
+        <v>14</v>
       </c>
       <c r="Q6" t="n">
-        <v>12.6</v>
+        <v>13.33</v>
       </c>
       <c r="R6" t="n">
-        <v>5.2</v>
+        <v>5.17</v>
       </c>
       <c r="S6" t="n">
-        <v>0.4</v>
+        <v>0.67</v>
       </c>
       <c r="T6" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -3057,28 +3057,28 @@
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>57.2</v>
+        <v>58</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>11.4</v>
+        <v>11.67</v>
       </c>
       <c r="AA6" t="n">
-        <v>7</v>
+        <v>7.83</v>
       </c>
       <c r="AB6" t="n">
-        <v>4.4</v>
+        <v>3.83</v>
       </c>
       <c r="AC6" t="n">
-        <v>21.6</v>
+        <v>21.33</v>
       </c>
       <c r="AD6" t="n">
         <v>1.46</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AF6" t="n">
         <v>0.14</v>
@@ -3162,70 +3162,70 @@
         <v>2.43</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="BH6" t="n">
         <v>8.92</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="BJ6" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
       <c r="BN6" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="BP6" t="n">
-        <v>3.5</v>
+        <v>3.54</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.42</v>
+        <v>5.38</v>
       </c>
       <c r="BR6" t="n">
-        <v>83.33</v>
+        <v>84.62</v>
       </c>
       <c r="BS6" t="n">
-        <v>50</v>
+        <v>53.85</v>
       </c>
       <c r="BT6" t="n">
-        <v>33.33</v>
+        <v>38.46</v>
       </c>
       <c r="BU6" t="n">
-        <v>16.67</v>
+        <v>15.38</v>
       </c>
       <c r="BV6" t="n">
-        <v>16.67</v>
+        <v>15.38</v>
       </c>
       <c r="BW6" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BX6" t="n">
-        <v>25</v>
+        <v>30.77</v>
       </c>
       <c r="BY6" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="BZ6" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.29</v>
+        <v>3.27</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.42</v>
+        <v>3.38</v>
       </c>
       <c r="CC6" t="n">
         <v>4.22</v>
@@ -3234,13 +3234,13 @@
         <v>4.63</v>
       </c>
       <c r="CE6" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="CG6" t="n">
-        <v>2.65</v>
+        <v>2.64</v>
       </c>
       <c r="CH6" t="n">
         <v>1.36</v>
@@ -3255,10 +3255,10 @@
         <v>1.64</v>
       </c>
       <c r="CL6" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="CN6" t="n">
         <v>1.67</v>
@@ -3267,10 +3267,10 @@
         <v>1.36</v>
       </c>
       <c r="CP6" t="n">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="CQ6" t="n">
-        <v>3.88</v>
+        <v>3.9</v>
       </c>
       <c r="CR6" t="n">
         <v>1.46</v>
@@ -3285,106 +3285,106 @@
         <v>1.4</v>
       </c>
       <c r="CV6" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="CW6" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CX6" t="n">
         <v>1.67</v>
       </c>
       <c r="CY6" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="CZ6" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="DA6" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="DB6" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="DC6" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="DD6" t="n">
-        <v>3.89</v>
+        <v>3.99</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.59</v>
+        <v>1.46</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.33</v>
+        <v>2.46</v>
       </c>
       <c r="DH6" t="n">
-        <v>93.42</v>
+        <v>94.92</v>
       </c>
       <c r="DI6" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.75</v>
+        <v>2.69</v>
       </c>
       <c r="DK6" t="n">
-        <v>4.25</v>
+        <v>4.38</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="DM6" t="n">
-        <v>44.17</v>
+        <v>46.46</v>
       </c>
       <c r="DN6" t="n">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="DO6" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="DP6" t="n">
-        <v>13.33</v>
+        <v>13.46</v>
       </c>
       <c r="DQ6" t="n">
-        <v>13.34</v>
+        <v>13.62</v>
       </c>
       <c r="DR6" t="n">
-        <v>7.59</v>
+        <v>7.39</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>51.33</v>
+        <v>52.15</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DX6" t="n">
-        <v>9.5</v>
+        <v>9.77</v>
       </c>
       <c r="DY6" t="n">
-        <v>6.59</v>
+        <v>7</v>
       </c>
       <c r="DZ6" t="n">
-        <v>2.92</v>
+        <v>2.77</v>
       </c>
       <c r="EA6" t="n">
-        <v>20.42</v>
+        <v>20.38</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
     </row>
     <row r="7">
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D7" t="n">
         <v>7</v>
@@ -3406,82 +3406,82 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="G7" t="n">
-        <v>4</v>
+        <v>3.29</v>
       </c>
       <c r="H7" t="n">
-        <v>97.33</v>
+        <v>91.43000000000001</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="K7" t="n">
-        <v>5.5</v>
+        <v>4.86</v>
       </c>
       <c r="L7" t="n">
-        <v>0.33</v>
+        <v>0.14</v>
       </c>
       <c r="M7" t="n">
-        <v>45</v>
+        <v>41.86</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>1.5</v>
+        <v>1.14</v>
       </c>
       <c r="P7" t="n">
-        <v>14.5</v>
+        <v>13.29</v>
       </c>
       <c r="Q7" t="n">
-        <v>11.67</v>
+        <v>12</v>
       </c>
       <c r="R7" t="n">
-        <v>8.17</v>
+        <v>8</v>
       </c>
       <c r="S7" t="n">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>51.14</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>10.43</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>7.57</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>18.71</v>
+      </c>
+      <c r="AD7" t="n">
         <v>1.17</v>
       </c>
-      <c r="T7" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" t="n">
-        <v>0</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" t="n">
-        <v>54</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>11.17</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>8</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>3.17</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>19</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.26</v>
-      </c>
       <c r="AE7" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AF7" t="n">
         <v>0.29</v>
@@ -3565,70 +3565,70 @@
         <v>1.71</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="BH7" t="n">
-        <v>8.08</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="BP7" t="n">
-        <v>3.38</v>
+        <v>3.07</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.69</v>
+        <v>4.29</v>
       </c>
       <c r="BR7" t="n">
-        <v>84.62</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BS7" t="n">
-        <v>46.15</v>
+        <v>42.86</v>
       </c>
       <c r="BT7" t="n">
-        <v>46.15</v>
+        <v>42.86</v>
       </c>
       <c r="BU7" t="n">
-        <v>38.46</v>
+        <v>35.71</v>
       </c>
       <c r="BV7" t="n">
-        <v>30.77</v>
+        <v>28.57</v>
       </c>
       <c r="BW7" t="n">
-        <v>15.38</v>
+        <v>14.29</v>
       </c>
       <c r="BX7" t="n">
-        <v>30.77</v>
+        <v>28.57</v>
       </c>
       <c r="BY7" t="n">
-        <v>2.74</v>
+        <v>2.68</v>
       </c>
       <c r="BZ7" t="n">
-        <v>2.91</v>
+        <v>2.82</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.49</v>
+        <v>3.44</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.64</v>
+        <v>3.6</v>
       </c>
       <c r="CC7" t="n">
         <v>5.21</v>
@@ -3640,10 +3640,10 @@
         <v>1.41</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.87</v>
+        <v>2.89</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="CH7" t="n">
         <v>1.39</v>
@@ -3655,34 +3655,34 @@
         <v>1.89</v>
       </c>
       <c r="CK7" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="CL7" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="CN7" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="CO7" t="n">
         <v>1.3</v>
       </c>
       <c r="CP7" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="CQ7" t="n">
-        <v>3.47</v>
+        <v>3.53</v>
       </c>
       <c r="CR7" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CS7" t="n">
-        <v>3.04</v>
+        <v>3.07</v>
       </c>
       <c r="CT7" t="n">
-        <v>2.96</v>
+        <v>2.93</v>
       </c>
       <c r="CU7" t="n">
         <v>1.41</v>
@@ -3694,100 +3694,100 @@
         <v>1.91</v>
       </c>
       <c r="CX7" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CY7" t="n">
-        <v>1.99</v>
+        <v>2.01</v>
       </c>
       <c r="CZ7" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="DA7" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="DB7" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="DC7" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="DD7" t="n">
-        <v>3.64</v>
+        <v>3.67</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="DG7" t="n">
-        <v>3.08</v>
+        <v>2.79</v>
       </c>
       <c r="DH7" t="n">
-        <v>84.54000000000001</v>
+        <v>82.5</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DJ7" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="DK7" t="n">
-        <v>4.15</v>
+        <v>3.93</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.31</v>
+        <v>0.22</v>
       </c>
       <c r="DM7" t="n">
-        <v>38.54</v>
+        <v>37.43</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DO7" t="n">
-        <v>1.07</v>
+        <v>0.92</v>
       </c>
       <c r="DP7" t="n">
-        <v>13.69</v>
+        <v>13.14</v>
       </c>
       <c r="DQ7" t="n">
-        <v>12.08</v>
+        <v>12.22</v>
       </c>
       <c r="DR7" t="n">
-        <v>8.69</v>
+        <v>8.57</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>47.77</v>
+        <v>46.78</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DX7" t="n">
-        <v>11.46</v>
+        <v>11.07</v>
       </c>
       <c r="DY7" t="n">
-        <v>7.31</v>
+        <v>7.14</v>
       </c>
       <c r="DZ7" t="n">
-        <v>4.16</v>
+        <v>3.93</v>
       </c>
       <c r="EA7" t="n">
-        <v>18.15</v>
+        <v>18.07</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="EC7" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="8">
@@ -3797,13 +3797,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C8" t="n">
         <v>7</v>
       </c>
       <c r="D8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -3887,52 +3887,52 @@
         <v>3.14</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AG8" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>81.43000000000001</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>28.71</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="AP8" t="n">
         <v>2</v>
       </c>
-      <c r="AH8" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>81.67</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>4</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>29.67</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AQ8" t="n">
-        <v>15</v>
+        <v>14.43</v>
       </c>
       <c r="AR8" t="n">
-        <v>13.33</v>
+        <v>13.29</v>
       </c>
       <c r="AS8" t="n">
-        <v>10</v>
+        <v>10.57</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.83</v>
+        <v>1.14</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="AV8" t="n">
         <v>0</v>
@@ -3944,82 +3944,82 @@
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>43.5</v>
+        <v>43.14</v>
       </c>
       <c r="AZ8" t="n">
         <v>0</v>
       </c>
       <c r="BA8" t="n">
-        <v>8.33</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="BB8" t="n">
-        <v>6.17</v>
+        <v>5.86</v>
       </c>
       <c r="BC8" t="n">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="BD8" t="n">
-        <v>20.17</v>
+        <v>20.29</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.9</v>
+        <v>0.89</v>
       </c>
       <c r="BF8" t="n">
-        <v>2.33</v>
+        <v>2.14</v>
       </c>
       <c r="BG8" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="BH8" t="n">
-        <v>8.85</v>
+        <v>9.5</v>
       </c>
       <c r="BI8" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.38</v>
+        <v>0.43</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.46</v>
+        <v>0.57</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="BN8" t="n">
-        <v>0.85</v>
+        <v>0.93</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="BP8" t="n">
-        <v>3.85</v>
+        <v>4.29</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5</v>
+        <v>5.21</v>
       </c>
       <c r="BR8" t="n">
-        <v>69.23</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BS8" t="n">
-        <v>30.77</v>
+        <v>35.71</v>
       </c>
       <c r="BT8" t="n">
-        <v>23.08</v>
+        <v>28.57</v>
       </c>
       <c r="BU8" t="n">
-        <v>15.38</v>
+        <v>14.29</v>
       </c>
       <c r="BV8" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BW8" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BX8" t="n">
-        <v>30.77</v>
+        <v>28.57</v>
       </c>
       <c r="BY8" t="n">
         <v>2.1</v>
@@ -4028,136 +4028,136 @@
         <v>2.28</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.22</v>
+        <v>3.28</v>
       </c>
       <c r="CC8" t="n">
-        <v>3.39</v>
+        <v>3.68</v>
       </c>
       <c r="CD8" t="n">
-        <v>3.7</v>
+        <v>4.06</v>
       </c>
       <c r="CE8" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CF8" t="n">
-        <v>3.29</v>
+        <v>3.24</v>
       </c>
       <c r="CG8" t="n">
-        <v>2.47</v>
+        <v>2.51</v>
       </c>
       <c r="CH8" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="CI8" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="CJ8" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CL8" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="CM8" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="CN8" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="CO8" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="CP8" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="CQ8" t="n">
+        <v>4.27</v>
+      </c>
+      <c r="CR8" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="CS8" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="CT8" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="CU8" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="CV8" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="CW8" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="CX8" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="CY8" t="n">
         <v>2.09</v>
       </c>
-      <c r="CN8" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="CO8" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="CP8" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="CQ8" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="CR8" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="CS8" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="CT8" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="CU8" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="CV8" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="CW8" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="CX8" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="CY8" t="n">
-        <v>2.11</v>
-      </c>
       <c r="CZ8" t="n">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="DA8" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="DB8" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="DC8" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="DD8" t="n">
-        <v>4.68</v>
+        <v>4.55</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DF8" t="n">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.46</v>
+        <v>2.43</v>
       </c>
       <c r="DH8" t="n">
-        <v>92.08</v>
+        <v>91.22</v>
       </c>
       <c r="DI8" t="n">
         <v>0</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.77</v>
+        <v>2.64</v>
       </c>
       <c r="DK8" t="n">
-        <v>4.61</v>
+        <v>4.64</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DM8" t="n">
-        <v>41</v>
+        <v>39.71</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.15</v>
+        <v>2.22</v>
       </c>
       <c r="DP8" t="n">
-        <v>14.31</v>
+        <v>14.07</v>
       </c>
       <c r="DQ8" t="n">
-        <v>13.69</v>
+        <v>13.64</v>
       </c>
       <c r="DR8" t="n">
-        <v>8.77</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="DS8" t="n">
         <v>0</v>
@@ -4169,28 +4169,28 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>49</v>
+        <v>48.42</v>
       </c>
       <c r="DW8" t="n">
         <v>0</v>
       </c>
       <c r="DX8" t="n">
-        <v>9.69</v>
+        <v>9.5</v>
       </c>
       <c r="DY8" t="n">
-        <v>7.23</v>
+        <v>7</v>
       </c>
       <c r="DZ8" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="EA8" t="n">
-        <v>19.85</v>
+        <v>19.93</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="EC8" t="n">
-        <v>2.77</v>
+        <v>2.64</v>
       </c>
     </row>
     <row r="9">
@@ -4200,94 +4200,94 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D9" t="n">
         <v>7</v>
       </c>
       <c r="E9" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="F9" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="G9" t="n">
-        <v>2.5</v>
+        <v>2.86</v>
       </c>
       <c r="H9" t="n">
-        <v>102.5</v>
+        <v>103.29</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>2.67</v>
+        <v>3.14</v>
       </c>
       <c r="K9" t="n">
+        <v>5.14</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>55.14</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="O9" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="P9" t="n">
+        <v>15.71</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>13.71</v>
+      </c>
+      <c r="R9" t="n">
+        <v>5.14</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>56.14</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>16.29</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>11.29</v>
+      </c>
+      <c r="AB9" t="n">
         <v>5</v>
       </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>51</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="O9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="P9" t="n">
-        <v>16.17</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>14.33</v>
-      </c>
-      <c r="R9" t="n">
-        <v>5.33</v>
-      </c>
-      <c r="S9" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="T9" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="V9" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="W9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X9" t="n">
-        <v>55.17</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>15.33</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>4.83</v>
-      </c>
       <c r="AC9" t="n">
-        <v>20.5</v>
+        <v>21.29</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.68</v>
+        <v>1.78</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.5</v>
+        <v>2.86</v>
       </c>
       <c r="AF9" t="n">
         <v>0.29</v>
@@ -4371,49 +4371,49 @@
         <v>3</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.62</v>
+        <v>2.71</v>
       </c>
       <c r="BH9" t="n">
-        <v>8.77</v>
+        <v>8.93</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.62</v>
+        <v>2.71</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.46</v>
+        <v>1.64</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.38</v>
+        <v>4.29</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.38</v>
+        <v>4.64</v>
       </c>
       <c r="BR9" t="n">
-        <v>92.31</v>
+        <v>92.86</v>
       </c>
       <c r="BS9" t="n">
-        <v>76.92</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="BT9" t="n">
-        <v>53.85</v>
+        <v>57.14</v>
       </c>
       <c r="BU9" t="n">
-        <v>38.46</v>
+        <v>42.86</v>
       </c>
       <c r="BV9" t="n">
         <v>0</v>
@@ -4422,19 +4422,19 @@
         <v>0</v>
       </c>
       <c r="BX9" t="n">
-        <v>69.23</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BY9" t="n">
-        <v>2.11</v>
+        <v>2.14</v>
       </c>
       <c r="BZ9" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="CA9" t="n">
         <v>3.29</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.46</v>
+        <v>3.45</v>
       </c>
       <c r="CC9" t="n">
         <v>3.1</v>
@@ -4449,43 +4449,43 @@
         <v>2.71</v>
       </c>
       <c r="CG9" t="n">
-        <v>2.95</v>
+        <v>2.96</v>
       </c>
       <c r="CH9" t="n">
         <v>1.42</v>
       </c>
       <c r="CI9" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="CK9" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="CL9" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.44</v>
+        <v>2.41</v>
       </c>
       <c r="CN9" t="n">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="CO9" t="n">
         <v>1.26</v>
       </c>
       <c r="CP9" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CQ9" t="n">
-        <v>3.11</v>
+        <v>3.1</v>
       </c>
       <c r="CR9" t="n">
         <v>1.41</v>
       </c>
       <c r="CS9" t="n">
-        <v>2.95</v>
+        <v>2.96</v>
       </c>
       <c r="CT9" t="n">
         <v>3.02</v>
@@ -4494,106 +4494,106 @@
         <v>1.43</v>
       </c>
       <c r="CV9" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="CW9" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CX9" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="CY9" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="CZ9" t="n">
-        <v>2.37</v>
+        <v>2.34</v>
       </c>
       <c r="DA9" t="n">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="DB9" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="DC9" t="n">
         <v>1.95</v>
       </c>
       <c r="DD9" t="n">
-        <v>3.29</v>
+        <v>3.32</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="DG9" t="n">
-        <v>2.16</v>
+        <v>2.36</v>
       </c>
       <c r="DH9" t="n">
-        <v>96.77</v>
+        <v>97.58</v>
       </c>
       <c r="DI9" t="n">
-        <v>-0.08</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="DJ9" t="n">
-        <v>3</v>
+        <v>3.22</v>
       </c>
       <c r="DK9" t="n">
-        <v>4.31</v>
+        <v>4.42</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DM9" t="n">
-        <v>45.08</v>
+        <v>47.57</v>
       </c>
       <c r="DN9" t="n">
-        <v>1.15</v>
+        <v>1.36</v>
       </c>
       <c r="DO9" t="n">
-        <v>2.16</v>
+        <v>2.08</v>
       </c>
       <c r="DP9" t="n">
-        <v>16.31</v>
+        <v>16.07</v>
       </c>
       <c r="DQ9" t="n">
-        <v>14.77</v>
+        <v>14.42</v>
       </c>
       <c r="DR9" t="n">
-        <v>6.39</v>
+        <v>6.21</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>53.69</v>
+        <v>54.28</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.15</v>
+        <v>0.22</v>
       </c>
       <c r="DX9" t="n">
-        <v>14.08</v>
+        <v>14.64</v>
       </c>
       <c r="DY9" t="n">
-        <v>9.390000000000001</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="DZ9" t="n">
-        <v>4.69</v>
+        <v>4.79</v>
       </c>
       <c r="EA9" t="n">
-        <v>21.85</v>
+        <v>22.14</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.77</v>
+        <v>2.93</v>
       </c>
     </row>
     <row r="10">
@@ -4603,13 +4603,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
         <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E10" t="n">
         <v>0.17</v>
@@ -4696,136 +4696,136 @@
         <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.43</v>
+        <v>1.62</v>
       </c>
       <c r="AI10" t="n">
-        <v>81.14</v>
+        <v>78.5</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.57</v>
+        <v>2.88</v>
       </c>
       <c r="AL10" t="n">
         <v>5</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="AN10" t="n">
-        <v>34.57</v>
+        <v>32.62</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.43</v>
+        <v>0.75</v>
       </c>
       <c r="AP10" t="n">
-        <v>3.57</v>
+        <v>3.38</v>
       </c>
       <c r="AQ10" t="n">
-        <v>12.29</v>
+        <v>12</v>
       </c>
       <c r="AR10" t="n">
-        <v>12.29</v>
+        <v>12.25</v>
       </c>
       <c r="AS10" t="n">
-        <v>7.86</v>
+        <v>8.25</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AU10" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="AX10" t="n">
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>49.14</v>
+        <v>47.75</v>
       </c>
       <c r="AZ10" t="n">
         <v>0</v>
       </c>
       <c r="BA10" t="n">
-        <v>13.57</v>
+        <v>13</v>
       </c>
       <c r="BB10" t="n">
-        <v>7.86</v>
+        <v>7.62</v>
       </c>
       <c r="BC10" t="n">
-        <v>5.71</v>
+        <v>5.38</v>
       </c>
       <c r="BD10" t="n">
-        <v>14.71</v>
+        <v>14.12</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="BF10" t="n">
-        <v>2.57</v>
+        <v>2.88</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.77</v>
+        <v>2.86</v>
       </c>
       <c r="BH10" t="n">
-        <v>8.08</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.77</v>
+        <v>2.86</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.46</v>
+        <v>1.64</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="BP10" t="n">
-        <v>4.08</v>
+        <v>4</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4</v>
+        <v>4.29</v>
       </c>
       <c r="BR10" t="n">
-        <v>92.31</v>
+        <v>92.86</v>
       </c>
       <c r="BS10" t="n">
-        <v>84.62</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BT10" t="n">
-        <v>53.85</v>
+        <v>57.14</v>
       </c>
       <c r="BU10" t="n">
-        <v>30.77</v>
+        <v>35.71</v>
       </c>
       <c r="BV10" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BW10" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BX10" t="n">
-        <v>53.85</v>
+        <v>57.14</v>
       </c>
       <c r="BY10" t="n">
         <v>1.91</v>
@@ -4834,55 +4834,55 @@
         <v>1.89</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.19</v>
+        <v>3.2</v>
       </c>
       <c r="CB10" t="n">
         <v>3.36</v>
       </c>
       <c r="CC10" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="CD10" t="n">
-        <v>2.77</v>
+        <v>2.85</v>
       </c>
       <c r="CE10" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.96</v>
+        <v>2.93</v>
       </c>
       <c r="CG10" t="n">
-        <v>2.77</v>
+        <v>2.8</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CI10" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="CJ10" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="CK10" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CL10" t="n">
         <v>2.09</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="CN10" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="CO10" t="n">
         <v>1.33</v>
       </c>
       <c r="CP10" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="CQ10" t="n">
-        <v>3.61</v>
+        <v>3.56</v>
       </c>
       <c r="CR10" t="n">
         <v>1.46</v>
@@ -4894,25 +4894,25 @@
         <v>2.82</v>
       </c>
       <c r="CU10" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CV10" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="CW10" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CX10" t="n">
         <v>1.67</v>
       </c>
       <c r="CY10" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="CZ10" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="DA10" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="DB10" t="n">
         <v>1.35</v>
@@ -4921,82 +4921,82 @@
         <v>2.13</v>
       </c>
       <c r="DD10" t="n">
-        <v>3.79</v>
+        <v>3.78</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="DG10" t="n">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="DH10" t="n">
-        <v>89.54000000000001</v>
+        <v>87.43000000000001</v>
       </c>
       <c r="DI10" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.39</v>
+        <v>2.58</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.46</v>
+        <v>4.5</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DM10" t="n">
-        <v>39.15</v>
+        <v>37.71</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.61</v>
+        <v>2.57</v>
       </c>
       <c r="DP10" t="n">
-        <v>12.54</v>
+        <v>12.36</v>
       </c>
       <c r="DQ10" t="n">
-        <v>12.54</v>
+        <v>12.5</v>
       </c>
       <c r="DR10" t="n">
-        <v>6.85</v>
+        <v>7.14</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.23</v>
+        <v>0.29</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.23</v>
+        <v>0.29</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>51.07</v>
+        <v>50.14</v>
       </c>
       <c r="DW10" t="n">
         <v>0</v>
       </c>
       <c r="DX10" t="n">
-        <v>13</v>
+        <v>12.71</v>
       </c>
       <c r="DY10" t="n">
-        <v>8</v>
+        <v>7.86</v>
       </c>
       <c r="DZ10" t="n">
-        <v>5</v>
+        <v>4.86</v>
       </c>
       <c r="EA10" t="n">
-        <v>17.07</v>
+        <v>16.57</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="EC10" t="n">
-        <v>2.39</v>
+        <v>2.58</v>
       </c>
     </row>
     <row r="11">
@@ -5535,7 +5535,7 @@
         <v>13.86</v>
       </c>
       <c r="AR12" t="n">
-        <v>15</v>
+        <v>15.14</v>
       </c>
       <c r="AS12" t="n">
         <v>9</v>
@@ -5643,13 +5643,13 @@
         <v>3.2</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="CC12" t="n">
         <v>3.61</v>
       </c>
       <c r="CD12" t="n">
-        <v>4</v>
+        <v>4.02</v>
       </c>
       <c r="CE12" t="n">
         <v>1.46</v>
@@ -5691,22 +5691,22 @@
         <v>4.01</v>
       </c>
       <c r="CR12" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="CS12" t="n">
-        <v>3.23</v>
+        <v>3.25</v>
       </c>
       <c r="CT12" t="n">
-        <v>2.68</v>
+        <v>2.67</v>
       </c>
       <c r="CU12" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CV12" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CW12" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="CX12" t="n">
         <v>1.69</v>
@@ -5724,10 +5724,10 @@
         <v>1.42</v>
       </c>
       <c r="DC12" t="n">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="DD12" t="n">
-        <v>4.34</v>
+        <v>4.36</v>
       </c>
       <c r="DE12" t="n">
         <v>0.14</v>
@@ -5766,7 +5766,7 @@
         <v>13.28</v>
       </c>
       <c r="DQ12" t="n">
-        <v>15.36</v>
+        <v>15.42</v>
       </c>
       <c r="DR12" t="n">
         <v>8.140000000000001</v>
@@ -5812,13 +5812,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C13" t="n">
         <v>6</v>
       </c>
       <c r="D13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E13" t="n">
         <v>0.5</v>
@@ -5905,127 +5905,127 @@
         <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AI13" t="n">
-        <v>84.56999999999999</v>
+        <v>83</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="AK13" t="n">
-        <v>3.29</v>
+        <v>3.12</v>
       </c>
       <c r="AL13" t="n">
-        <v>3.71</v>
+        <v>3.62</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="AN13" t="n">
-        <v>35</v>
+        <v>34.88</v>
       </c>
       <c r="AO13" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AQ13" t="n">
-        <v>11.14</v>
+        <v>11.88</v>
       </c>
       <c r="AR13" t="n">
-        <v>13.57</v>
+        <v>13.75</v>
       </c>
       <c r="AS13" t="n">
-        <v>8.710000000000001</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="AT13" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="AU13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>10.25</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>19.12</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>3</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>1</v>
+      </c>
+      <c r="BO13" t="n">
         <v>0.86</v>
       </c>
-      <c r="AV13" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>51.14</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>10</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>5.71</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>4.29</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>19.57</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="BH13" t="n">
-        <v>9.380000000000001</v>
-      </c>
-      <c r="BI13" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="BJ13" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="BK13" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="BL13" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="BM13" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="BN13" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="BO13" t="n">
-        <v>0.85</v>
-      </c>
       <c r="BP13" t="n">
-        <v>4.23</v>
+        <v>4.21</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4.38</v>
+        <v>4.43</v>
       </c>
       <c r="BR13" t="n">
-        <v>76.92</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="BS13" t="n">
-        <v>61.54</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="BT13" t="n">
-        <v>30.77</v>
+        <v>35.71</v>
       </c>
       <c r="BU13" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BV13" t="n">
         <v>0</v>
@@ -6034,7 +6034,7 @@
         <v>0</v>
       </c>
       <c r="BX13" t="n">
-        <v>46.15</v>
+        <v>50</v>
       </c>
       <c r="BY13" t="n">
         <v>2.17</v>
@@ -6046,13 +6046,13 @@
         <v>3</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.11</v>
+        <v>3.09</v>
       </c>
       <c r="CC13" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="CD13" t="n">
-        <v>3.01</v>
+        <v>3.03</v>
       </c>
       <c r="CE13" t="n">
         <v>1.49</v>
@@ -6064,7 +6064,7 @@
         <v>2.5</v>
       </c>
       <c r="CH13" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="CI13" t="n">
         <v>1.76</v>
@@ -6079,7 +6079,7 @@
         <v>2.14</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="CN13" t="n">
         <v>1.69</v>
@@ -6088,10 +6088,10 @@
         <v>1.43</v>
       </c>
       <c r="CP13" t="n">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="CQ13" t="n">
-        <v>4.39</v>
+        <v>4.38</v>
       </c>
       <c r="CR13" t="n">
         <v>1.55</v>
@@ -6127,85 +6127,85 @@
         <v>1.48</v>
       </c>
       <c r="DC13" t="n">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="DD13" t="n">
-        <v>4.82</v>
+        <v>4.85</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="DF13" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="DG13" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="DH13" t="n">
-        <v>87.69</v>
+        <v>86.56999999999999</v>
       </c>
       <c r="DI13" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DJ13" t="n">
-        <v>3.47</v>
+        <v>3.36</v>
       </c>
       <c r="DK13" t="n">
-        <v>4.69</v>
+        <v>4.57</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="DM13" t="n">
-        <v>36.85</v>
+        <v>36.65</v>
       </c>
       <c r="DN13" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="DO13" t="n">
-        <v>2.46</v>
+        <v>2.43</v>
       </c>
       <c r="DP13" t="n">
-        <v>12.77</v>
+        <v>13.08</v>
       </c>
       <c r="DQ13" t="n">
-        <v>14.84</v>
+        <v>14.86</v>
       </c>
       <c r="DR13" t="n">
-        <v>8.380000000000001</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>51.08</v>
+        <v>50.14</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DX13" t="n">
-        <v>10.84</v>
+        <v>10.93</v>
       </c>
       <c r="DY13" t="n">
-        <v>6.61</v>
+        <v>6.65</v>
       </c>
       <c r="DZ13" t="n">
-        <v>4.23</v>
+        <v>4.29</v>
       </c>
       <c r="EA13" t="n">
-        <v>20.61</v>
+        <v>20.28</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="EC13" t="n">
-        <v>3.31</v>
+        <v>3.21</v>
       </c>
     </row>
     <row r="14">
@@ -6215,10 +6215,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D14" t="n">
         <v>7</v>
@@ -6227,49 +6227,49 @@
         <v>0</v>
       </c>
       <c r="F14" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="H14" t="n">
+        <v>95.56999999999999</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="K14" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="M14" t="n">
+        <v>40.71</v>
+      </c>
+      <c r="N14" t="n">
         <v>2</v>
       </c>
-      <c r="G14" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="H14" t="n">
-        <v>94.67</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>4.17</v>
-      </c>
-      <c r="K14" t="n">
-        <v>3</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="M14" t="n">
-        <v>40.17</v>
-      </c>
-      <c r="N14" t="n">
-        <v>2.17</v>
-      </c>
       <c r="O14" t="n">
-        <v>1.33</v>
+        <v>1.71</v>
       </c>
       <c r="P14" t="n">
-        <v>17.17</v>
+        <v>17.71</v>
       </c>
       <c r="Q14" t="n">
-        <v>12.17</v>
+        <v>12.14</v>
       </c>
       <c r="R14" t="n">
-        <v>7.5</v>
+        <v>7.43</v>
       </c>
       <c r="S14" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="T14" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
@@ -6281,28 +6281,28 @@
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>46.17</v>
+        <v>46.57</v>
       </c>
       <c r="Y14" t="n">
         <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>12.5</v>
+        <v>12.43</v>
       </c>
       <c r="AA14" t="n">
-        <v>8.17</v>
+        <v>8.43</v>
       </c>
       <c r="AB14" t="n">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="AC14" t="n">
-        <v>15.83</v>
+        <v>15.57</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AE14" t="n">
-        <v>4.17</v>
+        <v>4.14</v>
       </c>
       <c r="AF14" t="n">
         <v>0.14</v>
@@ -6386,70 +6386,70 @@
         <v>2.14</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.69</v>
+        <v>2.64</v>
       </c>
       <c r="BH14" t="n">
-        <v>8.85</v>
+        <v>9</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.69</v>
+        <v>2.64</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.85</v>
+        <v>0.93</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="BP14" t="n">
-        <v>3.85</v>
+        <v>3.93</v>
       </c>
       <c r="BQ14" t="n">
-        <v>5</v>
+        <v>5.07</v>
       </c>
       <c r="BR14" t="n">
-        <v>92.31</v>
+        <v>92.86</v>
       </c>
       <c r="BS14" t="n">
-        <v>69.23</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BT14" t="n">
-        <v>46.15</v>
+        <v>42.86</v>
       </c>
       <c r="BU14" t="n">
-        <v>30.77</v>
+        <v>28.57</v>
       </c>
       <c r="BV14" t="n">
-        <v>23.08</v>
+        <v>21.43</v>
       </c>
       <c r="BW14" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BX14" t="n">
-        <v>61.54</v>
+        <v>57.14</v>
       </c>
       <c r="BY14" t="n">
-        <v>3.08</v>
+        <v>3.07</v>
       </c>
       <c r="BZ14" t="n">
-        <v>3.57</v>
+        <v>3.54</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.16</v>
+        <v>3.15</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.4</v>
+        <v>3.37</v>
       </c>
       <c r="CC14" t="n">
         <v>4.72</v>
@@ -6458,61 +6458,61 @@
         <v>5.16</v>
       </c>
       <c r="CE14" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="CF14" t="n">
-        <v>3.23</v>
+        <v>3.25</v>
       </c>
       <c r="CG14" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="CH14" t="n">
         <v>1.31</v>
       </c>
       <c r="CI14" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CJ14" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="CK14" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="CL14" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="CN14" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="CO14" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CP14" t="n">
-        <v>2.27</v>
+        <v>2.29</v>
       </c>
       <c r="CQ14" t="n">
-        <v>4.27</v>
+        <v>4.36</v>
       </c>
       <c r="CR14" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="CS14" t="n">
         <v>3.25</v>
       </c>
       <c r="CT14" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="CU14" t="n">
         <v>1.36</v>
       </c>
       <c r="CV14" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="CW14" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="CX14" t="n">
         <v>1.72</v>
@@ -6527,88 +6527,88 @@
         <v>1.68</v>
       </c>
       <c r="DB14" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="DC14" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="DD14" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="DE14" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="DF14" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="DG14" t="n">
         <v>1.43</v>
       </c>
-      <c r="DC14" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="DD14" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="DE14" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="DF14" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="DG14" t="n">
-        <v>1.31</v>
-      </c>
       <c r="DH14" t="n">
-        <v>84.69</v>
+        <v>85.86</v>
       </c>
       <c r="DI14" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DJ14" t="n">
-        <v>3.23</v>
+        <v>3.28</v>
       </c>
       <c r="DK14" t="n">
-        <v>2.62</v>
+        <v>2.93</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DM14" t="n">
-        <v>33.54</v>
+        <v>34.29</v>
       </c>
       <c r="DN14" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="DO14" t="n">
-        <v>1.31</v>
+        <v>1.5</v>
       </c>
       <c r="DP14" t="n">
-        <v>15.39</v>
+        <v>15.78</v>
       </c>
       <c r="DQ14" t="n">
-        <v>12.31</v>
+        <v>12.28</v>
       </c>
       <c r="DR14" t="n">
-        <v>10</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>40.16</v>
+        <v>40.79</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DX14" t="n">
-        <v>10.31</v>
+        <v>10.43</v>
       </c>
       <c r="DY14" t="n">
-        <v>6.77</v>
+        <v>7</v>
       </c>
       <c r="DZ14" t="n">
-        <v>3.54</v>
+        <v>3.43</v>
       </c>
       <c r="EA14" t="n">
-        <v>16.77</v>
+        <v>16.57</v>
       </c>
       <c r="EB14" t="n">
         <v>1.15</v>
       </c>
       <c r="EC14" t="n">
-        <v>3.08</v>
+        <v>3.14</v>
       </c>
     </row>
     <row r="15">
@@ -6618,13 +6618,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C15" t="n">
         <v>7</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E15" t="n">
         <v>0.14</v>
@@ -6708,139 +6708,139 @@
         <v>1.86</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.17</v>
+        <v>1.71</v>
       </c>
       <c r="AI15" t="n">
-        <v>79.83</v>
+        <v>85.86</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.5</v>
+        <v>2.71</v>
       </c>
       <c r="AL15" t="n">
-        <v>3.5</v>
+        <v>4.29</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.17</v>
+        <v>0</v>
       </c>
       <c r="AN15" t="n">
-        <v>36.17</v>
+        <v>41.86</v>
       </c>
       <c r="AO15" t="n">
         <v>1</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AQ15" t="n">
-        <v>13.5</v>
+        <v>13.57</v>
       </c>
       <c r="AR15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AS15" t="n">
-        <v>7.5</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AX15" t="n">
         <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>47.5</v>
+        <v>50.14</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="BA15" t="n">
-        <v>9.17</v>
+        <v>10.14</v>
       </c>
       <c r="BB15" t="n">
-        <v>6.33</v>
+        <v>7.29</v>
       </c>
       <c r="BC15" t="n">
-        <v>2.83</v>
+        <v>2.86</v>
       </c>
       <c r="BD15" t="n">
-        <v>24.33</v>
+        <v>23.71</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.04</v>
+        <v>1.15</v>
       </c>
       <c r="BF15" t="n">
         <v>2</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.54</v>
+        <v>2.43</v>
       </c>
       <c r="BH15" t="n">
-        <v>8.380000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.54</v>
+        <v>2.43</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="BL15" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="BO15" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="BP15" t="n">
-        <v>3.62</v>
+        <v>3.29</v>
       </c>
       <c r="BQ15" t="n">
-        <v>4.77</v>
+        <v>4.36</v>
       </c>
       <c r="BR15" t="n">
         <v>100</v>
       </c>
       <c r="BS15" t="n">
-        <v>69.23</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="BT15" t="n">
-        <v>53.85</v>
+        <v>50</v>
       </c>
       <c r="BU15" t="n">
-        <v>23.08</v>
+        <v>21.43</v>
       </c>
       <c r="BV15" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BW15" t="n">
         <v>0</v>
       </c>
       <c r="BX15" t="n">
-        <v>46.15</v>
+        <v>42.86</v>
       </c>
       <c r="BY15" t="n">
         <v>2.25</v>
@@ -6849,22 +6849,22 @@
         <v>2.28</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.21</v>
+        <v>3.19</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.35</v>
+        <v>3.34</v>
       </c>
       <c r="CC15" t="n">
-        <v>3.96</v>
+        <v>3.89</v>
       </c>
       <c r="CD15" t="n">
-        <v>4.46</v>
+        <v>4.35</v>
       </c>
       <c r="CE15" t="n">
         <v>1.47</v>
       </c>
       <c r="CF15" t="n">
-        <v>3.17</v>
+        <v>3.16</v>
       </c>
       <c r="CG15" t="n">
         <v>2.61</v>
@@ -6873,22 +6873,22 @@
         <v>1.33</v>
       </c>
       <c r="CI15" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CJ15" t="n">
         <v>1.98</v>
       </c>
       <c r="CK15" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="CL15" t="n">
-        <v>2.14</v>
+        <v>2.17</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="CN15" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CO15" t="n">
         <v>1.38</v>
@@ -6897,121 +6897,121 @@
         <v>2.25</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.98</v>
+        <v>4</v>
       </c>
       <c r="CR15" t="n">
         <v>1.49</v>
       </c>
       <c r="CS15" t="n">
-        <v>3.16</v>
+        <v>3.18</v>
       </c>
       <c r="CT15" t="n">
         <v>2.74</v>
       </c>
       <c r="CU15" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="CV15" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="CW15" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="CX15" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="CY15" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="CZ15" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="DA15" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="DB15" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="DC15" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="DD15" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="DE15" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="DF15" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="DG15" t="n">
+        <v>2</v>
+      </c>
+      <c r="DH15" t="n">
+        <v>88.08</v>
+      </c>
+      <c r="DI15" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="DJ15" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="DK15" t="n">
+        <v>4</v>
+      </c>
+      <c r="DL15" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="DM15" t="n">
+        <v>46.08</v>
+      </c>
+      <c r="DN15" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="DO15" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="DP15" t="n">
+        <v>13.36</v>
+      </c>
+      <c r="DQ15" t="n">
+        <v>12.57</v>
+      </c>
+      <c r="DR15" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="DS15" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="DT15" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="DU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV15" t="n">
+        <v>52.07</v>
+      </c>
+      <c r="DW15" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="DX15" t="n">
+        <v>12.14</v>
+      </c>
+      <c r="DY15" t="n">
+        <v>8.140000000000001</v>
+      </c>
+      <c r="DZ15" t="n">
+        <v>4</v>
+      </c>
+      <c r="EA15" t="n">
+        <v>23.21</v>
+      </c>
+      <c r="EB15" t="n">
         <v>1.38</v>
       </c>
-      <c r="CV15" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="CW15" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="CX15" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="CY15" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="CZ15" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="DA15" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="DB15" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="DC15" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="DD15" t="n">
-        <v>4.38</v>
-      </c>
-      <c r="DE15" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="DF15" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="DG15" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="DH15" t="n">
-        <v>85.45999999999999</v>
-      </c>
-      <c r="DI15" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="DJ15" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="DK15" t="n">
-        <v>3.61</v>
-      </c>
-      <c r="DL15" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="DM15" t="n">
-        <v>43.77</v>
-      </c>
-      <c r="DN15" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="DO15" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="DP15" t="n">
-        <v>13.31</v>
-      </c>
-      <c r="DQ15" t="n">
-        <v>13.08</v>
-      </c>
-      <c r="DR15" t="n">
-        <v>7.16</v>
-      </c>
-      <c r="DS15" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="DT15" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="DU15" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV15" t="n">
-        <v>51</v>
-      </c>
-      <c r="DW15" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="DX15" t="n">
-        <v>11.85</v>
-      </c>
-      <c r="DY15" t="n">
-        <v>7.77</v>
-      </c>
-      <c r="DZ15" t="n">
-        <v>4.07</v>
-      </c>
-      <c r="EA15" t="n">
-        <v>23.46</v>
-      </c>
-      <c r="EB15" t="n">
-        <v>1.35</v>
-      </c>
       <c r="EC15" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
     </row>
     <row r="16">
@@ -7033,7 +7033,7 @@
         <v>0.25</v>
       </c>
       <c r="F16" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="G16" t="n">
         <v>4.38</v>
@@ -7045,7 +7045,7 @@
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="K16" t="n">
         <v>7.88</v>
@@ -7063,7 +7063,7 @@
         <v>3.5</v>
       </c>
       <c r="P16" t="n">
-        <v>12.38</v>
+        <v>12.5</v>
       </c>
       <c r="Q16" t="n">
         <v>14.12</v>
@@ -7108,7 +7108,7 @@
         <v>1.79</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="AF16" t="n">
         <v>0</v>
@@ -7249,13 +7249,13 @@
         <v>1.81</v>
       </c>
       <c r="BZ16" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CA16" t="n">
         <v>3.71</v>
       </c>
       <c r="CB16" t="n">
-        <v>3.88</v>
+        <v>3.87</v>
       </c>
       <c r="CC16" t="n">
         <v>3.18</v>
@@ -7303,19 +7303,19 @@
         <v>2.66</v>
       </c>
       <c r="CR16" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CS16" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="CT16" t="n">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="CU16" t="n">
         <v>1.53</v>
       </c>
       <c r="CV16" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="CW16" t="n">
         <v>1.64</v>
@@ -7333,19 +7333,19 @@
         <v>1.95</v>
       </c>
       <c r="DB16" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="DC16" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="DD16" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="DE16" t="n">
         <v>0.14</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="DG16" t="n">
         <v>3.65</v>
@@ -7357,7 +7357,7 @@
         <v>0.21</v>
       </c>
       <c r="DJ16" t="n">
-        <v>2.86</v>
+        <v>2.92</v>
       </c>
       <c r="DK16" t="n">
         <v>6.57</v>
@@ -7375,7 +7375,7 @@
         <v>2.93</v>
       </c>
       <c r="DP16" t="n">
-        <v>12.93</v>
+        <v>13</v>
       </c>
       <c r="DQ16" t="n">
         <v>15.07</v>
@@ -7414,7 +7414,7 @@
         <v>1.61</v>
       </c>
       <c r="EC16" t="n">
-        <v>2.64</v>
+        <v>2.71</v>
       </c>
     </row>
     <row r="17">
@@ -7893,7 +7893,7 @@
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>55.88</v>
+        <v>55.75</v>
       </c>
       <c r="Y18" t="n">
         <v>0</v>
@@ -8199,7 +8199,7 @@
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>53.43</v>
+        <v>53.36</v>
       </c>
       <c r="DW18" t="n">
         <v>0.07000000000000001</v>
@@ -8230,10 +8230,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D19" t="n">
         <v>7</v>
@@ -8242,49 +8242,49 @@
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="G19" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="H19" t="n">
-        <v>92</v>
+        <v>94.86</v>
       </c>
       <c r="I19" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="J19" t="n">
         <v>4</v>
       </c>
       <c r="K19" t="n">
-        <v>3.67</v>
+        <v>3.86</v>
       </c>
       <c r="L19" t="n">
-        <v>0.33</v>
+        <v>0.71</v>
       </c>
       <c r="M19" t="n">
-        <v>39.33</v>
+        <v>39.29</v>
       </c>
       <c r="N19" t="n">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="O19" t="n">
-        <v>2.5</v>
+        <v>2.71</v>
       </c>
       <c r="P19" t="n">
-        <v>13.17</v>
+        <v>12.57</v>
       </c>
       <c r="Q19" t="n">
-        <v>15.33</v>
+        <v>14.43</v>
       </c>
       <c r="R19" t="n">
-        <v>8.33</v>
+        <v>7.86</v>
       </c>
       <c r="S19" t="n">
-        <v>2</v>
+        <v>1.71</v>
       </c>
       <c r="T19" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
@@ -8296,25 +8296,25 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>49</v>
+        <v>49.57</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="Z19" t="n">
-        <v>10.5</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="AA19" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="AB19" t="n">
-        <v>3</v>
+        <v>2.86</v>
       </c>
       <c r="AC19" t="n">
-        <v>23.5</v>
+        <v>24</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="AE19" t="n">
         <v>3</v>
@@ -8401,70 +8401,70 @@
         <v>2.43</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.31</v>
+        <v>2.21</v>
       </c>
       <c r="BH19" t="n">
-        <v>10.46</v>
+        <v>10.29</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.31</v>
+        <v>2.21</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.23</v>
+        <v>0.29</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="BO19" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="BP19" t="n">
-        <v>5.38</v>
+        <v>5.36</v>
       </c>
       <c r="BQ19" t="n">
-        <v>5</v>
+        <v>4.86</v>
       </c>
       <c r="BR19" t="n">
-        <v>92.31</v>
+        <v>92.86</v>
       </c>
       <c r="BS19" t="n">
-        <v>53.85</v>
+        <v>50</v>
       </c>
       <c r="BT19" t="n">
-        <v>30.77</v>
+        <v>28.57</v>
       </c>
       <c r="BU19" t="n">
-        <v>30.77</v>
+        <v>28.57</v>
       </c>
       <c r="BV19" t="n">
-        <v>15.38</v>
+        <v>14.29</v>
       </c>
       <c r="BW19" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BX19" t="n">
-        <v>38.46</v>
+        <v>35.71</v>
       </c>
       <c r="BY19" t="n">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
       <c r="BZ19" t="n">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="CA19" t="n">
-        <v>3.23</v>
+        <v>3.2</v>
       </c>
       <c r="CB19" t="n">
-        <v>3.38</v>
+        <v>3.34</v>
       </c>
       <c r="CC19" t="n">
         <v>3.71</v>
@@ -8473,22 +8473,22 @@
         <v>4.33</v>
       </c>
       <c r="CE19" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CF19" t="n">
-        <v>3</v>
+        <v>3.06</v>
       </c>
       <c r="CG19" t="n">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="CH19" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="CI19" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="CJ19" t="n">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="CK19" t="n">
         <v>1.59</v>
@@ -8503,94 +8503,94 @@
         <v>1.81</v>
       </c>
       <c r="CO19" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="CP19" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="CQ19" t="n">
-        <v>3.74</v>
+        <v>3.88</v>
       </c>
       <c r="CR19" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="CS19" t="n">
         <v>3.19</v>
       </c>
       <c r="CT19" t="n">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="CU19" t="n">
         <v>1.38</v>
       </c>
       <c r="CV19" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="CW19" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="CX19" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CY19" t="n">
         <v>1.99</v>
       </c>
       <c r="CZ19" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="DA19" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="DB19" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="DC19" t="n">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="DD19" t="n">
-        <v>3.82</v>
+        <v>3.99</v>
       </c>
       <c r="DE19" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DF19" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="DG19" t="n">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="DH19" t="n">
-        <v>91.84</v>
+        <v>93.28</v>
       </c>
       <c r="DI19" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DJ19" t="n">
-        <v>3.15</v>
+        <v>3.22</v>
       </c>
       <c r="DK19" t="n">
-        <v>5.16</v>
+        <v>5.14</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.31</v>
+        <v>0.5</v>
       </c>
       <c r="DM19" t="n">
-        <v>42.46</v>
+        <v>42.22</v>
       </c>
       <c r="DN19" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="DO19" t="n">
-        <v>2.46</v>
+        <v>2.57</v>
       </c>
       <c r="DP19" t="n">
-        <v>13.92</v>
+        <v>13.57</v>
       </c>
       <c r="DQ19" t="n">
-        <v>15.92</v>
+        <v>15.43</v>
       </c>
       <c r="DR19" t="n">
-        <v>7</v>
+        <v>6.86</v>
       </c>
       <c r="DS19" t="n">
         <v>0</v>
@@ -8602,28 +8602,28 @@
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>49.38</v>
+        <v>49.64</v>
       </c>
       <c r="DW19" t="n">
-        <v>0.31</v>
+        <v>0.36</v>
       </c>
       <c r="DX19" t="n">
-        <v>12.46</v>
+        <v>12</v>
       </c>
       <c r="DY19" t="n">
-        <v>9.31</v>
+        <v>8.93</v>
       </c>
       <c r="DZ19" t="n">
-        <v>3.16</v>
+        <v>3.08</v>
       </c>
       <c r="EA19" t="n">
-        <v>20.85</v>
+        <v>21.28</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="EC19" t="n">
-        <v>2.69</v>
+        <v>2.72</v>
       </c>
     </row>
     <row r="20">
@@ -8633,13 +8633,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C20" t="n">
         <v>7</v>
       </c>
       <c r="D20" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -8723,52 +8723,52 @@
         <v>2.14</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AH20" t="n">
-        <v>3.17</v>
+        <v>3.14</v>
       </c>
       <c r="AI20" t="n">
-        <v>102.17</v>
+        <v>99.70999999999999</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AK20" t="n">
-        <v>2.33</v>
+        <v>2.71</v>
       </c>
       <c r="AL20" t="n">
-        <v>4.67</v>
+        <v>4.43</v>
       </c>
       <c r="AM20" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AN20" t="n">
-        <v>41.33</v>
+        <v>38.43</v>
       </c>
       <c r="AO20" t="n">
-        <v>0.67</v>
+        <v>0.86</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="AQ20" t="n">
-        <v>11.33</v>
+        <v>11.43</v>
       </c>
       <c r="AR20" t="n">
-        <v>13.83</v>
+        <v>13.71</v>
       </c>
       <c r="AS20" t="n">
-        <v>7</v>
+        <v>6.57</v>
       </c>
       <c r="AT20" t="n">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="AU20" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="AV20" t="n">
         <v>0</v>
@@ -8780,82 +8780,82 @@
         <v>0</v>
       </c>
       <c r="AY20" t="n">
-        <v>52.33</v>
+        <v>50.29</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="BA20" t="n">
-        <v>10.5</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="BB20" t="n">
-        <v>7.5</v>
+        <v>6.86</v>
       </c>
       <c r="BC20" t="n">
         <v>3</v>
       </c>
       <c r="BD20" t="n">
-        <v>21.33</v>
+        <v>19.71</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.67</v>
+        <v>2.14</v>
       </c>
       <c r="BG20" t="n">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="BH20" t="n">
-        <v>9.08</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="BI20" t="n">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="BJ20" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="BK20" t="n">
-        <v>0.23</v>
+        <v>0.29</v>
       </c>
       <c r="BL20" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="BM20" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="BN20" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="BO20" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="BP20" t="n">
-        <v>4.23</v>
+        <v>4.29</v>
       </c>
       <c r="BQ20" t="n">
-        <v>4.85</v>
+        <v>5.07</v>
       </c>
       <c r="BR20" t="n">
-        <v>84.62</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BS20" t="n">
-        <v>69.23</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BT20" t="n">
-        <v>46.15</v>
+        <v>42.86</v>
       </c>
       <c r="BU20" t="n">
-        <v>23.08</v>
+        <v>21.43</v>
       </c>
       <c r="BV20" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BW20" t="n">
         <v>0</v>
       </c>
       <c r="BX20" t="n">
-        <v>53.85</v>
+        <v>57.14</v>
       </c>
       <c r="BY20" t="n">
         <v>1.93</v>
@@ -8864,55 +8864,55 @@
         <v>2.09</v>
       </c>
       <c r="CA20" t="n">
-        <v>3.16</v>
+        <v>3.15</v>
       </c>
       <c r="CB20" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="CC20" t="n">
         <v>3.26</v>
       </c>
-      <c r="CC20" t="n">
-        <v>3.31</v>
-      </c>
       <c r="CD20" t="n">
-        <v>3.7</v>
+        <v>3.62</v>
       </c>
       <c r="CE20" t="n">
         <v>1.48</v>
       </c>
       <c r="CF20" t="n">
-        <v>3.33</v>
+        <v>3.32</v>
       </c>
       <c r="CG20" t="n">
-        <v>2.47</v>
+        <v>2.48</v>
       </c>
       <c r="CH20" t="n">
         <v>1.3</v>
       </c>
       <c r="CI20" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CJ20" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="CK20" t="n">
         <v>1.65</v>
       </c>
       <c r="CL20" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="CM20" t="n">
         <v>2.12</v>
       </c>
       <c r="CN20" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CO20" t="n">
         <v>1.44</v>
       </c>
       <c r="CP20" t="n">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="CQ20" t="n">
-        <v>4.41</v>
+        <v>4.43</v>
       </c>
       <c r="CR20" t="n">
         <v>1.56</v>
@@ -8921,7 +8921,7 @@
         <v>3.24</v>
       </c>
       <c r="CT20" t="n">
-        <v>2.56</v>
+        <v>2.55</v>
       </c>
       <c r="CU20" t="n">
         <v>1.36</v>
@@ -8951,82 +8951,82 @@
         <v>2.49</v>
       </c>
       <c r="DD20" t="n">
-        <v>4.76</v>
+        <v>4.78</v>
       </c>
       <c r="DE20" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DF20" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="DG20" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="DH20" t="n">
-        <v>110.23</v>
+        <v>108.42</v>
       </c>
       <c r="DI20" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DJ20" t="n">
-        <v>2.23</v>
+        <v>2.43</v>
       </c>
       <c r="DK20" t="n">
-        <v>4.92</v>
+        <v>4.78</v>
       </c>
       <c r="DL20" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="DM20" t="n">
-        <v>49.23</v>
+        <v>47.22</v>
       </c>
       <c r="DN20" t="n">
-        <v>0.77</v>
+        <v>0.86</v>
       </c>
       <c r="DO20" t="n">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="DP20" t="n">
-        <v>13.77</v>
+        <v>13.64</v>
       </c>
       <c r="DQ20" t="n">
-        <v>12.69</v>
+        <v>12.71</v>
       </c>
       <c r="DR20" t="n">
-        <v>7.46</v>
+        <v>7.22</v>
       </c>
       <c r="DS20" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DT20" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DU20" t="n">
         <v>0</v>
       </c>
       <c r="DV20" t="n">
-        <v>52.77</v>
+        <v>51.72</v>
       </c>
       <c r="DW20" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DX20" t="n">
-        <v>13.15</v>
+        <v>12.64</v>
       </c>
       <c r="DY20" t="n">
-        <v>8.77</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="DZ20" t="n">
-        <v>4.38</v>
+        <v>4.28</v>
       </c>
       <c r="EA20" t="n">
-        <v>20.08</v>
+        <v>19.36</v>
       </c>
       <c r="EB20" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="EC20" t="n">
-        <v>1.92</v>
+        <v>2.14</v>
       </c>
     </row>
     <row r="21">
@@ -9036,13 +9036,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C21" t="n">
         <v>7</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -9129,49 +9129,49 @@
         <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.33</v>
+        <v>2.29</v>
       </c>
       <c r="AI21" t="n">
-        <v>80.33</v>
+        <v>82.70999999999999</v>
       </c>
       <c r="AJ21" t="n">
         <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="AL21" t="n">
-        <v>3.67</v>
+        <v>3.57</v>
       </c>
       <c r="AM21" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="AN21" t="n">
-        <v>34.33</v>
+        <v>35.57</v>
       </c>
       <c r="AO21" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AQ21" t="n">
-        <v>11.17</v>
+        <v>10.86</v>
       </c>
       <c r="AR21" t="n">
-        <v>14.5</v>
+        <v>13.71</v>
       </c>
       <c r="AS21" t="n">
-        <v>7.83</v>
+        <v>7.14</v>
       </c>
       <c r="AT21" t="n">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="AU21" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="AV21" t="n">
         <v>0</v>
@@ -9183,73 +9183,73 @@
         <v>0</v>
       </c>
       <c r="AY21" t="n">
-        <v>49.33</v>
+        <v>49</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="BA21" t="n">
-        <v>9.83</v>
+        <v>9.57</v>
       </c>
       <c r="BB21" t="n">
-        <v>8.33</v>
+        <v>8</v>
       </c>
       <c r="BC21" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="BD21" t="n">
-        <v>17.5</v>
+        <v>18.57</v>
       </c>
       <c r="BE21" t="n">
         <v>0.98</v>
       </c>
       <c r="BF21" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="BG21" t="n">
-        <v>2.31</v>
+        <v>2.21</v>
       </c>
       <c r="BH21" t="n">
-        <v>8.92</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="BI21" t="n">
-        <v>2.31</v>
+        <v>2.21</v>
       </c>
       <c r="BJ21" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="BK21" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="BL21" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="BM21" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="BN21" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="BO21" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="BP21" t="n">
-        <v>3.77</v>
+        <v>3.86</v>
       </c>
       <c r="BQ21" t="n">
-        <v>5.08</v>
+        <v>4.93</v>
       </c>
       <c r="BR21" t="n">
         <v>100</v>
       </c>
       <c r="BS21" t="n">
-        <v>69.23</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="BT21" t="n">
-        <v>46.15</v>
+        <v>42.86</v>
       </c>
       <c r="BU21" t="n">
-        <v>15.38</v>
+        <v>14.29</v>
       </c>
       <c r="BV21" t="n">
         <v>0</v>
@@ -9258,7 +9258,7 @@
         <v>0</v>
       </c>
       <c r="BX21" t="n">
-        <v>53.85</v>
+        <v>50</v>
       </c>
       <c r="BY21" t="n">
         <v>2.41</v>
@@ -9267,22 +9267,22 @@
         <v>2.61</v>
       </c>
       <c r="CA21" t="n">
-        <v>2.89</v>
+        <v>2.87</v>
       </c>
       <c r="CB21" t="n">
-        <v>2.99</v>
+        <v>2.98</v>
       </c>
       <c r="CC21" t="n">
         <v>3.2</v>
       </c>
       <c r="CD21" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="CE21" t="n">
         <v>1.59</v>
       </c>
       <c r="CF21" t="n">
-        <v>3.76</v>
+        <v>3.77</v>
       </c>
       <c r="CG21" t="n">
         <v>2.27</v>
@@ -9294,142 +9294,142 @@
         <v>1.64</v>
       </c>
       <c r="CJ21" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="CK21" t="n">
         <v>1.74</v>
       </c>
       <c r="CL21" t="n">
-        <v>2.29</v>
+        <v>2.26</v>
       </c>
       <c r="CM21" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="CN21" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CO21" t="n">
         <v>1.54</v>
       </c>
       <c r="CP21" t="n">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="CQ21" t="n">
-        <v>5.13</v>
+        <v>5.18</v>
       </c>
       <c r="CR21" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CS21" t="n">
         <v>3.3</v>
       </c>
       <c r="CT21" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="CU21" t="n">
         <v>1.35</v>
       </c>
       <c r="CV21" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CW21" t="n">
         <v>2.29</v>
       </c>
       <c r="CX21" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="CY21" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="CZ21" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="DA21" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="DB21" t="n">
         <v>1.61</v>
       </c>
       <c r="DC21" t="n">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="DD21" t="n">
-        <v>5.82</v>
+        <v>5.85</v>
       </c>
       <c r="DE21" t="n">
         <v>0</v>
       </c>
       <c r="DF21" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="DG21" t="n">
-        <v>2.46</v>
+        <v>2.43</v>
       </c>
       <c r="DH21" t="n">
-        <v>87.69</v>
+        <v>88.34999999999999</v>
       </c>
       <c r="DI21" t="n">
         <v>0</v>
       </c>
       <c r="DJ21" t="n">
-        <v>2.31</v>
+        <v>2.22</v>
       </c>
       <c r="DK21" t="n">
-        <v>4.31</v>
+        <v>4.22</v>
       </c>
       <c r="DL21" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="DM21" t="n">
-        <v>39.15</v>
+        <v>39.43</v>
       </c>
       <c r="DN21" t="n">
-        <v>0.85</v>
+        <v>0.78</v>
       </c>
       <c r="DO21" t="n">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
       <c r="DP21" t="n">
-        <v>13.61</v>
+        <v>13.28</v>
       </c>
       <c r="DQ21" t="n">
-        <v>13.62</v>
+        <v>13.28</v>
       </c>
       <c r="DR21" t="n">
-        <v>8.619999999999999</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="DS21" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DT21" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DU21" t="n">
         <v>0</v>
       </c>
       <c r="DV21" t="n">
-        <v>48.31</v>
+        <v>48.22</v>
       </c>
       <c r="DW21" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DX21" t="n">
-        <v>11</v>
+        <v>10.78</v>
       </c>
       <c r="DY21" t="n">
-        <v>8.460000000000001</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="DZ21" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="EA21" t="n">
-        <v>21.69</v>
+        <v>21.93</v>
       </c>
       <c r="EB21" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="EC21" t="n">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
     </row>
     <row r="22">
@@ -9439,10 +9439,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C22" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D22" t="n">
         <v>6</v>
@@ -9451,82 +9451,82 @@
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="G22" t="n">
-        <v>1.86</v>
+        <v>2.25</v>
       </c>
       <c r="H22" t="n">
-        <v>103.43</v>
+        <v>110.38</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="K22" t="n">
-        <v>4.29</v>
+        <v>5</v>
       </c>
       <c r="L22" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="M22" t="n">
-        <v>46</v>
+        <v>47.62</v>
       </c>
       <c r="N22" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="O22" t="n">
-        <v>2.43</v>
+        <v>2.75</v>
       </c>
       <c r="P22" t="n">
-        <v>13.14</v>
+        <v>13.12</v>
       </c>
       <c r="Q22" t="n">
-        <v>11.57</v>
+        <v>11.5</v>
       </c>
       <c r="R22" t="n">
-        <v>7.86</v>
+        <v>7</v>
       </c>
       <c r="S22" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T22" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>42.71</v>
+        <v>45.12</v>
       </c>
       <c r="Y22" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="Z22" t="n">
-        <v>12</v>
+        <v>12.12</v>
       </c>
       <c r="AA22" t="n">
-        <v>7.29</v>
+        <v>7.25</v>
       </c>
       <c r="AB22" t="n">
-        <v>4.71</v>
+        <v>4.88</v>
       </c>
       <c r="AC22" t="n">
-        <v>20.86</v>
+        <v>20.62</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="AF22" t="n">
         <v>0.33</v>
@@ -9610,70 +9610,70 @@
         <v>3.17</v>
       </c>
       <c r="BG22" t="n">
-        <v>2.85</v>
+        <v>2.79</v>
       </c>
       <c r="BH22" t="n">
-        <v>8.77</v>
+        <v>9.07</v>
       </c>
       <c r="BI22" t="n">
-        <v>2.85</v>
+        <v>2.79</v>
       </c>
       <c r="BJ22" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="BK22" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="BL22" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="BM22" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="BN22" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="BO22" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="BP22" t="n">
-        <v>4.23</v>
+        <v>4.29</v>
       </c>
       <c r="BQ22" t="n">
-        <v>4.46</v>
+        <v>4.71</v>
       </c>
       <c r="BR22" t="n">
-        <v>92.31</v>
+        <v>92.86</v>
       </c>
       <c r="BS22" t="n">
-        <v>61.54</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="BT22" t="n">
-        <v>61.54</v>
+        <v>57.14</v>
       </c>
       <c r="BU22" t="n">
-        <v>30.77</v>
+        <v>28.57</v>
       </c>
       <c r="BV22" t="n">
-        <v>23.08</v>
+        <v>21.43</v>
       </c>
       <c r="BW22" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BX22" t="n">
-        <v>61.54</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="BY22" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="BZ22" t="n">
-        <v>2.07</v>
+        <v>2.14</v>
       </c>
       <c r="CA22" t="n">
-        <v>3.27</v>
+        <v>3.26</v>
       </c>
       <c r="CB22" t="n">
-        <v>3.37</v>
+        <v>3.35</v>
       </c>
       <c r="CC22" t="n">
         <v>3.46</v>
@@ -9682,28 +9682,28 @@
         <v>3.41</v>
       </c>
       <c r="CE22" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CF22" t="n">
-        <v>3.02</v>
+        <v>3.04</v>
       </c>
       <c r="CG22" t="n">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="CH22" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CI22" t="n">
         <v>1.91</v>
       </c>
       <c r="CJ22" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CK22" t="n">
         <v>1.62</v>
       </c>
       <c r="CL22" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="CM22" t="n">
         <v>2.18</v>
@@ -9715,28 +9715,28 @@
         <v>1.34</v>
       </c>
       <c r="CP22" t="n">
-        <v>2.06</v>
+        <v>2.09</v>
       </c>
       <c r="CQ22" t="n">
-        <v>3.66</v>
+        <v>3.73</v>
       </c>
       <c r="CR22" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="CS22" t="n">
         <v>3.06</v>
       </c>
       <c r="CT22" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="CU22" t="n">
         <v>1.41</v>
       </c>
       <c r="CV22" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CW22" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="CX22" t="n">
         <v>1.63</v>
@@ -9745,94 +9745,94 @@
         <v>2.05</v>
       </c>
       <c r="CZ22" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="DA22" t="n">
         <v>1.78</v>
       </c>
       <c r="DB22" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="DC22" t="n">
-        <v>2.24</v>
+        <v>2.27</v>
       </c>
       <c r="DD22" t="n">
-        <v>4.07</v>
+        <v>4.16</v>
       </c>
       <c r="DE22" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DF22" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="DG22" t="n">
-        <v>1.69</v>
+        <v>1.93</v>
       </c>
       <c r="DH22" t="n">
-        <v>93.92</v>
+        <v>98.56999999999999</v>
       </c>
       <c r="DI22" t="n">
         <v>0</v>
       </c>
       <c r="DJ22" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="DK22" t="n">
-        <v>3.31</v>
+        <v>3.79</v>
       </c>
       <c r="DL22" t="n">
-        <v>0.53</v>
+        <v>0.57</v>
       </c>
       <c r="DM22" t="n">
-        <v>38.31</v>
+        <v>39.78</v>
       </c>
       <c r="DN22" t="n">
-        <v>0.61</v>
+        <v>0.64</v>
       </c>
       <c r="DO22" t="n">
-        <v>1.62</v>
+        <v>1.86</v>
       </c>
       <c r="DP22" t="n">
-        <v>12.69</v>
+        <v>12.71</v>
       </c>
       <c r="DQ22" t="n">
-        <v>11.54</v>
+        <v>11.5</v>
       </c>
       <c r="DR22" t="n">
-        <v>8.16</v>
+        <v>7.64</v>
       </c>
       <c r="DS22" t="n">
-        <v>0.15</v>
+        <v>0.21</v>
       </c>
       <c r="DT22" t="n">
-        <v>0.15</v>
+        <v>0.21</v>
       </c>
       <c r="DU22" t="n">
         <v>0</v>
       </c>
       <c r="DV22" t="n">
-        <v>41.15</v>
+        <v>42.64</v>
       </c>
       <c r="DW22" t="n">
-        <v>0.31</v>
+        <v>0.28</v>
       </c>
       <c r="DX22" t="n">
-        <v>9.84</v>
+        <v>10.07</v>
       </c>
       <c r="DY22" t="n">
-        <v>5.54</v>
+        <v>5.64</v>
       </c>
       <c r="DZ22" t="n">
-        <v>4.3</v>
+        <v>4.43</v>
       </c>
       <c r="EA22" t="n">
-        <v>20.15</v>
+        <v>20.07</v>
       </c>
       <c r="EB22" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="EC22" t="n">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
     </row>
     <row r="23">
@@ -9989,7 +9989,7 @@
         <v>0</v>
       </c>
       <c r="AY23" t="n">
-        <v>57.29</v>
+        <v>57.43</v>
       </c>
       <c r="AZ23" t="n">
         <v>0</v>
@@ -10214,7 +10214,7 @@
         <v>0</v>
       </c>
       <c r="DV23" t="n">
-        <v>56.43</v>
+        <v>56.5</v>
       </c>
       <c r="DW23" t="n">
         <v>0.22</v>

--- a/data/teams/leagues/Averages_Spain_Segunda_División_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Spain_Segunda_División_2025-2026.xlsx
@@ -3409,7 +3409,7 @@
         <v>1.14</v>
       </c>
       <c r="G7" t="n">
-        <v>3.29</v>
+        <v>3.43</v>
       </c>
       <c r="H7" t="n">
         <v>91.43000000000001</v>
@@ -3424,7 +3424,7 @@
         <v>4.86</v>
       </c>
       <c r="L7" t="n">
-        <v>0.14</v>
+        <v>0.29</v>
       </c>
       <c r="M7" t="n">
         <v>41.86</v>
@@ -3433,7 +3433,7 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>1.14</v>
+        <v>1.43</v>
       </c>
       <c r="P7" t="n">
         <v>13.29</v>
@@ -3592,10 +3592,10 @@
         <v>1.29</v>
       </c>
       <c r="BP7" t="n">
-        <v>3.07</v>
+        <v>3.43</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.29</v>
+        <v>4.79</v>
       </c>
       <c r="BR7" t="n">
         <v>85.70999999999999</v>
@@ -3721,7 +3721,7 @@
         <v>1.28</v>
       </c>
       <c r="DG7" t="n">
-        <v>2.79</v>
+        <v>2.86</v>
       </c>
       <c r="DH7" t="n">
         <v>82.5</v>
@@ -3736,7 +3736,7 @@
         <v>3.93</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.22</v>
+        <v>0.29</v>
       </c>
       <c r="DM7" t="n">
         <v>37.43</v>
@@ -3745,7 +3745,7 @@
         <v>0.22</v>
       </c>
       <c r="DO7" t="n">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="DP7" t="n">
         <v>13.14</v>
@@ -6714,7 +6714,7 @@
         <v>1.43</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.71</v>
+        <v>2.71</v>
       </c>
       <c r="AI15" t="n">
         <v>85.86</v>
@@ -6729,7 +6729,7 @@
         <v>4.29</v>
       </c>
       <c r="AM15" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="AN15" t="n">
         <v>41.86</v>
@@ -6738,7 +6738,7 @@
         <v>1</v>
       </c>
       <c r="AP15" t="n">
-        <v>1</v>
+        <v>1.57</v>
       </c>
       <c r="AQ15" t="n">
         <v>13.57</v>
@@ -6816,10 +6816,10 @@
         <v>0.86</v>
       </c>
       <c r="BP15" t="n">
-        <v>3.29</v>
+        <v>3.64</v>
       </c>
       <c r="BQ15" t="n">
-        <v>4.36</v>
+        <v>4.86</v>
       </c>
       <c r="BR15" t="n">
         <v>100</v>
@@ -6945,7 +6945,7 @@
         <v>1.43</v>
       </c>
       <c r="DG15" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="DH15" t="n">
         <v>88.08</v>
@@ -6960,7 +6960,7 @@
         <v>4</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.14</v>
       </c>
       <c r="DM15" t="n">
         <v>46.08</v>
@@ -6969,7 +6969,7 @@
         <v>0.78</v>
       </c>
       <c r="DO15" t="n">
-        <v>1.21</v>
+        <v>1.5</v>
       </c>
       <c r="DP15" t="n">
         <v>13.36</v>

--- a/data/teams/leagues/Averages_Spain_Segunda_División_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Spain_Segunda_División_2025-2026.xlsx
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" t="n">
         <v>7</v>
       </c>
       <c r="D2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -1469,139 +1469,139 @@
         <v>1.57</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.43</v>
+        <v>1.62</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.86</v>
+        <v>1.62</v>
       </c>
       <c r="AI2" t="n">
-        <v>85.43000000000001</v>
+        <v>84</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AK2" t="n">
-        <v>3.29</v>
+        <v>3.5</v>
       </c>
       <c r="AL2" t="n">
-        <v>4.29</v>
+        <v>4.12</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="AN2" t="n">
-        <v>41</v>
+        <v>40.25</v>
       </c>
       <c r="AO2" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AP2" t="n">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="AQ2" t="n">
-        <v>12.43</v>
+        <v>12.88</v>
       </c>
       <c r="AR2" t="n">
-        <v>12.86</v>
+        <v>13.25</v>
       </c>
       <c r="AS2" t="n">
-        <v>9.43</v>
+        <v>9</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AX2" t="n">
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>42.71</v>
+        <v>42.38</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="BA2" t="n">
-        <v>11.86</v>
+        <v>11.62</v>
       </c>
       <c r="BB2" t="n">
-        <v>6.57</v>
+        <v>6.62</v>
       </c>
       <c r="BC2" t="n">
-        <v>5.29</v>
+        <v>5</v>
       </c>
       <c r="BD2" t="n">
-        <v>23.14</v>
+        <v>23.5</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="BF2" t="n">
-        <v>2.43</v>
+        <v>2.75</v>
       </c>
       <c r="BG2" t="n">
-        <v>3.14</v>
+        <v>3.13</v>
       </c>
       <c r="BH2" t="n">
-        <v>10.5</v>
+        <v>10.33</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.14</v>
+        <v>3.13</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.36</v>
+        <v>0.47</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="BL2" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="BM2" t="n">
         <v>1.07</v>
       </c>
       <c r="BN2" t="n">
-        <v>2.21</v>
+        <v>2.13</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.93</v>
+        <v>1</v>
       </c>
       <c r="BP2" t="n">
-        <v>5.21</v>
+        <v>5.13</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.21</v>
+        <v>5.13</v>
       </c>
       <c r="BR2" t="n">
-        <v>78.56999999999999</v>
+        <v>80</v>
       </c>
       <c r="BS2" t="n">
-        <v>64.29000000000001</v>
+        <v>66.67</v>
       </c>
       <c r="BT2" t="n">
-        <v>57.14</v>
+        <v>60</v>
       </c>
       <c r="BU2" t="n">
-        <v>42.86</v>
+        <v>40</v>
       </c>
       <c r="BV2" t="n">
-        <v>35.71</v>
+        <v>33.33</v>
       </c>
       <c r="BW2" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="BX2" t="n">
-        <v>57.14</v>
+        <v>60</v>
       </c>
       <c r="BY2" t="n">
         <v>2.16</v>
@@ -1610,40 +1610,40 @@
         <v>2.12</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.32</v>
+        <v>3.34</v>
       </c>
       <c r="CB2" t="n">
         <v>3.57</v>
       </c>
       <c r="CC2" t="n">
-        <v>3.77</v>
+        <v>3.86</v>
       </c>
       <c r="CD2" t="n">
-        <v>4.21</v>
+        <v>4.36</v>
       </c>
       <c r="CE2" t="n">
         <v>1.37</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="CH2" t="n">
         <v>1.42</v>
       </c>
       <c r="CI2" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="CJ2" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CK2" t="n">
         <v>1.5</v>
       </c>
       <c r="CL2" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="CM2" t="n">
         <v>2.46</v>
@@ -1655,28 +1655,28 @@
         <v>1.27</v>
       </c>
       <c r="CP2" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="CQ2" t="n">
-        <v>3.21</v>
+        <v>3.24</v>
       </c>
       <c r="CR2" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CS2" t="n">
-        <v>2.82</v>
+        <v>2.85</v>
       </c>
       <c r="CT2" t="n">
-        <v>3.08</v>
+        <v>3.06</v>
       </c>
       <c r="CU2" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CV2" t="n">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="CW2" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CX2" t="n">
         <v>1.51</v>
@@ -1688,91 +1688,91 @@
         <v>2.44</v>
       </c>
       <c r="DA2" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="DB2" t="n">
         <v>1.29</v>
       </c>
       <c r="DC2" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="DD2" t="n">
-        <v>3.28</v>
+        <v>3.31</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.22</v>
+        <v>2.06</v>
       </c>
       <c r="DH2" t="n">
-        <v>88.43000000000001</v>
+        <v>87.47</v>
       </c>
       <c r="DI2" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.58</v>
+        <v>2.73</v>
       </c>
       <c r="DK2" t="n">
-        <v>4.65</v>
+        <v>4.53</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.43</v>
+        <v>0.47</v>
       </c>
       <c r="DM2" t="n">
-        <v>44.93</v>
+        <v>44.27</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.78</v>
+        <v>0.87</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.43</v>
+        <v>2.47</v>
       </c>
       <c r="DP2" t="n">
-        <v>11.14</v>
+        <v>11.47</v>
       </c>
       <c r="DQ2" t="n">
-        <v>11.22</v>
+        <v>11.53</v>
       </c>
       <c r="DR2" t="n">
-        <v>8.279999999999999</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>43.28</v>
+        <v>43.07</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="DX2" t="n">
-        <v>13.78</v>
+        <v>13.53</v>
       </c>
       <c r="DY2" t="n">
-        <v>8.640000000000001</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="DZ2" t="n">
-        <v>5.14</v>
+        <v>5</v>
       </c>
       <c r="EA2" t="n">
-        <v>24</v>
+        <v>24.13</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="EC2" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="3">
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C5" t="n">
         <v>7</v>
       </c>
       <c r="D5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E5" t="n">
         <v>0.14</v>
@@ -2678,52 +2678,52 @@
         <v>3.29</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="AI5" t="n">
-        <v>95</v>
+        <v>92.88</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="AL5" t="n">
-        <v>5.43</v>
+        <v>5.25</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.71</v>
+        <v>0.88</v>
       </c>
       <c r="AN5" t="n">
-        <v>52.14</v>
+        <v>52.88</v>
       </c>
       <c r="AO5" t="n">
         <v>1</v>
       </c>
       <c r="AP5" t="n">
-        <v>3.14</v>
+        <v>3</v>
       </c>
       <c r="AQ5" t="n">
-        <v>12.86</v>
+        <v>12.88</v>
       </c>
       <c r="AR5" t="n">
-        <v>14.57</v>
+        <v>14.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>6.57</v>
+        <v>6.25</v>
       </c>
       <c r="AT5" t="n">
         <v>1</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.86</v>
+        <v>1.12</v>
       </c>
       <c r="AV5" t="n">
         <v>0</v>
@@ -2735,82 +2735,82 @@
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>52</v>
+        <v>50.88</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="BA5" t="n">
-        <v>11.71</v>
+        <v>12.25</v>
       </c>
       <c r="BB5" t="n">
-        <v>7.43</v>
+        <v>7.75</v>
       </c>
       <c r="BC5" t="n">
-        <v>4.29</v>
+        <v>4.5</v>
       </c>
       <c r="BD5" t="n">
-        <v>19.29</v>
+        <v>19.62</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="BF5" t="n">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.79</v>
+        <v>2.87</v>
       </c>
       <c r="BH5" t="n">
-        <v>10.64</v>
+        <v>10.33</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.79</v>
+        <v>2.87</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="BL5" t="n">
         <v>1</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.57</v>
+        <v>0.67</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="BP5" t="n">
-        <v>5.57</v>
+        <v>5.33</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.07</v>
+        <v>5</v>
       </c>
       <c r="BR5" t="n">
-        <v>85.70999999999999</v>
+        <v>86.67</v>
       </c>
       <c r="BS5" t="n">
-        <v>57.14</v>
+        <v>60</v>
       </c>
       <c r="BT5" t="n">
-        <v>50</v>
+        <v>53.33</v>
       </c>
       <c r="BU5" t="n">
-        <v>35.71</v>
+        <v>40</v>
       </c>
       <c r="BV5" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="BW5" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="BX5" t="n">
-        <v>57.14</v>
+        <v>60</v>
       </c>
       <c r="BY5" t="n">
         <v>1.68</v>
@@ -2819,25 +2819,25 @@
         <v>1.68</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.61</v>
+        <v>3.59</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.89</v>
+        <v>3.86</v>
       </c>
       <c r="CC5" t="n">
-        <v>2.86</v>
+        <v>2.83</v>
       </c>
       <c r="CD5" t="n">
-        <v>3.11</v>
+        <v>3.06</v>
       </c>
       <c r="CE5" t="n">
         <v>1.33</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.56</v>
+        <v>2.57</v>
       </c>
       <c r="CG5" t="n">
-        <v>3.1</v>
+        <v>3.11</v>
       </c>
       <c r="CH5" t="n">
         <v>1.48</v>
@@ -2846,16 +2846,16 @@
         <v>2.13</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CK5" t="n">
         <v>1.53</v>
       </c>
       <c r="CL5" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="CN5" t="n">
         <v>1.85</v>
@@ -2876,7 +2876,7 @@
         <v>2.75</v>
       </c>
       <c r="CT5" t="n">
-        <v>3.14</v>
+        <v>3.15</v>
       </c>
       <c r="CU5" t="n">
         <v>1.49</v>
@@ -2891,13 +2891,13 @@
         <v>1.55</v>
       </c>
       <c r="CY5" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="CZ5" t="n">
         <v>2.39</v>
       </c>
       <c r="DA5" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="DB5" t="n">
         <v>1.24</v>
@@ -2906,82 +2906,82 @@
         <v>1.78</v>
       </c>
       <c r="DD5" t="n">
-        <v>2.91</v>
+        <v>2.92</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF5" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="DG5" t="n">
-        <v>3.14</v>
+        <v>3.07</v>
       </c>
       <c r="DH5" t="n">
-        <v>101.57</v>
+        <v>100</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.14</v>
+        <v>0.2</v>
       </c>
       <c r="DJ5" t="n">
-        <v>3.22</v>
+        <v>3.13</v>
       </c>
       <c r="DK5" t="n">
-        <v>6.86</v>
+        <v>6.67</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.64</v>
+        <v>0.74</v>
       </c>
       <c r="DM5" t="n">
-        <v>60.28</v>
+        <v>60.14</v>
       </c>
       <c r="DN5" t="n">
         <v>1</v>
       </c>
       <c r="DO5" t="n">
-        <v>3.72</v>
+        <v>3.6</v>
       </c>
       <c r="DP5" t="n">
-        <v>12.93</v>
+        <v>12.94</v>
       </c>
       <c r="DQ5" t="n">
-        <v>14.93</v>
+        <v>14.87</v>
       </c>
       <c r="DR5" t="n">
-        <v>5.86</v>
+        <v>5.73</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>56.28</v>
+        <v>55.4</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="DX5" t="n">
-        <v>14.14</v>
+        <v>14.27</v>
       </c>
       <c r="DY5" t="n">
-        <v>9.140000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="DZ5" t="n">
-        <v>5</v>
+        <v>5.06</v>
       </c>
       <c r="EA5" t="n">
-        <v>18.64</v>
+        <v>18.86</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="EC5" t="n">
-        <v>2.79</v>
+        <v>2.74</v>
       </c>
     </row>
     <row r="6">
@@ -5006,10 +5006,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D11" t="n">
         <v>8</v>
@@ -5018,49 +5018,49 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="G11" t="n">
-        <v>4.17</v>
+        <v>3.86</v>
       </c>
       <c r="H11" t="n">
-        <v>94.33</v>
+        <v>108.14</v>
       </c>
       <c r="I11" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="J11" t="n">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="K11" t="n">
-        <v>6.17</v>
+        <v>5.57</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>47.17</v>
+        <v>48.29</v>
       </c>
       <c r="N11" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="O11" t="n">
-        <v>2</v>
+        <v>1.71</v>
       </c>
       <c r="P11" t="n">
-        <v>14.17</v>
+        <v>14.14</v>
       </c>
       <c r="Q11" t="n">
-        <v>15.67</v>
+        <v>15.29</v>
       </c>
       <c r="R11" t="n">
-        <v>8</v>
+        <v>8.43</v>
       </c>
       <c r="S11" t="n">
-        <v>0.83</v>
+        <v>1.14</v>
       </c>
       <c r="T11" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
@@ -5072,25 +5072,25 @@
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>57.83</v>
+        <v>57.71</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="Z11" t="n">
-        <v>13.67</v>
+        <v>13.14</v>
       </c>
       <c r="AA11" t="n">
-        <v>8.67</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="AB11" t="n">
-        <v>5</v>
+        <v>4.86</v>
       </c>
       <c r="AC11" t="n">
-        <v>18</v>
+        <v>19.29</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="AE11" t="n">
         <v>2</v>
@@ -5177,70 +5177,70 @@
         <v>2.88</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.57</v>
+        <v>2.67</v>
       </c>
       <c r="BH11" t="n">
-        <v>9.359999999999999</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.57</v>
+        <v>2.67</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="BL11" t="n">
         <v>1.07</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.64</v>
+        <v>0.73</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="BO11" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.21</v>
+        <v>4.07</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.07</v>
+        <v>5</v>
       </c>
       <c r="BR11" t="n">
-        <v>85.70999999999999</v>
+        <v>86.67</v>
       </c>
       <c r="BS11" t="n">
-        <v>78.56999999999999</v>
+        <v>80</v>
       </c>
       <c r="BT11" t="n">
-        <v>57.14</v>
+        <v>60</v>
       </c>
       <c r="BU11" t="n">
-        <v>28.57</v>
+        <v>33.33</v>
       </c>
       <c r="BV11" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BW11" t="n">
         <v>0</v>
       </c>
       <c r="BX11" t="n">
-        <v>64.29000000000001</v>
+        <v>66.67</v>
       </c>
       <c r="BY11" t="n">
-        <v>2.14</v>
+        <v>2.19</v>
       </c>
       <c r="BZ11" t="n">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.23</v>
+        <v>3.24</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.43</v>
+        <v>3.42</v>
       </c>
       <c r="CC11" t="n">
         <v>3.72</v>
@@ -5249,22 +5249,22 @@
         <v>3.98</v>
       </c>
       <c r="CE11" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.97</v>
+        <v>2.95</v>
       </c>
       <c r="CG11" t="n">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="CH11" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CI11" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="CJ11" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CK11" t="n">
         <v>1.66</v>
@@ -5273,133 +5273,133 @@
         <v>2.16</v>
       </c>
       <c r="CM11" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="CN11" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="CO11" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="CP11" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="CQ11" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="CR11" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="CS11" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="CT11" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="CU11" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="CV11" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="CW11" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="CX11" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="CY11" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="CZ11" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="DA11" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="DB11" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="DC11" t="n">
         <v>2.12</v>
       </c>
-      <c r="CN11" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="CO11" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="CP11" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="CQ11" t="n">
-        <v>3.67</v>
-      </c>
-      <c r="CR11" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="CS11" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="CT11" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="CU11" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="CV11" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="CW11" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="CX11" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="CY11" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="CZ11" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="DA11" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="DB11" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="DC11" t="n">
-        <v>2.14</v>
-      </c>
       <c r="DD11" t="n">
-        <v>3.84</v>
+        <v>3.8</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="DG11" t="n">
-        <v>3.15</v>
+        <v>3.07</v>
       </c>
       <c r="DH11" t="n">
-        <v>94.93000000000001</v>
+        <v>101.33</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.71</v>
+        <v>2.66</v>
       </c>
       <c r="DK11" t="n">
-        <v>4.86</v>
+        <v>4.67</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DM11" t="n">
-        <v>43.29</v>
+        <v>44.07</v>
       </c>
       <c r="DN11" t="n">
         <v>1.07</v>
       </c>
       <c r="DO11" t="n">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="DP11" t="n">
-        <v>14.43</v>
+        <v>14.4</v>
       </c>
       <c r="DQ11" t="n">
-        <v>15.43</v>
+        <v>15.27</v>
       </c>
       <c r="DR11" t="n">
-        <v>7.36</v>
+        <v>7.6</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>56.43</v>
+        <v>56.47</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DX11" t="n">
-        <v>14.36</v>
+        <v>14.07</v>
       </c>
       <c r="DY11" t="n">
-        <v>9.5</v>
+        <v>9.27</v>
       </c>
       <c r="DZ11" t="n">
-        <v>4.86</v>
+        <v>4.8</v>
       </c>
       <c r="EA11" t="n">
-        <v>17.5</v>
+        <v>18.13</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
     </row>
     <row r="12">
@@ -9842,61 +9842,61 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C23" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D23" t="n">
         <v>7</v>
       </c>
       <c r="E23" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="F23" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="G23" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="H23" t="n">
+        <v>96.62</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="K23" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M23" t="n">
+        <v>39.25</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="O23" t="n">
         <v>2</v>
       </c>
-      <c r="G23" t="n">
-        <v>2</v>
-      </c>
-      <c r="H23" t="n">
-        <v>99.56999999999999</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="K23" t="n">
-        <v>4.14</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="M23" t="n">
-        <v>40.29</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="O23" t="n">
-        <v>2.14</v>
-      </c>
       <c r="P23" t="n">
-        <v>13.57</v>
+        <v>13.88</v>
       </c>
       <c r="Q23" t="n">
-        <v>17.14</v>
+        <v>17</v>
       </c>
       <c r="R23" t="n">
-        <v>6.14</v>
+        <v>6.12</v>
       </c>
       <c r="S23" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="T23" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="U23" t="n">
         <v>0</v>
@@ -9908,28 +9908,28 @@
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>55.57</v>
+        <v>56.12</v>
       </c>
       <c r="Y23" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="Z23" t="n">
-        <v>12.86</v>
+        <v>12.5</v>
       </c>
       <c r="AA23" t="n">
-        <v>8.140000000000001</v>
+        <v>8</v>
       </c>
       <c r="AB23" t="n">
-        <v>4.71</v>
+        <v>4.5</v>
       </c>
       <c r="AC23" t="n">
-        <v>19.57</v>
+        <v>19.38</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AF23" t="n">
         <v>0</v>
@@ -10013,49 +10013,49 @@
         <v>2</v>
       </c>
       <c r="BG23" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="BH23" t="n">
-        <v>7.86</v>
+        <v>7.87</v>
       </c>
       <c r="BI23" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="BJ23" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="BK23" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="BL23" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="BM23" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="BN23" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="BO23" t="n">
-        <v>0.86</v>
+        <v>0.93</v>
       </c>
       <c r="BP23" t="n">
-        <v>3.57</v>
+        <v>3.6</v>
       </c>
       <c r="BQ23" t="n">
-        <v>4.29</v>
+        <v>4.27</v>
       </c>
       <c r="BR23" t="n">
-        <v>78.56999999999999</v>
+        <v>80</v>
       </c>
       <c r="BS23" t="n">
-        <v>42.86</v>
+        <v>46.67</v>
       </c>
       <c r="BT23" t="n">
-        <v>28.57</v>
+        <v>33.33</v>
       </c>
       <c r="BU23" t="n">
-        <v>21.43</v>
+        <v>20</v>
       </c>
       <c r="BV23" t="n">
         <v>0</v>
@@ -10064,19 +10064,19 @@
         <v>0</v>
       </c>
       <c r="BX23" t="n">
-        <v>42.86</v>
+        <v>46.67</v>
       </c>
       <c r="BY23" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="BZ23" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="CA23" t="n">
-        <v>3.16</v>
+        <v>3.19</v>
       </c>
       <c r="CB23" t="n">
-        <v>3.3</v>
+        <v>3.32</v>
       </c>
       <c r="CC23" t="n">
         <v>3.09</v>
@@ -10088,10 +10088,10 @@
         <v>1.47</v>
       </c>
       <c r="CF23" t="n">
-        <v>3.24</v>
+        <v>3.22</v>
       </c>
       <c r="CG23" t="n">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="CH23" t="n">
         <v>1.32</v>
@@ -10103,34 +10103,34 @@
         <v>1.99</v>
       </c>
       <c r="CK23" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CL23" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="CM23" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="CN23" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CO23" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CP23" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="CQ23" t="n">
-        <v>4.23</v>
+        <v>4.19</v>
       </c>
       <c r="CR23" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CS23" t="n">
-        <v>3.18</v>
+        <v>3.19</v>
       </c>
       <c r="CT23" t="n">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="CU23" t="n">
         <v>1.37</v>
@@ -10139,70 +10139,70 @@
         <v>1.83</v>
       </c>
       <c r="CW23" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="CX23" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="CY23" t="n">
-        <v>2.24</v>
+        <v>2.21</v>
       </c>
       <c r="CZ23" t="n">
-        <v>2.06</v>
+        <v>2.09</v>
       </c>
       <c r="DA23" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="DB23" t="n">
         <v>1.45</v>
       </c>
       <c r="DC23" t="n">
-        <v>2.43</v>
+        <v>2.41</v>
       </c>
       <c r="DD23" t="n">
-        <v>4.63</v>
+        <v>4.57</v>
       </c>
       <c r="DE23" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DF23" t="n">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="DG23" t="n">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="DH23" t="n">
-        <v>94.36</v>
+        <v>93.13</v>
       </c>
       <c r="DI23" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DJ23" t="n">
-        <v>2.22</v>
+        <v>2.13</v>
       </c>
       <c r="DK23" t="n">
-        <v>4</v>
+        <v>4.07</v>
       </c>
       <c r="DL23" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DM23" t="n">
-        <v>36.86</v>
+        <v>36.53</v>
       </c>
       <c r="DN23" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="DO23" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="DP23" t="n">
-        <v>12.93</v>
+        <v>13.14</v>
       </c>
       <c r="DQ23" t="n">
-        <v>18.57</v>
+        <v>18.4</v>
       </c>
       <c r="DR23" t="n">
-        <v>7.57</v>
+        <v>7.46</v>
       </c>
       <c r="DS23" t="n">
         <v>0</v>
@@ -10214,28 +10214,28 @@
         <v>0</v>
       </c>
       <c r="DV23" t="n">
-        <v>56.5</v>
+        <v>56.73</v>
       </c>
       <c r="DW23" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DX23" t="n">
-        <v>11.5</v>
+        <v>11.4</v>
       </c>
       <c r="DY23" t="n">
-        <v>7.64</v>
+        <v>7.6</v>
       </c>
       <c r="DZ23" t="n">
-        <v>3.86</v>
+        <v>3.8</v>
       </c>
       <c r="EA23" t="n">
-        <v>18.5</v>
+        <v>18.47</v>
       </c>
       <c r="EB23" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="EC23" t="n">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Spain_Segunda_División_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Spain_Segunda_División_2025-2026.xlsx
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C3" t="n">
         <v>7</v>
       </c>
       <c r="D3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E3" t="n">
         <v>0.14</v>
@@ -1875,136 +1875,136 @@
         <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="AI3" t="n">
-        <v>102.5</v>
+        <v>94.56999999999999</v>
       </c>
       <c r="AJ3" t="n">
         <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>3.33</v>
+        <v>3.43</v>
       </c>
       <c r="AL3" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="AM3" t="n">
         <v>0</v>
       </c>
       <c r="AN3" t="n">
-        <v>42.5</v>
+        <v>39.43</v>
       </c>
       <c r="AO3" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AQ3" t="n">
-        <v>13.83</v>
+        <v>14.29</v>
       </c>
       <c r="AR3" t="n">
-        <v>15.83</v>
+        <v>14.71</v>
       </c>
       <c r="AS3" t="n">
-        <v>7.5</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AX3" t="n">
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>53.17</v>
+        <v>51.57</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="BA3" t="n">
-        <v>13.17</v>
+        <v>12.29</v>
       </c>
       <c r="BB3" t="n">
-        <v>9.83</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="BC3" t="n">
-        <v>3.33</v>
+        <v>3.43</v>
       </c>
       <c r="BD3" t="n">
-        <v>21.17</v>
+        <v>20</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="BF3" t="n">
-        <v>3.17</v>
+        <v>3.29</v>
       </c>
       <c r="BG3" t="n">
-        <v>3.38</v>
+        <v>3.36</v>
       </c>
       <c r="BH3" t="n">
-        <v>10.15</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.38</v>
+        <v>3.36</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="BL3" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="BN3" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="BP3" t="n">
-        <v>4.62</v>
+        <v>4.36</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5.46</v>
+        <v>5.36</v>
       </c>
       <c r="BR3" t="n">
         <v>100</v>
       </c>
       <c r="BS3" t="n">
-        <v>76.92</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="BT3" t="n">
-        <v>61.54</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="BU3" t="n">
-        <v>46.15</v>
+        <v>42.86</v>
       </c>
       <c r="BV3" t="n">
-        <v>23.08</v>
+        <v>21.43</v>
       </c>
       <c r="BW3" t="n">
-        <v>15.38</v>
+        <v>14.29</v>
       </c>
       <c r="BX3" t="n">
-        <v>69.23</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="BY3" t="n">
         <v>1.69</v>
@@ -2013,34 +2013,34 @@
         <v>1.76</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.51</v>
+        <v>3.47</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.72</v>
+        <v>3.68</v>
       </c>
       <c r="CC3" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="CD3" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="CE3" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.61</v>
+        <v>2.63</v>
       </c>
       <c r="CG3" t="n">
-        <v>2.99</v>
+        <v>2.97</v>
       </c>
       <c r="CH3" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CI3" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="CJ3" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="CK3" t="n">
         <v>1.49</v>
@@ -2049,19 +2049,19 @@
         <v>1.89</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="CN3" t="n">
         <v>1.91</v>
       </c>
       <c r="CO3" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="CP3" t="n">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="CQ3" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="CR3" t="n">
         <v>1.38</v>
@@ -2076,106 +2076,106 @@
         <v>1.47</v>
       </c>
       <c r="CV3" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="CW3" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="CX3" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="CY3" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="CZ3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="DA3" t="n">
         <v>1.9</v>
       </c>
-      <c r="CZ3" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="DA3" t="n">
-        <v>1.91</v>
-      </c>
       <c r="DB3" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="DC3" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="DD3" t="n">
-        <v>3.08</v>
+        <v>3.16</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="DG3" t="n">
-        <v>2.92</v>
+        <v>2.72</v>
       </c>
       <c r="DH3" t="n">
-        <v>98.92</v>
+        <v>95.22</v>
       </c>
       <c r="DI3" t="n">
         <v>0</v>
       </c>
       <c r="DJ3" t="n">
-        <v>3</v>
+        <v>3.07</v>
       </c>
       <c r="DK3" t="n">
-        <v>6</v>
+        <v>5.57</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.31</v>
+        <v>0.28</v>
       </c>
       <c r="DM3" t="n">
-        <v>47.23</v>
+        <v>45.36</v>
       </c>
       <c r="DN3" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="DO3" t="n">
-        <v>3</v>
+        <v>2.78</v>
       </c>
       <c r="DP3" t="n">
-        <v>13.77</v>
+        <v>14</v>
       </c>
       <c r="DQ3" t="n">
-        <v>12.85</v>
+        <v>12.5</v>
       </c>
       <c r="DR3" t="n">
-        <v>7.54</v>
+        <v>7.86</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.31</v>
+        <v>0.28</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.31</v>
+        <v>0.28</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>54.08</v>
+        <v>53.22</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DX3" t="n">
-        <v>16.38</v>
+        <v>15.72</v>
       </c>
       <c r="DY3" t="n">
-        <v>10.46</v>
+        <v>9.93</v>
       </c>
       <c r="DZ3" t="n">
-        <v>5.92</v>
+        <v>5.79</v>
       </c>
       <c r="EA3" t="n">
-        <v>18.77</v>
+        <v>18.36</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.79</v>
+        <v>1.72</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.77</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="4">
@@ -2185,94 +2185,94 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D4" t="n">
         <v>7</v>
       </c>
       <c r="E4" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="F4" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="G4" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="H4" t="n">
-        <v>92.56999999999999</v>
+        <v>94.5</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="K4" t="n">
-        <v>3.43</v>
+        <v>3.75</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>45</v>
+        <v>47.12</v>
       </c>
       <c r="N4" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="O4" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="P4" t="n">
-        <v>13.43</v>
+        <v>13.88</v>
       </c>
       <c r="Q4" t="n">
-        <v>14.57</v>
+        <v>14.75</v>
       </c>
       <c r="R4" t="n">
-        <v>8.140000000000001</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="S4" t="n">
-        <v>0.57</v>
+        <v>0.75</v>
       </c>
       <c r="T4" t="n">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="U4" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="V4" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>49.29</v>
+        <v>49.62</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>10.57</v>
+        <v>10.38</v>
       </c>
       <c r="AA4" t="n">
-        <v>7.43</v>
+        <v>7.5</v>
       </c>
       <c r="AB4" t="n">
-        <v>3.14</v>
+        <v>2.88</v>
       </c>
       <c r="AC4" t="n">
-        <v>26.43</v>
+        <v>26.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AE4" t="n">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="AF4" t="n">
         <v>0.14</v>
@@ -2356,64 +2356,64 @@
         <v>2.29</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="BH4" t="n">
-        <v>7.71</v>
+        <v>7.8</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="BO4" t="n">
         <v>1.07</v>
       </c>
       <c r="BP4" t="n">
-        <v>3.86</v>
+        <v>3.8</v>
       </c>
       <c r="BQ4" t="n">
-        <v>3.86</v>
+        <v>4</v>
       </c>
       <c r="BR4" t="n">
-        <v>78.56999999999999</v>
+        <v>80</v>
       </c>
       <c r="BS4" t="n">
-        <v>64.29000000000001</v>
+        <v>66.67</v>
       </c>
       <c r="BT4" t="n">
-        <v>50</v>
+        <v>46.67</v>
       </c>
       <c r="BU4" t="n">
-        <v>21.43</v>
+        <v>20</v>
       </c>
       <c r="BV4" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="BW4" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BX4" t="n">
-        <v>57.14</v>
+        <v>53.33</v>
       </c>
       <c r="BY4" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="BZ4" t="n">
-        <v>2.27</v>
+        <v>2.29</v>
       </c>
       <c r="CA4" t="n">
         <v>3.01</v>
@@ -2431,25 +2431,25 @@
         <v>1.55</v>
       </c>
       <c r="CF4" t="n">
-        <v>3.49</v>
+        <v>3.47</v>
       </c>
       <c r="CG4" t="n">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="CH4" t="n">
         <v>1.26</v>
       </c>
       <c r="CI4" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CJ4" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="CK4" t="n">
         <v>1.74</v>
       </c>
       <c r="CL4" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="CM4" t="n">
         <v>2.02</v>
@@ -2458,127 +2458,127 @@
         <v>1.63</v>
       </c>
       <c r="CO4" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CP4" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="CQ4" t="n">
-        <v>4.9</v>
+        <v>4.84</v>
       </c>
       <c r="CR4" t="n">
         <v>1.6</v>
       </c>
       <c r="CS4" t="n">
-        <v>3.39</v>
+        <v>3.4</v>
       </c>
       <c r="CT4" t="n">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="CU4" t="n">
         <v>1.33</v>
       </c>
       <c r="CV4" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="CW4" t="n">
-        <v>2.27</v>
+        <v>2.24</v>
       </c>
       <c r="CX4" t="n">
         <v>1.8</v>
       </c>
       <c r="CY4" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="CZ4" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="DA4" t="n">
         <v>1.61</v>
       </c>
       <c r="DB4" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="DC4" t="n">
-        <v>2.74</v>
+        <v>2.71</v>
       </c>
       <c r="DD4" t="n">
-        <v>5.53</v>
+        <v>5.43</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="DG4" t="n">
-        <v>1.86</v>
+        <v>1.94</v>
       </c>
       <c r="DH4" t="n">
-        <v>88.86</v>
+        <v>90.13</v>
       </c>
       <c r="DI4" t="n">
         <v>0</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.64</v>
+        <v>2.73</v>
       </c>
       <c r="DK4" t="n">
-        <v>3.64</v>
+        <v>3.8</v>
       </c>
       <c r="DL4" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DM4" t="n">
-        <v>42.22</v>
+        <v>43.53</v>
       </c>
       <c r="DN4" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="DO4" t="n">
-        <v>1.78</v>
+        <v>1.87</v>
       </c>
       <c r="DP4" t="n">
-        <v>13.57</v>
+        <v>13.8</v>
       </c>
       <c r="DQ4" t="n">
-        <v>14.07</v>
+        <v>14.2</v>
       </c>
       <c r="DR4" t="n">
-        <v>8.779999999999999</v>
+        <v>9</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>47.72</v>
+        <v>48</v>
       </c>
       <c r="DW4" t="n">
         <v>0</v>
       </c>
       <c r="DX4" t="n">
-        <v>9.720000000000001</v>
+        <v>9.67</v>
       </c>
       <c r="DY4" t="n">
-        <v>6.57</v>
+        <v>6.66</v>
       </c>
       <c r="DZ4" t="n">
-        <v>3.14</v>
+        <v>3</v>
       </c>
       <c r="EA4" t="n">
-        <v>24.43</v>
+        <v>24.6</v>
       </c>
       <c r="EB4" t="n">
         <v>1.14</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.64</v>
+        <v>2.73</v>
       </c>
     </row>
     <row r="5">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C6" t="n">
         <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E6" t="n">
         <v>0.17</v>
@@ -3081,139 +3081,139 @@
         <v>2.5</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.86</v>
+        <v>1.62</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.43</v>
+        <v>1.62</v>
       </c>
       <c r="AI6" t="n">
-        <v>82.14</v>
+        <v>80.12</v>
       </c>
       <c r="AJ6" t="n">
         <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.86</v>
+        <v>2.5</v>
       </c>
       <c r="AL6" t="n">
-        <v>3.14</v>
+        <v>3.25</v>
       </c>
       <c r="AM6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>34</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>12.62</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>13.75</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>9.380000000000001</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>47.75</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>6.62</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>19.75</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>8.859999999999999</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="BL6" t="n">
         <v>0.57</v>
       </c>
-      <c r="AN6" t="n">
-        <v>33.57</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>13</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>13.86</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>9.289999999999999</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>47.14</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>8.140000000000001</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>6.29</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>19.57</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>8.92</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>0.54</v>
-      </c>
       <c r="BM6" t="n">
-        <v>0.31</v>
+        <v>0.36</v>
       </c>
       <c r="BN6" t="n">
-        <v>0.85</v>
+        <v>0.93</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="BP6" t="n">
-        <v>3.54</v>
+        <v>3.5</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.38</v>
+        <v>5.36</v>
       </c>
       <c r="BR6" t="n">
-        <v>84.62</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BS6" t="n">
-        <v>53.85</v>
+        <v>57.14</v>
       </c>
       <c r="BT6" t="n">
-        <v>38.46</v>
+        <v>42.86</v>
       </c>
       <c r="BU6" t="n">
-        <v>15.38</v>
+        <v>14.29</v>
       </c>
       <c r="BV6" t="n">
-        <v>15.38</v>
+        <v>14.29</v>
       </c>
       <c r="BW6" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BX6" t="n">
-        <v>30.77</v>
+        <v>35.71</v>
       </c>
       <c r="BY6" t="n">
         <v>2.34</v>
@@ -3222,25 +3222,25 @@
         <v>2.52</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.27</v>
+        <v>3.29</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.38</v>
+        <v>3.4</v>
       </c>
       <c r="CC6" t="n">
-        <v>4.22</v>
+        <v>4.26</v>
       </c>
       <c r="CD6" t="n">
-        <v>4.63</v>
+        <v>4.67</v>
       </c>
       <c r="CE6" t="n">
         <v>1.44</v>
       </c>
       <c r="CF6" t="n">
-        <v>3</v>
+        <v>3.01</v>
       </c>
       <c r="CG6" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="CH6" t="n">
         <v>1.36</v>
@@ -3252,13 +3252,13 @@
         <v>1.94</v>
       </c>
       <c r="CK6" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CL6" t="n">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="CN6" t="n">
         <v>1.67</v>
@@ -3267,19 +3267,19 @@
         <v>1.36</v>
       </c>
       <c r="CP6" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="CQ6" t="n">
-        <v>3.9</v>
+        <v>3.89</v>
       </c>
       <c r="CR6" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CS6" t="n">
         <v>3.12</v>
       </c>
       <c r="CT6" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="CU6" t="n">
         <v>1.4</v>
@@ -3297,94 +3297,94 @@
         <v>2.1</v>
       </c>
       <c r="CZ6" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="DA6" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="DB6" t="n">
         <v>1.37</v>
       </c>
       <c r="DC6" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="DD6" t="n">
-        <v>3.99</v>
+        <v>3.95</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.46</v>
+        <v>1.35</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="DH6" t="n">
-        <v>94.92</v>
+        <v>92.84999999999999</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.69</v>
+        <v>2.5</v>
       </c>
       <c r="DK6" t="n">
-        <v>4.38</v>
+        <v>4.36</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="DM6" t="n">
-        <v>46.46</v>
+        <v>45.79</v>
       </c>
       <c r="DN6" t="n">
-        <v>1.16</v>
+        <v>1.07</v>
       </c>
       <c r="DO6" t="n">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="DP6" t="n">
-        <v>13.46</v>
+        <v>13.21</v>
       </c>
       <c r="DQ6" t="n">
-        <v>13.62</v>
+        <v>13.57</v>
       </c>
       <c r="DR6" t="n">
-        <v>7.39</v>
+        <v>7.58</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>52.15</v>
+        <v>52.14</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DX6" t="n">
-        <v>9.77</v>
+        <v>10</v>
       </c>
       <c r="DY6" t="n">
-        <v>7</v>
+        <v>7.14</v>
       </c>
       <c r="DZ6" t="n">
-        <v>2.77</v>
+        <v>2.85</v>
       </c>
       <c r="EA6" t="n">
-        <v>20.38</v>
+        <v>20.43</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.46</v>
+        <v>2.28</v>
       </c>
     </row>
     <row r="7">
@@ -3394,13 +3394,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C7" t="n">
         <v>7</v>
       </c>
       <c r="D7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -3484,139 +3484,139 @@
         <v>1</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AH7" t="n">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="AI7" t="n">
-        <v>73.56999999999999</v>
+        <v>75.25</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AK7" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AL7" t="n">
-        <v>3</v>
+        <v>3.38</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.29</v>
+        <v>0.5</v>
       </c>
       <c r="AN7" t="n">
-        <v>33</v>
+        <v>33.25</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="AP7" t="n">
-        <v>0.71</v>
+        <v>1.12</v>
       </c>
       <c r="AQ7" t="n">
-        <v>13</v>
+        <v>12.88</v>
       </c>
       <c r="AR7" t="n">
-        <v>12.43</v>
+        <v>12.25</v>
       </c>
       <c r="AS7" t="n">
-        <v>9.140000000000001</v>
+        <v>10</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AX7" t="n">
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>42.43</v>
+        <v>43.25</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="BA7" t="n">
-        <v>11.71</v>
+        <v>12</v>
       </c>
       <c r="BB7" t="n">
-        <v>6.71</v>
+        <v>6.75</v>
       </c>
       <c r="BC7" t="n">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="BD7" t="n">
-        <v>17.43</v>
+        <v>16.62</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="BH7" t="n">
-        <v>8.210000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.57</v>
+        <v>0.6</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.71</v>
+        <v>0.8</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="BP7" t="n">
-        <v>3.43</v>
+        <v>3.73</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.79</v>
+        <v>5.07</v>
       </c>
       <c r="BR7" t="n">
-        <v>85.70999999999999</v>
+        <v>86.67</v>
       </c>
       <c r="BS7" t="n">
-        <v>42.86</v>
+        <v>46.67</v>
       </c>
       <c r="BT7" t="n">
-        <v>42.86</v>
+        <v>46.67</v>
       </c>
       <c r="BU7" t="n">
-        <v>35.71</v>
+        <v>33.33</v>
       </c>
       <c r="BV7" t="n">
-        <v>28.57</v>
+        <v>26.67</v>
       </c>
       <c r="BW7" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="BX7" t="n">
-        <v>28.57</v>
+        <v>33.33</v>
       </c>
       <c r="BY7" t="n">
         <v>2.68</v>
@@ -3625,34 +3625,34 @@
         <v>2.82</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.44</v>
+        <v>3.41</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.6</v>
+        <v>3.57</v>
       </c>
       <c r="CC7" t="n">
-        <v>5.21</v>
+        <v>4.98</v>
       </c>
       <c r="CD7" t="n">
-        <v>5.79</v>
+        <v>5.54</v>
       </c>
       <c r="CE7" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.84</v>
+        <v>2.81</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CI7" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CJ7" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CK7" t="n">
         <v>1.58</v>
@@ -3667,127 +3667,127 @@
         <v>1.8</v>
       </c>
       <c r="CO7" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="CP7" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="CQ7" t="n">
-        <v>3.53</v>
+        <v>3.57</v>
       </c>
       <c r="CR7" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="CS7" t="n">
-        <v>3.07</v>
+        <v>3.1</v>
       </c>
       <c r="CT7" t="n">
-        <v>2.93</v>
+        <v>2.9</v>
       </c>
       <c r="CU7" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CV7" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CW7" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CX7" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CY7" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="CZ7" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="DA7" t="n">
         <v>1.8</v>
       </c>
       <c r="DB7" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="DC7" t="n">
-        <v>2.08</v>
+        <v>2.11</v>
       </c>
       <c r="DD7" t="n">
-        <v>3.67</v>
+        <v>3.74</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="DG7" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="DH7" t="n">
+        <v>82.8</v>
+      </c>
+      <c r="DI7" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="DJ7" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="DK7" t="n">
+        <v>4.07</v>
+      </c>
+      <c r="DL7" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="DM7" t="n">
+        <v>37.27</v>
+      </c>
+      <c r="DN7" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="DO7" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="DP7" t="n">
+        <v>13.07</v>
+      </c>
+      <c r="DQ7" t="n">
+        <v>12.13</v>
+      </c>
+      <c r="DR7" t="n">
+        <v>9.07</v>
+      </c>
+      <c r="DS7" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="DT7" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="DU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV7" t="n">
+        <v>46.93</v>
+      </c>
+      <c r="DW7" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="DX7" t="n">
+        <v>11.27</v>
+      </c>
+      <c r="DY7" t="n">
+        <v>7.13</v>
+      </c>
+      <c r="DZ7" t="n">
+        <v>4.13</v>
+      </c>
+      <c r="EA7" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="EB7" t="n">
         <v>1.28</v>
       </c>
-      <c r="DG7" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="DH7" t="n">
-        <v>82.5</v>
-      </c>
-      <c r="DI7" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="DJ7" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="DK7" t="n">
-        <v>3.93</v>
-      </c>
-      <c r="DL7" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="DM7" t="n">
-        <v>37.43</v>
-      </c>
-      <c r="DN7" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="DO7" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="DP7" t="n">
-        <v>13.14</v>
-      </c>
-      <c r="DQ7" t="n">
-        <v>12.22</v>
-      </c>
-      <c r="DR7" t="n">
-        <v>8.57</v>
-      </c>
-      <c r="DS7" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="DT7" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="DU7" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV7" t="n">
-        <v>46.78</v>
-      </c>
-      <c r="DW7" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="DX7" t="n">
-        <v>11.07</v>
-      </c>
-      <c r="DY7" t="n">
-        <v>7.14</v>
-      </c>
-      <c r="DZ7" t="n">
-        <v>3.93</v>
-      </c>
-      <c r="EA7" t="n">
-        <v>18.07</v>
-      </c>
-      <c r="EB7" t="n">
-        <v>1.25</v>
-      </c>
       <c r="EC7" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="8">
@@ -3797,10 +3797,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D8" t="n">
         <v>7</v>
@@ -3809,49 +3809,49 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>2.43</v>
+        <v>2.25</v>
       </c>
       <c r="G8" t="n">
-        <v>2.71</v>
+        <v>3.25</v>
       </c>
       <c r="H8" t="n">
-        <v>101</v>
+        <v>99.25</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>3.14</v>
+        <v>2.88</v>
       </c>
       <c r="K8" t="n">
-        <v>5.14</v>
+        <v>5.88</v>
       </c>
       <c r="L8" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="M8" t="n">
-        <v>50.71</v>
+        <v>52.62</v>
       </c>
       <c r="N8" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="O8" t="n">
-        <v>2.43</v>
+        <v>2.62</v>
       </c>
       <c r="P8" t="n">
-        <v>13.71</v>
+        <v>13.38</v>
       </c>
       <c r="Q8" t="n">
-        <v>14</v>
+        <v>13.62</v>
       </c>
       <c r="R8" t="n">
-        <v>7.71</v>
+        <v>7.25</v>
       </c>
       <c r="S8" t="n">
-        <v>0.57</v>
+        <v>0.75</v>
       </c>
       <c r="T8" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
@@ -3863,28 +3863,28 @@
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>53.71</v>
+        <v>53.38</v>
       </c>
       <c r="Y8" t="n">
         <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>10.86</v>
+        <v>11.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>8.140000000000001</v>
+        <v>8.25</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.71</v>
+        <v>3.25</v>
       </c>
       <c r="AC8" t="n">
-        <v>19.57</v>
+        <v>19.75</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="AE8" t="n">
-        <v>3.14</v>
+        <v>2.88</v>
       </c>
       <c r="AF8" t="n">
         <v>0.14</v>
@@ -3968,70 +3968,70 @@
         <v>2.14</v>
       </c>
       <c r="BG8" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="BH8" t="n">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="BI8" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.43</v>
+        <v>0.47</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.29</v>
+        <v>0.4</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="BN8" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.71</v>
+        <v>0.87</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.29</v>
+        <v>4.53</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.21</v>
+        <v>5.47</v>
       </c>
       <c r="BR8" t="n">
-        <v>71.43000000000001</v>
+        <v>73.33</v>
       </c>
       <c r="BS8" t="n">
-        <v>35.71</v>
+        <v>40</v>
       </c>
       <c r="BT8" t="n">
-        <v>28.57</v>
+        <v>33.33</v>
       </c>
       <c r="BU8" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="BV8" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BW8" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BX8" t="n">
-        <v>28.57</v>
+        <v>33.33</v>
       </c>
       <c r="BY8" t="n">
         <v>2.1</v>
       </c>
       <c r="BZ8" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.1</v>
+        <v>3.09</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.28</v>
+        <v>3.27</v>
       </c>
       <c r="CC8" t="n">
         <v>3.68</v>
@@ -4040,13 +4040,13 @@
         <v>4.06</v>
       </c>
       <c r="CE8" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="CF8" t="n">
         <v>3.24</v>
       </c>
       <c r="CG8" t="n">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="CH8" t="n">
         <v>1.31</v>
@@ -4058,19 +4058,19 @@
         <v>2.02</v>
       </c>
       <c r="CK8" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="CL8" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="CM8" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="CN8" t="n">
         <v>1.68</v>
       </c>
-      <c r="CL8" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="CM8" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="CN8" t="n">
-        <v>1.67</v>
-      </c>
       <c r="CO8" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CP8" t="n">
         <v>2.31</v>
@@ -4082,13 +4082,13 @@
         <v>1.52</v>
       </c>
       <c r="CS8" t="n">
-        <v>3.21</v>
+        <v>3.22</v>
       </c>
       <c r="CT8" t="n">
-        <v>2.66</v>
+        <v>2.65</v>
       </c>
       <c r="CU8" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CV8" t="n">
         <v>1.84</v>
@@ -4103,7 +4103,7 @@
         <v>2.09</v>
       </c>
       <c r="CZ8" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="DA8" t="n">
         <v>1.73</v>
@@ -4121,43 +4121,43 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="DF8" t="n">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.43</v>
+        <v>2.73</v>
       </c>
       <c r="DH8" t="n">
-        <v>91.22</v>
+        <v>90.93000000000001</v>
       </c>
       <c r="DI8" t="n">
         <v>0</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.64</v>
+        <v>2.53</v>
       </c>
       <c r="DK8" t="n">
-        <v>4.64</v>
+        <v>5.07</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.14</v>
+        <v>0.2</v>
       </c>
       <c r="DM8" t="n">
-        <v>39.71</v>
+        <v>41.46</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.22</v>
+        <v>2.33</v>
       </c>
       <c r="DP8" t="n">
-        <v>14.07</v>
+        <v>13.87</v>
       </c>
       <c r="DQ8" t="n">
-        <v>13.64</v>
+        <v>13.47</v>
       </c>
       <c r="DR8" t="n">
-        <v>9.140000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="DS8" t="n">
         <v>0</v>
@@ -4169,28 +4169,28 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>48.42</v>
+        <v>48.6</v>
       </c>
       <c r="DW8" t="n">
         <v>0</v>
       </c>
       <c r="DX8" t="n">
-        <v>9.5</v>
+        <v>9.93</v>
       </c>
       <c r="DY8" t="n">
-        <v>7</v>
+        <v>7.13</v>
       </c>
       <c r="DZ8" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="EA8" t="n">
-        <v>19.93</v>
+        <v>20</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="EC8" t="n">
-        <v>2.64</v>
+        <v>2.53</v>
       </c>
     </row>
     <row r="9">
@@ -4200,13 +4200,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C9" t="n">
         <v>7</v>
       </c>
       <c r="D9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E9" t="n">
         <v>0.14</v>
@@ -4290,52 +4290,52 @@
         <v>2.86</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.86</v>
+        <v>2.38</v>
       </c>
       <c r="AI9" t="n">
-        <v>91.86</v>
+        <v>91.5</v>
       </c>
       <c r="AJ9" t="n">
-        <v>-0.14</v>
+        <v>-0.12</v>
       </c>
       <c r="AK9" t="n">
-        <v>3.29</v>
+        <v>3.5</v>
       </c>
       <c r="AL9" t="n">
-        <v>3.71</v>
+        <v>4.25</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AN9" t="n">
         <v>40</v>
       </c>
       <c r="AO9" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="AQ9" t="n">
-        <v>16.43</v>
+        <v>16.88</v>
       </c>
       <c r="AR9" t="n">
-        <v>15.14</v>
+        <v>14.62</v>
       </c>
       <c r="AS9" t="n">
-        <v>7.29</v>
+        <v>7.12</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AV9" t="n">
         <v>0</v>
@@ -4347,73 +4347,73 @@
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>52.43</v>
+        <v>52.25</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="BA9" t="n">
-        <v>13</v>
+        <v>12.75</v>
       </c>
       <c r="BB9" t="n">
-        <v>8.43</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="BC9" t="n">
-        <v>4.57</v>
+        <v>4.62</v>
       </c>
       <c r="BD9" t="n">
-        <v>23</v>
+        <v>22.88</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="BF9" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.71</v>
+        <v>2.67</v>
       </c>
       <c r="BH9" t="n">
-        <v>8.93</v>
+        <v>9.33</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.71</v>
+        <v>2.67</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.29</v>
+        <v>4.33</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.64</v>
+        <v>5</v>
       </c>
       <c r="BR9" t="n">
-        <v>92.86</v>
+        <v>93.33</v>
       </c>
       <c r="BS9" t="n">
-        <v>78.56999999999999</v>
+        <v>80</v>
       </c>
       <c r="BT9" t="n">
-        <v>57.14</v>
+        <v>53.33</v>
       </c>
       <c r="BU9" t="n">
-        <v>42.86</v>
+        <v>40</v>
       </c>
       <c r="BV9" t="n">
         <v>0</v>
@@ -4422,7 +4422,7 @@
         <v>0</v>
       </c>
       <c r="BX9" t="n">
-        <v>71.43000000000001</v>
+        <v>73.33</v>
       </c>
       <c r="BY9" t="n">
         <v>2.14</v>
@@ -4431,25 +4431,25 @@
         <v>2.15</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.29</v>
+        <v>3.28</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.45</v>
+        <v>3.44</v>
       </c>
       <c r="CC9" t="n">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="CD9" t="n">
         <v>3.3</v>
       </c>
       <c r="CE9" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.71</v>
+        <v>2.72</v>
       </c>
       <c r="CG9" t="n">
-        <v>2.96</v>
+        <v>2.95</v>
       </c>
       <c r="CH9" t="n">
         <v>1.42</v>
@@ -4458,16 +4458,16 @@
         <v>2.08</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="CK9" t="n">
         <v>1.52</v>
       </c>
       <c r="CL9" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="CN9" t="n">
         <v>1.88</v>
@@ -4476,19 +4476,19 @@
         <v>1.26</v>
       </c>
       <c r="CP9" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="CQ9" t="n">
-        <v>3.1</v>
+        <v>3.12</v>
       </c>
       <c r="CR9" t="n">
         <v>1.41</v>
       </c>
       <c r="CS9" t="n">
-        <v>2.96</v>
+        <v>2.97</v>
       </c>
       <c r="CT9" t="n">
-        <v>3.02</v>
+        <v>3.01</v>
       </c>
       <c r="CU9" t="n">
         <v>1.43</v>
@@ -4506,7 +4506,7 @@
         <v>1.93</v>
       </c>
       <c r="CZ9" t="n">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="DA9" t="n">
         <v>1.88</v>
@@ -4515,85 +4515,85 @@
         <v>1.29</v>
       </c>
       <c r="DC9" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="DD9" t="n">
-        <v>3.32</v>
+        <v>3.34</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.78</v>
+        <v>1.87</v>
       </c>
       <c r="DG9" t="n">
-        <v>2.36</v>
+        <v>2.6</v>
       </c>
       <c r="DH9" t="n">
-        <v>97.58</v>
+        <v>97</v>
       </c>
       <c r="DI9" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.06</v>
       </c>
       <c r="DJ9" t="n">
-        <v>3.22</v>
+        <v>3.33</v>
       </c>
       <c r="DK9" t="n">
-        <v>4.42</v>
+        <v>4.67</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DM9" t="n">
-        <v>47.57</v>
+        <v>47.07</v>
       </c>
       <c r="DN9" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="DO9" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="DP9" t="n">
-        <v>16.07</v>
+        <v>16.33</v>
       </c>
       <c r="DQ9" t="n">
-        <v>14.42</v>
+        <v>14.2</v>
       </c>
       <c r="DR9" t="n">
-        <v>6.21</v>
+        <v>6.2</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>54.28</v>
+        <v>54.07</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DX9" t="n">
-        <v>14.64</v>
+        <v>14.4</v>
       </c>
       <c r="DY9" t="n">
-        <v>9.859999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="DZ9" t="n">
-        <v>4.79</v>
+        <v>4.8</v>
       </c>
       <c r="EA9" t="n">
         <v>22.14</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.93</v>
+        <v>3.07</v>
       </c>
     </row>
     <row r="10">
@@ -4603,94 +4603,94 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D10" t="n">
         <v>8</v>
       </c>
       <c r="E10" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="F10" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="G10" t="n">
-        <v>2.33</v>
+        <v>2.29</v>
       </c>
       <c r="H10" t="n">
-        <v>99.33</v>
+        <v>98.14</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="K10" t="n">
-        <v>3.83</v>
+        <v>3.86</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="M10" t="n">
-        <v>44.5</v>
+        <v>44.29</v>
       </c>
       <c r="N10" t="n">
         <v>1</v>
       </c>
       <c r="O10" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="P10" t="n">
-        <v>12.83</v>
+        <v>12.86</v>
       </c>
       <c r="Q10" t="n">
-        <v>12.83</v>
+        <v>12.43</v>
       </c>
       <c r="R10" t="n">
-        <v>5.67</v>
+        <v>6.57</v>
       </c>
       <c r="S10" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="T10" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="U10" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="V10" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>53.33</v>
+        <v>52.57</v>
       </c>
       <c r="Y10" t="n">
         <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>12.33</v>
+        <v>12.86</v>
       </c>
       <c r="AA10" t="n">
-        <v>8.17</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="AB10" t="n">
-        <v>4.17</v>
+        <v>4.57</v>
       </c>
       <c r="AC10" t="n">
-        <v>19.83</v>
+        <v>18.71</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="AF10" t="n">
         <v>0</v>
@@ -4774,70 +4774,70 @@
         <v>2.88</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
       <c r="BH10" t="n">
-        <v>8.289999999999999</v>
+        <v>8.27</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="BP10" t="n">
-        <v>4</v>
+        <v>3.93</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.29</v>
+        <v>4.33</v>
       </c>
       <c r="BR10" t="n">
-        <v>92.86</v>
+        <v>93.33</v>
       </c>
       <c r="BS10" t="n">
-        <v>85.70999999999999</v>
+        <v>86.67</v>
       </c>
       <c r="BT10" t="n">
-        <v>57.14</v>
+        <v>60</v>
       </c>
       <c r="BU10" t="n">
-        <v>35.71</v>
+        <v>33.33</v>
       </c>
       <c r="BV10" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BW10" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BX10" t="n">
-        <v>57.14</v>
+        <v>60</v>
       </c>
       <c r="BY10" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="BZ10" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.2</v>
+        <v>3.22</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.36</v>
+        <v>3.38</v>
       </c>
       <c r="CC10" t="n">
         <v>2.8</v>
@@ -4846,13 +4846,13 @@
         <v>2.85</v>
       </c>
       <c r="CE10" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.93</v>
+        <v>2.95</v>
       </c>
       <c r="CG10" t="n">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="CH10" t="n">
         <v>1.37</v>
@@ -4864,13 +4864,13 @@
         <v>1.83</v>
       </c>
       <c r="CK10" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CL10" t="n">
-        <v>2.09</v>
+        <v>2.12</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="CN10" t="n">
         <v>1.71</v>
@@ -4879,7 +4879,7 @@
         <v>1.33</v>
       </c>
       <c r="CP10" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="CQ10" t="n">
         <v>3.56</v>
@@ -4888,16 +4888,16 @@
         <v>1.46</v>
       </c>
       <c r="CS10" t="n">
-        <v>3.16</v>
+        <v>3.15</v>
       </c>
       <c r="CT10" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="CU10" t="n">
         <v>1.39</v>
       </c>
       <c r="CV10" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CW10" t="n">
         <v>1.88</v>
@@ -4906,97 +4906,97 @@
         <v>1.67</v>
       </c>
       <c r="CY10" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="CZ10" t="n">
         <v>2.18</v>
       </c>
       <c r="DA10" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="DB10" t="n">
         <v>1.35</v>
       </c>
       <c r="DC10" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="DD10" t="n">
-        <v>3.78</v>
+        <v>3.76</v>
       </c>
       <c r="DE10" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="DG10" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="DH10" t="n">
-        <v>87.43000000000001</v>
+        <v>87.67</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.5</v>
+        <v>4.47</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.22</v>
+        <v>0.27</v>
       </c>
       <c r="DM10" t="n">
-        <v>37.71</v>
+        <v>38.07</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.57</v>
+        <v>2.54</v>
       </c>
       <c r="DP10" t="n">
-        <v>12.36</v>
+        <v>12.4</v>
       </c>
       <c r="DQ10" t="n">
-        <v>12.5</v>
+        <v>12.33</v>
       </c>
       <c r="DR10" t="n">
-        <v>7.14</v>
+        <v>7.47</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>50.14</v>
+        <v>50</v>
       </c>
       <c r="DW10" t="n">
         <v>0</v>
       </c>
       <c r="DX10" t="n">
-        <v>12.71</v>
+        <v>12.93</v>
       </c>
       <c r="DY10" t="n">
-        <v>7.86</v>
+        <v>7.93</v>
       </c>
       <c r="DZ10" t="n">
-        <v>4.86</v>
+        <v>5</v>
       </c>
       <c r="EA10" t="n">
-        <v>16.57</v>
+        <v>16.26</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="EC10" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="11">
@@ -5409,61 +5409,61 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D12" t="n">
         <v>7</v>
       </c>
       <c r="E12" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="F12" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="G12" t="n">
-        <v>3.29</v>
+        <v>3.38</v>
       </c>
       <c r="H12" t="n">
-        <v>92</v>
+        <v>90.75</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="K12" t="n">
-        <v>5.86</v>
+        <v>6</v>
       </c>
       <c r="L12" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="M12" t="n">
-        <v>44.29</v>
+        <v>44.25</v>
       </c>
       <c r="N12" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="O12" t="n">
-        <v>2.57</v>
+        <v>2.62</v>
       </c>
       <c r="P12" t="n">
-        <v>12.71</v>
+        <v>12.5</v>
       </c>
       <c r="Q12" t="n">
-        <v>15.71</v>
+        <v>16.25</v>
       </c>
       <c r="R12" t="n">
-        <v>7.29</v>
+        <v>7.38</v>
       </c>
       <c r="S12" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="T12" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="U12" t="n">
         <v>0</v>
@@ -5475,28 +5475,28 @@
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>51.57</v>
+        <v>51.25</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="Z12" t="n">
-        <v>14.29</v>
+        <v>14.75</v>
       </c>
       <c r="AA12" t="n">
-        <v>10.86</v>
+        <v>10.88</v>
       </c>
       <c r="AB12" t="n">
-        <v>3.43</v>
+        <v>3.88</v>
       </c>
       <c r="AC12" t="n">
-        <v>22.29</v>
+        <v>22.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.43</v>
+        <v>1.62</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>
@@ -5580,64 +5580,64 @@
         <v>2.57</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="BH12" t="n">
-        <v>8.789999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="BP12" t="n">
-        <v>3.71</v>
+        <v>3.8</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.07</v>
+        <v>5.4</v>
       </c>
       <c r="BR12" t="n">
-        <v>78.56999999999999</v>
+        <v>80</v>
       </c>
       <c r="BS12" t="n">
-        <v>71.43000000000001</v>
+        <v>73.33</v>
       </c>
       <c r="BT12" t="n">
-        <v>57.14</v>
+        <v>53.33</v>
       </c>
       <c r="BU12" t="n">
-        <v>35.71</v>
+        <v>33.33</v>
       </c>
       <c r="BV12" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BW12" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BX12" t="n">
-        <v>57.14</v>
+        <v>60</v>
       </c>
       <c r="BY12" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="BZ12" t="n">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="CA12" t="n">
         <v>3.2</v>
@@ -5655,25 +5655,25 @@
         <v>1.46</v>
       </c>
       <c r="CF12" t="n">
-        <v>3.18</v>
+        <v>3.16</v>
       </c>
       <c r="CG12" t="n">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="CH12" t="n">
         <v>1.32</v>
       </c>
       <c r="CI12" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="CJ12" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CL12" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CM12" t="n">
         <v>2.19</v>
@@ -5685,37 +5685,37 @@
         <v>1.38</v>
       </c>
       <c r="CP12" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="CQ12" t="n">
-        <v>4.01</v>
+        <v>3.97</v>
       </c>
       <c r="CR12" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CS12" t="n">
-        <v>3.25</v>
+        <v>3.23</v>
       </c>
       <c r="CT12" t="n">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="CU12" t="n">
         <v>1.35</v>
       </c>
       <c r="CV12" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="CW12" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="CX12" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CY12" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="CZ12" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="DA12" t="n">
         <v>1.72</v>
@@ -5724,49 +5724,49 @@
         <v>1.42</v>
       </c>
       <c r="DC12" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="DD12" t="n">
-        <v>4.36</v>
+        <v>4.31</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.14</v>
+        <v>2.27</v>
       </c>
       <c r="DH12" t="n">
-        <v>91.15000000000001</v>
+        <v>90.54000000000001</v>
       </c>
       <c r="DI12" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="DK12" t="n">
-        <v>4.08</v>
+        <v>4.27</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="DM12" t="n">
-        <v>39.93</v>
+        <v>40.2</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="DO12" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="DP12" t="n">
-        <v>13.28</v>
+        <v>13.13</v>
       </c>
       <c r="DQ12" t="n">
-        <v>15.42</v>
+        <v>15.73</v>
       </c>
       <c r="DR12" t="n">
         <v>8.140000000000001</v>
@@ -5781,28 +5781,28 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>48.57</v>
+        <v>48.6</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="DX12" t="n">
-        <v>12.22</v>
+        <v>12.6</v>
       </c>
       <c r="DY12" t="n">
-        <v>8.779999999999999</v>
+        <v>8.93</v>
       </c>
       <c r="DZ12" t="n">
-        <v>3.43</v>
+        <v>3.67</v>
       </c>
       <c r="EA12" t="n">
-        <v>22.43</v>
+        <v>22.53</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="EC12" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
     </row>
     <row r="13">
@@ -5812,61 +5812,61 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D13" t="n">
         <v>8</v>
       </c>
       <c r="E13" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="F13" t="n">
-        <v>2.33</v>
+        <v>2.14</v>
       </c>
       <c r="G13" t="n">
-        <v>2.17</v>
+        <v>2.43</v>
       </c>
       <c r="H13" t="n">
-        <v>91.33</v>
+        <v>86.86</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>3.67</v>
+        <v>3.29</v>
       </c>
       <c r="K13" t="n">
-        <v>5.83</v>
+        <v>5.71</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>39</v>
+        <v>41.57</v>
       </c>
       <c r="N13" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="O13" t="n">
-        <v>3.67</v>
+        <v>3.29</v>
       </c>
       <c r="P13" t="n">
-        <v>14.67</v>
+        <v>13.71</v>
       </c>
       <c r="Q13" t="n">
-        <v>16.33</v>
+        <v>16.43</v>
       </c>
       <c r="R13" t="n">
-        <v>8</v>
+        <v>7.57</v>
       </c>
       <c r="S13" t="n">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="T13" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -5878,28 +5878,28 @@
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="Z13" t="n">
-        <v>11.83</v>
+        <v>13.29</v>
       </c>
       <c r="AA13" t="n">
-        <v>7.67</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="AB13" t="n">
-        <v>4.17</v>
+        <v>5</v>
       </c>
       <c r="AC13" t="n">
-        <v>21.83</v>
+        <v>22</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.32</v>
+        <v>1.49</v>
       </c>
       <c r="AE13" t="n">
-        <v>3.5</v>
+        <v>3.14</v>
       </c>
       <c r="AF13" t="n">
         <v>0</v>
@@ -5983,49 +5983,49 @@
         <v>3</v>
       </c>
       <c r="BG13" t="n">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="BH13" t="n">
-        <v>9.359999999999999</v>
+        <v>9.07</v>
       </c>
       <c r="BI13" t="n">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.43</v>
+        <v>0.47</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.64</v>
+        <v>0.73</v>
       </c>
       <c r="BN13" t="n">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="BO13" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="BP13" t="n">
-        <v>4.21</v>
+        <v>4</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4.43</v>
+        <v>4.4</v>
       </c>
       <c r="BR13" t="n">
-        <v>78.56999999999999</v>
+        <v>80</v>
       </c>
       <c r="BS13" t="n">
-        <v>64.29000000000001</v>
+        <v>66.67</v>
       </c>
       <c r="BT13" t="n">
-        <v>35.71</v>
+        <v>40</v>
       </c>
       <c r="BU13" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BV13" t="n">
         <v>0</v>
@@ -6034,13 +6034,13 @@
         <v>0</v>
       </c>
       <c r="BX13" t="n">
-        <v>50</v>
+        <v>46.67</v>
       </c>
       <c r="BY13" t="n">
-        <v>2.17</v>
+        <v>2.24</v>
       </c>
       <c r="BZ13" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="CA13" t="n">
         <v>3</v>
@@ -6058,40 +6058,40 @@
         <v>1.49</v>
       </c>
       <c r="CF13" t="n">
-        <v>3.33</v>
+        <v>3.29</v>
       </c>
       <c r="CG13" t="n">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="CH13" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="CI13" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CJ13" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="CK13" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CL13" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="CN13" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CO13" t="n">
         <v>1.43</v>
       </c>
       <c r="CP13" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="CQ13" t="n">
-        <v>4.38</v>
+        <v>4.32</v>
       </c>
       <c r="CR13" t="n">
         <v>1.55</v>
@@ -6106,106 +6106,106 @@
         <v>1.34</v>
       </c>
       <c r="CV13" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CW13" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="CX13" t="n">
         <v>1.71</v>
       </c>
       <c r="CY13" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="CZ13" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="DA13" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="DB13" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="DC13" t="n">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="DD13" t="n">
-        <v>4.85</v>
+        <v>4.8</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DF13" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="DG13" t="n">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="DH13" t="n">
-        <v>86.56999999999999</v>
+        <v>84.8</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DJ13" t="n">
-        <v>3.36</v>
+        <v>3.2</v>
       </c>
       <c r="DK13" t="n">
-        <v>4.57</v>
+        <v>4.6</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="DM13" t="n">
-        <v>36.65</v>
+        <v>38</v>
       </c>
       <c r="DN13" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="DO13" t="n">
-        <v>2.43</v>
+        <v>2.34</v>
       </c>
       <c r="DP13" t="n">
-        <v>13.08</v>
+        <v>12.73</v>
       </c>
       <c r="DQ13" t="n">
-        <v>14.86</v>
+        <v>15</v>
       </c>
       <c r="DR13" t="n">
-        <v>8.640000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>50.14</v>
+        <v>50.67</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DX13" t="n">
-        <v>10.93</v>
+        <v>11.67</v>
       </c>
       <c r="DY13" t="n">
-        <v>6.65</v>
+        <v>7</v>
       </c>
       <c r="DZ13" t="n">
-        <v>4.29</v>
+        <v>4.67</v>
       </c>
       <c r="EA13" t="n">
-        <v>20.28</v>
+        <v>20.46</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.26</v>
+        <v>1.34</v>
       </c>
       <c r="EC13" t="n">
-        <v>3.21</v>
+        <v>3.07</v>
       </c>
     </row>
     <row r="14">
@@ -6215,13 +6215,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C14" t="n">
         <v>7</v>
       </c>
       <c r="D14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -6305,139 +6305,139 @@
         <v>4.14</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AH14" t="n">
         <v>1</v>
       </c>
       <c r="AI14" t="n">
-        <v>76.14</v>
+        <v>76.5</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AK14" t="n">
-        <v>2.43</v>
+        <v>2.75</v>
       </c>
       <c r="AL14" t="n">
-        <v>2.29</v>
+        <v>2.12</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AN14" t="n">
-        <v>27.86</v>
+        <v>29.5</v>
       </c>
       <c r="AO14" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="AQ14" t="n">
-        <v>13.86</v>
+        <v>14.25</v>
       </c>
       <c r="AR14" t="n">
-        <v>12.43</v>
+        <v>13.25</v>
       </c>
       <c r="AS14" t="n">
-        <v>12.14</v>
+        <v>11.38</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.43</v>
+        <v>1.62</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AX14" t="n">
         <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>35</v>
+        <v>35.5</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="BA14" t="n">
-        <v>8.43</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="BB14" t="n">
-        <v>5.57</v>
+        <v>5.88</v>
       </c>
       <c r="BC14" t="n">
-        <v>2.86</v>
+        <v>3.25</v>
       </c>
       <c r="BD14" t="n">
-        <v>17.57</v>
+        <v>17.38</v>
       </c>
       <c r="BE14" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.02</v>
       </c>
       <c r="BF14" t="n">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.64</v>
+        <v>2.8</v>
       </c>
       <c r="BH14" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.64</v>
+        <v>2.8</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.43</v>
+        <v>0.53</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.57</v>
+        <v>0.6</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.93</v>
+        <v>1</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="BP14" t="n">
-        <v>3.93</v>
+        <v>3.73</v>
       </c>
       <c r="BQ14" t="n">
-        <v>5.07</v>
+        <v>4.87</v>
       </c>
       <c r="BR14" t="n">
-        <v>92.86</v>
+        <v>93.33</v>
       </c>
       <c r="BS14" t="n">
-        <v>71.43000000000001</v>
+        <v>73.33</v>
       </c>
       <c r="BT14" t="n">
-        <v>42.86</v>
+        <v>46.67</v>
       </c>
       <c r="BU14" t="n">
-        <v>28.57</v>
+        <v>33.33</v>
       </c>
       <c r="BV14" t="n">
-        <v>21.43</v>
+        <v>26.67</v>
       </c>
       <c r="BW14" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BX14" t="n">
-        <v>57.14</v>
+        <v>60</v>
       </c>
       <c r="BY14" t="n">
         <v>3.07</v>
@@ -6446,16 +6446,16 @@
         <v>3.54</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.15</v>
+        <v>3.17</v>
       </c>
       <c r="CB14" t="n">
         <v>3.37</v>
       </c>
       <c r="CC14" t="n">
-        <v>4.72</v>
+        <v>4.68</v>
       </c>
       <c r="CD14" t="n">
-        <v>5.16</v>
+        <v>5.09</v>
       </c>
       <c r="CE14" t="n">
         <v>1.49</v>
@@ -6479,13 +6479,13 @@
         <v>1.71</v>
       </c>
       <c r="CL14" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="CN14" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CO14" t="n">
         <v>1.4</v>
@@ -6494,16 +6494,16 @@
         <v>2.29</v>
       </c>
       <c r="CQ14" t="n">
-        <v>4.36</v>
+        <v>4.34</v>
       </c>
       <c r="CR14" t="n">
         <v>1.53</v>
       </c>
       <c r="CS14" t="n">
-        <v>3.25</v>
+        <v>3.28</v>
       </c>
       <c r="CT14" t="n">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="CU14" t="n">
         <v>1.36</v>
@@ -6530,85 +6530,85 @@
         <v>1.44</v>
       </c>
       <c r="DC14" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="DD14" t="n">
-        <v>4.53</v>
+        <v>4.52</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="DG14" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="DH14" t="n">
-        <v>85.86</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="DI14" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DJ14" t="n">
-        <v>3.28</v>
+        <v>3.4</v>
       </c>
       <c r="DK14" t="n">
-        <v>2.93</v>
+        <v>2.8</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DM14" t="n">
-        <v>34.29</v>
+        <v>34.73</v>
       </c>
       <c r="DN14" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="DO14" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="DP14" t="n">
-        <v>15.78</v>
+        <v>15.86</v>
       </c>
       <c r="DQ14" t="n">
-        <v>12.28</v>
+        <v>12.73</v>
       </c>
       <c r="DR14" t="n">
-        <v>9.779999999999999</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>40.79</v>
+        <v>40.67</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="DX14" t="n">
-        <v>10.43</v>
+        <v>10.66</v>
       </c>
       <c r="DY14" t="n">
-        <v>7</v>
+        <v>7.07</v>
       </c>
       <c r="DZ14" t="n">
-        <v>3.43</v>
+        <v>3.6</v>
       </c>
       <c r="EA14" t="n">
-        <v>16.57</v>
+        <v>16.54</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="EC14" t="n">
-        <v>3.14</v>
+        <v>3.13</v>
       </c>
     </row>
     <row r="15">
@@ -6618,61 +6618,61 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D15" t="n">
         <v>7</v>
       </c>
       <c r="E15" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="F15" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="G15" t="n">
-        <v>2.29</v>
+        <v>2.12</v>
       </c>
       <c r="H15" t="n">
-        <v>90.29000000000001</v>
+        <v>91.25</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="K15" t="n">
-        <v>3.71</v>
+        <v>3.5</v>
       </c>
       <c r="L15" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="M15" t="n">
-        <v>50.29</v>
+        <v>49.38</v>
       </c>
       <c r="N15" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="O15" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="P15" t="n">
-        <v>13.14</v>
+        <v>13.88</v>
       </c>
       <c r="Q15" t="n">
-        <v>13.14</v>
+        <v>13.62</v>
       </c>
       <c r="R15" t="n">
-        <v>6.86</v>
+        <v>7</v>
       </c>
       <c r="S15" t="n">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="T15" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
@@ -6684,28 +6684,28 @@
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>54</v>
+        <v>54.88</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="Z15" t="n">
-        <v>14.14</v>
+        <v>14.62</v>
       </c>
       <c r="AA15" t="n">
-        <v>9</v>
+        <v>8.75</v>
       </c>
       <c r="AB15" t="n">
-        <v>5.14</v>
+        <v>5.88</v>
       </c>
       <c r="AC15" t="n">
-        <v>22.71</v>
+        <v>22</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.61</v>
+        <v>1.69</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AF15" t="n">
         <v>0.14</v>
@@ -6789,70 +6789,70 @@
         <v>2</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.43</v>
+        <v>2.6</v>
       </c>
       <c r="BH15" t="n">
-        <v>8.5</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.43</v>
+        <v>2.6</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.57</v>
+        <v>0.67</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="BL15" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.43</v>
+        <v>0.53</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="BO15" t="n">
-        <v>0.86</v>
+        <v>0.93</v>
       </c>
       <c r="BP15" t="n">
-        <v>3.64</v>
+        <v>3.47</v>
       </c>
       <c r="BQ15" t="n">
-        <v>4.86</v>
+        <v>4.67</v>
       </c>
       <c r="BR15" t="n">
         <v>100</v>
       </c>
       <c r="BS15" t="n">
-        <v>64.29000000000001</v>
+        <v>66.67</v>
       </c>
       <c r="BT15" t="n">
-        <v>50</v>
+        <v>53.33</v>
       </c>
       <c r="BU15" t="n">
-        <v>21.43</v>
+        <v>26.67</v>
       </c>
       <c r="BV15" t="n">
-        <v>7.14</v>
+        <v>13.33</v>
       </c>
       <c r="BW15" t="n">
         <v>0</v>
       </c>
       <c r="BX15" t="n">
-        <v>42.86</v>
+        <v>46.67</v>
       </c>
       <c r="BY15" t="n">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="BZ15" t="n">
-        <v>2.28</v>
+        <v>2.23</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.19</v>
+        <v>3.2</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.34</v>
+        <v>3.35</v>
       </c>
       <c r="CC15" t="n">
         <v>3.89</v>
@@ -6867,13 +6867,13 @@
         <v>3.16</v>
       </c>
       <c r="CG15" t="n">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="CH15" t="n">
         <v>1.33</v>
       </c>
       <c r="CI15" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CJ15" t="n">
         <v>1.98</v>
@@ -6882,7 +6882,7 @@
         <v>1.61</v>
       </c>
       <c r="CL15" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="CM15" t="n">
         <v>2.19</v>
@@ -6903,7 +6903,7 @@
         <v>1.49</v>
       </c>
       <c r="CS15" t="n">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="CT15" t="n">
         <v>2.74</v>
@@ -6912,7 +6912,7 @@
         <v>1.37</v>
       </c>
       <c r="CV15" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CW15" t="n">
         <v>2.02</v>
@@ -6936,49 +6936,49 @@
         <v>2.32</v>
       </c>
       <c r="DD15" t="n">
-        <v>4.35</v>
+        <v>4.34</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="DG15" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="DH15" t="n">
-        <v>88.08</v>
+        <v>88.73</v>
       </c>
       <c r="DI15" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DJ15" t="n">
-        <v>2.43</v>
+        <v>2.33</v>
       </c>
       <c r="DK15" t="n">
-        <v>4</v>
+        <v>3.87</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DM15" t="n">
-        <v>46.08</v>
+        <v>45.87</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.78</v>
+        <v>0.73</v>
       </c>
       <c r="DO15" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="DP15" t="n">
-        <v>13.36</v>
+        <v>13.74</v>
       </c>
       <c r="DQ15" t="n">
-        <v>12.57</v>
+        <v>12.86</v>
       </c>
       <c r="DR15" t="n">
-        <v>7.5</v>
+        <v>7.53</v>
       </c>
       <c r="DS15" t="n">
         <v>0.07000000000000001</v>
@@ -6990,28 +6990,28 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>52.07</v>
+        <v>52.67</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="DX15" t="n">
-        <v>12.14</v>
+        <v>12.53</v>
       </c>
       <c r="DY15" t="n">
-        <v>8.140000000000001</v>
+        <v>8.07</v>
       </c>
       <c r="DZ15" t="n">
-        <v>4</v>
+        <v>4.47</v>
       </c>
       <c r="EA15" t="n">
-        <v>23.21</v>
+        <v>22.8</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="EC15" t="n">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
     </row>
     <row r="16">
@@ -7021,13 +7021,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C16" t="n">
         <v>8</v>
       </c>
       <c r="D16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E16" t="n">
         <v>0.25</v>
@@ -7114,49 +7114,49 @@
         <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.83</v>
+        <v>2.14</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="AI16" t="n">
-        <v>91</v>
+        <v>90.29000000000001</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="AK16" t="n">
-        <v>3.33</v>
+        <v>3.57</v>
       </c>
       <c r="AL16" t="n">
-        <v>4.83</v>
+        <v>4.57</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="AN16" t="n">
-        <v>35.67</v>
+        <v>36.57</v>
       </c>
       <c r="AO16" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AP16" t="n">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="AQ16" t="n">
-        <v>13.67</v>
+        <v>14</v>
       </c>
       <c r="AR16" t="n">
-        <v>16.33</v>
+        <v>16.43</v>
       </c>
       <c r="AS16" t="n">
-        <v>8.17</v>
+        <v>8</v>
       </c>
       <c r="AT16" t="n">
-        <v>2</v>
+        <v>1.71</v>
       </c>
       <c r="AU16" t="n">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="AV16" t="n">
         <v>0</v>
@@ -7168,82 +7168,82 @@
         <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>50.5</v>
+        <v>50.14</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="BA16" t="n">
-        <v>11.83</v>
+        <v>12.29</v>
       </c>
       <c r="BB16" t="n">
-        <v>6.67</v>
+        <v>7.29</v>
       </c>
       <c r="BC16" t="n">
-        <v>5.17</v>
+        <v>5</v>
       </c>
       <c r="BD16" t="n">
-        <v>16.67</v>
+        <v>17.29</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="BF16" t="n">
-        <v>2.83</v>
+        <v>3.14</v>
       </c>
       <c r="BG16" t="n">
-        <v>3.86</v>
+        <v>3.73</v>
       </c>
       <c r="BH16" t="n">
-        <v>11.64</v>
+        <v>11.47</v>
       </c>
       <c r="BI16" t="n">
-        <v>3.86</v>
+        <v>3.73</v>
       </c>
       <c r="BJ16" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.57</v>
+        <v>0.6</v>
       </c>
       <c r="BL16" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="BM16" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="BN16" t="n">
-        <v>2.21</v>
+        <v>2.13</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="BP16" t="n">
-        <v>5.86</v>
+        <v>5.67</v>
       </c>
       <c r="BQ16" t="n">
-        <v>5.79</v>
+        <v>5.8</v>
       </c>
       <c r="BR16" t="n">
         <v>100</v>
       </c>
       <c r="BS16" t="n">
-        <v>92.86</v>
+        <v>93.33</v>
       </c>
       <c r="BT16" t="n">
-        <v>92.86</v>
+        <v>86.67</v>
       </c>
       <c r="BU16" t="n">
-        <v>64.29000000000001</v>
+        <v>60</v>
       </c>
       <c r="BV16" t="n">
-        <v>28.57</v>
+        <v>26.67</v>
       </c>
       <c r="BW16" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BX16" t="n">
-        <v>85.70999999999999</v>
+        <v>80</v>
       </c>
       <c r="BY16" t="n">
         <v>1.81</v>
@@ -7252,169 +7252,169 @@
         <v>1.82</v>
       </c>
       <c r="CA16" t="n">
-        <v>3.71</v>
+        <v>3.66</v>
       </c>
       <c r="CB16" t="n">
-        <v>3.87</v>
+        <v>3.82</v>
       </c>
       <c r="CC16" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="CD16" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="CE16" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="CF16" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="CG16" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="CH16" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="CI16" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="CJ16" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="CK16" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="CL16" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="CM16" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="CN16" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="CO16" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="CP16" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="CQ16" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="CR16" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="CS16" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="CT16" t="n">
         <v>3.18</v>
       </c>
-      <c r="CD16" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="CE16" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="CF16" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="CG16" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="CH16" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="CI16" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="CJ16" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="CK16" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="CL16" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="CM16" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="CN16" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="CO16" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="CP16" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="CQ16" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="CR16" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="CS16" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="CT16" t="n">
-        <v>3.24</v>
-      </c>
       <c r="CU16" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="CV16" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="CW16" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="CX16" t="n">
         <v>1.53</v>
       </c>
-      <c r="CV16" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="CW16" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="CX16" t="n">
-        <v>1.51</v>
-      </c>
       <c r="CY16" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="CZ16" t="n">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="DA16" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="DB16" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="DC16" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="DD16" t="n">
-        <v>2.78</v>
+        <v>2.87</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.93</v>
+        <v>2.07</v>
       </c>
       <c r="DG16" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="DH16" t="n">
-        <v>97.43000000000001</v>
+        <v>96.67</v>
       </c>
       <c r="DI16" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DJ16" t="n">
-        <v>2.92</v>
+        <v>3.06</v>
       </c>
       <c r="DK16" t="n">
-        <v>6.57</v>
+        <v>6.34</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="DM16" t="n">
-        <v>43.79</v>
+        <v>43.67</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="DO16" t="n">
-        <v>2.93</v>
+        <v>2.73</v>
       </c>
       <c r="DP16" t="n">
-        <v>13</v>
+        <v>13.2</v>
       </c>
       <c r="DQ16" t="n">
-        <v>15.07</v>
+        <v>15.2</v>
       </c>
       <c r="DR16" t="n">
-        <v>7.72</v>
+        <v>7.67</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>53.21</v>
+        <v>52.87</v>
       </c>
       <c r="DW16" t="n">
         <v>0.14</v>
       </c>
       <c r="DX16" t="n">
-        <v>14.21</v>
+        <v>14.27</v>
       </c>
       <c r="DY16" t="n">
-        <v>8.57</v>
+        <v>8.74</v>
       </c>
       <c r="DZ16" t="n">
-        <v>5.64</v>
+        <v>5.53</v>
       </c>
       <c r="EA16" t="n">
-        <v>18</v>
+        <v>18.2</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="EC16" t="n">
-        <v>2.71</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="17">
@@ -7424,22 +7424,22 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D17" t="n">
         <v>7</v>
       </c>
       <c r="E17" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="F17" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="G17" t="n">
-        <v>0.57</v>
+        <v>1</v>
       </c>
       <c r="H17" t="n">
         <v>78</v>
@@ -7448,70 +7448,70 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>3.14</v>
+        <v>3.12</v>
       </c>
       <c r="K17" t="n">
-        <v>2.86</v>
+        <v>3</v>
       </c>
       <c r="L17" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="M17" t="n">
-        <v>31.57</v>
+        <v>31.62</v>
       </c>
       <c r="N17" t="n">
         <v>1</v>
       </c>
       <c r="O17" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="P17" t="n">
-        <v>20.14</v>
+        <v>19.25</v>
       </c>
       <c r="Q17" t="n">
-        <v>13.71</v>
+        <v>13.38</v>
       </c>
       <c r="R17" t="n">
-        <v>8.140000000000001</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="S17" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="T17" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="U17" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="V17" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>44.14</v>
+        <v>44</v>
       </c>
       <c r="Y17" t="n">
         <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>10.29</v>
+        <v>10.5</v>
       </c>
       <c r="AA17" t="n">
-        <v>6.43</v>
+        <v>6.62</v>
       </c>
       <c r="AB17" t="n">
-        <v>3.86</v>
+        <v>3.88</v>
       </c>
       <c r="AC17" t="n">
-        <v>20.43</v>
+        <v>20.25</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AE17" t="n">
-        <v>3.14</v>
+        <v>3.12</v>
       </c>
       <c r="AF17" t="n">
         <v>0</v>
@@ -7595,70 +7595,70 @@
         <v>2.71</v>
       </c>
       <c r="BG17" t="n">
-        <v>3.29</v>
+        <v>3.13</v>
       </c>
       <c r="BH17" t="n">
-        <v>9</v>
+        <v>9.27</v>
       </c>
       <c r="BI17" t="n">
-        <v>3.29</v>
+        <v>3.13</v>
       </c>
       <c r="BJ17" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="BL17" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="BP17" t="n">
-        <v>4.29</v>
+        <v>4.07</v>
       </c>
       <c r="BQ17" t="n">
-        <v>4</v>
+        <v>4.53</v>
       </c>
       <c r="BR17" t="n">
         <v>100</v>
       </c>
       <c r="BS17" t="n">
-        <v>71.43000000000001</v>
+        <v>66.67</v>
       </c>
       <c r="BT17" t="n">
-        <v>57.14</v>
+        <v>53.33</v>
       </c>
       <c r="BU17" t="n">
-        <v>28.57</v>
+        <v>26.67</v>
       </c>
       <c r="BV17" t="n">
-        <v>21.43</v>
+        <v>20</v>
       </c>
       <c r="BW17" t="n">
-        <v>21.43</v>
+        <v>20</v>
       </c>
       <c r="BX17" t="n">
-        <v>57.14</v>
+        <v>53.33</v>
       </c>
       <c r="BY17" t="n">
-        <v>3.21</v>
+        <v>3.24</v>
       </c>
       <c r="BZ17" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.5</v>
+        <v>3.48</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.74</v>
+        <v>3.71</v>
       </c>
       <c r="CC17" t="n">
         <v>5.67</v>
@@ -7673,7 +7673,7 @@
         <v>3.04</v>
       </c>
       <c r="CG17" t="n">
-        <v>2.73</v>
+        <v>2.72</v>
       </c>
       <c r="CH17" t="n">
         <v>1.36</v>
@@ -7682,13 +7682,13 @@
         <v>1.81</v>
       </c>
       <c r="CJ17" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CK17" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="CL17" t="n">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="CM17" t="n">
         <v>2.25</v>
@@ -7700,10 +7700,10 @@
         <v>1.34</v>
       </c>
       <c r="CP17" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="CQ17" t="n">
-        <v>3.65</v>
+        <v>3.66</v>
       </c>
       <c r="CR17" t="n">
         <v>1.48</v>
@@ -7730,7 +7730,7 @@
         <v>2.06</v>
       </c>
       <c r="CZ17" t="n">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="DA17" t="n">
         <v>1.77</v>
@@ -7739,85 +7739,85 @@
         <v>1.38</v>
       </c>
       <c r="DC17" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="DD17" t="n">
-        <v>4</v>
+        <v>4.01</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="DG17" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="DH17" t="n">
-        <v>82.5</v>
+        <v>82.2</v>
       </c>
       <c r="DI17" t="n">
         <v>0</v>
       </c>
       <c r="DJ17" t="n">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="DK17" t="n">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DM17" t="n">
-        <v>29.36</v>
+        <v>29.53</v>
       </c>
       <c r="DN17" t="n">
         <v>1.14</v>
       </c>
       <c r="DO17" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="DP17" t="n">
-        <v>18.36</v>
+        <v>18</v>
       </c>
       <c r="DQ17" t="n">
-        <v>13.57</v>
+        <v>13.4</v>
       </c>
       <c r="DR17" t="n">
-        <v>8.43</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>44</v>
+        <v>43.93</v>
       </c>
       <c r="DW17" t="n">
         <v>0</v>
       </c>
       <c r="DX17" t="n">
-        <v>10.79</v>
+        <v>10.87</v>
       </c>
       <c r="DY17" t="n">
-        <v>6.64</v>
+        <v>6.73</v>
       </c>
       <c r="DZ17" t="n">
-        <v>4.15</v>
+        <v>4.14</v>
       </c>
       <c r="EA17" t="n">
-        <v>21.93</v>
+        <v>21.73</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="EC17" t="n">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
     </row>
     <row r="18">
@@ -7827,13 +7827,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C18" t="n">
         <v>8</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -7920,136 +7920,136 @@
         <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.67</v>
+        <v>3.43</v>
       </c>
       <c r="AI18" t="n">
-        <v>107.17</v>
+        <v>112.14</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AK18" t="n">
-        <v>3.5</v>
+        <v>3.43</v>
       </c>
       <c r="AL18" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AM18" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="AN18" t="n">
-        <v>43.33</v>
+        <v>49.57</v>
       </c>
       <c r="AO18" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AP18" t="n">
-        <v>2.83</v>
+        <v>2.57</v>
       </c>
       <c r="AQ18" t="n">
-        <v>19</v>
+        <v>17.86</v>
       </c>
       <c r="AR18" t="n">
-        <v>14.5</v>
+        <v>14.29</v>
       </c>
       <c r="AS18" t="n">
-        <v>8.5</v>
+        <v>8.57</v>
       </c>
       <c r="AT18" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="AU18" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="AV18" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AW18" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AX18" t="n">
         <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>50.17</v>
+        <v>51.14</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="BA18" t="n">
-        <v>12</v>
+        <v>13.14</v>
       </c>
       <c r="BB18" t="n">
-        <v>8.33</v>
+        <v>9.57</v>
       </c>
       <c r="BC18" t="n">
-        <v>3.67</v>
+        <v>3.57</v>
       </c>
       <c r="BD18" t="n">
-        <v>22.33</v>
+        <v>23.57</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.34</v>
+        <v>1.44</v>
       </c>
       <c r="BF18" t="n">
-        <v>3.33</v>
+        <v>3.29</v>
       </c>
       <c r="BG18" t="n">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="BH18" t="n">
-        <v>8.710000000000001</v>
+        <v>9</v>
       </c>
       <c r="BI18" t="n">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.29</v>
+        <v>0.33</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BL18" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="BO18" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="BP18" t="n">
-        <v>3.29</v>
+        <v>3.13</v>
       </c>
       <c r="BQ18" t="n">
-        <v>5.43</v>
+        <v>5.87</v>
       </c>
       <c r="BR18" t="n">
-        <v>85.70999999999999</v>
+        <v>86.67</v>
       </c>
       <c r="BS18" t="n">
-        <v>57.14</v>
+        <v>53.33</v>
       </c>
       <c r="BT18" t="n">
-        <v>28.57</v>
+        <v>26.67</v>
       </c>
       <c r="BU18" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="BV18" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BW18" t="n">
         <v>0</v>
       </c>
       <c r="BX18" t="n">
-        <v>42.86</v>
+        <v>40</v>
       </c>
       <c r="BY18" t="n">
         <v>1.94</v>
@@ -8058,46 +8058,46 @@
         <v>2.01</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.3</v>
+        <v>3.29</v>
       </c>
       <c r="CB18" t="n">
-        <v>3.41</v>
+        <v>3.39</v>
       </c>
       <c r="CC18" t="n">
-        <v>2.88</v>
+        <v>2.77</v>
       </c>
       <c r="CD18" t="n">
-        <v>3.14</v>
+        <v>3</v>
       </c>
       <c r="CE18" t="n">
         <v>1.41</v>
       </c>
       <c r="CF18" t="n">
-        <v>2.95</v>
+        <v>2.96</v>
       </c>
       <c r="CG18" t="n">
-        <v>2.73</v>
+        <v>2.72</v>
       </c>
       <c r="CH18" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CI18" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CJ18" t="n">
         <v>1.9</v>
       </c>
       <c r="CK18" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CL18" t="n">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="CM18" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="CN18" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CO18" t="n">
         <v>1.34</v>
@@ -8106,7 +8106,7 @@
         <v>2.15</v>
       </c>
       <c r="CQ18" t="n">
-        <v>3.79</v>
+        <v>3.8</v>
       </c>
       <c r="CR18" t="n">
         <v>1.46</v>
@@ -8127,16 +8127,16 @@
         <v>1.92</v>
       </c>
       <c r="CX18" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CY18" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="CZ18" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="DA18" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="DB18" t="n">
         <v>1.37</v>
@@ -8145,82 +8145,82 @@
         <v>2.2</v>
       </c>
       <c r="DD18" t="n">
-        <v>3.99</v>
+        <v>4</v>
       </c>
       <c r="DE18" t="n">
         <v>0</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="DG18" t="n">
-        <v>3.86</v>
+        <v>4.13</v>
       </c>
       <c r="DH18" t="n">
-        <v>114</v>
+        <v>115.86</v>
       </c>
       <c r="DI18" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DJ18" t="n">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
       <c r="DK18" t="n">
-        <v>6.29</v>
+        <v>6.47</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="DM18" t="n">
-        <v>58.35</v>
+        <v>60.26</v>
       </c>
       <c r="DN18" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="DO18" t="n">
-        <v>2.42</v>
+        <v>2.33</v>
       </c>
       <c r="DP18" t="n">
-        <v>18.29</v>
+        <v>17.8</v>
       </c>
       <c r="DQ18" t="n">
-        <v>13.64</v>
+        <v>13.6</v>
       </c>
       <c r="DR18" t="n">
-        <v>6.85</v>
+        <v>7</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DT18" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DU18" t="n">
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>53.36</v>
+        <v>53.6</v>
       </c>
       <c r="DW18" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DX18" t="n">
-        <v>14.79</v>
+        <v>15.13</v>
       </c>
       <c r="DY18" t="n">
-        <v>10.07</v>
+        <v>10.54</v>
       </c>
       <c r="DZ18" t="n">
-        <v>4.72</v>
+        <v>4.6</v>
       </c>
       <c r="EA18" t="n">
-        <v>25.71</v>
+        <v>26.07</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="EC18" t="n">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="19">
@@ -8230,13 +8230,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C19" t="n">
         <v>7</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -8320,139 +8320,139 @@
         <v>3</v>
       </c>
       <c r="AF19" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AG19" t="n">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="AH19" t="n">
-        <v>3.86</v>
+        <v>3.38</v>
       </c>
       <c r="AI19" t="n">
-        <v>91.70999999999999</v>
+        <v>88</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AK19" t="n">
-        <v>2.43</v>
+        <v>2.62</v>
       </c>
       <c r="AL19" t="n">
-        <v>6.43</v>
+        <v>5.62</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AN19" t="n">
-        <v>45.14</v>
+        <v>41</v>
       </c>
       <c r="AO19" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AP19" t="n">
-        <v>2.43</v>
+        <v>2.12</v>
       </c>
       <c r="AQ19" t="n">
-        <v>14.57</v>
+        <v>14</v>
       </c>
       <c r="AR19" t="n">
-        <v>16.43</v>
+        <v>16.5</v>
       </c>
       <c r="AS19" t="n">
-        <v>5.86</v>
+        <v>6.25</v>
       </c>
       <c r="AT19" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AU19" t="n">
-        <v>0.71</v>
+        <v>0.88</v>
       </c>
       <c r="AV19" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="AW19" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="AX19" t="n">
         <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>49.71</v>
+        <v>47.62</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="BA19" t="n">
-        <v>14.14</v>
+        <v>12.75</v>
       </c>
       <c r="BB19" t="n">
-        <v>10.86</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="BC19" t="n">
-        <v>3.29</v>
+        <v>3.12</v>
       </c>
       <c r="BD19" t="n">
-        <v>18.57</v>
+        <v>18</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.45</v>
+        <v>1.32</v>
       </c>
       <c r="BF19" t="n">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.21</v>
+        <v>2.27</v>
       </c>
       <c r="BH19" t="n">
-        <v>10.29</v>
+        <v>10.07</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.21</v>
+        <v>2.27</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.29</v>
+        <v>0.33</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="BO19" t="n">
-        <v>0.64</v>
+        <v>0.73</v>
       </c>
       <c r="BP19" t="n">
-        <v>5.36</v>
+        <v>5.27</v>
       </c>
       <c r="BQ19" t="n">
-        <v>4.86</v>
+        <v>4.73</v>
       </c>
       <c r="BR19" t="n">
-        <v>92.86</v>
+        <v>93.33</v>
       </c>
       <c r="BS19" t="n">
-        <v>50</v>
+        <v>53.33</v>
       </c>
       <c r="BT19" t="n">
-        <v>28.57</v>
+        <v>33.33</v>
       </c>
       <c r="BU19" t="n">
-        <v>28.57</v>
+        <v>26.67</v>
       </c>
       <c r="BV19" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="BW19" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BX19" t="n">
-        <v>35.71</v>
+        <v>40</v>
       </c>
       <c r="BY19" t="n">
         <v>2.25</v>
@@ -8461,34 +8461,34 @@
         <v>2.42</v>
       </c>
       <c r="CA19" t="n">
-        <v>3.2</v>
+        <v>3.21</v>
       </c>
       <c r="CB19" t="n">
-        <v>3.34</v>
+        <v>3.35</v>
       </c>
       <c r="CC19" t="n">
-        <v>3.71</v>
+        <v>3.81</v>
       </c>
       <c r="CD19" t="n">
-        <v>4.33</v>
+        <v>4.48</v>
       </c>
       <c r="CE19" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="CF19" t="n">
-        <v>3.06</v>
+        <v>3.09</v>
       </c>
       <c r="CG19" t="n">
-        <v>2.66</v>
+        <v>2.65</v>
       </c>
       <c r="CH19" t="n">
         <v>1.34</v>
       </c>
       <c r="CI19" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="CJ19" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="CK19" t="n">
         <v>1.59</v>
@@ -8497,7 +8497,7 @@
         <v>2.01</v>
       </c>
       <c r="CM19" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="CN19" t="n">
         <v>1.81</v>
@@ -8506,34 +8506,34 @@
         <v>1.36</v>
       </c>
       <c r="CP19" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="CQ19" t="n">
-        <v>3.88</v>
+        <v>3.95</v>
       </c>
       <c r="CR19" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="CS19" t="n">
-        <v>3.19</v>
+        <v>3.2</v>
       </c>
       <c r="CT19" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="CU19" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CV19" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="CW19" t="n">
         <v>1.95</v>
-      </c>
-      <c r="CW19" t="n">
-        <v>1.93</v>
       </c>
       <c r="CX19" t="n">
         <v>1.61</v>
       </c>
       <c r="CY19" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="CZ19" t="n">
         <v>2.27</v>
@@ -8542,88 +8542,88 @@
         <v>1.81</v>
       </c>
       <c r="DB19" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="DC19" t="n">
-        <v>2.21</v>
+        <v>2.23</v>
       </c>
       <c r="DD19" t="n">
-        <v>3.99</v>
+        <v>4.04</v>
       </c>
       <c r="DE19" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="DG19" t="n">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="DH19" t="n">
-        <v>93.28</v>
+        <v>91.2</v>
       </c>
       <c r="DI19" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DJ19" t="n">
-        <v>3.22</v>
+        <v>3.26</v>
       </c>
       <c r="DK19" t="n">
-        <v>5.14</v>
+        <v>4.8</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="DM19" t="n">
-        <v>42.22</v>
+        <v>40.2</v>
       </c>
       <c r="DN19" t="n">
         <v>1.93</v>
       </c>
       <c r="DO19" t="n">
-        <v>2.57</v>
+        <v>2.4</v>
       </c>
       <c r="DP19" t="n">
-        <v>13.57</v>
+        <v>13.33</v>
       </c>
       <c r="DQ19" t="n">
-        <v>15.43</v>
+        <v>15.53</v>
       </c>
       <c r="DR19" t="n">
-        <v>6.86</v>
+        <v>7</v>
       </c>
       <c r="DS19" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="DT19" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="DU19" t="n">
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>49.64</v>
+        <v>48.53</v>
       </c>
       <c r="DW19" t="n">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="DX19" t="n">
-        <v>12</v>
+        <v>11.4</v>
       </c>
       <c r="DY19" t="n">
-        <v>8.93</v>
+        <v>8.4</v>
       </c>
       <c r="DZ19" t="n">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="EA19" t="n">
-        <v>21.28</v>
+        <v>20.8</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="EC19" t="n">
-        <v>2.72</v>
+        <v>2.73</v>
       </c>
     </row>
     <row r="20">
@@ -8633,10 +8633,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C20" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D20" t="n">
         <v>7</v>
@@ -8645,82 +8645,82 @@
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="G20" t="n">
-        <v>2.57</v>
+        <v>2.62</v>
       </c>
       <c r="H20" t="n">
-        <v>117.14</v>
+        <v>112.88</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>2.14</v>
+        <v>2.62</v>
       </c>
       <c r="K20" t="n">
-        <v>5.14</v>
+        <v>5.38</v>
       </c>
       <c r="L20" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="M20" t="n">
-        <v>56</v>
+        <v>58.5</v>
       </c>
       <c r="N20" t="n">
-        <v>0.86</v>
+        <v>1.25</v>
       </c>
       <c r="O20" t="n">
-        <v>2.57</v>
+        <v>2.75</v>
       </c>
       <c r="P20" t="n">
-        <v>15.86</v>
+        <v>16.12</v>
       </c>
       <c r="Q20" t="n">
-        <v>11.71</v>
+        <v>11.38</v>
       </c>
       <c r="R20" t="n">
-        <v>7.86</v>
+        <v>6.88</v>
       </c>
       <c r="S20" t="n">
-        <v>0.57</v>
+        <v>0.75</v>
       </c>
       <c r="T20" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="U20" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="V20" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>53.14</v>
+        <v>54.88</v>
       </c>
       <c r="Y20" t="n">
         <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>15.43</v>
+        <v>16.38</v>
       </c>
       <c r="AA20" t="n">
-        <v>9.859999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AB20" t="n">
-        <v>5.57</v>
+        <v>5.88</v>
       </c>
       <c r="AC20" t="n">
-        <v>19</v>
+        <v>18.62</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.77</v>
+        <v>1.87</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.14</v>
+        <v>2.62</v>
       </c>
       <c r="AF20" t="n">
         <v>0.14</v>
@@ -8804,70 +8804,70 @@
         <v>2.14</v>
       </c>
       <c r="BG20" t="n">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="BH20" t="n">
-        <v>9.359999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BI20" t="n">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="BJ20" t="n">
-        <v>0.57</v>
+        <v>0.6</v>
       </c>
       <c r="BK20" t="n">
-        <v>0.29</v>
+        <v>0.33</v>
       </c>
       <c r="BL20" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="BM20" t="n">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="BN20" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="BO20" t="n">
-        <v>0.86</v>
+        <v>0.93</v>
       </c>
       <c r="BP20" t="n">
-        <v>4.29</v>
+        <v>4.27</v>
       </c>
       <c r="BQ20" t="n">
-        <v>5.07</v>
+        <v>4.93</v>
       </c>
       <c r="BR20" t="n">
-        <v>85.70999999999999</v>
+        <v>86.67</v>
       </c>
       <c r="BS20" t="n">
-        <v>71.43000000000001</v>
+        <v>73.33</v>
       </c>
       <c r="BT20" t="n">
-        <v>42.86</v>
+        <v>46.67</v>
       </c>
       <c r="BU20" t="n">
-        <v>21.43</v>
+        <v>20</v>
       </c>
       <c r="BV20" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BW20" t="n">
         <v>0</v>
       </c>
       <c r="BX20" t="n">
-        <v>57.14</v>
+        <v>60</v>
       </c>
       <c r="BY20" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="BZ20" t="n">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="CA20" t="n">
-        <v>3.15</v>
+        <v>3.17</v>
       </c>
       <c r="CB20" t="n">
-        <v>3.24</v>
+        <v>3.25</v>
       </c>
       <c r="CC20" t="n">
         <v>3.26</v>
@@ -8879,7 +8879,7 @@
         <v>1.48</v>
       </c>
       <c r="CF20" t="n">
-        <v>3.32</v>
+        <v>3.33</v>
       </c>
       <c r="CG20" t="n">
         <v>2.48</v>
@@ -8891,7 +8891,7 @@
         <v>1.73</v>
       </c>
       <c r="CJ20" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="CK20" t="n">
         <v>1.65</v>
@@ -8900,7 +8900,7 @@
         <v>2.08</v>
       </c>
       <c r="CM20" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="CN20" t="n">
         <v>1.73</v>
@@ -8909,34 +8909,34 @@
         <v>1.44</v>
       </c>
       <c r="CP20" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="CQ20" t="n">
-        <v>4.43</v>
+        <v>4.46</v>
       </c>
       <c r="CR20" t="n">
         <v>1.56</v>
       </c>
       <c r="CS20" t="n">
-        <v>3.24</v>
+        <v>3.25</v>
       </c>
       <c r="CT20" t="n">
         <v>2.55</v>
       </c>
       <c r="CU20" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CV20" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CW20" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="CX20" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="CY20" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="CZ20" t="n">
         <v>2.15</v>
@@ -8957,76 +8957,76 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="DF20" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="DG20" t="n">
         <v>2.86</v>
       </c>
       <c r="DH20" t="n">
-        <v>108.42</v>
+        <v>106.73</v>
       </c>
       <c r="DI20" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DJ20" t="n">
-        <v>2.43</v>
+        <v>2.66</v>
       </c>
       <c r="DK20" t="n">
-        <v>4.78</v>
+        <v>4.94</v>
       </c>
       <c r="DL20" t="n">
-        <v>0.36</v>
+        <v>0.34</v>
       </c>
       <c r="DM20" t="n">
-        <v>47.22</v>
+        <v>49.13</v>
       </c>
       <c r="DN20" t="n">
-        <v>0.86</v>
+        <v>1.07</v>
       </c>
       <c r="DO20" t="n">
-        <v>1.93</v>
+        <v>2.07</v>
       </c>
       <c r="DP20" t="n">
-        <v>13.64</v>
+        <v>13.93</v>
       </c>
       <c r="DQ20" t="n">
-        <v>12.71</v>
+        <v>12.47</v>
       </c>
       <c r="DR20" t="n">
-        <v>7.22</v>
+        <v>6.74</v>
       </c>
       <c r="DS20" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DT20" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DU20" t="n">
         <v>0</v>
       </c>
       <c r="DV20" t="n">
-        <v>51.72</v>
+        <v>52.74</v>
       </c>
       <c r="DW20" t="n">
         <v>0.14</v>
       </c>
       <c r="DX20" t="n">
-        <v>12.64</v>
+        <v>13.34</v>
       </c>
       <c r="DY20" t="n">
-        <v>8.359999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="DZ20" t="n">
-        <v>4.28</v>
+        <v>4.54</v>
       </c>
       <c r="EA20" t="n">
-        <v>19.36</v>
+        <v>19.13</v>
       </c>
       <c r="EB20" t="n">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="EC20" t="n">
-        <v>2.14</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="21">
@@ -9036,10 +9036,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D21" t="n">
         <v>7</v>
@@ -9048,82 +9048,82 @@
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="G21" t="n">
-        <v>2.57</v>
+        <v>2.62</v>
       </c>
       <c r="H21" t="n">
-        <v>94</v>
+        <v>95.38</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>2.14</v>
+        <v>1.88</v>
       </c>
       <c r="K21" t="n">
-        <v>4.86</v>
+        <v>5.12</v>
       </c>
       <c r="L21" t="n">
-        <v>0.43</v>
+        <v>0.75</v>
       </c>
       <c r="M21" t="n">
-        <v>43.29</v>
+        <v>43.38</v>
       </c>
       <c r="N21" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="O21" t="n">
-        <v>2.14</v>
+        <v>2.38</v>
       </c>
       <c r="P21" t="n">
-        <v>15.71</v>
+        <v>14.75</v>
       </c>
       <c r="Q21" t="n">
-        <v>12.86</v>
+        <v>12.75</v>
       </c>
       <c r="R21" t="n">
-        <v>9.289999999999999</v>
+        <v>9.75</v>
       </c>
       <c r="S21" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="T21" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="U21" t="n">
-        <v>0.14</v>
+        <v>0.38</v>
       </c>
       <c r="V21" t="n">
-        <v>0.14</v>
+        <v>0.38</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>47.43</v>
+        <v>46.12</v>
       </c>
       <c r="Y21" t="n">
         <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>12</v>
+        <v>12.12</v>
       </c>
       <c r="AA21" t="n">
-        <v>8.57</v>
+        <v>8.5</v>
       </c>
       <c r="AB21" t="n">
-        <v>3.43</v>
+        <v>3.62</v>
       </c>
       <c r="AC21" t="n">
-        <v>25.29</v>
+        <v>24.25</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.14</v>
+        <v>1.88</v>
       </c>
       <c r="AF21" t="n">
         <v>0</v>
@@ -9207,49 +9207,49 @@
         <v>2</v>
       </c>
       <c r="BG21" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="BH21" t="n">
-        <v>8.859999999999999</v>
+        <v>9.07</v>
       </c>
       <c r="BI21" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="BJ21" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="BK21" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="BL21" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="BM21" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="BN21" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="BO21" t="n">
         <v>1.07</v>
       </c>
       <c r="BP21" t="n">
-        <v>3.86</v>
+        <v>4.2</v>
       </c>
       <c r="BQ21" t="n">
-        <v>4.93</v>
+        <v>4.8</v>
       </c>
       <c r="BR21" t="n">
         <v>100</v>
       </c>
       <c r="BS21" t="n">
-        <v>64.29000000000001</v>
+        <v>66.67</v>
       </c>
       <c r="BT21" t="n">
-        <v>42.86</v>
+        <v>40</v>
       </c>
       <c r="BU21" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="BV21" t="n">
         <v>0</v>
@@ -9258,13 +9258,13 @@
         <v>0</v>
       </c>
       <c r="BX21" t="n">
-        <v>50</v>
+        <v>46.67</v>
       </c>
       <c r="BY21" t="n">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
       <c r="BZ21" t="n">
-        <v>2.61</v>
+        <v>2.57</v>
       </c>
       <c r="CA21" t="n">
         <v>2.87</v>
@@ -9285,7 +9285,7 @@
         <v>3.77</v>
       </c>
       <c r="CG21" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="CH21" t="n">
         <v>1.23</v>
@@ -9294,13 +9294,13 @@
         <v>1.64</v>
       </c>
       <c r="CJ21" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="CK21" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CL21" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="CM21" t="n">
         <v>2.04</v>
@@ -9309,13 +9309,13 @@
         <v>1.67</v>
       </c>
       <c r="CO21" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="CP21" t="n">
-        <v>2.65</v>
+        <v>2.66</v>
       </c>
       <c r="CQ21" t="n">
-        <v>5.18</v>
+        <v>5.22</v>
       </c>
       <c r="CR21" t="n">
         <v>1.64</v>
@@ -9324,7 +9324,7 @@
         <v>3.3</v>
       </c>
       <c r="CT21" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="CU21" t="n">
         <v>1.35</v>
@@ -9333,7 +9333,7 @@
         <v>1.66</v>
       </c>
       <c r="CW21" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="CX21" t="n">
         <v>1.78</v>
@@ -9348,88 +9348,88 @@
         <v>1.62</v>
       </c>
       <c r="DB21" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="DC21" t="n">
-        <v>2.89</v>
+        <v>2.91</v>
       </c>
       <c r="DD21" t="n">
-        <v>5.85</v>
+        <v>5.92</v>
       </c>
       <c r="DE21" t="n">
         <v>0</v>
       </c>
       <c r="DF21" t="n">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="DG21" t="n">
-        <v>2.43</v>
+        <v>2.47</v>
       </c>
       <c r="DH21" t="n">
-        <v>88.34999999999999</v>
+        <v>89.47</v>
       </c>
       <c r="DI21" t="n">
         <v>0</v>
       </c>
       <c r="DJ21" t="n">
-        <v>2.22</v>
+        <v>2.07</v>
       </c>
       <c r="DK21" t="n">
-        <v>4.22</v>
+        <v>4.4</v>
       </c>
       <c r="DL21" t="n">
-        <v>0.43</v>
+        <v>0.6</v>
       </c>
       <c r="DM21" t="n">
-        <v>39.43</v>
+        <v>39.74</v>
       </c>
       <c r="DN21" t="n">
-        <v>0.78</v>
+        <v>0.73</v>
       </c>
       <c r="DO21" t="n">
-        <v>1.72</v>
+        <v>1.87</v>
       </c>
       <c r="DP21" t="n">
-        <v>13.28</v>
+        <v>12.93</v>
       </c>
       <c r="DQ21" t="n">
-        <v>13.28</v>
+        <v>13.2</v>
       </c>
       <c r="DR21" t="n">
-        <v>8.220000000000001</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="DS21" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.2</v>
       </c>
       <c r="DT21" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.2</v>
       </c>
       <c r="DU21" t="n">
         <v>0</v>
       </c>
       <c r="DV21" t="n">
-        <v>48.22</v>
+        <v>47.46</v>
       </c>
       <c r="DW21" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DX21" t="n">
-        <v>10.78</v>
+        <v>10.93</v>
       </c>
       <c r="DY21" t="n">
-        <v>8.279999999999999</v>
+        <v>8.27</v>
       </c>
       <c r="DZ21" t="n">
-        <v>2.5</v>
+        <v>2.66</v>
       </c>
       <c r="EA21" t="n">
-        <v>21.93</v>
+        <v>21.6</v>
       </c>
       <c r="EB21" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="EC21" t="n">
-        <v>2.07</v>
+        <v>1.94</v>
       </c>
     </row>
     <row r="22">
@@ -9439,13 +9439,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C22" t="n">
         <v>8</v>
       </c>
       <c r="D22" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -9529,139 +9529,139 @@
         <v>1.88</v>
       </c>
       <c r="AF22" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AG22" t="n">
-        <v>2.67</v>
+        <v>2.43</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="AI22" t="n">
-        <v>82.83</v>
+        <v>86.70999999999999</v>
       </c>
       <c r="AJ22" t="n">
         <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>3.5</v>
+        <v>3.14</v>
       </c>
       <c r="AL22" t="n">
-        <v>2.17</v>
+        <v>2.57</v>
       </c>
       <c r="AM22" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AN22" t="n">
-        <v>29.33</v>
+        <v>33</v>
       </c>
       <c r="AO22" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="AP22" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>12.43</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>11</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>8.289999999999999</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>42.71</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>4.43</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>19.29</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="BH22" t="n">
+        <v>9.27</v>
+      </c>
+      <c r="BI22" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="BJ22" t="n">
         <v>0.67</v>
       </c>
-      <c r="AQ22" t="n">
-        <v>12.17</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>39.33</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>7.33</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>3.83</v>
-      </c>
-      <c r="BD22" t="n">
-        <v>19.33</v>
-      </c>
-      <c r="BE22" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="BF22" t="n">
-        <v>3.17</v>
-      </c>
-      <c r="BG22" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="BH22" t="n">
-        <v>9.07</v>
-      </c>
-      <c r="BI22" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="BJ22" t="n">
-        <v>0.64</v>
-      </c>
       <c r="BK22" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="BL22" t="n">
         <v>0.93</v>
       </c>
       <c r="BM22" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BN22" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="BO22" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="BP22" t="n">
-        <v>4.29</v>
+        <v>4.6</v>
       </c>
       <c r="BQ22" t="n">
-        <v>4.71</v>
+        <v>4.6</v>
       </c>
       <c r="BR22" t="n">
-        <v>92.86</v>
+        <v>93.33</v>
       </c>
       <c r="BS22" t="n">
-        <v>64.29000000000001</v>
+        <v>66.67</v>
       </c>
       <c r="BT22" t="n">
-        <v>57.14</v>
+        <v>53.33</v>
       </c>
       <c r="BU22" t="n">
-        <v>28.57</v>
+        <v>26.67</v>
       </c>
       <c r="BV22" t="n">
-        <v>21.43</v>
+        <v>20</v>
       </c>
       <c r="BW22" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BX22" t="n">
-        <v>64.29000000000001</v>
+        <v>60</v>
       </c>
       <c r="BY22" t="n">
         <v>2.1</v>
@@ -9670,169 +9670,169 @@
         <v>2.14</v>
       </c>
       <c r="CA22" t="n">
-        <v>3.26</v>
+        <v>3.23</v>
       </c>
       <c r="CB22" t="n">
-        <v>3.35</v>
+        <v>3.32</v>
       </c>
       <c r="CC22" t="n">
-        <v>3.46</v>
+        <v>3.37</v>
       </c>
       <c r="CD22" t="n">
-        <v>3.41</v>
+        <v>3.47</v>
       </c>
       <c r="CE22" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CF22" t="n">
-        <v>3.04</v>
+        <v>3.09</v>
       </c>
       <c r="CG22" t="n">
-        <v>2.75</v>
+        <v>2.71</v>
       </c>
       <c r="CH22" t="n">
         <v>1.35</v>
       </c>
       <c r="CI22" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="CJ22" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="CK22" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CL22" t="n">
         <v>2.11</v>
       </c>
       <c r="CM22" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="CN22" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CO22" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="CP22" t="n">
-        <v>2.09</v>
+        <v>2.14</v>
       </c>
       <c r="CQ22" t="n">
-        <v>3.73</v>
+        <v>3.87</v>
       </c>
       <c r="CR22" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="CS22" t="n">
         <v>3.06</v>
       </c>
       <c r="CT22" t="n">
-        <v>2.86</v>
+        <v>2.82</v>
       </c>
       <c r="CU22" t="n">
         <v>1.41</v>
       </c>
       <c r="CV22" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="CW22" t="n">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="CX22" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CY22" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="CZ22" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="DA22" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="DB22" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="DC22" t="n">
-        <v>2.27</v>
+        <v>2.34</v>
       </c>
       <c r="DD22" t="n">
-        <v>4.16</v>
+        <v>4.37</v>
       </c>
       <c r="DE22" t="n">
         <v>0.14</v>
       </c>
       <c r="DF22" t="n">
+        <v>2</v>
+      </c>
+      <c r="DG22" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="DH22" t="n">
+        <v>99.33</v>
+      </c>
+      <c r="DI22" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ22" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="DK22" t="n">
+        <v>3.87</v>
+      </c>
+      <c r="DL22" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="DM22" t="n">
+        <v>40.8</v>
+      </c>
+      <c r="DN22" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="DO22" t="n">
         <v>2.07</v>
       </c>
-      <c r="DG22" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="DH22" t="n">
-        <v>98.56999999999999</v>
-      </c>
-      <c r="DI22" t="n">
-        <v>0</v>
-      </c>
-      <c r="DJ22" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="DK22" t="n">
-        <v>3.79</v>
-      </c>
-      <c r="DL22" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="DM22" t="n">
-        <v>39.78</v>
-      </c>
-      <c r="DN22" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="DO22" t="n">
-        <v>1.86</v>
-      </c>
       <c r="DP22" t="n">
-        <v>12.71</v>
+        <v>12.8</v>
       </c>
       <c r="DQ22" t="n">
-        <v>11.5</v>
+        <v>11.27</v>
       </c>
       <c r="DR22" t="n">
-        <v>7.64</v>
+        <v>7.6</v>
       </c>
       <c r="DS22" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DT22" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DU22" t="n">
         <v>0</v>
       </c>
       <c r="DV22" t="n">
-        <v>42.64</v>
+        <v>44</v>
       </c>
       <c r="DW22" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="DX22" t="n">
-        <v>10.07</v>
+        <v>10.2</v>
       </c>
       <c r="DY22" t="n">
-        <v>5.64</v>
+        <v>5.93</v>
       </c>
       <c r="DZ22" t="n">
-        <v>4.43</v>
+        <v>4.27</v>
       </c>
       <c r="EA22" t="n">
-        <v>20.07</v>
+        <v>20</v>
       </c>
       <c r="EB22" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="EC22" t="n">
-        <v>2.43</v>
+        <v>2.34</v>
       </c>
     </row>
     <row r="23">

--- a/data/teams/leagues/Averages_Spain_Segunda_División_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Spain_Segunda_División_2025-2026.xlsx
@@ -7490,16 +7490,16 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>44</v>
+        <v>43.88</v>
       </c>
       <c r="Y17" t="n">
         <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>10.5</v>
+        <v>10.62</v>
       </c>
       <c r="AA17" t="n">
-        <v>6.62</v>
+        <v>6.75</v>
       </c>
       <c r="AB17" t="n">
         <v>3.88</v>
@@ -7508,7 +7508,7 @@
         <v>20.25</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AE17" t="n">
         <v>3.12</v>
@@ -7658,7 +7658,7 @@
         <v>3.48</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.71</v>
+        <v>3.72</v>
       </c>
       <c r="CC17" t="n">
         <v>5.67</v>
@@ -7709,19 +7709,19 @@
         <v>1.48</v>
       </c>
       <c r="CS17" t="n">
-        <v>3.05</v>
+        <v>3.06</v>
       </c>
       <c r="CT17" t="n">
         <v>2.78</v>
       </c>
       <c r="CU17" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CV17" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="CW17" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CX17" t="n">
         <v>1.64</v>
@@ -7730,19 +7730,19 @@
         <v>2.06</v>
       </c>
       <c r="CZ17" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="DA17" t="n">
         <v>1.77</v>
       </c>
       <c r="DB17" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="DC17" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="DD17" t="n">
-        <v>4.01</v>
+        <v>3.98</v>
       </c>
       <c r="DE17" t="n">
         <v>0.06</v>
@@ -7796,16 +7796,16 @@
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>43.93</v>
+        <v>43.87</v>
       </c>
       <c r="DW17" t="n">
         <v>0</v>
       </c>
       <c r="DX17" t="n">
-        <v>10.87</v>
+        <v>10.93</v>
       </c>
       <c r="DY17" t="n">
-        <v>6.73</v>
+        <v>6.8</v>
       </c>
       <c r="DZ17" t="n">
         <v>4.14</v>
@@ -7956,7 +7956,7 @@
         <v>14.29</v>
       </c>
       <c r="AS18" t="n">
-        <v>8.57</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="AT18" t="n">
         <v>0.71</v>
@@ -7974,7 +7974,7 @@
         <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>51.14</v>
+        <v>51.29</v>
       </c>
       <c r="AZ18" t="n">
         <v>0.14</v>
@@ -8061,13 +8061,13 @@
         <v>3.29</v>
       </c>
       <c r="CB18" t="n">
-        <v>3.39</v>
+        <v>3.4</v>
       </c>
       <c r="CC18" t="n">
         <v>2.77</v>
       </c>
       <c r="CD18" t="n">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="CE18" t="n">
         <v>1.41</v>
@@ -8112,7 +8112,7 @@
         <v>1.46</v>
       </c>
       <c r="CS18" t="n">
-        <v>3.09</v>
+        <v>3.1</v>
       </c>
       <c r="CT18" t="n">
         <v>2.84</v>
@@ -8121,31 +8121,31 @@
         <v>1.4</v>
       </c>
       <c r="CV18" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CW18" t="n">
         <v>1.92</v>
       </c>
       <c r="CX18" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CY18" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="CZ18" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="DA18" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="DB18" t="n">
         <v>1.37</v>
       </c>
       <c r="DC18" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="DD18" t="n">
-        <v>4</v>
+        <v>3.98</v>
       </c>
       <c r="DE18" t="n">
         <v>0</v>
@@ -8187,7 +8187,7 @@
         <v>13.6</v>
       </c>
       <c r="DR18" t="n">
-        <v>7</v>
+        <v>7.06</v>
       </c>
       <c r="DS18" t="n">
         <v>0.2</v>
@@ -8199,7 +8199,7 @@
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>53.6</v>
+        <v>53.67</v>
       </c>
       <c r="DW18" t="n">
         <v>0.07000000000000001</v>

--- a/data/teams/leagues/Averages_Spain_Segunda_División_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Spain_Segunda_División_2025-2026.xlsx
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="n">
         <v>7</v>
       </c>
       <c r="D3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E3" t="n">
         <v>0.14</v>
@@ -1875,136 +1875,136 @@
         <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.86</v>
+        <v>1.5</v>
       </c>
       <c r="AI3" t="n">
-        <v>94.56999999999999</v>
+        <v>88.12</v>
       </c>
       <c r="AJ3" t="n">
         <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>3.43</v>
+        <v>3.62</v>
       </c>
       <c r="AL3" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>-0.12</v>
       </c>
       <c r="AN3" t="n">
-        <v>39.43</v>
+        <v>36.88</v>
       </c>
       <c r="AO3" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.14</v>
+        <v>0.88</v>
       </c>
       <c r="AQ3" t="n">
-        <v>14.29</v>
+        <v>14.62</v>
       </c>
       <c r="AR3" t="n">
-        <v>14.71</v>
+        <v>14.38</v>
       </c>
       <c r="AS3" t="n">
-        <v>8.140000000000001</v>
+        <v>7.88</v>
       </c>
       <c r="AT3" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AX3" t="n">
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>51.57</v>
+        <v>52.25</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="BA3" t="n">
-        <v>12.29</v>
+        <v>12.62</v>
       </c>
       <c r="BB3" t="n">
-        <v>8.859999999999999</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="BC3" t="n">
-        <v>3.43</v>
+        <v>3.75</v>
       </c>
       <c r="BD3" t="n">
-        <v>20</v>
+        <v>20.62</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="BF3" t="n">
-        <v>3.29</v>
+        <v>3.5</v>
       </c>
       <c r="BG3" t="n">
-        <v>3.36</v>
+        <v>3.47</v>
       </c>
       <c r="BH3" t="n">
-        <v>9.789999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.36</v>
+        <v>3.47</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="BL3" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="BM3" t="n">
         <v>1</v>
       </c>
       <c r="BN3" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="BP3" t="n">
-        <v>4.36</v>
+        <v>4</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5.36</v>
+        <v>4.93</v>
       </c>
       <c r="BR3" t="n">
         <v>100</v>
       </c>
       <c r="BS3" t="n">
-        <v>78.56999999999999</v>
+        <v>80</v>
       </c>
       <c r="BT3" t="n">
-        <v>64.29000000000001</v>
+        <v>66.67</v>
       </c>
       <c r="BU3" t="n">
-        <v>42.86</v>
+        <v>46.67</v>
       </c>
       <c r="BV3" t="n">
-        <v>21.43</v>
+        <v>26.67</v>
       </c>
       <c r="BW3" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="BX3" t="n">
-        <v>64.29000000000001</v>
+        <v>66.67</v>
       </c>
       <c r="BY3" t="n">
         <v>1.69</v>
@@ -2013,22 +2013,22 @@
         <v>1.76</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.47</v>
+        <v>3.45</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.68</v>
+        <v>3.65</v>
       </c>
       <c r="CC3" t="n">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="CD3" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="CE3" t="n">
         <v>1.35</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.63</v>
+        <v>2.64</v>
       </c>
       <c r="CG3" t="n">
         <v>2.97</v>
@@ -2046,34 +2046,34 @@
         <v>1.49</v>
       </c>
       <c r="CL3" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CO3" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="CP3" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3</v>
+        <v>3.01</v>
       </c>
       <c r="CR3" t="n">
         <v>1.38</v>
       </c>
       <c r="CS3" t="n">
-        <v>2.81</v>
+        <v>2.82</v>
       </c>
       <c r="CT3" t="n">
-        <v>3.16</v>
+        <v>3.15</v>
       </c>
       <c r="CU3" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CV3" t="n">
         <v>2.23</v>
@@ -2097,85 +2097,85 @@
         <v>1.27</v>
       </c>
       <c r="DC3" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="DD3" t="n">
-        <v>3.16</v>
+        <v>3.17</v>
       </c>
       <c r="DE3" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="DG3" t="n">
-        <v>2.72</v>
+        <v>2.47</v>
       </c>
       <c r="DH3" t="n">
-        <v>95.22</v>
+        <v>91.73</v>
       </c>
       <c r="DI3" t="n">
         <v>0</v>
       </c>
       <c r="DJ3" t="n">
-        <v>3.07</v>
+        <v>3.2</v>
       </c>
       <c r="DK3" t="n">
-        <v>5.57</v>
+        <v>5.33</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.28</v>
+        <v>0.2</v>
       </c>
       <c r="DM3" t="n">
-        <v>45.36</v>
+        <v>43.6</v>
       </c>
       <c r="DN3" t="n">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="DO3" t="n">
-        <v>2.78</v>
+        <v>2.54</v>
       </c>
       <c r="DP3" t="n">
-        <v>14</v>
+        <v>14.2</v>
       </c>
       <c r="DQ3" t="n">
-        <v>12.5</v>
+        <v>12.47</v>
       </c>
       <c r="DR3" t="n">
-        <v>7.86</v>
+        <v>7.74</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>53.22</v>
+        <v>53.47</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DX3" t="n">
-        <v>15.72</v>
+        <v>15.66</v>
       </c>
       <c r="DY3" t="n">
-        <v>9.93</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="DZ3" t="n">
-        <v>5.79</v>
+        <v>5.8</v>
       </c>
       <c r="EA3" t="n">
-        <v>18.36</v>
+        <v>18.8</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.86</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -2991,94 +2991,94 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D6" t="n">
         <v>8</v>
       </c>
       <c r="E6" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="G6" t="n">
-        <v>3.67</v>
+        <v>3</v>
       </c>
       <c r="H6" t="n">
-        <v>109.83</v>
+        <v>101</v>
       </c>
       <c r="I6" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="J6" t="n">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="K6" t="n">
-        <v>5.83</v>
+        <v>5.29</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5</v>
+        <v>0.29</v>
       </c>
       <c r="M6" t="n">
-        <v>61.5</v>
+        <v>55.43</v>
       </c>
       <c r="N6" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="O6" t="n">
-        <v>2.17</v>
+        <v>1.71</v>
       </c>
       <c r="P6" t="n">
-        <v>14</v>
+        <v>13.71</v>
       </c>
       <c r="Q6" t="n">
-        <v>13.33</v>
+        <v>13.71</v>
       </c>
       <c r="R6" t="n">
-        <v>5.17</v>
+        <v>5.43</v>
       </c>
       <c r="S6" t="n">
-        <v>0.67</v>
+        <v>0.86</v>
       </c>
       <c r="T6" t="n">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>58</v>
+        <v>55.86</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>11.67</v>
+        <v>11.43</v>
       </c>
       <c r="AA6" t="n">
-        <v>7.83</v>
+        <v>7.14</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.83</v>
+        <v>4.29</v>
       </c>
       <c r="AC6" t="n">
-        <v>21.33</v>
+        <v>21.29</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="AF6" t="n">
         <v>0.12</v>
@@ -3162,70 +3162,70 @@
         <v>2.12</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.21</v>
+        <v>2.4</v>
       </c>
       <c r="BH6" t="n">
-        <v>8.859999999999999</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.21</v>
+        <v>2.4</v>
       </c>
       <c r="BJ6" t="n">
         <v>0.93</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.57</v>
+        <v>0.67</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="BN6" t="n">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="BP6" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.36</v>
+        <v>4.93</v>
       </c>
       <c r="BR6" t="n">
-        <v>85.70999999999999</v>
+        <v>86.67</v>
       </c>
       <c r="BS6" t="n">
-        <v>57.14</v>
+        <v>60</v>
       </c>
       <c r="BT6" t="n">
-        <v>42.86</v>
+        <v>46.67</v>
       </c>
       <c r="BU6" t="n">
-        <v>14.29</v>
+        <v>20</v>
       </c>
       <c r="BV6" t="n">
-        <v>14.29</v>
+        <v>20</v>
       </c>
       <c r="BW6" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BX6" t="n">
-        <v>35.71</v>
+        <v>40</v>
       </c>
       <c r="BY6" t="n">
-        <v>2.34</v>
+        <v>2.42</v>
       </c>
       <c r="BZ6" t="n">
-        <v>2.52</v>
+        <v>2.63</v>
       </c>
       <c r="CA6" t="n">
         <v>3.29</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.4</v>
+        <v>3.39</v>
       </c>
       <c r="CC6" t="n">
         <v>4.26</v>
@@ -3234,61 +3234,61 @@
         <v>4.67</v>
       </c>
       <c r="CE6" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CF6" t="n">
-        <v>3.01</v>
+        <v>2.99</v>
       </c>
       <c r="CG6" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="CH6" t="n">
         <v>1.36</v>
       </c>
       <c r="CI6" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CJ6" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="CK6" t="n">
         <v>1.65</v>
       </c>
       <c r="CL6" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="CN6" t="n">
         <v>1.67</v>
       </c>
       <c r="CO6" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CP6" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="CQ6" t="n">
-        <v>3.89</v>
+        <v>3.84</v>
       </c>
       <c r="CR6" t="n">
         <v>1.45</v>
       </c>
       <c r="CS6" t="n">
-        <v>3.12</v>
+        <v>3.1</v>
       </c>
       <c r="CT6" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="CU6" t="n">
         <v>1.4</v>
       </c>
       <c r="CV6" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="CW6" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CX6" t="n">
         <v>1.67</v>
@@ -3303,88 +3303,88 @@
         <v>1.73</v>
       </c>
       <c r="DB6" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="DC6" t="n">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="DD6" t="n">
-        <v>3.95</v>
+        <v>3.91</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.14</v>
+        <v>0.2</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.5</v>
+        <v>2.26</v>
       </c>
       <c r="DH6" t="n">
-        <v>92.84999999999999</v>
+        <v>89.86</v>
       </c>
       <c r="DI6" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="DK6" t="n">
-        <v>4.36</v>
+        <v>4.2</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="DM6" t="n">
-        <v>45.79</v>
+        <v>44</v>
       </c>
       <c r="DN6" t="n">
         <v>1.07</v>
       </c>
       <c r="DO6" t="n">
-        <v>1.86</v>
+        <v>1.66</v>
       </c>
       <c r="DP6" t="n">
-        <v>13.21</v>
+        <v>13.13</v>
       </c>
       <c r="DQ6" t="n">
-        <v>13.57</v>
+        <v>13.73</v>
       </c>
       <c r="DR6" t="n">
-        <v>7.58</v>
+        <v>7.54</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.14</v>
+        <v>0.2</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.14</v>
+        <v>0.2</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>52.14</v>
+        <v>51.53</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DX6" t="n">
         <v>10</v>
       </c>
       <c r="DY6" t="n">
-        <v>7.14</v>
+        <v>6.86</v>
       </c>
       <c r="DZ6" t="n">
-        <v>2.85</v>
+        <v>3.13</v>
       </c>
       <c r="EA6" t="n">
-        <v>20.43</v>
+        <v>20.47</v>
       </c>
       <c r="EB6" t="n">
         <v>1.17</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.28</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="7">
@@ -5006,13 +5006,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
         <v>7</v>
       </c>
       <c r="D11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -5096,139 +5096,139 @@
         <v>2</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AG11" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>93.44</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>39.56</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>13.89</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>14.78</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>7.11</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>55.44</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>14.33</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>9.890000000000001</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>17.89</v>
+      </c>
+      <c r="BE11" t="n">
         <v>1.5</v>
       </c>
-      <c r="AH11" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>95.38</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>40.38</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>14.62</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>15.25</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>6.88</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>55.38</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>14.88</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>10.12</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>17.12</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>1.57</v>
-      </c>
       <c r="BF11" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.67</v>
+        <v>2.62</v>
       </c>
       <c r="BH11" t="n">
-        <v>9.130000000000001</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.67</v>
+        <v>2.62</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="BL11" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="BO11" t="n">
-        <v>0.87</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.07</v>
+        <v>4.06</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="BR11" t="n">
-        <v>86.67</v>
+        <v>87.5</v>
       </c>
       <c r="BS11" t="n">
-        <v>80</v>
+        <v>81.25</v>
       </c>
       <c r="BT11" t="n">
-        <v>60</v>
+        <v>56.25</v>
       </c>
       <c r="BU11" t="n">
-        <v>33.33</v>
+        <v>31.25</v>
       </c>
       <c r="BV11" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BW11" t="n">
         <v>0</v>
       </c>
       <c r="BX11" t="n">
-        <v>66.67</v>
+        <v>68.75</v>
       </c>
       <c r="BY11" t="n">
         <v>2.19</v>
@@ -5237,16 +5237,16 @@
         <v>2.25</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.24</v>
+        <v>3.25</v>
       </c>
       <c r="CB11" t="n">
         <v>3.42</v>
       </c>
       <c r="CC11" t="n">
-        <v>3.72</v>
+        <v>3.71</v>
       </c>
       <c r="CD11" t="n">
-        <v>3.98</v>
+        <v>4.04</v>
       </c>
       <c r="CE11" t="n">
         <v>1.42</v>
@@ -5255,7 +5255,7 @@
         <v>2.95</v>
       </c>
       <c r="CG11" t="n">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="CH11" t="n">
         <v>1.36</v>
@@ -5264,19 +5264,19 @@
         <v>1.92</v>
       </c>
       <c r="CJ11" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CK11" t="n">
         <v>1.66</v>
       </c>
       <c r="CL11" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="CN11" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CO11" t="n">
         <v>1.33</v>
@@ -5285,22 +5285,22 @@
         <v>2.07</v>
       </c>
       <c r="CQ11" t="n">
-        <v>3.62</v>
+        <v>3.61</v>
       </c>
       <c r="CR11" t="n">
         <v>1.45</v>
       </c>
       <c r="CS11" t="n">
-        <v>3.06</v>
+        <v>3.07</v>
       </c>
       <c r="CT11" t="n">
         <v>2.87</v>
       </c>
       <c r="CU11" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CV11" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CW11" t="n">
         <v>1.88</v>
@@ -5312,10 +5312,10 @@
         <v>2.1</v>
       </c>
       <c r="CZ11" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="DA11" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="DB11" t="n">
         <v>1.35</v>
@@ -5330,43 +5330,43 @@
         <v>0.06</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.53</v>
+        <v>1.69</v>
       </c>
       <c r="DG11" t="n">
-        <v>3.07</v>
+        <v>3.06</v>
       </c>
       <c r="DH11" t="n">
-        <v>101.33</v>
+        <v>99.87</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.66</v>
+        <v>2.75</v>
       </c>
       <c r="DK11" t="n">
-        <v>4.67</v>
+        <v>4.69</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.06</v>
+        <v>0.12</v>
       </c>
       <c r="DM11" t="n">
-        <v>44.07</v>
+        <v>43.38</v>
       </c>
       <c r="DN11" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="DO11" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="DP11" t="n">
-        <v>14.4</v>
+        <v>14</v>
       </c>
       <c r="DQ11" t="n">
-        <v>15.27</v>
+        <v>15</v>
       </c>
       <c r="DR11" t="n">
-        <v>7.6</v>
+        <v>7.69</v>
       </c>
       <c r="DS11" t="n">
         <v>0.06</v>
@@ -5378,28 +5378,28 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>56.47</v>
+        <v>56.43</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DX11" t="n">
-        <v>14.07</v>
+        <v>13.81</v>
       </c>
       <c r="DY11" t="n">
-        <v>9.27</v>
+        <v>9.19</v>
       </c>
       <c r="DZ11" t="n">
-        <v>4.8</v>
+        <v>4.62</v>
       </c>
       <c r="EA11" t="n">
-        <v>18.13</v>
+        <v>18.5</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.47</v>
+        <v>2.56</v>
       </c>
     </row>
     <row r="12">
@@ -9439,10 +9439,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D22" t="n">
         <v>7</v>
@@ -9451,82 +9451,82 @@
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>1.62</v>
+        <v>1.78</v>
       </c>
       <c r="G22" t="n">
-        <v>2.25</v>
+        <v>2.67</v>
       </c>
       <c r="H22" t="n">
-        <v>110.38</v>
+        <v>112.11</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="K22" t="n">
-        <v>5</v>
+        <v>5.33</v>
       </c>
       <c r="L22" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="M22" t="n">
-        <v>47.62</v>
+        <v>48.44</v>
       </c>
       <c r="N22" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="O22" t="n">
-        <v>2.75</v>
+        <v>2.67</v>
       </c>
       <c r="P22" t="n">
-        <v>13.12</v>
+        <v>12.89</v>
       </c>
       <c r="Q22" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="R22" t="n">
-        <v>7</v>
+        <v>7.33</v>
       </c>
       <c r="S22" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T22" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="U22" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="V22" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>45.12</v>
+        <v>45</v>
       </c>
       <c r="Y22" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="Z22" t="n">
-        <v>12.12</v>
+        <v>13.33</v>
       </c>
       <c r="AA22" t="n">
-        <v>7.25</v>
+        <v>7.89</v>
       </c>
       <c r="AB22" t="n">
-        <v>4.88</v>
+        <v>5.44</v>
       </c>
       <c r="AC22" t="n">
-        <v>20.62</v>
+        <v>20.22</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.46</v>
+        <v>1.58</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AF22" t="n">
         <v>0.29</v>
@@ -9610,70 +9610,70 @@
         <v>2.86</v>
       </c>
       <c r="BG22" t="n">
-        <v>2.73</v>
+        <v>2.69</v>
       </c>
       <c r="BH22" t="n">
-        <v>9.27</v>
+        <v>9.5</v>
       </c>
       <c r="BI22" t="n">
-        <v>2.73</v>
+        <v>2.69</v>
       </c>
       <c r="BJ22" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BK22" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BL22" t="n">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BM22" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="BN22" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="BO22" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="BP22" t="n">
-        <v>4.6</v>
+        <v>4.56</v>
       </c>
       <c r="BQ22" t="n">
-        <v>4.6</v>
+        <v>4.88</v>
       </c>
       <c r="BR22" t="n">
-        <v>93.33</v>
+        <v>93.75</v>
       </c>
       <c r="BS22" t="n">
-        <v>66.67</v>
+        <v>68.75</v>
       </c>
       <c r="BT22" t="n">
-        <v>53.33</v>
+        <v>50</v>
       </c>
       <c r="BU22" t="n">
-        <v>26.67</v>
+        <v>25</v>
       </c>
       <c r="BV22" t="n">
-        <v>20</v>
+        <v>18.75</v>
       </c>
       <c r="BW22" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BX22" t="n">
-        <v>60</v>
+        <v>62.5</v>
       </c>
       <c r="BY22" t="n">
         <v>2.1</v>
       </c>
       <c r="BZ22" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="CA22" t="n">
         <v>3.23</v>
       </c>
       <c r="CB22" t="n">
-        <v>3.32</v>
+        <v>3.33</v>
       </c>
       <c r="CC22" t="n">
         <v>3.37</v>
@@ -9685,10 +9685,10 @@
         <v>1.43</v>
       </c>
       <c r="CF22" t="n">
-        <v>3.09</v>
+        <v>3.07</v>
       </c>
       <c r="CG22" t="n">
-        <v>2.71</v>
+        <v>2.72</v>
       </c>
       <c r="CH22" t="n">
         <v>1.35</v>
@@ -9706,7 +9706,7 @@
         <v>2.11</v>
       </c>
       <c r="CM22" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="CN22" t="n">
         <v>1.72</v>
@@ -9718,19 +9718,19 @@
         <v>2.14</v>
       </c>
       <c r="CQ22" t="n">
-        <v>3.87</v>
+        <v>3.84</v>
       </c>
       <c r="CR22" t="n">
         <v>1.47</v>
       </c>
       <c r="CS22" t="n">
-        <v>3.06</v>
+        <v>3.07</v>
       </c>
       <c r="CT22" t="n">
         <v>2.82</v>
       </c>
       <c r="CU22" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CV22" t="n">
         <v>1.95</v>
@@ -9745,67 +9745,67 @@
         <v>2.07</v>
       </c>
       <c r="CZ22" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="DA22" t="n">
         <v>1.76</v>
       </c>
       <c r="DB22" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="DC22" t="n">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="DD22" t="n">
-        <v>4.37</v>
+        <v>4.33</v>
       </c>
       <c r="DE22" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF22" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="DG22" t="n">
-        <v>1.8</v>
+        <v>2.07</v>
       </c>
       <c r="DH22" t="n">
-        <v>99.33</v>
+        <v>101</v>
       </c>
       <c r="DI22" t="n">
         <v>0</v>
       </c>
       <c r="DJ22" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="DK22" t="n">
-        <v>3.87</v>
+        <v>4.12</v>
       </c>
       <c r="DL22" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="DM22" t="n">
-        <v>40.8</v>
+        <v>41.68</v>
       </c>
       <c r="DN22" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DO22" t="n">
         <v>2.07</v>
       </c>
       <c r="DP22" t="n">
-        <v>12.8</v>
+        <v>12.69</v>
       </c>
       <c r="DQ22" t="n">
-        <v>11.27</v>
+        <v>11</v>
       </c>
       <c r="DR22" t="n">
-        <v>7.6</v>
+        <v>7.75</v>
       </c>
       <c r="DS22" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="DT22" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="DU22" t="n">
         <v>0</v>
@@ -9814,25 +9814,25 @@
         <v>44</v>
       </c>
       <c r="DW22" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DX22" t="n">
-        <v>10.2</v>
+        <v>11</v>
       </c>
       <c r="DY22" t="n">
-        <v>5.93</v>
+        <v>6.38</v>
       </c>
       <c r="DZ22" t="n">
-        <v>4.27</v>
+        <v>4.62</v>
       </c>
       <c r="EA22" t="n">
-        <v>20</v>
+        <v>19.81</v>
       </c>
       <c r="EB22" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="EC22" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="23">

--- a/data/teams/leagues/Averages_Spain_Segunda_División_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Spain_Segunda_División_2025-2026.xlsx
@@ -2185,13 +2185,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C4" t="n">
         <v>8</v>
       </c>
       <c r="D4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E4" t="n">
         <v>0.12</v>
@@ -2275,139 +2275,139 @@
         <v>3.12</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.43</v>
+        <v>1.62</v>
       </c>
       <c r="AH4" t="n">
-        <v>2</v>
+        <v>2.38</v>
       </c>
       <c r="AI4" t="n">
-        <v>85.14</v>
+        <v>86.25</v>
       </c>
       <c r="AJ4" t="n">
         <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="AL4" t="n">
-        <v>3.86</v>
+        <v>4.25</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="AN4" t="n">
-        <v>39.43</v>
+        <v>39.5</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="AQ4" t="n">
-        <v>13.71</v>
+        <v>13.5</v>
       </c>
       <c r="AR4" t="n">
-        <v>13.57</v>
+        <v>14.5</v>
       </c>
       <c r="AS4" t="n">
-        <v>9.43</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="AX4" t="n">
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>46.14</v>
+        <v>46.25</v>
       </c>
       <c r="AZ4" t="n">
         <v>0</v>
       </c>
       <c r="BA4" t="n">
-        <v>8.859999999999999</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="BB4" t="n">
-        <v>5.71</v>
+        <v>6</v>
       </c>
       <c r="BC4" t="n">
-        <v>3.14</v>
+        <v>2.88</v>
       </c>
       <c r="BD4" t="n">
-        <v>22.43</v>
+        <v>21.88</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="BF4" t="n">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="BH4" t="n">
-        <v>7.8</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="BP4" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4</v>
+        <v>4.38</v>
       </c>
       <c r="BR4" t="n">
-        <v>80</v>
+        <v>81.25</v>
       </c>
       <c r="BS4" t="n">
-        <v>66.67</v>
+        <v>62.5</v>
       </c>
       <c r="BT4" t="n">
-        <v>46.67</v>
+        <v>43.75</v>
       </c>
       <c r="BU4" t="n">
-        <v>20</v>
+        <v>18.75</v>
       </c>
       <c r="BV4" t="n">
-        <v>13.33</v>
+        <v>12.5</v>
       </c>
       <c r="BW4" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BX4" t="n">
-        <v>53.33</v>
+        <v>50</v>
       </c>
       <c r="BY4" t="n">
         <v>2.3</v>
@@ -2416,16 +2416,16 @@
         <v>2.29</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.01</v>
+        <v>3</v>
       </c>
       <c r="CB4" t="n">
         <v>3.09</v>
       </c>
       <c r="CC4" t="n">
-        <v>3.58</v>
+        <v>3.56</v>
       </c>
       <c r="CD4" t="n">
-        <v>3.91</v>
+        <v>3.9</v>
       </c>
       <c r="CE4" t="n">
         <v>1.55</v>
@@ -2434,7 +2434,7 @@
         <v>3.47</v>
       </c>
       <c r="CG4" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="CH4" t="n">
         <v>1.26</v>
@@ -2449,7 +2449,7 @@
         <v>1.74</v>
       </c>
       <c r="CL4" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="CM4" t="n">
         <v>2.02</v>
@@ -2458,13 +2458,13 @@
         <v>1.63</v>
       </c>
       <c r="CO4" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="CP4" t="n">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="CQ4" t="n">
-        <v>4.84</v>
+        <v>4.85</v>
       </c>
       <c r="CR4" t="n">
         <v>1.6</v>
@@ -2485,7 +2485,7 @@
         <v>2.24</v>
       </c>
       <c r="CX4" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CY4" t="n">
         <v>2.26</v>
@@ -2494,7 +2494,7 @@
         <v>2.02</v>
       </c>
       <c r="DA4" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="DB4" t="n">
         <v>1.55</v>
@@ -2506,79 +2506,79 @@
         <v>5.43</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="DG4" t="n">
-        <v>1.94</v>
+        <v>2.13</v>
       </c>
       <c r="DH4" t="n">
-        <v>90.13</v>
+        <v>90.38</v>
       </c>
       <c r="DI4" t="n">
         <v>0</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="DK4" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.12</v>
       </c>
       <c r="DM4" t="n">
-        <v>43.53</v>
+        <v>43.31</v>
       </c>
       <c r="DN4" t="n">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="DO4" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="DP4" t="n">
-        <v>13.8</v>
+        <v>13.69</v>
       </c>
       <c r="DQ4" t="n">
-        <v>14.2</v>
+        <v>14.62</v>
       </c>
       <c r="DR4" t="n">
         <v>9</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>48</v>
+        <v>47.94</v>
       </c>
       <c r="DW4" t="n">
         <v>0</v>
       </c>
       <c r="DX4" t="n">
-        <v>9.67</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="DY4" t="n">
-        <v>6.66</v>
+        <v>6.75</v>
       </c>
       <c r="DZ4" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="EA4" t="n">
-        <v>24.6</v>
+        <v>24.19</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="5">
@@ -2991,94 +2991,94 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D6" t="n">
         <v>8</v>
       </c>
       <c r="E6" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="F6" t="n">
-        <v>1.14</v>
+        <v>1.5</v>
       </c>
       <c r="G6" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="H6" t="n">
-        <v>101</v>
+        <v>99.38</v>
       </c>
       <c r="I6" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="J6" t="n">
-        <v>2.57</v>
+        <v>2.88</v>
       </c>
       <c r="K6" t="n">
-        <v>5.29</v>
+        <v>5.88</v>
       </c>
       <c r="L6" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="M6" t="n">
-        <v>55.43</v>
+        <v>55.25</v>
       </c>
       <c r="N6" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="O6" t="n">
-        <v>1.71</v>
+        <v>2.12</v>
       </c>
       <c r="P6" t="n">
-        <v>13.71</v>
+        <v>14.62</v>
       </c>
       <c r="Q6" t="n">
-        <v>13.71</v>
+        <v>13.5</v>
       </c>
       <c r="R6" t="n">
-        <v>5.43</v>
+        <v>5.25</v>
       </c>
       <c r="S6" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="T6" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="U6" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="V6" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>55.86</v>
+        <v>55.5</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>11.43</v>
+        <v>11.75</v>
       </c>
       <c r="AA6" t="n">
-        <v>7.14</v>
+        <v>7.38</v>
       </c>
       <c r="AB6" t="n">
-        <v>4.29</v>
+        <v>4.38</v>
       </c>
       <c r="AC6" t="n">
-        <v>21.29</v>
+        <v>21.25</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.57</v>
+        <v>2.88</v>
       </c>
       <c r="AF6" t="n">
         <v>0.12</v>
@@ -3162,70 +3162,70 @@
         <v>2.12</v>
       </c>
       <c r="BG6" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>9.06</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>1</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>56.25</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>43.75</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="BY6" t="n">
         <v>2.4</v>
       </c>
-      <c r="BH6" t="n">
-        <v>8.529999999999999</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="BM6" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="BN6" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="BO6" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="BP6" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BQ6" t="n">
-        <v>4.93</v>
-      </c>
-      <c r="BR6" t="n">
-        <v>86.67</v>
-      </c>
-      <c r="BS6" t="n">
-        <v>60</v>
-      </c>
-      <c r="BT6" t="n">
-        <v>46.67</v>
-      </c>
-      <c r="BU6" t="n">
-        <v>20</v>
-      </c>
-      <c r="BV6" t="n">
-        <v>20</v>
-      </c>
-      <c r="BW6" t="n">
-        <v>6.67</v>
-      </c>
-      <c r="BX6" t="n">
-        <v>40</v>
-      </c>
-      <c r="BY6" t="n">
-        <v>2.42</v>
-      </c>
       <c r="BZ6" t="n">
-        <v>2.63</v>
+        <v>2.58</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.29</v>
+        <v>3.26</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.39</v>
+        <v>3.37</v>
       </c>
       <c r="CC6" t="n">
         <v>4.26</v>
@@ -3234,22 +3234,22 @@
         <v>4.67</v>
       </c>
       <c r="CE6" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.99</v>
+        <v>3.02</v>
       </c>
       <c r="CG6" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="CH6" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CI6" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CJ6" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="CK6" t="n">
         <v>1.65</v>
@@ -3264,13 +3264,13 @@
         <v>1.67</v>
       </c>
       <c r="CO6" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CP6" t="n">
-        <v>2.16</v>
+        <v>2.19</v>
       </c>
       <c r="CQ6" t="n">
-        <v>3.84</v>
+        <v>3.91</v>
       </c>
       <c r="CR6" t="n">
         <v>1.45</v>
@@ -3285,10 +3285,10 @@
         <v>1.4</v>
       </c>
       <c r="CV6" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="CW6" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="CX6" t="n">
         <v>1.67</v>
@@ -3297,94 +3297,94 @@
         <v>2.1</v>
       </c>
       <c r="CZ6" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="DA6" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="DB6" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="DC6" t="n">
-        <v>2.17</v>
+        <v>2.21</v>
       </c>
       <c r="DD6" t="n">
-        <v>3.91</v>
+        <v>4.02</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.4</v>
+        <v>1.56</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.26</v>
+        <v>2.44</v>
       </c>
       <c r="DH6" t="n">
-        <v>89.86</v>
+        <v>89.75</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.12</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.53</v>
+        <v>2.69</v>
       </c>
       <c r="DK6" t="n">
-        <v>4.2</v>
+        <v>4.56</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="DM6" t="n">
-        <v>44</v>
+        <v>44.62</v>
       </c>
       <c r="DN6" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="DO6" t="n">
-        <v>1.66</v>
+        <v>1.87</v>
       </c>
       <c r="DP6" t="n">
-        <v>13.13</v>
+        <v>13.62</v>
       </c>
       <c r="DQ6" t="n">
-        <v>13.73</v>
+        <v>13.62</v>
       </c>
       <c r="DR6" t="n">
-        <v>7.54</v>
+        <v>7.32</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>51.53</v>
+        <v>51.62</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DX6" t="n">
-        <v>10</v>
+        <v>10.25</v>
       </c>
       <c r="DY6" t="n">
-        <v>6.86</v>
+        <v>7</v>
       </c>
       <c r="DZ6" t="n">
-        <v>3.13</v>
+        <v>3.25</v>
       </c>
       <c r="EA6" t="n">
-        <v>20.47</v>
+        <v>20.5</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="7">
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D7" t="n">
         <v>8</v>
@@ -3406,49 +3406,49 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="G7" t="n">
-        <v>3.43</v>
+        <v>3.5</v>
       </c>
       <c r="H7" t="n">
-        <v>91.43000000000001</v>
+        <v>90</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="K7" t="n">
-        <v>4.86</v>
+        <v>4.75</v>
       </c>
       <c r="L7" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="M7" t="n">
-        <v>41.86</v>
+        <v>40.25</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="P7" t="n">
-        <v>13.29</v>
+        <v>13</v>
       </c>
       <c r="Q7" t="n">
-        <v>12</v>
+        <v>13.25</v>
       </c>
       <c r="R7" t="n">
-        <v>8</v>
+        <v>8.25</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
       </c>
       <c r="T7" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -3460,28 +3460,28 @@
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>51.14</v>
+        <v>51.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="Z7" t="n">
-        <v>10.43</v>
+        <v>10.38</v>
       </c>
       <c r="AA7" t="n">
-        <v>7.57</v>
+        <v>7.38</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.86</v>
+        <v>3</v>
       </c>
       <c r="AC7" t="n">
-        <v>18.71</v>
+        <v>19.12</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AE7" t="n">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="AF7" t="n">
         <v>0.25</v>
@@ -3565,70 +3565,70 @@
         <v>1.62</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.53</v>
+        <v>2.44</v>
       </c>
       <c r="BH7" t="n">
-        <v>8.800000000000001</v>
+        <v>8.75</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.53</v>
+        <v>2.44</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="BP7" t="n">
-        <v>3.73</v>
+        <v>3.69</v>
       </c>
       <c r="BQ7" t="n">
-        <v>5.07</v>
+        <v>5.06</v>
       </c>
       <c r="BR7" t="n">
-        <v>86.67</v>
+        <v>87.5</v>
       </c>
       <c r="BS7" t="n">
-        <v>46.67</v>
+        <v>43.75</v>
       </c>
       <c r="BT7" t="n">
-        <v>46.67</v>
+        <v>43.75</v>
       </c>
       <c r="BU7" t="n">
-        <v>33.33</v>
+        <v>31.25</v>
       </c>
       <c r="BV7" t="n">
-        <v>26.67</v>
+        <v>25</v>
       </c>
       <c r="BW7" t="n">
-        <v>13.33</v>
+        <v>12.5</v>
       </c>
       <c r="BX7" t="n">
-        <v>33.33</v>
+        <v>31.25</v>
       </c>
       <c r="BY7" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="BZ7" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.41</v>
+        <v>3.4</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.57</v>
+        <v>3.53</v>
       </c>
       <c r="CC7" t="n">
         <v>4.98</v>
@@ -3640,10 +3640,10 @@
         <v>1.42</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.81</v>
+        <v>2.79</v>
       </c>
       <c r="CH7" t="n">
         <v>1.38</v>
@@ -3652,13 +3652,13 @@
         <v>1.88</v>
       </c>
       <c r="CJ7" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CK7" t="n">
         <v>1.58</v>
       </c>
       <c r="CL7" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="CM7" t="n">
         <v>2.27</v>
@@ -3673,7 +3673,7 @@
         <v>2.05</v>
       </c>
       <c r="CQ7" t="n">
-        <v>3.57</v>
+        <v>3.58</v>
       </c>
       <c r="CR7" t="n">
         <v>1.45</v>
@@ -3709,52 +3709,52 @@
         <v>1.35</v>
       </c>
       <c r="DC7" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="DD7" t="n">
-        <v>3.74</v>
+        <v>3.77</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="DG7" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="DH7" t="n">
-        <v>82.8</v>
+        <v>82.62</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DJ7" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="DK7" t="n">
-        <v>4.07</v>
+        <v>4.06</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="DM7" t="n">
-        <v>37.27</v>
+        <v>36.75</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DO7" t="n">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="DP7" t="n">
-        <v>13.07</v>
+        <v>12.94</v>
       </c>
       <c r="DQ7" t="n">
-        <v>12.13</v>
+        <v>12.75</v>
       </c>
       <c r="DR7" t="n">
-        <v>9.07</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="DS7" t="n">
         <v>0.06</v>
@@ -3766,28 +3766,28 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>46.93</v>
+        <v>47.38</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DX7" t="n">
-        <v>11.27</v>
+        <v>11.19</v>
       </c>
       <c r="DY7" t="n">
-        <v>7.13</v>
+        <v>7.06</v>
       </c>
       <c r="DZ7" t="n">
-        <v>4.13</v>
+        <v>4.12</v>
       </c>
       <c r="EA7" t="n">
-        <v>17.6</v>
+        <v>17.87</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="EC7" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
     </row>
     <row r="8">
@@ -5409,13 +5409,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C12" t="n">
         <v>8</v>
       </c>
       <c r="D12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E12" t="n">
         <v>0.25</v>
@@ -5508,40 +5508,40 @@
         <v>1</v>
       </c>
       <c r="AI12" t="n">
-        <v>90.29000000000001</v>
+        <v>92</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AK12" t="n">
         <v>3</v>
       </c>
       <c r="AL12" t="n">
-        <v>2.29</v>
+        <v>2.5</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="AN12" t="n">
-        <v>35.57</v>
+        <v>36.88</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AQ12" t="n">
-        <v>13.86</v>
+        <v>14.88</v>
       </c>
       <c r="AR12" t="n">
-        <v>15.14</v>
+        <v>14.62</v>
       </c>
       <c r="AS12" t="n">
-        <v>9</v>
+        <v>8.75</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AU12" t="n">
         <v>1</v>
@@ -5556,82 +5556,82 @@
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>45.57</v>
+        <v>45.62</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="BA12" t="n">
-        <v>10.14</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="BB12" t="n">
-        <v>6.71</v>
+        <v>6.5</v>
       </c>
       <c r="BC12" t="n">
-        <v>3.43</v>
+        <v>3.38</v>
       </c>
       <c r="BD12" t="n">
-        <v>22.57</v>
+        <v>20.75</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="BF12" t="n">
-        <v>2.57</v>
+        <v>2.62</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.199999999999999</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="BP12" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.4</v>
+        <v>5.38</v>
       </c>
       <c r="BR12" t="n">
-        <v>80</v>
+        <v>81.25</v>
       </c>
       <c r="BS12" t="n">
-        <v>73.33</v>
+        <v>68.75</v>
       </c>
       <c r="BT12" t="n">
-        <v>53.33</v>
+        <v>50</v>
       </c>
       <c r="BU12" t="n">
-        <v>33.33</v>
+        <v>31.25</v>
       </c>
       <c r="BV12" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BW12" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BX12" t="n">
-        <v>60</v>
+        <v>56.25</v>
       </c>
       <c r="BY12" t="n">
         <v>2.14</v>
@@ -5643,13 +5643,13 @@
         <v>3.2</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.28</v>
+        <v>3.26</v>
       </c>
       <c r="CC12" t="n">
-        <v>3.61</v>
+        <v>3.52</v>
       </c>
       <c r="CD12" t="n">
-        <v>4.02</v>
+        <v>3.9</v>
       </c>
       <c r="CE12" t="n">
         <v>1.46</v>
@@ -5667,16 +5667,16 @@
         <v>1.84</v>
       </c>
       <c r="CJ12" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CL12" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="CN12" t="n">
         <v>1.77</v>
@@ -5688,7 +5688,7 @@
         <v>2.22</v>
       </c>
       <c r="CQ12" t="n">
-        <v>3.97</v>
+        <v>3.96</v>
       </c>
       <c r="CR12" t="n">
         <v>1.5</v>
@@ -5703,22 +5703,22 @@
         <v>1.35</v>
       </c>
       <c r="CV12" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CW12" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CX12" t="n">
         <v>1.68</v>
       </c>
       <c r="CY12" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="CZ12" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="DA12" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="DB12" t="n">
         <v>1.42</v>
@@ -5727,49 +5727,49 @@
         <v>2.32</v>
       </c>
       <c r="DD12" t="n">
-        <v>4.31</v>
+        <v>4.3</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="DH12" t="n">
-        <v>90.54000000000001</v>
+        <v>91.38</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="DK12" t="n">
-        <v>4.27</v>
+        <v>4.25</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="DM12" t="n">
-        <v>40.2</v>
+        <v>40.56</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="DO12" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="DP12" t="n">
-        <v>13.13</v>
+        <v>13.69</v>
       </c>
       <c r="DQ12" t="n">
-        <v>15.73</v>
+        <v>15.43</v>
       </c>
       <c r="DR12" t="n">
-        <v>8.140000000000001</v>
+        <v>8.06</v>
       </c>
       <c r="DS12" t="n">
         <v>0</v>
@@ -5781,28 +5781,28 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>48.6</v>
+        <v>48.44</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DX12" t="n">
-        <v>12.6</v>
+        <v>12.32</v>
       </c>
       <c r="DY12" t="n">
-        <v>8.93</v>
+        <v>8.69</v>
       </c>
       <c r="DZ12" t="n">
-        <v>3.67</v>
+        <v>3.63</v>
       </c>
       <c r="EA12" t="n">
-        <v>22.53</v>
+        <v>21.62</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="13">

--- a/data/teams/leagues/Averages_Spain_Segunda_División_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Spain_Segunda_División_2025-2026.xlsx
@@ -1379,10 +1379,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D2" t="n">
         <v>8</v>
@@ -1391,49 +1391,49 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="G2" t="n">
-        <v>2.57</v>
+        <v>2.88</v>
       </c>
       <c r="H2" t="n">
-        <v>91.43000000000001</v>
+        <v>92</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.14</v>
+        <v>-0.12</v>
       </c>
       <c r="J2" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="K2" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="L2" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="M2" t="n">
-        <v>48.86</v>
+        <v>45.75</v>
       </c>
       <c r="N2" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="O2" t="n">
-        <v>2.43</v>
+        <v>2.62</v>
       </c>
       <c r="P2" t="n">
-        <v>9.859999999999999</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="Q2" t="n">
-        <v>9.57</v>
+        <v>9</v>
       </c>
       <c r="R2" t="n">
-        <v>7.14</v>
+        <v>6.75</v>
       </c>
       <c r="S2" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="T2" t="n">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -1445,28 +1445,28 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>43.86</v>
+        <v>43.62</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="Z2" t="n">
-        <v>15.71</v>
+        <v>15.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>10.71</v>
+        <v>10.75</v>
       </c>
       <c r="AB2" t="n">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="AC2" t="n">
-        <v>24.86</v>
+        <v>24.75</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AF2" t="n">
         <v>0.38</v>
@@ -1550,70 +1550,70 @@
         <v>2.75</v>
       </c>
       <c r="BG2" t="n">
-        <v>3.13</v>
+        <v>3.06</v>
       </c>
       <c r="BH2" t="n">
-        <v>10.33</v>
+        <v>10.56</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.13</v>
+        <v>3.06</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BL2" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="BN2" t="n">
-        <v>2.13</v>
+        <v>2.06</v>
       </c>
       <c r="BO2" t="n">
         <v>1</v>
       </c>
       <c r="BP2" t="n">
-        <v>5.13</v>
+        <v>5.19</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.13</v>
+        <v>5.31</v>
       </c>
       <c r="BR2" t="n">
-        <v>80</v>
+        <v>81.25</v>
       </c>
       <c r="BS2" t="n">
-        <v>66.67</v>
+        <v>68.75</v>
       </c>
       <c r="BT2" t="n">
-        <v>60</v>
+        <v>56.25</v>
       </c>
       <c r="BU2" t="n">
-        <v>40</v>
+        <v>37.5</v>
       </c>
       <c r="BV2" t="n">
-        <v>33.33</v>
+        <v>31.25</v>
       </c>
       <c r="BW2" t="n">
-        <v>13.33</v>
+        <v>12.5</v>
       </c>
       <c r="BX2" t="n">
-        <v>60</v>
+        <v>56.25</v>
       </c>
       <c r="BY2" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="BZ2" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.34</v>
+        <v>3.33</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.57</v>
+        <v>3.55</v>
       </c>
       <c r="CC2" t="n">
         <v>3.86</v>
@@ -1628,13 +1628,13 @@
         <v>2.7</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="CH2" t="n">
         <v>1.42</v>
       </c>
       <c r="CI2" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="CJ2" t="n">
         <v>1.74</v>
@@ -1643,10 +1643,10 @@
         <v>1.5</v>
       </c>
       <c r="CL2" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="CN2" t="n">
         <v>1.89</v>
@@ -1658,31 +1658,31 @@
         <v>1.91</v>
       </c>
       <c r="CQ2" t="n">
-        <v>3.24</v>
+        <v>3.23</v>
       </c>
       <c r="CR2" t="n">
         <v>1.41</v>
       </c>
       <c r="CS2" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="CT2" t="n">
-        <v>3.06</v>
+        <v>3.05</v>
       </c>
       <c r="CU2" t="n">
         <v>1.46</v>
       </c>
       <c r="CV2" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="CW2" t="n">
         <v>1.77</v>
       </c>
       <c r="CX2" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="CY2" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="CZ2" t="n">
         <v>2.44</v>
@@ -1700,46 +1700,46 @@
         <v>3.31</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.06</v>
+        <v>2.25</v>
       </c>
       <c r="DH2" t="n">
-        <v>87.47</v>
+        <v>88</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.73</v>
+        <v>2.62</v>
       </c>
       <c r="DK2" t="n">
-        <v>4.53</v>
+        <v>4.81</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="DM2" t="n">
-        <v>44.27</v>
+        <v>43</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.87</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.47</v>
+        <v>2.56</v>
       </c>
       <c r="DP2" t="n">
-        <v>11.47</v>
+        <v>11.38</v>
       </c>
       <c r="DQ2" t="n">
-        <v>11.53</v>
+        <v>11.12</v>
       </c>
       <c r="DR2" t="n">
-        <v>8.130000000000001</v>
+        <v>7.88</v>
       </c>
       <c r="DS2" t="n">
         <v>0.06</v>
@@ -1751,28 +1751,28 @@
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>43.07</v>
+        <v>43</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DX2" t="n">
-        <v>13.53</v>
+        <v>13.56</v>
       </c>
       <c r="DY2" t="n">
-        <v>8.529999999999999</v>
+        <v>8.68</v>
       </c>
       <c r="DZ2" t="n">
-        <v>5</v>
+        <v>4.88</v>
       </c>
       <c r="EA2" t="n">
-        <v>24.13</v>
+        <v>24.12</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="3">
@@ -1782,94 +1782,94 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D3" t="n">
         <v>8</v>
       </c>
       <c r="E3" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="F3" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="G3" t="n">
-        <v>3.57</v>
+        <v>4.38</v>
       </c>
       <c r="H3" t="n">
-        <v>95.86</v>
+        <v>101.25</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>2.71</v>
+        <v>2.5</v>
       </c>
       <c r="K3" t="n">
-        <v>8.140000000000001</v>
+        <v>8.75</v>
       </c>
       <c r="L3" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="M3" t="n">
-        <v>51.29</v>
+        <v>58.62</v>
       </c>
       <c r="N3" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="O3" t="n">
-        <v>4.43</v>
+        <v>4.25</v>
       </c>
       <c r="P3" t="n">
-        <v>13.71</v>
+        <v>13.38</v>
       </c>
       <c r="Q3" t="n">
-        <v>10.29</v>
+        <v>9.75</v>
       </c>
       <c r="R3" t="n">
-        <v>7.57</v>
+        <v>7.5</v>
       </c>
       <c r="S3" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="T3" t="n">
-        <v>2.71</v>
+        <v>2.38</v>
       </c>
       <c r="U3" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="V3" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>54.86</v>
+        <v>56.62</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="Z3" t="n">
-        <v>19.14</v>
+        <v>19.75</v>
       </c>
       <c r="AA3" t="n">
-        <v>11</v>
+        <v>11.88</v>
       </c>
       <c r="AB3" t="n">
-        <v>8.140000000000001</v>
+        <v>7.88</v>
       </c>
       <c r="AC3" t="n">
-        <v>16.71</v>
+        <v>17.25</v>
       </c>
       <c r="AD3" t="n">
-        <v>2.14</v>
+        <v>2.22</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.43</v>
+        <v>2.25</v>
       </c>
       <c r="AF3" t="n">
         <v>0</v>
@@ -1953,58 +1953,58 @@
         <v>3.5</v>
       </c>
       <c r="BG3" t="n">
-        <v>3.47</v>
+        <v>3.25</v>
       </c>
       <c r="BH3" t="n">
-        <v>9.4</v>
+        <v>9.69</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.47</v>
+        <v>3.25</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BL3" t="n">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="BM3" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BN3" t="n">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="BP3" t="n">
         <v>4</v>
       </c>
       <c r="BQ3" t="n">
-        <v>4.93</v>
+        <v>5.25</v>
       </c>
       <c r="BR3" t="n">
-        <v>100</v>
+        <v>93.75</v>
       </c>
       <c r="BS3" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="BT3" t="n">
-        <v>66.67</v>
+        <v>62.5</v>
       </c>
       <c r="BU3" t="n">
-        <v>46.67</v>
+        <v>43.75</v>
       </c>
       <c r="BV3" t="n">
-        <v>26.67</v>
+        <v>25</v>
       </c>
       <c r="BW3" t="n">
-        <v>13.33</v>
+        <v>12.5</v>
       </c>
       <c r="BX3" t="n">
-        <v>66.67</v>
+        <v>62.5</v>
       </c>
       <c r="BY3" t="n">
         <v>1.69</v>
@@ -2013,7 +2013,7 @@
         <v>1.76</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.45</v>
+        <v>3.46</v>
       </c>
       <c r="CB3" t="n">
         <v>3.65</v>
@@ -2025,28 +2025,28 @@
         <v>2.92</v>
       </c>
       <c r="CE3" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.64</v>
+        <v>2.69</v>
       </c>
       <c r="CG3" t="n">
-        <v>2.97</v>
+        <v>2.96</v>
       </c>
       <c r="CH3" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CI3" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="CJ3" t="n">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="CK3" t="n">
         <v>1.49</v>
       </c>
       <c r="CL3" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="CM3" t="n">
         <v>2.38</v>
@@ -2058,31 +2058,31 @@
         <v>1.25</v>
       </c>
       <c r="CP3" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.01</v>
+        <v>3.09</v>
       </c>
       <c r="CR3" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CS3" t="n">
-        <v>2.82</v>
+        <v>2.87</v>
       </c>
       <c r="CT3" t="n">
-        <v>3.15</v>
+        <v>3.11</v>
       </c>
       <c r="CU3" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CV3" t="n">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="CW3" t="n">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="CX3" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CY3" t="n">
         <v>1.91</v>
@@ -2094,88 +2094,88 @@
         <v>1.9</v>
       </c>
       <c r="DB3" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="DC3" t="n">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="DD3" t="n">
-        <v>3.17</v>
+        <v>3.24</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="DG3" t="n">
-        <v>2.47</v>
+        <v>2.94</v>
       </c>
       <c r="DH3" t="n">
-        <v>91.73</v>
+        <v>94.68000000000001</v>
       </c>
       <c r="DI3" t="n">
         <v>0</v>
       </c>
       <c r="DJ3" t="n">
-        <v>3.2</v>
+        <v>3.06</v>
       </c>
       <c r="DK3" t="n">
-        <v>5.33</v>
+        <v>5.82</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="DM3" t="n">
-        <v>43.6</v>
+        <v>47.75</v>
       </c>
       <c r="DN3" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="DO3" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="DP3" t="n">
-        <v>14.2</v>
+        <v>14</v>
       </c>
       <c r="DQ3" t="n">
-        <v>12.47</v>
+        <v>12.07</v>
       </c>
       <c r="DR3" t="n">
-        <v>7.74</v>
+        <v>7.69</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>53.47</v>
+        <v>54.44</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DX3" t="n">
-        <v>15.66</v>
+        <v>16.18</v>
       </c>
       <c r="DY3" t="n">
-        <v>9.869999999999999</v>
+        <v>10.38</v>
       </c>
       <c r="DZ3" t="n">
-        <v>5.8</v>
+        <v>5.82</v>
       </c>
       <c r="EA3" t="n">
-        <v>18.8</v>
+        <v>18.94</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="EC3" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
     </row>
     <row r="4">
@@ -2419,13 +2419,13 @@
         <v>3</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.09</v>
+        <v>3.08</v>
       </c>
       <c r="CC4" t="n">
         <v>3.56</v>
       </c>
       <c r="CD4" t="n">
-        <v>3.9</v>
+        <v>3.89</v>
       </c>
       <c r="CE4" t="n">
         <v>1.55</v>
@@ -2473,13 +2473,13 @@
         <v>3.4</v>
       </c>
       <c r="CT4" t="n">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="CU4" t="n">
         <v>1.33</v>
       </c>
       <c r="CV4" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="CW4" t="n">
         <v>2.24</v>
@@ -2500,10 +2500,10 @@
         <v>1.55</v>
       </c>
       <c r="DC4" t="n">
-        <v>2.71</v>
+        <v>2.72</v>
       </c>
       <c r="DD4" t="n">
-        <v>5.43</v>
+        <v>5.46</v>
       </c>
       <c r="DE4" t="n">
         <v>0.12</v>
@@ -2588,94 +2588,94 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D5" t="n">
         <v>8</v>
       </c>
       <c r="E5" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="F5" t="n">
-        <v>2.71</v>
+        <v>2.62</v>
       </c>
       <c r="G5" t="n">
-        <v>4</v>
+        <v>3.62</v>
       </c>
       <c r="H5" t="n">
-        <v>108.14</v>
+        <v>109.38</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>3.86</v>
+        <v>3.75</v>
       </c>
       <c r="K5" t="n">
-        <v>8.289999999999999</v>
+        <v>7.62</v>
       </c>
       <c r="L5" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="M5" t="n">
-        <v>68.43000000000001</v>
+        <v>65</v>
       </c>
       <c r="N5" t="n">
         <v>1</v>
       </c>
       <c r="O5" t="n">
-        <v>4.29</v>
+        <v>4</v>
       </c>
       <c r="P5" t="n">
-        <v>13</v>
+        <v>13.12</v>
       </c>
       <c r="Q5" t="n">
-        <v>15.29</v>
+        <v>14.5</v>
       </c>
       <c r="R5" t="n">
-        <v>5.14</v>
+        <v>4.88</v>
       </c>
       <c r="S5" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="T5" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="U5" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="V5" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>60.57</v>
+        <v>58.62</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="Z5" t="n">
-        <v>16.57</v>
+        <v>16.75</v>
       </c>
       <c r="AA5" t="n">
-        <v>10.86</v>
+        <v>11.12</v>
       </c>
       <c r="AB5" t="n">
-        <v>5.71</v>
+        <v>5.62</v>
       </c>
       <c r="AC5" t="n">
-        <v>18</v>
+        <v>18.25</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="AE5" t="n">
-        <v>3.29</v>
+        <v>3.25</v>
       </c>
       <c r="AF5" t="n">
         <v>0.12</v>
@@ -2759,70 +2759,70 @@
         <v>2.25</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.87</v>
+        <v>2.75</v>
       </c>
       <c r="BH5" t="n">
-        <v>10.33</v>
+        <v>10.06</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.87</v>
+        <v>2.75</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BL5" t="n">
         <v>1</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="BP5" t="n">
-        <v>5.33</v>
+        <v>5.25</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5</v>
+        <v>4.81</v>
       </c>
       <c r="BR5" t="n">
-        <v>86.67</v>
+        <v>87.5</v>
       </c>
       <c r="BS5" t="n">
-        <v>60</v>
+        <v>56.25</v>
       </c>
       <c r="BT5" t="n">
-        <v>53.33</v>
+        <v>50</v>
       </c>
       <c r="BU5" t="n">
-        <v>40</v>
+        <v>37.5</v>
       </c>
       <c r="BV5" t="n">
-        <v>13.33</v>
+        <v>12.5</v>
       </c>
       <c r="BW5" t="n">
-        <v>13.33</v>
+        <v>12.5</v>
       </c>
       <c r="BX5" t="n">
-        <v>60</v>
+        <v>56.25</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.68</v>
+        <v>1.74</v>
       </c>
       <c r="BZ5" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.59</v>
+        <v>3.58</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.86</v>
+        <v>3.83</v>
       </c>
       <c r="CC5" t="n">
         <v>2.83</v>
@@ -2834,40 +2834,40 @@
         <v>1.33</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.57</v>
+        <v>2.59</v>
       </c>
       <c r="CG5" t="n">
-        <v>3.11</v>
+        <v>3.09</v>
       </c>
       <c r="CH5" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CI5" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="CL5" t="n">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CO5" t="n">
         <v>1.21</v>
       </c>
       <c r="CP5" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="CQ5" t="n">
-        <v>2.82</v>
+        <v>2.85</v>
       </c>
       <c r="CR5" t="n">
         <v>1.38</v>
@@ -2882,106 +2882,106 @@
         <v>1.49</v>
       </c>
       <c r="CV5" t="n">
-        <v>2.26</v>
+        <v>2.23</v>
       </c>
       <c r="CW5" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="CX5" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="CY5" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CZ5" t="n">
-        <v>2.39</v>
+        <v>2.37</v>
       </c>
       <c r="DA5" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="DB5" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="DC5" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="DD5" t="n">
-        <v>2.92</v>
+        <v>2.99</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DF5" t="n">
         <v>2</v>
       </c>
       <c r="DG5" t="n">
-        <v>3.07</v>
+        <v>2.94</v>
       </c>
       <c r="DH5" t="n">
-        <v>100</v>
+        <v>101.13</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DJ5" t="n">
-        <v>3.13</v>
+        <v>3.12</v>
       </c>
       <c r="DK5" t="n">
-        <v>6.67</v>
+        <v>6.44</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.74</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="DM5" t="n">
-        <v>60.14</v>
+        <v>58.94</v>
       </c>
       <c r="DN5" t="n">
         <v>1</v>
       </c>
       <c r="DO5" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="DP5" t="n">
-        <v>12.94</v>
+        <v>13</v>
       </c>
       <c r="DQ5" t="n">
-        <v>14.87</v>
+        <v>14.5</v>
       </c>
       <c r="DR5" t="n">
-        <v>5.73</v>
+        <v>5.56</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>55.4</v>
+        <v>54.75</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DX5" t="n">
-        <v>14.27</v>
+        <v>14.5</v>
       </c>
       <c r="DY5" t="n">
-        <v>9.199999999999999</v>
+        <v>9.43</v>
       </c>
       <c r="DZ5" t="n">
         <v>5.06</v>
       </c>
       <c r="EA5" t="n">
-        <v>18.86</v>
+        <v>18.94</v>
       </c>
       <c r="EB5" t="n">
         <v>1.69</v>
       </c>
       <c r="EC5" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="6">
@@ -3219,13 +3219,13 @@
         <v>2.4</v>
       </c>
       <c r="BZ6" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="CA6" t="n">
         <v>3.26</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.37</v>
+        <v>3.36</v>
       </c>
       <c r="CC6" t="n">
         <v>4.26</v>
@@ -3273,13 +3273,13 @@
         <v>3.91</v>
       </c>
       <c r="CR6" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="CS6" t="n">
         <v>3.1</v>
       </c>
       <c r="CT6" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="CU6" t="n">
         <v>1.4</v>
@@ -3306,10 +3306,10 @@
         <v>1.38</v>
       </c>
       <c r="DC6" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="DD6" t="n">
-        <v>4.02</v>
+        <v>4.05</v>
       </c>
       <c r="DE6" t="n">
         <v>0.18</v>
@@ -3628,7 +3628,7 @@
         <v>3.4</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.53</v>
+        <v>3.54</v>
       </c>
       <c r="CC7" t="n">
         <v>4.98</v>
@@ -3679,10 +3679,10 @@
         <v>1.45</v>
       </c>
       <c r="CS7" t="n">
-        <v>3.1</v>
+        <v>3.11</v>
       </c>
       <c r="CT7" t="n">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="CU7" t="n">
         <v>1.4</v>
@@ -3691,10 +3691,10 @@
         <v>1.97</v>
       </c>
       <c r="CW7" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CX7" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CY7" t="n">
         <v>2.02</v>
@@ -3709,10 +3709,10 @@
         <v>1.35</v>
       </c>
       <c r="DC7" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="DD7" t="n">
-        <v>3.77</v>
+        <v>3.75</v>
       </c>
       <c r="DE7" t="n">
         <v>0.12</v>
@@ -3797,13 +3797,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C8" t="n">
         <v>8</v>
       </c>
       <c r="D8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -3887,52 +3887,52 @@
         <v>2.88</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="AI8" t="n">
-        <v>81.43000000000001</v>
+        <v>82.38</v>
       </c>
       <c r="AJ8" t="n">
         <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.14</v>
+        <v>2.38</v>
       </c>
       <c r="AL8" t="n">
-        <v>4.14</v>
+        <v>4.12</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AN8" t="n">
-        <v>28.71</v>
+        <v>27.88</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="AP8" t="n">
         <v>2</v>
       </c>
       <c r="AQ8" t="n">
-        <v>14.43</v>
+        <v>15.38</v>
       </c>
       <c r="AR8" t="n">
-        <v>13.29</v>
+        <v>13.5</v>
       </c>
       <c r="AS8" t="n">
-        <v>10.57</v>
+        <v>10.88</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.71</v>
+        <v>0.88</v>
       </c>
       <c r="AV8" t="n">
         <v>0</v>
@@ -3944,82 +3944,82 @@
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>43.14</v>
+        <v>41.62</v>
       </c>
       <c r="AZ8" t="n">
         <v>0</v>
       </c>
       <c r="BA8" t="n">
-        <v>8.140000000000001</v>
+        <v>8</v>
       </c>
       <c r="BB8" t="n">
-        <v>5.86</v>
+        <v>5.5</v>
       </c>
       <c r="BC8" t="n">
-        <v>2.29</v>
+        <v>2.5</v>
       </c>
       <c r="BD8" t="n">
-        <v>20.29</v>
+        <v>20.25</v>
       </c>
       <c r="BE8" t="n">
         <v>0.89</v>
       </c>
       <c r="BF8" t="n">
-        <v>2.14</v>
+        <v>2.38</v>
       </c>
       <c r="BG8" t="n">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="BH8" t="n">
-        <v>10</v>
+        <v>9.94</v>
       </c>
       <c r="BI8" t="n">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.33</v>
+        <v>0.44</v>
       </c>
       <c r="BN8" t="n">
-        <v>0.87</v>
+        <v>1</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.87</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.53</v>
+        <v>4.56</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.47</v>
+        <v>5.38</v>
       </c>
       <c r="BR8" t="n">
-        <v>73.33</v>
+        <v>75</v>
       </c>
       <c r="BS8" t="n">
-        <v>40</v>
+        <v>43.75</v>
       </c>
       <c r="BT8" t="n">
-        <v>33.33</v>
+        <v>37.5</v>
       </c>
       <c r="BU8" t="n">
-        <v>13.33</v>
+        <v>12.5</v>
       </c>
       <c r="BV8" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BW8" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BX8" t="n">
-        <v>33.33</v>
+        <v>37.5</v>
       </c>
       <c r="BY8" t="n">
         <v>2.1</v>
@@ -4028,22 +4028,22 @@
         <v>2.27</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.09</v>
+        <v>3.1</v>
       </c>
       <c r="CB8" t="n">
         <v>3.27</v>
       </c>
       <c r="CC8" t="n">
-        <v>3.68</v>
+        <v>3.76</v>
       </c>
       <c r="CD8" t="n">
-        <v>4.06</v>
+        <v>4.15</v>
       </c>
       <c r="CE8" t="n">
         <v>1.48</v>
       </c>
       <c r="CF8" t="n">
-        <v>3.24</v>
+        <v>3.22</v>
       </c>
       <c r="CG8" t="n">
         <v>2.5</v>
@@ -4052,31 +4052,31 @@
         <v>1.31</v>
       </c>
       <c r="CI8" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="CJ8" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CL8" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
       <c r="CN8" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="CO8" t="n">
         <v>1.4</v>
       </c>
       <c r="CP8" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="CQ8" t="n">
-        <v>4.27</v>
+        <v>4.24</v>
       </c>
       <c r="CR8" t="n">
         <v>1.52</v>
@@ -4085,79 +4085,79 @@
         <v>3.22</v>
       </c>
       <c r="CT8" t="n">
-        <v>2.65</v>
+        <v>2.66</v>
       </c>
       <c r="CU8" t="n">
         <v>1.36</v>
       </c>
       <c r="CV8" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CW8" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="CX8" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CY8" t="n">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="CZ8" t="n">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="DA8" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="DB8" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="DC8" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="DD8" t="n">
-        <v>4.55</v>
+        <v>4.48</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DF8" t="n">
-        <v>2.07</v>
+        <v>2.12</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.73</v>
+        <v>2.68</v>
       </c>
       <c r="DH8" t="n">
-        <v>90.93000000000001</v>
+        <v>90.81999999999999</v>
       </c>
       <c r="DI8" t="n">
         <v>0</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.53</v>
+        <v>2.63</v>
       </c>
       <c r="DK8" t="n">
-        <v>5.07</v>
+        <v>5</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DM8" t="n">
-        <v>41.46</v>
+        <v>40.25</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="DP8" t="n">
-        <v>13.87</v>
+        <v>14.38</v>
       </c>
       <c r="DQ8" t="n">
-        <v>13.47</v>
+        <v>13.56</v>
       </c>
       <c r="DR8" t="n">
-        <v>8.800000000000001</v>
+        <v>9.07</v>
       </c>
       <c r="DS8" t="n">
         <v>0</v>
@@ -4169,28 +4169,28 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>48.6</v>
+        <v>47.5</v>
       </c>
       <c r="DW8" t="n">
         <v>0</v>
       </c>
       <c r="DX8" t="n">
-        <v>9.93</v>
+        <v>9.75</v>
       </c>
       <c r="DY8" t="n">
-        <v>7.13</v>
+        <v>6.88</v>
       </c>
       <c r="DZ8" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="EA8" t="n">
         <v>20</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="EC8" t="n">
-        <v>2.53</v>
+        <v>2.63</v>
       </c>
     </row>
     <row r="9">
@@ -4200,94 +4200,94 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D9" t="n">
         <v>8</v>
       </c>
       <c r="E9" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="F9" t="n">
-        <v>1.86</v>
+        <v>1.62</v>
       </c>
       <c r="G9" t="n">
-        <v>2.86</v>
+        <v>2.75</v>
       </c>
       <c r="H9" t="n">
-        <v>103.29</v>
+        <v>102.62</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>3.14</v>
+        <v>3</v>
       </c>
       <c r="K9" t="n">
-        <v>5.14</v>
+        <v>5.12</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="M9" t="n">
-        <v>55.14</v>
+        <v>54.5</v>
       </c>
       <c r="N9" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="O9" t="n">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="P9" t="n">
-        <v>15.71</v>
+        <v>15.62</v>
       </c>
       <c r="Q9" t="n">
-        <v>13.71</v>
+        <v>14.75</v>
       </c>
       <c r="R9" t="n">
-        <v>5.14</v>
+        <v>5.38</v>
       </c>
       <c r="S9" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="T9" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="U9" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="V9" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>56.14</v>
+        <v>57.75</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="Z9" t="n">
-        <v>16.29</v>
+        <v>16.75</v>
       </c>
       <c r="AA9" t="n">
-        <v>11.29</v>
+        <v>11.62</v>
       </c>
       <c r="AB9" t="n">
-        <v>5</v>
+        <v>5.12</v>
       </c>
       <c r="AC9" t="n">
-        <v>21.29</v>
+        <v>21.38</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.86</v>
+        <v>2.75</v>
       </c>
       <c r="AF9" t="n">
         <v>0.25</v>
@@ -4371,49 +4371,49 @@
         <v>3.25</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="BH9" t="n">
-        <v>9.33</v>
+        <v>9.31</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.87</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="BO9" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.33</v>
+        <v>4.38</v>
       </c>
       <c r="BQ9" t="n">
-        <v>5</v>
+        <v>4.94</v>
       </c>
       <c r="BR9" t="n">
-        <v>93.33</v>
+        <v>93.75</v>
       </c>
       <c r="BS9" t="n">
-        <v>80</v>
+        <v>81.25</v>
       </c>
       <c r="BT9" t="n">
-        <v>53.33</v>
+        <v>56.25</v>
       </c>
       <c r="BU9" t="n">
-        <v>40</v>
+        <v>37.5</v>
       </c>
       <c r="BV9" t="n">
         <v>0</v>
@@ -4422,19 +4422,19 @@
         <v>0</v>
       </c>
       <c r="BX9" t="n">
-        <v>73.33</v>
+        <v>75</v>
       </c>
       <c r="BY9" t="n">
-        <v>2.14</v>
+        <v>2.11</v>
       </c>
       <c r="BZ9" t="n">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="CA9" t="n">
         <v>3.28</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.44</v>
+        <v>3.43</v>
       </c>
       <c r="CC9" t="n">
         <v>3.08</v>
@@ -4446,22 +4446,22 @@
         <v>1.38</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.72</v>
+        <v>2.73</v>
       </c>
       <c r="CG9" t="n">
-        <v>2.95</v>
+        <v>2.92</v>
       </c>
       <c r="CH9" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CI9" t="n">
         <v>2.08</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CK9" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CL9" t="n">
         <v>1.91</v>
@@ -4470,130 +4470,130 @@
         <v>2.4</v>
       </c>
       <c r="CN9" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CO9" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="CP9" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="CQ9" t="n">
-        <v>3.12</v>
+        <v>3.16</v>
       </c>
       <c r="CR9" t="n">
         <v>1.41</v>
       </c>
       <c r="CS9" t="n">
-        <v>2.97</v>
+        <v>2.98</v>
       </c>
       <c r="CT9" t="n">
-        <v>3.01</v>
+        <v>3</v>
       </c>
       <c r="CU9" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="CV9" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="CW9" t="n">
         <v>1.74</v>
       </c>
       <c r="CX9" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CY9" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CZ9" t="n">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="DA9" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="DB9" t="n">
         <v>1.29</v>
       </c>
       <c r="DC9" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="DD9" t="n">
-        <v>3.34</v>
+        <v>3.36</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="DG9" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="DH9" t="n">
-        <v>97</v>
+        <v>97.06</v>
       </c>
       <c r="DI9" t="n">
         <v>-0.06</v>
       </c>
       <c r="DJ9" t="n">
-        <v>3.33</v>
+        <v>3.25</v>
       </c>
       <c r="DK9" t="n">
-        <v>4.67</v>
+        <v>4.69</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.06</v>
+        <v>0.18</v>
       </c>
       <c r="DM9" t="n">
-        <v>47.07</v>
+        <v>47.25</v>
       </c>
       <c r="DN9" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="DO9" t="n">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="DP9" t="n">
-        <v>16.33</v>
+        <v>16.25</v>
       </c>
       <c r="DQ9" t="n">
-        <v>14.2</v>
+        <v>14.68</v>
       </c>
       <c r="DR9" t="n">
-        <v>6.2</v>
+        <v>6.25</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>54.07</v>
+        <v>55</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DX9" t="n">
-        <v>14.4</v>
+        <v>14.75</v>
       </c>
       <c r="DY9" t="n">
-        <v>9.6</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="DZ9" t="n">
-        <v>4.8</v>
+        <v>4.87</v>
       </c>
       <c r="EA9" t="n">
-        <v>22.14</v>
+        <v>22.13</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="EC9" t="n">
-        <v>3.07</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -4603,13 +4603,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C10" t="n">
         <v>7</v>
       </c>
       <c r="D10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E10" t="n">
         <v>0.14</v>
@@ -4696,136 +4696,136 @@
         <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.62</v>
+        <v>1.78</v>
       </c>
       <c r="AI10" t="n">
-        <v>78.5</v>
+        <v>78.11</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.88</v>
+        <v>2.67</v>
       </c>
       <c r="AL10" t="n">
         <v>5</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.38</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AN10" t="n">
-        <v>32.62</v>
+        <v>33.56</v>
       </c>
       <c r="AO10" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>11.22</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>12</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>8.44</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>48.89</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>12.44</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>7.33</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>5.11</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>14.22</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>8.619999999999999</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BL10" t="n">
         <v>0.75</v>
       </c>
-      <c r="AP10" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>12</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>12.25</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>8.25</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>47.75</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>13</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>7.62</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>5.38</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>14.12</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="BH10" t="n">
-        <v>8.27</v>
-      </c>
-      <c r="BI10" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="BJ10" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="BK10" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>0.8</v>
-      </c>
       <c r="BM10" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="BP10" t="n">
-        <v>3.93</v>
+        <v>4.06</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.33</v>
+        <v>4.56</v>
       </c>
       <c r="BR10" t="n">
-        <v>93.33</v>
+        <v>93.75</v>
       </c>
       <c r="BS10" t="n">
-        <v>86.67</v>
+        <v>87.5</v>
       </c>
       <c r="BT10" t="n">
-        <v>60</v>
+        <v>56.25</v>
       </c>
       <c r="BU10" t="n">
-        <v>33.33</v>
+        <v>31.25</v>
       </c>
       <c r="BV10" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BW10" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BX10" t="n">
-        <v>60</v>
+        <v>56.25</v>
       </c>
       <c r="BY10" t="n">
         <v>1.89</v>
@@ -4837,166 +4837,166 @@
         <v>3.22</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.38</v>
+        <v>3.37</v>
       </c>
       <c r="CC10" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="CD10" t="n">
         <v>2.85</v>
       </c>
       <c r="CE10" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.95</v>
+        <v>2.93</v>
       </c>
       <c r="CG10" t="n">
-        <v>2.81</v>
+        <v>2.83</v>
       </c>
       <c r="CH10" t="n">
         <v>1.37</v>
       </c>
       <c r="CI10" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CJ10" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CK10" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CL10" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="CM10" t="n">
         <v>2.14</v>
       </c>
       <c r="CN10" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CO10" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="CP10" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="CQ10" t="n">
-        <v>3.56</v>
+        <v>3.54</v>
       </c>
       <c r="CR10" t="n">
         <v>1.46</v>
       </c>
       <c r="CS10" t="n">
-        <v>3.15</v>
+        <v>3.14</v>
       </c>
       <c r="CT10" t="n">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="CU10" t="n">
         <v>1.39</v>
       </c>
       <c r="CV10" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="CW10" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CX10" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CY10" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="CZ10" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="DA10" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="DB10" t="n">
         <v>1.35</v>
       </c>
       <c r="DC10" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="DD10" t="n">
-        <v>3.76</v>
+        <v>3.73</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="DG10" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="DH10" t="n">
-        <v>87.67</v>
+        <v>86.87</v>
       </c>
       <c r="DI10" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.47</v>
+        <v>4.5</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.27</v>
+        <v>0.38</v>
       </c>
       <c r="DM10" t="n">
-        <v>38.07</v>
+        <v>38.25</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.87</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="DP10" t="n">
-        <v>12.4</v>
+        <v>11.94</v>
       </c>
       <c r="DQ10" t="n">
-        <v>12.33</v>
+        <v>12.19</v>
       </c>
       <c r="DR10" t="n">
-        <v>7.47</v>
+        <v>7.62</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>50</v>
+        <v>50.5</v>
       </c>
       <c r="DW10" t="n">
         <v>0</v>
       </c>
       <c r="DX10" t="n">
-        <v>12.93</v>
+        <v>12.62</v>
       </c>
       <c r="DY10" t="n">
-        <v>7.93</v>
+        <v>7.75</v>
       </c>
       <c r="DZ10" t="n">
-        <v>5</v>
+        <v>4.87</v>
       </c>
       <c r="EA10" t="n">
-        <v>16.26</v>
+        <v>16.18</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="EC10" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="11">
@@ -5099,7 +5099,7 @@
         <v>0.11</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="AH11" t="n">
         <v>2.44</v>
@@ -5111,7 +5111,7 @@
         <v>0.22</v>
       </c>
       <c r="AK11" t="n">
-        <v>3.22</v>
+        <v>3.11</v>
       </c>
       <c r="AL11" t="n">
         <v>4</v>
@@ -5174,7 +5174,7 @@
         <v>1.5</v>
       </c>
       <c r="BF11" t="n">
-        <v>3</v>
+        <v>2.89</v>
       </c>
       <c r="BG11" t="n">
         <v>2.62</v>
@@ -5330,7 +5330,7 @@
         <v>0.06</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.69</v>
+        <v>1.63</v>
       </c>
       <c r="DG11" t="n">
         <v>3.06</v>
@@ -5342,7 +5342,7 @@
         <v>0.18</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.75</v>
+        <v>2.69</v>
       </c>
       <c r="DK11" t="n">
         <v>4.69</v>
@@ -5399,7 +5399,7 @@
         <v>1.51</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="12">
@@ -5643,13 +5643,13 @@
         <v>3.2</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.26</v>
+        <v>3.27</v>
       </c>
       <c r="CC12" t="n">
         <v>3.52</v>
       </c>
       <c r="CD12" t="n">
-        <v>3.9</v>
+        <v>3.88</v>
       </c>
       <c r="CE12" t="n">
         <v>1.46</v>
@@ -5697,7 +5697,7 @@
         <v>3.23</v>
       </c>
       <c r="CT12" t="n">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="CU12" t="n">
         <v>1.35</v>
@@ -5709,7 +5709,7 @@
         <v>1.97</v>
       </c>
       <c r="CX12" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CY12" t="n">
         <v>2.11</v>
@@ -5721,13 +5721,13 @@
         <v>1.73</v>
       </c>
       <c r="DB12" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="DC12" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="DD12" t="n">
-        <v>4.3</v>
+        <v>4.29</v>
       </c>
       <c r="DE12" t="n">
         <v>0.12</v>
@@ -5812,13 +5812,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C13" t="n">
         <v>7</v>
       </c>
       <c r="D13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E13" t="n">
         <v>0.43</v>
@@ -5905,136 +5905,136 @@
         <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.75</v>
+        <v>2.11</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AI13" t="n">
-        <v>83</v>
+        <v>81.11</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AK13" t="n">
-        <v>3.12</v>
+        <v>3.67</v>
       </c>
       <c r="AL13" t="n">
-        <v>3.62</v>
+        <v>3.56</v>
       </c>
       <c r="AM13" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>32.78</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>12.56</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>13.78</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>9.109999999999999</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>48.11</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>9.56</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>5.44</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>19</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>9</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="BK13" t="n">
         <v>0.5</v>
       </c>
-      <c r="AN13" t="n">
-        <v>34.88</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>11.88</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>13.75</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>9.119999999999999</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>49.5</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>10.25</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>5.88</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>4.38</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>19.12</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>3</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="BH13" t="n">
-        <v>9.07</v>
-      </c>
-      <c r="BI13" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="BJ13" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="BK13" t="n">
-        <v>0.47</v>
-      </c>
       <c r="BL13" t="n">
-        <v>0.33</v>
+        <v>0.44</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="BO13" t="n">
-        <v>0.87</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BP13" t="n">
-        <v>4</v>
+        <v>4.06</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4.4</v>
+        <v>4.31</v>
       </c>
       <c r="BR13" t="n">
-        <v>80</v>
+        <v>81.25</v>
       </c>
       <c r="BS13" t="n">
-        <v>66.67</v>
+        <v>68.75</v>
       </c>
       <c r="BT13" t="n">
-        <v>40</v>
+        <v>43.75</v>
       </c>
       <c r="BU13" t="n">
-        <v>6.67</v>
+        <v>12.5</v>
       </c>
       <c r="BV13" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="BW13" t="n">
         <v>0</v>
       </c>
       <c r="BX13" t="n">
-        <v>46.67</v>
+        <v>50</v>
       </c>
       <c r="BY13" t="n">
         <v>2.24</v>
@@ -6049,34 +6049,34 @@
         <v>3.09</v>
       </c>
       <c r="CC13" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="CD13" t="n">
-        <v>3.03</v>
+        <v>3.02</v>
       </c>
       <c r="CE13" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="CF13" t="n">
-        <v>3.29</v>
+        <v>3.32</v>
       </c>
       <c r="CG13" t="n">
-        <v>2.51</v>
+        <v>2.49</v>
       </c>
       <c r="CH13" t="n">
         <v>1.3</v>
       </c>
       <c r="CI13" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CJ13" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="CK13" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CL13" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="CM13" t="n">
         <v>2.18</v>
@@ -6085,13 +6085,13 @@
         <v>1.7</v>
       </c>
       <c r="CO13" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CP13" t="n">
-        <v>2.36</v>
+        <v>2.39</v>
       </c>
       <c r="CQ13" t="n">
-        <v>4.32</v>
+        <v>4.38</v>
       </c>
       <c r="CR13" t="n">
         <v>1.55</v>
@@ -6100,7 +6100,7 @@
         <v>3.3</v>
       </c>
       <c r="CT13" t="n">
-        <v>2.56</v>
+        <v>2.55</v>
       </c>
       <c r="CU13" t="n">
         <v>1.34</v>
@@ -6112,7 +6112,7 @@
         <v>2.05</v>
       </c>
       <c r="CX13" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="CY13" t="n">
         <v>2.15</v>
@@ -6133,79 +6133,79 @@
         <v>4.8</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.93</v>
+        <v>2.12</v>
       </c>
       <c r="DG13" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="DH13" t="n">
-        <v>84.8</v>
+        <v>83.63</v>
       </c>
       <c r="DI13" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ13" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="DK13" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DM13" t="n">
-        <v>38</v>
+        <v>36.63</v>
       </c>
       <c r="DN13" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="DO13" t="n">
-        <v>2.34</v>
+        <v>2.25</v>
       </c>
       <c r="DP13" t="n">
-        <v>12.73</v>
+        <v>13.06</v>
       </c>
       <c r="DQ13" t="n">
-        <v>15</v>
+        <v>14.94</v>
       </c>
       <c r="DR13" t="n">
-        <v>8.4</v>
+        <v>8.44</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.06</v>
+        <v>0.12</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.06</v>
+        <v>0.12</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>50.67</v>
+        <v>49.81</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.13</v>
+        <v>0.25</v>
       </c>
       <c r="DX13" t="n">
-        <v>11.67</v>
+        <v>11.19</v>
       </c>
       <c r="DY13" t="n">
-        <v>7</v>
+        <v>6.69</v>
       </c>
       <c r="DZ13" t="n">
-        <v>4.67</v>
+        <v>4.5</v>
       </c>
       <c r="EA13" t="n">
-        <v>20.46</v>
+        <v>20.31</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="EC13" t="n">
-        <v>3.07</v>
+        <v>3.12</v>
       </c>
     </row>
     <row r="14">
@@ -6215,10 +6215,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D14" t="n">
         <v>8</v>
@@ -6227,49 +6227,49 @@
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="G14" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="H14" t="n">
-        <v>95.56999999999999</v>
+        <v>98.75</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>4.14</v>
+        <v>4</v>
       </c>
       <c r="K14" t="n">
-        <v>3.57</v>
+        <v>3.38</v>
       </c>
       <c r="L14" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="M14" t="n">
-        <v>40.71</v>
+        <v>41.62</v>
       </c>
       <c r="N14" t="n">
         <v>2</v>
       </c>
       <c r="O14" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="P14" t="n">
-        <v>17.71</v>
+        <v>17.38</v>
       </c>
       <c r="Q14" t="n">
-        <v>12.14</v>
+        <v>12.5</v>
       </c>
       <c r="R14" t="n">
-        <v>7.43</v>
+        <v>7.25</v>
       </c>
       <c r="S14" t="n">
-        <v>1.86</v>
+        <v>1.62</v>
       </c>
       <c r="T14" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
@@ -6281,28 +6281,28 @@
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>46.57</v>
+        <v>47.75</v>
       </c>
       <c r="Y14" t="n">
         <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>12.43</v>
+        <v>12.88</v>
       </c>
       <c r="AA14" t="n">
-        <v>8.43</v>
+        <v>8.75</v>
       </c>
       <c r="AB14" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>16.38</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AE14" t="n">
         <v>4</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>15.57</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>4.14</v>
       </c>
       <c r="AF14" t="n">
         <v>0.12</v>
@@ -6386,70 +6386,70 @@
         <v>2.25</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.8</v>
+        <v>2.69</v>
       </c>
       <c r="BH14" t="n">
-        <v>8.6</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.8</v>
+        <v>2.69</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="BM14" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="BP14" t="n">
-        <v>3.73</v>
+        <v>3.62</v>
       </c>
       <c r="BQ14" t="n">
-        <v>4.87</v>
+        <v>4.75</v>
       </c>
       <c r="BR14" t="n">
-        <v>93.33</v>
+        <v>93.75</v>
       </c>
       <c r="BS14" t="n">
-        <v>73.33</v>
+        <v>68.75</v>
       </c>
       <c r="BT14" t="n">
-        <v>46.67</v>
+        <v>43.75</v>
       </c>
       <c r="BU14" t="n">
-        <v>33.33</v>
+        <v>31.25</v>
       </c>
       <c r="BV14" t="n">
-        <v>26.67</v>
+        <v>25</v>
       </c>
       <c r="BW14" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BX14" t="n">
-        <v>60</v>
+        <v>56.25</v>
       </c>
       <c r="BY14" t="n">
-        <v>3.07</v>
+        <v>2.94</v>
       </c>
       <c r="BZ14" t="n">
-        <v>3.54</v>
+        <v>3.36</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.17</v>
+        <v>3.16</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.37</v>
+        <v>3.36</v>
       </c>
       <c r="CC14" t="n">
         <v>4.68</v>
@@ -6458,10 +6458,10 @@
         <v>5.09</v>
       </c>
       <c r="CE14" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CF14" t="n">
-        <v>3.25</v>
+        <v>3.23</v>
       </c>
       <c r="CG14" t="n">
         <v>2.54</v>
@@ -6470,16 +6470,16 @@
         <v>1.31</v>
       </c>
       <c r="CI14" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CJ14" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="CK14" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="CL14" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="CM14" t="n">
         <v>2.1</v>
@@ -6494,7 +6494,7 @@
         <v>2.29</v>
       </c>
       <c r="CQ14" t="n">
-        <v>4.34</v>
+        <v>4.32</v>
       </c>
       <c r="CR14" t="n">
         <v>1.53</v>
@@ -6503,22 +6503,22 @@
         <v>3.28</v>
       </c>
       <c r="CT14" t="n">
-        <v>2.63</v>
+        <v>2.64</v>
       </c>
       <c r="CU14" t="n">
         <v>1.36</v>
       </c>
       <c r="CV14" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CW14" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CX14" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CY14" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="CZ14" t="n">
         <v>2.11</v>
@@ -6530,85 +6530,85 @@
         <v>1.44</v>
       </c>
       <c r="DC14" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="DD14" t="n">
-        <v>4.52</v>
+        <v>4.49</v>
       </c>
       <c r="DE14" t="n">
         <v>0.06</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="DG14" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="DH14" t="n">
-        <v>85.40000000000001</v>
+        <v>87.62</v>
       </c>
       <c r="DI14" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ14" t="n">
-        <v>3.4</v>
+        <v>3.38</v>
       </c>
       <c r="DK14" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DM14" t="n">
-        <v>34.73</v>
+        <v>35.56</v>
       </c>
       <c r="DN14" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="DO14" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="DP14" t="n">
-        <v>15.86</v>
+        <v>15.82</v>
       </c>
       <c r="DQ14" t="n">
-        <v>12.73</v>
+        <v>12.88</v>
       </c>
       <c r="DR14" t="n">
-        <v>9.539999999999999</v>
+        <v>9.32</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>40.67</v>
+        <v>41.62</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DX14" t="n">
-        <v>10.66</v>
+        <v>11</v>
       </c>
       <c r="DY14" t="n">
-        <v>7.07</v>
+        <v>7.32</v>
       </c>
       <c r="DZ14" t="n">
-        <v>3.6</v>
+        <v>3.68</v>
       </c>
       <c r="EA14" t="n">
-        <v>16.54</v>
+        <v>16.88</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="EC14" t="n">
-        <v>3.13</v>
+        <v>3.12</v>
       </c>
     </row>
     <row r="15">
@@ -6618,13 +6618,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C15" t="n">
         <v>8</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E15" t="n">
         <v>0.12</v>
@@ -6708,139 +6708,139 @@
         <v>1.75</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.71</v>
+        <v>2.5</v>
       </c>
       <c r="AI15" t="n">
-        <v>85.86</v>
+        <v>88.25</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.71</v>
+        <v>2.62</v>
       </c>
       <c r="AL15" t="n">
-        <v>4.29</v>
+        <v>4</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AN15" t="n">
-        <v>41.86</v>
+        <v>46.5</v>
       </c>
       <c r="AO15" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AQ15" t="n">
-        <v>13.57</v>
+        <v>13.38</v>
       </c>
       <c r="AR15" t="n">
-        <v>12</v>
+        <v>12.88</v>
       </c>
       <c r="AS15" t="n">
-        <v>8.140000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AX15" t="n">
         <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>50.14</v>
+        <v>50.5</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="BA15" t="n">
-        <v>10.14</v>
+        <v>9.5</v>
       </c>
       <c r="BB15" t="n">
-        <v>7.29</v>
+        <v>6.62</v>
       </c>
       <c r="BC15" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="BD15" t="n">
-        <v>23.71</v>
+        <v>23.88</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="BF15" t="n">
         <v>2</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="BH15" t="n">
-        <v>8.130000000000001</v>
+        <v>8.19</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="BL15" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="BO15" t="n">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BP15" t="n">
-        <v>3.47</v>
+        <v>3.44</v>
       </c>
       <c r="BQ15" t="n">
-        <v>4.67</v>
+        <v>4.75</v>
       </c>
       <c r="BR15" t="n">
         <v>100</v>
       </c>
       <c r="BS15" t="n">
-        <v>66.67</v>
+        <v>68.75</v>
       </c>
       <c r="BT15" t="n">
-        <v>53.33</v>
+        <v>50</v>
       </c>
       <c r="BU15" t="n">
-        <v>26.67</v>
+        <v>25</v>
       </c>
       <c r="BV15" t="n">
-        <v>13.33</v>
+        <v>12.5</v>
       </c>
       <c r="BW15" t="n">
         <v>0</v>
       </c>
       <c r="BX15" t="n">
-        <v>46.67</v>
+        <v>50</v>
       </c>
       <c r="BY15" t="n">
         <v>2.21</v>
@@ -6849,25 +6849,25 @@
         <v>2.23</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.2</v>
+        <v>3.23</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.35</v>
+        <v>3.37</v>
       </c>
       <c r="CC15" t="n">
-        <v>3.89</v>
+        <v>4.08</v>
       </c>
       <c r="CD15" t="n">
-        <v>4.35</v>
+        <v>4.47</v>
       </c>
       <c r="CE15" t="n">
         <v>1.47</v>
       </c>
       <c r="CF15" t="n">
-        <v>3.16</v>
+        <v>3.14</v>
       </c>
       <c r="CG15" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="CH15" t="n">
         <v>1.33</v>
@@ -6882,22 +6882,22 @@
         <v>1.61</v>
       </c>
       <c r="CL15" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="CM15" t="n">
         <v>2.19</v>
       </c>
       <c r="CN15" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CO15" t="n">
         <v>1.38</v>
       </c>
       <c r="CP15" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="CQ15" t="n">
-        <v>4</v>
+        <v>3.97</v>
       </c>
       <c r="CR15" t="n">
         <v>1.49</v>
@@ -6906,7 +6906,7 @@
         <v>3.2</v>
       </c>
       <c r="CT15" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="CU15" t="n">
         <v>1.37</v>
@@ -6933,85 +6933,85 @@
         <v>1.41</v>
       </c>
       <c r="DC15" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="DD15" t="n">
-        <v>4.34</v>
+        <v>4.31</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="DG15" t="n">
-        <v>2.4</v>
+        <v>2.31</v>
       </c>
       <c r="DH15" t="n">
-        <v>88.73</v>
+        <v>89.75</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DJ15" t="n">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="DK15" t="n">
-        <v>3.87</v>
+        <v>3.75</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DM15" t="n">
-        <v>45.87</v>
+        <v>47.94</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="DO15" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="DP15" t="n">
-        <v>13.74</v>
+        <v>13.63</v>
       </c>
       <c r="DQ15" t="n">
-        <v>12.86</v>
+        <v>13.25</v>
       </c>
       <c r="DR15" t="n">
-        <v>7.53</v>
+        <v>7.75</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DU15" t="n">
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>52.67</v>
+        <v>52.69</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DX15" t="n">
-        <v>12.53</v>
+        <v>12.06</v>
       </c>
       <c r="DY15" t="n">
-        <v>8.07</v>
+        <v>7.68</v>
       </c>
       <c r="DZ15" t="n">
-        <v>4.47</v>
+        <v>4.38</v>
       </c>
       <c r="EA15" t="n">
-        <v>22.8</v>
+        <v>22.94</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="EC15" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="16">
@@ -7021,94 +7021,94 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D16" t="n">
         <v>7</v>
       </c>
       <c r="E16" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="F16" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="G16" t="n">
-        <v>4.38</v>
+        <v>4</v>
       </c>
       <c r="H16" t="n">
-        <v>102.25</v>
+        <v>101.11</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>2.62</v>
+        <v>2.33</v>
       </c>
       <c r="K16" t="n">
-        <v>7.88</v>
+        <v>7.33</v>
       </c>
       <c r="L16" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="M16" t="n">
-        <v>49.88</v>
+        <v>47.44</v>
       </c>
       <c r="N16" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="O16" t="n">
-        <v>3.5</v>
+        <v>3.33</v>
       </c>
       <c r="P16" t="n">
-        <v>12.5</v>
+        <v>12.56</v>
       </c>
       <c r="Q16" t="n">
-        <v>14.12</v>
+        <v>14.67</v>
       </c>
       <c r="R16" t="n">
-        <v>7.38</v>
+        <v>7.33</v>
       </c>
       <c r="S16" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="T16" t="n">
-        <v>2.25</v>
+        <v>2.44</v>
       </c>
       <c r="U16" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="V16" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>55.25</v>
+        <v>55</v>
       </c>
       <c r="Y16" t="n">
         <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>16</v>
+        <v>15.44</v>
       </c>
       <c r="AA16" t="n">
-        <v>10</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="AB16" t="n">
-        <v>6</v>
+        <v>6.22</v>
       </c>
       <c r="AC16" t="n">
-        <v>19</v>
+        <v>19.44</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.62</v>
+        <v>2.33</v>
       </c>
       <c r="AF16" t="n">
         <v>0</v>
@@ -7192,70 +7192,70 @@
         <v>3.14</v>
       </c>
       <c r="BG16" t="n">
-        <v>3.73</v>
+        <v>3.75</v>
       </c>
       <c r="BH16" t="n">
-        <v>11.47</v>
+        <v>11.25</v>
       </c>
       <c r="BI16" t="n">
-        <v>3.73</v>
+        <v>3.75</v>
       </c>
       <c r="BJ16" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BL16" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="BM16" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="BN16" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="BP16" t="n">
-        <v>5.67</v>
+        <v>5.56</v>
       </c>
       <c r="BQ16" t="n">
-        <v>5.8</v>
+        <v>5.69</v>
       </c>
       <c r="BR16" t="n">
         <v>100</v>
       </c>
       <c r="BS16" t="n">
-        <v>93.33</v>
+        <v>93.75</v>
       </c>
       <c r="BT16" t="n">
-        <v>86.67</v>
+        <v>87.5</v>
       </c>
       <c r="BU16" t="n">
-        <v>60</v>
+        <v>62.5</v>
       </c>
       <c r="BV16" t="n">
-        <v>26.67</v>
+        <v>25</v>
       </c>
       <c r="BW16" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BX16" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="BY16" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="BZ16" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="CA16" t="n">
-        <v>3.66</v>
+        <v>3.65</v>
       </c>
       <c r="CB16" t="n">
-        <v>3.82</v>
+        <v>3.8</v>
       </c>
       <c r="CC16" t="n">
         <v>3.14</v>
@@ -7264,58 +7264,58 @@
         <v>3.61</v>
       </c>
       <c r="CE16" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="CF16" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="CG16" t="n">
-        <v>3.08</v>
+        <v>3.07</v>
       </c>
       <c r="CH16" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CI16" t="n">
         <v>2.16</v>
       </c>
       <c r="CJ16" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CK16" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="CL16" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="CM16" t="n">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="CN16" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CO16" t="n">
         <v>1.22</v>
       </c>
       <c r="CP16" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CQ16" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="CR16" t="n">
         <v>1.38</v>
       </c>
       <c r="CS16" t="n">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="CT16" t="n">
-        <v>3.18</v>
+        <v>3.16</v>
       </c>
       <c r="CU16" t="n">
         <v>1.51</v>
       </c>
       <c r="CV16" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="CW16" t="n">
         <v>1.66</v>
@@ -7324,7 +7324,7 @@
         <v>1.53</v>
       </c>
       <c r="CY16" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CZ16" t="n">
         <v>2.42</v>
@@ -7336,58 +7336,58 @@
         <v>1.23</v>
       </c>
       <c r="DC16" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="DD16" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="DE16" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="DF16" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="DG16" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="DH16" t="n">
+        <v>96.38</v>
+      </c>
+      <c r="DI16" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="DJ16" t="n">
         <v>2.87</v>
       </c>
-      <c r="DE16" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="DF16" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="DG16" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="DH16" t="n">
-        <v>96.67</v>
-      </c>
-      <c r="DI16" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="DJ16" t="n">
-        <v>3.06</v>
-      </c>
       <c r="DK16" t="n">
-        <v>6.34</v>
+        <v>6.12</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DM16" t="n">
-        <v>43.67</v>
+        <v>42.68</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="DO16" t="n">
-        <v>2.73</v>
+        <v>2.69</v>
       </c>
       <c r="DP16" t="n">
-        <v>13.2</v>
+        <v>13.19</v>
       </c>
       <c r="DQ16" t="n">
-        <v>15.2</v>
+        <v>15.44</v>
       </c>
       <c r="DR16" t="n">
-        <v>7.67</v>
+        <v>7.62</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
@@ -7396,25 +7396,25 @@
         <v>52.87</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DX16" t="n">
-        <v>14.27</v>
+        <v>14.06</v>
       </c>
       <c r="DY16" t="n">
-        <v>8.74</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="DZ16" t="n">
-        <v>5.53</v>
+        <v>5.69</v>
       </c>
       <c r="EA16" t="n">
-        <v>18.2</v>
+        <v>18.5</v>
       </c>
       <c r="EB16" t="n">
         <v>1.6</v>
       </c>
       <c r="EC16" t="n">
-        <v>2.86</v>
+        <v>2.68</v>
       </c>
     </row>
     <row r="17">
@@ -7424,13 +7424,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C17" t="n">
         <v>8</v>
       </c>
       <c r="D17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E17" t="n">
         <v>0.12</v>
@@ -7517,49 +7517,49 @@
         <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.43</v>
+        <v>2.38</v>
       </c>
       <c r="AI17" t="n">
-        <v>87</v>
+        <v>85.12</v>
       </c>
       <c r="AJ17" t="n">
         <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>2.71</v>
+        <v>2.88</v>
       </c>
       <c r="AL17" t="n">
-        <v>3.43</v>
+        <v>3.38</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AN17" t="n">
-        <v>27.14</v>
+        <v>28.5</v>
       </c>
       <c r="AO17" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="AP17" t="n">
         <v>1</v>
       </c>
       <c r="AQ17" t="n">
-        <v>16.57</v>
+        <v>16.38</v>
       </c>
       <c r="AR17" t="n">
-        <v>13.43</v>
+        <v>13.62</v>
       </c>
       <c r="AS17" t="n">
-        <v>8.710000000000001</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="AT17" t="n">
-        <v>2.43</v>
+        <v>2.25</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AV17" t="n">
         <v>0</v>
@@ -7571,82 +7571,82 @@
         <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>43.86</v>
+        <v>43.88</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="BA17" t="n">
-        <v>11.29</v>
+        <v>11.88</v>
       </c>
       <c r="BB17" t="n">
-        <v>6.86</v>
+        <v>7.25</v>
       </c>
       <c r="BC17" t="n">
-        <v>4.43</v>
+        <v>4.62</v>
       </c>
       <c r="BD17" t="n">
-        <v>23.43</v>
+        <v>22.62</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="BF17" t="n">
-        <v>2.71</v>
+        <v>2.62</v>
       </c>
       <c r="BG17" t="n">
-        <v>3.13</v>
+        <v>3</v>
       </c>
       <c r="BH17" t="n">
-        <v>9.27</v>
+        <v>9</v>
       </c>
       <c r="BI17" t="n">
-        <v>3.13</v>
+        <v>3</v>
       </c>
       <c r="BJ17" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="BL17" t="n">
         <v>1</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="BP17" t="n">
-        <v>4.07</v>
+        <v>3.94</v>
       </c>
       <c r="BQ17" t="n">
-        <v>4.53</v>
+        <v>4.44</v>
       </c>
       <c r="BR17" t="n">
         <v>100</v>
       </c>
       <c r="BS17" t="n">
-        <v>66.67</v>
+        <v>62.5</v>
       </c>
       <c r="BT17" t="n">
-        <v>53.33</v>
+        <v>50</v>
       </c>
       <c r="BU17" t="n">
-        <v>26.67</v>
+        <v>25</v>
       </c>
       <c r="BV17" t="n">
-        <v>20</v>
+        <v>18.75</v>
       </c>
       <c r="BW17" t="n">
-        <v>20</v>
+        <v>18.75</v>
       </c>
       <c r="BX17" t="n">
-        <v>53.33</v>
+        <v>50</v>
       </c>
       <c r="BY17" t="n">
         <v>3.24</v>
@@ -7655,16 +7655,16 @@
         <v>3.55</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.48</v>
+        <v>3.45</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.72</v>
+        <v>3.69</v>
       </c>
       <c r="CC17" t="n">
-        <v>5.67</v>
+        <v>5.37</v>
       </c>
       <c r="CD17" t="n">
-        <v>6.87</v>
+        <v>6.55</v>
       </c>
       <c r="CE17" t="n">
         <v>1.42</v>
@@ -7673,10 +7673,10 @@
         <v>3.04</v>
       </c>
       <c r="CG17" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="CH17" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CI17" t="n">
         <v>1.81</v>
@@ -7691,7 +7691,7 @@
         <v>2.11</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="CN17" t="n">
         <v>1.78</v>
@@ -7700,16 +7700,16 @@
         <v>1.34</v>
       </c>
       <c r="CP17" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="CQ17" t="n">
-        <v>3.66</v>
+        <v>3.69</v>
       </c>
       <c r="CR17" t="n">
         <v>1.48</v>
       </c>
       <c r="CS17" t="n">
-        <v>3.06</v>
+        <v>3.08</v>
       </c>
       <c r="CT17" t="n">
         <v>2.78</v>
@@ -7718,22 +7718,22 @@
         <v>1.41</v>
       </c>
       <c r="CV17" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="CW17" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CX17" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CY17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="CZ17" t="n">
         <v>2.22</v>
       </c>
       <c r="DA17" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="DB17" t="n">
         <v>1.37</v>
@@ -7742,82 +7742,82 @@
         <v>2.19</v>
       </c>
       <c r="DD17" t="n">
-        <v>3.98</v>
+        <v>3.99</v>
       </c>
       <c r="DE17" t="n">
         <v>0.06</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="DG17" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="DH17" t="n">
-        <v>82.2</v>
+        <v>81.56</v>
       </c>
       <c r="DI17" t="n">
         <v>0</v>
       </c>
       <c r="DJ17" t="n">
-        <v>2.93</v>
+        <v>3</v>
       </c>
       <c r="DK17" t="n">
-        <v>3.2</v>
+        <v>3.19</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DM17" t="n">
-        <v>29.53</v>
+        <v>30.06</v>
       </c>
       <c r="DN17" t="n">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="DO17" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="DP17" t="n">
-        <v>18</v>
+        <v>17.81</v>
       </c>
       <c r="DQ17" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="DR17" t="n">
-        <v>8.800000000000001</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>43.87</v>
+        <v>43.88</v>
       </c>
       <c r="DW17" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="DX17" t="n">
-        <v>10.93</v>
+        <v>11.25</v>
       </c>
       <c r="DY17" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="DZ17" t="n">
-        <v>4.14</v>
+        <v>4.25</v>
       </c>
       <c r="EA17" t="n">
-        <v>21.73</v>
+        <v>21.44</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="EC17" t="n">
-        <v>2.93</v>
+        <v>2.87</v>
       </c>
     </row>
     <row r="18">
@@ -7827,94 +7827,94 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C18" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D18" t="n">
         <v>7</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="F18" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="G18" t="n">
-        <v>4.75</v>
+        <v>4.78</v>
       </c>
       <c r="H18" t="n">
-        <v>119.12</v>
+        <v>117.22</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>2.38</v>
+        <v>2.56</v>
       </c>
       <c r="K18" t="n">
-        <v>6.88</v>
+        <v>6.89</v>
       </c>
       <c r="L18" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="M18" t="n">
-        <v>69.62</v>
+        <v>66.78</v>
       </c>
       <c r="N18" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="O18" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="P18" t="n">
-        <v>17.75</v>
+        <v>17.89</v>
       </c>
       <c r="Q18" t="n">
-        <v>13</v>
+        <v>12.89</v>
       </c>
       <c r="R18" t="n">
-        <v>5.62</v>
+        <v>5.11</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
       </c>
       <c r="T18" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="U18" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="V18" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>55.75</v>
+        <v>54.78</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="Z18" t="n">
-        <v>16.88</v>
+        <v>17.33</v>
       </c>
       <c r="AA18" t="n">
-        <v>11.38</v>
+        <v>11.78</v>
       </c>
       <c r="AB18" t="n">
-        <v>5.5</v>
+        <v>5.56</v>
       </c>
       <c r="AC18" t="n">
-        <v>28.25</v>
+        <v>29</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="AF18" t="n">
         <v>0</v>
@@ -7998,70 +7998,70 @@
         <v>3.29</v>
       </c>
       <c r="BG18" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="BH18" t="n">
         <v>9</v>
       </c>
       <c r="BI18" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="BL18" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="BO18" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BP18" t="n">
-        <v>3.13</v>
+        <v>3.12</v>
       </c>
       <c r="BQ18" t="n">
-        <v>5.87</v>
+        <v>5.88</v>
       </c>
       <c r="BR18" t="n">
-        <v>86.67</v>
+        <v>87.5</v>
       </c>
       <c r="BS18" t="n">
-        <v>53.33</v>
+        <v>56.25</v>
       </c>
       <c r="BT18" t="n">
-        <v>26.67</v>
+        <v>25</v>
       </c>
       <c r="BU18" t="n">
-        <v>13.33</v>
+        <v>12.5</v>
       </c>
       <c r="BV18" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BW18" t="n">
         <v>0</v>
       </c>
       <c r="BX18" t="n">
-        <v>40</v>
+        <v>43.75</v>
       </c>
       <c r="BY18" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="BZ18" t="n">
-        <v>2.01</v>
+        <v>1.98</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.29</v>
+        <v>3.31</v>
       </c>
       <c r="CB18" t="n">
-        <v>3.4</v>
+        <v>3.42</v>
       </c>
       <c r="CC18" t="n">
         <v>2.77</v>
@@ -8073,7 +8073,7 @@
         <v>1.41</v>
       </c>
       <c r="CF18" t="n">
-        <v>2.96</v>
+        <v>2.95</v>
       </c>
       <c r="CG18" t="n">
         <v>2.72</v>
@@ -8088,10 +8088,10 @@
         <v>1.9</v>
       </c>
       <c r="CK18" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CL18" t="n">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
       <c r="CM18" t="n">
         <v>2.14</v>
@@ -8106,7 +8106,7 @@
         <v>2.15</v>
       </c>
       <c r="CQ18" t="n">
-        <v>3.8</v>
+        <v>3.78</v>
       </c>
       <c r="CR18" t="n">
         <v>1.46</v>
@@ -8121,19 +8121,19 @@
         <v>1.4</v>
       </c>
       <c r="CV18" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CW18" t="n">
         <v>1.92</v>
       </c>
       <c r="CX18" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CY18" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="CZ18" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="DA18" t="n">
         <v>1.71</v>
@@ -8145,82 +8145,82 @@
         <v>2.19</v>
       </c>
       <c r="DD18" t="n">
-        <v>3.98</v>
+        <v>3.97</v>
       </c>
       <c r="DE18" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="DG18" t="n">
-        <v>4.13</v>
+        <v>4.19</v>
       </c>
       <c r="DH18" t="n">
-        <v>115.86</v>
+        <v>115</v>
       </c>
       <c r="DI18" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DJ18" t="n">
-        <v>2.87</v>
+        <v>2.94</v>
       </c>
       <c r="DK18" t="n">
-        <v>6.47</v>
+        <v>6.5</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.53</v>
+        <v>0.63</v>
       </c>
       <c r="DM18" t="n">
-        <v>60.26</v>
+        <v>59.25</v>
       </c>
       <c r="DN18" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="DO18" t="n">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="DP18" t="n">
-        <v>17.8</v>
+        <v>17.88</v>
       </c>
       <c r="DQ18" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="DR18" t="n">
-        <v>7.06</v>
+        <v>6.68</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DT18" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DU18" t="n">
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>53.67</v>
+        <v>53.25</v>
       </c>
       <c r="DW18" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.12</v>
       </c>
       <c r="DX18" t="n">
-        <v>15.13</v>
+        <v>15.5</v>
       </c>
       <c r="DY18" t="n">
-        <v>10.54</v>
+        <v>10.81</v>
       </c>
       <c r="DZ18" t="n">
-        <v>4.6</v>
+        <v>4.69</v>
       </c>
       <c r="EA18" t="n">
-        <v>26.07</v>
+        <v>26.62</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="EC18" t="n">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
     </row>
     <row r="19">
@@ -8230,10 +8230,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D19" t="n">
         <v>8</v>
@@ -8242,49 +8242,49 @@
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="G19" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="H19" t="n">
-        <v>94.86</v>
+        <v>96</v>
       </c>
       <c r="I19" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="J19" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K19" t="n">
         <v>4</v>
       </c>
-      <c r="K19" t="n">
-        <v>3.86</v>
-      </c>
       <c r="L19" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="M19" t="n">
-        <v>39.29</v>
+        <v>43.25</v>
       </c>
       <c r="N19" t="n">
-        <v>2.29</v>
+        <v>2.12</v>
       </c>
       <c r="O19" t="n">
-        <v>2.71</v>
+        <v>2.88</v>
       </c>
       <c r="P19" t="n">
-        <v>12.57</v>
+        <v>12.88</v>
       </c>
       <c r="Q19" t="n">
-        <v>14.43</v>
+        <v>14.88</v>
       </c>
       <c r="R19" t="n">
-        <v>7.86</v>
+        <v>7.12</v>
       </c>
       <c r="S19" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="T19" t="n">
-        <v>0.43</v>
+        <v>0.75</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
@@ -8296,28 +8296,28 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>49.57</v>
+        <v>51.25</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="Z19" t="n">
-        <v>9.859999999999999</v>
+        <v>11.12</v>
       </c>
       <c r="AA19" t="n">
-        <v>7</v>
+        <v>7.25</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.86</v>
+        <v>3.88</v>
       </c>
       <c r="AC19" t="n">
-        <v>24</v>
+        <v>23.12</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.11</v>
+        <v>1.29</v>
       </c>
       <c r="AE19" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="AF19" t="n">
         <v>0.12</v>
@@ -8401,70 +8401,70 @@
         <v>2.5</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.27</v>
+        <v>2.44</v>
       </c>
       <c r="BH19" t="n">
-        <v>10.07</v>
+        <v>9.94</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.27</v>
+        <v>2.44</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.4</v>
+        <v>0.44</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="BO19" t="n">
-        <v>0.73</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BP19" t="n">
-        <v>5.27</v>
+        <v>5.25</v>
       </c>
       <c r="BQ19" t="n">
-        <v>4.73</v>
+        <v>4.62</v>
       </c>
       <c r="BR19" t="n">
-        <v>93.33</v>
+        <v>93.75</v>
       </c>
       <c r="BS19" t="n">
-        <v>53.33</v>
+        <v>56.25</v>
       </c>
       <c r="BT19" t="n">
-        <v>33.33</v>
+        <v>37.5</v>
       </c>
       <c r="BU19" t="n">
-        <v>26.67</v>
+        <v>31.25</v>
       </c>
       <c r="BV19" t="n">
-        <v>13.33</v>
+        <v>18.75</v>
       </c>
       <c r="BW19" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BX19" t="n">
-        <v>40</v>
+        <v>43.75</v>
       </c>
       <c r="BY19" t="n">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="BZ19" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="CA19" t="n">
-        <v>3.21</v>
+        <v>3.2</v>
       </c>
       <c r="CB19" t="n">
-        <v>3.35</v>
+        <v>3.33</v>
       </c>
       <c r="CC19" t="n">
         <v>3.81</v>
@@ -8473,43 +8473,43 @@
         <v>4.48</v>
       </c>
       <c r="CE19" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="CF19" t="n">
-        <v>3.09</v>
+        <v>3.13</v>
       </c>
       <c r="CG19" t="n">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="CH19" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="CI19" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CJ19" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="CK19" t="n">
         <v>1.59</v>
       </c>
       <c r="CL19" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CM19" t="n">
         <v>2.3</v>
       </c>
       <c r="CN19" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CO19" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="CP19" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="CQ19" t="n">
-        <v>3.95</v>
+        <v>4.03</v>
       </c>
       <c r="CR19" t="n">
         <v>1.49</v>
@@ -8518,28 +8518,28 @@
         <v>3.2</v>
       </c>
       <c r="CT19" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="CU19" t="n">
         <v>1.37</v>
       </c>
       <c r="CV19" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CW19" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CX19" t="n">
         <v>1.61</v>
       </c>
       <c r="CY19" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="CZ19" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="DA19" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="DB19" t="n">
         <v>1.39</v>
@@ -8554,43 +8554,43 @@
         <v>0.06</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="DG19" t="n">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="DH19" t="n">
-        <v>91.2</v>
+        <v>92</v>
       </c>
       <c r="DI19" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DJ19" t="n">
-        <v>3.26</v>
+        <v>3.18</v>
       </c>
       <c r="DK19" t="n">
-        <v>4.8</v>
+        <v>4.81</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="DM19" t="n">
-        <v>40.2</v>
+        <v>42.12</v>
       </c>
       <c r="DN19" t="n">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="DO19" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="DP19" t="n">
-        <v>13.33</v>
+        <v>13.44</v>
       </c>
       <c r="DQ19" t="n">
-        <v>15.53</v>
+        <v>15.69</v>
       </c>
       <c r="DR19" t="n">
-        <v>7</v>
+        <v>6.68</v>
       </c>
       <c r="DS19" t="n">
         <v>0.06</v>
@@ -8602,28 +8602,28 @@
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>48.53</v>
+        <v>49.44</v>
       </c>
       <c r="DW19" t="n">
-        <v>0.4</v>
+        <v>0.37</v>
       </c>
       <c r="DX19" t="n">
-        <v>11.4</v>
+        <v>11.93</v>
       </c>
       <c r="DY19" t="n">
-        <v>8.4</v>
+        <v>8.43</v>
       </c>
       <c r="DZ19" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="EA19" t="n">
-        <v>20.8</v>
+        <v>20.56</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="EC19" t="n">
-        <v>2.73</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="20">
@@ -8633,13 +8633,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C20" t="n">
         <v>8</v>
       </c>
       <c r="D20" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -8723,52 +8723,52 @@
         <v>2.62</v>
       </c>
       <c r="AF20" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AH20" t="n">
-        <v>3.14</v>
+        <v>3.12</v>
       </c>
       <c r="AI20" t="n">
-        <v>99.70999999999999</v>
+        <v>100.12</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="AK20" t="n">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="AL20" t="n">
-        <v>4.43</v>
+        <v>4.5</v>
       </c>
       <c r="AM20" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="AN20" t="n">
-        <v>38.43</v>
+        <v>38.38</v>
       </c>
       <c r="AO20" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="AQ20" t="n">
-        <v>11.43</v>
+        <v>12.38</v>
       </c>
       <c r="AR20" t="n">
-        <v>13.71</v>
+        <v>13.62</v>
       </c>
       <c r="AS20" t="n">
-        <v>6.57</v>
+        <v>6.62</v>
       </c>
       <c r="AT20" t="n">
-        <v>1.71</v>
+        <v>2</v>
       </c>
       <c r="AU20" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="AV20" t="n">
         <v>0</v>
@@ -8780,82 +8780,82 @@
         <v>0</v>
       </c>
       <c r="AY20" t="n">
-        <v>50.29</v>
+        <v>49.88</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="BA20" t="n">
-        <v>9.859999999999999</v>
+        <v>10.25</v>
       </c>
       <c r="BB20" t="n">
-        <v>6.86</v>
+        <v>6.88</v>
       </c>
       <c r="BC20" t="n">
-        <v>3</v>
+        <v>3.38</v>
       </c>
       <c r="BD20" t="n">
-        <v>19.71</v>
+        <v>19.5</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="BF20" t="n">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="BG20" t="n">
-        <v>2.33</v>
+        <v>2.44</v>
       </c>
       <c r="BH20" t="n">
-        <v>9.199999999999999</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="BI20" t="n">
-        <v>2.33</v>
+        <v>2.44</v>
       </c>
       <c r="BJ20" t="n">
-        <v>0.6</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BK20" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="BL20" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="BM20" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="BN20" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BO20" t="n">
         <v>1</v>
       </c>
-      <c r="BM20" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="BN20" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="BO20" t="n">
-        <v>0.93</v>
-      </c>
       <c r="BP20" t="n">
-        <v>4.27</v>
+        <v>4.25</v>
       </c>
       <c r="BQ20" t="n">
-        <v>4.93</v>
+        <v>4.88</v>
       </c>
       <c r="BR20" t="n">
-        <v>86.67</v>
+        <v>87.5</v>
       </c>
       <c r="BS20" t="n">
-        <v>73.33</v>
+        <v>75</v>
       </c>
       <c r="BT20" t="n">
-        <v>46.67</v>
+        <v>50</v>
       </c>
       <c r="BU20" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="BV20" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BW20" t="n">
         <v>0</v>
       </c>
       <c r="BX20" t="n">
-        <v>60</v>
+        <v>56.25</v>
       </c>
       <c r="BY20" t="n">
         <v>1.9</v>
@@ -8864,169 +8864,169 @@
         <v>2.05</v>
       </c>
       <c r="CA20" t="n">
-        <v>3.17</v>
+        <v>3.19</v>
       </c>
       <c r="CB20" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="CC20" t="n">
         <v>3.25</v>
       </c>
-      <c r="CC20" t="n">
-        <v>3.26</v>
-      </c>
       <c r="CD20" t="n">
-        <v>3.62</v>
+        <v>3.64</v>
       </c>
       <c r="CE20" t="n">
         <v>1.48</v>
       </c>
       <c r="CF20" t="n">
-        <v>3.33</v>
+        <v>3.29</v>
       </c>
       <c r="CG20" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="CH20" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="CI20" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="CJ20" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="CK20" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CL20" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="CM20" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="CN20" t="n">
         <v>1.73</v>
       </c>
       <c r="CO20" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CP20" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="CQ20" t="n">
-        <v>4.46</v>
+        <v>4.38</v>
       </c>
       <c r="CR20" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="CS20" t="n">
-        <v>3.25</v>
+        <v>3.22</v>
       </c>
       <c r="CT20" t="n">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="CU20" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CV20" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="CW20" t="n">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="CX20" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CY20" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="CZ20" t="n">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="DA20" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="DB20" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="DC20" t="n">
-        <v>2.49</v>
+        <v>2.46</v>
       </c>
       <c r="DD20" t="n">
-        <v>4.78</v>
+        <v>4.69</v>
       </c>
       <c r="DE20" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DF20" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="DG20" t="n">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
       <c r="DH20" t="n">
-        <v>106.73</v>
+        <v>106.5</v>
       </c>
       <c r="DI20" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.12</v>
       </c>
       <c r="DJ20" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="DK20" t="n">
         <v>4.94</v>
       </c>
       <c r="DL20" t="n">
-        <v>0.34</v>
+        <v>0.38</v>
       </c>
       <c r="DM20" t="n">
-        <v>49.13</v>
+        <v>48.44</v>
       </c>
       <c r="DN20" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="DO20" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="DP20" t="n">
-        <v>13.93</v>
+        <v>14.25</v>
       </c>
       <c r="DQ20" t="n">
-        <v>12.47</v>
+        <v>12.5</v>
       </c>
       <c r="DR20" t="n">
-        <v>6.74</v>
+        <v>6.75</v>
       </c>
       <c r="DS20" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DT20" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DU20" t="n">
         <v>0</v>
       </c>
       <c r="DV20" t="n">
-        <v>52.74</v>
+        <v>52.38</v>
       </c>
       <c r="DW20" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DX20" t="n">
-        <v>13.34</v>
+        <v>13.32</v>
       </c>
       <c r="DY20" t="n">
-        <v>8.800000000000001</v>
+        <v>8.69</v>
       </c>
       <c r="DZ20" t="n">
-        <v>4.54</v>
+        <v>4.63</v>
       </c>
       <c r="EA20" t="n">
-        <v>19.13</v>
+        <v>19.06</v>
       </c>
       <c r="EB20" t="n">
         <v>1.52</v>
       </c>
       <c r="EC20" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
     </row>
     <row r="21">
@@ -9036,13 +9036,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C21" t="n">
         <v>8</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -9129,49 +9129,49 @@
         <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.29</v>
+        <v>2</v>
       </c>
       <c r="AI21" t="n">
-        <v>82.70999999999999</v>
+        <v>80.62</v>
       </c>
       <c r="AJ21" t="n">
         <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>2.29</v>
+        <v>2</v>
       </c>
       <c r="AL21" t="n">
-        <v>3.57</v>
+        <v>3.25</v>
       </c>
       <c r="AM21" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="AN21" t="n">
-        <v>35.57</v>
+        <v>32.88</v>
       </c>
       <c r="AO21" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AQ21" t="n">
-        <v>10.86</v>
+        <v>10.25</v>
       </c>
       <c r="AR21" t="n">
-        <v>13.71</v>
+        <v>13.38</v>
       </c>
       <c r="AS21" t="n">
-        <v>7.14</v>
+        <v>7.75</v>
       </c>
       <c r="AT21" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="AU21" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="AV21" t="n">
         <v>0</v>
@@ -9183,73 +9183,73 @@
         <v>0</v>
       </c>
       <c r="AY21" t="n">
-        <v>49</v>
+        <v>46.75</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="BA21" t="n">
-        <v>9.57</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="BB21" t="n">
-        <v>8</v>
+        <v>7.38</v>
       </c>
       <c r="BC21" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="BD21" t="n">
-        <v>18.57</v>
+        <v>18.12</v>
       </c>
       <c r="BE21" t="n">
-        <v>0.98</v>
+        <v>0.91</v>
       </c>
       <c r="BF21" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="BG21" t="n">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="BH21" t="n">
-        <v>9.07</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="BI21" t="n">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="BJ21" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BK21" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="BL21" t="n">
-        <v>0.87</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BM21" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="BN21" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="BO21" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="BP21" t="n">
-        <v>4.2</v>
+        <v>4.19</v>
       </c>
       <c r="BQ21" t="n">
-        <v>4.8</v>
+        <v>5.12</v>
       </c>
       <c r="BR21" t="n">
-        <v>100</v>
+        <v>93.75</v>
       </c>
       <c r="BS21" t="n">
-        <v>66.67</v>
+        <v>62.5</v>
       </c>
       <c r="BT21" t="n">
-        <v>40</v>
+        <v>37.5</v>
       </c>
       <c r="BU21" t="n">
-        <v>13.33</v>
+        <v>12.5</v>
       </c>
       <c r="BV21" t="n">
         <v>0</v>
@@ -9258,7 +9258,7 @@
         <v>0</v>
       </c>
       <c r="BX21" t="n">
-        <v>46.67</v>
+        <v>43.75</v>
       </c>
       <c r="BY21" t="n">
         <v>2.39</v>
@@ -9267,169 +9267,169 @@
         <v>2.57</v>
       </c>
       <c r="CA21" t="n">
-        <v>2.87</v>
+        <v>2.91</v>
       </c>
       <c r="CB21" t="n">
-        <v>2.98</v>
+        <v>3.02</v>
       </c>
       <c r="CC21" t="n">
-        <v>3.2</v>
+        <v>3.48</v>
       </c>
       <c r="CD21" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="CE21" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="CF21" t="n">
         <v>3.75</v>
       </c>
-      <c r="CE21" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="CF21" t="n">
-        <v>3.77</v>
-      </c>
       <c r="CG21" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="CH21" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="CI21" t="n">
         <v>1.64</v>
       </c>
       <c r="CJ21" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="CK21" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CL21" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="CM21" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="CN21" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CO21" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="CP21" t="n">
-        <v>2.66</v>
+        <v>2.63</v>
       </c>
       <c r="CQ21" t="n">
-        <v>5.22</v>
+        <v>5.15</v>
       </c>
       <c r="CR21" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CS21" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="CT21" t="n">
-        <v>2.35</v>
+        <v>2.37</v>
       </c>
       <c r="CU21" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="CV21" t="n">
         <v>1.66</v>
       </c>
       <c r="CW21" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="CX21" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="CY21" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="CZ21" t="n">
-        <v>2.04</v>
+        <v>2.07</v>
       </c>
       <c r="DA21" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="DB21" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="DC21" t="n">
-        <v>2.91</v>
+        <v>2.87</v>
       </c>
       <c r="DD21" t="n">
-        <v>5.92</v>
+        <v>5.82</v>
       </c>
       <c r="DE21" t="n">
         <v>0</v>
       </c>
       <c r="DF21" t="n">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="DG21" t="n">
-        <v>2.47</v>
+        <v>2.31</v>
       </c>
       <c r="DH21" t="n">
-        <v>89.47</v>
+        <v>88</v>
       </c>
       <c r="DI21" t="n">
         <v>0</v>
       </c>
       <c r="DJ21" t="n">
-        <v>2.07</v>
+        <v>1.94</v>
       </c>
       <c r="DK21" t="n">
-        <v>4.4</v>
+        <v>4.19</v>
       </c>
       <c r="DL21" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DM21" t="n">
-        <v>39.74</v>
+        <v>38.13</v>
       </c>
       <c r="DN21" t="n">
-        <v>0.73</v>
+        <v>0.68</v>
       </c>
       <c r="DO21" t="n">
-        <v>1.87</v>
+        <v>1.82</v>
       </c>
       <c r="DP21" t="n">
-        <v>12.93</v>
+        <v>12.5</v>
       </c>
       <c r="DQ21" t="n">
-        <v>13.2</v>
+        <v>13.07</v>
       </c>
       <c r="DR21" t="n">
-        <v>8.529999999999999</v>
+        <v>8.75</v>
       </c>
       <c r="DS21" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DT21" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DU21" t="n">
         <v>0</v>
       </c>
       <c r="DV21" t="n">
-        <v>47.46</v>
+        <v>46.44</v>
       </c>
       <c r="DW21" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DX21" t="n">
-        <v>10.93</v>
+        <v>10.5</v>
       </c>
       <c r="DY21" t="n">
-        <v>8.27</v>
+        <v>7.94</v>
       </c>
       <c r="DZ21" t="n">
-        <v>2.66</v>
+        <v>2.56</v>
       </c>
       <c r="EA21" t="n">
-        <v>21.6</v>
+        <v>21.18</v>
       </c>
       <c r="EB21" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="EC21" t="n">
-        <v>1.94</v>
+        <v>1.82</v>
       </c>
     </row>
     <row r="22">
@@ -9842,13 +9842,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C23" t="n">
         <v>8</v>
       </c>
       <c r="D23" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E23" t="n">
         <v>0.12</v>
@@ -9935,49 +9935,49 @@
         <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AH23" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AI23" t="n">
-        <v>89.14</v>
+        <v>89.75</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AK23" t="n">
         <v>2</v>
       </c>
       <c r="AL23" t="n">
-        <v>3.86</v>
+        <v>3.75</v>
       </c>
       <c r="AM23" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="AN23" t="n">
-        <v>33.43</v>
+        <v>34.25</v>
       </c>
       <c r="AO23" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="AQ23" t="n">
-        <v>12.29</v>
+        <v>11.88</v>
       </c>
       <c r="AR23" t="n">
-        <v>20</v>
+        <v>19.25</v>
       </c>
       <c r="AS23" t="n">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="AT23" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="AU23" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="AV23" t="n">
         <v>0</v>
@@ -9989,73 +9989,73 @@
         <v>0</v>
       </c>
       <c r="AY23" t="n">
-        <v>57.43</v>
+        <v>57.12</v>
       </c>
       <c r="AZ23" t="n">
         <v>0</v>
       </c>
       <c r="BA23" t="n">
-        <v>10.14</v>
+        <v>10.12</v>
       </c>
       <c r="BB23" t="n">
-        <v>7.14</v>
+        <v>7.38</v>
       </c>
       <c r="BC23" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="BD23" t="n">
-        <v>17.43</v>
+        <v>17.88</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="BF23" t="n">
         <v>2</v>
       </c>
       <c r="BG23" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="BH23" t="n">
-        <v>7.87</v>
+        <v>7.75</v>
       </c>
       <c r="BI23" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="BJ23" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BK23" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="BL23" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="BM23" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BN23" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="BO23" t="n">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="BP23" t="n">
-        <v>3.6</v>
+        <v>3.62</v>
       </c>
       <c r="BQ23" t="n">
-        <v>4.27</v>
+        <v>4.12</v>
       </c>
       <c r="BR23" t="n">
-        <v>80</v>
+        <v>81.25</v>
       </c>
       <c r="BS23" t="n">
-        <v>46.67</v>
+        <v>43.75</v>
       </c>
       <c r="BT23" t="n">
-        <v>33.33</v>
+        <v>31.25</v>
       </c>
       <c r="BU23" t="n">
-        <v>20</v>
+        <v>18.75</v>
       </c>
       <c r="BV23" t="n">
         <v>0</v>
@@ -10064,7 +10064,7 @@
         <v>0</v>
       </c>
       <c r="BX23" t="n">
-        <v>46.67</v>
+        <v>43.75</v>
       </c>
       <c r="BY23" t="n">
         <v>1.84</v>
@@ -10073,25 +10073,25 @@
         <v>1.9</v>
       </c>
       <c r="CA23" t="n">
-        <v>3.19</v>
+        <v>3.2</v>
       </c>
       <c r="CB23" t="n">
-        <v>3.32</v>
+        <v>3.33</v>
       </c>
       <c r="CC23" t="n">
-        <v>3.09</v>
+        <v>3.11</v>
       </c>
       <c r="CD23" t="n">
-        <v>3.32</v>
+        <v>3.44</v>
       </c>
       <c r="CE23" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CF23" t="n">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
       <c r="CG23" t="n">
-        <v>2.53</v>
+        <v>2.54</v>
       </c>
       <c r="CH23" t="n">
         <v>1.32</v>
@@ -10100,28 +10100,28 @@
         <v>1.81</v>
       </c>
       <c r="CJ23" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="CK23" t="n">
         <v>1.68</v>
       </c>
       <c r="CL23" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="CM23" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="CN23" t="n">
         <v>1.68</v>
       </c>
       <c r="CO23" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CP23" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="CQ23" t="n">
-        <v>4.19</v>
+        <v>4.13</v>
       </c>
       <c r="CR23" t="n">
         <v>1.51</v>
@@ -10136,7 +10136,7 @@
         <v>1.37</v>
       </c>
       <c r="CV23" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CW23" t="n">
         <v>2.05</v>
@@ -10145,64 +10145,64 @@
         <v>1.75</v>
       </c>
       <c r="CY23" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="CZ23" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="DA23" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="DB23" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="DC23" t="n">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
       <c r="DD23" t="n">
-        <v>4.57</v>
+        <v>4.53</v>
       </c>
       <c r="DE23" t="n">
         <v>0.06</v>
       </c>
       <c r="DF23" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="DG23" t="n">
-        <v>2.13</v>
+        <v>2.06</v>
       </c>
       <c r="DH23" t="n">
-        <v>93.13</v>
+        <v>93.18000000000001</v>
       </c>
       <c r="DI23" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DJ23" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="DK23" t="n">
-        <v>4.07</v>
+        <v>4</v>
       </c>
       <c r="DL23" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="DM23" t="n">
-        <v>36.53</v>
+        <v>36.75</v>
       </c>
       <c r="DN23" t="n">
-        <v>0.4</v>
+        <v>0.44</v>
       </c>
       <c r="DO23" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="DP23" t="n">
-        <v>13.14</v>
+        <v>12.88</v>
       </c>
       <c r="DQ23" t="n">
-        <v>18.4</v>
+        <v>18.12</v>
       </c>
       <c r="DR23" t="n">
-        <v>7.46</v>
+        <v>7.81</v>
       </c>
       <c r="DS23" t="n">
         <v>0</v>
@@ -10214,28 +10214,28 @@
         <v>0</v>
       </c>
       <c r="DV23" t="n">
-        <v>56.73</v>
+        <v>56.62</v>
       </c>
       <c r="DW23" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DX23" t="n">
-        <v>11.4</v>
+        <v>11.31</v>
       </c>
       <c r="DY23" t="n">
-        <v>7.6</v>
+        <v>7.69</v>
       </c>
       <c r="DZ23" t="n">
-        <v>3.8</v>
+        <v>3.62</v>
       </c>
       <c r="EA23" t="n">
-        <v>18.47</v>
+        <v>18.63</v>
       </c>
       <c r="EB23" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="EC23" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Spain_Segunda_División_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Spain_Segunda_División_2025-2026.xlsx
@@ -3944,7 +3944,7 @@
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>41.62</v>
+        <v>41.5</v>
       </c>
       <c r="AZ8" t="n">
         <v>0</v>
@@ -4169,7 +4169,7 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>47.5</v>
+        <v>47.44</v>
       </c>
       <c r="DW8" t="n">
         <v>0</v>
@@ -4266,7 +4266,7 @@
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>57.75</v>
+        <v>57.88</v>
       </c>
       <c r="Y9" t="n">
         <v>0.25</v>
@@ -4572,7 +4572,7 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>55</v>
+        <v>55.06</v>
       </c>
       <c r="DW9" t="n">
         <v>0.18</v>
@@ -7577,10 +7577,10 @@
         <v>0.12</v>
       </c>
       <c r="BA17" t="n">
-        <v>11.88</v>
+        <v>11.75</v>
       </c>
       <c r="BB17" t="n">
-        <v>7.25</v>
+        <v>7.12</v>
       </c>
       <c r="BC17" t="n">
         <v>4.62</v>
@@ -7802,10 +7802,10 @@
         <v>0.06</v>
       </c>
       <c r="DX17" t="n">
-        <v>11.25</v>
+        <v>11.18</v>
       </c>
       <c r="DY17" t="n">
-        <v>7</v>
+        <v>6.94</v>
       </c>
       <c r="DZ17" t="n">
         <v>4.25</v>
@@ -7899,10 +7899,10 @@
         <v>0.11</v>
       </c>
       <c r="Z18" t="n">
-        <v>17.33</v>
+        <v>17.44</v>
       </c>
       <c r="AA18" t="n">
-        <v>11.78</v>
+        <v>11.89</v>
       </c>
       <c r="AB18" t="n">
         <v>5.56</v>
@@ -8205,10 +8205,10 @@
         <v>0.12</v>
       </c>
       <c r="DX18" t="n">
-        <v>15.5</v>
+        <v>15.56</v>
       </c>
       <c r="DY18" t="n">
-        <v>10.81</v>
+        <v>10.88</v>
       </c>
       <c r="DZ18" t="n">
         <v>4.69</v>

--- a/data/teams/leagues/Averages_Spain_Segunda_División_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Spain_Segunda_División_2025-2026.xlsx
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C3" t="n">
         <v>8</v>
       </c>
       <c r="D3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E3" t="n">
         <v>0.12</v>
@@ -1875,136 +1875,136 @@
         <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="AI3" t="n">
-        <v>88.12</v>
+        <v>86.11</v>
       </c>
       <c r="AJ3" t="n">
         <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>3.62</v>
+        <v>3.44</v>
       </c>
       <c r="AL3" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="AM3" t="n">
-        <v>-0.12</v>
+        <v>-0.11</v>
       </c>
       <c r="AN3" t="n">
-        <v>36.88</v>
+        <v>38.22</v>
       </c>
       <c r="AO3" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="AQ3" t="n">
-        <v>14.62</v>
+        <v>14.44</v>
       </c>
       <c r="AR3" t="n">
-        <v>14.38</v>
+        <v>14.33</v>
       </c>
       <c r="AS3" t="n">
-        <v>7.88</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AX3" t="n">
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>52.25</v>
+        <v>50.89</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="BA3" t="n">
-        <v>12.62</v>
+        <v>13.11</v>
       </c>
       <c r="BB3" t="n">
-        <v>8.880000000000001</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="BC3" t="n">
-        <v>3.75</v>
+        <v>4.22</v>
       </c>
       <c r="BD3" t="n">
-        <v>20.62</v>
+        <v>21.56</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="BF3" t="n">
-        <v>3.5</v>
+        <v>3.33</v>
       </c>
       <c r="BG3" t="n">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="BH3" t="n">
-        <v>9.69</v>
+        <v>9.94</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BL3" t="n">
         <v>1.12</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.9399999999999999</v>
+        <v>1</v>
       </c>
       <c r="BN3" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="BP3" t="n">
-        <v>4</v>
+        <v>4.12</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5.25</v>
+        <v>5.41</v>
       </c>
       <c r="BR3" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BS3" t="n">
-        <v>75</v>
+        <v>76.47</v>
       </c>
       <c r="BT3" t="n">
-        <v>62.5</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BU3" t="n">
-        <v>43.75</v>
+        <v>41.18</v>
       </c>
       <c r="BV3" t="n">
-        <v>25</v>
+        <v>23.53</v>
       </c>
       <c r="BW3" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BX3" t="n">
-        <v>62.5</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BY3" t="n">
         <v>1.69</v>
@@ -2013,40 +2013,40 @@
         <v>1.76</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.46</v>
+        <v>3.47</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.65</v>
+        <v>3.64</v>
       </c>
       <c r="CC3" t="n">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="CD3" t="n">
-        <v>2.92</v>
+        <v>2.86</v>
       </c>
       <c r="CE3" t="n">
         <v>1.36</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.69</v>
+        <v>2.68</v>
       </c>
       <c r="CG3" t="n">
-        <v>2.96</v>
+        <v>2.97</v>
       </c>
       <c r="CH3" t="n">
         <v>1.44</v>
       </c>
       <c r="CI3" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="CJ3" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CK3" t="n">
         <v>1.49</v>
       </c>
       <c r="CL3" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CM3" t="n">
         <v>2.38</v>
@@ -2082,7 +2082,7 @@
         <v>1.74</v>
       </c>
       <c r="CX3" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="CY3" t="n">
         <v>1.91</v>
@@ -2106,76 +2106,76 @@
         <v>0.06</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="DG3" t="n">
-        <v>2.94</v>
+        <v>2.89</v>
       </c>
       <c r="DH3" t="n">
-        <v>94.68000000000001</v>
+        <v>93.23</v>
       </c>
       <c r="DI3" t="n">
         <v>0</v>
       </c>
       <c r="DJ3" t="n">
-        <v>3.06</v>
+        <v>3</v>
       </c>
       <c r="DK3" t="n">
-        <v>5.82</v>
+        <v>5.71</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DM3" t="n">
-        <v>47.75</v>
+        <v>47.82</v>
       </c>
       <c r="DN3" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="DO3" t="n">
-        <v>2.56</v>
+        <v>2.53</v>
       </c>
       <c r="DP3" t="n">
-        <v>14</v>
+        <v>13.94</v>
       </c>
       <c r="DQ3" t="n">
-        <v>12.07</v>
+        <v>12.17</v>
       </c>
       <c r="DR3" t="n">
-        <v>7.69</v>
+        <v>7.82</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>54.44</v>
+        <v>53.59</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DX3" t="n">
-        <v>16.18</v>
+        <v>16.23</v>
       </c>
       <c r="DY3" t="n">
-        <v>10.38</v>
+        <v>10.3</v>
       </c>
       <c r="DZ3" t="n">
-        <v>5.82</v>
+        <v>5.94</v>
       </c>
       <c r="EA3" t="n">
-        <v>18.94</v>
+        <v>19.53</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
     </row>
     <row r="4">
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C5" t="n">
         <v>8</v>
       </c>
       <c r="D5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E5" t="n">
         <v>0.12</v>
@@ -2678,52 +2678,52 @@
         <v>3.25</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.38</v>
+        <v>1.67</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.25</v>
+        <v>2.56</v>
       </c>
       <c r="AI5" t="n">
-        <v>92.88</v>
+        <v>93.44</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.5</v>
+        <v>2.89</v>
       </c>
       <c r="AL5" t="n">
-        <v>5.25</v>
+        <v>5.67</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AN5" t="n">
-        <v>52.88</v>
+        <v>53.22</v>
       </c>
       <c r="AO5" t="n">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="AP5" t="n">
-        <v>3</v>
+        <v>3.11</v>
       </c>
       <c r="AQ5" t="n">
-        <v>12.88</v>
+        <v>13.11</v>
       </c>
       <c r="AR5" t="n">
-        <v>14.5</v>
+        <v>14.33</v>
       </c>
       <c r="AS5" t="n">
-        <v>6.25</v>
+        <v>5.89</v>
       </c>
       <c r="AT5" t="n">
         <v>1</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.12</v>
+        <v>1.33</v>
       </c>
       <c r="AV5" t="n">
         <v>0</v>
@@ -2735,82 +2735,82 @@
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>50.88</v>
+        <v>51.44</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="BA5" t="n">
-        <v>12.25</v>
+        <v>12.78</v>
       </c>
       <c r="BB5" t="n">
-        <v>7.75</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="BC5" t="n">
-        <v>4.5</v>
+        <v>4.56</v>
       </c>
       <c r="BD5" t="n">
-        <v>19.62</v>
+        <v>19.78</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="BF5" t="n">
-        <v>2.25</v>
+        <v>2.67</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.75</v>
+        <v>2.82</v>
       </c>
       <c r="BH5" t="n">
-        <v>10.06</v>
+        <v>10.18</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.75</v>
+        <v>2.82</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.44</v>
+        <v>0.47</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="BL5" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.62</v>
+        <v>0.76</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="BO5" t="n">
         <v>1.12</v>
       </c>
       <c r="BP5" t="n">
-        <v>5.25</v>
+        <v>5.29</v>
       </c>
       <c r="BQ5" t="n">
-        <v>4.81</v>
+        <v>4.88</v>
       </c>
       <c r="BR5" t="n">
-        <v>87.5</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="BS5" t="n">
-        <v>56.25</v>
+        <v>58.82</v>
       </c>
       <c r="BT5" t="n">
-        <v>50</v>
+        <v>52.94</v>
       </c>
       <c r="BU5" t="n">
-        <v>37.5</v>
+        <v>41.18</v>
       </c>
       <c r="BV5" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BW5" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BX5" t="n">
-        <v>56.25</v>
+        <v>58.82</v>
       </c>
       <c r="BY5" t="n">
         <v>1.74</v>
@@ -2819,16 +2819,16 @@
         <v>1.72</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.58</v>
+        <v>3.54</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.83</v>
+        <v>3.8</v>
       </c>
       <c r="CC5" t="n">
-        <v>2.83</v>
+        <v>2.84</v>
       </c>
       <c r="CD5" t="n">
-        <v>3.06</v>
+        <v>3.08</v>
       </c>
       <c r="CE5" t="n">
         <v>1.33</v>
@@ -2849,13 +2849,13 @@
         <v>1.68</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CL5" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="CN5" t="n">
         <v>1.84</v>
@@ -2867,7 +2867,7 @@
         <v>1.76</v>
       </c>
       <c r="CQ5" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="CR5" t="n">
         <v>1.38</v>
@@ -2885,7 +2885,7 @@
         <v>2.23</v>
       </c>
       <c r="CW5" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CX5" t="n">
         <v>1.56</v>
@@ -2897,91 +2897,91 @@
         <v>2.37</v>
       </c>
       <c r="DA5" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="DB5" t="n">
         <v>1.25</v>
       </c>
       <c r="DC5" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="DD5" t="n">
-        <v>2.99</v>
+        <v>3.01</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DF5" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="DG5" t="n">
-        <v>2.94</v>
+        <v>3.06</v>
       </c>
       <c r="DH5" t="n">
-        <v>101.13</v>
+        <v>100.94</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.19</v>
+        <v>0.17</v>
       </c>
       <c r="DJ5" t="n">
-        <v>3.12</v>
+        <v>3.29</v>
       </c>
       <c r="DK5" t="n">
-        <v>6.44</v>
+        <v>6.59</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="DM5" t="n">
-        <v>58.94</v>
+        <v>58.76</v>
       </c>
       <c r="DN5" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="DO5" t="n">
-        <v>3.5</v>
+        <v>3.53</v>
       </c>
       <c r="DP5" t="n">
-        <v>13</v>
+        <v>13.11</v>
       </c>
       <c r="DQ5" t="n">
-        <v>14.5</v>
+        <v>14.41</v>
       </c>
       <c r="DR5" t="n">
-        <v>5.56</v>
+        <v>5.41</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>54.75</v>
+        <v>54.82</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DX5" t="n">
-        <v>14.5</v>
+        <v>14.65</v>
       </c>
       <c r="DY5" t="n">
-        <v>9.43</v>
+        <v>9.58</v>
       </c>
       <c r="DZ5" t="n">
         <v>5.06</v>
       </c>
       <c r="EA5" t="n">
-        <v>18.94</v>
+        <v>19.06</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="EC5" t="n">
-        <v>2.75</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="6">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C6" t="n">
         <v>8</v>
       </c>
       <c r="D6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E6" t="n">
         <v>0.25</v>
@@ -3081,139 +3081,139 @@
         <v>2.88</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AI6" t="n">
-        <v>80.12</v>
+        <v>79.67</v>
       </c>
       <c r="AJ6" t="n">
         <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="AL6" t="n">
-        <v>3.25</v>
+        <v>3.11</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AN6" t="n">
-        <v>34</v>
+        <v>33.78</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="AQ6" t="n">
-        <v>12.62</v>
+        <v>12.56</v>
       </c>
       <c r="AR6" t="n">
-        <v>13.75</v>
+        <v>13.33</v>
       </c>
       <c r="AS6" t="n">
-        <v>9.380000000000001</v>
+        <v>9.67</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AX6" t="n">
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>47.75</v>
+        <v>47.22</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="BA6" t="n">
-        <v>8.75</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="BB6" t="n">
-        <v>6.62</v>
+        <v>6.56</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="BD6" t="n">
-        <v>19.75</v>
+        <v>20.11</v>
       </c>
       <c r="BE6" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="BF6" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="BH6" t="n">
-        <v>9.06</v>
+        <v>8.94</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="BJ6" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.38</v>
+        <v>0.41</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.38</v>
+        <v>0.35</v>
       </c>
       <c r="BN6" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="BP6" t="n">
-        <v>3.44</v>
+        <v>3.47</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.25</v>
+        <v>5.12</v>
       </c>
       <c r="BR6" t="n">
-        <v>87.5</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="BS6" t="n">
-        <v>56.25</v>
+        <v>58.82</v>
       </c>
       <c r="BT6" t="n">
-        <v>43.75</v>
+        <v>41.18</v>
       </c>
       <c r="BU6" t="n">
-        <v>18.75</v>
+        <v>17.65</v>
       </c>
       <c r="BV6" t="n">
-        <v>18.75</v>
+        <v>17.65</v>
       </c>
       <c r="BW6" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BX6" t="n">
-        <v>37.5</v>
+        <v>41.18</v>
       </c>
       <c r="BY6" t="n">
         <v>2.4</v>
@@ -3222,22 +3222,22 @@
         <v>2.6</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.26</v>
+        <v>3.25</v>
       </c>
       <c r="CB6" t="n">
         <v>3.36</v>
       </c>
       <c r="CC6" t="n">
-        <v>4.26</v>
+        <v>4.21</v>
       </c>
       <c r="CD6" t="n">
-        <v>4.67</v>
+        <v>4.59</v>
       </c>
       <c r="CE6" t="n">
         <v>1.44</v>
       </c>
       <c r="CF6" t="n">
-        <v>3.02</v>
+        <v>3.03</v>
       </c>
       <c r="CG6" t="n">
         <v>2.66</v>
@@ -3249,13 +3249,13 @@
         <v>1.84</v>
       </c>
       <c r="CJ6" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CK6" t="n">
         <v>1.65</v>
       </c>
       <c r="CL6" t="n">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="CM6" t="n">
         <v>2.11</v>
@@ -3264,31 +3264,31 @@
         <v>1.67</v>
       </c>
       <c r="CO6" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CP6" t="n">
         <v>2.19</v>
       </c>
       <c r="CQ6" t="n">
-        <v>3.91</v>
+        <v>3.93</v>
       </c>
       <c r="CR6" t="n">
         <v>1.46</v>
       </c>
       <c r="CS6" t="n">
-        <v>3.1</v>
+        <v>3.13</v>
       </c>
       <c r="CT6" t="n">
-        <v>2.84</v>
+        <v>2.83</v>
       </c>
       <c r="CU6" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CV6" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="CW6" t="n">
         <v>1.94</v>
-      </c>
-      <c r="CW6" t="n">
-        <v>1.93</v>
       </c>
       <c r="CX6" t="n">
         <v>1.67</v>
@@ -3309,82 +3309,82 @@
         <v>2.22</v>
       </c>
       <c r="DD6" t="n">
-        <v>4.05</v>
+        <v>4.06</v>
       </c>
       <c r="DE6" t="n">
         <v>0.18</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.44</v>
+        <v>2.41</v>
       </c>
       <c r="DH6" t="n">
-        <v>89.75</v>
+        <v>88.95</v>
       </c>
       <c r="DI6" t="n">
         <v>0.12</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.69</v>
+        <v>2.65</v>
       </c>
       <c r="DK6" t="n">
-        <v>4.56</v>
+        <v>4.41</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.38</v>
+        <v>0.35</v>
       </c>
       <c r="DM6" t="n">
-        <v>44.62</v>
+        <v>43.88</v>
       </c>
       <c r="DN6" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="DO6" t="n">
-        <v>1.87</v>
+        <v>1.76</v>
       </c>
       <c r="DP6" t="n">
-        <v>13.62</v>
+        <v>13.53</v>
       </c>
       <c r="DQ6" t="n">
-        <v>13.62</v>
+        <v>13.41</v>
       </c>
       <c r="DR6" t="n">
-        <v>7.32</v>
+        <v>7.59</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>51.62</v>
+        <v>51.12</v>
       </c>
       <c r="DW6" t="n">
         <v>0.12</v>
       </c>
       <c r="DX6" t="n">
-        <v>10.25</v>
+        <v>10.18</v>
       </c>
       <c r="DY6" t="n">
-        <v>7</v>
+        <v>6.95</v>
       </c>
       <c r="DZ6" t="n">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="EA6" t="n">
-        <v>20.5</v>
+        <v>20.65</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
     </row>
     <row r="7">
@@ -3394,13 +3394,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C7" t="n">
         <v>8</v>
       </c>
       <c r="D7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -3484,139 +3484,139 @@
         <v>1.12</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AH7" t="n">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="AI7" t="n">
-        <v>75.25</v>
+        <v>74.22</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AL7" t="n">
-        <v>3.38</v>
+        <v>3.44</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AN7" t="n">
-        <v>33.25</v>
+        <v>32</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AQ7" t="n">
-        <v>12.88</v>
+        <v>12.33</v>
       </c>
       <c r="AR7" t="n">
-        <v>12.25</v>
+        <v>12.11</v>
       </c>
       <c r="AS7" t="n">
-        <v>10</v>
+        <v>10.44</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="AX7" t="n">
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>43.25</v>
+        <v>43</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="BA7" t="n">
         <v>12</v>
       </c>
       <c r="BB7" t="n">
-        <v>6.75</v>
+        <v>7</v>
       </c>
       <c r="BC7" t="n">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="BD7" t="n">
-        <v>16.62</v>
+        <v>17.67</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.62</v>
+        <v>1.78</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="BH7" t="n">
-        <v>8.75</v>
+        <v>8.94</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.59</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="BN7" t="n">
         <v>1.06</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="BP7" t="n">
-        <v>3.69</v>
+        <v>3.71</v>
       </c>
       <c r="BQ7" t="n">
-        <v>5.06</v>
+        <v>5.24</v>
       </c>
       <c r="BR7" t="n">
-        <v>87.5</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="BS7" t="n">
-        <v>43.75</v>
+        <v>47.06</v>
       </c>
       <c r="BT7" t="n">
-        <v>43.75</v>
+        <v>47.06</v>
       </c>
       <c r="BU7" t="n">
-        <v>31.25</v>
+        <v>29.41</v>
       </c>
       <c r="BV7" t="n">
-        <v>25</v>
+        <v>23.53</v>
       </c>
       <c r="BW7" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BX7" t="n">
-        <v>31.25</v>
+        <v>35.29</v>
       </c>
       <c r="BY7" t="n">
         <v>2.66</v>
@@ -3625,22 +3625,22 @@
         <v>2.8</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.4</v>
+        <v>3.39</v>
       </c>
       <c r="CB7" t="n">
         <v>3.54</v>
       </c>
       <c r="CC7" t="n">
-        <v>4.98</v>
+        <v>4.96</v>
       </c>
       <c r="CD7" t="n">
-        <v>5.54</v>
+        <v>5.55</v>
       </c>
       <c r="CE7" t="n">
         <v>1.42</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.92</v>
+        <v>2.91</v>
       </c>
       <c r="CG7" t="n">
         <v>2.79</v>
@@ -3649,10 +3649,10 @@
         <v>1.38</v>
       </c>
       <c r="CI7" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CJ7" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CK7" t="n">
         <v>1.58</v>
@@ -3664,130 +3664,130 @@
         <v>2.27</v>
       </c>
       <c r="CN7" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CO7" t="n">
         <v>1.31</v>
       </c>
       <c r="CP7" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="CQ7" t="n">
-        <v>3.58</v>
+        <v>3.59</v>
       </c>
       <c r="CR7" t="n">
         <v>1.45</v>
       </c>
       <c r="CS7" t="n">
-        <v>3.11</v>
+        <v>3.13</v>
       </c>
       <c r="CT7" t="n">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="CU7" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CV7" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CW7" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CX7" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CY7" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="CZ7" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="DA7" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="DB7" t="n">
         <v>1.35</v>
       </c>
       <c r="DC7" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="DD7" t="n">
-        <v>3.75</v>
+        <v>3.78</v>
       </c>
       <c r="DE7" t="n">
         <v>0.12</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="DG7" t="n">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="DH7" t="n">
-        <v>82.62</v>
+        <v>81.65000000000001</v>
       </c>
       <c r="DI7" t="n">
         <v>0.12</v>
       </c>
       <c r="DJ7" t="n">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="DK7" t="n">
         <v>4.06</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.38</v>
+        <v>0.35</v>
       </c>
       <c r="DM7" t="n">
-        <v>36.75</v>
+        <v>35.88</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="DO7" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="DP7" t="n">
-        <v>12.94</v>
+        <v>12.65</v>
       </c>
       <c r="DQ7" t="n">
-        <v>12.75</v>
+        <v>12.65</v>
       </c>
       <c r="DR7" t="n">
-        <v>9.119999999999999</v>
+        <v>9.41</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.06</v>
+        <v>0.12</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.06</v>
+        <v>0.12</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>47.38</v>
+        <v>47</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DX7" t="n">
-        <v>11.19</v>
+        <v>11.24</v>
       </c>
       <c r="DY7" t="n">
-        <v>7.06</v>
+        <v>7.18</v>
       </c>
       <c r="DZ7" t="n">
-        <v>4.12</v>
+        <v>4.06</v>
       </c>
       <c r="EA7" t="n">
-        <v>17.87</v>
+        <v>18.35</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="EC7" t="n">
-        <v>1.37</v>
+        <v>1.47</v>
       </c>
     </row>
     <row r="8">
@@ -3797,61 +3797,61 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D8" t="n">
         <v>8</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="F8" t="n">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="G8" t="n">
-        <v>3.25</v>
+        <v>3.33</v>
       </c>
       <c r="H8" t="n">
-        <v>99.25</v>
+        <v>95.11</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>2.88</v>
+        <v>3.22</v>
       </c>
       <c r="K8" t="n">
-        <v>5.88</v>
+        <v>5.78</v>
       </c>
       <c r="L8" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="M8" t="n">
-        <v>52.62</v>
+        <v>50.33</v>
       </c>
       <c r="N8" t="n">
-        <v>0.62</v>
+        <v>1</v>
       </c>
       <c r="O8" t="n">
-        <v>2.62</v>
+        <v>2.44</v>
       </c>
       <c r="P8" t="n">
-        <v>13.38</v>
+        <v>14.33</v>
       </c>
       <c r="Q8" t="n">
-        <v>13.62</v>
+        <v>13.44</v>
       </c>
       <c r="R8" t="n">
-        <v>7.25</v>
+        <v>7.11</v>
       </c>
       <c r="S8" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="T8" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
@@ -3863,28 +3863,28 @@
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>53.38</v>
+        <v>50.78</v>
       </c>
       <c r="Y8" t="n">
         <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>11.5</v>
+        <v>11.89</v>
       </c>
       <c r="AA8" t="n">
-        <v>8.25</v>
+        <v>8.44</v>
       </c>
       <c r="AB8" t="n">
-        <v>3.25</v>
+        <v>3.44</v>
       </c>
       <c r="AC8" t="n">
-        <v>19.75</v>
+        <v>19.11</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.88</v>
+        <v>3.22</v>
       </c>
       <c r="AF8" t="n">
         <v>0.12</v>
@@ -3968,67 +3968,67 @@
         <v>2.38</v>
       </c>
       <c r="BG8" t="n">
-        <v>1.81</v>
+        <v>2</v>
       </c>
       <c r="BH8" t="n">
-        <v>9.94</v>
+        <v>10.06</v>
       </c>
       <c r="BI8" t="n">
-        <v>1.81</v>
+        <v>2</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.44</v>
+        <v>0.53</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.38</v>
+        <v>0.41</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.44</v>
+        <v>0.53</v>
       </c>
       <c r="BN8" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.56</v>
+        <v>4.65</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.38</v>
+        <v>5.41</v>
       </c>
       <c r="BR8" t="n">
-        <v>75</v>
+        <v>76.47</v>
       </c>
       <c r="BS8" t="n">
-        <v>43.75</v>
+        <v>47.06</v>
       </c>
       <c r="BT8" t="n">
-        <v>37.5</v>
+        <v>41.18</v>
       </c>
       <c r="BU8" t="n">
-        <v>12.5</v>
+        <v>17.65</v>
       </c>
       <c r="BV8" t="n">
-        <v>6.25</v>
+        <v>11.76</v>
       </c>
       <c r="BW8" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BX8" t="n">
-        <v>37.5</v>
+        <v>41.18</v>
       </c>
       <c r="BY8" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="BZ8" t="n">
-        <v>2.27</v>
+        <v>2.37</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.1</v>
+        <v>3.11</v>
       </c>
       <c r="CB8" t="n">
         <v>3.27</v>
@@ -4040,124 +4040,124 @@
         <v>4.15</v>
       </c>
       <c r="CE8" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CF8" t="n">
-        <v>3.22</v>
+        <v>3.18</v>
       </c>
       <c r="CG8" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="CH8" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="CI8" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="CJ8" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="CK8" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="CL8" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="CM8" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="CN8" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="CO8" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="CP8" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="CQ8" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="CR8" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="CS8" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="CT8" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="CU8" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="CV8" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="CW8" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="CX8" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="CY8" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="CZ8" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="DA8" t="n">
         <v>1.76</v>
       </c>
-      <c r="CJ8" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="CK8" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="CL8" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="CM8" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="CN8" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="CO8" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="CP8" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="CQ8" t="n">
-        <v>4.24</v>
-      </c>
-      <c r="CR8" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="CS8" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="CT8" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="CU8" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="CV8" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="CW8" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="CX8" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="CY8" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="CZ8" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="DA8" t="n">
-        <v>1.75</v>
-      </c>
       <c r="DB8" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="DC8" t="n">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="DD8" t="n">
-        <v>4.48</v>
+        <v>4.41</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="DF8" t="n">
         <v>2.12</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.68</v>
+        <v>2.76</v>
       </c>
       <c r="DH8" t="n">
-        <v>90.81999999999999</v>
+        <v>89.12</v>
       </c>
       <c r="DI8" t="n">
         <v>0</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.63</v>
+        <v>2.82</v>
       </c>
       <c r="DK8" t="n">
         <v>5</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DM8" t="n">
-        <v>40.25</v>
+        <v>39.77</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.5</v>
+        <v>0.71</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.31</v>
+        <v>2.23</v>
       </c>
       <c r="DP8" t="n">
-        <v>14.38</v>
+        <v>14.82</v>
       </c>
       <c r="DQ8" t="n">
-        <v>13.56</v>
+        <v>13.47</v>
       </c>
       <c r="DR8" t="n">
-        <v>9.07</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="DS8" t="n">
         <v>0</v>
@@ -4169,28 +4169,28 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>47.44</v>
+        <v>46.41</v>
       </c>
       <c r="DW8" t="n">
         <v>0</v>
       </c>
       <c r="DX8" t="n">
-        <v>9.75</v>
+        <v>10.06</v>
       </c>
       <c r="DY8" t="n">
-        <v>6.88</v>
+        <v>7.06</v>
       </c>
       <c r="DZ8" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="EA8" t="n">
-        <v>20</v>
+        <v>19.65</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="EC8" t="n">
-        <v>2.63</v>
+        <v>2.82</v>
       </c>
     </row>
     <row r="9">
@@ -4200,13 +4200,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C9" t="n">
         <v>8</v>
       </c>
       <c r="D9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E9" t="n">
         <v>0.12</v>
@@ -4290,52 +4290,52 @@
         <v>2.75</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="AI9" t="n">
-        <v>91.5</v>
+        <v>91.67</v>
       </c>
       <c r="AJ9" t="n">
-        <v>-0.12</v>
+        <v>-0.11</v>
       </c>
       <c r="AK9" t="n">
-        <v>3.5</v>
+        <v>3.22</v>
       </c>
       <c r="AL9" t="n">
-        <v>4.25</v>
+        <v>4.33</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AN9" t="n">
-        <v>40</v>
+        <v>40.22</v>
       </c>
       <c r="AO9" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="AQ9" t="n">
-        <v>16.88</v>
+        <v>16.56</v>
       </c>
       <c r="AR9" t="n">
-        <v>14.62</v>
+        <v>14.78</v>
       </c>
       <c r="AS9" t="n">
-        <v>7.12</v>
+        <v>6.89</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AV9" t="n">
         <v>0</v>
@@ -4347,73 +4347,73 @@
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>52.25</v>
+        <v>53.11</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="BA9" t="n">
-        <v>12.75</v>
+        <v>13</v>
       </c>
       <c r="BB9" t="n">
-        <v>8.119999999999999</v>
+        <v>8.56</v>
       </c>
       <c r="BC9" t="n">
-        <v>4.62</v>
+        <v>4.44</v>
       </c>
       <c r="BD9" t="n">
-        <v>22.88</v>
+        <v>23.22</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="BF9" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.69</v>
+        <v>2.53</v>
       </c>
       <c r="BH9" t="n">
-        <v>9.31</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.69</v>
+        <v>2.53</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.44</v>
+        <v>0.41</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.38</v>
+        <v>4.41</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.94</v>
+        <v>4.88</v>
       </c>
       <c r="BR9" t="n">
-        <v>93.75</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="BS9" t="n">
-        <v>81.25</v>
+        <v>76.47</v>
       </c>
       <c r="BT9" t="n">
-        <v>56.25</v>
+        <v>52.94</v>
       </c>
       <c r="BU9" t="n">
-        <v>37.5</v>
+        <v>35.29</v>
       </c>
       <c r="BV9" t="n">
         <v>0</v>
@@ -4422,7 +4422,7 @@
         <v>0</v>
       </c>
       <c r="BX9" t="n">
-        <v>75</v>
+        <v>70.59</v>
       </c>
       <c r="BY9" t="n">
         <v>2.11</v>
@@ -4431,25 +4431,25 @@
         <v>2.12</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.28</v>
+        <v>3.26</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.43</v>
+        <v>3.41</v>
       </c>
       <c r="CC9" t="n">
-        <v>3.08</v>
+        <v>3.05</v>
       </c>
       <c r="CD9" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="CE9" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.73</v>
+        <v>2.76</v>
       </c>
       <c r="CG9" t="n">
-        <v>2.92</v>
+        <v>2.91</v>
       </c>
       <c r="CH9" t="n">
         <v>1.41</v>
@@ -4461,34 +4461,34 @@
         <v>1.72</v>
       </c>
       <c r="CK9" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="CL9" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CM9" t="n">
         <v>2.4</v>
       </c>
       <c r="CN9" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CO9" t="n">
         <v>1.27</v>
       </c>
       <c r="CP9" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="CQ9" t="n">
-        <v>3.16</v>
+        <v>3.19</v>
       </c>
       <c r="CR9" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CS9" t="n">
-        <v>2.98</v>
+        <v>2.99</v>
       </c>
       <c r="CT9" t="n">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="CU9" t="n">
         <v>1.42</v>
@@ -4497,103 +4497,103 @@
         <v>2.16</v>
       </c>
       <c r="CW9" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CX9" t="n">
         <v>1.56</v>
       </c>
       <c r="CY9" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="CZ9" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="DA9" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="DB9" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="DC9" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="DD9" t="n">
-        <v>3.36</v>
+        <v>3.39</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="DG9" t="n">
-        <v>2.56</v>
+        <v>2.59</v>
       </c>
       <c r="DH9" t="n">
-        <v>97.06</v>
+        <v>96.81999999999999</v>
       </c>
       <c r="DI9" t="n">
         <v>-0.06</v>
       </c>
       <c r="DJ9" t="n">
-        <v>3.25</v>
+        <v>3.12</v>
       </c>
       <c r="DK9" t="n">
-        <v>4.69</v>
+        <v>4.7</v>
       </c>
       <c r="DL9" t="n">
         <v>0.18</v>
       </c>
       <c r="DM9" t="n">
-        <v>47.25</v>
+        <v>46.94</v>
       </c>
       <c r="DN9" t="n">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="DO9" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="DP9" t="n">
-        <v>16.25</v>
+        <v>16.12</v>
       </c>
       <c r="DQ9" t="n">
-        <v>14.68</v>
+        <v>14.77</v>
       </c>
       <c r="DR9" t="n">
-        <v>6.25</v>
+        <v>6.18</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>55.06</v>
+        <v>55.35</v>
       </c>
       <c r="DW9" t="n">
         <v>0.18</v>
       </c>
       <c r="DX9" t="n">
-        <v>14.75</v>
+        <v>14.76</v>
       </c>
       <c r="DY9" t="n">
-        <v>9.869999999999999</v>
+        <v>10</v>
       </c>
       <c r="DZ9" t="n">
-        <v>4.87</v>
+        <v>4.76</v>
       </c>
       <c r="EA9" t="n">
-        <v>22.13</v>
+        <v>22.35</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="EC9" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
     </row>
     <row r="10">
@@ -4603,94 +4603,94 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D10" t="n">
         <v>9</v>
       </c>
       <c r="E10" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="F10" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="G10" t="n">
-        <v>2.29</v>
+        <v>2.12</v>
       </c>
       <c r="H10" t="n">
-        <v>98.14</v>
+        <v>93.88</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>2.29</v>
+        <v>2.62</v>
       </c>
       <c r="K10" t="n">
-        <v>3.86</v>
+        <v>3.75</v>
       </c>
       <c r="L10" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="M10" t="n">
-        <v>44.29</v>
+        <v>41.88</v>
       </c>
       <c r="N10" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="O10" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="P10" t="n">
-        <v>12.86</v>
+        <v>12.88</v>
       </c>
       <c r="Q10" t="n">
-        <v>12.43</v>
+        <v>12.75</v>
       </c>
       <c r="R10" t="n">
-        <v>6.57</v>
+        <v>7</v>
       </c>
       <c r="S10" t="n">
-        <v>0.43</v>
+        <v>0.75</v>
       </c>
       <c r="T10" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="U10" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="V10" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>52.57</v>
+        <v>51.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="Z10" t="n">
-        <v>12.86</v>
+        <v>12</v>
       </c>
       <c r="AA10" t="n">
-        <v>8.289999999999999</v>
+        <v>7.62</v>
       </c>
       <c r="AB10" t="n">
-        <v>4.57</v>
+        <v>4.38</v>
       </c>
       <c r="AC10" t="n">
-        <v>18.71</v>
+        <v>18.75</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.46</v>
+        <v>1.37</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="AF10" t="n">
         <v>0</v>
@@ -4774,67 +4774,67 @@
         <v>2.67</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.81</v>
+        <v>2.88</v>
       </c>
       <c r="BH10" t="n">
-        <v>8.619999999999999</v>
+        <v>8.82</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.81</v>
+        <v>2.88</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="BP10" t="n">
-        <v>4.06</v>
+        <v>4.18</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.56</v>
+        <v>4.65</v>
       </c>
       <c r="BR10" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BS10" t="n">
-        <v>87.5</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="BT10" t="n">
-        <v>56.25</v>
+        <v>58.82</v>
       </c>
       <c r="BU10" t="n">
-        <v>31.25</v>
+        <v>35.29</v>
       </c>
       <c r="BV10" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BW10" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BX10" t="n">
-        <v>56.25</v>
+        <v>58.82</v>
       </c>
       <c r="BY10" t="n">
-        <v>1.89</v>
+        <v>1.96</v>
       </c>
       <c r="BZ10" t="n">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.22</v>
+        <v>3.21</v>
       </c>
       <c r="CB10" t="n">
         <v>3.37</v>
@@ -4849,40 +4849,40 @@
         <v>1.41</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.93</v>
+        <v>2.91</v>
       </c>
       <c r="CG10" t="n">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CI10" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CJ10" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CK10" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CL10" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="CM10" t="n">
         <v>2.14</v>
       </c>
       <c r="CN10" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CO10" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="CP10" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="CQ10" t="n">
-        <v>3.54</v>
+        <v>3.5</v>
       </c>
       <c r="CR10" t="n">
         <v>1.46</v>
@@ -4897,106 +4897,106 @@
         <v>1.39</v>
       </c>
       <c r="CV10" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="CW10" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CX10" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CY10" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="CZ10" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="DA10" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="DB10" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="DC10" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="DD10" t="n">
-        <v>3.73</v>
+        <v>3.72</v>
       </c>
       <c r="DE10" t="n">
         <v>0.06</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="DG10" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="DH10" t="n">
-        <v>86.87</v>
+        <v>85.53</v>
       </c>
       <c r="DI10" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.5</v>
+        <v>4.41</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.38</v>
+        <v>0.41</v>
       </c>
       <c r="DM10" t="n">
-        <v>38.25</v>
+        <v>37.48</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="DP10" t="n">
-        <v>11.94</v>
+        <v>12</v>
       </c>
       <c r="DQ10" t="n">
-        <v>12.19</v>
+        <v>12.35</v>
       </c>
       <c r="DR10" t="n">
-        <v>7.62</v>
+        <v>7.76</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>50.5</v>
+        <v>50.12</v>
       </c>
       <c r="DW10" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="DX10" t="n">
-        <v>12.62</v>
+        <v>12.23</v>
       </c>
       <c r="DY10" t="n">
-        <v>7.75</v>
+        <v>7.47</v>
       </c>
       <c r="DZ10" t="n">
-        <v>4.87</v>
+        <v>4.77</v>
       </c>
       <c r="EA10" t="n">
-        <v>16.18</v>
+        <v>16.35</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="EC10" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
     </row>
     <row r="11">
@@ -5006,10 +5006,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D11" t="n">
         <v>9</v>
@@ -5018,49 +5018,49 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="G11" t="n">
-        <v>3.86</v>
+        <v>4.12</v>
       </c>
       <c r="H11" t="n">
-        <v>108.14</v>
+        <v>105.12</v>
       </c>
       <c r="I11" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="J11" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="K11" t="n">
-        <v>5.57</v>
+        <v>6.12</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="M11" t="n">
-        <v>48.29</v>
+        <v>48.75</v>
       </c>
       <c r="N11" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="O11" t="n">
-        <v>1.71</v>
+        <v>2</v>
       </c>
       <c r="P11" t="n">
-        <v>14.14</v>
+        <v>14.12</v>
       </c>
       <c r="Q11" t="n">
-        <v>15.29</v>
+        <v>15</v>
       </c>
       <c r="R11" t="n">
-        <v>8.43</v>
+        <v>8.5</v>
       </c>
       <c r="S11" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="T11" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
@@ -5072,28 +5072,28 @@
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>57.71</v>
+        <v>58</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="Z11" t="n">
-        <v>13.14</v>
+        <v>13.88</v>
       </c>
       <c r="AA11" t="n">
-        <v>8.289999999999999</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="AB11" t="n">
-        <v>4.86</v>
+        <v>5</v>
       </c>
       <c r="AC11" t="n">
-        <v>19.29</v>
+        <v>19.25</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="AE11" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AF11" t="n">
         <v>0.11</v>
@@ -5177,67 +5177,67 @@
         <v>2.89</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="BH11" t="n">
-        <v>9.380000000000001</v>
+        <v>9.65</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.44</v>
+        <v>0.41</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.38</v>
+        <v>0.35</v>
       </c>
       <c r="BL11" t="n">
         <v>1.06</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.75</v>
+        <v>0.82</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.81</v>
+        <v>1.88</v>
       </c>
       <c r="BO11" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.06</v>
+        <v>4.18</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.25</v>
+        <v>5.41</v>
       </c>
       <c r="BR11" t="n">
-        <v>87.5</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="BS11" t="n">
-        <v>81.25</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="BT11" t="n">
-        <v>56.25</v>
+        <v>58.82</v>
       </c>
       <c r="BU11" t="n">
-        <v>31.25</v>
+        <v>29.41</v>
       </c>
       <c r="BV11" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BW11" t="n">
         <v>0</v>
       </c>
       <c r="BX11" t="n">
-        <v>68.75</v>
+        <v>70.59</v>
       </c>
       <c r="BY11" t="n">
-        <v>2.19</v>
+        <v>2.27</v>
       </c>
       <c r="BZ11" t="n">
-        <v>2.25</v>
+        <v>2.37</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.25</v>
+        <v>3.27</v>
       </c>
       <c r="CB11" t="n">
         <v>3.42</v>
@@ -5252,121 +5252,121 @@
         <v>1.42</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.95</v>
+        <v>2.93</v>
       </c>
       <c r="CG11" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="CH11" t="n">
         <v>1.36</v>
       </c>
       <c r="CI11" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="CJ11" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CK11" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CL11" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="CN11" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CO11" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="CP11" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CQ11" t="n">
-        <v>3.61</v>
+        <v>3.58</v>
       </c>
       <c r="CR11" t="n">
         <v>1.45</v>
       </c>
       <c r="CS11" t="n">
-        <v>3.07</v>
+        <v>3.06</v>
       </c>
       <c r="CT11" t="n">
-        <v>2.87</v>
+        <v>2.88</v>
       </c>
       <c r="CU11" t="n">
         <v>1.4</v>
       </c>
       <c r="CV11" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="CW11" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CX11" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CY11" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="CZ11" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="DA11" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="DB11" t="n">
         <v>1.35</v>
       </c>
       <c r="DC11" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="DD11" t="n">
-        <v>3.8</v>
+        <v>3.76</v>
       </c>
       <c r="DE11" t="n">
         <v>0.06</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="DG11" t="n">
-        <v>3.06</v>
+        <v>3.23</v>
       </c>
       <c r="DH11" t="n">
-        <v>99.87</v>
+        <v>98.94</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.69</v>
+        <v>2.59</v>
       </c>
       <c r="DK11" t="n">
-        <v>4.69</v>
+        <v>5</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.12</v>
+        <v>0.17</v>
       </c>
       <c r="DM11" t="n">
-        <v>43.38</v>
+        <v>43.88</v>
       </c>
       <c r="DN11" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="DO11" t="n">
-        <v>1.63</v>
+        <v>1.77</v>
       </c>
       <c r="DP11" t="n">
         <v>14</v>
       </c>
       <c r="DQ11" t="n">
-        <v>15</v>
+        <v>14.88</v>
       </c>
       <c r="DR11" t="n">
-        <v>7.69</v>
+        <v>7.76</v>
       </c>
       <c r="DS11" t="n">
         <v>0.06</v>
@@ -5378,28 +5378,28 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>56.43</v>
+        <v>56.64</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DX11" t="n">
-        <v>13.81</v>
+        <v>14.12</v>
       </c>
       <c r="DY11" t="n">
-        <v>9.19</v>
+        <v>9.41</v>
       </c>
       <c r="DZ11" t="n">
-        <v>4.62</v>
+        <v>4.7</v>
       </c>
       <c r="EA11" t="n">
-        <v>18.5</v>
+        <v>18.53</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
     </row>
     <row r="12">
@@ -5409,61 +5409,61 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D12" t="n">
         <v>8</v>
       </c>
       <c r="E12" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="F12" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="G12" t="n">
-        <v>3.38</v>
+        <v>3.11</v>
       </c>
       <c r="H12" t="n">
-        <v>90.75</v>
+        <v>92.56</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="K12" t="n">
-        <v>6</v>
+        <v>5.89</v>
       </c>
       <c r="L12" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="M12" t="n">
-        <v>44.25</v>
+        <v>44.89</v>
       </c>
       <c r="N12" t="n">
-        <v>0.62</v>
+        <v>0.78</v>
       </c>
       <c r="O12" t="n">
-        <v>2.62</v>
+        <v>2.78</v>
       </c>
       <c r="P12" t="n">
-        <v>12.5</v>
+        <v>12.22</v>
       </c>
       <c r="Q12" t="n">
-        <v>16.25</v>
+        <v>15.78</v>
       </c>
       <c r="R12" t="n">
-        <v>7.38</v>
+        <v>7.33</v>
       </c>
       <c r="S12" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="T12" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="U12" t="n">
         <v>0</v>
@@ -5475,28 +5475,28 @@
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>51.25</v>
+        <v>51.89</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="Z12" t="n">
-        <v>14.75</v>
+        <v>14.78</v>
       </c>
       <c r="AA12" t="n">
-        <v>10.88</v>
+        <v>11</v>
       </c>
       <c r="AB12" t="n">
-        <v>3.88</v>
+        <v>3.78</v>
       </c>
       <c r="AC12" t="n">
-        <v>22.5</v>
+        <v>22.67</v>
       </c>
       <c r="AD12" t="n">
         <v>1.52</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>
@@ -5580,67 +5580,67 @@
         <v>2.62</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.119999999999999</v>
+        <v>9</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="BP12" t="n">
-        <v>3.75</v>
+        <v>3.76</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.38</v>
+        <v>5.24</v>
       </c>
       <c r="BR12" t="n">
-        <v>81.25</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="BS12" t="n">
-        <v>68.75</v>
+        <v>70.59</v>
       </c>
       <c r="BT12" t="n">
-        <v>50</v>
+        <v>47.06</v>
       </c>
       <c r="BU12" t="n">
-        <v>31.25</v>
+        <v>29.41</v>
       </c>
       <c r="BV12" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BW12" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BX12" t="n">
-        <v>56.25</v>
+        <v>58.82</v>
       </c>
       <c r="BY12" t="n">
-        <v>2.14</v>
+        <v>2.09</v>
       </c>
       <c r="BZ12" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="CB12" t="n">
         <v>3.27</v>
@@ -5670,13 +5670,13 @@
         <v>1.93</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="CL12" t="n">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="CN12" t="n">
         <v>1.77</v>
@@ -5685,16 +5685,16 @@
         <v>1.38</v>
       </c>
       <c r="CP12" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="CQ12" t="n">
-        <v>3.96</v>
+        <v>3.98</v>
       </c>
       <c r="CR12" t="n">
         <v>1.5</v>
       </c>
       <c r="CS12" t="n">
-        <v>3.23</v>
+        <v>3.25</v>
       </c>
       <c r="CT12" t="n">
         <v>2.7</v>
@@ -5733,43 +5733,43 @@
         <v>0.12</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.19</v>
+        <v>2.12</v>
       </c>
       <c r="DH12" t="n">
-        <v>91.38</v>
+        <v>92.3</v>
       </c>
       <c r="DI12" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.44</v>
+        <v>2.41</v>
       </c>
       <c r="DK12" t="n">
-        <v>4.25</v>
+        <v>4.29</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.44</v>
+        <v>0.41</v>
       </c>
       <c r="DM12" t="n">
-        <v>40.56</v>
+        <v>41.12</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.75</v>
+        <v>0.83</v>
       </c>
       <c r="DO12" t="n">
-        <v>2.06</v>
+        <v>2.18</v>
       </c>
       <c r="DP12" t="n">
-        <v>13.69</v>
+        <v>13.47</v>
       </c>
       <c r="DQ12" t="n">
-        <v>15.43</v>
+        <v>15.23</v>
       </c>
       <c r="DR12" t="n">
-        <v>8.06</v>
+        <v>8</v>
       </c>
       <c r="DS12" t="n">
         <v>0</v>
@@ -5781,25 +5781,25 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>48.44</v>
+        <v>48.94</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DX12" t="n">
-        <v>12.32</v>
+        <v>12.47</v>
       </c>
       <c r="DY12" t="n">
-        <v>8.69</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="DZ12" t="n">
-        <v>3.63</v>
+        <v>3.59</v>
       </c>
       <c r="EA12" t="n">
-        <v>21.62</v>
+        <v>21.77</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="EC12" t="n">
         <v>2.12</v>
@@ -5812,61 +5812,61 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D13" t="n">
         <v>9</v>
       </c>
       <c r="E13" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="F13" t="n">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="G13" t="n">
-        <v>2.43</v>
+        <v>2.25</v>
       </c>
       <c r="H13" t="n">
-        <v>86.86</v>
+        <v>87.38</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>3.29</v>
+        <v>3.25</v>
       </c>
       <c r="K13" t="n">
-        <v>5.71</v>
+        <v>5.5</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="M13" t="n">
-        <v>41.57</v>
+        <v>42.62</v>
       </c>
       <c r="N13" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="O13" t="n">
-        <v>3.29</v>
+        <v>3.25</v>
       </c>
       <c r="P13" t="n">
-        <v>13.71</v>
+        <v>14.12</v>
       </c>
       <c r="Q13" t="n">
-        <v>16.43</v>
+        <v>16.12</v>
       </c>
       <c r="R13" t="n">
-        <v>7.57</v>
+        <v>7.75</v>
       </c>
       <c r="S13" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="T13" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -5878,28 +5878,28 @@
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>52</v>
+        <v>50.5</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="Z13" t="n">
-        <v>13.29</v>
+        <v>12.38</v>
       </c>
       <c r="AA13" t="n">
-        <v>8.289999999999999</v>
+        <v>7.75</v>
       </c>
       <c r="AB13" t="n">
-        <v>5</v>
+        <v>4.62</v>
       </c>
       <c r="AC13" t="n">
-        <v>22</v>
+        <v>22.75</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.49</v>
+        <v>1.42</v>
       </c>
       <c r="AE13" t="n">
-        <v>3.14</v>
+        <v>3.12</v>
       </c>
       <c r="AF13" t="n">
         <v>0</v>
@@ -5983,64 +5983,64 @@
         <v>3.11</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="BH13" t="n">
         <v>9</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.44</v>
+        <v>0.41</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.44</v>
+        <v>0.41</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="BO13" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="BP13" t="n">
-        <v>4.06</v>
+        <v>4.12</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4.31</v>
+        <v>4.29</v>
       </c>
       <c r="BR13" t="n">
-        <v>81.25</v>
+        <v>76.47</v>
       </c>
       <c r="BS13" t="n">
-        <v>68.75</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BT13" t="n">
-        <v>43.75</v>
+        <v>41.18</v>
       </c>
       <c r="BU13" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BV13" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BW13" t="n">
         <v>0</v>
       </c>
       <c r="BX13" t="n">
-        <v>50</v>
+        <v>47.06</v>
       </c>
       <c r="BY13" t="n">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="BZ13" t="n">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="CA13" t="n">
         <v>3</v>
@@ -6058,19 +6058,19 @@
         <v>1.5</v>
       </c>
       <c r="CF13" t="n">
-        <v>3.32</v>
+        <v>3.31</v>
       </c>
       <c r="CG13" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="CH13" t="n">
         <v>1.3</v>
       </c>
       <c r="CI13" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="CJ13" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="CK13" t="n">
         <v>1.61</v>
@@ -6082,97 +6082,97 @@
         <v>2.18</v>
       </c>
       <c r="CN13" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="CO13" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CP13" t="n">
-        <v>2.39</v>
+        <v>2.37</v>
       </c>
       <c r="CQ13" t="n">
-        <v>4.38</v>
+        <v>4.33</v>
       </c>
       <c r="CR13" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CS13" t="n">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="CT13" t="n">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="CU13" t="n">
         <v>1.34</v>
       </c>
       <c r="CV13" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CW13" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="CX13" t="n">
         <v>1.7</v>
       </c>
       <c r="CY13" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="CZ13" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="DA13" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="DB13" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="DC13" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="DD13" t="n">
-        <v>4.8</v>
+        <v>4.74</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DF13" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="DG13" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="DH13" t="n">
-        <v>83.63</v>
+        <v>84.06</v>
       </c>
       <c r="DI13" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ13" t="n">
-        <v>3.5</v>
+        <v>3.47</v>
       </c>
       <c r="DK13" t="n">
-        <v>4.5</v>
+        <v>4.47</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.25</v>
+        <v>0.29</v>
       </c>
       <c r="DM13" t="n">
-        <v>36.63</v>
+        <v>37.41</v>
       </c>
       <c r="DN13" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="DO13" t="n">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="DP13" t="n">
-        <v>13.06</v>
+        <v>13.29</v>
       </c>
       <c r="DQ13" t="n">
-        <v>14.94</v>
+        <v>14.88</v>
       </c>
       <c r="DR13" t="n">
-        <v>8.44</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="DS13" t="n">
         <v>0.12</v>
@@ -6184,28 +6184,28 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>49.81</v>
+        <v>49.23</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DX13" t="n">
-        <v>11.19</v>
+        <v>10.89</v>
       </c>
       <c r="DY13" t="n">
-        <v>6.69</v>
+        <v>6.53</v>
       </c>
       <c r="DZ13" t="n">
-        <v>4.5</v>
+        <v>4.35</v>
       </c>
       <c r="EA13" t="n">
-        <v>20.31</v>
+        <v>20.76</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="EC13" t="n">
-        <v>3.12</v>
+        <v>3.11</v>
       </c>
     </row>
     <row r="14">
@@ -7021,13 +7021,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C16" t="n">
         <v>9</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E16" t="n">
         <v>0.22</v>
@@ -7114,49 +7114,49 @@
         <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.71</v>
+        <v>2.62</v>
       </c>
       <c r="AI16" t="n">
-        <v>90.29000000000001</v>
+        <v>90.5</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="AK16" t="n">
-        <v>3.57</v>
+        <v>3.62</v>
       </c>
       <c r="AL16" t="n">
-        <v>4.57</v>
+        <v>4.88</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="AN16" t="n">
-        <v>36.57</v>
+        <v>37.88</v>
       </c>
       <c r="AO16" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.86</v>
+        <v>2.25</v>
       </c>
       <c r="AQ16" t="n">
-        <v>14</v>
+        <v>13.75</v>
       </c>
       <c r="AR16" t="n">
-        <v>16.43</v>
+        <v>17.12</v>
       </c>
       <c r="AS16" t="n">
         <v>8</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AU16" t="n">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="AV16" t="n">
         <v>0</v>
@@ -7168,82 +7168,82 @@
         <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>50.14</v>
+        <v>52.62</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="BA16" t="n">
-        <v>12.29</v>
+        <v>12.5</v>
       </c>
       <c r="BB16" t="n">
-        <v>7.29</v>
+        <v>7.12</v>
       </c>
       <c r="BC16" t="n">
-        <v>5</v>
+        <v>5.38</v>
       </c>
       <c r="BD16" t="n">
-        <v>17.29</v>
+        <v>17.25</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="BF16" t="n">
-        <v>3.14</v>
+        <v>3.25</v>
       </c>
       <c r="BG16" t="n">
-        <v>3.75</v>
+        <v>3.82</v>
       </c>
       <c r="BH16" t="n">
-        <v>11.25</v>
+        <v>11.29</v>
       </c>
       <c r="BI16" t="n">
-        <v>3.75</v>
+        <v>3.82</v>
       </c>
       <c r="BJ16" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.59</v>
       </c>
       <c r="BL16" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="BM16" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="BN16" t="n">
         <v>2.12</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="BP16" t="n">
-        <v>5.56</v>
+        <v>5.59</v>
       </c>
       <c r="BQ16" t="n">
-        <v>5.69</v>
+        <v>5.71</v>
       </c>
       <c r="BR16" t="n">
         <v>100</v>
       </c>
       <c r="BS16" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BT16" t="n">
-        <v>87.5</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="BU16" t="n">
-        <v>62.5</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BV16" t="n">
-        <v>25</v>
+        <v>29.41</v>
       </c>
       <c r="BW16" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BX16" t="n">
-        <v>75</v>
+        <v>76.47</v>
       </c>
       <c r="BY16" t="n">
         <v>1.84</v>
@@ -7252,16 +7252,16 @@
         <v>1.84</v>
       </c>
       <c r="CA16" t="n">
-        <v>3.65</v>
+        <v>3.63</v>
       </c>
       <c r="CB16" t="n">
-        <v>3.8</v>
+        <v>3.77</v>
       </c>
       <c r="CC16" t="n">
-        <v>3.14</v>
+        <v>3.03</v>
       </c>
       <c r="CD16" t="n">
-        <v>3.61</v>
+        <v>3.46</v>
       </c>
       <c r="CE16" t="n">
         <v>1.34</v>
@@ -7276,7 +7276,7 @@
         <v>1.47</v>
       </c>
       <c r="CI16" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="CJ16" t="n">
         <v>1.66</v>
@@ -7288,7 +7288,7 @@
         <v>1.91</v>
       </c>
       <c r="CM16" t="n">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="CN16" t="n">
         <v>1.91</v>
@@ -7297,28 +7297,28 @@
         <v>1.22</v>
       </c>
       <c r="CP16" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CQ16" t="n">
-        <v>2.77</v>
+        <v>2.8</v>
       </c>
       <c r="CR16" t="n">
         <v>1.38</v>
       </c>
       <c r="CS16" t="n">
-        <v>2.69</v>
+        <v>2.71</v>
       </c>
       <c r="CT16" t="n">
-        <v>3.16</v>
+        <v>3.15</v>
       </c>
       <c r="CU16" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CV16" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="CW16" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CX16" t="n">
         <v>1.53</v>
@@ -7333,13 +7333,13 @@
         <v>1.92</v>
       </c>
       <c r="DB16" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="DC16" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="DD16" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="DE16" t="n">
         <v>0.12</v>
@@ -7348,40 +7348,40 @@
         <v>1.94</v>
       </c>
       <c r="DG16" t="n">
-        <v>3.44</v>
+        <v>3.35</v>
       </c>
       <c r="DH16" t="n">
-        <v>96.38</v>
+        <v>96.12</v>
       </c>
       <c r="DI16" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DJ16" t="n">
-        <v>2.87</v>
+        <v>2.94</v>
       </c>
       <c r="DK16" t="n">
-        <v>6.12</v>
+        <v>6.18</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.59</v>
       </c>
       <c r="DM16" t="n">
-        <v>42.68</v>
+        <v>42.94</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.88</v>
+        <v>0.95</v>
       </c>
       <c r="DO16" t="n">
-        <v>2.69</v>
+        <v>2.82</v>
       </c>
       <c r="DP16" t="n">
-        <v>13.19</v>
+        <v>13.12</v>
       </c>
       <c r="DQ16" t="n">
-        <v>15.44</v>
+        <v>15.82</v>
       </c>
       <c r="DR16" t="n">
-        <v>7.62</v>
+        <v>7.65</v>
       </c>
       <c r="DS16" t="n">
         <v>0.12</v>
@@ -7393,28 +7393,28 @@
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>52.87</v>
+        <v>53.88</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DX16" t="n">
         <v>14.06</v>
       </c>
       <c r="DY16" t="n">
-        <v>8.380000000000001</v>
+        <v>8.23</v>
       </c>
       <c r="DZ16" t="n">
-        <v>5.69</v>
+        <v>5.82</v>
       </c>
       <c r="EA16" t="n">
-        <v>18.5</v>
+        <v>18.41</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="EC16" t="n">
-        <v>2.68</v>
+        <v>2.76</v>
       </c>
     </row>
     <row r="17">
@@ -7424,94 +7424,94 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D17" t="n">
         <v>8</v>
       </c>
       <c r="E17" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="F17" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="G17" t="n">
         <v>1</v>
       </c>
       <c r="H17" t="n">
-        <v>78</v>
+        <v>80.56</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="J17" t="n">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="K17" t="n">
-        <v>3</v>
+        <v>3.11</v>
       </c>
       <c r="L17" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="M17" t="n">
-        <v>31.62</v>
+        <v>31.78</v>
       </c>
       <c r="N17" t="n">
         <v>1</v>
       </c>
       <c r="O17" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="P17" t="n">
-        <v>19.25</v>
+        <v>18.33</v>
       </c>
       <c r="Q17" t="n">
-        <v>13.38</v>
+        <v>13.22</v>
       </c>
       <c r="R17" t="n">
-        <v>8.880000000000001</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="S17" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="T17" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="U17" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="V17" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>43.88</v>
+        <v>45.44</v>
       </c>
       <c r="Y17" t="n">
         <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>10.62</v>
+        <v>10.33</v>
       </c>
       <c r="AA17" t="n">
-        <v>6.75</v>
+        <v>6.78</v>
       </c>
       <c r="AB17" t="n">
-        <v>3.88</v>
+        <v>3.56</v>
       </c>
       <c r="AC17" t="n">
-        <v>20.25</v>
+        <v>19.89</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AE17" t="n">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="AF17" t="n">
         <v>0</v>
@@ -7595,58 +7595,58 @@
         <v>2.62</v>
       </c>
       <c r="BG17" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="BH17" t="n">
-        <v>9</v>
+        <v>9.06</v>
       </c>
       <c r="BI17" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="BJ17" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="BL17" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.62</v>
+        <v>0.65</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="BP17" t="n">
         <v>3.94</v>
       </c>
       <c r="BQ17" t="n">
-        <v>4.44</v>
+        <v>4.53</v>
       </c>
       <c r="BR17" t="n">
         <v>100</v>
       </c>
       <c r="BS17" t="n">
-        <v>62.5</v>
+        <v>58.82</v>
       </c>
       <c r="BT17" t="n">
-        <v>50</v>
+        <v>47.06</v>
       </c>
       <c r="BU17" t="n">
-        <v>25</v>
+        <v>23.53</v>
       </c>
       <c r="BV17" t="n">
-        <v>18.75</v>
+        <v>17.65</v>
       </c>
       <c r="BW17" t="n">
-        <v>18.75</v>
+        <v>17.65</v>
       </c>
       <c r="BX17" t="n">
-        <v>50</v>
+        <v>47.06</v>
       </c>
       <c r="BY17" t="n">
         <v>3.24</v>
@@ -7655,10 +7655,10 @@
         <v>3.55</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.45</v>
+        <v>3.42</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.69</v>
+        <v>3.66</v>
       </c>
       <c r="CC17" t="n">
         <v>5.37</v>
@@ -7667,13 +7667,13 @@
         <v>6.55</v>
       </c>
       <c r="CE17" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CF17" t="n">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="CG17" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="CH17" t="n">
         <v>1.35</v>
@@ -7682,52 +7682,52 @@
         <v>1.81</v>
       </c>
       <c r="CJ17" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CK17" t="n">
         <v>1.6</v>
       </c>
       <c r="CL17" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="CM17" t="n">
         <v>2.24</v>
       </c>
       <c r="CN17" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CO17" t="n">
         <v>1.34</v>
       </c>
       <c r="CP17" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="CQ17" t="n">
-        <v>3.69</v>
+        <v>3.7</v>
       </c>
       <c r="CR17" t="n">
         <v>1.48</v>
       </c>
       <c r="CS17" t="n">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="CT17" t="n">
         <v>2.78</v>
       </c>
       <c r="CU17" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CV17" t="n">
         <v>1.88</v>
       </c>
       <c r="CW17" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="CX17" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CY17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CZ17" t="n">
         <v>2.22</v>
@@ -7748,76 +7748,76 @@
         <v>0.06</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="DG17" t="n">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="DH17" t="n">
-        <v>81.56</v>
+        <v>82.70999999999999</v>
       </c>
       <c r="DI17" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="DJ17" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="DK17" t="n">
-        <v>3.19</v>
+        <v>3.24</v>
       </c>
       <c r="DL17" t="n">
         <v>0.18</v>
       </c>
       <c r="DM17" t="n">
-        <v>30.06</v>
+        <v>30.24</v>
       </c>
       <c r="DN17" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="DO17" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="DP17" t="n">
-        <v>17.81</v>
+        <v>17.41</v>
       </c>
       <c r="DQ17" t="n">
-        <v>13.5</v>
+        <v>13.41</v>
       </c>
       <c r="DR17" t="n">
-        <v>8.880000000000001</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.19</v>
+        <v>0.17</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.19</v>
+        <v>0.17</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>43.88</v>
+        <v>44.71</v>
       </c>
       <c r="DW17" t="n">
         <v>0.06</v>
       </c>
       <c r="DX17" t="n">
-        <v>11.18</v>
+        <v>11</v>
       </c>
       <c r="DY17" t="n">
         <v>6.94</v>
       </c>
       <c r="DZ17" t="n">
-        <v>4.25</v>
+        <v>4.06</v>
       </c>
       <c r="EA17" t="n">
-        <v>21.44</v>
+        <v>21.17</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="EC17" t="n">
-        <v>2.87</v>
+        <v>2.82</v>
       </c>
     </row>
     <row r="18">
@@ -7827,13 +7827,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C18" t="n">
         <v>9</v>
       </c>
       <c r="D18" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E18" t="n">
         <v>0.11</v>
@@ -7917,139 +7917,139 @@
         <v>2.44</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="AH18" t="n">
-        <v>3.43</v>
+        <v>3.38</v>
       </c>
       <c r="AI18" t="n">
-        <v>112.14</v>
+        <v>108.5</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AK18" t="n">
-        <v>3.43</v>
+        <v>3.5</v>
       </c>
       <c r="AL18" t="n">
-        <v>6</v>
+        <v>5.88</v>
       </c>
       <c r="AM18" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="AN18" t="n">
-        <v>49.57</v>
+        <v>47.38</v>
       </c>
       <c r="AO18" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AP18" t="n">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="AQ18" t="n">
-        <v>17.86</v>
+        <v>17.75</v>
       </c>
       <c r="AR18" t="n">
-        <v>14.29</v>
+        <v>13.75</v>
       </c>
       <c r="AS18" t="n">
-        <v>8.710000000000001</v>
+        <v>8.75</v>
       </c>
       <c r="AT18" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="AU18" t="n">
-        <v>0.57</v>
+        <v>1</v>
       </c>
       <c r="AV18" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AW18" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AX18" t="n">
         <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>51.29</v>
+        <v>51.12</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="BA18" t="n">
-        <v>13.14</v>
+        <v>13</v>
       </c>
       <c r="BB18" t="n">
-        <v>9.57</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="BC18" t="n">
-        <v>3.57</v>
+        <v>3.88</v>
       </c>
       <c r="BD18" t="n">
-        <v>23.57</v>
+        <v>23</v>
       </c>
       <c r="BE18" t="n">
         <v>1.44</v>
       </c>
       <c r="BF18" t="n">
-        <v>3.29</v>
+        <v>3.38</v>
       </c>
       <c r="BG18" t="n">
-        <v>1.88</v>
+        <v>2.06</v>
       </c>
       <c r="BH18" t="n">
-        <v>9</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="BI18" t="n">
-        <v>1.88</v>
+        <v>2.06</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.38</v>
+        <v>0.35</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.44</v>
+        <v>0.53</v>
       </c>
       <c r="BL18" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.38</v>
+        <v>0.47</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="BO18" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.88</v>
       </c>
       <c r="BP18" t="n">
-        <v>3.12</v>
+        <v>3.18</v>
       </c>
       <c r="BQ18" t="n">
-        <v>5.88</v>
+        <v>5.94</v>
       </c>
       <c r="BR18" t="n">
-        <v>87.5</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="BS18" t="n">
-        <v>56.25</v>
+        <v>58.82</v>
       </c>
       <c r="BT18" t="n">
-        <v>25</v>
+        <v>29.41</v>
       </c>
       <c r="BU18" t="n">
-        <v>12.5</v>
+        <v>17.65</v>
       </c>
       <c r="BV18" t="n">
-        <v>6.25</v>
+        <v>11.76</v>
       </c>
       <c r="BW18" t="n">
         <v>0</v>
       </c>
       <c r="BX18" t="n">
-        <v>43.75</v>
+        <v>47.06</v>
       </c>
       <c r="BY18" t="n">
         <v>1.91</v>
@@ -8058,40 +8058,40 @@
         <v>1.98</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.31</v>
+        <v>3.28</v>
       </c>
       <c r="CB18" t="n">
-        <v>3.42</v>
+        <v>3.39</v>
       </c>
       <c r="CC18" t="n">
-        <v>2.77</v>
+        <v>2.74</v>
       </c>
       <c r="CD18" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="CE18" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="CF18" t="n">
         <v>2.99</v>
       </c>
-      <c r="CE18" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="CF18" t="n">
-        <v>2.95</v>
-      </c>
       <c r="CG18" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="CH18" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CI18" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CJ18" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="CK18" t="n">
         <v>1.62</v>
       </c>
       <c r="CL18" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="CM18" t="n">
         <v>2.14</v>
@@ -8100,127 +8100,127 @@
         <v>1.74</v>
       </c>
       <c r="CO18" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CP18" t="n">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="CQ18" t="n">
-        <v>3.78</v>
+        <v>3.85</v>
       </c>
       <c r="CR18" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="CS18" t="n">
         <v>3.1</v>
       </c>
       <c r="CT18" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="CU18" t="n">
         <v>1.4</v>
       </c>
       <c r="CV18" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CW18" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="CX18" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CY18" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="CZ18" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="DA18" t="n">
         <v>1.71</v>
       </c>
       <c r="DB18" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="DC18" t="n">
-        <v>2.19</v>
+        <v>2.22</v>
       </c>
       <c r="DD18" t="n">
-        <v>3.97</v>
+        <v>4.05</v>
       </c>
       <c r="DE18" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="DG18" t="n">
-        <v>4.19</v>
+        <v>4.12</v>
       </c>
       <c r="DH18" t="n">
-        <v>115</v>
+        <v>113.12</v>
       </c>
       <c r="DI18" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ18" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="DK18" t="n">
-        <v>6.5</v>
+        <v>6.41</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.63</v>
+        <v>0.59</v>
       </c>
       <c r="DM18" t="n">
-        <v>59.25</v>
+        <v>57.65</v>
       </c>
       <c r="DN18" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="DO18" t="n">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="DP18" t="n">
-        <v>17.88</v>
+        <v>17.82</v>
       </c>
       <c r="DQ18" t="n">
-        <v>13.5</v>
+        <v>13.29</v>
       </c>
       <c r="DR18" t="n">
-        <v>6.68</v>
+        <v>6.82</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DT18" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DU18" t="n">
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>53.25</v>
+        <v>53.06</v>
       </c>
       <c r="DW18" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DX18" t="n">
-        <v>15.56</v>
+        <v>15.35</v>
       </c>
       <c r="DY18" t="n">
-        <v>10.88</v>
+        <v>10.59</v>
       </c>
       <c r="DZ18" t="n">
-        <v>4.69</v>
+        <v>4.77</v>
       </c>
       <c r="EA18" t="n">
-        <v>26.62</v>
+        <v>26.18</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="EC18" t="n">
-        <v>2.81</v>
+        <v>2.88</v>
       </c>
     </row>
     <row r="19">
@@ -8633,10 +8633,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C20" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D20" t="n">
         <v>8</v>
@@ -8645,82 +8645,82 @@
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="G20" t="n">
-        <v>2.62</v>
+        <v>3</v>
       </c>
       <c r="H20" t="n">
-        <v>112.88</v>
+        <v>114.89</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="K20" t="n">
-        <v>5.38</v>
+        <v>5.67</v>
       </c>
       <c r="L20" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="M20" t="n">
-        <v>58.5</v>
+        <v>60.33</v>
       </c>
       <c r="N20" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="O20" t="n">
-        <v>2.75</v>
+        <v>2.67</v>
       </c>
       <c r="P20" t="n">
-        <v>16.12</v>
+        <v>15.67</v>
       </c>
       <c r="Q20" t="n">
-        <v>11.38</v>
+        <v>11</v>
       </c>
       <c r="R20" t="n">
-        <v>6.88</v>
+        <v>6.56</v>
       </c>
       <c r="S20" t="n">
-        <v>0.75</v>
+        <v>0.89</v>
       </c>
       <c r="T20" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="U20" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="V20" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>54.88</v>
+        <v>55.33</v>
       </c>
       <c r="Y20" t="n">
         <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>16.38</v>
+        <v>17</v>
       </c>
       <c r="AA20" t="n">
-        <v>10.5</v>
+        <v>11.22</v>
       </c>
       <c r="AB20" t="n">
-        <v>5.88</v>
+        <v>5.78</v>
       </c>
       <c r="AC20" t="n">
-        <v>18.62</v>
+        <v>18.33</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="AF20" t="n">
         <v>0.12</v>
@@ -8804,70 +8804,70 @@
         <v>2.25</v>
       </c>
       <c r="BG20" t="n">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="BH20" t="n">
-        <v>9.119999999999999</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="BI20" t="n">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="BJ20" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="BK20" t="n">
-        <v>0.31</v>
+        <v>0.35</v>
       </c>
       <c r="BL20" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM20" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="BN20" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BO20" t="n">
         <v>1.06</v>
       </c>
-      <c r="BM20" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="BN20" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="BO20" t="n">
-        <v>1</v>
-      </c>
       <c r="BP20" t="n">
-        <v>4.25</v>
+        <v>4.24</v>
       </c>
       <c r="BQ20" t="n">
-        <v>4.88</v>
+        <v>5.06</v>
       </c>
       <c r="BR20" t="n">
-        <v>87.5</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="BS20" t="n">
-        <v>75</v>
+        <v>76.47</v>
       </c>
       <c r="BT20" t="n">
-        <v>50</v>
+        <v>52.94</v>
       </c>
       <c r="BU20" t="n">
-        <v>25</v>
+        <v>23.53</v>
       </c>
       <c r="BV20" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BW20" t="n">
         <v>0</v>
       </c>
       <c r="BX20" t="n">
-        <v>56.25</v>
+        <v>58.82</v>
       </c>
       <c r="BY20" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="BZ20" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="CA20" t="n">
         <v>3.19</v>
       </c>
       <c r="CB20" t="n">
-        <v>3.27</v>
+        <v>3.28</v>
       </c>
       <c r="CC20" t="n">
         <v>3.25</v>
@@ -8876,19 +8876,19 @@
         <v>3.64</v>
       </c>
       <c r="CE20" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CF20" t="n">
-        <v>3.29</v>
+        <v>3.26</v>
       </c>
       <c r="CG20" t="n">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="CH20" t="n">
         <v>1.31</v>
       </c>
       <c r="CI20" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CJ20" t="n">
         <v>2.03</v>
@@ -8897,7 +8897,7 @@
         <v>1.64</v>
       </c>
       <c r="CL20" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="CM20" t="n">
         <v>2.14</v>
@@ -8906,22 +8906,22 @@
         <v>1.73</v>
       </c>
       <c r="CO20" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="CP20" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="CQ20" t="n">
-        <v>4.38</v>
+        <v>4.34</v>
       </c>
       <c r="CR20" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CS20" t="n">
-        <v>3.22</v>
+        <v>3.24</v>
       </c>
       <c r="CT20" t="n">
-        <v>2.58</v>
+        <v>2.59</v>
       </c>
       <c r="CU20" t="n">
         <v>1.36</v>
@@ -8948,52 +8948,52 @@
         <v>1.46</v>
       </c>
       <c r="DC20" t="n">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="DD20" t="n">
-        <v>4.69</v>
+        <v>4.66</v>
       </c>
       <c r="DE20" t="n">
         <v>0.06</v>
       </c>
       <c r="DF20" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="DG20" t="n">
-        <v>2.87</v>
+        <v>3.06</v>
       </c>
       <c r="DH20" t="n">
-        <v>106.5</v>
+        <v>107.94</v>
       </c>
       <c r="DI20" t="n">
         <v>0.12</v>
       </c>
       <c r="DJ20" t="n">
-        <v>2.68</v>
+        <v>2.65</v>
       </c>
       <c r="DK20" t="n">
-        <v>4.94</v>
+        <v>5.12</v>
       </c>
       <c r="DL20" t="n">
-        <v>0.38</v>
+        <v>0.35</v>
       </c>
       <c r="DM20" t="n">
-        <v>48.44</v>
+        <v>50</v>
       </c>
       <c r="DN20" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="DO20" t="n">
         <v>2.06</v>
       </c>
       <c r="DP20" t="n">
-        <v>14.25</v>
+        <v>14.12</v>
       </c>
       <c r="DQ20" t="n">
-        <v>12.5</v>
+        <v>12.23</v>
       </c>
       <c r="DR20" t="n">
-        <v>6.75</v>
+        <v>6.59</v>
       </c>
       <c r="DS20" t="n">
         <v>0.12</v>
@@ -9005,28 +9005,28 @@
         <v>0</v>
       </c>
       <c r="DV20" t="n">
-        <v>52.38</v>
+        <v>52.77</v>
       </c>
       <c r="DW20" t="n">
         <v>0.12</v>
       </c>
       <c r="DX20" t="n">
-        <v>13.32</v>
+        <v>13.82</v>
       </c>
       <c r="DY20" t="n">
-        <v>8.69</v>
+        <v>9.18</v>
       </c>
       <c r="DZ20" t="n">
-        <v>4.63</v>
+        <v>4.65</v>
       </c>
       <c r="EA20" t="n">
-        <v>19.06</v>
+        <v>18.88</v>
       </c>
       <c r="EB20" t="n">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="EC20" t="n">
-        <v>2.44</v>
+        <v>2.41</v>
       </c>
     </row>
     <row r="21">
@@ -9036,10 +9036,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D21" t="n">
         <v>8</v>
@@ -9048,82 +9048,82 @@
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="G21" t="n">
-        <v>2.62</v>
+        <v>2.78</v>
       </c>
       <c r="H21" t="n">
-        <v>95.38</v>
+        <v>98.78</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="K21" t="n">
-        <v>5.12</v>
+        <v>5.22</v>
       </c>
       <c r="L21" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="M21" t="n">
-        <v>43.38</v>
+        <v>44.22</v>
       </c>
       <c r="N21" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="O21" t="n">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="P21" t="n">
-        <v>14.75</v>
+        <v>14.22</v>
       </c>
       <c r="Q21" t="n">
-        <v>12.75</v>
+        <v>13.22</v>
       </c>
       <c r="R21" t="n">
-        <v>9.75</v>
+        <v>9.44</v>
       </c>
       <c r="S21" t="n">
-        <v>0.88</v>
+        <v>1.22</v>
       </c>
       <c r="T21" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="U21" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="V21" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>46.12</v>
+        <v>46.56</v>
       </c>
       <c r="Y21" t="n">
         <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>12.12</v>
+        <v>12.11</v>
       </c>
       <c r="AA21" t="n">
-        <v>8.5</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="AB21" t="n">
-        <v>3.62</v>
+        <v>3.89</v>
       </c>
       <c r="AC21" t="n">
-        <v>24.25</v>
+        <v>24.33</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="AF21" t="n">
         <v>0</v>
@@ -9207,67 +9207,67 @@
         <v>1.75</v>
       </c>
       <c r="BG21" t="n">
-        <v>2.06</v>
+        <v>2.24</v>
       </c>
       <c r="BH21" t="n">
-        <v>9.380000000000001</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="BI21" t="n">
-        <v>2.06</v>
+        <v>2.24</v>
       </c>
       <c r="BJ21" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BK21" t="n">
-        <v>0.38</v>
+        <v>0.47</v>
       </c>
       <c r="BL21" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="BM21" t="n">
-        <v>0.25</v>
+        <v>0.35</v>
       </c>
       <c r="BN21" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BO21" t="n">
         <v>1.06</v>
       </c>
-      <c r="BO21" t="n">
-        <v>1</v>
-      </c>
       <c r="BP21" t="n">
-        <v>4.19</v>
+        <v>4.18</v>
       </c>
       <c r="BQ21" t="n">
-        <v>5.12</v>
+        <v>5.24</v>
       </c>
       <c r="BR21" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BS21" t="n">
-        <v>62.5</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BT21" t="n">
-        <v>37.5</v>
+        <v>41.18</v>
       </c>
       <c r="BU21" t="n">
-        <v>12.5</v>
+        <v>17.65</v>
       </c>
       <c r="BV21" t="n">
-        <v>0</v>
+        <v>5.88</v>
       </c>
       <c r="BW21" t="n">
         <v>0</v>
       </c>
       <c r="BX21" t="n">
-        <v>43.75</v>
+        <v>47.06</v>
       </c>
       <c r="BY21" t="n">
-        <v>2.39</v>
+        <v>2.47</v>
       </c>
       <c r="BZ21" t="n">
-        <v>2.57</v>
+        <v>2.67</v>
       </c>
       <c r="CA21" t="n">
-        <v>2.91</v>
+        <v>2.89</v>
       </c>
       <c r="CB21" t="n">
         <v>3.02</v>
@@ -9282,25 +9282,25 @@
         <v>1.58</v>
       </c>
       <c r="CF21" t="n">
-        <v>3.75</v>
+        <v>3.74</v>
       </c>
       <c r="CG21" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="CH21" t="n">
         <v>1.24</v>
       </c>
       <c r="CI21" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CJ21" t="n">
         <v>2.19</v>
       </c>
       <c r="CK21" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CL21" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="CM21" t="n">
         <v>2.06</v>
@@ -9309,13 +9309,13 @@
         <v>1.68</v>
       </c>
       <c r="CO21" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="CP21" t="n">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="CQ21" t="n">
-        <v>5.15</v>
+        <v>5.14</v>
       </c>
       <c r="CR21" t="n">
         <v>1.63</v>
@@ -9324,49 +9324,49 @@
         <v>3.35</v>
       </c>
       <c r="CT21" t="n">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="CU21" t="n">
         <v>1.34</v>
       </c>
       <c r="CV21" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CW21" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="CX21" t="n">
         <v>1.76</v>
       </c>
       <c r="CY21" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="CZ21" t="n">
         <v>2.07</v>
       </c>
       <c r="DA21" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="DB21" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="DC21" t="n">
-        <v>2.87</v>
+        <v>2.86</v>
       </c>
       <c r="DD21" t="n">
-        <v>5.82</v>
+        <v>5.79</v>
       </c>
       <c r="DE21" t="n">
         <v>0</v>
       </c>
       <c r="DF21" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="DG21" t="n">
-        <v>2.31</v>
+        <v>2.41</v>
       </c>
       <c r="DH21" t="n">
-        <v>88</v>
+        <v>90.23</v>
       </c>
       <c r="DI21" t="n">
         <v>0</v>
@@ -9375,58 +9375,58 @@
         <v>1.94</v>
       </c>
       <c r="DK21" t="n">
-        <v>4.19</v>
+        <v>4.29</v>
       </c>
       <c r="DL21" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.59</v>
       </c>
       <c r="DM21" t="n">
-        <v>38.13</v>
+        <v>38.88</v>
       </c>
       <c r="DN21" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="DO21" t="n">
         <v>1.82</v>
       </c>
       <c r="DP21" t="n">
-        <v>12.5</v>
+        <v>12.35</v>
       </c>
       <c r="DQ21" t="n">
-        <v>13.07</v>
+        <v>13.3</v>
       </c>
       <c r="DR21" t="n">
-        <v>8.75</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="DS21" t="n">
-        <v>0.19</v>
+        <v>0.17</v>
       </c>
       <c r="DT21" t="n">
-        <v>0.19</v>
+        <v>0.17</v>
       </c>
       <c r="DU21" t="n">
         <v>0</v>
       </c>
       <c r="DV21" t="n">
-        <v>46.44</v>
+        <v>46.65</v>
       </c>
       <c r="DW21" t="n">
         <v>0.06</v>
       </c>
       <c r="DX21" t="n">
-        <v>10.5</v>
+        <v>10.59</v>
       </c>
       <c r="DY21" t="n">
-        <v>7.94</v>
+        <v>7.82</v>
       </c>
       <c r="DZ21" t="n">
-        <v>2.56</v>
+        <v>2.77</v>
       </c>
       <c r="EA21" t="n">
-        <v>21.18</v>
+        <v>21.41</v>
       </c>
       <c r="EB21" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="EC21" t="n">
         <v>1.82</v>
@@ -9439,13 +9439,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C22" t="n">
         <v>9</v>
       </c>
       <c r="D22" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -9529,139 +9529,139 @@
         <v>2</v>
       </c>
       <c r="AF22" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AG22" t="n">
-        <v>2.43</v>
+        <v>2.75</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.29</v>
+        <v>1.75</v>
       </c>
       <c r="AI22" t="n">
-        <v>86.70999999999999</v>
+        <v>88.62</v>
       </c>
       <c r="AJ22" t="n">
         <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>3.14</v>
+        <v>3.62</v>
       </c>
       <c r="AL22" t="n">
-        <v>2.57</v>
+        <v>3</v>
       </c>
       <c r="AM22" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AN22" t="n">
-        <v>33</v>
+        <v>34.12</v>
       </c>
       <c r="AO22" t="n">
-        <v>0.71</v>
+        <v>0.88</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AQ22" t="n">
-        <v>12.43</v>
+        <v>12.38</v>
       </c>
       <c r="AR22" t="n">
         <v>11</v>
       </c>
       <c r="AS22" t="n">
-        <v>8.289999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="AT22" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="AU22" t="n">
         <v>1</v>
       </c>
       <c r="AV22" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AW22" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AX22" t="n">
         <v>0</v>
       </c>
       <c r="AY22" t="n">
-        <v>42.71</v>
+        <v>42.62</v>
       </c>
       <c r="AZ22" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="BA22" t="n">
-        <v>8</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="BB22" t="n">
-        <v>4.43</v>
+        <v>4.75</v>
       </c>
       <c r="BC22" t="n">
-        <v>3.57</v>
+        <v>3.38</v>
       </c>
       <c r="BD22" t="n">
-        <v>19.29</v>
+        <v>20.38</v>
       </c>
       <c r="BE22" t="n">
         <v>1</v>
       </c>
       <c r="BF22" t="n">
-        <v>2.86</v>
+        <v>3.38</v>
       </c>
       <c r="BG22" t="n">
-        <v>2.69</v>
+        <v>2.59</v>
       </c>
       <c r="BH22" t="n">
-        <v>9.5</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="BI22" t="n">
-        <v>2.69</v>
+        <v>2.59</v>
       </c>
       <c r="BJ22" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BK22" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BL22" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="BM22" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="BN22" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="BO22" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="BP22" t="n">
-        <v>4.56</v>
+        <v>4.53</v>
       </c>
       <c r="BQ22" t="n">
-        <v>4.88</v>
+        <v>4.94</v>
       </c>
       <c r="BR22" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BS22" t="n">
-        <v>68.75</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BT22" t="n">
-        <v>50</v>
+        <v>47.06</v>
       </c>
       <c r="BU22" t="n">
-        <v>25</v>
+        <v>23.53</v>
       </c>
       <c r="BV22" t="n">
-        <v>18.75</v>
+        <v>17.65</v>
       </c>
       <c r="BW22" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BX22" t="n">
-        <v>62.5</v>
+        <v>58.82</v>
       </c>
       <c r="BY22" t="n">
         <v>2.1</v>
@@ -9670,31 +9670,31 @@
         <v>2.12</v>
       </c>
       <c r="CA22" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="CB22" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="CC22" t="n">
         <v>3.23</v>
       </c>
-      <c r="CB22" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="CC22" t="n">
-        <v>3.37</v>
-      </c>
       <c r="CD22" t="n">
-        <v>3.47</v>
+        <v>3.31</v>
       </c>
       <c r="CE22" t="n">
         <v>1.43</v>
       </c>
       <c r="CF22" t="n">
-        <v>3.07</v>
+        <v>3.08</v>
       </c>
       <c r="CG22" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="CH22" t="n">
         <v>1.35</v>
       </c>
       <c r="CI22" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CJ22" t="n">
         <v>1.87</v>
@@ -9703,7 +9703,7 @@
         <v>1.63</v>
       </c>
       <c r="CL22" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="CM22" t="n">
         <v>2.15</v>
@@ -9724,10 +9724,10 @@
         <v>1.47</v>
       </c>
       <c r="CS22" t="n">
-        <v>3.07</v>
+        <v>3.09</v>
       </c>
       <c r="CT22" t="n">
-        <v>2.82</v>
+        <v>2.81</v>
       </c>
       <c r="CU22" t="n">
         <v>1.4</v>
@@ -9736,7 +9736,7 @@
         <v>1.95</v>
       </c>
       <c r="CW22" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CX22" t="n">
         <v>1.64</v>
@@ -9754,85 +9754,85 @@
         <v>1.42</v>
       </c>
       <c r="DC22" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="DD22" t="n">
-        <v>4.33</v>
+        <v>4.31</v>
       </c>
       <c r="DE22" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DF22" t="n">
-        <v>2.06</v>
+        <v>2.24</v>
       </c>
       <c r="DG22" t="n">
-        <v>2.07</v>
+        <v>2.24</v>
       </c>
       <c r="DH22" t="n">
-        <v>101</v>
+        <v>101.06</v>
       </c>
       <c r="DI22" t="n">
         <v>0</v>
       </c>
       <c r="DJ22" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="DK22" t="n">
-        <v>4.12</v>
+        <v>4.23</v>
       </c>
       <c r="DL22" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="DM22" t="n">
-        <v>41.68</v>
+        <v>41.7</v>
       </c>
       <c r="DN22" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.65</v>
       </c>
       <c r="DO22" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="DP22" t="n">
-        <v>12.69</v>
+        <v>12.65</v>
       </c>
       <c r="DQ22" t="n">
         <v>11</v>
       </c>
       <c r="DR22" t="n">
-        <v>7.75</v>
+        <v>7.88</v>
       </c>
       <c r="DS22" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DT22" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DU22" t="n">
         <v>0</v>
       </c>
       <c r="DV22" t="n">
-        <v>44</v>
+        <v>43.88</v>
       </c>
       <c r="DW22" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DX22" t="n">
-        <v>11</v>
+        <v>10.88</v>
       </c>
       <c r="DY22" t="n">
-        <v>6.38</v>
+        <v>6.41</v>
       </c>
       <c r="DZ22" t="n">
-        <v>4.62</v>
+        <v>4.47</v>
       </c>
       <c r="EA22" t="n">
-        <v>19.81</v>
+        <v>20.3</v>
       </c>
       <c r="EB22" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="EC22" t="n">
-        <v>2.38</v>
+        <v>2.65</v>
       </c>
     </row>
     <row r="23">

--- a/data/teams/leagues/Averages_Spain_Segunda_División_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Spain_Segunda_División_2025-2026.xlsx
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C2" t="n">
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -1469,139 +1469,139 @@
         <v>1.5</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.62</v>
+        <v>1.78</v>
       </c>
       <c r="AI2" t="n">
-        <v>84</v>
+        <v>86.44</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AK2" t="n">
-        <v>3.5</v>
+        <v>3.22</v>
       </c>
       <c r="AL2" t="n">
-        <v>4.12</v>
+        <v>4.22</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="AN2" t="n">
-        <v>40.25</v>
+        <v>39.89</v>
       </c>
       <c r="AO2" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AP2" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="AQ2" t="n">
-        <v>12.88</v>
+        <v>12.78</v>
       </c>
       <c r="AR2" t="n">
-        <v>13.25</v>
+        <v>13.33</v>
       </c>
       <c r="AS2" t="n">
         <v>9</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AX2" t="n">
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>42.38</v>
+        <v>42.78</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="BA2" t="n">
-        <v>11.62</v>
+        <v>11.33</v>
       </c>
       <c r="BB2" t="n">
-        <v>6.62</v>
+        <v>6.67</v>
       </c>
       <c r="BC2" t="n">
-        <v>5</v>
+        <v>4.67</v>
       </c>
       <c r="BD2" t="n">
-        <v>23.5</v>
+        <v>24.11</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="BF2" t="n">
-        <v>2.75</v>
+        <v>2.56</v>
       </c>
       <c r="BG2" t="n">
-        <v>3.06</v>
+        <v>2.94</v>
       </c>
       <c r="BH2" t="n">
-        <v>10.56</v>
+        <v>10.53</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.06</v>
+        <v>2.94</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.44</v>
+        <v>0.41</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="BL2" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BM2" t="n">
         <v>1.06</v>
       </c>
       <c r="BN2" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="BO2" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BP2" t="n">
-        <v>5.19</v>
+        <v>5.06</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.31</v>
+        <v>5.41</v>
       </c>
       <c r="BR2" t="n">
-        <v>81.25</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="BS2" t="n">
-        <v>68.75</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BT2" t="n">
-        <v>56.25</v>
+        <v>52.94</v>
       </c>
       <c r="BU2" t="n">
-        <v>37.5</v>
+        <v>35.29</v>
       </c>
       <c r="BV2" t="n">
-        <v>31.25</v>
+        <v>29.41</v>
       </c>
       <c r="BW2" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BX2" t="n">
-        <v>56.25</v>
+        <v>52.94</v>
       </c>
       <c r="BY2" t="n">
         <v>2.2</v>
@@ -1610,136 +1610,136 @@
         <v>2.2</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.33</v>
+        <v>3.31</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.55</v>
+        <v>3.53</v>
       </c>
       <c r="CC2" t="n">
-        <v>3.86</v>
+        <v>3.85</v>
       </c>
       <c r="CD2" t="n">
-        <v>4.36</v>
+        <v>4.38</v>
       </c>
       <c r="CE2" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.92</v>
+        <v>2.89</v>
       </c>
       <c r="CH2" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="CI2" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="CJ2" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="CK2" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="CL2" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="CM2" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="CN2" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="CO2" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="CP2" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="CQ2" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="CR2" t="n">
         <v>1.42</v>
       </c>
-      <c r="CI2" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="CJ2" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="CK2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="CL2" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="CM2" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="CN2" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="CO2" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="CP2" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="CQ2" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="CR2" t="n">
-        <v>1.41</v>
-      </c>
       <c r="CS2" t="n">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="CT2" t="n">
-        <v>3.05</v>
+        <v>3.01</v>
       </c>
       <c r="CU2" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CV2" t="n">
-        <v>2.14</v>
+        <v>2.11</v>
       </c>
       <c r="CW2" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="CX2" t="n">
         <v>1.52</v>
       </c>
       <c r="CY2" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="CZ2" t="n">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="DA2" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="DB2" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="DC2" t="n">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="DD2" t="n">
-        <v>3.31</v>
+        <v>3.42</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.19</v>
+        <v>0.17</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="DH2" t="n">
-        <v>88</v>
+        <v>89.06</v>
       </c>
       <c r="DI2" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.62</v>
+        <v>2.53</v>
       </c>
       <c r="DK2" t="n">
-        <v>4.81</v>
+        <v>4.82</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="DM2" t="n">
-        <v>43</v>
+        <v>42.65</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="DP2" t="n">
-        <v>11.38</v>
+        <v>11.42</v>
       </c>
       <c r="DQ2" t="n">
-        <v>11.12</v>
+        <v>11.29</v>
       </c>
       <c r="DR2" t="n">
-        <v>7.88</v>
+        <v>7.94</v>
       </c>
       <c r="DS2" t="n">
         <v>0.06</v>
@@ -1751,28 +1751,28 @@
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>43</v>
+        <v>43.18</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DX2" t="n">
-        <v>13.56</v>
+        <v>13.29</v>
       </c>
       <c r="DY2" t="n">
-        <v>8.68</v>
+        <v>8.59</v>
       </c>
       <c r="DZ2" t="n">
-        <v>4.88</v>
+        <v>4.71</v>
       </c>
       <c r="EA2" t="n">
-        <v>24.12</v>
+        <v>24.41</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
     </row>
     <row r="3">
@@ -2185,94 +2185,94 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D4" t="n">
         <v>8</v>
       </c>
       <c r="E4" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="F4" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="G4" t="n">
-        <v>1.88</v>
+        <v>2.11</v>
       </c>
       <c r="H4" t="n">
-        <v>94.5</v>
+        <v>94.89</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>3.12</v>
+        <v>3.11</v>
       </c>
       <c r="K4" t="n">
-        <v>3.75</v>
+        <v>3.89</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>47.12</v>
+        <v>46.11</v>
       </c>
       <c r="N4" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="O4" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="P4" t="n">
-        <v>13.88</v>
+        <v>13.89</v>
       </c>
       <c r="Q4" t="n">
-        <v>14.75</v>
+        <v>14.44</v>
       </c>
       <c r="R4" t="n">
-        <v>8.619999999999999</v>
+        <v>8.44</v>
       </c>
       <c r="S4" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="T4" t="n">
-        <v>1.12</v>
+        <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="V4" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>49.62</v>
+        <v>50.11</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>10.38</v>
+        <v>10.67</v>
       </c>
       <c r="AA4" t="n">
-        <v>7.5</v>
+        <v>7.78</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="AC4" t="n">
-        <v>26.5</v>
+        <v>26.89</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AE4" t="n">
-        <v>3.12</v>
+        <v>3.11</v>
       </c>
       <c r="AF4" t="n">
         <v>0.12</v>
@@ -2356,64 +2356,64 @@
         <v>2.38</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="BH4" t="n">
-        <v>8.380000000000001</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.62</v>
+        <v>0.65</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="BP4" t="n">
-        <v>4</v>
+        <v>3.94</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.38</v>
+        <v>4.53</v>
       </c>
       <c r="BR4" t="n">
-        <v>81.25</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="BS4" t="n">
-        <v>62.5</v>
+        <v>58.82</v>
       </c>
       <c r="BT4" t="n">
-        <v>43.75</v>
+        <v>41.18</v>
       </c>
       <c r="BU4" t="n">
-        <v>18.75</v>
+        <v>17.65</v>
       </c>
       <c r="BV4" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BW4" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BX4" t="n">
-        <v>50</v>
+        <v>47.06</v>
       </c>
       <c r="BY4" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="BZ4" t="n">
-        <v>2.29</v>
+        <v>2.26</v>
       </c>
       <c r="CA4" t="n">
         <v>3</v>
@@ -2431,7 +2431,7 @@
         <v>1.55</v>
       </c>
       <c r="CF4" t="n">
-        <v>3.47</v>
+        <v>3.46</v>
       </c>
       <c r="CG4" t="n">
         <v>2.36</v>
@@ -2440,145 +2440,145 @@
         <v>1.26</v>
       </c>
       <c r="CI4" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CJ4" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CL4" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CO4" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CP4" t="n">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="CQ4" t="n">
-        <v>4.85</v>
+        <v>4.82</v>
       </c>
       <c r="CR4" t="n">
         <v>1.6</v>
       </c>
       <c r="CS4" t="n">
-        <v>3.4</v>
+        <v>3.38</v>
       </c>
       <c r="CT4" t="n">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="CU4" t="n">
         <v>1.33</v>
       </c>
       <c r="CV4" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CW4" t="n">
         <v>2.24</v>
       </c>
       <c r="CX4" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CY4" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="CZ4" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="DA4" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="DB4" t="n">
         <v>1.55</v>
       </c>
       <c r="DC4" t="n">
-        <v>2.72</v>
+        <v>2.71</v>
       </c>
       <c r="DD4" t="n">
-        <v>5.46</v>
+        <v>5.44</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.13</v>
+        <v>2.24</v>
       </c>
       <c r="DH4" t="n">
-        <v>90.38</v>
+        <v>90.81999999999999</v>
       </c>
       <c r="DI4" t="n">
         <v>0</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="DK4" t="n">
-        <v>4</v>
+        <v>4.06</v>
       </c>
       <c r="DL4" t="n">
         <v>0.12</v>
       </c>
       <c r="DM4" t="n">
-        <v>43.31</v>
+        <v>43</v>
       </c>
       <c r="DN4" t="n">
         <v>1.06</v>
       </c>
       <c r="DO4" t="n">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="DP4" t="n">
-        <v>13.69</v>
+        <v>13.71</v>
       </c>
       <c r="DQ4" t="n">
-        <v>14.62</v>
+        <v>14.47</v>
       </c>
       <c r="DR4" t="n">
-        <v>9</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.38</v>
+        <v>0.35</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.38</v>
+        <v>0.35</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>47.94</v>
+        <v>48.29</v>
       </c>
       <c r="DW4" t="n">
         <v>0</v>
       </c>
       <c r="DX4" t="n">
-        <v>9.630000000000001</v>
+        <v>9.83</v>
       </c>
       <c r="DY4" t="n">
-        <v>6.75</v>
+        <v>6.94</v>
       </c>
       <c r="DZ4" t="n">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="EA4" t="n">
-        <v>24.19</v>
+        <v>24.53</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
     </row>
     <row r="5">
@@ -3523,7 +3523,7 @@
         <v>12.11</v>
       </c>
       <c r="AS7" t="n">
-        <v>10.44</v>
+        <v>10.56</v>
       </c>
       <c r="AT7" t="n">
         <v>1.56</v>
@@ -3541,7 +3541,7 @@
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>43</v>
+        <v>43.11</v>
       </c>
       <c r="AZ7" t="n">
         <v>0.11</v>
@@ -3556,7 +3556,7 @@
         <v>5</v>
       </c>
       <c r="BD7" t="n">
-        <v>17.67</v>
+        <v>17.78</v>
       </c>
       <c r="BE7" t="n">
         <v>1.34</v>
@@ -3754,7 +3754,7 @@
         <v>12.65</v>
       </c>
       <c r="DR7" t="n">
-        <v>9.41</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="DS7" t="n">
         <v>0.12</v>
@@ -3766,7 +3766,7 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>47</v>
+        <v>47.06</v>
       </c>
       <c r="DW7" t="n">
         <v>0.11</v>
@@ -3781,7 +3781,7 @@
         <v>4.06</v>
       </c>
       <c r="EA7" t="n">
-        <v>18.35</v>
+        <v>18.41</v>
       </c>
       <c r="EB7" t="n">
         <v>1.26</v>
@@ -4362,7 +4362,7 @@
         <v>4.44</v>
       </c>
       <c r="BD9" t="n">
-        <v>23.22</v>
+        <v>23.33</v>
       </c>
       <c r="BE9" t="n">
         <v>1.43</v>
@@ -4587,7 +4587,7 @@
         <v>4.76</v>
       </c>
       <c r="EA9" t="n">
-        <v>22.35</v>
+        <v>22.41</v>
       </c>
       <c r="EB9" t="n">
         <v>1.61</v>
@@ -4684,7 +4684,7 @@
         <v>4.38</v>
       </c>
       <c r="AC10" t="n">
-        <v>18.75</v>
+        <v>18.88</v>
       </c>
       <c r="AD10" t="n">
         <v>1.37</v>
@@ -4990,7 +4990,7 @@
         <v>4.77</v>
       </c>
       <c r="EA10" t="n">
-        <v>16.35</v>
+        <v>16.41</v>
       </c>
       <c r="EB10" t="n">
         <v>1.38</v>
@@ -5490,7 +5490,7 @@
         <v>3.78</v>
       </c>
       <c r="AC12" t="n">
-        <v>22.67</v>
+        <v>22.78</v>
       </c>
       <c r="AD12" t="n">
         <v>1.52</v>
@@ -5796,7 +5796,7 @@
         <v>3.59</v>
       </c>
       <c r="EA12" t="n">
-        <v>21.77</v>
+        <v>21.82</v>
       </c>
       <c r="EB12" t="n">
         <v>1.34</v>
@@ -6215,13 +6215,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C14" t="n">
         <v>8</v>
       </c>
       <c r="D14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -6305,139 +6305,139 @@
         <v>4</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AH14" t="n">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="AI14" t="n">
-        <v>76.5</v>
+        <v>78.89</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AK14" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="AL14" t="n">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AN14" t="n">
-        <v>29.5</v>
+        <v>29.78</v>
       </c>
       <c r="AO14" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AQ14" t="n">
-        <v>14.25</v>
+        <v>13.89</v>
       </c>
       <c r="AR14" t="n">
-        <v>13.25</v>
+        <v>13.22</v>
       </c>
       <c r="AS14" t="n">
-        <v>11.38</v>
+        <v>10.89</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AX14" t="n">
         <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>35.5</v>
+        <v>37.33</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="BA14" t="n">
-        <v>9.119999999999999</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="BB14" t="n">
+        <v>6.44</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>17.22</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>8.18</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>88.23999999999999</v>
+      </c>
+      <c r="BS14" t="n">
+        <v>64.70999999999999</v>
+      </c>
+      <c r="BT14" t="n">
+        <v>41.18</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>29.41</v>
+      </c>
+      <c r="BV14" t="n">
+        <v>23.53</v>
+      </c>
+      <c r="BW14" t="n">
         <v>5.88</v>
       </c>
-      <c r="BC14" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>17.38</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="BG14" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="BH14" t="n">
-        <v>8.380000000000001</v>
-      </c>
-      <c r="BI14" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="BJ14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="BK14" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="BL14" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="BM14" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="BN14" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="BO14" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="BP14" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="BQ14" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="BR14" t="n">
-        <v>93.75</v>
-      </c>
-      <c r="BS14" t="n">
-        <v>68.75</v>
-      </c>
-      <c r="BT14" t="n">
-        <v>43.75</v>
-      </c>
-      <c r="BU14" t="n">
-        <v>31.25</v>
-      </c>
-      <c r="BV14" t="n">
-        <v>25</v>
-      </c>
-      <c r="BW14" t="n">
-        <v>6.25</v>
-      </c>
       <c r="BX14" t="n">
-        <v>56.25</v>
+        <v>52.94</v>
       </c>
       <c r="BY14" t="n">
         <v>2.94</v>
@@ -6446,16 +6446,16 @@
         <v>3.36</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.16</v>
+        <v>3.2</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.36</v>
+        <v>3.4</v>
       </c>
       <c r="CC14" t="n">
-        <v>4.68</v>
+        <v>4.87</v>
       </c>
       <c r="CD14" t="n">
-        <v>5.09</v>
+        <v>5.25</v>
       </c>
       <c r="CE14" t="n">
         <v>1.48</v>
@@ -6464,22 +6464,22 @@
         <v>3.23</v>
       </c>
       <c r="CG14" t="n">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="CH14" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="CI14" t="n">
         <v>1.74</v>
       </c>
       <c r="CJ14" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="CK14" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="CL14" t="n">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="CM14" t="n">
         <v>2.1</v>
@@ -6488,43 +6488,43 @@
         <v>1.68</v>
       </c>
       <c r="CO14" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CP14" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="CQ14" t="n">
-        <v>4.32</v>
+        <v>4.31</v>
       </c>
       <c r="CR14" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CS14" t="n">
         <v>3.28</v>
       </c>
       <c r="CT14" t="n">
-        <v>2.64</v>
+        <v>2.65</v>
       </c>
       <c r="CU14" t="n">
         <v>1.36</v>
       </c>
       <c r="CV14" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CW14" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="CX14" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CY14" t="n">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="CZ14" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="DA14" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="DB14" t="n">
         <v>1.44</v>
@@ -6533,49 +6533,49 @@
         <v>2.36</v>
       </c>
       <c r="DD14" t="n">
-        <v>4.49</v>
+        <v>4.47</v>
       </c>
       <c r="DE14" t="n">
         <v>0.06</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="DG14" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="DH14" t="n">
-        <v>87.62</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="DI14" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ14" t="n">
-        <v>3.38</v>
+        <v>3.35</v>
       </c>
       <c r="DK14" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DM14" t="n">
-        <v>35.56</v>
+        <v>35.35</v>
       </c>
       <c r="DN14" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="DO14" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="DP14" t="n">
-        <v>15.82</v>
+        <v>15.53</v>
       </c>
       <c r="DQ14" t="n">
         <v>12.88</v>
       </c>
       <c r="DR14" t="n">
-        <v>9.32</v>
+        <v>9.18</v>
       </c>
       <c r="DS14" t="n">
         <v>0.12</v>
@@ -6587,25 +6587,25 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>41.62</v>
+        <v>42.23</v>
       </c>
       <c r="DW14" t="n">
         <v>0.12</v>
       </c>
       <c r="DX14" t="n">
-        <v>11</v>
+        <v>11.24</v>
       </c>
       <c r="DY14" t="n">
-        <v>7.32</v>
+        <v>7.53</v>
       </c>
       <c r="DZ14" t="n">
-        <v>3.68</v>
+        <v>3.7</v>
       </c>
       <c r="EA14" t="n">
-        <v>16.88</v>
+        <v>16.82</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="EC14" t="n">
         <v>3.12</v>
@@ -6618,94 +6618,94 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D15" t="n">
         <v>8</v>
       </c>
       <c r="E15" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="F15" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="G15" t="n">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="H15" t="n">
-        <v>91.25</v>
+        <v>88.22</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="K15" t="n">
+        <v>4</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="M15" t="n">
+        <v>48.33</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="P15" t="n">
+        <v>13.56</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>12.89</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7.56</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>53</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>15.11</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>9.109999999999999</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>21.22</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AE15" t="n">
         <v>2</v>
-      </c>
-      <c r="K15" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="M15" t="n">
-        <v>49.38</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="O15" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="P15" t="n">
-        <v>13.88</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>13.62</v>
-      </c>
-      <c r="R15" t="n">
-        <v>7</v>
-      </c>
-      <c r="S15" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" t="n">
-        <v>0</v>
-      </c>
-      <c r="W15" t="n">
-        <v>0</v>
-      </c>
-      <c r="X15" t="n">
-        <v>54.88</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>14.62</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>8.75</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>5.88</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>22</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.75</v>
       </c>
       <c r="AF15" t="n">
         <v>0.12</v>
@@ -6789,70 +6789,70 @@
         <v>2</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.56</v>
+        <v>2.53</v>
       </c>
       <c r="BH15" t="n">
-        <v>8.19</v>
+        <v>8.41</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.56</v>
+        <v>2.53</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="BL15" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.59</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="BO15" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="BP15" t="n">
-        <v>3.44</v>
+        <v>3.59</v>
       </c>
       <c r="BQ15" t="n">
-        <v>4.75</v>
+        <v>4.82</v>
       </c>
       <c r="BR15" t="n">
         <v>100</v>
       </c>
       <c r="BS15" t="n">
-        <v>68.75</v>
+        <v>70.59</v>
       </c>
       <c r="BT15" t="n">
-        <v>50</v>
+        <v>47.06</v>
       </c>
       <c r="BU15" t="n">
-        <v>25</v>
+        <v>23.53</v>
       </c>
       <c r="BV15" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BW15" t="n">
         <v>0</v>
       </c>
       <c r="BX15" t="n">
-        <v>50</v>
+        <v>52.94</v>
       </c>
       <c r="BY15" t="n">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="BZ15" t="n">
         <v>2.23</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.23</v>
+        <v>3.21</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.37</v>
+        <v>3.35</v>
       </c>
       <c r="CC15" t="n">
         <v>4.08</v>
@@ -6867,25 +6867,25 @@
         <v>3.14</v>
       </c>
       <c r="CG15" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="CH15" t="n">
         <v>1.33</v>
       </c>
       <c r="CI15" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CJ15" t="n">
         <v>1.98</v>
       </c>
       <c r="CK15" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CL15" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="CN15" t="n">
         <v>1.74</v>
@@ -6897,16 +6897,16 @@
         <v>2.24</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.97</v>
+        <v>3.96</v>
       </c>
       <c r="CR15" t="n">
         <v>1.49</v>
       </c>
       <c r="CS15" t="n">
-        <v>3.2</v>
+        <v>3.22</v>
       </c>
       <c r="CT15" t="n">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="CU15" t="n">
         <v>1.37</v>
@@ -6939,46 +6939,46 @@
         <v>4.31</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="DG15" t="n">
-        <v>2.31</v>
+        <v>2.35</v>
       </c>
       <c r="DH15" t="n">
-        <v>89.75</v>
+        <v>88.23</v>
       </c>
       <c r="DI15" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ15" t="n">
-        <v>2.31</v>
+        <v>2.41</v>
       </c>
       <c r="DK15" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.12</v>
+        <v>0.23</v>
       </c>
       <c r="DM15" t="n">
-        <v>47.94</v>
+        <v>47.47</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="DO15" t="n">
-        <v>1.44</v>
+        <v>1.65</v>
       </c>
       <c r="DP15" t="n">
-        <v>13.63</v>
+        <v>13.48</v>
       </c>
       <c r="DQ15" t="n">
-        <v>13.25</v>
+        <v>12.89</v>
       </c>
       <c r="DR15" t="n">
-        <v>7.75</v>
+        <v>8</v>
       </c>
       <c r="DS15" t="n">
         <v>0.06</v>
@@ -6990,28 +6990,28 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>52.69</v>
+        <v>51.82</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DX15" t="n">
-        <v>12.06</v>
+        <v>12.47</v>
       </c>
       <c r="DY15" t="n">
-        <v>7.68</v>
+        <v>7.94</v>
       </c>
       <c r="DZ15" t="n">
-        <v>4.38</v>
+        <v>4.53</v>
       </c>
       <c r="EA15" t="n">
-        <v>22.94</v>
+        <v>22.47</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="EC15" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -7490,7 +7490,7 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>45.44</v>
+        <v>45.33</v>
       </c>
       <c r="Y17" t="n">
         <v>0</v>
@@ -7796,7 +7796,7 @@
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>44.71</v>
+        <v>44.65</v>
       </c>
       <c r="DW17" t="n">
         <v>0.06</v>
@@ -8230,13 +8230,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C19" t="n">
         <v>8</v>
       </c>
       <c r="D19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -8320,139 +8320,139 @@
         <v>2.88</v>
       </c>
       <c r="AF19" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AG19" t="n">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="AH19" t="n">
-        <v>3.38</v>
+        <v>3.33</v>
       </c>
       <c r="AI19" t="n">
-        <v>88</v>
+        <v>89.67</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AK19" t="n">
-        <v>2.62</v>
+        <v>3</v>
       </c>
       <c r="AL19" t="n">
-        <v>5.62</v>
+        <v>5.44</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AN19" t="n">
-        <v>41</v>
+        <v>42.22</v>
       </c>
       <c r="AO19" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AP19" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="AQ19" t="n">
-        <v>14</v>
+        <v>13.22</v>
       </c>
       <c r="AR19" t="n">
-        <v>16.5</v>
+        <v>15.78</v>
       </c>
       <c r="AS19" t="n">
-        <v>6.25</v>
+        <v>6.56</v>
       </c>
       <c r="AT19" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AU19" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AV19" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="AW19" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="AX19" t="n">
         <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>47.62</v>
+        <v>49.22</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="BA19" t="n">
-        <v>12.75</v>
+        <v>13</v>
       </c>
       <c r="BB19" t="n">
-        <v>9.619999999999999</v>
+        <v>9.67</v>
       </c>
       <c r="BC19" t="n">
-        <v>3.12</v>
+        <v>3.33</v>
       </c>
       <c r="BD19" t="n">
-        <v>18</v>
+        <v>17.78</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="BF19" t="n">
-        <v>2.5</v>
+        <v>2.67</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.44</v>
+        <v>2.41</v>
       </c>
       <c r="BH19" t="n">
-        <v>9.94</v>
+        <v>10.06</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.44</v>
+        <v>2.41</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.38</v>
+        <v>0.41</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.44</v>
+        <v>0.41</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="BM19" t="n">
         <v>0.88</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="BO19" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="BP19" t="n">
-        <v>5.25</v>
+        <v>5.29</v>
       </c>
       <c r="BQ19" t="n">
-        <v>4.62</v>
+        <v>4.71</v>
       </c>
       <c r="BR19" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BS19" t="n">
-        <v>56.25</v>
+        <v>58.82</v>
       </c>
       <c r="BT19" t="n">
-        <v>37.5</v>
+        <v>35.29</v>
       </c>
       <c r="BU19" t="n">
-        <v>31.25</v>
+        <v>29.41</v>
       </c>
       <c r="BV19" t="n">
-        <v>18.75</v>
+        <v>17.65</v>
       </c>
       <c r="BW19" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BX19" t="n">
-        <v>43.75</v>
+        <v>47.06</v>
       </c>
       <c r="BY19" t="n">
         <v>2.31</v>
@@ -8461,16 +8461,16 @@
         <v>2.46</v>
       </c>
       <c r="CA19" t="n">
-        <v>3.2</v>
+        <v>3.19</v>
       </c>
       <c r="CB19" t="n">
-        <v>3.33</v>
+        <v>3.31</v>
       </c>
       <c r="CC19" t="n">
-        <v>3.81</v>
+        <v>3.75</v>
       </c>
       <c r="CD19" t="n">
-        <v>4.48</v>
+        <v>4.39</v>
       </c>
       <c r="CE19" t="n">
         <v>1.46</v>
@@ -8479,22 +8479,22 @@
         <v>3.13</v>
       </c>
       <c r="CG19" t="n">
-        <v>2.63</v>
+        <v>2.61</v>
       </c>
       <c r="CH19" t="n">
         <v>1.33</v>
       </c>
       <c r="CI19" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CJ19" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CK19" t="n">
         <v>1.59</v>
       </c>
       <c r="CL19" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="CM19" t="n">
         <v>2.3</v>
@@ -8509,13 +8509,13 @@
         <v>2.22</v>
       </c>
       <c r="CQ19" t="n">
-        <v>4.03</v>
+        <v>4.01</v>
       </c>
       <c r="CR19" t="n">
         <v>1.49</v>
       </c>
       <c r="CS19" t="n">
-        <v>3.2</v>
+        <v>3.22</v>
       </c>
       <c r="CT19" t="n">
         <v>2.74</v>
@@ -8545,85 +8545,85 @@
         <v>1.39</v>
       </c>
       <c r="DC19" t="n">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="DD19" t="n">
-        <v>4.04</v>
+        <v>4.06</v>
       </c>
       <c r="DE19" t="n">
         <v>0.06</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="DG19" t="n">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="DH19" t="n">
-        <v>92</v>
+        <v>92.65000000000001</v>
       </c>
       <c r="DI19" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="DJ19" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="DK19" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="DL19" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="DM19" t="n">
+        <v>42.7</v>
+      </c>
+      <c r="DN19" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="DO19" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="DP19" t="n">
+        <v>13.06</v>
+      </c>
+      <c r="DQ19" t="n">
+        <v>15.36</v>
+      </c>
+      <c r="DR19" t="n">
+        <v>6.82</v>
+      </c>
+      <c r="DS19" t="n">
         <v>0.12</v>
       </c>
-      <c r="DJ19" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="DK19" t="n">
-        <v>4.81</v>
-      </c>
-      <c r="DL19" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="DM19" t="n">
-        <v>42.12</v>
-      </c>
-      <c r="DN19" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="DO19" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="DP19" t="n">
-        <v>13.44</v>
-      </c>
-      <c r="DQ19" t="n">
-        <v>15.69</v>
-      </c>
-      <c r="DR19" t="n">
-        <v>6.68</v>
-      </c>
-      <c r="DS19" t="n">
-        <v>0.06</v>
-      </c>
       <c r="DT19" t="n">
-        <v>0.06</v>
+        <v>0.12</v>
       </c>
       <c r="DU19" t="n">
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>49.44</v>
+        <v>50.18</v>
       </c>
       <c r="DW19" t="n">
-        <v>0.37</v>
+        <v>0.41</v>
       </c>
       <c r="DX19" t="n">
-        <v>11.93</v>
+        <v>12.12</v>
       </c>
       <c r="DY19" t="n">
-        <v>8.43</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="DZ19" t="n">
-        <v>3.5</v>
+        <v>3.59</v>
       </c>
       <c r="EA19" t="n">
-        <v>20.56</v>
+        <v>20.29</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="EC19" t="n">
-        <v>2.69</v>
+        <v>2.77</v>
       </c>
     </row>
     <row r="20">
@@ -8699,7 +8699,7 @@
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>55.33</v>
+        <v>55.22</v>
       </c>
       <c r="Y20" t="n">
         <v>0</v>
@@ -9005,7 +9005,7 @@
         <v>0</v>
       </c>
       <c r="DV20" t="n">
-        <v>52.77</v>
+        <v>52.71</v>
       </c>
       <c r="DW20" t="n">
         <v>0.12</v>
@@ -9586,7 +9586,7 @@
         <v>0</v>
       </c>
       <c r="AY22" t="n">
-        <v>42.62</v>
+        <v>42.75</v>
       </c>
       <c r="AZ22" t="n">
         <v>0.25</v>
@@ -9811,7 +9811,7 @@
         <v>0</v>
       </c>
       <c r="DV22" t="n">
-        <v>43.88</v>
+        <v>43.94</v>
       </c>
       <c r="DW22" t="n">
         <v>0.23</v>
@@ -9842,61 +9842,61 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C23" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D23" t="n">
         <v>8</v>
       </c>
       <c r="E23" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="F23" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="G23" t="n">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="H23" t="n">
-        <v>96.62</v>
+        <v>96.89</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="K23" t="n">
-        <v>4.25</v>
+        <v>4</v>
       </c>
       <c r="L23" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="M23" t="n">
-        <v>39.25</v>
+        <v>38.56</v>
       </c>
       <c r="N23" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="O23" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="P23" t="n">
-        <v>13.88</v>
+        <v>13.78</v>
       </c>
       <c r="Q23" t="n">
-        <v>17</v>
+        <v>16.33</v>
       </c>
       <c r="R23" t="n">
-        <v>6.12</v>
+        <v>6.11</v>
       </c>
       <c r="S23" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="T23" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="U23" t="n">
         <v>0</v>
@@ -9908,28 +9908,28 @@
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>56.12</v>
+        <v>55.22</v>
       </c>
       <c r="Y23" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="Z23" t="n">
-        <v>12.5</v>
+        <v>12.22</v>
       </c>
       <c r="AA23" t="n">
-        <v>8</v>
+        <v>7.89</v>
       </c>
       <c r="AB23" t="n">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="AC23" t="n">
-        <v>19.38</v>
+        <v>19.22</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AF23" t="n">
         <v>0</v>
@@ -10013,49 +10013,49 @@
         <v>2</v>
       </c>
       <c r="BG23" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="BH23" t="n">
-        <v>7.75</v>
+        <v>7.59</v>
       </c>
       <c r="BI23" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="BJ23" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="BK23" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="BL23" t="n">
-        <v>0.38</v>
+        <v>0.35</v>
       </c>
       <c r="BM23" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BN23" t="n">
-        <v>0.88</v>
+        <v>0.82</v>
       </c>
       <c r="BO23" t="n">
-        <v>0.88</v>
+        <v>0.82</v>
       </c>
       <c r="BP23" t="n">
-        <v>3.62</v>
+        <v>3.53</v>
       </c>
       <c r="BQ23" t="n">
-        <v>4.12</v>
+        <v>4.06</v>
       </c>
       <c r="BR23" t="n">
-        <v>81.25</v>
+        <v>76.47</v>
       </c>
       <c r="BS23" t="n">
-        <v>43.75</v>
+        <v>41.18</v>
       </c>
       <c r="BT23" t="n">
-        <v>31.25</v>
+        <v>29.41</v>
       </c>
       <c r="BU23" t="n">
-        <v>18.75</v>
+        <v>17.65</v>
       </c>
       <c r="BV23" t="n">
         <v>0</v>
@@ -10064,19 +10064,19 @@
         <v>0</v>
       </c>
       <c r="BX23" t="n">
-        <v>43.75</v>
+        <v>41.18</v>
       </c>
       <c r="BY23" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="BZ23" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="CA23" t="n">
-        <v>3.2</v>
+        <v>3.24</v>
       </c>
       <c r="CB23" t="n">
-        <v>3.33</v>
+        <v>3.37</v>
       </c>
       <c r="CC23" t="n">
         <v>3.11</v>
@@ -10097,16 +10097,16 @@
         <v>1.32</v>
       </c>
       <c r="CI23" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CJ23" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="CK23" t="n">
         <v>1.68</v>
       </c>
       <c r="CL23" t="n">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="CM23" t="n">
         <v>2.09</v>
@@ -10115,7 +10115,7 @@
         <v>1.68</v>
       </c>
       <c r="CO23" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CP23" t="n">
         <v>2.2</v>
@@ -10127,7 +10127,7 @@
         <v>1.51</v>
       </c>
       <c r="CS23" t="n">
-        <v>3.19</v>
+        <v>3.2</v>
       </c>
       <c r="CT23" t="n">
         <v>2.69</v>
@@ -10136,73 +10136,73 @@
         <v>1.37</v>
       </c>
       <c r="CV23" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CW23" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="CX23" t="n">
         <v>1.75</v>
       </c>
       <c r="CY23" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="CZ23" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="DA23" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="DB23" t="n">
         <v>1.44</v>
       </c>
       <c r="DC23" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="DD23" t="n">
-        <v>4.53</v>
+        <v>4.5</v>
       </c>
       <c r="DE23" t="n">
         <v>0.06</v>
       </c>
       <c r="DF23" t="n">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="DG23" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="DH23" t="n">
-        <v>93.18000000000001</v>
+        <v>93.53</v>
       </c>
       <c r="DI23" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ23" t="n">
-        <v>2.12</v>
+        <v>2.17</v>
       </c>
       <c r="DK23" t="n">
-        <v>4</v>
+        <v>3.88</v>
       </c>
       <c r="DL23" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DM23" t="n">
-        <v>36.75</v>
+        <v>36.53</v>
       </c>
       <c r="DN23" t="n">
-        <v>0.44</v>
+        <v>0.47</v>
       </c>
       <c r="DO23" t="n">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="DP23" t="n">
-        <v>12.88</v>
+        <v>12.89</v>
       </c>
       <c r="DQ23" t="n">
-        <v>18.12</v>
+        <v>17.7</v>
       </c>
       <c r="DR23" t="n">
-        <v>7.81</v>
+        <v>7.71</v>
       </c>
       <c r="DS23" t="n">
         <v>0</v>
@@ -10214,28 +10214,28 @@
         <v>0</v>
       </c>
       <c r="DV23" t="n">
-        <v>56.62</v>
+        <v>56.11</v>
       </c>
       <c r="DW23" t="n">
-        <v>0.19</v>
+        <v>0.23</v>
       </c>
       <c r="DX23" t="n">
-        <v>11.31</v>
+        <v>11.23</v>
       </c>
       <c r="DY23" t="n">
-        <v>7.69</v>
+        <v>7.65</v>
       </c>
       <c r="DZ23" t="n">
-        <v>3.62</v>
+        <v>3.59</v>
       </c>
       <c r="EA23" t="n">
-        <v>18.63</v>
+        <v>18.59</v>
       </c>
       <c r="EB23" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="EC23" t="n">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Spain_Segunda_División_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Spain_Segunda_División_2025-2026.xlsx
@@ -2711,7 +2711,7 @@
         <v>3.11</v>
       </c>
       <c r="AQ5" t="n">
-        <v>13.11</v>
+        <v>12.89</v>
       </c>
       <c r="AR5" t="n">
         <v>14.33</v>
@@ -2942,7 +2942,7 @@
         <v>3.53</v>
       </c>
       <c r="DP5" t="n">
-        <v>13.11</v>
+        <v>13</v>
       </c>
       <c r="DQ5" t="n">
         <v>14.41</v>
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D7" t="n">
         <v>9</v>
@@ -3406,82 +3406,82 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="G7" t="n">
-        <v>3.5</v>
+        <v>3.33</v>
       </c>
       <c r="H7" t="n">
-        <v>90</v>
+        <v>90.11</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="K7" t="n">
-        <v>4.75</v>
+        <v>4.78</v>
       </c>
       <c r="L7" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="M7" t="n">
-        <v>40.25</v>
+        <v>41.11</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="P7" t="n">
-        <v>13</v>
+        <v>12.33</v>
       </c>
       <c r="Q7" t="n">
-        <v>13.25</v>
+        <v>13.11</v>
       </c>
       <c r="R7" t="n">
-        <v>8.25</v>
+        <v>7.89</v>
       </c>
       <c r="S7" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>52.56</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>11.11</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>7.67</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>19.11</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AE7" t="n">
         <v>1</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" t="n">
-        <v>0</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" t="n">
-        <v>51.5</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>10.38</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>7.38</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>19.12</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.12</v>
       </c>
       <c r="AF7" t="n">
         <v>0.22</v>
@@ -3565,70 +3565,70 @@
         <v>1.78</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.47</v>
+        <v>2.44</v>
       </c>
       <c r="BH7" t="n">
-        <v>8.94</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.47</v>
+        <v>2.44</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.53</v>
+        <v>0.61</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="BP7" t="n">
-        <v>3.71</v>
+        <v>3.89</v>
       </c>
       <c r="BQ7" t="n">
-        <v>5.24</v>
+        <v>5.22</v>
       </c>
       <c r="BR7" t="n">
-        <v>88.23999999999999</v>
+        <v>88.89</v>
       </c>
       <c r="BS7" t="n">
-        <v>47.06</v>
+        <v>50</v>
       </c>
       <c r="BT7" t="n">
-        <v>47.06</v>
+        <v>44.44</v>
       </c>
       <c r="BU7" t="n">
-        <v>29.41</v>
+        <v>27.78</v>
       </c>
       <c r="BV7" t="n">
-        <v>23.53</v>
+        <v>22.22</v>
       </c>
       <c r="BW7" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BX7" t="n">
-        <v>35.29</v>
+        <v>33.33</v>
       </c>
       <c r="BY7" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="BZ7" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.39</v>
+        <v>3.36</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.54</v>
+        <v>3.5</v>
       </c>
       <c r="CC7" t="n">
         <v>4.96</v>
@@ -3637,43 +3637,43 @@
         <v>5.55</v>
       </c>
       <c r="CE7" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.91</v>
+        <v>2.95</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.79</v>
+        <v>2.76</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CI7" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CJ7" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="CK7" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CL7" t="n">
         <v>2.02</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="CN7" t="n">
         <v>1.79</v>
       </c>
       <c r="CO7" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="CP7" t="n">
-        <v>2.06</v>
+        <v>2.09</v>
       </c>
       <c r="CQ7" t="n">
-        <v>3.59</v>
+        <v>3.67</v>
       </c>
       <c r="CR7" t="n">
         <v>1.45</v>
@@ -3688,10 +3688,10 @@
         <v>1.39</v>
       </c>
       <c r="CV7" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CW7" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="CX7" t="n">
         <v>1.63</v>
@@ -3706,88 +3706,88 @@
         <v>1.79</v>
       </c>
       <c r="DB7" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="DC7" t="n">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="DD7" t="n">
-        <v>3.78</v>
+        <v>3.87</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="DG7" t="n">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="DH7" t="n">
-        <v>81.65000000000001</v>
+        <v>82.16</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DJ7" t="n">
-        <v>1.71</v>
+        <v>1.61</v>
       </c>
       <c r="DK7" t="n">
-        <v>4.06</v>
+        <v>4.11</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="DM7" t="n">
-        <v>35.88</v>
+        <v>36.56</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.3</v>
+        <v>0.28</v>
       </c>
       <c r="DO7" t="n">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="DP7" t="n">
-        <v>12.65</v>
+        <v>12.33</v>
       </c>
       <c r="DQ7" t="n">
-        <v>12.65</v>
+        <v>12.61</v>
       </c>
       <c r="DR7" t="n">
-        <v>9.470000000000001</v>
+        <v>9.23</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>47.06</v>
+        <v>47.84</v>
       </c>
       <c r="DW7" t="n">
         <v>0.11</v>
       </c>
       <c r="DX7" t="n">
-        <v>11.24</v>
+        <v>11.56</v>
       </c>
       <c r="DY7" t="n">
-        <v>7.18</v>
+        <v>7.34</v>
       </c>
       <c r="DZ7" t="n">
-        <v>4.06</v>
+        <v>4.22</v>
       </c>
       <c r="EA7" t="n">
-        <v>18.41</v>
+        <v>18.44</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="EC7" t="n">
-        <v>1.47</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="8">
@@ -4353,10 +4353,10 @@
         <v>0.11</v>
       </c>
       <c r="BA9" t="n">
-        <v>13</v>
+        <v>12.89</v>
       </c>
       <c r="BB9" t="n">
-        <v>8.56</v>
+        <v>8.44</v>
       </c>
       <c r="BC9" t="n">
         <v>4.44</v>
@@ -4365,7 +4365,7 @@
         <v>23.33</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="BF9" t="n">
         <v>3</v>
@@ -4578,10 +4578,10 @@
         <v>0.18</v>
       </c>
       <c r="DX9" t="n">
-        <v>14.76</v>
+        <v>14.71</v>
       </c>
       <c r="DY9" t="n">
-        <v>10</v>
+        <v>9.94</v>
       </c>
       <c r="DZ9" t="n">
         <v>4.76</v>
@@ -4590,7 +4590,7 @@
         <v>22.41</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="EC9" t="n">
         <v>2.88</v>
@@ -8705,10 +8705,10 @@
         <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>17</v>
+        <v>17.11</v>
       </c>
       <c r="AA20" t="n">
-        <v>11.22</v>
+        <v>11.33</v>
       </c>
       <c r="AB20" t="n">
         <v>5.78</v>
@@ -8717,7 +8717,7 @@
         <v>18.33</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AE20" t="n">
         <v>2.56</v>
@@ -9011,10 +9011,10 @@
         <v>0.12</v>
       </c>
       <c r="DX20" t="n">
-        <v>13.82</v>
+        <v>13.88</v>
       </c>
       <c r="DY20" t="n">
-        <v>9.18</v>
+        <v>9.24</v>
       </c>
       <c r="DZ20" t="n">
         <v>4.65</v>
@@ -9023,7 +9023,7 @@
         <v>18.88</v>
       </c>
       <c r="EB20" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="EC20" t="n">
         <v>2.41</v>
@@ -9036,13 +9036,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C21" t="n">
         <v>9</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -9129,49 +9129,49 @@
         <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AH21" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AI21" t="n">
-        <v>80.62</v>
+        <v>80.67</v>
       </c>
       <c r="AJ21" t="n">
         <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AL21" t="n">
-        <v>3.25</v>
+        <v>3.67</v>
       </c>
       <c r="AM21" t="n">
-        <v>0.38</v>
+        <v>0.78</v>
       </c>
       <c r="AN21" t="n">
-        <v>32.88</v>
+        <v>32.33</v>
       </c>
       <c r="AO21" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.25</v>
+        <v>1.56</v>
       </c>
       <c r="AQ21" t="n">
-        <v>10.25</v>
+        <v>10.56</v>
       </c>
       <c r="AR21" t="n">
-        <v>13.38</v>
+        <v>12.67</v>
       </c>
       <c r="AS21" t="n">
-        <v>7.75</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="AT21" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AU21" t="n">
-        <v>0.38</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AV21" t="n">
         <v>0</v>
@@ -9183,82 +9183,82 @@
         <v>0</v>
       </c>
       <c r="AY21" t="n">
-        <v>46.75</v>
+        <v>45.89</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="BA21" t="n">
-        <v>8.880000000000001</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="BB21" t="n">
-        <v>7.38</v>
+        <v>7</v>
       </c>
       <c r="BC21" t="n">
-        <v>1.5</v>
+        <v>1.78</v>
       </c>
       <c r="BD21" t="n">
-        <v>18.12</v>
+        <v>17.33</v>
       </c>
       <c r="BE21" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="BG21" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="BH21" t="n">
-        <v>9.470000000000001</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="BI21" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="BJ21" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BK21" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="BL21" t="n">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="BM21" t="n">
-        <v>0.35</v>
+        <v>0.44</v>
       </c>
       <c r="BN21" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="BO21" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="BP21" t="n">
-        <v>4.18</v>
+        <v>4.33</v>
       </c>
       <c r="BQ21" t="n">
-        <v>5.24</v>
+        <v>5.22</v>
       </c>
       <c r="BR21" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BS21" t="n">
-        <v>64.70999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="BT21" t="n">
-        <v>41.18</v>
+        <v>38.89</v>
       </c>
       <c r="BU21" t="n">
-        <v>17.65</v>
+        <v>16.67</v>
       </c>
       <c r="BV21" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BW21" t="n">
         <v>0</v>
       </c>
       <c r="BX21" t="n">
-        <v>47.06</v>
+        <v>44.44</v>
       </c>
       <c r="BY21" t="n">
         <v>2.47</v>
@@ -9270,19 +9270,19 @@
         <v>2.89</v>
       </c>
       <c r="CB21" t="n">
-        <v>3.02</v>
+        <v>3.01</v>
       </c>
       <c r="CC21" t="n">
-        <v>3.48</v>
+        <v>3.44</v>
       </c>
       <c r="CD21" t="n">
-        <v>3.96</v>
+        <v>3.92</v>
       </c>
       <c r="CE21" t="n">
         <v>1.58</v>
       </c>
       <c r="CF21" t="n">
-        <v>3.74</v>
+        <v>3.73</v>
       </c>
       <c r="CG21" t="n">
         <v>2.29</v>
@@ -9297,25 +9297,25 @@
         <v>2.19</v>
       </c>
       <c r="CK21" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="CL21" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="CM21" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="CN21" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CO21" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CP21" t="n">
         <v>2.62</v>
       </c>
       <c r="CQ21" t="n">
-        <v>5.14</v>
+        <v>5.13</v>
       </c>
       <c r="CR21" t="n">
         <v>1.63</v>
@@ -9336,13 +9336,13 @@
         <v>2.28</v>
       </c>
       <c r="CX21" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CY21" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="CZ21" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="DA21" t="n">
         <v>1.65</v>
@@ -9351,85 +9351,85 @@
         <v>1.6</v>
       </c>
       <c r="DC21" t="n">
-        <v>2.86</v>
+        <v>2.85</v>
       </c>
       <c r="DD21" t="n">
-        <v>5.79</v>
+        <v>5.77</v>
       </c>
       <c r="DE21" t="n">
         <v>0</v>
       </c>
       <c r="DF21" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="DG21" t="n">
-        <v>2.41</v>
+        <v>2.44</v>
       </c>
       <c r="DH21" t="n">
-        <v>90.23</v>
+        <v>89.72</v>
       </c>
       <c r="DI21" t="n">
         <v>0</v>
       </c>
       <c r="DJ21" t="n">
+        <v>2</v>
+      </c>
+      <c r="DK21" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="DL21" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="DM21" t="n">
+        <v>38.28</v>
+      </c>
+      <c r="DN21" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="DO21" t="n">
         <v>1.94</v>
       </c>
-      <c r="DK21" t="n">
-        <v>4.29</v>
-      </c>
-      <c r="DL21" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="DM21" t="n">
-        <v>38.88</v>
-      </c>
-      <c r="DN21" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="DO21" t="n">
-        <v>1.82</v>
-      </c>
       <c r="DP21" t="n">
-        <v>12.35</v>
+        <v>12.39</v>
       </c>
       <c r="DQ21" t="n">
-        <v>13.3</v>
+        <v>12.94</v>
       </c>
       <c r="DR21" t="n">
-        <v>8.640000000000001</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="DS21" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DT21" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DU21" t="n">
         <v>0</v>
       </c>
       <c r="DV21" t="n">
-        <v>46.65</v>
+        <v>46.22</v>
       </c>
       <c r="DW21" t="n">
         <v>0.06</v>
       </c>
       <c r="DX21" t="n">
-        <v>10.59</v>
+        <v>10.44</v>
       </c>
       <c r="DY21" t="n">
-        <v>7.82</v>
+        <v>7.61</v>
       </c>
       <c r="DZ21" t="n">
-        <v>2.77</v>
+        <v>2.84</v>
       </c>
       <c r="EA21" t="n">
-        <v>21.41</v>
+        <v>20.83</v>
       </c>
       <c r="EB21" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="EC21" t="n">
-        <v>1.82</v>
+        <v>1.89</v>
       </c>
     </row>
     <row r="22">

--- a/data/teams/leagues/Averages_Spain_Segunda_División_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Spain_Segunda_División_2025-2026.xlsx
@@ -1379,10 +1379,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2" t="n">
         <v>9</v>
@@ -1391,49 +1391,49 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="G2" t="n">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="H2" t="n">
-        <v>92</v>
+        <v>91.89</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.12</v>
+        <v>-0.11</v>
       </c>
       <c r="J2" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="K2" t="n">
-        <v>5.5</v>
+        <v>5.56</v>
       </c>
       <c r="L2" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="M2" t="n">
-        <v>45.75</v>
+        <v>45.67</v>
       </c>
       <c r="N2" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="O2" t="n">
-        <v>2.62</v>
+        <v>2.67</v>
       </c>
       <c r="P2" t="n">
-        <v>9.880000000000001</v>
+        <v>9.44</v>
       </c>
       <c r="Q2" t="n">
-        <v>9</v>
+        <v>8.44</v>
       </c>
       <c r="R2" t="n">
-        <v>6.75</v>
+        <v>6.44</v>
       </c>
       <c r="S2" t="n">
-        <v>1.62</v>
+        <v>1.78</v>
       </c>
       <c r="T2" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -1445,28 +1445,28 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>43.62</v>
+        <v>43.56</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="Z2" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AA2" t="n">
-        <v>10.75</v>
+        <v>10.22</v>
       </c>
       <c r="AB2" t="n">
-        <v>4.75</v>
+        <v>4.78</v>
       </c>
       <c r="AC2" t="n">
-        <v>24.75</v>
+        <v>25.22</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="AF2" t="n">
         <v>0.33</v>
@@ -1550,70 +1550,70 @@
         <v>2.56</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="BH2" t="n">
-        <v>10.53</v>
+        <v>10.56</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.41</v>
+        <v>0.44</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.06</v>
+        <v>1.17</v>
       </c>
       <c r="BN2" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="BO2" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="BP2" t="n">
-        <v>5.06</v>
+        <v>5</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.41</v>
+        <v>5.5</v>
       </c>
       <c r="BR2" t="n">
-        <v>82.34999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BS2" t="n">
-        <v>64.70999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="BT2" t="n">
-        <v>52.94</v>
+        <v>55.56</v>
       </c>
       <c r="BU2" t="n">
-        <v>35.29</v>
+        <v>38.89</v>
       </c>
       <c r="BV2" t="n">
-        <v>29.41</v>
+        <v>27.78</v>
       </c>
       <c r="BW2" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BX2" t="n">
-        <v>52.94</v>
+        <v>55.56</v>
       </c>
       <c r="BY2" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="BZ2" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="CA2" t="n">
         <v>3.31</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.53</v>
+        <v>3.52</v>
       </c>
       <c r="CC2" t="n">
         <v>3.85</v>
@@ -1625,7 +1625,7 @@
         <v>1.39</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.73</v>
+        <v>2.74</v>
       </c>
       <c r="CG2" t="n">
         <v>2.89</v>
@@ -1634,43 +1634,43 @@
         <v>1.41</v>
       </c>
       <c r="CI2" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CJ2" t="n">
         <v>1.76</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CL2" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CM2" t="n">
         <v>2.43</v>
       </c>
       <c r="CN2" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CO2" t="n">
         <v>1.28</v>
       </c>
       <c r="CP2" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CQ2" t="n">
-        <v>3.29</v>
+        <v>3.3</v>
       </c>
       <c r="CR2" t="n">
         <v>1.42</v>
       </c>
       <c r="CS2" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="CT2" t="n">
-        <v>3.01</v>
+        <v>3</v>
       </c>
       <c r="CU2" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CV2" t="n">
         <v>2.11</v>
@@ -1682,7 +1682,7 @@
         <v>1.52</v>
       </c>
       <c r="CY2" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CZ2" t="n">
         <v>2.43</v>
@@ -1691,7 +1691,7 @@
         <v>1.93</v>
       </c>
       <c r="DB2" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="DC2" t="n">
         <v>1.99</v>
@@ -1700,46 +1700,46 @@
         <v>3.42</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="DH2" t="n">
-        <v>89.06</v>
+        <v>89.16</v>
       </c>
       <c r="DI2" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="DK2" t="n">
-        <v>4.82</v>
+        <v>4.89</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="DM2" t="n">
-        <v>42.65</v>
+        <v>42.78</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.76</v>
+        <v>0.72</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="DP2" t="n">
-        <v>11.42</v>
+        <v>11.11</v>
       </c>
       <c r="DQ2" t="n">
-        <v>11.29</v>
+        <v>10.88</v>
       </c>
       <c r="DR2" t="n">
-        <v>7.94</v>
+        <v>7.72</v>
       </c>
       <c r="DS2" t="n">
         <v>0.06</v>
@@ -1751,25 +1751,25 @@
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>43.18</v>
+        <v>43.17</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DX2" t="n">
-        <v>13.29</v>
+        <v>13.16</v>
       </c>
       <c r="DY2" t="n">
-        <v>8.59</v>
+        <v>8.44</v>
       </c>
       <c r="DZ2" t="n">
-        <v>4.71</v>
+        <v>4.73</v>
       </c>
       <c r="EA2" t="n">
-        <v>24.41</v>
+        <v>24.67</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="EC2" t="n">
         <v>2.06</v>
@@ -1782,94 +1782,94 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D3" t="n">
         <v>9</v>
       </c>
       <c r="E3" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="F3" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="G3" t="n">
-        <v>4.38</v>
+        <v>4.11</v>
       </c>
       <c r="H3" t="n">
-        <v>101.25</v>
+        <v>103.67</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="K3" t="n">
-        <v>8.75</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="L3" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="M3" t="n">
-        <v>58.62</v>
+        <v>58.11</v>
       </c>
       <c r="N3" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="O3" t="n">
-        <v>4.25</v>
+        <v>3.89</v>
       </c>
       <c r="P3" t="n">
-        <v>13.38</v>
+        <v>14.22</v>
       </c>
       <c r="Q3" t="n">
-        <v>9.75</v>
+        <v>10.78</v>
       </c>
       <c r="R3" t="n">
-        <v>7.5</v>
+        <v>7.22</v>
       </c>
       <c r="S3" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="T3" t="n">
-        <v>2.38</v>
+        <v>2.22</v>
       </c>
       <c r="U3" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="V3" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>56.62</v>
+        <v>57.56</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="Z3" t="n">
-        <v>19.75</v>
+        <v>18.67</v>
       </c>
       <c r="AA3" t="n">
-        <v>11.88</v>
+        <v>11.22</v>
       </c>
       <c r="AB3" t="n">
-        <v>7.88</v>
+        <v>7.44</v>
       </c>
       <c r="AC3" t="n">
-        <v>17.25</v>
+        <v>18.33</v>
       </c>
       <c r="AD3" t="n">
-        <v>2.22</v>
+        <v>2.12</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="AF3" t="n">
         <v>0</v>
@@ -1953,70 +1953,70 @@
         <v>3.33</v>
       </c>
       <c r="BG3" t="n">
-        <v>3.24</v>
+        <v>3.22</v>
       </c>
       <c r="BH3" t="n">
-        <v>9.94</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.24</v>
+        <v>3.22</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="BL3" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="BM3" t="n">
         <v>1</v>
       </c>
       <c r="BN3" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="BP3" t="n">
-        <v>4.12</v>
+        <v>3.94</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5.41</v>
+        <v>5.28</v>
       </c>
       <c r="BR3" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BS3" t="n">
-        <v>76.47</v>
+        <v>77.78</v>
       </c>
       <c r="BT3" t="n">
-        <v>64.70999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="BU3" t="n">
-        <v>41.18</v>
+        <v>38.89</v>
       </c>
       <c r="BV3" t="n">
-        <v>23.53</v>
+        <v>22.22</v>
       </c>
       <c r="BW3" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BX3" t="n">
-        <v>64.70999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="BZ3" t="n">
         <v>1.76</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.47</v>
+        <v>3.45</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.64</v>
+        <v>3.63</v>
       </c>
       <c r="CC3" t="n">
         <v>2.58</v>
@@ -2028,25 +2028,25 @@
         <v>1.36</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.68</v>
+        <v>2.71</v>
       </c>
       <c r="CG3" t="n">
-        <v>2.97</v>
+        <v>2.94</v>
       </c>
       <c r="CH3" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CI3" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="CJ3" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="CL3" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="CM3" t="n">
         <v>2.38</v>
@@ -2055,34 +2055,34 @@
         <v>1.9</v>
       </c>
       <c r="CO3" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="CP3" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.09</v>
+        <v>3.14</v>
       </c>
       <c r="CR3" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CS3" t="n">
-        <v>2.87</v>
+        <v>2.91</v>
       </c>
       <c r="CT3" t="n">
-        <v>3.11</v>
+        <v>3.08</v>
       </c>
       <c r="CU3" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CV3" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="CW3" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="CX3" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CY3" t="n">
         <v>1.91</v>
@@ -2094,25 +2094,25 @@
         <v>1.9</v>
       </c>
       <c r="DB3" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="DC3" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="DD3" t="n">
-        <v>3.24</v>
+        <v>3.3</v>
       </c>
       <c r="DE3" t="n">
         <v>0.06</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="DG3" t="n">
-        <v>2.89</v>
+        <v>2.84</v>
       </c>
       <c r="DH3" t="n">
-        <v>93.23</v>
+        <v>94.89</v>
       </c>
       <c r="DI3" t="n">
         <v>0</v>
@@ -2121,61 +2121,61 @@
         <v>3</v>
       </c>
       <c r="DK3" t="n">
-        <v>5.71</v>
+        <v>5.56</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.23</v>
+        <v>0.28</v>
       </c>
       <c r="DM3" t="n">
-        <v>47.82</v>
+        <v>48.16</v>
       </c>
       <c r="DN3" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="DO3" t="n">
-        <v>2.53</v>
+        <v>2.44</v>
       </c>
       <c r="DP3" t="n">
-        <v>13.94</v>
+        <v>14.33</v>
       </c>
       <c r="DQ3" t="n">
-        <v>12.17</v>
+        <v>12.56</v>
       </c>
       <c r="DR3" t="n">
-        <v>7.82</v>
+        <v>7.66</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>53.59</v>
+        <v>54.22</v>
       </c>
       <c r="DW3" t="n">
         <v>0.11</v>
       </c>
       <c r="DX3" t="n">
-        <v>16.23</v>
+        <v>15.89</v>
       </c>
       <c r="DY3" t="n">
-        <v>10.3</v>
+        <v>10.06</v>
       </c>
       <c r="DZ3" t="n">
-        <v>5.94</v>
+        <v>5.83</v>
       </c>
       <c r="EA3" t="n">
-        <v>19.53</v>
+        <v>19.94</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
     </row>
     <row r="4">
@@ -2185,13 +2185,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C4" t="n">
         <v>9</v>
       </c>
       <c r="D4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E4" t="n">
         <v>0.11</v>
@@ -2275,139 +2275,139 @@
         <v>3.11</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.38</v>
+        <v>2.22</v>
       </c>
       <c r="AI4" t="n">
-        <v>86.25</v>
+        <v>84.89</v>
       </c>
       <c r="AJ4" t="n">
         <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="AL4" t="n">
-        <v>4.25</v>
+        <v>3.89</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AN4" t="n">
-        <v>39.5</v>
+        <v>38</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AQ4" t="n">
-        <v>13.5</v>
+        <v>14.11</v>
       </c>
       <c r="AR4" t="n">
-        <v>14.5</v>
+        <v>15.11</v>
       </c>
       <c r="AS4" t="n">
-        <v>9.380000000000001</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="AX4" t="n">
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>46.25</v>
+        <v>45</v>
       </c>
       <c r="AZ4" t="n">
         <v>0</v>
       </c>
       <c r="BA4" t="n">
-        <v>8.880000000000001</v>
+        <v>8.67</v>
       </c>
       <c r="BB4" t="n">
-        <v>6</v>
+        <v>5.89</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="BD4" t="n">
-        <v>21.88</v>
+        <v>21.67</v>
       </c>
       <c r="BE4" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>8.220000000000001</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BO4" t="n">
         <v>1.06</v>
       </c>
-      <c r="BF4" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>8.470000000000001</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>1</v>
-      </c>
       <c r="BP4" t="n">
-        <v>3.94</v>
+        <v>3.78</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.53</v>
+        <v>4.44</v>
       </c>
       <c r="BR4" t="n">
-        <v>82.34999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BS4" t="n">
-        <v>58.82</v>
+        <v>61.11</v>
       </c>
       <c r="BT4" t="n">
-        <v>41.18</v>
+        <v>44.44</v>
       </c>
       <c r="BU4" t="n">
-        <v>17.65</v>
+        <v>16.67</v>
       </c>
       <c r="BV4" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BW4" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BX4" t="n">
-        <v>47.06</v>
+        <v>50</v>
       </c>
       <c r="BY4" t="n">
         <v>2.26</v>
@@ -2416,22 +2416,22 @@
         <v>2.26</v>
       </c>
       <c r="CA4" t="n">
-        <v>3</v>
+        <v>3.01</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.08</v>
+        <v>3.11</v>
       </c>
       <c r="CC4" t="n">
-        <v>3.56</v>
+        <v>3.67</v>
       </c>
       <c r="CD4" t="n">
-        <v>3.89</v>
+        <v>4.04</v>
       </c>
       <c r="CE4" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CF4" t="n">
-        <v>3.46</v>
+        <v>3.45</v>
       </c>
       <c r="CG4" t="n">
         <v>2.36</v>
@@ -2443,37 +2443,37 @@
         <v>1.68</v>
       </c>
       <c r="CJ4" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CL4" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CO4" t="n">
         <v>1.49</v>
       </c>
       <c r="CP4" t="n">
-        <v>2.52</v>
+        <v>2.51</v>
       </c>
       <c r="CQ4" t="n">
-        <v>4.82</v>
+        <v>4.78</v>
       </c>
       <c r="CR4" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CS4" t="n">
-        <v>3.38</v>
+        <v>3.39</v>
       </c>
       <c r="CT4" t="n">
-        <v>2.43</v>
+        <v>2.44</v>
       </c>
       <c r="CU4" t="n">
         <v>1.33</v>
@@ -2482,103 +2482,103 @@
         <v>1.7</v>
       </c>
       <c r="CW4" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="CX4" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="CY4" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="CZ4" t="n">
-        <v>2.04</v>
+        <v>2.07</v>
       </c>
       <c r="DA4" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="DB4" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="DC4" t="n">
-        <v>2.71</v>
+        <v>2.69</v>
       </c>
       <c r="DD4" t="n">
-        <v>5.44</v>
+        <v>5.38</v>
       </c>
       <c r="DE4" t="n">
         <v>0.11</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.24</v>
+        <v>2.16</v>
       </c>
       <c r="DH4" t="n">
-        <v>90.81999999999999</v>
+        <v>89.89</v>
       </c>
       <c r="DI4" t="n">
         <v>0</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
       <c r="DK4" t="n">
-        <v>4.06</v>
+        <v>3.89</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DM4" t="n">
-        <v>43</v>
+        <v>42.06</v>
       </c>
       <c r="DN4" t="n">
-        <v>1.06</v>
+        <v>1.16</v>
       </c>
       <c r="DO4" t="n">
-        <v>1.83</v>
+        <v>1.72</v>
       </c>
       <c r="DP4" t="n">
-        <v>13.71</v>
+        <v>14</v>
       </c>
       <c r="DQ4" t="n">
-        <v>14.47</v>
+        <v>14.78</v>
       </c>
       <c r="DR4" t="n">
-        <v>8.880000000000001</v>
+        <v>8.77</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.35</v>
+        <v>0.38</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.35</v>
+        <v>0.38</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>48.29</v>
+        <v>47.56</v>
       </c>
       <c r="DW4" t="n">
         <v>0</v>
       </c>
       <c r="DX4" t="n">
-        <v>9.83</v>
+        <v>9.67</v>
       </c>
       <c r="DY4" t="n">
-        <v>6.94</v>
+        <v>6.84</v>
       </c>
       <c r="DZ4" t="n">
-        <v>2.89</v>
+        <v>2.84</v>
       </c>
       <c r="EA4" t="n">
-        <v>24.53</v>
+        <v>24.28</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="5">
@@ -2991,94 +2991,94 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D6" t="n">
         <v>9</v>
       </c>
       <c r="E6" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="F6" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="G6" t="n">
-        <v>3.25</v>
+        <v>2.78</v>
       </c>
       <c r="H6" t="n">
-        <v>99.38</v>
+        <v>99.22</v>
       </c>
       <c r="I6" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="J6" t="n">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="K6" t="n">
-        <v>5.88</v>
+        <v>5.44</v>
       </c>
       <c r="L6" t="n">
-        <v>0.25</v>
+        <v>0.11</v>
       </c>
       <c r="M6" t="n">
-        <v>55.25</v>
+        <v>54.56</v>
       </c>
       <c r="N6" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="O6" t="n">
-        <v>2.12</v>
+        <v>1.78</v>
       </c>
       <c r="P6" t="n">
-        <v>14.62</v>
+        <v>14.78</v>
       </c>
       <c r="Q6" t="n">
-        <v>13.5</v>
+        <v>13.22</v>
       </c>
       <c r="R6" t="n">
-        <v>5.25</v>
+        <v>5.33</v>
       </c>
       <c r="S6" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="T6" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="U6" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="V6" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>55.5</v>
+        <v>54.33</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>11.75</v>
+        <v>12.11</v>
       </c>
       <c r="AA6" t="n">
-        <v>7.38</v>
+        <v>7.78</v>
       </c>
       <c r="AB6" t="n">
-        <v>4.38</v>
+        <v>4.33</v>
       </c>
       <c r="AC6" t="n">
-        <v>21.25</v>
+        <v>21.22</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="AF6" t="n">
         <v>0.11</v>
@@ -3162,70 +3162,70 @@
         <v>2.11</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="BH6" t="n">
-        <v>8.94</v>
+        <v>8.83</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.35</v>
+        <v>0.39</v>
       </c>
       <c r="BN6" t="n">
-        <v>0.9399999999999999</v>
+        <v>1</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="BP6" t="n">
-        <v>3.47</v>
+        <v>3.22</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.12</v>
+        <v>4.78</v>
       </c>
       <c r="BR6" t="n">
-        <v>88.23999999999999</v>
+        <v>88.89</v>
       </c>
       <c r="BS6" t="n">
-        <v>58.82</v>
+        <v>61.11</v>
       </c>
       <c r="BT6" t="n">
-        <v>41.18</v>
+        <v>38.89</v>
       </c>
       <c r="BU6" t="n">
-        <v>17.65</v>
+        <v>16.67</v>
       </c>
       <c r="BV6" t="n">
-        <v>17.65</v>
+        <v>16.67</v>
       </c>
       <c r="BW6" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BX6" t="n">
-        <v>41.18</v>
+        <v>44.44</v>
       </c>
       <c r="BY6" t="n">
-        <v>2.4</v>
+        <v>2.43</v>
       </c>
       <c r="BZ6" t="n">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.25</v>
+        <v>3.22</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.36</v>
+        <v>3.34</v>
       </c>
       <c r="CC6" t="n">
         <v>4.21</v>
@@ -3234,157 +3234,157 @@
         <v>4.59</v>
       </c>
       <c r="CE6" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="CF6" t="n">
-        <v>3.03</v>
+        <v>3.05</v>
       </c>
       <c r="CG6" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="CH6" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="CI6" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CJ6" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="CK6" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="CL6" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="CN6" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CO6" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CP6" t="n">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="CQ6" t="n">
-        <v>3.93</v>
+        <v>3.99</v>
       </c>
       <c r="CR6" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="CS6" t="n">
         <v>3.13</v>
       </c>
       <c r="CT6" t="n">
-        <v>2.83</v>
+        <v>2.8</v>
       </c>
       <c r="CU6" t="n">
         <v>1.39</v>
       </c>
       <c r="CV6" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CW6" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CX6" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="CY6" t="n">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="CZ6" t="n">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="DA6" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="DB6" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="DC6" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="DD6" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="DE6" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="DF6" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="DG6" t="n">
         <v>2.22</v>
       </c>
-      <c r="DD6" t="n">
-        <v>4.06</v>
-      </c>
-      <c r="DE6" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="DF6" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="DG6" t="n">
-        <v>2.41</v>
-      </c>
       <c r="DH6" t="n">
-        <v>88.95</v>
+        <v>89.44</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.65</v>
+        <v>2.61</v>
       </c>
       <c r="DK6" t="n">
-        <v>4.41</v>
+        <v>4.28</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.35</v>
+        <v>0.28</v>
       </c>
       <c r="DM6" t="n">
-        <v>43.88</v>
+        <v>44.17</v>
       </c>
       <c r="DN6" t="n">
         <v>1</v>
       </c>
       <c r="DO6" t="n">
-        <v>1.76</v>
+        <v>1.61</v>
       </c>
       <c r="DP6" t="n">
-        <v>13.53</v>
+        <v>13.67</v>
       </c>
       <c r="DQ6" t="n">
-        <v>13.41</v>
+        <v>13.27</v>
       </c>
       <c r="DR6" t="n">
-        <v>7.59</v>
+        <v>7.5</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>51.12</v>
+        <v>50.78</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DX6" t="n">
-        <v>10.18</v>
+        <v>10.44</v>
       </c>
       <c r="DY6" t="n">
-        <v>6.95</v>
+        <v>7.17</v>
       </c>
       <c r="DZ6" t="n">
-        <v>3.24</v>
+        <v>3.28</v>
       </c>
       <c r="EA6" t="n">
-        <v>20.65</v>
+        <v>20.67</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.47</v>
+        <v>2.44</v>
       </c>
     </row>
     <row r="7">
@@ -3622,7 +3622,7 @@
         <v>2.62</v>
       </c>
       <c r="BZ7" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="CA7" t="n">
         <v>3.36</v>
@@ -3709,10 +3709,10 @@
         <v>1.36</v>
       </c>
       <c r="DC7" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="DD7" t="n">
-        <v>3.87</v>
+        <v>3.89</v>
       </c>
       <c r="DE7" t="n">
         <v>0.11</v>
@@ -3797,13 +3797,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C8" t="n">
         <v>9</v>
       </c>
       <c r="D8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E8" t="n">
         <v>0.11</v>
@@ -3887,52 +3887,52 @@
         <v>3.22</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AG8" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="AI8" t="n">
-        <v>82.38</v>
+        <v>84</v>
       </c>
       <c r="AJ8" t="n">
         <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.38</v>
+        <v>2.67</v>
       </c>
       <c r="AL8" t="n">
-        <v>4.12</v>
+        <v>4.11</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AN8" t="n">
-        <v>27.88</v>
+        <v>28.89</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.38</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AP8" t="n">
         <v>2</v>
       </c>
       <c r="AQ8" t="n">
-        <v>15.38</v>
+        <v>16</v>
       </c>
       <c r="AR8" t="n">
-        <v>13.5</v>
+        <v>13.33</v>
       </c>
       <c r="AS8" t="n">
-        <v>10.88</v>
+        <v>10.44</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="AV8" t="n">
         <v>0</v>
@@ -3944,82 +3944,82 @@
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>41.5</v>
+        <v>41.44</v>
       </c>
       <c r="AZ8" t="n">
         <v>0</v>
       </c>
       <c r="BA8" t="n">
-        <v>8</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="BB8" t="n">
-        <v>5.5</v>
+        <v>5.22</v>
       </c>
       <c r="BC8" t="n">
-        <v>2.5</v>
+        <v>2.89</v>
       </c>
       <c r="BD8" t="n">
-        <v>20.25</v>
+        <v>19.22</v>
       </c>
       <c r="BE8" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>10.17</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BO8" t="n">
         <v>0.89</v>
       </c>
-      <c r="BF8" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>2</v>
-      </c>
-      <c r="BH8" t="n">
-        <v>10.06</v>
-      </c>
-      <c r="BI8" t="n">
-        <v>2</v>
-      </c>
-      <c r="BJ8" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="BK8" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="BM8" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="BN8" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="BO8" t="n">
-        <v>0.9399999999999999</v>
-      </c>
       <c r="BP8" t="n">
-        <v>4.65</v>
+        <v>4.61</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.41</v>
+        <v>5.56</v>
       </c>
       <c r="BR8" t="n">
-        <v>76.47</v>
+        <v>77.78</v>
       </c>
       <c r="BS8" t="n">
-        <v>47.06</v>
+        <v>50</v>
       </c>
       <c r="BT8" t="n">
-        <v>41.18</v>
+        <v>44.44</v>
       </c>
       <c r="BU8" t="n">
-        <v>17.65</v>
+        <v>16.67</v>
       </c>
       <c r="BV8" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BW8" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BX8" t="n">
-        <v>41.18</v>
+        <v>44.44</v>
       </c>
       <c r="BY8" t="n">
         <v>2.18</v>
@@ -4028,25 +4028,25 @@
         <v>2.37</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.11</v>
+        <v>3.1</v>
       </c>
       <c r="CB8" t="n">
         <v>3.27</v>
       </c>
       <c r="CC8" t="n">
-        <v>3.76</v>
+        <v>3.7</v>
       </c>
       <c r="CD8" t="n">
-        <v>4.15</v>
+        <v>4.12</v>
       </c>
       <c r="CE8" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="CF8" t="n">
-        <v>3.18</v>
+        <v>3.19</v>
       </c>
       <c r="CG8" t="n">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="CH8" t="n">
         <v>1.32</v>
@@ -4064,19 +4064,19 @@
         <v>2.21</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="CN8" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CO8" t="n">
         <v>1.39</v>
       </c>
       <c r="CP8" t="n">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="CQ8" t="n">
-        <v>4.18</v>
+        <v>4.21</v>
       </c>
       <c r="CR8" t="n">
         <v>1.51</v>
@@ -4097,67 +4097,67 @@
         <v>2.01</v>
       </c>
       <c r="CX8" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CY8" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="CZ8" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="DA8" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="DB8" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="DC8" t="n">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="DD8" t="n">
-        <v>4.41</v>
+        <v>4.42</v>
       </c>
       <c r="DE8" t="n">
         <v>0.11</v>
       </c>
       <c r="DF8" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="DH8" t="n">
-        <v>89.12</v>
+        <v>89.56</v>
       </c>
       <c r="DI8" t="n">
         <v>0</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.82</v>
+        <v>2.94</v>
       </c>
       <c r="DK8" t="n">
-        <v>5</v>
+        <v>4.94</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DM8" t="n">
-        <v>39.77</v>
+        <v>39.61</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.71</v>
+        <v>0.78</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="DP8" t="n">
-        <v>14.82</v>
+        <v>15.16</v>
       </c>
       <c r="DQ8" t="n">
-        <v>13.47</v>
+        <v>13.38</v>
       </c>
       <c r="DR8" t="n">
-        <v>8.880000000000001</v>
+        <v>8.77</v>
       </c>
       <c r="DS8" t="n">
         <v>0</v>
@@ -4169,28 +4169,28 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>46.41</v>
+        <v>46.11</v>
       </c>
       <c r="DW8" t="n">
         <v>0</v>
       </c>
       <c r="DX8" t="n">
-        <v>10.06</v>
+        <v>10</v>
       </c>
       <c r="DY8" t="n">
-        <v>7.06</v>
+        <v>6.83</v>
       </c>
       <c r="DZ8" t="n">
-        <v>3</v>
+        <v>3.16</v>
       </c>
       <c r="EA8" t="n">
-        <v>19.65</v>
+        <v>19.17</v>
       </c>
       <c r="EB8" t="n">
         <v>1.14</v>
       </c>
       <c r="EC8" t="n">
-        <v>2.82</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="9">
@@ -4200,94 +4200,94 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D9" t="n">
         <v>9</v>
       </c>
       <c r="E9" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="F9" t="n">
-        <v>1.62</v>
+        <v>1.78</v>
       </c>
       <c r="G9" t="n">
-        <v>2.75</v>
+        <v>2.67</v>
       </c>
       <c r="H9" t="n">
-        <v>102.62</v>
+        <v>102.56</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="J9" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="K9" t="n">
+        <v>5.11</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="M9" t="n">
+        <v>54.89</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="O9" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="P9" t="n">
+        <v>15.78</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>15.22</v>
+      </c>
+      <c r="R9" t="n">
+        <v>5</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>59.56</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>16.33</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>11.56</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>21.78</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AE9" t="n">
         <v>3</v>
-      </c>
-      <c r="K9" t="n">
-        <v>5.12</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="M9" t="n">
-        <v>54.5</v>
-      </c>
-      <c r="N9" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="O9" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="P9" t="n">
-        <v>15.62</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>14.75</v>
-      </c>
-      <c r="R9" t="n">
-        <v>5.38</v>
-      </c>
-      <c r="S9" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="T9" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="V9" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="W9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X9" t="n">
-        <v>57.88</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>16.75</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>11.62</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>5.12</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>21.38</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>2.75</v>
       </c>
       <c r="AF9" t="n">
         <v>0.22</v>
@@ -4371,49 +4371,49 @@
         <v>3</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.53</v>
+        <v>2.39</v>
       </c>
       <c r="BH9" t="n">
-        <v>9.289999999999999</v>
+        <v>9.06</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.53</v>
+        <v>2.39</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.76</v>
+        <v>0.72</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.88</v>
+        <v>0.83</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.88</v>
+        <v>0.83</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.41</v>
+        <v>4.33</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.88</v>
+        <v>4.72</v>
       </c>
       <c r="BR9" t="n">
-        <v>88.23999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BS9" t="n">
-        <v>76.47</v>
+        <v>72.22</v>
       </c>
       <c r="BT9" t="n">
-        <v>52.94</v>
+        <v>50</v>
       </c>
       <c r="BU9" t="n">
-        <v>35.29</v>
+        <v>33.33</v>
       </c>
       <c r="BV9" t="n">
         <v>0</v>
@@ -4422,19 +4422,19 @@
         <v>0</v>
       </c>
       <c r="BX9" t="n">
-        <v>70.59</v>
+        <v>66.67</v>
       </c>
       <c r="BY9" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="BZ9" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.26</v>
+        <v>3.27</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.41</v>
+        <v>3.4</v>
       </c>
       <c r="CC9" t="n">
         <v>3.05</v>
@@ -4446,7 +4446,7 @@
         <v>1.39</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.76</v>
+        <v>2.77</v>
       </c>
       <c r="CG9" t="n">
         <v>2.91</v>
@@ -4455,19 +4455,19 @@
         <v>1.41</v>
       </c>
       <c r="CI9" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CK9" t="n">
         <v>1.52</v>
       </c>
       <c r="CL9" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="CN9" t="n">
         <v>1.88</v>
@@ -4476,28 +4476,28 @@
         <v>1.27</v>
       </c>
       <c r="CP9" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CQ9" t="n">
-        <v>3.19</v>
+        <v>3.21</v>
       </c>
       <c r="CR9" t="n">
         <v>1.42</v>
       </c>
       <c r="CS9" t="n">
-        <v>2.99</v>
+        <v>3.01</v>
       </c>
       <c r="CT9" t="n">
-        <v>2.99</v>
+        <v>2.98</v>
       </c>
       <c r="CU9" t="n">
         <v>1.42</v>
       </c>
       <c r="CV9" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="CW9" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CX9" t="n">
         <v>1.56</v>
@@ -4515,85 +4515,85 @@
         <v>1.3</v>
       </c>
       <c r="DC9" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="DD9" t="n">
-        <v>3.39</v>
+        <v>3.41</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="DG9" t="n">
-        <v>2.59</v>
+        <v>2.56</v>
       </c>
       <c r="DH9" t="n">
-        <v>96.81999999999999</v>
+        <v>97.12</v>
       </c>
       <c r="DI9" t="n">
-        <v>-0.06</v>
+        <v>0</v>
       </c>
       <c r="DJ9" t="n">
-        <v>3.12</v>
+        <v>3.22</v>
       </c>
       <c r="DK9" t="n">
-        <v>4.7</v>
+        <v>4.72</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.18</v>
+        <v>0.22</v>
       </c>
       <c r="DM9" t="n">
-        <v>46.94</v>
+        <v>47.56</v>
       </c>
       <c r="DN9" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="DO9" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="DP9" t="n">
-        <v>16.12</v>
+        <v>16.17</v>
       </c>
       <c r="DQ9" t="n">
-        <v>14.77</v>
+        <v>15</v>
       </c>
       <c r="DR9" t="n">
-        <v>6.18</v>
+        <v>5.94</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>55.35</v>
+        <v>56.34</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DX9" t="n">
-        <v>14.71</v>
+        <v>14.61</v>
       </c>
       <c r="DY9" t="n">
-        <v>9.94</v>
+        <v>10</v>
       </c>
       <c r="DZ9" t="n">
-        <v>4.76</v>
+        <v>4.61</v>
       </c>
       <c r="EA9" t="n">
-        <v>22.41</v>
+        <v>22.56</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -4603,94 +4603,94 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D10" t="n">
         <v>9</v>
       </c>
       <c r="E10" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="F10" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="G10" t="n">
-        <v>2.12</v>
+        <v>2.44</v>
       </c>
       <c r="H10" t="n">
-        <v>93.88</v>
+        <v>95.22</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>2.62</v>
+        <v>2.33</v>
       </c>
       <c r="K10" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="L10" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="M10" t="n">
-        <v>41.88</v>
+        <v>44.22</v>
       </c>
       <c r="N10" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="O10" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="P10" t="n">
-        <v>12.88</v>
+        <v>12</v>
       </c>
       <c r="Q10" t="n">
-        <v>12.75</v>
+        <v>13.33</v>
       </c>
       <c r="R10" t="n">
-        <v>7</v>
+        <v>7.22</v>
       </c>
       <c r="S10" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="T10" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="U10" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="V10" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>51.5</v>
+        <v>53.44</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="Z10" t="n">
-        <v>12</v>
+        <v>12.56</v>
       </c>
       <c r="AA10" t="n">
-        <v>7.62</v>
+        <v>7.67</v>
       </c>
       <c r="AB10" t="n">
-        <v>4.38</v>
+        <v>4.89</v>
       </c>
       <c r="AC10" t="n">
-        <v>18.88</v>
+        <v>19.67</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.37</v>
+        <v>1.46</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.38</v>
+        <v>2.11</v>
       </c>
       <c r="AF10" t="n">
         <v>0</v>
@@ -4774,70 +4774,70 @@
         <v>2.67</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="BH10" t="n">
-        <v>8.82</v>
+        <v>8.83</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="BM10" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="BP10" t="n">
-        <v>4.18</v>
+        <v>4.11</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.65</v>
+        <v>4.72</v>
       </c>
       <c r="BR10" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BS10" t="n">
-        <v>88.23999999999999</v>
+        <v>88.89</v>
       </c>
       <c r="BT10" t="n">
-        <v>58.82</v>
+        <v>61.11</v>
       </c>
       <c r="BU10" t="n">
-        <v>35.29</v>
+        <v>33.33</v>
       </c>
       <c r="BV10" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BW10" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BX10" t="n">
-        <v>58.82</v>
+        <v>55.56</v>
       </c>
       <c r="BY10" t="n">
-        <v>1.96</v>
+        <v>1.9</v>
       </c>
       <c r="BZ10" t="n">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.21</v>
+        <v>3.28</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.37</v>
+        <v>3.43</v>
       </c>
       <c r="CC10" t="n">
         <v>2.76</v>
@@ -4849,154 +4849,154 @@
         <v>1.41</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="CG10" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="CH10" t="n">
         <v>1.38</v>
       </c>
       <c r="CI10" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CJ10" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CK10" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CL10" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="CN10" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CO10" t="n">
         <v>1.31</v>
       </c>
       <c r="CP10" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="CQ10" t="n">
-        <v>3.5</v>
+        <v>3.47</v>
       </c>
       <c r="CR10" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CS10" t="n">
-        <v>3.14</v>
+        <v>3.12</v>
       </c>
       <c r="CT10" t="n">
-        <v>2.85</v>
+        <v>2.87</v>
       </c>
       <c r="CU10" t="n">
         <v>1.39</v>
       </c>
       <c r="CV10" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="CW10" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="CX10" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CY10" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="CZ10" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="DA10" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="DB10" t="n">
         <v>1.34</v>
       </c>
       <c r="DC10" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="DD10" t="n">
-        <v>3.72</v>
+        <v>3.69</v>
       </c>
       <c r="DE10" t="n">
         <v>0.06</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="DG10" t="n">
-        <v>1.94</v>
+        <v>2.11</v>
       </c>
       <c r="DH10" t="n">
-        <v>85.53</v>
+        <v>86.66</v>
       </c>
       <c r="DI10" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.65</v>
+        <v>2.5</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.41</v>
+        <v>4.5</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="DM10" t="n">
-        <v>37.48</v>
+        <v>38.89</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.47</v>
+        <v>2.39</v>
       </c>
       <c r="DP10" t="n">
-        <v>12</v>
+        <v>11.61</v>
       </c>
       <c r="DQ10" t="n">
-        <v>12.35</v>
+        <v>12.66</v>
       </c>
       <c r="DR10" t="n">
-        <v>7.76</v>
+        <v>7.83</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>50.12</v>
+        <v>51.16</v>
       </c>
       <c r="DW10" t="n">
         <v>0.06</v>
       </c>
       <c r="DX10" t="n">
-        <v>12.23</v>
+        <v>12.5</v>
       </c>
       <c r="DY10" t="n">
-        <v>7.47</v>
+        <v>7.5</v>
       </c>
       <c r="DZ10" t="n">
-        <v>4.77</v>
+        <v>5</v>
       </c>
       <c r="EA10" t="n">
-        <v>16.41</v>
+        <v>16.95</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="EC10" t="n">
-        <v>2.53</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="11">
@@ -5006,13 +5006,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C11" t="n">
         <v>8</v>
       </c>
       <c r="D11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -5096,139 +5096,139 @@
         <v>1.88</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="AI11" t="n">
-        <v>93.44</v>
+        <v>96.5</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AK11" t="n">
-        <v>3.11</v>
+        <v>3</v>
       </c>
       <c r="AL11" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AN11" t="n">
-        <v>39.56</v>
+        <v>39.6</v>
       </c>
       <c r="AO11" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AQ11" t="n">
-        <v>13.89</v>
+        <v>13.8</v>
       </c>
       <c r="AR11" t="n">
-        <v>14.78</v>
+        <v>15.2</v>
       </c>
       <c r="AS11" t="n">
-        <v>7.11</v>
+        <v>7.4</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AX11" t="n">
         <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>55.44</v>
+        <v>56.7</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="BA11" t="n">
-        <v>14.33</v>
+        <v>13.8</v>
       </c>
       <c r="BB11" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>18</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BH11" t="n">
         <v>9.890000000000001</v>
       </c>
-      <c r="BC11" t="n">
+      <c r="BI11" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="BP11" t="n">
         <v>4.44</v>
       </c>
-      <c r="BD11" t="n">
-        <v>17.89</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="BH11" t="n">
-        <v>9.65</v>
-      </c>
-      <c r="BI11" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="BJ11" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="BK11" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="BL11" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="BM11" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="BN11" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="BO11" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="BP11" t="n">
-        <v>4.18</v>
-      </c>
       <c r="BQ11" t="n">
-        <v>5.41</v>
+        <v>5.39</v>
       </c>
       <c r="BR11" t="n">
-        <v>88.23999999999999</v>
+        <v>88.89</v>
       </c>
       <c r="BS11" t="n">
-        <v>82.34999999999999</v>
+        <v>77.78</v>
       </c>
       <c r="BT11" t="n">
-        <v>58.82</v>
+        <v>55.56</v>
       </c>
       <c r="BU11" t="n">
-        <v>29.41</v>
+        <v>27.78</v>
       </c>
       <c r="BV11" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BW11" t="n">
         <v>0</v>
       </c>
       <c r="BX11" t="n">
-        <v>70.59</v>
+        <v>66.67</v>
       </c>
       <c r="BY11" t="n">
         <v>2.27</v>
@@ -5237,31 +5237,31 @@
         <v>2.37</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.27</v>
+        <v>3.3</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.42</v>
+        <v>3.47</v>
       </c>
       <c r="CC11" t="n">
-        <v>3.71</v>
+        <v>3.95</v>
       </c>
       <c r="CD11" t="n">
-        <v>4.04</v>
+        <v>4.21</v>
       </c>
       <c r="CE11" t="n">
         <v>1.42</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.93</v>
+        <v>2.91</v>
       </c>
       <c r="CG11" t="n">
-        <v>2.78</v>
+        <v>2.79</v>
       </c>
       <c r="CH11" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CI11" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CJ11" t="n">
         <v>1.84</v>
@@ -5270,7 +5270,7 @@
         <v>1.65</v>
       </c>
       <c r="CL11" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="CM11" t="n">
         <v>2.13</v>
@@ -5282,91 +5282,91 @@
         <v>1.32</v>
       </c>
       <c r="CP11" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="CQ11" t="n">
-        <v>3.58</v>
+        <v>3.56</v>
       </c>
       <c r="CR11" t="n">
         <v>1.45</v>
       </c>
       <c r="CS11" t="n">
-        <v>3.06</v>
+        <v>3.05</v>
       </c>
       <c r="CT11" t="n">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="CU11" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CV11" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CW11" t="n">
         <v>1.87</v>
       </c>
       <c r="CX11" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CY11" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="CZ11" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="DA11" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="DB11" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="DC11" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="DD11" t="n">
-        <v>3.76</v>
+        <v>3.73</v>
       </c>
       <c r="DE11" t="n">
         <v>0.06</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="DG11" t="n">
-        <v>3.23</v>
+        <v>3.22</v>
       </c>
       <c r="DH11" t="n">
-        <v>98.94</v>
+        <v>100.33</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.59</v>
+        <v>2.56</v>
       </c>
       <c r="DK11" t="n">
-        <v>5</v>
+        <v>5.05</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DM11" t="n">
-        <v>43.88</v>
+        <v>43.67</v>
       </c>
       <c r="DN11" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="DO11" t="n">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="DP11" t="n">
-        <v>14</v>
+        <v>13.94</v>
       </c>
       <c r="DQ11" t="n">
-        <v>14.88</v>
+        <v>15.11</v>
       </c>
       <c r="DR11" t="n">
-        <v>7.76</v>
+        <v>7.89</v>
       </c>
       <c r="DS11" t="n">
         <v>0.06</v>
@@ -5378,28 +5378,28 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>56.64</v>
+        <v>57.28</v>
       </c>
       <c r="DW11" t="n">
         <v>0.11</v>
       </c>
       <c r="DX11" t="n">
-        <v>14.12</v>
+        <v>13.84</v>
       </c>
       <c r="DY11" t="n">
-        <v>9.41</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="DZ11" t="n">
-        <v>4.7</v>
+        <v>4.56</v>
       </c>
       <c r="EA11" t="n">
-        <v>18.53</v>
+        <v>18.56</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="12">
@@ -5409,13 +5409,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C12" t="n">
         <v>9</v>
       </c>
       <c r="D12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E12" t="n">
         <v>0.22</v>
@@ -5505,46 +5505,46 @@
         <v>2</v>
       </c>
       <c r="AH12" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AI12" t="n">
-        <v>92</v>
+        <v>90.56</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AK12" t="n">
-        <v>3</v>
+        <v>2.89</v>
       </c>
       <c r="AL12" t="n">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="AN12" t="n">
-        <v>36.88</v>
+        <v>36.67</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AQ12" t="n">
-        <v>14.88</v>
+        <v>14.33</v>
       </c>
       <c r="AR12" t="n">
-        <v>14.62</v>
+        <v>14.56</v>
       </c>
       <c r="AS12" t="n">
-        <v>8.75</v>
+        <v>8.44</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AU12" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AV12" t="n">
         <v>0</v>
@@ -5556,82 +5556,82 @@
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>45.62</v>
+        <v>45.78</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="BA12" t="n">
-        <v>9.880000000000001</v>
+        <v>9.56</v>
       </c>
       <c r="BB12" t="n">
-        <v>6.5</v>
+        <v>6.33</v>
       </c>
       <c r="BC12" t="n">
-        <v>3.38</v>
+        <v>3.22</v>
       </c>
       <c r="BD12" t="n">
-        <v>20.75</v>
+        <v>21.22</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="BF12" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.47</v>
+        <v>2.39</v>
       </c>
       <c r="BH12" t="n">
-        <v>9</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.47</v>
+        <v>2.39</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="BP12" t="n">
-        <v>3.76</v>
+        <v>3.83</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.24</v>
+        <v>5.06</v>
       </c>
       <c r="BR12" t="n">
-        <v>82.34999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BS12" t="n">
-        <v>70.59</v>
+        <v>66.67</v>
       </c>
       <c r="BT12" t="n">
-        <v>47.06</v>
+        <v>44.44</v>
       </c>
       <c r="BU12" t="n">
-        <v>29.41</v>
+        <v>27.78</v>
       </c>
       <c r="BV12" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BW12" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BX12" t="n">
-        <v>58.82</v>
+        <v>55.56</v>
       </c>
       <c r="BY12" t="n">
         <v>2.09</v>
@@ -5640,22 +5640,22 @@
         <v>2.3</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.18</v>
+        <v>3.19</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.27</v>
+        <v>3.26</v>
       </c>
       <c r="CC12" t="n">
-        <v>3.52</v>
+        <v>3.46</v>
       </c>
       <c r="CD12" t="n">
-        <v>3.88</v>
+        <v>3.87</v>
       </c>
       <c r="CE12" t="n">
         <v>1.46</v>
       </c>
       <c r="CF12" t="n">
-        <v>3.16</v>
+        <v>3.17</v>
       </c>
       <c r="CG12" t="n">
         <v>2.62</v>
@@ -5664,19 +5664,19 @@
         <v>1.32</v>
       </c>
       <c r="CI12" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CJ12" t="n">
         <v>1.93</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CL12" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="CN12" t="n">
         <v>1.77</v>
@@ -5685,7 +5685,7 @@
         <v>1.38</v>
       </c>
       <c r="CP12" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="CQ12" t="n">
         <v>3.98</v>
@@ -5694,7 +5694,7 @@
         <v>1.5</v>
       </c>
       <c r="CS12" t="n">
-        <v>3.25</v>
+        <v>3.26</v>
       </c>
       <c r="CT12" t="n">
         <v>2.7</v>
@@ -5730,46 +5730,46 @@
         <v>4.29</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="DH12" t="n">
-        <v>92.3</v>
+        <v>91.56</v>
       </c>
       <c r="DI12" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
       <c r="DK12" t="n">
-        <v>4.29</v>
+        <v>4.11</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.41</v>
+        <v>0.38</v>
       </c>
       <c r="DM12" t="n">
-        <v>41.12</v>
+        <v>40.78</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.83</v>
+        <v>0.78</v>
       </c>
       <c r="DO12" t="n">
-        <v>2.18</v>
+        <v>2.11</v>
       </c>
       <c r="DP12" t="n">
-        <v>13.47</v>
+        <v>13.27</v>
       </c>
       <c r="DQ12" t="n">
-        <v>15.23</v>
+        <v>15.17</v>
       </c>
       <c r="DR12" t="n">
-        <v>8</v>
+        <v>7.89</v>
       </c>
       <c r="DS12" t="n">
         <v>0</v>
@@ -5781,25 +5781,25 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>48.94</v>
+        <v>48.84</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DX12" t="n">
-        <v>12.47</v>
+        <v>12.17</v>
       </c>
       <c r="DY12" t="n">
-        <v>8.880000000000001</v>
+        <v>8.66</v>
       </c>
       <c r="DZ12" t="n">
-        <v>3.59</v>
+        <v>3.5</v>
       </c>
       <c r="EA12" t="n">
-        <v>21.82</v>
+        <v>22</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="EC12" t="n">
         <v>2.12</v>
@@ -5812,13 +5812,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C13" t="n">
         <v>8</v>
       </c>
       <c r="D13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E13" t="n">
         <v>0.38</v>
@@ -5905,136 +5905,136 @@
         <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.22</v>
+        <v>1.6</v>
       </c>
       <c r="AI13" t="n">
-        <v>81.11</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AK13" t="n">
-        <v>3.67</v>
+        <v>3.6</v>
       </c>
       <c r="AL13" t="n">
-        <v>3.56</v>
+        <v>3.9</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AN13" t="n">
-        <v>32.78</v>
+        <v>33.1</v>
       </c>
       <c r="AO13" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AQ13" t="n">
-        <v>12.56</v>
+        <v>12.4</v>
       </c>
       <c r="AR13" t="n">
-        <v>13.78</v>
+        <v>13.8</v>
       </c>
       <c r="AS13" t="n">
-        <v>9.109999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="AT13" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AX13" t="n">
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>48.11</v>
+        <v>48.8</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="BA13" t="n">
-        <v>9.56</v>
+        <v>10.1</v>
       </c>
       <c r="BB13" t="n">
-        <v>5.44</v>
+        <v>6</v>
       </c>
       <c r="BC13" t="n">
-        <v>4.11</v>
+        <v>4.1</v>
       </c>
       <c r="BD13" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="BF13" t="n">
-        <v>3.11</v>
+        <v>3.1</v>
       </c>
       <c r="BG13" t="n">
         <v>2</v>
       </c>
       <c r="BH13" t="n">
-        <v>9</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="BI13" t="n">
         <v>2</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.41</v>
+        <v>0.44</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="BO13" t="n">
-        <v>0.88</v>
+        <v>0.83</v>
       </c>
       <c r="BP13" t="n">
-        <v>4.12</v>
+        <v>4.17</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4.29</v>
+        <v>4.56</v>
       </c>
       <c r="BR13" t="n">
-        <v>76.47</v>
+        <v>77.78</v>
       </c>
       <c r="BS13" t="n">
-        <v>64.70999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="BT13" t="n">
-        <v>41.18</v>
+        <v>38.89</v>
       </c>
       <c r="BU13" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BV13" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BW13" t="n">
         <v>0</v>
       </c>
       <c r="BX13" t="n">
-        <v>47.06</v>
+        <v>50</v>
       </c>
       <c r="BY13" t="n">
         <v>2.3</v>
@@ -6043,166 +6043,166 @@
         <v>2.4</v>
       </c>
       <c r="CA13" t="n">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.09</v>
+        <v>3.16</v>
       </c>
       <c r="CC13" t="n">
-        <v>2.82</v>
+        <v>3.02</v>
       </c>
       <c r="CD13" t="n">
-        <v>3.02</v>
+        <v>3.22</v>
       </c>
       <c r="CE13" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CF13" t="n">
-        <v>3.31</v>
+        <v>3.26</v>
       </c>
       <c r="CG13" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="CH13" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="CI13" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="CJ13" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="CK13" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CL13" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="CN13" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="CO13" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="CP13" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="CQ13" t="n">
+        <v>4.23</v>
+      </c>
+      <c r="CR13" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="CS13" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="CT13" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="CU13" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="CV13" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="CW13" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="CX13" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="CY13" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="CZ13" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="DA13" t="n">
         <v>1.71</v>
       </c>
-      <c r="CO13" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="CP13" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="CQ13" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="CR13" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="CS13" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="CT13" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="CU13" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="CV13" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="CW13" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="CX13" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="CY13" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="CZ13" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="DA13" t="n">
-        <v>1.69</v>
-      </c>
       <c r="DB13" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="DC13" t="n">
-        <v>2.47</v>
+        <v>2.43</v>
       </c>
       <c r="DD13" t="n">
-        <v>4.74</v>
+        <v>4.62</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DF13" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="DG13" t="n">
-        <v>1.7</v>
+        <v>1.89</v>
       </c>
       <c r="DH13" t="n">
-        <v>84.06</v>
+        <v>84.45</v>
       </c>
       <c r="DI13" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ13" t="n">
-        <v>3.47</v>
+        <v>3.44</v>
       </c>
       <c r="DK13" t="n">
-        <v>4.47</v>
+        <v>4.61</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="DM13" t="n">
-        <v>37.41</v>
+        <v>37.33</v>
       </c>
       <c r="DN13" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="DO13" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="DP13" t="n">
-        <v>13.29</v>
+        <v>13.16</v>
       </c>
       <c r="DQ13" t="n">
-        <v>14.88</v>
+        <v>14.83</v>
       </c>
       <c r="DR13" t="n">
-        <v>8.470000000000001</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>49.23</v>
+        <v>49.56</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DX13" t="n">
-        <v>10.89</v>
+        <v>11.11</v>
       </c>
       <c r="DY13" t="n">
-        <v>6.53</v>
+        <v>6.78</v>
       </c>
       <c r="DZ13" t="n">
-        <v>4.35</v>
+        <v>4.33</v>
       </c>
       <c r="EA13" t="n">
-        <v>20.76</v>
+        <v>20.94</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="EC13" t="n">
         <v>3.11</v>
@@ -6618,13 +6618,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C15" t="n">
         <v>9</v>
       </c>
       <c r="D15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E15" t="n">
         <v>0.11</v>
@@ -6708,139 +6708,139 @@
         <v>2</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.5</v>
+        <v>2.67</v>
       </c>
       <c r="AI15" t="n">
-        <v>88.25</v>
+        <v>90.56</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.62</v>
+        <v>2.44</v>
       </c>
       <c r="AL15" t="n">
-        <v>4</v>
+        <v>4.11</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="AN15" t="n">
-        <v>46.5</v>
+        <v>46.33</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AQ15" t="n">
-        <v>13.38</v>
+        <v>12.33</v>
       </c>
       <c r="AR15" t="n">
-        <v>12.88</v>
+        <v>12.33</v>
       </c>
       <c r="AS15" t="n">
-        <v>8.5</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.5</v>
+        <v>0.78</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="AX15" t="n">
         <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>50.5</v>
+        <v>51.22</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="BA15" t="n">
-        <v>9.5</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="BB15" t="n">
-        <v>6.62</v>
+        <v>6.67</v>
       </c>
       <c r="BC15" t="n">
-        <v>2.88</v>
+        <v>3.11</v>
       </c>
       <c r="BD15" t="n">
-        <v>23.88</v>
+        <v>23.89</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="BF15" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.53</v>
+        <v>2.61</v>
       </c>
       <c r="BH15" t="n">
-        <v>8.41</v>
+        <v>8.56</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.53</v>
+        <v>2.61</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="BL15" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.59</v>
+        <v>0.72</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.59</v>
+        <v>1.67</v>
       </c>
       <c r="BO15" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="BP15" t="n">
-        <v>3.59</v>
+        <v>3.61</v>
       </c>
       <c r="BQ15" t="n">
-        <v>4.82</v>
+        <v>4.94</v>
       </c>
       <c r="BR15" t="n">
         <v>100</v>
       </c>
       <c r="BS15" t="n">
-        <v>70.59</v>
+        <v>72.22</v>
       </c>
       <c r="BT15" t="n">
-        <v>47.06</v>
+        <v>50</v>
       </c>
       <c r="BU15" t="n">
-        <v>23.53</v>
+        <v>27.78</v>
       </c>
       <c r="BV15" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BW15" t="n">
         <v>0</v>
       </c>
       <c r="BX15" t="n">
-        <v>52.94</v>
+        <v>55.56</v>
       </c>
       <c r="BY15" t="n">
         <v>2.19</v>
@@ -6852,10 +6852,10 @@
         <v>3.21</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.35</v>
+        <v>3.36</v>
       </c>
       <c r="CC15" t="n">
-        <v>4.08</v>
+        <v>4.06</v>
       </c>
       <c r="CD15" t="n">
         <v>4.47</v>
@@ -6864,154 +6864,154 @@
         <v>1.47</v>
       </c>
       <c r="CF15" t="n">
-        <v>3.14</v>
+        <v>3.13</v>
       </c>
       <c r="CG15" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="CH15" t="n">
         <v>1.33</v>
       </c>
       <c r="CI15" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CJ15" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="CK15" t="n">
         <v>1.6</v>
       </c>
       <c r="CL15" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="CN15" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CO15" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CP15" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.96</v>
+        <v>3.93</v>
       </c>
       <c r="CR15" t="n">
         <v>1.49</v>
       </c>
       <c r="CS15" t="n">
-        <v>3.22</v>
+        <v>3.21</v>
       </c>
       <c r="CT15" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="CU15" t="n">
         <v>1.37</v>
       </c>
       <c r="CV15" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="CW15" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="CX15" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CY15" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CZ15" t="n">
-        <v>2.21</v>
+        <v>2.23</v>
       </c>
       <c r="DA15" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="DB15" t="n">
         <v>1.41</v>
       </c>
       <c r="DC15" t="n">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="DD15" t="n">
-        <v>4.31</v>
+        <v>4.27</v>
       </c>
       <c r="DE15" t="n">
         <v>0.11</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="DG15" t="n">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="DH15" t="n">
-        <v>88.23</v>
+        <v>89.39</v>
       </c>
       <c r="DI15" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ15" t="n">
-        <v>2.41</v>
+        <v>2.33</v>
       </c>
       <c r="DK15" t="n">
-        <v>4</v>
+        <v>4.06</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.23</v>
+        <v>0.28</v>
       </c>
       <c r="DM15" t="n">
-        <v>47.47</v>
+        <v>47.33</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="DO15" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="DP15" t="n">
-        <v>13.48</v>
+        <v>12.94</v>
       </c>
       <c r="DQ15" t="n">
-        <v>12.89</v>
+        <v>12.61</v>
       </c>
       <c r="DR15" t="n">
-        <v>8</v>
+        <v>7.89</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="DU15" t="n">
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>51.82</v>
+        <v>52.11</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="DX15" t="n">
-        <v>12.47</v>
+        <v>12.44</v>
       </c>
       <c r="DY15" t="n">
-        <v>7.94</v>
+        <v>7.89</v>
       </c>
       <c r="DZ15" t="n">
-        <v>4.53</v>
+        <v>4.56</v>
       </c>
       <c r="EA15" t="n">
-        <v>22.47</v>
+        <v>22.56</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="EC15" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
     </row>
     <row r="16">
@@ -7021,94 +7021,94 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D16" t="n">
         <v>8</v>
       </c>
       <c r="E16" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="F16" t="n">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="G16" t="n">
         <v>4</v>
       </c>
       <c r="H16" t="n">
-        <v>101.11</v>
+        <v>100.4</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="K16" t="n">
-        <v>7.33</v>
+        <v>7.3</v>
       </c>
       <c r="L16" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="M16" t="n">
-        <v>47.44</v>
+        <v>47.1</v>
       </c>
       <c r="N16" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="O16" t="n">
-        <v>3.33</v>
+        <v>3.3</v>
       </c>
       <c r="P16" t="n">
-        <v>12.56</v>
+        <v>12.7</v>
       </c>
       <c r="Q16" t="n">
-        <v>14.67</v>
+        <v>14.3</v>
       </c>
       <c r="R16" t="n">
-        <v>7.33</v>
+        <v>7.6</v>
       </c>
       <c r="S16" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T16" t="n">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="U16" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="V16" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="Y16" t="n">
         <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>15.44</v>
+        <v>15.6</v>
       </c>
       <c r="AA16" t="n">
-        <v>9.220000000000001</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AB16" t="n">
-        <v>6.22</v>
+        <v>6.3</v>
       </c>
       <c r="AC16" t="n">
-        <v>19.44</v>
+        <v>18.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="AF16" t="n">
         <v>0</v>
@@ -7192,70 +7192,70 @@
         <v>3.25</v>
       </c>
       <c r="BG16" t="n">
-        <v>3.82</v>
+        <v>3.72</v>
       </c>
       <c r="BH16" t="n">
-        <v>11.29</v>
+        <v>11.44</v>
       </c>
       <c r="BI16" t="n">
-        <v>3.82</v>
+        <v>3.72</v>
       </c>
       <c r="BJ16" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BL16" t="n">
         <v>1</v>
       </c>
       <c r="BM16" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="BN16" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.71</v>
+        <v>1.61</v>
       </c>
       <c r="BP16" t="n">
-        <v>5.59</v>
+        <v>5.56</v>
       </c>
       <c r="BQ16" t="n">
-        <v>5.71</v>
+        <v>5.89</v>
       </c>
       <c r="BR16" t="n">
         <v>100</v>
       </c>
       <c r="BS16" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BT16" t="n">
-        <v>88.23999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BU16" t="n">
-        <v>64.70999999999999</v>
+        <v>61.11</v>
       </c>
       <c r="BV16" t="n">
-        <v>29.41</v>
+        <v>27.78</v>
       </c>
       <c r="BW16" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BX16" t="n">
-        <v>76.47</v>
+        <v>77.78</v>
       </c>
       <c r="BY16" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="BZ16" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="CA16" t="n">
-        <v>3.63</v>
+        <v>3.64</v>
       </c>
       <c r="CB16" t="n">
-        <v>3.77</v>
+        <v>3.8</v>
       </c>
       <c r="CC16" t="n">
         <v>3.03</v>
@@ -7270,7 +7270,7 @@
         <v>2.5</v>
       </c>
       <c r="CG16" t="n">
-        <v>3.07</v>
+        <v>3.09</v>
       </c>
       <c r="CH16" t="n">
         <v>1.47</v>
@@ -7288,7 +7288,7 @@
         <v>1.91</v>
       </c>
       <c r="CM16" t="n">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="CN16" t="n">
         <v>1.91</v>
@@ -7297,19 +7297,19 @@
         <v>1.22</v>
       </c>
       <c r="CP16" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CQ16" t="n">
-        <v>2.8</v>
+        <v>2.79</v>
       </c>
       <c r="CR16" t="n">
         <v>1.38</v>
       </c>
       <c r="CS16" t="n">
-        <v>2.71</v>
+        <v>2.7</v>
       </c>
       <c r="CT16" t="n">
-        <v>3.15</v>
+        <v>3.16</v>
       </c>
       <c r="CU16" t="n">
         <v>1.5</v>
@@ -7324,7 +7324,7 @@
         <v>1.53</v>
       </c>
       <c r="CY16" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CZ16" t="n">
         <v>2.42</v>
@@ -7333,88 +7333,88 @@
         <v>1.92</v>
       </c>
       <c r="DB16" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="DC16" t="n">
         <v>1.77</v>
       </c>
       <c r="DD16" t="n">
-        <v>2.92</v>
+        <v>2.91</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
       <c r="DG16" t="n">
-        <v>3.35</v>
+        <v>3.39</v>
       </c>
       <c r="DH16" t="n">
-        <v>96.12</v>
+        <v>96</v>
       </c>
       <c r="DI16" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DJ16" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="DK16" t="n">
-        <v>6.18</v>
+        <v>6.22</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="DM16" t="n">
-        <v>42.94</v>
+        <v>43</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.95</v>
+        <v>0.89</v>
       </c>
       <c r="DO16" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="DP16" t="n">
-        <v>13.12</v>
+        <v>13.17</v>
       </c>
       <c r="DQ16" t="n">
-        <v>15.82</v>
+        <v>15.55</v>
       </c>
       <c r="DR16" t="n">
-        <v>7.65</v>
+        <v>7.78</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>53.88</v>
+        <v>53.39</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DX16" t="n">
-        <v>14.06</v>
+        <v>14.22</v>
       </c>
       <c r="DY16" t="n">
-        <v>8.23</v>
+        <v>8.33</v>
       </c>
       <c r="DZ16" t="n">
-        <v>5.82</v>
+        <v>5.89</v>
       </c>
       <c r="EA16" t="n">
-        <v>18.41</v>
+        <v>17.94</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="EC16" t="n">
-        <v>2.76</v>
+        <v>2.83</v>
       </c>
     </row>
     <row r="17">
@@ -7424,13 +7424,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C17" t="n">
         <v>9</v>
       </c>
       <c r="D17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E17" t="n">
         <v>0.11</v>
@@ -7517,49 +7517,49 @@
         <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.38</v>
+        <v>2.22</v>
       </c>
       <c r="AI17" t="n">
-        <v>85.12</v>
+        <v>83.89</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="AK17" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="AL17" t="n">
-        <v>3.38</v>
+        <v>3.33</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AN17" t="n">
-        <v>28.5</v>
+        <v>28.44</v>
       </c>
       <c r="AO17" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AP17" t="n">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="AQ17" t="n">
-        <v>16.38</v>
+        <v>16.56</v>
       </c>
       <c r="AR17" t="n">
-        <v>13.62</v>
+        <v>12.67</v>
       </c>
       <c r="AS17" t="n">
-        <v>8.880000000000001</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="AT17" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AU17" t="n">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="AV17" t="n">
         <v>0</v>
@@ -7571,82 +7571,82 @@
         <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>43.88</v>
+        <v>42.44</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="BA17" t="n">
-        <v>11.75</v>
+        <v>11.56</v>
       </c>
       <c r="BB17" t="n">
-        <v>7.12</v>
+        <v>7.11</v>
       </c>
       <c r="BC17" t="n">
-        <v>4.62</v>
+        <v>4.44</v>
       </c>
       <c r="BD17" t="n">
-        <v>22.62</v>
+        <v>22.33</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="BF17" t="n">
-        <v>2.62</v>
+        <v>2.78</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="BH17" t="n">
         <v>9.06</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="BJ17" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.29</v>
+        <v>0.33</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.65</v>
+        <v>0.72</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="BP17" t="n">
-        <v>3.94</v>
+        <v>3.89</v>
       </c>
       <c r="BQ17" t="n">
-        <v>4.53</v>
+        <v>4.61</v>
       </c>
       <c r="BR17" t="n">
         <v>100</v>
       </c>
       <c r="BS17" t="n">
-        <v>58.82</v>
+        <v>61.11</v>
       </c>
       <c r="BT17" t="n">
-        <v>47.06</v>
+        <v>50</v>
       </c>
       <c r="BU17" t="n">
-        <v>23.53</v>
+        <v>22.22</v>
       </c>
       <c r="BV17" t="n">
-        <v>17.65</v>
+        <v>16.67</v>
       </c>
       <c r="BW17" t="n">
-        <v>17.65</v>
+        <v>16.67</v>
       </c>
       <c r="BX17" t="n">
-        <v>47.06</v>
+        <v>44.44</v>
       </c>
       <c r="BY17" t="n">
         <v>3.24</v>
@@ -7655,169 +7655,169 @@
         <v>3.55</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.42</v>
+        <v>3.48</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.66</v>
+        <v>3.71</v>
       </c>
       <c r="CC17" t="n">
-        <v>5.37</v>
+        <v>5.51</v>
       </c>
       <c r="CD17" t="n">
-        <v>6.55</v>
+        <v>6.59</v>
       </c>
       <c r="CE17" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="CF17" t="n">
-        <v>3.05</v>
+        <v>3.02</v>
       </c>
       <c r="CG17" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="CH17" t="n">
         <v>1.35</v>
       </c>
       <c r="CI17" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CJ17" t="n">
         <v>1.94</v>
       </c>
       <c r="CK17" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CL17" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="CN17" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CO17" t="n">
         <v>1.34</v>
       </c>
       <c r="CP17" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="CQ17" t="n">
-        <v>3.7</v>
+        <v>3.66</v>
       </c>
       <c r="CR17" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CS17" t="n">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="CT17" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="CU17" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CV17" t="n">
         <v>1.88</v>
       </c>
       <c r="CW17" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="CX17" t="n">
         <v>1.64</v>
       </c>
       <c r="CY17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="CZ17" t="n">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="DA17" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="DB17" t="n">
         <v>1.37</v>
       </c>
       <c r="DC17" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="DD17" t="n">
-        <v>3.99</v>
+        <v>3.95</v>
       </c>
       <c r="DE17" t="n">
         <v>0.06</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="DG17" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="DH17" t="n">
-        <v>82.70999999999999</v>
+        <v>82.22</v>
       </c>
       <c r="DI17" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="DJ17" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="DK17" t="n">
-        <v>3.24</v>
+        <v>3.22</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DM17" t="n">
-        <v>30.24</v>
+        <v>30.11</v>
       </c>
       <c r="DN17" t="n">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="DO17" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="DP17" t="n">
-        <v>17.41</v>
+        <v>17.44</v>
       </c>
       <c r="DQ17" t="n">
-        <v>13.41</v>
+        <v>12.94</v>
       </c>
       <c r="DR17" t="n">
-        <v>8.890000000000001</v>
+        <v>8.84</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>44.65</v>
+        <v>43.88</v>
       </c>
       <c r="DW17" t="n">
         <v>0.06</v>
       </c>
       <c r="DX17" t="n">
-        <v>11</v>
+        <v>10.94</v>
       </c>
       <c r="DY17" t="n">
         <v>6.94</v>
       </c>
       <c r="DZ17" t="n">
-        <v>4.06</v>
+        <v>4</v>
       </c>
       <c r="EA17" t="n">
-        <v>21.17</v>
+        <v>21.11</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="EC17" t="n">
-        <v>2.82</v>
+        <v>2.89</v>
       </c>
     </row>
     <row r="18">
@@ -7827,94 +7827,94 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D18" t="n">
         <v>8</v>
       </c>
       <c r="E18" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="F18" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="G18" t="n">
-        <v>4.78</v>
+        <v>4.5</v>
       </c>
       <c r="H18" t="n">
-        <v>117.22</v>
+        <v>113</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="J18" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="K18" t="n">
-        <v>6.89</v>
+        <v>7</v>
       </c>
       <c r="L18" t="n">
-        <v>0.67</v>
+        <v>0.8</v>
       </c>
       <c r="M18" t="n">
-        <v>66.78</v>
+        <v>65.7</v>
       </c>
       <c r="N18" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="O18" t="n">
-        <v>2.11</v>
+        <v>2.5</v>
       </c>
       <c r="P18" t="n">
-        <v>17.89</v>
+        <v>17.6</v>
       </c>
       <c r="Q18" t="n">
-        <v>12.89</v>
+        <v>12.9</v>
       </c>
       <c r="R18" t="n">
-        <v>5.11</v>
+        <v>5.2</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
       </c>
       <c r="T18" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="U18" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="V18" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>54.78</v>
+        <v>52.5</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="Z18" t="n">
-        <v>17.44</v>
+        <v>17.4</v>
       </c>
       <c r="AA18" t="n">
-        <v>11.89</v>
+        <v>11.9</v>
       </c>
       <c r="AB18" t="n">
-        <v>5.56</v>
+        <v>5.5</v>
       </c>
       <c r="AC18" t="n">
-        <v>29</v>
+        <v>29.1</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="AF18" t="n">
         <v>0.12</v>
@@ -7998,70 +7998,70 @@
         <v>3.38</v>
       </c>
       <c r="BG18" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="BH18" t="n">
-        <v>9.119999999999999</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BL18" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="BO18" t="n">
-        <v>0.88</v>
+        <v>0.83</v>
       </c>
       <c r="BP18" t="n">
-        <v>3.18</v>
+        <v>3.5</v>
       </c>
       <c r="BQ18" t="n">
-        <v>5.94</v>
+        <v>5.89</v>
       </c>
       <c r="BR18" t="n">
-        <v>88.23999999999999</v>
+        <v>88.89</v>
       </c>
       <c r="BS18" t="n">
-        <v>58.82</v>
+        <v>55.56</v>
       </c>
       <c r="BT18" t="n">
-        <v>29.41</v>
+        <v>27.78</v>
       </c>
       <c r="BU18" t="n">
-        <v>17.65</v>
+        <v>16.67</v>
       </c>
       <c r="BV18" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BW18" t="n">
         <v>0</v>
       </c>
       <c r="BX18" t="n">
-        <v>47.06</v>
+        <v>44.44</v>
       </c>
       <c r="BY18" t="n">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="BZ18" t="n">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.28</v>
+        <v>3.31</v>
       </c>
       <c r="CB18" t="n">
-        <v>3.39</v>
+        <v>3.44</v>
       </c>
       <c r="CC18" t="n">
         <v>2.74</v>
@@ -8073,25 +8073,25 @@
         <v>1.42</v>
       </c>
       <c r="CF18" t="n">
-        <v>2.99</v>
+        <v>2.97</v>
       </c>
       <c r="CG18" t="n">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="CH18" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CI18" t="n">
         <v>1.84</v>
       </c>
       <c r="CJ18" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CK18" t="n">
         <v>1.62</v>
       </c>
       <c r="CL18" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="CM18" t="n">
         <v>2.14</v>
@@ -8103,19 +8103,19 @@
         <v>1.35</v>
       </c>
       <c r="CP18" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="CQ18" t="n">
-        <v>3.85</v>
+        <v>3.82</v>
       </c>
       <c r="CR18" t="n">
         <v>1.47</v>
       </c>
       <c r="CS18" t="n">
-        <v>3.1</v>
+        <v>3.09</v>
       </c>
       <c r="CT18" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="CU18" t="n">
         <v>1.4</v>
@@ -8127,100 +8127,100 @@
         <v>1.93</v>
       </c>
       <c r="CX18" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CY18" t="n">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="CZ18" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="DA18" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="DB18" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="DC18" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="DD18" t="n">
-        <v>4.05</v>
+        <v>4.01</v>
       </c>
       <c r="DE18" t="n">
         <v>0.11</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="DG18" t="n">
-        <v>4.12</v>
+        <v>4</v>
       </c>
       <c r="DH18" t="n">
-        <v>113.12</v>
+        <v>111</v>
       </c>
       <c r="DI18" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="DJ18" t="n">
         <v>3</v>
       </c>
       <c r="DK18" t="n">
-        <v>6.41</v>
+        <v>6.5</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.59</v>
+        <v>0.67</v>
       </c>
       <c r="DM18" t="n">
-        <v>57.65</v>
+        <v>57.56</v>
       </c>
       <c r="DN18" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="DO18" t="n">
-        <v>2.29</v>
+        <v>2.5</v>
       </c>
       <c r="DP18" t="n">
-        <v>17.82</v>
+        <v>17.67</v>
       </c>
       <c r="DQ18" t="n">
-        <v>13.29</v>
+        <v>13.28</v>
       </c>
       <c r="DR18" t="n">
-        <v>6.82</v>
+        <v>6.78</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DT18" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DU18" t="n">
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>53.06</v>
+        <v>51.89</v>
       </c>
       <c r="DW18" t="n">
         <v>0.11</v>
       </c>
       <c r="DX18" t="n">
-        <v>15.35</v>
+        <v>15.44</v>
       </c>
       <c r="DY18" t="n">
-        <v>10.59</v>
+        <v>10.66</v>
       </c>
       <c r="DZ18" t="n">
-        <v>4.77</v>
+        <v>4.78</v>
       </c>
       <c r="EA18" t="n">
-        <v>26.18</v>
+        <v>26.39</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="EC18" t="n">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
     </row>
     <row r="19">
@@ -8230,10 +8230,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D19" t="n">
         <v>9</v>
@@ -8242,49 +8242,49 @@
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="G19" t="n">
-        <v>1.12</v>
+        <v>1.67</v>
       </c>
       <c r="H19" t="n">
-        <v>96</v>
+        <v>94.67</v>
       </c>
       <c r="I19" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="J19" t="n">
-        <v>3.75</v>
+        <v>3.67</v>
       </c>
       <c r="K19" t="n">
-        <v>4</v>
+        <v>4.44</v>
       </c>
       <c r="L19" t="n">
-        <v>0.75</v>
+        <v>0.89</v>
       </c>
       <c r="M19" t="n">
-        <v>43.25</v>
+        <v>43.33</v>
       </c>
       <c r="N19" t="n">
-        <v>2.12</v>
+        <v>1.89</v>
       </c>
       <c r="O19" t="n">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="P19" t="n">
-        <v>12.88</v>
+        <v>12.89</v>
       </c>
       <c r="Q19" t="n">
-        <v>14.88</v>
+        <v>15.56</v>
       </c>
       <c r="R19" t="n">
-        <v>7.12</v>
+        <v>7.22</v>
       </c>
       <c r="S19" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="T19" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
@@ -8296,28 +8296,28 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>51.25</v>
+        <v>52.11</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="Z19" t="n">
-        <v>11.12</v>
+        <v>11.56</v>
       </c>
       <c r="AA19" t="n">
-        <v>7.25</v>
+        <v>8</v>
       </c>
       <c r="AB19" t="n">
-        <v>3.88</v>
+        <v>3.56</v>
       </c>
       <c r="AC19" t="n">
-        <v>23.12</v>
+        <v>23</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="AF19" t="n">
         <v>0.11</v>
@@ -8401,70 +8401,70 @@
         <v>2.67</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.41</v>
+        <v>2.44</v>
       </c>
       <c r="BH19" t="n">
-        <v>10.06</v>
+        <v>10.17</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.41</v>
+        <v>2.44</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.88</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.59</v>
+        <v>1.67</v>
       </c>
       <c r="BO19" t="n">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="BP19" t="n">
-        <v>5.29</v>
+        <v>5.22</v>
       </c>
       <c r="BQ19" t="n">
-        <v>4.71</v>
+        <v>4.89</v>
       </c>
       <c r="BR19" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BS19" t="n">
-        <v>58.82</v>
+        <v>61.11</v>
       </c>
       <c r="BT19" t="n">
-        <v>35.29</v>
+        <v>38.89</v>
       </c>
       <c r="BU19" t="n">
-        <v>29.41</v>
+        <v>27.78</v>
       </c>
       <c r="BV19" t="n">
-        <v>17.65</v>
+        <v>16.67</v>
       </c>
       <c r="BW19" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BX19" t="n">
-        <v>47.06</v>
+        <v>50</v>
       </c>
       <c r="BY19" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="BZ19" t="n">
-        <v>2.46</v>
+        <v>2.43</v>
       </c>
       <c r="CA19" t="n">
-        <v>3.19</v>
+        <v>3.17</v>
       </c>
       <c r="CB19" t="n">
-        <v>3.31</v>
+        <v>3.3</v>
       </c>
       <c r="CC19" t="n">
         <v>3.75</v>
@@ -8473,10 +8473,10 @@
         <v>4.39</v>
       </c>
       <c r="CE19" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="CF19" t="n">
-        <v>3.13</v>
+        <v>3.14</v>
       </c>
       <c r="CG19" t="n">
         <v>2.61</v>
@@ -8485,145 +8485,145 @@
         <v>1.33</v>
       </c>
       <c r="CI19" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CJ19" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CK19" t="n">
         <v>1.59</v>
       </c>
       <c r="CL19" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="CM19" t="n">
         <v>2.3</v>
       </c>
       <c r="CN19" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CO19" t="n">
         <v>1.38</v>
       </c>
       <c r="CP19" t="n">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="CQ19" t="n">
-        <v>4.01</v>
+        <v>4.06</v>
       </c>
       <c r="CR19" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="CS19" t="n">
         <v>3.22</v>
       </c>
       <c r="CT19" t="n">
-        <v>2.74</v>
+        <v>2.73</v>
       </c>
       <c r="CU19" t="n">
         <v>1.37</v>
       </c>
       <c r="CV19" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CW19" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="CX19" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CY19" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CZ19" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="DA19" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="DB19" t="n">
         <v>1.39</v>
       </c>
       <c r="DC19" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="DD19" t="n">
-        <v>4.06</v>
+        <v>4.1</v>
       </c>
       <c r="DE19" t="n">
         <v>0.06</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="DG19" t="n">
-        <v>2.29</v>
+        <v>2.5</v>
       </c>
       <c r="DH19" t="n">
-        <v>92.65000000000001</v>
+        <v>92.17</v>
       </c>
       <c r="DI19" t="n">
         <v>0.11</v>
       </c>
       <c r="DJ19" t="n">
-        <v>3.35</v>
+        <v>3.34</v>
       </c>
       <c r="DK19" t="n">
-        <v>4.76</v>
+        <v>4.94</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.47</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DM19" t="n">
-        <v>42.7</v>
+        <v>42.78</v>
       </c>
       <c r="DN19" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="DO19" t="n">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
       <c r="DP19" t="n">
         <v>13.06</v>
       </c>
       <c r="DQ19" t="n">
-        <v>15.36</v>
+        <v>15.67</v>
       </c>
       <c r="DR19" t="n">
-        <v>6.82</v>
+        <v>6.89</v>
       </c>
       <c r="DS19" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DT19" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DU19" t="n">
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>50.18</v>
+        <v>50.66</v>
       </c>
       <c r="DW19" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="DX19" t="n">
-        <v>12.12</v>
+        <v>12.28</v>
       </c>
       <c r="DY19" t="n">
-        <v>8.529999999999999</v>
+        <v>8.84</v>
       </c>
       <c r="DZ19" t="n">
-        <v>3.59</v>
+        <v>3.44</v>
       </c>
       <c r="EA19" t="n">
-        <v>20.29</v>
+        <v>20.39</v>
       </c>
       <c r="EB19" t="n">
         <v>1.33</v>
       </c>
       <c r="EC19" t="n">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="20">
@@ -8633,13 +8633,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C20" t="n">
         <v>9</v>
       </c>
       <c r="D20" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -8723,52 +8723,52 @@
         <v>2.56</v>
       </c>
       <c r="AF20" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AH20" t="n">
-        <v>3.12</v>
+        <v>2.78</v>
       </c>
       <c r="AI20" t="n">
-        <v>100.12</v>
+        <v>97.78</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AK20" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="AL20" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="AM20" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="AN20" t="n">
-        <v>38.38</v>
+        <v>37.56</v>
       </c>
       <c r="AO20" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AQ20" t="n">
-        <v>12.38</v>
+        <v>13.11</v>
       </c>
       <c r="AR20" t="n">
-        <v>13.62</v>
+        <v>14</v>
       </c>
       <c r="AS20" t="n">
-        <v>6.62</v>
+        <v>7.22</v>
       </c>
       <c r="AT20" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AU20" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AV20" t="n">
         <v>0</v>
@@ -8780,82 +8780,82 @@
         <v>0</v>
       </c>
       <c r="AY20" t="n">
-        <v>49.88</v>
+        <v>47.33</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="BA20" t="n">
-        <v>10.25</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="BB20" t="n">
-        <v>6.88</v>
+        <v>6.11</v>
       </c>
       <c r="BC20" t="n">
-        <v>3.38</v>
+        <v>3</v>
       </c>
       <c r="BD20" t="n">
-        <v>19.5</v>
+        <v>19.44</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.17</v>
+        <v>1.07</v>
       </c>
       <c r="BF20" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="BG20" t="n">
-        <v>2.47</v>
+        <v>2.33</v>
       </c>
       <c r="BH20" t="n">
-        <v>9.289999999999999</v>
+        <v>9.06</v>
       </c>
       <c r="BI20" t="n">
-        <v>2.47</v>
+        <v>2.33</v>
       </c>
       <c r="BJ20" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="BK20" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="BL20" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="BM20" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="BN20" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BO20" t="n">
         <v>1</v>
       </c>
-      <c r="BM20" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="BN20" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="BO20" t="n">
-        <v>1.06</v>
-      </c>
       <c r="BP20" t="n">
-        <v>4.24</v>
+        <v>4.17</v>
       </c>
       <c r="BQ20" t="n">
-        <v>5.06</v>
+        <v>4.89</v>
       </c>
       <c r="BR20" t="n">
-        <v>88.23999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BS20" t="n">
-        <v>76.47</v>
+        <v>72.22</v>
       </c>
       <c r="BT20" t="n">
-        <v>52.94</v>
+        <v>50</v>
       </c>
       <c r="BU20" t="n">
-        <v>23.53</v>
+        <v>22.22</v>
       </c>
       <c r="BV20" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BW20" t="n">
         <v>0</v>
       </c>
       <c r="BX20" t="n">
-        <v>58.82</v>
+        <v>55.56</v>
       </c>
       <c r="BY20" t="n">
         <v>1.88</v>
@@ -8864,55 +8864,55 @@
         <v>2.02</v>
       </c>
       <c r="CA20" t="n">
-        <v>3.19</v>
+        <v>3.2</v>
       </c>
       <c r="CB20" t="n">
         <v>3.28</v>
       </c>
       <c r="CC20" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="CD20" t="n">
-        <v>3.64</v>
+        <v>3.62</v>
       </c>
       <c r="CE20" t="n">
         <v>1.47</v>
       </c>
       <c r="CF20" t="n">
-        <v>3.26</v>
+        <v>3.25</v>
       </c>
       <c r="CG20" t="n">
-        <v>2.51</v>
+        <v>2.54</v>
       </c>
       <c r="CH20" t="n">
         <v>1.31</v>
       </c>
       <c r="CI20" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CJ20" t="n">
         <v>2.03</v>
       </c>
       <c r="CK20" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CL20" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="CM20" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="CN20" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CO20" t="n">
         <v>1.42</v>
       </c>
       <c r="CP20" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="CQ20" t="n">
-        <v>4.34</v>
+        <v>4.3</v>
       </c>
       <c r="CR20" t="n">
         <v>1.54</v>
@@ -8921,112 +8921,112 @@
         <v>3.24</v>
       </c>
       <c r="CT20" t="n">
-        <v>2.59</v>
+        <v>2.61</v>
       </c>
       <c r="CU20" t="n">
         <v>1.36</v>
       </c>
       <c r="CV20" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CW20" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="CX20" t="n">
         <v>1.68</v>
       </c>
       <c r="CY20" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="CZ20" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="DA20" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="DB20" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="DC20" t="n">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="DD20" t="n">
-        <v>4.66</v>
+        <v>4.62</v>
       </c>
       <c r="DE20" t="n">
         <v>0.06</v>
       </c>
       <c r="DF20" t="n">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="DG20" t="n">
-        <v>3.06</v>
+        <v>2.89</v>
       </c>
       <c r="DH20" t="n">
-        <v>107.94</v>
+        <v>106.34</v>
       </c>
       <c r="DI20" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DJ20" t="n">
-        <v>2.65</v>
+        <v>2.67</v>
       </c>
       <c r="DK20" t="n">
-        <v>5.12</v>
+        <v>4.84</v>
       </c>
       <c r="DL20" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="DM20" t="n">
-        <v>50</v>
+        <v>48.94</v>
       </c>
       <c r="DN20" t="n">
         <v>1</v>
       </c>
       <c r="DO20" t="n">
-        <v>2.06</v>
+        <v>1.95</v>
       </c>
       <c r="DP20" t="n">
-        <v>14.12</v>
+        <v>14.39</v>
       </c>
       <c r="DQ20" t="n">
-        <v>12.23</v>
+        <v>12.5</v>
       </c>
       <c r="DR20" t="n">
-        <v>6.59</v>
+        <v>6.89</v>
       </c>
       <c r="DS20" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DT20" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DU20" t="n">
         <v>0</v>
       </c>
       <c r="DV20" t="n">
-        <v>52.71</v>
+        <v>51.28</v>
       </c>
       <c r="DW20" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DX20" t="n">
-        <v>13.88</v>
+        <v>13.11</v>
       </c>
       <c r="DY20" t="n">
-        <v>9.24</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="DZ20" t="n">
-        <v>4.65</v>
+        <v>4.39</v>
       </c>
       <c r="EA20" t="n">
         <v>18.88</v>
       </c>
       <c r="EB20" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="EC20" t="n">
-        <v>2.41</v>
+        <v>2.44</v>
       </c>
     </row>
     <row r="21">
@@ -9276,7 +9276,7 @@
         <v>3.44</v>
       </c>
       <c r="CD21" t="n">
-        <v>3.92</v>
+        <v>3.96</v>
       </c>
       <c r="CE21" t="n">
         <v>1.58</v>
@@ -9351,10 +9351,10 @@
         <v>1.6</v>
       </c>
       <c r="DC21" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="DD21" t="n">
-        <v>5.77</v>
+        <v>5.78</v>
       </c>
       <c r="DE21" t="n">
         <v>0</v>
@@ -9439,10 +9439,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C22" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D22" t="n">
         <v>8</v>
@@ -9451,76 +9451,76 @@
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="G22" t="n">
-        <v>2.67</v>
+        <v>2.6</v>
       </c>
       <c r="H22" t="n">
-        <v>112.11</v>
+        <v>111</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="K22" t="n">
-        <v>5.33</v>
+        <v>5.4</v>
       </c>
       <c r="L22" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="M22" t="n">
-        <v>48.44</v>
+        <v>47.8</v>
       </c>
       <c r="N22" t="n">
-        <v>0.44</v>
+        <v>0.6</v>
       </c>
       <c r="O22" t="n">
-        <v>2.67</v>
+        <v>2.8</v>
       </c>
       <c r="P22" t="n">
-        <v>12.89</v>
+        <v>13</v>
       </c>
       <c r="Q22" t="n">
-        <v>11</v>
+        <v>10.9</v>
       </c>
       <c r="R22" t="n">
-        <v>7.33</v>
+        <v>6.9</v>
       </c>
       <c r="S22" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="T22" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="U22" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="V22" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>45</v>
+        <v>45.8</v>
       </c>
       <c r="Y22" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="Z22" t="n">
-        <v>13.33</v>
+        <v>13.5</v>
       </c>
       <c r="AA22" t="n">
-        <v>7.89</v>
+        <v>8.1</v>
       </c>
       <c r="AB22" t="n">
-        <v>5.44</v>
+        <v>5.4</v>
       </c>
       <c r="AC22" t="n">
-        <v>20.22</v>
+        <v>19.8</v>
       </c>
       <c r="AD22" t="n">
         <v>1.58</v>
@@ -9610,70 +9610,70 @@
         <v>3.38</v>
       </c>
       <c r="BG22" t="n">
-        <v>2.59</v>
+        <v>2.5</v>
       </c>
       <c r="BH22" t="n">
-        <v>9.529999999999999</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="BI22" t="n">
-        <v>2.59</v>
+        <v>2.5</v>
       </c>
       <c r="BJ22" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BK22" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BL22" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="BM22" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BN22" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="BO22" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="BP22" t="n">
-        <v>4.53</v>
+        <v>4.56</v>
       </c>
       <c r="BQ22" t="n">
-        <v>4.94</v>
+        <v>4.78</v>
       </c>
       <c r="BR22" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BS22" t="n">
-        <v>64.70999999999999</v>
+        <v>61.11</v>
       </c>
       <c r="BT22" t="n">
-        <v>47.06</v>
+        <v>44.44</v>
       </c>
       <c r="BU22" t="n">
-        <v>23.53</v>
+        <v>22.22</v>
       </c>
       <c r="BV22" t="n">
-        <v>17.65</v>
+        <v>16.67</v>
       </c>
       <c r="BW22" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BX22" t="n">
-        <v>58.82</v>
+        <v>55.56</v>
       </c>
       <c r="BY22" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="BZ22" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="CA22" t="n">
         <v>3.21</v>
       </c>
       <c r="CB22" t="n">
-        <v>3.32</v>
+        <v>3.31</v>
       </c>
       <c r="CC22" t="n">
         <v>3.23</v>
@@ -9685,13 +9685,13 @@
         <v>1.43</v>
       </c>
       <c r="CF22" t="n">
-        <v>3.08</v>
+        <v>3.09</v>
       </c>
       <c r="CG22" t="n">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="CH22" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="CI22" t="n">
         <v>1.88</v>
@@ -9700,13 +9700,13 @@
         <v>1.87</v>
       </c>
       <c r="CK22" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CL22" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="CM22" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="CN22" t="n">
         <v>1.72</v>
@@ -9715,16 +9715,16 @@
         <v>1.36</v>
       </c>
       <c r="CP22" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="CQ22" t="n">
-        <v>3.84</v>
+        <v>3.85</v>
       </c>
       <c r="CR22" t="n">
         <v>1.47</v>
       </c>
       <c r="CS22" t="n">
-        <v>3.09</v>
+        <v>3.11</v>
       </c>
       <c r="CT22" t="n">
         <v>2.81</v>
@@ -9733,22 +9733,22 @@
         <v>1.4</v>
       </c>
       <c r="CV22" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CW22" t="n">
         <v>1.96</v>
       </c>
       <c r="CX22" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CY22" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="CZ22" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="DA22" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="DB22" t="n">
         <v>1.42</v>
@@ -9760,79 +9760,79 @@
         <v>4.31</v>
       </c>
       <c r="DE22" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DF22" t="n">
-        <v>2.24</v>
+        <v>2.11</v>
       </c>
       <c r="DG22" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="DH22" t="n">
-        <v>101.06</v>
+        <v>101.05</v>
       </c>
       <c r="DI22" t="n">
         <v>0</v>
       </c>
       <c r="DJ22" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="DK22" t="n">
-        <v>4.23</v>
+        <v>4.33</v>
       </c>
       <c r="DL22" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="DM22" t="n">
-        <v>41.7</v>
+        <v>41.72</v>
       </c>
       <c r="DN22" t="n">
-        <v>0.65</v>
+        <v>0.72</v>
       </c>
       <c r="DO22" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="DP22" t="n">
-        <v>12.65</v>
+        <v>12.72</v>
       </c>
       <c r="DQ22" t="n">
-        <v>11</v>
+        <v>10.94</v>
       </c>
       <c r="DR22" t="n">
-        <v>7.88</v>
+        <v>7.61</v>
       </c>
       <c r="DS22" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DT22" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DU22" t="n">
         <v>0</v>
       </c>
       <c r="DV22" t="n">
-        <v>43.94</v>
+        <v>44.44</v>
       </c>
       <c r="DW22" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DX22" t="n">
-        <v>10.88</v>
+        <v>11.11</v>
       </c>
       <c r="DY22" t="n">
-        <v>6.41</v>
+        <v>6.61</v>
       </c>
       <c r="DZ22" t="n">
-        <v>4.47</v>
+        <v>4.5</v>
       </c>
       <c r="EA22" t="n">
-        <v>20.3</v>
+        <v>20.06</v>
       </c>
       <c r="EB22" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="EC22" t="n">
-        <v>2.65</v>
+        <v>2.61</v>
       </c>
     </row>
     <row r="23">
@@ -9842,13 +9842,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C23" t="n">
         <v>9</v>
       </c>
       <c r="D23" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E23" t="n">
         <v>0.11</v>
@@ -9935,49 +9935,49 @@
         <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.88</v>
+        <v>1.56</v>
       </c>
       <c r="AI23" t="n">
-        <v>89.75</v>
+        <v>91.33</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AK23" t="n">
         <v>2</v>
       </c>
       <c r="AL23" t="n">
-        <v>3.75</v>
+        <v>3.89</v>
       </c>
       <c r="AM23" t="n">
-        <v>0.25</v>
+        <v>0.11</v>
       </c>
       <c r="AN23" t="n">
-        <v>34.25</v>
+        <v>37.22</v>
       </c>
       <c r="AO23" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.88</v>
+        <v>1.56</v>
       </c>
       <c r="AQ23" t="n">
-        <v>11.88</v>
+        <v>11.78</v>
       </c>
       <c r="AR23" t="n">
-        <v>19.25</v>
+        <v>18.89</v>
       </c>
       <c r="AS23" t="n">
-        <v>9.5</v>
+        <v>9.33</v>
       </c>
       <c r="AT23" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="AU23" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="AV23" t="n">
         <v>0</v>
@@ -9989,73 +9989,73 @@
         <v>0</v>
       </c>
       <c r="AY23" t="n">
-        <v>57.12</v>
+        <v>56.89</v>
       </c>
       <c r="AZ23" t="n">
         <v>0</v>
       </c>
       <c r="BA23" t="n">
-        <v>10.12</v>
+        <v>10</v>
       </c>
       <c r="BB23" t="n">
-        <v>7.38</v>
+        <v>7.33</v>
       </c>
       <c r="BC23" t="n">
-        <v>2.75</v>
+        <v>2.67</v>
       </c>
       <c r="BD23" t="n">
-        <v>17.88</v>
+        <v>18</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="BF23" t="n">
         <v>2</v>
       </c>
       <c r="BG23" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="BH23" t="n">
-        <v>7.59</v>
+        <v>7.56</v>
       </c>
       <c r="BI23" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="BJ23" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BK23" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="BL23" t="n">
-        <v>0.35</v>
+        <v>0.39</v>
       </c>
       <c r="BM23" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="BN23" t="n">
-        <v>0.82</v>
+        <v>0.89</v>
       </c>
       <c r="BO23" t="n">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="BP23" t="n">
-        <v>3.53</v>
+        <v>3.28</v>
       </c>
       <c r="BQ23" t="n">
-        <v>4.06</v>
+        <v>3.78</v>
       </c>
       <c r="BR23" t="n">
-        <v>76.47</v>
+        <v>77.78</v>
       </c>
       <c r="BS23" t="n">
-        <v>41.18</v>
+        <v>44.44</v>
       </c>
       <c r="BT23" t="n">
-        <v>29.41</v>
+        <v>27.78</v>
       </c>
       <c r="BU23" t="n">
-        <v>17.65</v>
+        <v>16.67</v>
       </c>
       <c r="BV23" t="n">
         <v>0</v>
@@ -10064,7 +10064,7 @@
         <v>0</v>
       </c>
       <c r="BX23" t="n">
-        <v>41.18</v>
+        <v>44.44</v>
       </c>
       <c r="BY23" t="n">
         <v>1.81</v>
@@ -10073,136 +10073,136 @@
         <v>1.86</v>
       </c>
       <c r="CA23" t="n">
-        <v>3.24</v>
+        <v>3.22</v>
       </c>
       <c r="CB23" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="CC23" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="CD23" t="n">
         <v>3.37</v>
       </c>
-      <c r="CC23" t="n">
-        <v>3.11</v>
-      </c>
-      <c r="CD23" t="n">
-        <v>3.44</v>
-      </c>
       <c r="CE23" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="CF23" t="n">
-        <v>3.2</v>
+        <v>3.22</v>
       </c>
       <c r="CG23" t="n">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="CH23" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="CI23" t="n">
         <v>1.8</v>
       </c>
       <c r="CJ23" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="CK23" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="CL23" t="n">
-        <v>2.27</v>
+        <v>2.29</v>
       </c>
       <c r="CM23" t="n">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="CN23" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CO23" t="n">
         <v>1.39</v>
       </c>
       <c r="CP23" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="CQ23" t="n">
-        <v>4.13</v>
+        <v>4.18</v>
       </c>
       <c r="CR23" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="CS23" t="n">
         <v>3.2</v>
       </c>
       <c r="CT23" t="n">
-        <v>2.69</v>
+        <v>2.67</v>
       </c>
       <c r="CU23" t="n">
         <v>1.37</v>
       </c>
       <c r="CV23" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CW23" t="n">
         <v>2.06</v>
       </c>
       <c r="CX23" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="CY23" t="n">
-        <v>2.21</v>
+        <v>2.23</v>
       </c>
       <c r="CZ23" t="n">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="DA23" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="DB23" t="n">
         <v>1.44</v>
       </c>
       <c r="DC23" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="DD23" t="n">
-        <v>4.5</v>
+        <v>4.55</v>
       </c>
       <c r="DE23" t="n">
         <v>0.06</v>
       </c>
       <c r="DF23" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="DG23" t="n">
-        <v>2</v>
+        <v>1.84</v>
       </c>
       <c r="DH23" t="n">
-        <v>93.53</v>
+        <v>94.11</v>
       </c>
       <c r="DI23" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ23" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="DK23" t="n">
-        <v>3.88</v>
+        <v>3.94</v>
       </c>
       <c r="DL23" t="n">
-        <v>0.23</v>
+        <v>0.16</v>
       </c>
       <c r="DM23" t="n">
-        <v>36.53</v>
+        <v>37.89</v>
       </c>
       <c r="DN23" t="n">
-        <v>0.47</v>
+        <v>0.45</v>
       </c>
       <c r="DO23" t="n">
-        <v>1.89</v>
+        <v>1.72</v>
       </c>
       <c r="DP23" t="n">
-        <v>12.89</v>
+        <v>12.78</v>
       </c>
       <c r="DQ23" t="n">
-        <v>17.7</v>
+        <v>17.61</v>
       </c>
       <c r="DR23" t="n">
-        <v>7.71</v>
+        <v>7.72</v>
       </c>
       <c r="DS23" t="n">
         <v>0</v>
@@ -10214,28 +10214,28 @@
         <v>0</v>
       </c>
       <c r="DV23" t="n">
-        <v>56.11</v>
+        <v>56.06</v>
       </c>
       <c r="DW23" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DX23" t="n">
-        <v>11.23</v>
+        <v>11.11</v>
       </c>
       <c r="DY23" t="n">
-        <v>7.65</v>
+        <v>7.61</v>
       </c>
       <c r="DZ23" t="n">
-        <v>3.59</v>
+        <v>3.5</v>
       </c>
       <c r="EA23" t="n">
-        <v>18.59</v>
+        <v>18.61</v>
       </c>
       <c r="EB23" t="n">
         <v>1.23</v>
       </c>
       <c r="EC23" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Spain_Segunda_División_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Spain_Segunda_División_2025-2026.xlsx
@@ -1391,7 +1391,7 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>1.56</v>
+        <v>1.67</v>
       </c>
       <c r="G2" t="n">
         <v>2.89</v>
@@ -1403,7 +1403,7 @@
         <v>-0.11</v>
       </c>
       <c r="J2" t="n">
-        <v>1.78</v>
+        <v>1.89</v>
       </c>
       <c r="K2" t="n">
         <v>5.56</v>
@@ -1421,7 +1421,7 @@
         <v>2.67</v>
       </c>
       <c r="P2" t="n">
-        <v>9.44</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="Q2" t="n">
         <v>8.44</v>
@@ -1466,7 +1466,7 @@
         <v>1.61</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.56</v>
+        <v>1.67</v>
       </c>
       <c r="AF2" t="n">
         <v>0.33</v>
@@ -1703,7 +1703,7 @@
         <v>0.16</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="DG2" t="n">
         <v>2.34</v>
@@ -1715,7 +1715,7 @@
         <v>0.06</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="DK2" t="n">
         <v>4.89</v>
@@ -1733,7 +1733,7 @@
         <v>2.56</v>
       </c>
       <c r="DP2" t="n">
-        <v>11.11</v>
+        <v>11.28</v>
       </c>
       <c r="DQ2" t="n">
         <v>10.88</v>
@@ -1772,7 +1772,7 @@
         <v>1.47</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="3">
@@ -2470,7 +2470,7 @@
         <v>1.59</v>
       </c>
       <c r="CS4" t="n">
-        <v>3.39</v>
+        <v>3.38</v>
       </c>
       <c r="CT4" t="n">
         <v>2.44</v>
@@ -2588,94 +2588,94 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D5" t="n">
         <v>9</v>
       </c>
       <c r="E5" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="F5" t="n">
-        <v>2.62</v>
+        <v>2.67</v>
       </c>
       <c r="G5" t="n">
-        <v>3.62</v>
+        <v>3.56</v>
       </c>
       <c r="H5" t="n">
-        <v>109.38</v>
+        <v>108.67</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>3.75</v>
+        <v>3.89</v>
       </c>
       <c r="K5" t="n">
-        <v>7.62</v>
+        <v>7.33</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="M5" t="n">
-        <v>65</v>
+        <v>63.33</v>
       </c>
       <c r="N5" t="n">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="O5" t="n">
-        <v>4</v>
+        <v>3.78</v>
       </c>
       <c r="P5" t="n">
-        <v>13.12</v>
+        <v>13.44</v>
       </c>
       <c r="Q5" t="n">
-        <v>14.5</v>
+        <v>14.56</v>
       </c>
       <c r="R5" t="n">
-        <v>4.88</v>
+        <v>5</v>
       </c>
       <c r="S5" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="T5" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="U5" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="V5" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>58.62</v>
+        <v>59</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="Z5" t="n">
-        <v>16.75</v>
+        <v>16.78</v>
       </c>
       <c r="AA5" t="n">
-        <v>11.12</v>
+        <v>11.11</v>
       </c>
       <c r="AB5" t="n">
-        <v>5.62</v>
+        <v>5.67</v>
       </c>
       <c r="AC5" t="n">
-        <v>18.25</v>
+        <v>18.78</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="AE5" t="n">
-        <v>3.25</v>
+        <v>3.44</v>
       </c>
       <c r="AF5" t="n">
         <v>0.11</v>
@@ -2759,70 +2759,70 @@
         <v>2.67</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.82</v>
+        <v>2.89</v>
       </c>
       <c r="BH5" t="n">
-        <v>10.18</v>
+        <v>10.11</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.82</v>
+        <v>2.89</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.9399999999999999</v>
+        <v>1</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.76</v>
+        <v>0.72</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="BP5" t="n">
-        <v>5.29</v>
+        <v>5.17</v>
       </c>
       <c r="BQ5" t="n">
-        <v>4.88</v>
+        <v>4.94</v>
       </c>
       <c r="BR5" t="n">
-        <v>88.23999999999999</v>
+        <v>88.89</v>
       </c>
       <c r="BS5" t="n">
-        <v>58.82</v>
+        <v>61.11</v>
       </c>
       <c r="BT5" t="n">
-        <v>52.94</v>
+        <v>55.56</v>
       </c>
       <c r="BU5" t="n">
-        <v>41.18</v>
+        <v>44.44</v>
       </c>
       <c r="BV5" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BW5" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BX5" t="n">
-        <v>58.82</v>
+        <v>61.11</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="BZ5" t="n">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.54</v>
+        <v>3.61</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.8</v>
+        <v>3.88</v>
       </c>
       <c r="CC5" t="n">
         <v>2.84</v>
@@ -2834,25 +2834,25 @@
         <v>1.33</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="CG5" t="n">
-        <v>3.09</v>
+        <v>3.1</v>
       </c>
       <c r="CH5" t="n">
         <v>1.47</v>
       </c>
       <c r="CI5" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="CL5" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="CM5" t="n">
         <v>2.33</v>
@@ -2867,7 +2867,7 @@
         <v>1.76</v>
       </c>
       <c r="CQ5" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="CR5" t="n">
         <v>1.38</v>
@@ -2876,22 +2876,22 @@
         <v>2.75</v>
       </c>
       <c r="CT5" t="n">
-        <v>3.15</v>
+        <v>3.17</v>
       </c>
       <c r="CU5" t="n">
         <v>1.49</v>
       </c>
       <c r="CV5" t="n">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="CW5" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CX5" t="n">
         <v>1.56</v>
       </c>
       <c r="CY5" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="CZ5" t="n">
         <v>2.37</v>
@@ -2909,79 +2909,79 @@
         <v>3.01</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.11</v>
+        <v>0.16</v>
       </c>
       <c r="DF5" t="n">
-        <v>2.12</v>
+        <v>2.17</v>
       </c>
       <c r="DG5" t="n">
         <v>3.06</v>
       </c>
       <c r="DH5" t="n">
-        <v>100.94</v>
+        <v>101.06</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DJ5" t="n">
-        <v>3.29</v>
+        <v>3.39</v>
       </c>
       <c r="DK5" t="n">
-        <v>6.59</v>
+        <v>6.5</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="DM5" t="n">
-        <v>58.76</v>
+        <v>58.28</v>
       </c>
       <c r="DN5" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="DO5" t="n">
-        <v>3.53</v>
+        <v>3.44</v>
       </c>
       <c r="DP5" t="n">
-        <v>13</v>
+        <v>13.16</v>
       </c>
       <c r="DQ5" t="n">
-        <v>14.41</v>
+        <v>14.44</v>
       </c>
       <c r="DR5" t="n">
-        <v>5.41</v>
+        <v>5.44</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>54.82</v>
+        <v>55.22</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="DX5" t="n">
-        <v>14.65</v>
+        <v>14.78</v>
       </c>
       <c r="DY5" t="n">
-        <v>9.58</v>
+        <v>9.66</v>
       </c>
       <c r="DZ5" t="n">
-        <v>5.06</v>
+        <v>5.11</v>
       </c>
       <c r="EA5" t="n">
-        <v>19.06</v>
+        <v>19.28</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="EC5" t="n">
-        <v>2.94</v>
+        <v>3.06</v>
       </c>
     </row>
     <row r="6">
@@ -3006,7 +3006,7 @@
         <v>1.44</v>
       </c>
       <c r="G6" t="n">
-        <v>2.78</v>
+        <v>3.11</v>
       </c>
       <c r="H6" t="n">
         <v>99.22</v>
@@ -3021,7 +3021,7 @@
         <v>5.44</v>
       </c>
       <c r="L6" t="n">
-        <v>0.11</v>
+        <v>0.22</v>
       </c>
       <c r="M6" t="n">
         <v>54.56</v>
@@ -3030,7 +3030,7 @@
         <v>1.33</v>
       </c>
       <c r="O6" t="n">
-        <v>1.78</v>
+        <v>1.89</v>
       </c>
       <c r="P6" t="n">
         <v>14.78</v>
@@ -3189,10 +3189,10 @@
         <v>1.28</v>
       </c>
       <c r="BP6" t="n">
-        <v>3.22</v>
+        <v>3.56</v>
       </c>
       <c r="BQ6" t="n">
-        <v>4.78</v>
+        <v>4.94</v>
       </c>
       <c r="BR6" t="n">
         <v>88.89</v>
@@ -3225,7 +3225,7 @@
         <v>3.22</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.34</v>
+        <v>3.33</v>
       </c>
       <c r="CC6" t="n">
         <v>4.21</v>
@@ -3291,7 +3291,7 @@
         <v>1.95</v>
       </c>
       <c r="CX6" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CY6" t="n">
         <v>2.13</v>
@@ -3318,7 +3318,7 @@
         <v>1.56</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.22</v>
+        <v>2.39</v>
       </c>
       <c r="DH6" t="n">
         <v>89.44</v>
@@ -3333,7 +3333,7 @@
         <v>4.28</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.28</v>
+        <v>0.33</v>
       </c>
       <c r="DM6" t="n">
         <v>44.17</v>
@@ -3342,7 +3342,7 @@
         <v>1</v>
       </c>
       <c r="DO6" t="n">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="DP6" t="n">
         <v>13.67</v>
@@ -3944,7 +3944,7 @@
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>41.44</v>
+        <v>41.33</v>
       </c>
       <c r="AZ8" t="n">
         <v>0</v>
@@ -4169,7 +4169,7 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>46.11</v>
+        <v>46.06</v>
       </c>
       <c r="DW8" t="n">
         <v>0</v>
@@ -6215,13 +6215,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C14" t="n">
         <v>8</v>
       </c>
       <c r="D14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -6305,139 +6305,139 @@
         <v>4</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AH14" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>81.2</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>14</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>37.4</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>8.220000000000001</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BO14" t="n">
         <v>1.11</v>
       </c>
-      <c r="AI14" t="n">
-        <v>78.89</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>29.78</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>13.89</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>13.22</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>10.89</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>37.33</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>9.779999999999999</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>6.44</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>17.22</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="BG14" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="BH14" t="n">
-        <v>8.18</v>
-      </c>
-      <c r="BI14" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="BJ14" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="BK14" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="BL14" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="BM14" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="BN14" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="BO14" t="n">
-        <v>1.06</v>
-      </c>
       <c r="BP14" t="n">
-        <v>3.53</v>
+        <v>3.5</v>
       </c>
       <c r="BQ14" t="n">
-        <v>4.65</v>
+        <v>4.72</v>
       </c>
       <c r="BR14" t="n">
-        <v>88.23999999999999</v>
+        <v>88.89</v>
       </c>
       <c r="BS14" t="n">
-        <v>64.70999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="BT14" t="n">
-        <v>41.18</v>
+        <v>44.44</v>
       </c>
       <c r="BU14" t="n">
-        <v>29.41</v>
+        <v>33.33</v>
       </c>
       <c r="BV14" t="n">
-        <v>23.53</v>
+        <v>22.22</v>
       </c>
       <c r="BW14" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BX14" t="n">
-        <v>52.94</v>
+        <v>55.56</v>
       </c>
       <c r="BY14" t="n">
         <v>2.94</v>
@@ -6446,28 +6446,28 @@
         <v>3.36</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.4</v>
+        <v>3.51</v>
       </c>
       <c r="CC14" t="n">
-        <v>4.87</v>
+        <v>5.18</v>
       </c>
       <c r="CD14" t="n">
-        <v>5.25</v>
+        <v>5.65</v>
       </c>
       <c r="CE14" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CF14" t="n">
-        <v>3.23</v>
+        <v>3.19</v>
       </c>
       <c r="CG14" t="n">
-        <v>2.53</v>
+        <v>2.57</v>
       </c>
       <c r="CH14" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="CI14" t="n">
         <v>1.74</v>
@@ -6476,37 +6476,37 @@
         <v>2.05</v>
       </c>
       <c r="CK14" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="CL14" t="n">
         <v>2.21</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="CN14" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CO14" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CP14" t="n">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="CQ14" t="n">
-        <v>4.31</v>
+        <v>4.21</v>
       </c>
       <c r="CR14" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CS14" t="n">
-        <v>3.28</v>
+        <v>3.23</v>
       </c>
       <c r="CT14" t="n">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="CU14" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CV14" t="n">
         <v>1.82</v>
@@ -6515,16 +6515,16 @@
         <v>2.07</v>
       </c>
       <c r="CX14" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CY14" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="CZ14" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="DA14" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="DB14" t="n">
         <v>1.44</v>
@@ -6539,76 +6539,76 @@
         <v>0.06</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="DG14" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="DH14" t="n">
-        <v>88.23999999999999</v>
+        <v>89</v>
       </c>
       <c r="DI14" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ14" t="n">
-        <v>3.35</v>
+        <v>3.33</v>
       </c>
       <c r="DK14" t="n">
-        <v>2.77</v>
+        <v>2.84</v>
       </c>
       <c r="DL14" t="n">
         <v>0.11</v>
       </c>
       <c r="DM14" t="n">
-        <v>35.35</v>
+        <v>34.5</v>
       </c>
       <c r="DN14" t="n">
-        <v>1.59</v>
+        <v>1.5</v>
       </c>
       <c r="DO14" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="DP14" t="n">
-        <v>15.53</v>
+        <v>15.5</v>
       </c>
       <c r="DQ14" t="n">
-        <v>12.88</v>
+        <v>13</v>
       </c>
       <c r="DR14" t="n">
-        <v>9.18</v>
+        <v>9.17</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.12</v>
+        <v>0.17</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.12</v>
+        <v>0.17</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>42.23</v>
+        <v>42</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DX14" t="n">
-        <v>11.24</v>
+        <v>11.17</v>
       </c>
       <c r="DY14" t="n">
-        <v>7.53</v>
+        <v>7.56</v>
       </c>
       <c r="DZ14" t="n">
-        <v>3.7</v>
+        <v>3.61</v>
       </c>
       <c r="EA14" t="n">
-        <v>16.82</v>
+        <v>17.06</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="EC14" t="n">
-        <v>3.12</v>
+        <v>3.11</v>
       </c>
     </row>
     <row r="15">
@@ -7869,7 +7869,7 @@
         <v>2.5</v>
       </c>
       <c r="P18" t="n">
-        <v>17.6</v>
+        <v>18</v>
       </c>
       <c r="Q18" t="n">
         <v>12.9</v>
@@ -8181,7 +8181,7 @@
         <v>2.5</v>
       </c>
       <c r="DP18" t="n">
-        <v>17.67</v>
+        <v>17.89</v>
       </c>
       <c r="DQ18" t="n">
         <v>13.28</v>
@@ -8296,7 +8296,7 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>52.11</v>
+        <v>52.22</v>
       </c>
       <c r="Y19" t="n">
         <v>0.5600000000000001</v>
@@ -8602,7 +8602,7 @@
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>50.66</v>
+        <v>50.72</v>
       </c>
       <c r="DW19" t="n">
         <v>0.39</v>
@@ -9938,7 +9938,7 @@
         <v>1.44</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.56</v>
+        <v>1.67</v>
       </c>
       <c r="AI23" t="n">
         <v>91.33</v>
@@ -9953,7 +9953,7 @@
         <v>3.89</v>
       </c>
       <c r="AM23" t="n">
-        <v>0.11</v>
+        <v>0.22</v>
       </c>
       <c r="AN23" t="n">
         <v>37.22</v>
@@ -9962,7 +9962,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.56</v>
+        <v>2.22</v>
       </c>
       <c r="AQ23" t="n">
         <v>11.78</v>
@@ -9995,10 +9995,10 @@
         <v>0</v>
       </c>
       <c r="BA23" t="n">
-        <v>10</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="BB23" t="n">
-        <v>7.33</v>
+        <v>7.22</v>
       </c>
       <c r="BC23" t="n">
         <v>2.67</v>
@@ -10007,7 +10007,7 @@
         <v>18</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="BF23" t="n">
         <v>2</v>
@@ -10040,10 +10040,10 @@
         <v>0.78</v>
       </c>
       <c r="BP23" t="n">
-        <v>3.28</v>
+        <v>3.61</v>
       </c>
       <c r="BQ23" t="n">
-        <v>3.78</v>
+        <v>3.94</v>
       </c>
       <c r="BR23" t="n">
         <v>77.78</v>
@@ -10076,13 +10076,13 @@
         <v>3.22</v>
       </c>
       <c r="CB23" t="n">
-        <v>3.35</v>
+        <v>3.34</v>
       </c>
       <c r="CC23" t="n">
         <v>3.05</v>
       </c>
       <c r="CD23" t="n">
-        <v>3.37</v>
+        <v>3.38</v>
       </c>
       <c r="CE23" t="n">
         <v>1.47</v>
@@ -10142,7 +10142,7 @@
         <v>2.06</v>
       </c>
       <c r="CX23" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CY23" t="n">
         <v>2.23</v>
@@ -10169,7 +10169,7 @@
         <v>1.61</v>
       </c>
       <c r="DG23" t="n">
-        <v>1.84</v>
+        <v>1.89</v>
       </c>
       <c r="DH23" t="n">
         <v>94.11</v>
@@ -10184,7 +10184,7 @@
         <v>3.94</v>
       </c>
       <c r="DL23" t="n">
-        <v>0.16</v>
+        <v>0.22</v>
       </c>
       <c r="DM23" t="n">
         <v>37.89</v>
@@ -10193,7 +10193,7 @@
         <v>0.45</v>
       </c>
       <c r="DO23" t="n">
-        <v>1.72</v>
+        <v>2.05</v>
       </c>
       <c r="DP23" t="n">
         <v>12.78</v>
@@ -10220,10 +10220,10 @@
         <v>0.22</v>
       </c>
       <c r="DX23" t="n">
-        <v>11.11</v>
+        <v>11.06</v>
       </c>
       <c r="DY23" t="n">
-        <v>7.61</v>
+        <v>7.56</v>
       </c>
       <c r="DZ23" t="n">
         <v>3.5</v>

--- a/data/teams/leagues/Averages_Spain_Segunda_División_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Spain_Segunda_División_2025-2026.xlsx
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C3" t="n">
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E3" t="n">
         <v>0.11</v>
@@ -1875,136 +1875,136 @@
         <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AI3" t="n">
-        <v>86.11</v>
+        <v>86</v>
       </c>
       <c r="AJ3" t="n">
         <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>3.44</v>
+        <v>3.5</v>
       </c>
       <c r="AL3" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="AM3" t="n">
-        <v>-0.11</v>
+        <v>-0.1</v>
       </c>
       <c r="AN3" t="n">
-        <v>38.22</v>
+        <v>38.3</v>
       </c>
       <c r="AO3" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AP3" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="AQ3" t="n">
-        <v>14.44</v>
+        <v>13.8</v>
       </c>
       <c r="AR3" t="n">
-        <v>14.33</v>
+        <v>14.8</v>
       </c>
       <c r="AS3" t="n">
-        <v>8.109999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="AX3" t="n">
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>50.89</v>
+        <v>52.1</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="BA3" t="n">
-        <v>13.11</v>
+        <v>13.2</v>
       </c>
       <c r="BB3" t="n">
-        <v>8.890000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="BC3" t="n">
-        <v>4.22</v>
+        <v>4.3</v>
       </c>
       <c r="BD3" t="n">
-        <v>21.56</v>
+        <v>21.8</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="BF3" t="n">
-        <v>3.33</v>
+        <v>3.4</v>
       </c>
       <c r="BG3" t="n">
-        <v>3.22</v>
+        <v>3.21</v>
       </c>
       <c r="BH3" t="n">
-        <v>9.609999999999999</v>
+        <v>9.26</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.22</v>
+        <v>3.21</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BL3" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="BM3" t="n">
         <v>1</v>
       </c>
       <c r="BN3" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="BP3" t="n">
-        <v>3.94</v>
+        <v>3.89</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5.28</v>
+        <v>5</v>
       </c>
       <c r="BR3" t="n">
-        <v>94.44</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BS3" t="n">
-        <v>77.78</v>
+        <v>78.95</v>
       </c>
       <c r="BT3" t="n">
-        <v>66.67</v>
+        <v>68.42</v>
       </c>
       <c r="BU3" t="n">
-        <v>38.89</v>
+        <v>36.84</v>
       </c>
       <c r="BV3" t="n">
-        <v>22.22</v>
+        <v>21.05</v>
       </c>
       <c r="BW3" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BX3" t="n">
-        <v>66.67</v>
+        <v>68.42</v>
       </c>
       <c r="BY3" t="n">
         <v>1.7</v>
@@ -2013,25 +2013,25 @@
         <v>1.76</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.45</v>
+        <v>3.43</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.63</v>
+        <v>3.61</v>
       </c>
       <c r="CC3" t="n">
-        <v>2.58</v>
+        <v>2.55</v>
       </c>
       <c r="CD3" t="n">
-        <v>2.86</v>
+        <v>2.83</v>
       </c>
       <c r="CE3" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.71</v>
+        <v>2.72</v>
       </c>
       <c r="CG3" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="CH3" t="n">
         <v>1.43</v>
@@ -2049,10 +2049,10 @@
         <v>1.93</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CO3" t="n">
         <v>1.26</v>
@@ -2061,37 +2061,37 @@
         <v>1.88</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.14</v>
+        <v>3.16</v>
       </c>
       <c r="CR3" t="n">
         <v>1.4</v>
       </c>
       <c r="CS3" t="n">
-        <v>2.91</v>
+        <v>2.92</v>
       </c>
       <c r="CT3" t="n">
-        <v>3.08</v>
+        <v>3.07</v>
       </c>
       <c r="CU3" t="n">
         <v>1.44</v>
       </c>
       <c r="CV3" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="CW3" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CX3" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="CY3" t="n">
         <v>1.91</v>
       </c>
       <c r="CZ3" t="n">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="DA3" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="DB3" t="n">
         <v>1.29</v>
@@ -2103,79 +2103,79 @@
         <v>3.3</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="DG3" t="n">
-        <v>2.84</v>
+        <v>2.68</v>
       </c>
       <c r="DH3" t="n">
-        <v>94.89</v>
+        <v>94.37</v>
       </c>
       <c r="DI3" t="n">
         <v>0</v>
       </c>
       <c r="DJ3" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="DK3" t="n">
-        <v>5.56</v>
+        <v>5.37</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="DM3" t="n">
-        <v>48.16</v>
+        <v>47.68</v>
       </c>
       <c r="DN3" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="DO3" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="DP3" t="n">
-        <v>14.33</v>
+        <v>14</v>
       </c>
       <c r="DQ3" t="n">
-        <v>12.56</v>
+        <v>12.9</v>
       </c>
       <c r="DR3" t="n">
-        <v>7.66</v>
+        <v>7.53</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.22</v>
+        <v>0.26</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.22</v>
+        <v>0.26</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>54.22</v>
+        <v>54.69</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DX3" t="n">
-        <v>15.89</v>
+        <v>15.79</v>
       </c>
       <c r="DY3" t="n">
-        <v>10.06</v>
+        <v>10</v>
       </c>
       <c r="DZ3" t="n">
-        <v>5.83</v>
+        <v>5.79</v>
       </c>
       <c r="EA3" t="n">
-        <v>19.94</v>
+        <v>20.16</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.83</v>
+        <v>2.89</v>
       </c>
     </row>
     <row r="4">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C6" t="n">
         <v>9</v>
       </c>
       <c r="D6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E6" t="n">
         <v>0.22</v>
@@ -3081,139 +3081,139 @@
         <v>2.78</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AI6" t="n">
-        <v>79.67</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="AJ6" t="n">
         <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.44</v>
+        <v>2.7</v>
       </c>
       <c r="AL6" t="n">
-        <v>3.11</v>
+        <v>3.4</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AN6" t="n">
-        <v>33.78</v>
+        <v>35.8</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.44</v>
+        <v>1.9</v>
       </c>
       <c r="AQ6" t="n">
-        <v>12.56</v>
+        <v>12.7</v>
       </c>
       <c r="AR6" t="n">
-        <v>13.33</v>
+        <v>13.5</v>
       </c>
       <c r="AS6" t="n">
-        <v>9.67</v>
+        <v>9.1</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="AX6" t="n">
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>47.22</v>
+        <v>48</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="BA6" t="n">
-        <v>8.779999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB6" t="n">
-        <v>6.56</v>
+        <v>7.1</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.22</v>
+        <v>2.7</v>
       </c>
       <c r="BD6" t="n">
-        <v>20.11</v>
+        <v>20.3</v>
       </c>
       <c r="BE6" t="n">
-        <v>0.96</v>
+        <v>1.07</v>
       </c>
       <c r="BF6" t="n">
-        <v>2.11</v>
+        <v>2.4</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.28</v>
+        <v>2.37</v>
       </c>
       <c r="BH6" t="n">
-        <v>8.83</v>
+        <v>8.84</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.28</v>
+        <v>2.37</v>
       </c>
       <c r="BJ6" t="n">
         <v>0.89</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.39</v>
+        <v>0.42</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.39</v>
+        <v>0.47</v>
       </c>
       <c r="BN6" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="BP6" t="n">
-        <v>3.56</v>
+        <v>3.79</v>
       </c>
       <c r="BQ6" t="n">
-        <v>4.94</v>
+        <v>4.74</v>
       </c>
       <c r="BR6" t="n">
-        <v>88.89</v>
+        <v>89.47</v>
       </c>
       <c r="BS6" t="n">
-        <v>61.11</v>
+        <v>63.16</v>
       </c>
       <c r="BT6" t="n">
-        <v>38.89</v>
+        <v>42.11</v>
       </c>
       <c r="BU6" t="n">
-        <v>16.67</v>
+        <v>21.05</v>
       </c>
       <c r="BV6" t="n">
-        <v>16.67</v>
+        <v>15.79</v>
       </c>
       <c r="BW6" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BX6" t="n">
-        <v>44.44</v>
+        <v>47.37</v>
       </c>
       <c r="BY6" t="n">
         <v>2.43</v>
@@ -3222,22 +3222,22 @@
         <v>2.63</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.33</v>
+        <v>3.31</v>
       </c>
       <c r="CC6" t="n">
-        <v>4.21</v>
+        <v>4.06</v>
       </c>
       <c r="CD6" t="n">
-        <v>4.59</v>
+        <v>4.42</v>
       </c>
       <c r="CE6" t="n">
         <v>1.45</v>
       </c>
       <c r="CF6" t="n">
-        <v>3.05</v>
+        <v>3.06</v>
       </c>
       <c r="CG6" t="n">
         <v>2.64</v>
@@ -3255,10 +3255,10 @@
         <v>1.67</v>
       </c>
       <c r="CL6" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="CN6" t="n">
         <v>1.66</v>
@@ -3270,16 +3270,16 @@
         <v>2.21</v>
       </c>
       <c r="CQ6" t="n">
-        <v>3.99</v>
+        <v>4.02</v>
       </c>
       <c r="CR6" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="CS6" t="n">
-        <v>3.13</v>
+        <v>3.15</v>
       </c>
       <c r="CT6" t="n">
-        <v>2.8</v>
+        <v>2.79</v>
       </c>
       <c r="CU6" t="n">
         <v>1.39</v>
@@ -3306,85 +3306,85 @@
         <v>1.39</v>
       </c>
       <c r="DC6" t="n">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="DD6" t="n">
-        <v>4.14</v>
+        <v>4.15</v>
       </c>
       <c r="DE6" t="n">
         <v>0.16</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.56</v>
+        <v>1.73</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.39</v>
+        <v>2.26</v>
       </c>
       <c r="DH6" t="n">
-        <v>89.44</v>
+        <v>89.31</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.61</v>
+        <v>2.74</v>
       </c>
       <c r="DK6" t="n">
-        <v>4.28</v>
+        <v>4.37</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="DM6" t="n">
-        <v>44.17</v>
+        <v>44.69</v>
       </c>
       <c r="DN6" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="DO6" t="n">
-        <v>1.66</v>
+        <v>1.9</v>
       </c>
       <c r="DP6" t="n">
-        <v>13.67</v>
+        <v>13.69</v>
       </c>
       <c r="DQ6" t="n">
-        <v>13.27</v>
+        <v>13.37</v>
       </c>
       <c r="DR6" t="n">
-        <v>7.5</v>
+        <v>7.31</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.16</v>
+        <v>0.21</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.16</v>
+        <v>0.21</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>50.78</v>
+        <v>51</v>
       </c>
       <c r="DW6" t="n">
         <v>0.11</v>
       </c>
       <c r="DX6" t="n">
-        <v>10.44</v>
+        <v>10.89</v>
       </c>
       <c r="DY6" t="n">
-        <v>7.17</v>
+        <v>7.42</v>
       </c>
       <c r="DZ6" t="n">
-        <v>3.28</v>
+        <v>3.47</v>
       </c>
       <c r="EA6" t="n">
-        <v>20.67</v>
+        <v>20.74</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.44</v>
+        <v>2.58</v>
       </c>
     </row>
     <row r="7">
@@ -3394,13 +3394,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C7" t="n">
         <v>9</v>
       </c>
       <c r="D7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -3484,139 +3484,139 @@
         <v>1</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AH7" t="n">
-        <v>2.22</v>
+        <v>2.4</v>
       </c>
       <c r="AI7" t="n">
-        <v>74.22</v>
+        <v>75.7</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AK7" t="n">
         <v>2</v>
       </c>
       <c r="AL7" t="n">
-        <v>3.44</v>
+        <v>3.5</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AN7" t="n">
-        <v>32</v>
+        <v>32.6</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AQ7" t="n">
-        <v>12.33</v>
+        <v>12.4</v>
       </c>
       <c r="AR7" t="n">
-        <v>12.11</v>
+        <v>12</v>
       </c>
       <c r="AS7" t="n">
-        <v>10.56</v>
+        <v>9.9</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.56</v>
+        <v>1.8</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AX7" t="n">
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>43.11</v>
+        <v>44</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="BA7" t="n">
-        <v>12</v>
+        <v>12.1</v>
       </c>
       <c r="BB7" t="n">
-        <v>7</v>
+        <v>7.3</v>
       </c>
       <c r="BC7" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="BD7" t="n">
-        <v>17.78</v>
+        <v>17.9</v>
       </c>
       <c r="BE7" t="n">
         <v>1.34</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.44</v>
+        <v>2.53</v>
       </c>
       <c r="BH7" t="n">
-        <v>9.109999999999999</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.44</v>
+        <v>2.53</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.74</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.78</v>
+        <v>0.74</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.33</v>
+        <v>1.47</v>
       </c>
       <c r="BP7" t="n">
         <v>3.89</v>
       </c>
       <c r="BQ7" t="n">
-        <v>5.22</v>
+        <v>5.16</v>
       </c>
       <c r="BR7" t="n">
-        <v>88.89</v>
+        <v>89.47</v>
       </c>
       <c r="BS7" t="n">
-        <v>50</v>
+        <v>52.63</v>
       </c>
       <c r="BT7" t="n">
-        <v>44.44</v>
+        <v>47.37</v>
       </c>
       <c r="BU7" t="n">
-        <v>27.78</v>
+        <v>31.58</v>
       </c>
       <c r="BV7" t="n">
-        <v>22.22</v>
+        <v>21.05</v>
       </c>
       <c r="BW7" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BX7" t="n">
-        <v>33.33</v>
+        <v>31.58</v>
       </c>
       <c r="BY7" t="n">
         <v>2.62</v>
@@ -3625,22 +3625,22 @@
         <v>2.74</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.36</v>
+        <v>3.37</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.5</v>
+        <v>3.51</v>
       </c>
       <c r="CC7" t="n">
-        <v>4.96</v>
+        <v>5</v>
       </c>
       <c r="CD7" t="n">
-        <v>5.55</v>
+        <v>5.57</v>
       </c>
       <c r="CE7" t="n">
         <v>1.43</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.95</v>
+        <v>2.96</v>
       </c>
       <c r="CG7" t="n">
         <v>2.76</v>
@@ -3649,22 +3649,22 @@
         <v>1.37</v>
       </c>
       <c r="CI7" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CJ7" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CK7" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CL7" t="n">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="CN7" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CO7" t="n">
         <v>1.32</v>
@@ -3673,13 +3673,13 @@
         <v>2.09</v>
       </c>
       <c r="CQ7" t="n">
-        <v>3.67</v>
+        <v>3.68</v>
       </c>
       <c r="CR7" t="n">
         <v>1.45</v>
       </c>
       <c r="CS7" t="n">
-        <v>3.13</v>
+        <v>3.14</v>
       </c>
       <c r="CT7" t="n">
         <v>2.88</v>
@@ -3688,73 +3688,73 @@
         <v>1.39</v>
       </c>
       <c r="CV7" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="CW7" t="n">
         <v>1.95</v>
       </c>
-      <c r="CW7" t="n">
-        <v>1.94</v>
-      </c>
       <c r="CX7" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CY7" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="CZ7" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="DA7" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="DB7" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="DC7" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="DD7" t="n">
-        <v>3.89</v>
+        <v>3.91</v>
       </c>
       <c r="DE7" t="n">
         <v>0.11</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="DG7" t="n">
-        <v>2.78</v>
+        <v>2.84</v>
       </c>
       <c r="DH7" t="n">
-        <v>82.16</v>
+        <v>82.53</v>
       </c>
       <c r="DI7" t="n">
         <v>0.11</v>
       </c>
       <c r="DJ7" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="DK7" t="n">
         <v>4.11</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="DM7" t="n">
-        <v>36.56</v>
+        <v>36.63</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.28</v>
+        <v>0.32</v>
       </c>
       <c r="DO7" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="DP7" t="n">
-        <v>12.33</v>
+        <v>12.37</v>
       </c>
       <c r="DQ7" t="n">
-        <v>12.61</v>
+        <v>12.53</v>
       </c>
       <c r="DR7" t="n">
-        <v>9.23</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="DS7" t="n">
         <v>0.11</v>
@@ -3766,28 +3766,28 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>47.84</v>
+        <v>48.05</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DX7" t="n">
-        <v>11.56</v>
+        <v>11.63</v>
       </c>
       <c r="DY7" t="n">
-        <v>7.34</v>
+        <v>7.48</v>
       </c>
       <c r="DZ7" t="n">
-        <v>4.22</v>
+        <v>4.16</v>
       </c>
       <c r="EA7" t="n">
-        <v>18.44</v>
+        <v>18.47</v>
       </c>
       <c r="EB7" t="n">
         <v>1.29</v>
       </c>
       <c r="EC7" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="8">
@@ -4200,13 +4200,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C9" t="n">
         <v>9</v>
       </c>
       <c r="D9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E9" t="n">
         <v>0.11</v>
@@ -4290,52 +4290,52 @@
         <v>3</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.44</v>
+        <v>2.6</v>
       </c>
       <c r="AI9" t="n">
-        <v>91.67</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="AJ9" t="n">
-        <v>-0.11</v>
+        <v>-0.1</v>
       </c>
       <c r="AK9" t="n">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
       <c r="AL9" t="n">
-        <v>4.33</v>
+        <v>4.7</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AN9" t="n">
-        <v>40.22</v>
+        <v>41.2</v>
       </c>
       <c r="AO9" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.89</v>
+        <v>2.1</v>
       </c>
       <c r="AQ9" t="n">
-        <v>16.56</v>
+        <v>16.2</v>
       </c>
       <c r="AR9" t="n">
-        <v>14.78</v>
+        <v>15.1</v>
       </c>
       <c r="AS9" t="n">
-        <v>6.89</v>
+        <v>6.9</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="AV9" t="n">
         <v>0</v>
@@ -4347,73 +4347,73 @@
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>53.11</v>
+        <v>53.8</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="BA9" t="n">
-        <v>12.89</v>
+        <v>13.2</v>
       </c>
       <c r="BB9" t="n">
-        <v>8.44</v>
+        <v>8.6</v>
       </c>
       <c r="BC9" t="n">
-        <v>4.44</v>
+        <v>4.6</v>
       </c>
       <c r="BD9" t="n">
-        <v>23.33</v>
+        <v>22.7</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="BF9" t="n">
         <v>3</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.39</v>
+        <v>2.42</v>
       </c>
       <c r="BH9" t="n">
-        <v>9.06</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.39</v>
+        <v>2.42</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.44</v>
+        <v>0.47</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.39</v>
+        <v>0.42</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.72</v>
+        <v>0.68</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.83</v>
+        <v>0.89</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.33</v>
+        <v>4.63</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.72</v>
+        <v>4.89</v>
       </c>
       <c r="BR9" t="n">
-        <v>83.33</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="BS9" t="n">
-        <v>72.22</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="BT9" t="n">
-        <v>50</v>
+        <v>52.63</v>
       </c>
       <c r="BU9" t="n">
-        <v>33.33</v>
+        <v>31.58</v>
       </c>
       <c r="BV9" t="n">
         <v>0</v>
@@ -4422,7 +4422,7 @@
         <v>0</v>
       </c>
       <c r="BX9" t="n">
-        <v>66.67</v>
+        <v>68.42</v>
       </c>
       <c r="BY9" t="n">
         <v>2.1</v>
@@ -4431,136 +4431,136 @@
         <v>2.14</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.27</v>
+        <v>3.26</v>
       </c>
       <c r="CB9" t="n">
         <v>3.4</v>
       </c>
       <c r="CC9" t="n">
-        <v>3.05</v>
+        <v>2.97</v>
       </c>
       <c r="CD9" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="CE9" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CF9" t="n">
         <v>2.77</v>
       </c>
       <c r="CG9" t="n">
-        <v>2.91</v>
+        <v>2.89</v>
       </c>
       <c r="CH9" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CI9" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CK9" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="CL9" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.39</v>
+        <v>2.37</v>
       </c>
       <c r="CN9" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CO9" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="CP9" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="CQ9" t="n">
-        <v>3.21</v>
+        <v>3.24</v>
       </c>
       <c r="CR9" t="n">
         <v>1.42</v>
       </c>
       <c r="CS9" t="n">
-        <v>3.01</v>
+        <v>3.03</v>
       </c>
       <c r="CT9" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="CU9" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CV9" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="CW9" t="n">
         <v>1.76</v>
       </c>
       <c r="CX9" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CY9" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CZ9" t="n">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="DA9" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="DB9" t="n">
         <v>1.3</v>
       </c>
       <c r="DC9" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="DD9" t="n">
-        <v>3.41</v>
+        <v>3.45</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.16</v>
+        <v>0.21</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="DG9" t="n">
-        <v>2.56</v>
+        <v>2.63</v>
       </c>
       <c r="DH9" t="n">
-        <v>97.12</v>
+        <v>97.05</v>
       </c>
       <c r="DI9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DJ9" t="n">
-        <v>3.22</v>
+        <v>3.21</v>
       </c>
       <c r="DK9" t="n">
-        <v>4.72</v>
+        <v>4.89</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DM9" t="n">
-        <v>47.56</v>
+        <v>47.68</v>
       </c>
       <c r="DN9" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="DO9" t="n">
-        <v>2.16</v>
+        <v>2.26</v>
       </c>
       <c r="DP9" t="n">
-        <v>16.17</v>
+        <v>16</v>
       </c>
       <c r="DQ9" t="n">
-        <v>15</v>
+        <v>15.16</v>
       </c>
       <c r="DR9" t="n">
-        <v>5.94</v>
+        <v>6</v>
       </c>
       <c r="DS9" t="n">
         <v>0.16</v>
@@ -4572,25 +4572,25 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>56.34</v>
+        <v>56.53</v>
       </c>
       <c r="DW9" t="n">
         <v>0.16</v>
       </c>
       <c r="DX9" t="n">
-        <v>14.61</v>
+        <v>14.68</v>
       </c>
       <c r="DY9" t="n">
         <v>10</v>
       </c>
       <c r="DZ9" t="n">
-        <v>4.61</v>
+        <v>4.69</v>
       </c>
       <c r="EA9" t="n">
-        <v>22.56</v>
+        <v>22.26</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="EC9" t="n">
         <v>3</v>
@@ -4603,13 +4603,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C10" t="n">
         <v>9</v>
       </c>
       <c r="D10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E10" t="n">
         <v>0.11</v>
@@ -4696,136 +4696,136 @@
         <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AI10" t="n">
-        <v>78.11</v>
+        <v>78.3</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.67</v>
+        <v>2.8</v>
       </c>
       <c r="AL10" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="AN10" t="n">
-        <v>33.56</v>
+        <v>36.4</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="AP10" t="n">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
       <c r="AQ10" t="n">
-        <v>11.22</v>
+        <v>11.2</v>
       </c>
       <c r="AR10" t="n">
-        <v>12</v>
+        <v>12.1</v>
       </c>
       <c r="AS10" t="n">
-        <v>8.44</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AU10" t="n">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AX10" t="n">
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>48.89</v>
+        <v>48</v>
       </c>
       <c r="AZ10" t="n">
         <v>0</v>
       </c>
       <c r="BA10" t="n">
-        <v>12.44</v>
+        <v>12.2</v>
       </c>
       <c r="BB10" t="n">
-        <v>7.33</v>
+        <v>7.5</v>
       </c>
       <c r="BC10" t="n">
-        <v>5.11</v>
+        <v>4.7</v>
       </c>
       <c r="BD10" t="n">
-        <v>14.22</v>
+        <v>15.1</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="BF10" t="n">
-        <v>2.67</v>
+        <v>2.8</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.89</v>
+        <v>2.79</v>
       </c>
       <c r="BH10" t="n">
-        <v>8.83</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.89</v>
+        <v>2.79</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.67</v>
+        <v>0.63</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="BM10" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="BP10" t="n">
         <v>4.11</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.72</v>
+        <v>4.53</v>
       </c>
       <c r="BR10" t="n">
-        <v>94.44</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BS10" t="n">
-        <v>88.89</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="BT10" t="n">
-        <v>61.11</v>
+        <v>57.89</v>
       </c>
       <c r="BU10" t="n">
-        <v>33.33</v>
+        <v>31.58</v>
       </c>
       <c r="BV10" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BW10" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BX10" t="n">
-        <v>55.56</v>
+        <v>52.63</v>
       </c>
       <c r="BY10" t="n">
         <v>1.9</v>
@@ -4837,28 +4837,28 @@
         <v>3.28</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.43</v>
+        <v>3.42</v>
       </c>
       <c r="CC10" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="CD10" t="n">
-        <v>2.85</v>
+        <v>2.84</v>
       </c>
       <c r="CE10" t="n">
         <v>1.41</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="CG10" t="n">
-        <v>2.86</v>
+        <v>2.85</v>
       </c>
       <c r="CH10" t="n">
         <v>1.38</v>
       </c>
       <c r="CI10" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CJ10" t="n">
         <v>1.82</v>
@@ -4870,7 +4870,7 @@
         <v>2.08</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="CN10" t="n">
         <v>1.74</v>
@@ -4882,7 +4882,7 @@
         <v>2.02</v>
       </c>
       <c r="CQ10" t="n">
-        <v>3.47</v>
+        <v>3.46</v>
       </c>
       <c r="CR10" t="n">
         <v>1.45</v>
@@ -4891,25 +4891,25 @@
         <v>3.12</v>
       </c>
       <c r="CT10" t="n">
-        <v>2.87</v>
+        <v>2.88</v>
       </c>
       <c r="CU10" t="n">
         <v>1.39</v>
       </c>
       <c r="CV10" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="CW10" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CX10" t="n">
         <v>1.64</v>
       </c>
       <c r="CY10" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CZ10" t="n">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="DA10" t="n">
         <v>1.76</v>
@@ -4918,85 +4918,85 @@
         <v>1.34</v>
       </c>
       <c r="DC10" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="DD10" t="n">
-        <v>3.69</v>
+        <v>3.67</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.56</v>
+        <v>1.63</v>
       </c>
       <c r="DG10" t="n">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="DH10" t="n">
-        <v>86.66</v>
+        <v>86.31</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.5</v>
+        <v>4.47</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.39</v>
+        <v>0.42</v>
       </c>
       <c r="DM10" t="n">
-        <v>38.89</v>
+        <v>40.1</v>
       </c>
       <c r="DN10" t="n">
         <v>0.89</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.39</v>
+        <v>2.42</v>
       </c>
       <c r="DP10" t="n">
-        <v>11.61</v>
+        <v>11.58</v>
       </c>
       <c r="DQ10" t="n">
-        <v>12.66</v>
+        <v>12.68</v>
       </c>
       <c r="DR10" t="n">
-        <v>7.83</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>51.16</v>
+        <v>50.58</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DX10" t="n">
-        <v>12.5</v>
+        <v>12.37</v>
       </c>
       <c r="DY10" t="n">
-        <v>7.5</v>
+        <v>7.58</v>
       </c>
       <c r="DZ10" t="n">
-        <v>5</v>
+        <v>4.79</v>
       </c>
       <c r="EA10" t="n">
-        <v>16.95</v>
+        <v>17.26</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="EC10" t="n">
-        <v>2.39</v>
+        <v>2.47</v>
       </c>
     </row>
     <row r="11">
@@ -5006,10 +5006,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D11" t="n">
         <v>10</v>
@@ -5018,82 +5018,82 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="G11" t="n">
-        <v>4.12</v>
+        <v>3.67</v>
       </c>
       <c r="H11" t="n">
-        <v>105.12</v>
+        <v>104.67</v>
       </c>
       <c r="I11" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="J11" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="K11" t="n">
+        <v>5.56</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="M11" t="n">
+        <v>50.44</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="P11" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>14.56</v>
+      </c>
+      <c r="R11" t="n">
+        <v>8.56</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>58.22</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>13.67</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>8.779999999999999</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>4.89</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>19.44</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AE11" t="n">
         <v>2</v>
-      </c>
-      <c r="K11" t="n">
-        <v>6.12</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="M11" t="n">
-        <v>48.75</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="O11" t="n">
-        <v>2</v>
-      </c>
-      <c r="P11" t="n">
-        <v>14.12</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>15</v>
-      </c>
-      <c r="R11" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="S11" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" t="n">
-        <v>0</v>
-      </c>
-      <c r="W11" t="n">
-        <v>0</v>
-      </c>
-      <c r="X11" t="n">
-        <v>58</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>13.88</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>8.880000000000001</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>19.25</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.88</v>
       </c>
       <c r="AF11" t="n">
         <v>0.1</v>
@@ -5177,70 +5177,70 @@
         <v>2.8</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.56</v>
+        <v>2.47</v>
       </c>
       <c r="BH11" t="n">
-        <v>9.890000000000001</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.56</v>
+        <v>2.47</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.39</v>
+        <v>0.37</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="BL11" t="n">
         <v>1</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.83</v>
+        <v>0.79</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="BO11" t="n">
-        <v>0.72</v>
+        <v>0.68</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.44</v>
+        <v>4.42</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.39</v>
+        <v>5.16</v>
       </c>
       <c r="BR11" t="n">
-        <v>88.89</v>
+        <v>89.47</v>
       </c>
       <c r="BS11" t="n">
-        <v>77.78</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="BT11" t="n">
-        <v>55.56</v>
+        <v>52.63</v>
       </c>
       <c r="BU11" t="n">
-        <v>27.78</v>
+        <v>26.32</v>
       </c>
       <c r="BV11" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BW11" t="n">
         <v>0</v>
       </c>
       <c r="BX11" t="n">
-        <v>66.67</v>
+        <v>63.16</v>
       </c>
       <c r="BY11" t="n">
-        <v>2.27</v>
+        <v>2.32</v>
       </c>
       <c r="BZ11" t="n">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="CA11" t="n">
         <v>3.3</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.47</v>
+        <v>3.46</v>
       </c>
       <c r="CC11" t="n">
         <v>3.95</v>
@@ -5255,25 +5255,25 @@
         <v>2.91</v>
       </c>
       <c r="CG11" t="n">
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="CH11" t="n">
         <v>1.37</v>
       </c>
       <c r="CI11" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CJ11" t="n">
         <v>1.84</v>
       </c>
       <c r="CK11" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CL11" t="n">
         <v>2.14</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="CN11" t="n">
         <v>1.72</v>
@@ -5282,28 +5282,28 @@
         <v>1.32</v>
       </c>
       <c r="CP11" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="CQ11" t="n">
-        <v>3.56</v>
+        <v>3.55</v>
       </c>
       <c r="CR11" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CS11" t="n">
-        <v>3.05</v>
+        <v>3.04</v>
       </c>
       <c r="CT11" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="CU11" t="n">
         <v>1.41</v>
       </c>
       <c r="CV11" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="CW11" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CX11" t="n">
         <v>1.66</v>
@@ -5312,94 +5312,94 @@
         <v>2.08</v>
       </c>
       <c r="CZ11" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="DA11" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="DB11" t="n">
         <v>1.34</v>
       </c>
       <c r="DC11" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="DD11" t="n">
-        <v>3.73</v>
+        <v>3.71</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="DG11" t="n">
-        <v>3.22</v>
+        <v>3.05</v>
       </c>
       <c r="DH11" t="n">
-        <v>100.33</v>
+        <v>100.37</v>
       </c>
       <c r="DI11" t="n">
         <v>0.16</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="DK11" t="n">
-        <v>5.05</v>
+        <v>4.84</v>
       </c>
       <c r="DL11" t="n">
         <v>0.16</v>
       </c>
       <c r="DM11" t="n">
-        <v>43.67</v>
+        <v>44.73</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.95</v>
       </c>
       <c r="DO11" t="n">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="DP11" t="n">
-        <v>13.94</v>
+        <v>13.89</v>
       </c>
       <c r="DQ11" t="n">
-        <v>15.11</v>
+        <v>14.9</v>
       </c>
       <c r="DR11" t="n">
-        <v>7.89</v>
+        <v>7.95</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>57.28</v>
+        <v>57.42</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DX11" t="n">
-        <v>13.84</v>
+        <v>13.74</v>
       </c>
       <c r="DY11" t="n">
-        <v>9.279999999999999</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="DZ11" t="n">
-        <v>4.56</v>
+        <v>4.53</v>
       </c>
       <c r="EA11" t="n">
-        <v>18.56</v>
+        <v>18.68</v>
       </c>
       <c r="EB11" t="n">
         <v>1.51</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.39</v>
+        <v>2.42</v>
       </c>
     </row>
     <row r="12">
@@ -5812,61 +5812,61 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D13" t="n">
         <v>10</v>
       </c>
       <c r="E13" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="F13" t="n">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="G13" t="n">
-        <v>2.25</v>
+        <v>2.44</v>
       </c>
       <c r="H13" t="n">
-        <v>87.38</v>
+        <v>88.89</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="K13" t="n">
-        <v>5.5</v>
+        <v>5.56</v>
       </c>
       <c r="L13" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="M13" t="n">
-        <v>42.62</v>
+        <v>44</v>
       </c>
       <c r="N13" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="O13" t="n">
-        <v>3.25</v>
+        <v>3.11</v>
       </c>
       <c r="P13" t="n">
-        <v>14.12</v>
+        <v>13.44</v>
       </c>
       <c r="Q13" t="n">
-        <v>16.12</v>
+        <v>15.22</v>
       </c>
       <c r="R13" t="n">
-        <v>7.75</v>
+        <v>7.56</v>
       </c>
       <c r="S13" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T13" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -5878,28 +5878,28 @@
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>50.5</v>
+        <v>51.56</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="Z13" t="n">
-        <v>12.38</v>
+        <v>12.22</v>
       </c>
       <c r="AA13" t="n">
-        <v>7.75</v>
+        <v>7.67</v>
       </c>
       <c r="AB13" t="n">
-        <v>4.62</v>
+        <v>4.56</v>
       </c>
       <c r="AC13" t="n">
-        <v>22.75</v>
+        <v>23.11</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="AE13" t="n">
-        <v>3.12</v>
+        <v>2.89</v>
       </c>
       <c r="AF13" t="n">
         <v>0</v>
@@ -5983,70 +5983,70 @@
         <v>3.1</v>
       </c>
       <c r="BG13" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="BH13" t="n">
-        <v>9.279999999999999</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="BI13" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.39</v>
+        <v>0.37</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.72</v>
+        <v>0.74</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="BO13" t="n">
-        <v>0.83</v>
+        <v>0.79</v>
       </c>
       <c r="BP13" t="n">
-        <v>4.17</v>
+        <v>4.26</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4.56</v>
+        <v>4.68</v>
       </c>
       <c r="BR13" t="n">
-        <v>77.78</v>
+        <v>78.95</v>
       </c>
       <c r="BS13" t="n">
-        <v>66.67</v>
+        <v>63.16</v>
       </c>
       <c r="BT13" t="n">
-        <v>38.89</v>
+        <v>36.84</v>
       </c>
       <c r="BU13" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BV13" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BW13" t="n">
         <v>0</v>
       </c>
       <c r="BX13" t="n">
-        <v>50</v>
+        <v>47.37</v>
       </c>
       <c r="BY13" t="n">
         <v>2.3</v>
       </c>
       <c r="BZ13" t="n">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.04</v>
+        <v>3.03</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.16</v>
+        <v>3.15</v>
       </c>
       <c r="CC13" t="n">
         <v>3.02</v>
@@ -6061,7 +6061,7 @@
         <v>3.26</v>
       </c>
       <c r="CG13" t="n">
-        <v>2.56</v>
+        <v>2.55</v>
       </c>
       <c r="CH13" t="n">
         <v>1.31</v>
@@ -6070,7 +6070,7 @@
         <v>1.8</v>
       </c>
       <c r="CJ13" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="CK13" t="n">
         <v>1.6</v>
@@ -6088,10 +6088,10 @@
         <v>1.42</v>
       </c>
       <c r="CP13" t="n">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="CQ13" t="n">
-        <v>4.23</v>
+        <v>4.28</v>
       </c>
       <c r="CR13" t="n">
         <v>1.53</v>
@@ -6100,7 +6100,7 @@
         <v>3.2</v>
       </c>
       <c r="CT13" t="n">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="CU13" t="n">
         <v>1.37</v>
@@ -6127,52 +6127,52 @@
         <v>1.45</v>
       </c>
       <c r="DC13" t="n">
-        <v>2.43</v>
+        <v>2.44</v>
       </c>
       <c r="DD13" t="n">
-        <v>4.62</v>
+        <v>4.65</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DF13" t="n">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="DG13" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="DH13" t="n">
-        <v>84.45</v>
+        <v>85.31999999999999</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DJ13" t="n">
-        <v>3.44</v>
+        <v>3.32</v>
       </c>
       <c r="DK13" t="n">
-        <v>4.61</v>
+        <v>4.69</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="DM13" t="n">
-        <v>37.33</v>
+        <v>38.26</v>
       </c>
       <c r="DN13" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="DO13" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="DP13" t="n">
-        <v>13.16</v>
+        <v>12.89</v>
       </c>
       <c r="DQ13" t="n">
-        <v>14.83</v>
+        <v>14.47</v>
       </c>
       <c r="DR13" t="n">
-        <v>8.390000000000001</v>
+        <v>8.27</v>
       </c>
       <c r="DS13" t="n">
         <v>0.11</v>
@@ -6184,28 +6184,28 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>49.56</v>
+        <v>50.11</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DX13" t="n">
-        <v>11.11</v>
+        <v>11.1</v>
       </c>
       <c r="DY13" t="n">
-        <v>6.78</v>
+        <v>6.79</v>
       </c>
       <c r="DZ13" t="n">
-        <v>4.33</v>
+        <v>4.32</v>
       </c>
       <c r="EA13" t="n">
-        <v>20.94</v>
+        <v>21.21</v>
       </c>
       <c r="EB13" t="n">
         <v>1.28</v>
       </c>
       <c r="EC13" t="n">
-        <v>3.11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -6215,10 +6215,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D14" t="n">
         <v>10</v>
@@ -6227,49 +6227,49 @@
         <v>0</v>
       </c>
       <c r="F14" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="G14" t="n">
         <v>2</v>
       </c>
-      <c r="G14" t="n">
-        <v>1.75</v>
-      </c>
       <c r="H14" t="n">
-        <v>98.75</v>
+        <v>97.22</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>4</v>
+        <v>3.78</v>
       </c>
       <c r="K14" t="n">
-        <v>3.38</v>
+        <v>4.11</v>
       </c>
       <c r="L14" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="M14" t="n">
-        <v>41.62</v>
+        <v>41.33</v>
       </c>
       <c r="N14" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="O14" t="n">
-        <v>1.62</v>
+        <v>2.11</v>
       </c>
       <c r="P14" t="n">
-        <v>17.38</v>
+        <v>17.44</v>
       </c>
       <c r="Q14" t="n">
-        <v>12.5</v>
+        <v>12.56</v>
       </c>
       <c r="R14" t="n">
-        <v>7.25</v>
+        <v>7.67</v>
       </c>
       <c r="S14" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="T14" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
@@ -6281,28 +6281,28 @@
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>47.75</v>
+        <v>46.89</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="Z14" t="n">
-        <v>12.88</v>
+        <v>12.44</v>
       </c>
       <c r="AA14" t="n">
-        <v>8.75</v>
+        <v>8.56</v>
       </c>
       <c r="AB14" t="n">
-        <v>4.12</v>
+        <v>3.89</v>
       </c>
       <c r="AC14" t="n">
-        <v>16.38</v>
+        <v>17.56</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="AE14" t="n">
-        <v>4</v>
+        <v>3.67</v>
       </c>
       <c r="AF14" t="n">
         <v>0.1</v>
@@ -6386,70 +6386,70 @@
         <v>2.4</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.61</v>
+        <v>2.63</v>
       </c>
       <c r="BH14" t="n">
-        <v>8.220000000000001</v>
+        <v>8.74</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.61</v>
+        <v>2.63</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.61</v>
+        <v>0.63</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.67</v>
+        <v>0.63</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="BP14" t="n">
-        <v>3.5</v>
+        <v>3.84</v>
       </c>
       <c r="BQ14" t="n">
-        <v>4.72</v>
+        <v>4.89</v>
       </c>
       <c r="BR14" t="n">
-        <v>88.89</v>
+        <v>89.47</v>
       </c>
       <c r="BS14" t="n">
-        <v>66.67</v>
+        <v>68.42</v>
       </c>
       <c r="BT14" t="n">
-        <v>44.44</v>
+        <v>47.37</v>
       </c>
       <c r="BU14" t="n">
-        <v>33.33</v>
+        <v>31.58</v>
       </c>
       <c r="BV14" t="n">
-        <v>22.22</v>
+        <v>21.05</v>
       </c>
       <c r="BW14" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BX14" t="n">
-        <v>55.56</v>
+        <v>57.89</v>
       </c>
       <c r="BY14" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="BZ14" t="n">
         <v>3.36</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.28</v>
+        <v>3.27</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.51</v>
+        <v>3.5</v>
       </c>
       <c r="CC14" t="n">
         <v>5.18</v>
@@ -6458,13 +6458,13 @@
         <v>5.65</v>
       </c>
       <c r="CE14" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="CF14" t="n">
-        <v>3.19</v>
+        <v>3.17</v>
       </c>
       <c r="CG14" t="n">
-        <v>2.57</v>
+        <v>2.58</v>
       </c>
       <c r="CH14" t="n">
         <v>1.32</v>
@@ -6473,34 +6473,34 @@
         <v>1.74</v>
       </c>
       <c r="CJ14" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="CK14" t="n">
         <v>1.7</v>
       </c>
       <c r="CL14" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="CN14" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CO14" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CP14" t="n">
         <v>2.25</v>
       </c>
       <c r="CQ14" t="n">
-        <v>4.21</v>
+        <v>4.19</v>
       </c>
       <c r="CR14" t="n">
         <v>1.51</v>
       </c>
       <c r="CS14" t="n">
-        <v>3.23</v>
+        <v>3.24</v>
       </c>
       <c r="CT14" t="n">
         <v>2.7</v>
@@ -6509,106 +6509,106 @@
         <v>1.37</v>
       </c>
       <c r="CV14" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CW14" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CX14" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="CY14" t="n">
         <v>2.15</v>
       </c>
       <c r="CZ14" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="DA14" t="n">
         <v>1.69</v>
       </c>
       <c r="DB14" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="DC14" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="DD14" t="n">
-        <v>4.47</v>
+        <v>4.44</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="DG14" t="n">
-        <v>1.5</v>
+        <v>1.63</v>
       </c>
       <c r="DH14" t="n">
-        <v>89</v>
+        <v>88.79000000000001</v>
       </c>
       <c r="DI14" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DJ14" t="n">
-        <v>3.33</v>
+        <v>3.26</v>
       </c>
       <c r="DK14" t="n">
-        <v>2.84</v>
+        <v>3.21</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.11</v>
+        <v>0.16</v>
       </c>
       <c r="DM14" t="n">
-        <v>34.5</v>
+        <v>34.74</v>
       </c>
       <c r="DN14" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="DO14" t="n">
-        <v>1.33</v>
+        <v>1.58</v>
       </c>
       <c r="DP14" t="n">
-        <v>15.5</v>
+        <v>15.63</v>
       </c>
       <c r="DQ14" t="n">
         <v>13</v>
       </c>
       <c r="DR14" t="n">
-        <v>9.17</v>
+        <v>9.26</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>42</v>
+        <v>41.9</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.11</v>
+        <v>0.16</v>
       </c>
       <c r="DX14" t="n">
-        <v>11.17</v>
+        <v>11.05</v>
       </c>
       <c r="DY14" t="n">
-        <v>7.56</v>
+        <v>7.53</v>
       </c>
       <c r="DZ14" t="n">
-        <v>3.61</v>
+        <v>3.53</v>
       </c>
       <c r="EA14" t="n">
-        <v>17.06</v>
+        <v>17.58</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="EC14" t="n">
-        <v>3.11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -6618,61 +6618,61 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D15" t="n">
         <v>9</v>
       </c>
       <c r="E15" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="F15" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="G15" t="n">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="H15" t="n">
-        <v>88.22</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>2.22</v>
+        <v>2.5</v>
       </c>
       <c r="K15" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="L15" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="M15" t="n">
-        <v>48.33</v>
+        <v>46.9</v>
       </c>
       <c r="N15" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="O15" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="P15" t="n">
-        <v>13.56</v>
+        <v>14.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>12.89</v>
+        <v>12.4</v>
       </c>
       <c r="R15" t="n">
-        <v>7.56</v>
+        <v>7.9</v>
       </c>
       <c r="S15" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="T15" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
@@ -6684,28 +6684,28 @@
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>53</v>
+        <v>51.4</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="Z15" t="n">
-        <v>15.11</v>
+        <v>15.1</v>
       </c>
       <c r="AA15" t="n">
-        <v>9.109999999999999</v>
+        <v>9</v>
       </c>
       <c r="AB15" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="AC15" t="n">
-        <v>21.22</v>
+        <v>21.9</v>
       </c>
       <c r="AD15" t="n">
         <v>1.72</v>
       </c>
       <c r="AE15" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="AF15" t="n">
         <v>0.11</v>
@@ -6789,70 +6789,70 @@
         <v>1.89</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.61</v>
+        <v>2.63</v>
       </c>
       <c r="BH15" t="n">
-        <v>8.56</v>
+        <v>8.26</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.61</v>
+        <v>2.63</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.72</v>
+        <v>0.74</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.95</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.72</v>
+        <v>0.74</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="BO15" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.95</v>
       </c>
       <c r="BP15" t="n">
-        <v>3.61</v>
+        <v>3.58</v>
       </c>
       <c r="BQ15" t="n">
-        <v>4.94</v>
+        <v>4.68</v>
       </c>
       <c r="BR15" t="n">
         <v>100</v>
       </c>
       <c r="BS15" t="n">
-        <v>72.22</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="BT15" t="n">
-        <v>50</v>
+        <v>52.63</v>
       </c>
       <c r="BU15" t="n">
-        <v>27.78</v>
+        <v>26.32</v>
       </c>
       <c r="BV15" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BW15" t="n">
         <v>0</v>
       </c>
       <c r="BX15" t="n">
-        <v>55.56</v>
+        <v>57.89</v>
       </c>
       <c r="BY15" t="n">
-        <v>2.19</v>
+        <v>2.29</v>
       </c>
       <c r="BZ15" t="n">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="CA15" t="n">
         <v>3.21</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.36</v>
+        <v>3.35</v>
       </c>
       <c r="CC15" t="n">
         <v>4.06</v>
@@ -6864,7 +6864,7 @@
         <v>1.47</v>
       </c>
       <c r="CF15" t="n">
-        <v>3.13</v>
+        <v>3.11</v>
       </c>
       <c r="CG15" t="n">
         <v>2.62</v>
@@ -6873,145 +6873,145 @@
         <v>1.33</v>
       </c>
       <c r="CI15" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CJ15" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CK15" t="n">
         <v>1.6</v>
       </c>
       <c r="CL15" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="CM15" t="n">
         <v>2.21</v>
       </c>
       <c r="CN15" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CO15" t="n">
         <v>1.37</v>
       </c>
       <c r="CP15" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.93</v>
+        <v>3.9</v>
       </c>
       <c r="CR15" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CS15" t="n">
-        <v>3.21</v>
+        <v>3.2</v>
       </c>
       <c r="CT15" t="n">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="CU15" t="n">
         <v>1.37</v>
       </c>
       <c r="CV15" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="CW15" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="CX15" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CY15" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="CZ15" t="n">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="DA15" t="n">
         <v>1.76</v>
       </c>
       <c r="DB15" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="DC15" t="n">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="DD15" t="n">
-        <v>4.27</v>
+        <v>4.22</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="DG15" t="n">
-        <v>2.45</v>
+        <v>2.32</v>
       </c>
       <c r="DH15" t="n">
-        <v>89.39</v>
+        <v>88.63</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DJ15" t="n">
-        <v>2.33</v>
+        <v>2.47</v>
       </c>
       <c r="DK15" t="n">
-        <v>4.06</v>
+        <v>3.89</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="DM15" t="n">
-        <v>47.33</v>
+        <v>46.63</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.67</v>
+        <v>0.74</v>
       </c>
       <c r="DO15" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="DP15" t="n">
-        <v>12.94</v>
+        <v>13.31</v>
       </c>
       <c r="DQ15" t="n">
-        <v>12.61</v>
+        <v>12.37</v>
       </c>
       <c r="DR15" t="n">
-        <v>7.89</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DU15" t="n">
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>52.11</v>
+        <v>51.31</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DX15" t="n">
-        <v>12.44</v>
+        <v>12.58</v>
       </c>
       <c r="DY15" t="n">
-        <v>7.89</v>
+        <v>7.9</v>
       </c>
       <c r="DZ15" t="n">
-        <v>4.56</v>
+        <v>4.68</v>
       </c>
       <c r="EA15" t="n">
-        <v>22.56</v>
+        <v>22.84</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="EC15" t="n">
-        <v>1.94</v>
+        <v>2.11</v>
       </c>
     </row>
     <row r="16">
@@ -7021,13 +7021,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C16" t="n">
         <v>10</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E16" t="n">
         <v>0.2</v>
@@ -7114,49 +7114,49 @@
         <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.62</v>
+        <v>2.44</v>
       </c>
       <c r="AI16" t="n">
-        <v>90.5</v>
+        <v>91.11</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="AK16" t="n">
-        <v>3.62</v>
+        <v>3.44</v>
       </c>
       <c r="AL16" t="n">
-        <v>4.88</v>
+        <v>4.67</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="AN16" t="n">
-        <v>37.88</v>
+        <v>37.44</v>
       </c>
       <c r="AO16" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AP16" t="n">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="AQ16" t="n">
-        <v>13.75</v>
+        <v>13.44</v>
       </c>
       <c r="AR16" t="n">
-        <v>17.12</v>
+        <v>16.67</v>
       </c>
       <c r="AS16" t="n">
-        <v>8</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AU16" t="n">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="AV16" t="n">
         <v>0</v>
@@ -7168,82 +7168,82 @@
         <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>52.62</v>
+        <v>52.44</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="BA16" t="n">
-        <v>12.5</v>
+        <v>12.22</v>
       </c>
       <c r="BB16" t="n">
-        <v>7.12</v>
+        <v>7.11</v>
       </c>
       <c r="BC16" t="n">
-        <v>5.38</v>
+        <v>5.11</v>
       </c>
       <c r="BD16" t="n">
-        <v>17.25</v>
+        <v>16.78</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="BF16" t="n">
-        <v>3.25</v>
+        <v>3.11</v>
       </c>
       <c r="BG16" t="n">
-        <v>3.72</v>
+        <v>3.63</v>
       </c>
       <c r="BH16" t="n">
-        <v>11.44</v>
+        <v>11.42</v>
       </c>
       <c r="BI16" t="n">
-        <v>3.72</v>
+        <v>3.63</v>
       </c>
       <c r="BJ16" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="BL16" t="n">
         <v>1</v>
       </c>
       <c r="BM16" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="BN16" t="n">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="BP16" t="n">
-        <v>5.56</v>
+        <v>5.47</v>
       </c>
       <c r="BQ16" t="n">
-        <v>5.89</v>
+        <v>5.95</v>
       </c>
       <c r="BR16" t="n">
         <v>100</v>
       </c>
       <c r="BS16" t="n">
-        <v>94.44</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BT16" t="n">
-        <v>83.33</v>
+        <v>78.95</v>
       </c>
       <c r="BU16" t="n">
-        <v>61.11</v>
+        <v>57.89</v>
       </c>
       <c r="BV16" t="n">
-        <v>27.78</v>
+        <v>26.32</v>
       </c>
       <c r="BW16" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BX16" t="n">
-        <v>77.78</v>
+        <v>78.95</v>
       </c>
       <c r="BY16" t="n">
         <v>1.81</v>
@@ -7252,25 +7252,25 @@
         <v>1.82</v>
       </c>
       <c r="CA16" t="n">
-        <v>3.64</v>
+        <v>3.62</v>
       </c>
       <c r="CB16" t="n">
-        <v>3.8</v>
+        <v>3.77</v>
       </c>
       <c r="CC16" t="n">
-        <v>3.03</v>
+        <v>3</v>
       </c>
       <c r="CD16" t="n">
-        <v>3.46</v>
+        <v>3.39</v>
       </c>
       <c r="CE16" t="n">
         <v>1.34</v>
       </c>
       <c r="CF16" t="n">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="CG16" t="n">
-        <v>3.09</v>
+        <v>3.08</v>
       </c>
       <c r="CH16" t="n">
         <v>1.47</v>
@@ -7282,13 +7282,13 @@
         <v>1.66</v>
       </c>
       <c r="CK16" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="CL16" t="n">
         <v>1.91</v>
       </c>
       <c r="CM16" t="n">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="CN16" t="n">
         <v>1.91</v>
@@ -7297,25 +7297,25 @@
         <v>1.22</v>
       </c>
       <c r="CP16" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="CQ16" t="n">
-        <v>2.79</v>
+        <v>2.82</v>
       </c>
       <c r="CR16" t="n">
         <v>1.38</v>
       </c>
       <c r="CS16" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="CT16" t="n">
-        <v>3.16</v>
+        <v>3.15</v>
       </c>
       <c r="CU16" t="n">
         <v>1.5</v>
       </c>
       <c r="CV16" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="CW16" t="n">
         <v>1.67</v>
@@ -7324,7 +7324,7 @@
         <v>1.53</v>
       </c>
       <c r="CY16" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CZ16" t="n">
         <v>2.42</v>
@@ -7333,55 +7333,55 @@
         <v>1.92</v>
       </c>
       <c r="DB16" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="DC16" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="DD16" t="n">
-        <v>2.91</v>
+        <v>2.94</v>
       </c>
       <c r="DE16" t="n">
         <v>0.11</v>
       </c>
       <c r="DF16" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="DG16" t="n">
-        <v>3.39</v>
+        <v>3.26</v>
       </c>
       <c r="DH16" t="n">
         <v>96</v>
       </c>
       <c r="DI16" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DJ16" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="DK16" t="n">
-        <v>6.22</v>
+        <v>6.05</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.61</v>
+        <v>0.63</v>
       </c>
       <c r="DM16" t="n">
-        <v>43</v>
+        <v>42.52</v>
       </c>
       <c r="DN16" t="n">
         <v>0.89</v>
       </c>
       <c r="DO16" t="n">
-        <v>2.83</v>
+        <v>2.79</v>
       </c>
       <c r="DP16" t="n">
-        <v>13.17</v>
+        <v>13.05</v>
       </c>
       <c r="DQ16" t="n">
-        <v>15.55</v>
+        <v>15.42</v>
       </c>
       <c r="DR16" t="n">
-        <v>7.78</v>
+        <v>7.89</v>
       </c>
       <c r="DS16" t="n">
         <v>0.11</v>
@@ -7393,28 +7393,28 @@
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>53.39</v>
+        <v>53.26</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DX16" t="n">
-        <v>14.22</v>
+        <v>14</v>
       </c>
       <c r="DY16" t="n">
-        <v>8.33</v>
+        <v>8.26</v>
       </c>
       <c r="DZ16" t="n">
-        <v>5.89</v>
+        <v>5.74</v>
       </c>
       <c r="EA16" t="n">
-        <v>17.94</v>
+        <v>17.69</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="EC16" t="n">
-        <v>2.83</v>
+        <v>2.79</v>
       </c>
     </row>
     <row r="17">
@@ -7424,94 +7424,94 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D17" t="n">
         <v>9</v>
       </c>
       <c r="E17" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="F17" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="G17" t="n">
         <v>1</v>
       </c>
       <c r="H17" t="n">
-        <v>80.56</v>
+        <v>81.7</v>
       </c>
       <c r="I17" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="J17" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="K17" t="n">
-        <v>3.11</v>
+        <v>3.1</v>
       </c>
       <c r="L17" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="M17" t="n">
-        <v>31.78</v>
+        <v>32.4</v>
       </c>
       <c r="N17" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="O17" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="P17" t="n">
-        <v>18.33</v>
+        <v>18.1</v>
       </c>
       <c r="Q17" t="n">
-        <v>13.22</v>
+        <v>13.3</v>
       </c>
       <c r="R17" t="n">
-        <v>8.890000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="S17" t="n">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="T17" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="U17" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="V17" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>45.33</v>
+        <v>45.3</v>
       </c>
       <c r="Y17" t="n">
         <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>10.33</v>
+        <v>10.1</v>
       </c>
       <c r="AA17" t="n">
-        <v>6.78</v>
+        <v>6.4</v>
       </c>
       <c r="AB17" t="n">
-        <v>3.56</v>
+        <v>3.7</v>
       </c>
       <c r="AC17" t="n">
-        <v>19.89</v>
+        <v>20.4</v>
       </c>
       <c r="AD17" t="n">
         <v>1.14</v>
       </c>
       <c r="AE17" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="AF17" t="n">
         <v>0</v>
@@ -7595,70 +7595,70 @@
         <v>2.78</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.89</v>
+        <v>2.95</v>
       </c>
       <c r="BH17" t="n">
-        <v>9.06</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.89</v>
+        <v>2.95</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.95</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.33</v>
+        <v>0.37</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.89</v>
+        <v>0.84</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.72</v>
+        <v>0.79</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="BP17" t="n">
-        <v>3.89</v>
+        <v>4.11</v>
       </c>
       <c r="BQ17" t="n">
-        <v>4.61</v>
+        <v>4.42</v>
       </c>
       <c r="BR17" t="n">
         <v>100</v>
       </c>
       <c r="BS17" t="n">
-        <v>61.11</v>
+        <v>63.16</v>
       </c>
       <c r="BT17" t="n">
-        <v>50</v>
+        <v>52.63</v>
       </c>
       <c r="BU17" t="n">
-        <v>22.22</v>
+        <v>26.32</v>
       </c>
       <c r="BV17" t="n">
-        <v>16.67</v>
+        <v>15.79</v>
       </c>
       <c r="BW17" t="n">
-        <v>16.67</v>
+        <v>15.79</v>
       </c>
       <c r="BX17" t="n">
-        <v>44.44</v>
+        <v>47.37</v>
       </c>
       <c r="BY17" t="n">
-        <v>3.24</v>
+        <v>3.2</v>
       </c>
       <c r="BZ17" t="n">
-        <v>3.55</v>
+        <v>3.49</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.48</v>
+        <v>3.44</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.71</v>
+        <v>3.67</v>
       </c>
       <c r="CC17" t="n">
         <v>5.51</v>
@@ -7670,10 +7670,10 @@
         <v>1.42</v>
       </c>
       <c r="CF17" t="n">
-        <v>3.02</v>
+        <v>3.03</v>
       </c>
       <c r="CG17" t="n">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="CH17" t="n">
         <v>1.35</v>
@@ -7685,13 +7685,13 @@
         <v>1.94</v>
       </c>
       <c r="CK17" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="CL17" t="n">
         <v>2.08</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="CN17" t="n">
         <v>1.78</v>
@@ -7703,31 +7703,31 @@
         <v>2.1</v>
       </c>
       <c r="CQ17" t="n">
-        <v>3.66</v>
+        <v>3.7</v>
       </c>
       <c r="CR17" t="n">
         <v>1.47</v>
       </c>
       <c r="CS17" t="n">
-        <v>3.08</v>
+        <v>3.11</v>
       </c>
       <c r="CT17" t="n">
-        <v>2.8</v>
+        <v>2.79</v>
       </c>
       <c r="CU17" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CV17" t="n">
         <v>1.88</v>
       </c>
       <c r="CW17" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="CX17" t="n">
         <v>1.64</v>
       </c>
       <c r="CY17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="CZ17" t="n">
         <v>2.23</v>
@@ -7739,52 +7739,52 @@
         <v>1.37</v>
       </c>
       <c r="DC17" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="DD17" t="n">
-        <v>3.95</v>
+        <v>3.97</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.66</v>
+        <v>1.74</v>
       </c>
       <c r="DG17" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="DH17" t="n">
-        <v>82.22</v>
+        <v>82.73999999999999</v>
       </c>
       <c r="DI17" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DJ17" t="n">
-        <v>3</v>
+        <v>3.11</v>
       </c>
       <c r="DK17" t="n">
-        <v>3.22</v>
+        <v>3.21</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.16</v>
+        <v>0.21</v>
       </c>
       <c r="DM17" t="n">
-        <v>30.11</v>
+        <v>30.52</v>
       </c>
       <c r="DN17" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="DO17" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="DP17" t="n">
-        <v>17.44</v>
+        <v>17.37</v>
       </c>
       <c r="DQ17" t="n">
-        <v>12.94</v>
+        <v>13</v>
       </c>
       <c r="DR17" t="n">
-        <v>8.84</v>
+        <v>9</v>
       </c>
       <c r="DS17" t="n">
         <v>0.16</v>
@@ -7796,28 +7796,28 @@
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>43.88</v>
+        <v>43.95</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DX17" t="n">
-        <v>10.94</v>
+        <v>10.79</v>
       </c>
       <c r="DY17" t="n">
-        <v>6.94</v>
+        <v>6.74</v>
       </c>
       <c r="DZ17" t="n">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="EA17" t="n">
-        <v>21.11</v>
+        <v>21.31</v>
       </c>
       <c r="EB17" t="n">
         <v>1.19</v>
       </c>
       <c r="EC17" t="n">
-        <v>2.89</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -7827,13 +7827,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C18" t="n">
         <v>10</v>
       </c>
       <c r="D18" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E18" t="n">
         <v>0.1</v>
@@ -7917,139 +7917,139 @@
         <v>2.5</v>
       </c>
       <c r="AF18" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="AH18" t="n">
-        <v>3.38</v>
+        <v>3.44</v>
       </c>
       <c r="AI18" t="n">
-        <v>108.5</v>
+        <v>106.22</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AK18" t="n">
-        <v>3.5</v>
+        <v>3.56</v>
       </c>
       <c r="AL18" t="n">
-        <v>5.88</v>
+        <v>5.67</v>
       </c>
       <c r="AM18" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AN18" t="n">
-        <v>47.38</v>
+        <v>44.78</v>
       </c>
       <c r="AO18" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AP18" t="n">
-        <v>2.5</v>
+        <v>2.22</v>
       </c>
       <c r="AQ18" t="n">
-        <v>17.75</v>
+        <v>17.33</v>
       </c>
       <c r="AR18" t="n">
-        <v>13.75</v>
+        <v>14.22</v>
       </c>
       <c r="AS18" t="n">
-        <v>8.75</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="AT18" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AU18" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AV18" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AW18" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AX18" t="n">
         <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>51.12</v>
+        <v>52.56</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="BA18" t="n">
-        <v>13</v>
+        <v>12.22</v>
       </c>
       <c r="BB18" t="n">
-        <v>9.119999999999999</v>
+        <v>8.56</v>
       </c>
       <c r="BC18" t="n">
-        <v>3.88</v>
+        <v>3.67</v>
       </c>
       <c r="BD18" t="n">
-        <v>23</v>
+        <v>22.33</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="BF18" t="n">
-        <v>3.38</v>
+        <v>3.44</v>
       </c>
       <c r="BG18" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="BH18" t="n">
-        <v>9.390000000000001</v>
+        <v>9.26</v>
       </c>
       <c r="BI18" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.33</v>
+        <v>0.37</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BL18" t="n">
-        <v>0.67</v>
+        <v>0.74</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="BO18" t="n">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="BP18" t="n">
-        <v>3.5</v>
+        <v>3.47</v>
       </c>
       <c r="BQ18" t="n">
-        <v>5.89</v>
+        <v>5.79</v>
       </c>
       <c r="BR18" t="n">
-        <v>88.89</v>
+        <v>89.47</v>
       </c>
       <c r="BS18" t="n">
-        <v>55.56</v>
+        <v>57.89</v>
       </c>
       <c r="BT18" t="n">
-        <v>27.78</v>
+        <v>31.58</v>
       </c>
       <c r="BU18" t="n">
-        <v>16.67</v>
+        <v>15.79</v>
       </c>
       <c r="BV18" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BW18" t="n">
         <v>0</v>
       </c>
       <c r="BX18" t="n">
-        <v>44.44</v>
+        <v>42.11</v>
       </c>
       <c r="BY18" t="n">
         <v>1.87</v>
@@ -8058,22 +8058,22 @@
         <v>1.94</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.31</v>
+        <v>3.29</v>
       </c>
       <c r="CB18" t="n">
-        <v>3.44</v>
+        <v>3.41</v>
       </c>
       <c r="CC18" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="CD18" t="n">
-        <v>2.94</v>
+        <v>3.01</v>
       </c>
       <c r="CE18" t="n">
         <v>1.42</v>
       </c>
       <c r="CF18" t="n">
-        <v>2.97</v>
+        <v>2.98</v>
       </c>
       <c r="CG18" t="n">
         <v>2.71</v>
@@ -8085,19 +8085,19 @@
         <v>1.84</v>
       </c>
       <c r="CJ18" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CK18" t="n">
         <v>1.62</v>
       </c>
       <c r="CL18" t="n">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
       <c r="CM18" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="CN18" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CO18" t="n">
         <v>1.35</v>
@@ -8106,25 +8106,25 @@
         <v>2.16</v>
       </c>
       <c r="CQ18" t="n">
-        <v>3.82</v>
+        <v>3.84</v>
       </c>
       <c r="CR18" t="n">
         <v>1.47</v>
       </c>
       <c r="CS18" t="n">
-        <v>3.09</v>
+        <v>3.11</v>
       </c>
       <c r="CT18" t="n">
-        <v>2.83</v>
+        <v>2.8</v>
       </c>
       <c r="CU18" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CV18" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CW18" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="CX18" t="n">
         <v>1.68</v>
@@ -8139,55 +8139,55 @@
         <v>1.72</v>
       </c>
       <c r="DB18" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="DC18" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="DD18" t="n">
-        <v>4.01</v>
+        <v>4.07</v>
       </c>
       <c r="DE18" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="DG18" t="n">
         <v>4</v>
       </c>
       <c r="DH18" t="n">
-        <v>111</v>
+        <v>109.79</v>
       </c>
       <c r="DI18" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DJ18" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="DK18" t="n">
-        <v>6.5</v>
+        <v>6.37</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.67</v>
+        <v>0.63</v>
       </c>
       <c r="DM18" t="n">
-        <v>57.56</v>
+        <v>55.79</v>
       </c>
       <c r="DN18" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="DO18" t="n">
-        <v>2.5</v>
+        <v>2.37</v>
       </c>
       <c r="DP18" t="n">
-        <v>17.89</v>
+        <v>17.68</v>
       </c>
       <c r="DQ18" t="n">
-        <v>13.28</v>
+        <v>13.53</v>
       </c>
       <c r="DR18" t="n">
-        <v>6.78</v>
+        <v>6.63</v>
       </c>
       <c r="DS18" t="n">
         <v>0.16</v>
@@ -8199,28 +8199,28 @@
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>51.89</v>
+        <v>52.53</v>
       </c>
       <c r="DW18" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DX18" t="n">
-        <v>15.44</v>
+        <v>14.95</v>
       </c>
       <c r="DY18" t="n">
-        <v>10.66</v>
+        <v>10.32</v>
       </c>
       <c r="DZ18" t="n">
-        <v>4.78</v>
+        <v>4.63</v>
       </c>
       <c r="EA18" t="n">
-        <v>26.39</v>
+        <v>25.89</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="EC18" t="n">
-        <v>2.89</v>
+        <v>2.95</v>
       </c>
     </row>
     <row r="19">
@@ -8633,94 +8633,94 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D20" t="n">
         <v>9</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="F20" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="G20" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="H20" t="n">
-        <v>114.89</v>
+        <v>115.1</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="K20" t="n">
-        <v>5.67</v>
+        <v>5.4</v>
       </c>
       <c r="L20" t="n">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="M20" t="n">
-        <v>60.33</v>
+        <v>60.1</v>
       </c>
       <c r="N20" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="O20" t="n">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="P20" t="n">
-        <v>15.67</v>
+        <v>15.9</v>
       </c>
       <c r="Q20" t="n">
-        <v>11</v>
+        <v>11.3</v>
       </c>
       <c r="R20" t="n">
-        <v>6.56</v>
+        <v>6.4</v>
       </c>
       <c r="S20" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="T20" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="U20" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="V20" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>55.22</v>
+        <v>53.3</v>
       </c>
       <c r="Y20" t="n">
         <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>17.11</v>
+        <v>16.3</v>
       </c>
       <c r="AA20" t="n">
-        <v>11.33</v>
+        <v>10.7</v>
       </c>
       <c r="AB20" t="n">
-        <v>5.78</v>
+        <v>5.6</v>
       </c>
       <c r="AC20" t="n">
-        <v>18.33</v>
+        <v>18</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="AF20" t="n">
         <v>0.11</v>
@@ -8804,70 +8804,70 @@
         <v>2.33</v>
       </c>
       <c r="BG20" t="n">
-        <v>2.33</v>
+        <v>2.37</v>
       </c>
       <c r="BH20" t="n">
-        <v>9.06</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="BI20" t="n">
-        <v>2.33</v>
+        <v>2.37</v>
       </c>
       <c r="BJ20" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="BK20" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="BL20" t="n">
-        <v>0.9399999999999999</v>
+        <v>1</v>
       </c>
       <c r="BM20" t="n">
-        <v>0.39</v>
+        <v>0.37</v>
       </c>
       <c r="BN20" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="BO20" t="n">
         <v>1</v>
       </c>
       <c r="BP20" t="n">
-        <v>4.17</v>
+        <v>4.11</v>
       </c>
       <c r="BQ20" t="n">
-        <v>4.89</v>
+        <v>4.84</v>
       </c>
       <c r="BR20" t="n">
-        <v>83.33</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="BS20" t="n">
-        <v>72.22</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="BT20" t="n">
-        <v>50</v>
+        <v>52.63</v>
       </c>
       <c r="BU20" t="n">
-        <v>22.22</v>
+        <v>21.05</v>
       </c>
       <c r="BV20" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BW20" t="n">
         <v>0</v>
       </c>
       <c r="BX20" t="n">
-        <v>55.56</v>
+        <v>52.63</v>
       </c>
       <c r="BY20" t="n">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="BZ20" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="CA20" t="n">
-        <v>3.2</v>
+        <v>3.19</v>
       </c>
       <c r="CB20" t="n">
-        <v>3.28</v>
+        <v>3.26</v>
       </c>
       <c r="CC20" t="n">
         <v>3.3</v>
@@ -8879,37 +8879,37 @@
         <v>1.47</v>
       </c>
       <c r="CF20" t="n">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="CG20" t="n">
-        <v>2.54</v>
+        <v>2.55</v>
       </c>
       <c r="CH20" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="CI20" t="n">
         <v>1.75</v>
       </c>
       <c r="CJ20" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="CK20" t="n">
         <v>1.63</v>
       </c>
       <c r="CL20" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="CM20" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="CN20" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CO20" t="n">
         <v>1.42</v>
       </c>
       <c r="CP20" t="n">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="CQ20" t="n">
         <v>4.3</v>
@@ -8918,16 +8918,16 @@
         <v>1.54</v>
       </c>
       <c r="CS20" t="n">
-        <v>3.24</v>
+        <v>3.25</v>
       </c>
       <c r="CT20" t="n">
-        <v>2.61</v>
+        <v>2.59</v>
       </c>
       <c r="CU20" t="n">
         <v>1.36</v>
       </c>
       <c r="CV20" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CW20" t="n">
         <v>2.08</v>
@@ -8945,55 +8945,55 @@
         <v>1.72</v>
       </c>
       <c r="DB20" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="DC20" t="n">
-        <v>2.43</v>
+        <v>2.44</v>
       </c>
       <c r="DD20" t="n">
-        <v>4.62</v>
+        <v>4.65</v>
       </c>
       <c r="DE20" t="n">
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="DF20" t="n">
-        <v>1.56</v>
+        <v>1.63</v>
       </c>
       <c r="DG20" t="n">
-        <v>2.89</v>
+        <v>2.74</v>
       </c>
       <c r="DH20" t="n">
-        <v>106.34</v>
+        <v>106.9</v>
       </c>
       <c r="DI20" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DJ20" t="n">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="DK20" t="n">
-        <v>4.84</v>
+        <v>4.74</v>
       </c>
       <c r="DL20" t="n">
-        <v>0.33</v>
+        <v>0.37</v>
       </c>
       <c r="DM20" t="n">
-        <v>48.94</v>
+        <v>49.42</v>
       </c>
       <c r="DN20" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="DO20" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="DP20" t="n">
-        <v>14.39</v>
+        <v>14.58</v>
       </c>
       <c r="DQ20" t="n">
-        <v>12.5</v>
+        <v>12.58</v>
       </c>
       <c r="DR20" t="n">
-        <v>6.89</v>
+        <v>6.79</v>
       </c>
       <c r="DS20" t="n">
         <v>0.11</v>
@@ -9005,28 +9005,28 @@
         <v>0</v>
       </c>
       <c r="DV20" t="n">
-        <v>51.28</v>
+        <v>50.47</v>
       </c>
       <c r="DW20" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DX20" t="n">
-        <v>13.11</v>
+        <v>12.89</v>
       </c>
       <c r="DY20" t="n">
-        <v>8.720000000000001</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="DZ20" t="n">
-        <v>4.39</v>
+        <v>4.37</v>
       </c>
       <c r="EA20" t="n">
-        <v>18.88</v>
+        <v>18.68</v>
       </c>
       <c r="EB20" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="EC20" t="n">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
     </row>
     <row r="21">
@@ -9036,10 +9036,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D21" t="n">
         <v>9</v>
@@ -9048,82 +9048,82 @@
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>1.22</v>
+        <v>1.6</v>
       </c>
       <c r="G21" t="n">
-        <v>2.78</v>
+        <v>3.1</v>
       </c>
       <c r="H21" t="n">
-        <v>98.78</v>
+        <v>99.2</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>1.89</v>
+        <v>2.2</v>
       </c>
       <c r="K21" t="n">
-        <v>5.22</v>
+        <v>5.5</v>
       </c>
       <c r="L21" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="M21" t="n">
-        <v>44.22</v>
+        <v>46.2</v>
       </c>
       <c r="N21" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="O21" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="P21" t="n">
-        <v>14.22</v>
+        <v>14.1</v>
       </c>
       <c r="Q21" t="n">
-        <v>13.22</v>
+        <v>13</v>
       </c>
       <c r="R21" t="n">
-        <v>9.44</v>
+        <v>9.1</v>
       </c>
       <c r="S21" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T21" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="U21" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="V21" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>46.56</v>
+        <v>46.8</v>
       </c>
       <c r="Y21" t="n">
         <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>12.11</v>
+        <v>12.4</v>
       </c>
       <c r="AA21" t="n">
-        <v>8.220000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AB21" t="n">
-        <v>3.89</v>
+        <v>3.8</v>
       </c>
       <c r="AC21" t="n">
-        <v>24.33</v>
+        <v>24.2</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.89</v>
+        <v>2.2</v>
       </c>
       <c r="AF21" t="n">
         <v>0</v>
@@ -9207,70 +9207,70 @@
         <v>1.89</v>
       </c>
       <c r="BG21" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="BH21" t="n">
-        <v>9.609999999999999</v>
+        <v>9.68</v>
       </c>
       <c r="BI21" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="BJ21" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="BK21" t="n">
-        <v>0.44</v>
+        <v>0.47</v>
       </c>
       <c r="BL21" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="BM21" t="n">
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
       <c r="BN21" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="BO21" t="n">
         <v>1</v>
       </c>
       <c r="BP21" t="n">
-        <v>4.33</v>
+        <v>4.32</v>
       </c>
       <c r="BQ21" t="n">
-        <v>5.22</v>
+        <v>5.32</v>
       </c>
       <c r="BR21" t="n">
-        <v>94.44</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BS21" t="n">
-        <v>66.67</v>
+        <v>68.42</v>
       </c>
       <c r="BT21" t="n">
-        <v>38.89</v>
+        <v>36.84</v>
       </c>
       <c r="BU21" t="n">
-        <v>16.67</v>
+        <v>15.79</v>
       </c>
       <c r="BV21" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BW21" t="n">
         <v>0</v>
       </c>
       <c r="BX21" t="n">
-        <v>44.44</v>
+        <v>47.37</v>
       </c>
       <c r="BY21" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="BZ21" t="n">
         <v>2.67</v>
       </c>
       <c r="CA21" t="n">
-        <v>2.89</v>
+        <v>2.91</v>
       </c>
       <c r="CB21" t="n">
-        <v>3.01</v>
+        <v>3.02</v>
       </c>
       <c r="CC21" t="n">
         <v>3.44</v>
@@ -9279,124 +9279,124 @@
         <v>3.96</v>
       </c>
       <c r="CE21" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CF21" t="n">
-        <v>3.73</v>
+        <v>3.68</v>
       </c>
       <c r="CG21" t="n">
-        <v>2.29</v>
+        <v>2.32</v>
       </c>
       <c r="CH21" t="n">
         <v>1.24</v>
       </c>
       <c r="CI21" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="CJ21" t="n">
-        <v>2.19</v>
+        <v>2.16</v>
       </c>
       <c r="CK21" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="CL21" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="CM21" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="CN21" t="n">
         <v>1.69</v>
       </c>
       <c r="CO21" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CP21" t="n">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="CQ21" t="n">
-        <v>5.13</v>
+        <v>5.04</v>
       </c>
       <c r="CR21" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CS21" t="n">
-        <v>3.35</v>
+        <v>3.28</v>
       </c>
       <c r="CT21" t="n">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="CU21" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="CV21" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="CW21" t="n">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="CX21" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CY21" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="CZ21" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="DA21" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="DB21" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="DC21" t="n">
-        <v>2.86</v>
+        <v>2.81</v>
       </c>
       <c r="DD21" t="n">
-        <v>5.78</v>
+        <v>5.66</v>
       </c>
       <c r="DE21" t="n">
         <v>0</v>
       </c>
       <c r="DF21" t="n">
-        <v>1.28</v>
+        <v>1.47</v>
       </c>
       <c r="DG21" t="n">
-        <v>2.44</v>
+        <v>2.63</v>
       </c>
       <c r="DH21" t="n">
-        <v>89.72</v>
+        <v>90.42</v>
       </c>
       <c r="DI21" t="n">
         <v>0</v>
       </c>
       <c r="DJ21" t="n">
-        <v>2</v>
+        <v>2.16</v>
       </c>
       <c r="DK21" t="n">
-        <v>4.44</v>
+        <v>4.63</v>
       </c>
       <c r="DL21" t="n">
-        <v>0.78</v>
+        <v>0.74</v>
       </c>
       <c r="DM21" t="n">
-        <v>38.28</v>
+        <v>39.63</v>
       </c>
       <c r="DN21" t="n">
-        <v>0.67</v>
+        <v>0.63</v>
       </c>
       <c r="DO21" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="DP21" t="n">
-        <v>12.39</v>
+        <v>12.42</v>
       </c>
       <c r="DQ21" t="n">
-        <v>12.94</v>
+        <v>12.84</v>
       </c>
       <c r="DR21" t="n">
-        <v>9.109999999999999</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="DS21" t="n">
         <v>0.16</v>
@@ -9408,28 +9408,28 @@
         <v>0</v>
       </c>
       <c r="DV21" t="n">
-        <v>46.22</v>
+        <v>46.37</v>
       </c>
       <c r="DW21" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DX21" t="n">
-        <v>10.44</v>
+        <v>10.69</v>
       </c>
       <c r="DY21" t="n">
-        <v>7.61</v>
+        <v>7.84</v>
       </c>
       <c r="DZ21" t="n">
         <v>2.84</v>
       </c>
       <c r="EA21" t="n">
-        <v>20.83</v>
+        <v>20.95</v>
       </c>
       <c r="EB21" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="EC21" t="n">
-        <v>1.89</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="22">
@@ -9439,13 +9439,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C22" t="n">
         <v>10</v>
       </c>
       <c r="D22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -9529,139 +9529,139 @@
         <v>2</v>
       </c>
       <c r="AF22" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AG22" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AI22" t="n">
-        <v>88.62</v>
+        <v>86.67</v>
       </c>
       <c r="AJ22" t="n">
         <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>3.62</v>
+        <v>3.56</v>
       </c>
       <c r="AL22" t="n">
-        <v>3</v>
+        <v>3.44</v>
       </c>
       <c r="AM22" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AN22" t="n">
-        <v>34.12</v>
+        <v>34.56</v>
       </c>
       <c r="AO22" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.25</v>
+        <v>1.56</v>
       </c>
       <c r="AQ22" t="n">
-        <v>12.38</v>
+        <v>11.89</v>
       </c>
       <c r="AR22" t="n">
-        <v>11</v>
+        <v>10.67</v>
       </c>
       <c r="AS22" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="AT22" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AU22" t="n">
         <v>1</v>
       </c>
       <c r="AV22" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AW22" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AX22" t="n">
         <v>0</v>
       </c>
       <c r="AY22" t="n">
-        <v>42.75</v>
+        <v>42.44</v>
       </c>
       <c r="AZ22" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="BA22" t="n">
-        <v>8.119999999999999</v>
+        <v>8.44</v>
       </c>
       <c r="BB22" t="n">
-        <v>4.75</v>
+        <v>4.89</v>
       </c>
       <c r="BC22" t="n">
-        <v>3.38</v>
+        <v>3.56</v>
       </c>
       <c r="BD22" t="n">
-        <v>20.38</v>
+        <v>19.67</v>
       </c>
       <c r="BE22" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="BF22" t="n">
-        <v>3.38</v>
+        <v>3.33</v>
       </c>
       <c r="BG22" t="n">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="BH22" t="n">
-        <v>9.390000000000001</v>
+        <v>9.58</v>
       </c>
       <c r="BI22" t="n">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="BJ22" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="BK22" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="BL22" t="n">
-        <v>0.89</v>
+        <v>0.84</v>
       </c>
       <c r="BM22" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="BN22" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="BO22" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="BP22" t="n">
-        <v>4.56</v>
+        <v>4.63</v>
       </c>
       <c r="BQ22" t="n">
-        <v>4.78</v>
+        <v>4.89</v>
       </c>
       <c r="BR22" t="n">
-        <v>94.44</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BS22" t="n">
-        <v>61.11</v>
+        <v>57.89</v>
       </c>
       <c r="BT22" t="n">
-        <v>44.44</v>
+        <v>42.11</v>
       </c>
       <c r="BU22" t="n">
-        <v>22.22</v>
+        <v>21.05</v>
       </c>
       <c r="BV22" t="n">
-        <v>16.67</v>
+        <v>15.79</v>
       </c>
       <c r="BW22" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BX22" t="n">
-        <v>55.56</v>
+        <v>52.63</v>
       </c>
       <c r="BY22" t="n">
         <v>2.11</v>
@@ -9670,34 +9670,34 @@
         <v>2.13</v>
       </c>
       <c r="CA22" t="n">
-        <v>3.21</v>
+        <v>3.2</v>
       </c>
       <c r="CB22" t="n">
-        <v>3.31</v>
+        <v>3.29</v>
       </c>
       <c r="CC22" t="n">
-        <v>3.23</v>
+        <v>3.22</v>
       </c>
       <c r="CD22" t="n">
-        <v>3.31</v>
+        <v>3.32</v>
       </c>
       <c r="CE22" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CF22" t="n">
-        <v>3.09</v>
+        <v>3.1</v>
       </c>
       <c r="CG22" t="n">
-        <v>2.69</v>
+        <v>2.67</v>
       </c>
       <c r="CH22" t="n">
         <v>1.34</v>
       </c>
       <c r="CI22" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="CJ22" t="n">
         <v>1.88</v>
-      </c>
-      <c r="CJ22" t="n">
-        <v>1.87</v>
       </c>
       <c r="CK22" t="n">
         <v>1.62</v>
@@ -9712,22 +9712,22 @@
         <v>1.72</v>
       </c>
       <c r="CO22" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CP22" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="CQ22" t="n">
-        <v>3.85</v>
+        <v>3.92</v>
       </c>
       <c r="CR22" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="CS22" t="n">
         <v>3.11</v>
       </c>
       <c r="CT22" t="n">
-        <v>2.81</v>
+        <v>2.79</v>
       </c>
       <c r="CU22" t="n">
         <v>1.4</v>
@@ -9736,7 +9736,7 @@
         <v>1.94</v>
       </c>
       <c r="CW22" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="CX22" t="n">
         <v>1.65</v>
@@ -9754,85 +9754,85 @@
         <v>1.42</v>
       </c>
       <c r="DC22" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="DD22" t="n">
-        <v>4.31</v>
+        <v>4.36</v>
       </c>
       <c r="DE22" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DF22" t="n">
-        <v>2.11</v>
+        <v>2.16</v>
       </c>
       <c r="DG22" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="DH22" t="n">
-        <v>101.05</v>
+        <v>99.48</v>
       </c>
       <c r="DI22" t="n">
         <v>0</v>
       </c>
       <c r="DJ22" t="n">
-        <v>2.94</v>
+        <v>2.95</v>
       </c>
       <c r="DK22" t="n">
-        <v>4.33</v>
+        <v>4.47</v>
       </c>
       <c r="DL22" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="DM22" t="n">
-        <v>41.72</v>
+        <v>41.53</v>
       </c>
       <c r="DN22" t="n">
-        <v>0.72</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="DO22" t="n">
-        <v>2.11</v>
+        <v>2.21</v>
       </c>
       <c r="DP22" t="n">
-        <v>12.72</v>
+        <v>12.47</v>
       </c>
       <c r="DQ22" t="n">
-        <v>10.94</v>
+        <v>10.79</v>
       </c>
       <c r="DR22" t="n">
-        <v>7.61</v>
+        <v>7.89</v>
       </c>
       <c r="DS22" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DT22" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DU22" t="n">
         <v>0</v>
       </c>
       <c r="DV22" t="n">
-        <v>44.44</v>
+        <v>44.21</v>
       </c>
       <c r="DW22" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DX22" t="n">
-        <v>11.11</v>
+        <v>11.1</v>
       </c>
       <c r="DY22" t="n">
-        <v>6.61</v>
+        <v>6.58</v>
       </c>
       <c r="DZ22" t="n">
-        <v>4.5</v>
+        <v>4.53</v>
       </c>
       <c r="EA22" t="n">
-        <v>20.06</v>
+        <v>19.74</v>
       </c>
       <c r="EB22" t="n">
         <v>1.32</v>
       </c>
       <c r="EC22" t="n">
-        <v>2.61</v>
+        <v>2.63</v>
       </c>
     </row>
     <row r="23">
@@ -9842,61 +9842,61 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C23" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D23" t="n">
         <v>9</v>
       </c>
       <c r="E23" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="F23" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="G23" t="n">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="H23" t="n">
-        <v>96.89</v>
+        <v>95.5</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="K23" t="n">
         <v>4</v>
       </c>
       <c r="L23" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="M23" t="n">
-        <v>38.56</v>
+        <v>37.6</v>
       </c>
       <c r="N23" t="n">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="O23" t="n">
-        <v>1.89</v>
+        <v>2.1</v>
       </c>
       <c r="P23" t="n">
-        <v>13.78</v>
+        <v>13.5</v>
       </c>
       <c r="Q23" t="n">
-        <v>16.33</v>
+        <v>16</v>
       </c>
       <c r="R23" t="n">
-        <v>6.11</v>
+        <v>6.4</v>
       </c>
       <c r="S23" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="T23" t="n">
-        <v>1.33</v>
+        <v>1.6</v>
       </c>
       <c r="U23" t="n">
         <v>0</v>
@@ -9908,28 +9908,28 @@
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>55.22</v>
+        <v>54.5</v>
       </c>
       <c r="Y23" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="Z23" t="n">
-        <v>12.22</v>
+        <v>12</v>
       </c>
       <c r="AA23" t="n">
-        <v>7.89</v>
+        <v>7.7</v>
       </c>
       <c r="AB23" t="n">
-        <v>4.33</v>
+        <v>4.3</v>
       </c>
       <c r="AC23" t="n">
-        <v>19.22</v>
+        <v>18.6</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AF23" t="n">
         <v>0</v>
@@ -10013,49 +10013,49 @@
         <v>2</v>
       </c>
       <c r="BG23" t="n">
-        <v>1.67</v>
+        <v>1.79</v>
       </c>
       <c r="BH23" t="n">
-        <v>7.56</v>
+        <v>7.58</v>
       </c>
       <c r="BI23" t="n">
-        <v>1.67</v>
+        <v>1.79</v>
       </c>
       <c r="BJ23" t="n">
-        <v>0.5</v>
+        <v>0.68</v>
       </c>
       <c r="BK23" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="BL23" t="n">
-        <v>0.39</v>
+        <v>0.37</v>
       </c>
       <c r="BM23" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BN23" t="n">
-        <v>0.89</v>
+        <v>0.84</v>
       </c>
       <c r="BO23" t="n">
-        <v>0.78</v>
+        <v>0.95</v>
       </c>
       <c r="BP23" t="n">
-        <v>3.61</v>
+        <v>3.63</v>
       </c>
       <c r="BQ23" t="n">
-        <v>3.94</v>
+        <v>3.95</v>
       </c>
       <c r="BR23" t="n">
-        <v>77.78</v>
+        <v>78.95</v>
       </c>
       <c r="BS23" t="n">
-        <v>44.44</v>
+        <v>47.37</v>
       </c>
       <c r="BT23" t="n">
-        <v>27.78</v>
+        <v>31.58</v>
       </c>
       <c r="BU23" t="n">
-        <v>16.67</v>
+        <v>21.05</v>
       </c>
       <c r="BV23" t="n">
         <v>0</v>
@@ -10064,19 +10064,19 @@
         <v>0</v>
       </c>
       <c r="BX23" t="n">
-        <v>44.44</v>
+        <v>42.11</v>
       </c>
       <c r="BY23" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="BZ23" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="CA23" t="n">
-        <v>3.22</v>
+        <v>3.23</v>
       </c>
       <c r="CB23" t="n">
-        <v>3.34</v>
+        <v>3.36</v>
       </c>
       <c r="CC23" t="n">
         <v>3.05</v>
@@ -10088,10 +10088,10 @@
         <v>1.47</v>
       </c>
       <c r="CF23" t="n">
-        <v>3.22</v>
+        <v>3.21</v>
       </c>
       <c r="CG23" t="n">
-        <v>2.53</v>
+        <v>2.54</v>
       </c>
       <c r="CH23" t="n">
         <v>1.31</v>
@@ -10106,7 +10106,7 @@
         <v>1.7</v>
       </c>
       <c r="CL23" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="CM23" t="n">
         <v>2.07</v>
@@ -10121,16 +10121,16 @@
         <v>2.22</v>
       </c>
       <c r="CQ23" t="n">
-        <v>4.18</v>
+        <v>4.16</v>
       </c>
       <c r="CR23" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CS23" t="n">
         <v>3.2</v>
       </c>
       <c r="CT23" t="n">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
       <c r="CU23" t="n">
         <v>1.37</v>
@@ -10139,10 +10139,10 @@
         <v>1.82</v>
       </c>
       <c r="CW23" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="CX23" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CY23" t="n">
         <v>2.23</v>
@@ -10157,52 +10157,52 @@
         <v>1.44</v>
       </c>
       <c r="DC23" t="n">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="DD23" t="n">
-        <v>4.55</v>
+        <v>4.53</v>
       </c>
       <c r="DE23" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="DF23" t="n">
-        <v>1.61</v>
+        <v>1.52</v>
       </c>
       <c r="DG23" t="n">
-        <v>1.89</v>
+        <v>1.79</v>
       </c>
       <c r="DH23" t="n">
-        <v>94.11</v>
+        <v>93.52</v>
       </c>
       <c r="DI23" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DJ23" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="DK23" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="DL23" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="DM23" t="n">
+        <v>37.42</v>
+      </c>
+      <c r="DN23" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="DO23" t="n">
         <v>2.16</v>
       </c>
-      <c r="DK23" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="DL23" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="DM23" t="n">
-        <v>37.89</v>
-      </c>
-      <c r="DN23" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="DO23" t="n">
-        <v>2.05</v>
-      </c>
       <c r="DP23" t="n">
-        <v>12.78</v>
+        <v>12.69</v>
       </c>
       <c r="DQ23" t="n">
-        <v>17.61</v>
+        <v>17.37</v>
       </c>
       <c r="DR23" t="n">
-        <v>7.72</v>
+        <v>7.79</v>
       </c>
       <c r="DS23" t="n">
         <v>0</v>
@@ -10214,28 +10214,28 @@
         <v>0</v>
       </c>
       <c r="DV23" t="n">
-        <v>56.06</v>
+        <v>55.63</v>
       </c>
       <c r="DW23" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DX23" t="n">
-        <v>11.06</v>
+        <v>11</v>
       </c>
       <c r="DY23" t="n">
-        <v>7.56</v>
+        <v>7.47</v>
       </c>
       <c r="DZ23" t="n">
-        <v>3.5</v>
+        <v>3.53</v>
       </c>
       <c r="EA23" t="n">
-        <v>18.61</v>
+        <v>18.32</v>
       </c>
       <c r="EB23" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="EC23" t="n">
-        <v>1.84</v>
+        <v>1.79</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Spain_Segunda_División_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Spain_Segunda_División_2025-2026.xlsx
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C2" t="n">
         <v>9</v>
       </c>
       <c r="D2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -1469,139 +1469,139 @@
         <v>1.67</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="AI2" t="n">
-        <v>86.44</v>
+        <v>86.3</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AK2" t="n">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
       <c r="AL2" t="n">
-        <v>4.22</v>
+        <v>4.3</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AN2" t="n">
-        <v>39.89</v>
+        <v>39.2</v>
       </c>
       <c r="AO2" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AP2" t="n">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="AQ2" t="n">
-        <v>12.78</v>
+        <v>12.7</v>
       </c>
       <c r="AR2" t="n">
-        <v>13.33</v>
+        <v>13.1</v>
       </c>
       <c r="AS2" t="n">
-        <v>9</v>
+        <v>9.1</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="AX2" t="n">
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>42.78</v>
+        <v>42.8</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="BA2" t="n">
-        <v>11.33</v>
+        <v>11.5</v>
       </c>
       <c r="BB2" t="n">
-        <v>6.67</v>
+        <v>6.9</v>
       </c>
       <c r="BC2" t="n">
-        <v>4.67</v>
+        <v>4.6</v>
       </c>
       <c r="BD2" t="n">
-        <v>24.11</v>
+        <v>23.5</v>
       </c>
       <c r="BE2" t="n">
         <v>1.33</v>
       </c>
       <c r="BF2" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="BG2" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="BH2" t="n">
-        <v>10.56</v>
+        <v>10.58</v>
       </c>
       <c r="BI2" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.44</v>
+        <v>0.47</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.89</v>
+        <v>0.84</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="BN2" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.95</v>
       </c>
       <c r="BP2" t="n">
-        <v>5</v>
+        <v>4.95</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.5</v>
+        <v>5.58</v>
       </c>
       <c r="BR2" t="n">
-        <v>83.33</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="BS2" t="n">
-        <v>66.67</v>
+        <v>68.42</v>
       </c>
       <c r="BT2" t="n">
-        <v>55.56</v>
+        <v>52.63</v>
       </c>
       <c r="BU2" t="n">
-        <v>38.89</v>
+        <v>36.84</v>
       </c>
       <c r="BV2" t="n">
-        <v>27.78</v>
+        <v>26.32</v>
       </c>
       <c r="BW2" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BX2" t="n">
-        <v>55.56</v>
+        <v>57.89</v>
       </c>
       <c r="BY2" t="n">
         <v>2.16</v>
@@ -1610,25 +1610,25 @@
         <v>2.16</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.31</v>
+        <v>3.3</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.52</v>
+        <v>3.51</v>
       </c>
       <c r="CC2" t="n">
-        <v>3.85</v>
+        <v>3.83</v>
       </c>
       <c r="CD2" t="n">
-        <v>4.38</v>
+        <v>4.35</v>
       </c>
       <c r="CE2" t="n">
         <v>1.39</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.89</v>
+        <v>2.87</v>
       </c>
       <c r="CH2" t="n">
         <v>1.41</v>
@@ -1643,7 +1643,7 @@
         <v>1.5</v>
       </c>
       <c r="CL2" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CM2" t="n">
         <v>2.43</v>
@@ -1664,19 +1664,19 @@
         <v>1.42</v>
       </c>
       <c r="CS2" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="CT2" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="CU2" t="n">
         <v>1.44</v>
       </c>
       <c r="CV2" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="CW2" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CX2" t="n">
         <v>1.52</v>
@@ -1685,94 +1685,94 @@
         <v>1.87</v>
       </c>
       <c r="CZ2" t="n">
-        <v>2.43</v>
+        <v>2.44</v>
       </c>
       <c r="DA2" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="DB2" t="n">
         <v>1.31</v>
       </c>
       <c r="DC2" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="DD2" t="n">
-        <v>3.42</v>
+        <v>3.45</v>
       </c>
       <c r="DE2" t="n">
         <v>0.16</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.62</v>
+        <v>1.69</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.34</v>
+        <v>2.42</v>
       </c>
       <c r="DH2" t="n">
-        <v>89.16</v>
+        <v>88.95</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="DK2" t="n">
-        <v>4.89</v>
+        <v>4.9</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="DM2" t="n">
-        <v>42.78</v>
+        <v>42.26</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.72</v>
+        <v>0.68</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.56</v>
+        <v>2.48</v>
       </c>
       <c r="DP2" t="n">
-        <v>11.28</v>
+        <v>11.32</v>
       </c>
       <c r="DQ2" t="n">
-        <v>10.88</v>
+        <v>10.89</v>
       </c>
       <c r="DR2" t="n">
-        <v>7.72</v>
+        <v>7.84</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>43.17</v>
+        <v>43.16</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DX2" t="n">
         <v>13.16</v>
       </c>
       <c r="DY2" t="n">
-        <v>8.44</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="DZ2" t="n">
-        <v>4.73</v>
+        <v>4.69</v>
       </c>
       <c r="EA2" t="n">
-        <v>24.67</v>
+        <v>24.31</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
     </row>
     <row r="3">
@@ -2185,94 +2185,94 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D4" t="n">
         <v>9</v>
       </c>
       <c r="E4" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="F4" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="G4" t="n">
-        <v>2.11</v>
+        <v>2.3</v>
       </c>
       <c r="H4" t="n">
-        <v>94.89</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>3.11</v>
+        <v>2.9</v>
       </c>
       <c r="K4" t="n">
-        <v>3.89</v>
+        <v>4</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="M4" t="n">
-        <v>46.11</v>
+        <v>46.2</v>
       </c>
       <c r="N4" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="O4" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="P4" t="n">
-        <v>13.89</v>
+        <v>13.8</v>
       </c>
       <c r="Q4" t="n">
-        <v>14.44</v>
+        <v>14.5</v>
       </c>
       <c r="R4" t="n">
-        <v>8.44</v>
+        <v>9</v>
       </c>
       <c r="S4" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="V4" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>50.11</v>
+        <v>49.2</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>10.67</v>
+        <v>10.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>7.78</v>
+        <v>7.5</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.89</v>
+        <v>3</v>
       </c>
       <c r="AC4" t="n">
-        <v>26.89</v>
+        <v>25.7</v>
       </c>
       <c r="AD4" t="n">
         <v>1.21</v>
       </c>
       <c r="AE4" t="n">
-        <v>3.11</v>
+        <v>2.9</v>
       </c>
       <c r="AF4" t="n">
         <v>0.11</v>
@@ -2356,64 +2356,64 @@
         <v>2.44</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="BH4" t="n">
-        <v>8.220000000000001</v>
+        <v>8.42</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="BP4" t="n">
-        <v>3.78</v>
+        <v>3.84</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.44</v>
+        <v>4.58</v>
       </c>
       <c r="BR4" t="n">
-        <v>83.33</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="BS4" t="n">
-        <v>61.11</v>
+        <v>63.16</v>
       </c>
       <c r="BT4" t="n">
-        <v>44.44</v>
+        <v>42.11</v>
       </c>
       <c r="BU4" t="n">
-        <v>16.67</v>
+        <v>15.79</v>
       </c>
       <c r="BV4" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BW4" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BX4" t="n">
-        <v>50</v>
+        <v>52.63</v>
       </c>
       <c r="BY4" t="n">
-        <v>2.26</v>
+        <v>2.23</v>
       </c>
       <c r="BZ4" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="CA4" t="n">
         <v>3.01</v>
@@ -2428,10 +2428,10 @@
         <v>4.04</v>
       </c>
       <c r="CE4" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="CF4" t="n">
-        <v>3.45</v>
+        <v>3.46</v>
       </c>
       <c r="CG4" t="n">
         <v>2.36</v>
@@ -2440,7 +2440,7 @@
         <v>1.26</v>
       </c>
       <c r="CI4" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CJ4" t="n">
         <v>2.14</v>
@@ -2449,7 +2449,7 @@
         <v>1.72</v>
       </c>
       <c r="CL4" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="CM4" t="n">
         <v>2.06</v>
@@ -2464,16 +2464,16 @@
         <v>2.51</v>
       </c>
       <c r="CQ4" t="n">
-        <v>4.78</v>
+        <v>4.85</v>
       </c>
       <c r="CR4" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="CS4" t="n">
         <v>3.38</v>
       </c>
       <c r="CT4" t="n">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="CU4" t="n">
         <v>1.33</v>
@@ -2482,7 +2482,7 @@
         <v>1.7</v>
       </c>
       <c r="CW4" t="n">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="CX4" t="n">
         <v>1.76</v>
@@ -2500,85 +2500,85 @@
         <v>1.54</v>
       </c>
       <c r="DC4" t="n">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="DD4" t="n">
-        <v>5.38</v>
+        <v>5.42</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.61</v>
+        <v>1.52</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.16</v>
+        <v>2.26</v>
       </c>
       <c r="DH4" t="n">
-        <v>89.89</v>
+        <v>89.37</v>
       </c>
       <c r="DI4" t="n">
         <v>0</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.78</v>
+        <v>2.68</v>
       </c>
       <c r="DK4" t="n">
-        <v>3.89</v>
+        <v>3.95</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.11</v>
+        <v>0.16</v>
       </c>
       <c r="DM4" t="n">
-        <v>42.06</v>
+        <v>42.32</v>
       </c>
       <c r="DN4" t="n">
         <v>1.16</v>
       </c>
       <c r="DO4" t="n">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="DP4" t="n">
-        <v>14</v>
+        <v>13.95</v>
       </c>
       <c r="DQ4" t="n">
-        <v>14.78</v>
+        <v>14.79</v>
       </c>
       <c r="DR4" t="n">
-        <v>8.77</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.38</v>
+        <v>0.37</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.38</v>
+        <v>0.37</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>47.56</v>
+        <v>47.21</v>
       </c>
       <c r="DW4" t="n">
         <v>0</v>
       </c>
       <c r="DX4" t="n">
-        <v>9.67</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="DY4" t="n">
-        <v>6.84</v>
+        <v>6.74</v>
       </c>
       <c r="DZ4" t="n">
-        <v>2.84</v>
+        <v>2.9</v>
       </c>
       <c r="EA4" t="n">
-        <v>24.28</v>
+        <v>23.79</v>
       </c>
       <c r="EB4" t="n">
         <v>1.12</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.78</v>
+        <v>2.68</v>
       </c>
     </row>
     <row r="5">
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C5" t="n">
         <v>9</v>
       </c>
       <c r="D5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E5" t="n">
         <v>0.22</v>
@@ -2678,139 +2678,139 @@
         <v>3.44</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.56</v>
+        <v>3.2</v>
       </c>
       <c r="AI5" t="n">
-        <v>93.44</v>
+        <v>92.7</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.89</v>
+        <v>2.8</v>
       </c>
       <c r="AL5" t="n">
-        <v>5.67</v>
+        <v>6.3</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AN5" t="n">
-        <v>53.22</v>
+        <v>57.1</v>
       </c>
       <c r="AO5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>14</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>6</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>53</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>9</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>10.53</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BO5" t="n">
         <v>1.11</v>
       </c>
-      <c r="AP5" t="n">
-        <v>3.11</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>12.89</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>14.33</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>5.89</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>51.44</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>12.78</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>8.220000000000001</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>4.56</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>19.78</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>10.11</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>1</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>1.17</v>
-      </c>
       <c r="BP5" t="n">
-        <v>5.17</v>
+        <v>5.21</v>
       </c>
       <c r="BQ5" t="n">
-        <v>4.94</v>
+        <v>5.32</v>
       </c>
       <c r="BR5" t="n">
-        <v>88.89</v>
+        <v>89.47</v>
       </c>
       <c r="BS5" t="n">
-        <v>61.11</v>
+        <v>63.16</v>
       </c>
       <c r="BT5" t="n">
-        <v>55.56</v>
+        <v>52.63</v>
       </c>
       <c r="BU5" t="n">
-        <v>44.44</v>
+        <v>42.11</v>
       </c>
       <c r="BV5" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BW5" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BX5" t="n">
-        <v>61.11</v>
+        <v>57.89</v>
       </c>
       <c r="BY5" t="n">
         <v>1.7</v>
@@ -2819,31 +2819,31 @@
         <v>1.67</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.61</v>
+        <v>3.58</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.88</v>
+        <v>3.86</v>
       </c>
       <c r="CC5" t="n">
-        <v>2.84</v>
+        <v>2.77</v>
       </c>
       <c r="CD5" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="CE5" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="CF5" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="CG5" t="n">
         <v>3.08</v>
-      </c>
-      <c r="CE5" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="CF5" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="CG5" t="n">
-        <v>3.1</v>
       </c>
       <c r="CH5" t="n">
         <v>1.47</v>
       </c>
       <c r="CI5" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="CJ5" t="n">
         <v>1.69</v>
@@ -2852,7 +2852,7 @@
         <v>1.54</v>
       </c>
       <c r="CL5" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="CM5" t="n">
         <v>2.33</v>
@@ -2861,13 +2861,13 @@
         <v>1.84</v>
       </c>
       <c r="CO5" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="CP5" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CQ5" t="n">
-        <v>2.84</v>
+        <v>2.87</v>
       </c>
       <c r="CR5" t="n">
         <v>1.38</v>
@@ -2882,16 +2882,16 @@
         <v>1.49</v>
       </c>
       <c r="CV5" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="CW5" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CX5" t="n">
         <v>1.56</v>
       </c>
       <c r="CY5" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CZ5" t="n">
         <v>2.37</v>
@@ -2903,52 +2903,52 @@
         <v>1.25</v>
       </c>
       <c r="DC5" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="DD5" t="n">
-        <v>3.01</v>
+        <v>3.03</v>
       </c>
       <c r="DE5" t="n">
         <v>0.16</v>
       </c>
       <c r="DF5" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="DG5" t="n">
-        <v>3.06</v>
+        <v>3.37</v>
       </c>
       <c r="DH5" t="n">
-        <v>101.06</v>
+        <v>100.26</v>
       </c>
       <c r="DI5" t="n">
         <v>0.16</v>
       </c>
       <c r="DJ5" t="n">
-        <v>3.39</v>
+        <v>3.32</v>
       </c>
       <c r="DK5" t="n">
-        <v>6.5</v>
+        <v>6.79</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="DM5" t="n">
-        <v>58.28</v>
+        <v>60.05</v>
       </c>
       <c r="DN5" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="DO5" t="n">
-        <v>3.44</v>
+        <v>3.42</v>
       </c>
       <c r="DP5" t="n">
         <v>13.16</v>
       </c>
       <c r="DQ5" t="n">
-        <v>14.44</v>
+        <v>14.27</v>
       </c>
       <c r="DR5" t="n">
-        <v>5.44</v>
+        <v>5.53</v>
       </c>
       <c r="DS5" t="n">
         <v>0.16</v>
@@ -2960,28 +2960,28 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>55.22</v>
+        <v>55.84</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DX5" t="n">
-        <v>14.78</v>
+        <v>14.95</v>
       </c>
       <c r="DY5" t="n">
-        <v>9.66</v>
+        <v>10</v>
       </c>
       <c r="DZ5" t="n">
-        <v>5.11</v>
+        <v>4.95</v>
       </c>
       <c r="EA5" t="n">
-        <v>19.28</v>
+        <v>19.11</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="EC5" t="n">
-        <v>3.06</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -3797,61 +3797,61 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D8" t="n">
         <v>9</v>
       </c>
       <c r="E8" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="F8" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="G8" t="n">
-        <v>3.33</v>
+        <v>3.3</v>
       </c>
       <c r="H8" t="n">
-        <v>95.11</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="J8" t="n">
-        <v>3.22</v>
+        <v>3.3</v>
       </c>
       <c r="K8" t="n">
-        <v>5.78</v>
+        <v>5.8</v>
       </c>
       <c r="L8" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="M8" t="n">
-        <v>50.33</v>
+        <v>48.1</v>
       </c>
       <c r="N8" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="O8" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="P8" t="n">
-        <v>14.33</v>
+        <v>14</v>
       </c>
       <c r="Q8" t="n">
-        <v>13.44</v>
+        <v>13.4</v>
       </c>
       <c r="R8" t="n">
-        <v>7.11</v>
+        <v>7.5</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="T8" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
@@ -3863,28 +3863,28 @@
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>50.78</v>
+        <v>49</v>
       </c>
       <c r="Y8" t="n">
         <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>11.89</v>
+        <v>11.7</v>
       </c>
       <c r="AA8" t="n">
-        <v>8.44</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AB8" t="n">
-        <v>3.44</v>
+        <v>3.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>19.11</v>
+        <v>19.4</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AE8" t="n">
-        <v>3.22</v>
+        <v>3.3</v>
       </c>
       <c r="AF8" t="n">
         <v>0.11</v>
@@ -3968,70 +3968,70 @@
         <v>2.67</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="BH8" t="n">
-        <v>10.17</v>
+        <v>10.58</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.39</v>
+        <v>0.37</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.63</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.89</v>
+        <v>0.84</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.61</v>
+        <v>4.68</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.56</v>
+        <v>5.89</v>
       </c>
       <c r="BR8" t="n">
-        <v>77.78</v>
+        <v>78.95</v>
       </c>
       <c r="BS8" t="n">
-        <v>50</v>
+        <v>52.63</v>
       </c>
       <c r="BT8" t="n">
-        <v>44.44</v>
+        <v>42.11</v>
       </c>
       <c r="BU8" t="n">
-        <v>16.67</v>
+        <v>15.79</v>
       </c>
       <c r="BV8" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BW8" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BX8" t="n">
-        <v>44.44</v>
+        <v>42.11</v>
       </c>
       <c r="BY8" t="n">
-        <v>2.18</v>
+        <v>2.33</v>
       </c>
       <c r="BZ8" t="n">
-        <v>2.37</v>
+        <v>2.54</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.1</v>
+        <v>3.11</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.27</v>
+        <v>3.28</v>
       </c>
       <c r="CC8" t="n">
         <v>3.7</v>
@@ -4040,13 +4040,13 @@
         <v>4.12</v>
       </c>
       <c r="CE8" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CF8" t="n">
-        <v>3.19</v>
+        <v>3.17</v>
       </c>
       <c r="CG8" t="n">
-        <v>2.53</v>
+        <v>2.54</v>
       </c>
       <c r="CH8" t="n">
         <v>1.32</v>
@@ -4055,16 +4055,16 @@
         <v>1.78</v>
       </c>
       <c r="CJ8" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CL8" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="CN8" t="n">
         <v>1.72</v>
@@ -4073,10 +4073,10 @@
         <v>1.39</v>
       </c>
       <c r="CP8" t="n">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="CQ8" t="n">
-        <v>4.21</v>
+        <v>4.17</v>
       </c>
       <c r="CR8" t="n">
         <v>1.51</v>
@@ -4091,73 +4091,73 @@
         <v>1.37</v>
       </c>
       <c r="CV8" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="CW8" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CX8" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CY8" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="CZ8" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="DA8" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="DB8" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="DC8" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="DD8" t="n">
-        <v>4.42</v>
+        <v>4.36</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DF8" t="n">
         <v>2.16</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="DH8" t="n">
-        <v>89.56</v>
+        <v>89.05</v>
       </c>
       <c r="DI8" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="DK8" t="n">
-        <v>4.94</v>
+        <v>5</v>
       </c>
       <c r="DL8" t="n">
         <v>0.16</v>
       </c>
       <c r="DM8" t="n">
-        <v>39.61</v>
+        <v>39</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.78</v>
+        <v>0.84</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="DP8" t="n">
-        <v>15.16</v>
+        <v>14.95</v>
       </c>
       <c r="DQ8" t="n">
-        <v>13.38</v>
+        <v>13.37</v>
       </c>
       <c r="DR8" t="n">
-        <v>8.77</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="DS8" t="n">
         <v>0</v>
@@ -4169,7 +4169,7 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>46.06</v>
+        <v>45.37</v>
       </c>
       <c r="DW8" t="n">
         <v>0</v>
@@ -4178,19 +4178,19 @@
         <v>10</v>
       </c>
       <c r="DY8" t="n">
-        <v>6.83</v>
+        <v>6.79</v>
       </c>
       <c r="DZ8" t="n">
-        <v>3.16</v>
+        <v>3.21</v>
       </c>
       <c r="EA8" t="n">
-        <v>19.17</v>
+        <v>19.31</v>
       </c>
       <c r="EB8" t="n">
         <v>1.14</v>
       </c>
       <c r="EC8" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -4347,7 +4347,7 @@
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>53.8</v>
+        <v>53.7</v>
       </c>
       <c r="AZ9" t="n">
         <v>0.1</v>
@@ -4362,7 +4362,7 @@
         <v>4.6</v>
       </c>
       <c r="BD9" t="n">
-        <v>22.7</v>
+        <v>22.8</v>
       </c>
       <c r="BE9" t="n">
         <v>1.46</v>
@@ -4572,7 +4572,7 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>56.53</v>
+        <v>56.48</v>
       </c>
       <c r="DW9" t="n">
         <v>0.16</v>
@@ -4587,7 +4587,7 @@
         <v>4.69</v>
       </c>
       <c r="EA9" t="n">
-        <v>22.26</v>
+        <v>22.32</v>
       </c>
       <c r="EB9" t="n">
         <v>1.6</v>
@@ -5409,61 +5409,61 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D12" t="n">
         <v>9</v>
       </c>
       <c r="E12" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="F12" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="G12" t="n">
-        <v>3.11</v>
+        <v>3.1</v>
       </c>
       <c r="H12" t="n">
-        <v>92.56</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>1.89</v>
+        <v>2.1</v>
       </c>
       <c r="K12" t="n">
-        <v>5.89</v>
+        <v>5.9</v>
       </c>
       <c r="L12" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="M12" t="n">
-        <v>44.89</v>
+        <v>46.5</v>
       </c>
       <c r="N12" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="O12" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="P12" t="n">
-        <v>12.22</v>
+        <v>12.2</v>
       </c>
       <c r="Q12" t="n">
-        <v>15.78</v>
+        <v>15.4</v>
       </c>
       <c r="R12" t="n">
-        <v>7.33</v>
+        <v>7.6</v>
       </c>
       <c r="S12" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T12" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="U12" t="n">
         <v>0</v>
@@ -5475,28 +5475,28 @@
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>51.89</v>
+        <v>52.4</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="Z12" t="n">
-        <v>14.78</v>
+        <v>15.1</v>
       </c>
       <c r="AA12" t="n">
-        <v>11</v>
+        <v>11.2</v>
       </c>
       <c r="AB12" t="n">
-        <v>3.78</v>
+        <v>3.9</v>
       </c>
       <c r="AC12" t="n">
-        <v>22.78</v>
+        <v>22.6</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.67</v>
+        <v>1.9</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>
@@ -5580,64 +5580,64 @@
         <v>2.56</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.39</v>
+        <v>2.37</v>
       </c>
       <c r="BH12" t="n">
-        <v>8.890000000000001</v>
+        <v>9</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.39</v>
+        <v>2.37</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.61</v>
+        <v>0.63</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="BP12" t="n">
-        <v>3.83</v>
+        <v>3.84</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.06</v>
+        <v>5.16</v>
       </c>
       <c r="BR12" t="n">
-        <v>83.33</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="BS12" t="n">
-        <v>66.67</v>
+        <v>68.42</v>
       </c>
       <c r="BT12" t="n">
-        <v>44.44</v>
+        <v>42.11</v>
       </c>
       <c r="BU12" t="n">
-        <v>27.78</v>
+        <v>26.32</v>
       </c>
       <c r="BV12" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BW12" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BX12" t="n">
-        <v>55.56</v>
+        <v>57.89</v>
       </c>
       <c r="BY12" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="BZ12" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="CA12" t="n">
         <v>3.19</v>
@@ -5652,10 +5652,10 @@
         <v>3.87</v>
       </c>
       <c r="CE12" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CF12" t="n">
-        <v>3.17</v>
+        <v>3.15</v>
       </c>
       <c r="CG12" t="n">
         <v>2.62</v>
@@ -5664,31 +5664,31 @@
         <v>1.32</v>
       </c>
       <c r="CI12" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CJ12" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CL12" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="CN12" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CO12" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CP12" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="CQ12" t="n">
-        <v>3.98</v>
+        <v>3.95</v>
       </c>
       <c r="CR12" t="n">
         <v>1.5</v>
@@ -5697,7 +5697,7 @@
         <v>3.26</v>
       </c>
       <c r="CT12" t="n">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="CU12" t="n">
         <v>1.35</v>
@@ -5709,16 +5709,16 @@
         <v>1.97</v>
       </c>
       <c r="CX12" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CY12" t="n">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="CZ12" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="DA12" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="DB12" t="n">
         <v>1.41</v>
@@ -5727,49 +5727,49 @@
         <v>2.31</v>
       </c>
       <c r="DD12" t="n">
-        <v>4.29</v>
+        <v>4.27</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.11</v>
+        <v>0.16</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.56</v>
+        <v>1.63</v>
       </c>
       <c r="DG12" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="DH12" t="n">
-        <v>91.56</v>
+        <v>91.27</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.39</v>
+        <v>2.47</v>
       </c>
       <c r="DK12" t="n">
-        <v>4.11</v>
+        <v>4.21</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.38</v>
+        <v>0.42</v>
       </c>
       <c r="DM12" t="n">
-        <v>40.78</v>
+        <v>41.84</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="DO12" t="n">
-        <v>2.11</v>
+        <v>2.16</v>
       </c>
       <c r="DP12" t="n">
-        <v>13.27</v>
+        <v>13.21</v>
       </c>
       <c r="DQ12" t="n">
-        <v>15.17</v>
+        <v>15</v>
       </c>
       <c r="DR12" t="n">
-        <v>7.89</v>
+        <v>8</v>
       </c>
       <c r="DS12" t="n">
         <v>0</v>
@@ -5781,28 +5781,28 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>48.84</v>
+        <v>49.26</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DX12" t="n">
-        <v>12.17</v>
+        <v>12.48</v>
       </c>
       <c r="DY12" t="n">
-        <v>8.66</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="DZ12" t="n">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="EA12" t="n">
-        <v>22</v>
+        <v>21.95</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.12</v>
+        <v>2.21</v>
       </c>
     </row>
     <row r="13">
@@ -6281,7 +6281,7 @@
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>46.89</v>
+        <v>47</v>
       </c>
       <c r="Y14" t="n">
         <v>0.11</v>
@@ -6587,7 +6587,7 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>41.9</v>
+        <v>41.95</v>
       </c>
       <c r="DW14" t="n">
         <v>0.16</v>
@@ -8230,13 +8230,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C19" t="n">
         <v>9</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -8320,139 +8320,139 @@
         <v>2.89</v>
       </c>
       <c r="AF19" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AH19" t="n">
-        <v>3.33</v>
+        <v>3.3</v>
       </c>
       <c r="AI19" t="n">
-        <v>89.67</v>
+        <v>89.8</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AK19" t="n">
         <v>3</v>
       </c>
       <c r="AL19" t="n">
-        <v>5.44</v>
+        <v>5.6</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.22</v>
+        <v>0.5</v>
       </c>
       <c r="AN19" t="n">
-        <v>42.22</v>
+        <v>42.5</v>
       </c>
       <c r="AO19" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AP19" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AQ19" t="n">
-        <v>13.22</v>
+        <v>13.4</v>
       </c>
       <c r="AR19" t="n">
-        <v>15.78</v>
+        <v>15.5</v>
       </c>
       <c r="AS19" t="n">
-        <v>6.56</v>
+        <v>6.7</v>
       </c>
       <c r="AT19" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AU19" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AV19" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AW19" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AX19" t="n">
         <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>49.22</v>
+        <v>50.2</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="BA19" t="n">
-        <v>13</v>
+        <v>13.3</v>
       </c>
       <c r="BB19" t="n">
-        <v>9.67</v>
+        <v>9.9</v>
       </c>
       <c r="BC19" t="n">
-        <v>3.33</v>
+        <v>3.4</v>
       </c>
       <c r="BD19" t="n">
-        <v>17.78</v>
+        <v>18.2</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="BF19" t="n">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="BH19" t="n">
-        <v>10.17</v>
+        <v>10.26</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.39</v>
+        <v>0.42</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.39</v>
+        <v>0.37</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.72</v>
+        <v>0.68</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.95</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="BO19" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="BP19" t="n">
-        <v>5.22</v>
+        <v>5.21</v>
       </c>
       <c r="BQ19" t="n">
-        <v>4.89</v>
+        <v>5</v>
       </c>
       <c r="BR19" t="n">
-        <v>94.44</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BS19" t="n">
-        <v>61.11</v>
+        <v>63.16</v>
       </c>
       <c r="BT19" t="n">
-        <v>38.89</v>
+        <v>36.84</v>
       </c>
       <c r="BU19" t="n">
-        <v>27.78</v>
+        <v>26.32</v>
       </c>
       <c r="BV19" t="n">
-        <v>16.67</v>
+        <v>15.79</v>
       </c>
       <c r="BW19" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BX19" t="n">
-        <v>50</v>
+        <v>52.63</v>
       </c>
       <c r="BY19" t="n">
         <v>2.3</v>
@@ -8461,73 +8461,73 @@
         <v>2.43</v>
       </c>
       <c r="CA19" t="n">
-        <v>3.17</v>
+        <v>3.16</v>
       </c>
       <c r="CB19" t="n">
-        <v>3.3</v>
+        <v>3.29</v>
       </c>
       <c r="CC19" t="n">
-        <v>3.75</v>
+        <v>3.76</v>
       </c>
       <c r="CD19" t="n">
         <v>4.39</v>
       </c>
       <c r="CE19" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="CF19" t="n">
-        <v>3.14</v>
+        <v>3.17</v>
       </c>
       <c r="CG19" t="n">
-        <v>2.61</v>
+        <v>2.59</v>
       </c>
       <c r="CH19" t="n">
         <v>1.33</v>
       </c>
       <c r="CI19" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CJ19" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CK19" t="n">
         <v>1.59</v>
       </c>
       <c r="CL19" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="CM19" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="CN19" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CO19" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CP19" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="CQ19" t="n">
-        <v>4.06</v>
+        <v>4.17</v>
       </c>
       <c r="CR19" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="CS19" t="n">
         <v>3.22</v>
       </c>
       <c r="CT19" t="n">
-        <v>2.73</v>
+        <v>2.7</v>
       </c>
       <c r="CU19" t="n">
         <v>1.37</v>
       </c>
       <c r="CV19" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CW19" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="CX19" t="n">
         <v>1.6</v>
@@ -8542,55 +8542,55 @@
         <v>1.81</v>
       </c>
       <c r="DB19" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="DC19" t="n">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="DD19" t="n">
-        <v>4.1</v>
+        <v>4.21</v>
       </c>
       <c r="DE19" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="DG19" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="DH19" t="n">
-        <v>92.17</v>
+        <v>92.11</v>
       </c>
       <c r="DI19" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DJ19" t="n">
-        <v>3.34</v>
+        <v>3.32</v>
       </c>
       <c r="DK19" t="n">
-        <v>4.94</v>
+        <v>5.05</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.68</v>
       </c>
       <c r="DM19" t="n">
-        <v>42.78</v>
+        <v>42.89</v>
       </c>
       <c r="DN19" t="n">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="DO19" t="n">
-        <v>2.39</v>
+        <v>2.47</v>
       </c>
       <c r="DP19" t="n">
-        <v>13.06</v>
+        <v>13.16</v>
       </c>
       <c r="DQ19" t="n">
-        <v>15.67</v>
+        <v>15.53</v>
       </c>
       <c r="DR19" t="n">
-        <v>6.89</v>
+        <v>6.95</v>
       </c>
       <c r="DS19" t="n">
         <v>0.11</v>
@@ -8602,28 +8602,28 @@
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>50.72</v>
+        <v>51.16</v>
       </c>
       <c r="DW19" t="n">
-        <v>0.39</v>
+        <v>0.37</v>
       </c>
       <c r="DX19" t="n">
-        <v>12.28</v>
+        <v>12.48</v>
       </c>
       <c r="DY19" t="n">
-        <v>8.84</v>
+        <v>9</v>
       </c>
       <c r="DZ19" t="n">
-        <v>3.44</v>
+        <v>3.48</v>
       </c>
       <c r="EA19" t="n">
-        <v>20.39</v>
+        <v>20.47</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="EC19" t="n">
-        <v>2.78</v>
+        <v>2.79</v>
       </c>
     </row>
     <row r="20">

--- a/data/teams/leagues/Averages_Spain_Segunda_División_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Spain_Segunda_División_2025-2026.xlsx
@@ -1782,94 +1782,94 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D3" t="n">
         <v>10</v>
       </c>
       <c r="E3" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="F3" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="G3" t="n">
-        <v>4.11</v>
+        <v>3.9</v>
       </c>
       <c r="H3" t="n">
-        <v>103.67</v>
+        <v>101.6</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>2.56</v>
+        <v>2.7</v>
       </c>
       <c r="K3" t="n">
-        <v>8.109999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="L3" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="M3" t="n">
-        <v>58.11</v>
+        <v>54.9</v>
       </c>
       <c r="N3" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="O3" t="n">
-        <v>3.89</v>
+        <v>3.8</v>
       </c>
       <c r="P3" t="n">
-        <v>14.22</v>
+        <v>14.2</v>
       </c>
       <c r="Q3" t="n">
-        <v>10.78</v>
+        <v>11</v>
       </c>
       <c r="R3" t="n">
-        <v>7.22</v>
+        <v>7.3</v>
       </c>
       <c r="S3" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="T3" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="U3" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="V3" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>57.56</v>
+        <v>56.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="Z3" t="n">
-        <v>18.67</v>
+        <v>18</v>
       </c>
       <c r="AA3" t="n">
-        <v>11.22</v>
+        <v>10.6</v>
       </c>
       <c r="AB3" t="n">
-        <v>7.44</v>
+        <v>7.4</v>
       </c>
       <c r="AC3" t="n">
-        <v>18.33</v>
+        <v>18.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="AF3" t="n">
         <v>0</v>
@@ -1953,64 +1953,64 @@
         <v>3.4</v>
       </c>
       <c r="BG3" t="n">
-        <v>3.21</v>
+        <v>3.3</v>
       </c>
       <c r="BH3" t="n">
-        <v>9.26</v>
+        <v>9.4</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.21</v>
+        <v>3.3</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.68</v>
+        <v>0.7</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="BL3" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="BM3" t="n">
         <v>1</v>
       </c>
       <c r="BN3" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="BP3" t="n">
-        <v>3.89</v>
+        <v>4.1</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5</v>
+        <v>4.95</v>
       </c>
       <c r="BR3" t="n">
-        <v>94.73999999999999</v>
+        <v>95</v>
       </c>
       <c r="BS3" t="n">
-        <v>78.95</v>
+        <v>80</v>
       </c>
       <c r="BT3" t="n">
-        <v>68.42</v>
+        <v>70</v>
       </c>
       <c r="BU3" t="n">
-        <v>36.84</v>
+        <v>40</v>
       </c>
       <c r="BV3" t="n">
-        <v>21.05</v>
+        <v>25</v>
       </c>
       <c r="BW3" t="n">
-        <v>10.53</v>
+        <v>10</v>
       </c>
       <c r="BX3" t="n">
-        <v>68.42</v>
+        <v>70</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="BZ3" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="CA3" t="n">
         <v>3.43</v>
@@ -2028,16 +2028,16 @@
         <v>1.37</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.72</v>
+        <v>2.71</v>
       </c>
       <c r="CG3" t="n">
-        <v>2.92</v>
+        <v>2.91</v>
       </c>
       <c r="CH3" t="n">
         <v>1.43</v>
       </c>
       <c r="CI3" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="CJ3" t="n">
         <v>1.76</v>
@@ -2052,13 +2052,13 @@
         <v>2.37</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CO3" t="n">
         <v>1.26</v>
       </c>
       <c r="CP3" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CQ3" t="n">
         <v>3.16</v>
@@ -2079,13 +2079,13 @@
         <v>2.18</v>
       </c>
       <c r="CW3" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CX3" t="n">
         <v>1.55</v>
       </c>
       <c r="CY3" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CZ3" t="n">
         <v>2.39</v>
@@ -2100,40 +2100,40 @@
         <v>1.93</v>
       </c>
       <c r="DD3" t="n">
-        <v>3.3</v>
+        <v>3.31</v>
       </c>
       <c r="DE3" t="n">
         <v>0.05</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="DG3" t="n">
-        <v>2.68</v>
+        <v>2.65</v>
       </c>
       <c r="DH3" t="n">
-        <v>94.37</v>
+        <v>93.8</v>
       </c>
       <c r="DI3" t="n">
         <v>0</v>
       </c>
       <c r="DJ3" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="DK3" t="n">
-        <v>5.37</v>
+        <v>5.35</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.26</v>
+        <v>0.3</v>
       </c>
       <c r="DM3" t="n">
-        <v>47.68</v>
+        <v>46.6</v>
       </c>
       <c r="DN3" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="DO3" t="n">
-        <v>2.42</v>
+        <v>2.45</v>
       </c>
       <c r="DP3" t="n">
         <v>14</v>
@@ -2142,40 +2142,40 @@
         <v>12.9</v>
       </c>
       <c r="DR3" t="n">
-        <v>7.53</v>
+        <v>7.55</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>54.69</v>
+        <v>54.3</v>
       </c>
       <c r="DW3" t="n">
         <v>0.1</v>
       </c>
       <c r="DX3" t="n">
-        <v>15.79</v>
+        <v>15.6</v>
       </c>
       <c r="DY3" t="n">
-        <v>10</v>
+        <v>9.75</v>
       </c>
       <c r="DZ3" t="n">
-        <v>5.79</v>
+        <v>5.85</v>
       </c>
       <c r="EA3" t="n">
-        <v>20.16</v>
+        <v>20.15</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.89</v>
+        <v>2.95</v>
       </c>
     </row>
     <row r="4">
@@ -2185,13 +2185,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C4" t="n">
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E4" t="n">
         <v>0.1</v>
@@ -2275,58 +2275,58 @@
         <v>2.9</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AI4" t="n">
-        <v>84.89</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="AJ4" t="n">
         <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="AL4" t="n">
-        <v>3.89</v>
+        <v>4.1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AN4" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AO4" t="n">
         <v>1</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ4" t="n">
-        <v>14.11</v>
+        <v>14</v>
       </c>
       <c r="AR4" t="n">
-        <v>15.11</v>
+        <v>15.5</v>
       </c>
       <c r="AS4" t="n">
-        <v>9.109999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AX4" t="n">
         <v>0</v>
@@ -2338,76 +2338,76 @@
         <v>0</v>
       </c>
       <c r="BA4" t="n">
-        <v>8.67</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB4" t="n">
-        <v>5.89</v>
+        <v>6.3</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.78</v>
+        <v>2.9</v>
       </c>
       <c r="BD4" t="n">
-        <v>21.67</v>
+        <v>21.5</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="BF4" t="n">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="BH4" t="n">
-        <v>8.42</v>
+        <v>8.6</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.58</v>
+        <v>0.6</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.47</v>
+        <v>0.45</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="BO4" t="n">
         <v>1.05</v>
       </c>
       <c r="BP4" t="n">
-        <v>3.84</v>
+        <v>4.05</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.58</v>
+        <v>4.55</v>
       </c>
       <c r="BR4" t="n">
-        <v>84.20999999999999</v>
+        <v>85</v>
       </c>
       <c r="BS4" t="n">
-        <v>63.16</v>
+        <v>65</v>
       </c>
       <c r="BT4" t="n">
-        <v>42.11</v>
+        <v>40</v>
       </c>
       <c r="BU4" t="n">
-        <v>15.79</v>
+        <v>15</v>
       </c>
       <c r="BV4" t="n">
-        <v>10.53</v>
+        <v>10</v>
       </c>
       <c r="BW4" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BX4" t="n">
-        <v>52.63</v>
+        <v>50</v>
       </c>
       <c r="BY4" t="n">
         <v>2.23</v>
@@ -2422,16 +2422,16 @@
         <v>3.11</v>
       </c>
       <c r="CC4" t="n">
-        <v>3.67</v>
+        <v>3.71</v>
       </c>
       <c r="CD4" t="n">
-        <v>4.04</v>
+        <v>4.09</v>
       </c>
       <c r="CE4" t="n">
         <v>1.55</v>
       </c>
       <c r="CF4" t="n">
-        <v>3.46</v>
+        <v>3.45</v>
       </c>
       <c r="CG4" t="n">
         <v>2.36</v>
@@ -2443,34 +2443,34 @@
         <v>1.67</v>
       </c>
       <c r="CJ4" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CL4" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="CM4" t="n">
         <v>2.06</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CO4" t="n">
         <v>1.49</v>
       </c>
       <c r="CP4" t="n">
-        <v>2.51</v>
+        <v>2.52</v>
       </c>
       <c r="CQ4" t="n">
-        <v>4.85</v>
+        <v>4.84</v>
       </c>
       <c r="CR4" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CS4" t="n">
-        <v>3.38</v>
+        <v>3.4</v>
       </c>
       <c r="CT4" t="n">
         <v>2.43</v>
@@ -2485,16 +2485,16 @@
         <v>2.24</v>
       </c>
       <c r="CX4" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CY4" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="CZ4" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="DA4" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="DB4" t="n">
         <v>1.54</v>
@@ -2503,82 +2503,82 @@
         <v>2.7</v>
       </c>
       <c r="DD4" t="n">
-        <v>5.42</v>
+        <v>5.41</v>
       </c>
       <c r="DE4" t="n">
         <v>0.1</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.52</v>
+        <v>1.45</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="DH4" t="n">
-        <v>89.37</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="DI4" t="n">
         <v>0</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.68</v>
+        <v>2.6</v>
       </c>
       <c r="DK4" t="n">
-        <v>3.95</v>
+        <v>4.05</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DM4" t="n">
-        <v>42.32</v>
+        <v>41.6</v>
       </c>
       <c r="DN4" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="DO4" t="n">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="DP4" t="n">
-        <v>13.95</v>
+        <v>13.9</v>
       </c>
       <c r="DQ4" t="n">
-        <v>14.79</v>
+        <v>15</v>
       </c>
       <c r="DR4" t="n">
-        <v>9.050000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>47.21</v>
+        <v>47.1</v>
       </c>
       <c r="DW4" t="n">
         <v>0</v>
       </c>
       <c r="DX4" t="n">
-        <v>9.630000000000001</v>
+        <v>9.85</v>
       </c>
       <c r="DY4" t="n">
-        <v>6.74</v>
+        <v>6.9</v>
       </c>
       <c r="DZ4" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="EA4" t="n">
-        <v>23.79</v>
+        <v>23.6</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.68</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="5">
@@ -2588,94 +2588,94 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D5" t="n">
         <v>10</v>
       </c>
       <c r="E5" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="F5" t="n">
-        <v>2.67</v>
+        <v>2.6</v>
       </c>
       <c r="G5" t="n">
-        <v>3.56</v>
+        <v>3.3</v>
       </c>
       <c r="H5" t="n">
-        <v>108.67</v>
+        <v>104.5</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>3.89</v>
+        <v>3.7</v>
       </c>
       <c r="K5" t="n">
-        <v>7.33</v>
+        <v>6.7</v>
       </c>
       <c r="L5" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="M5" t="n">
-        <v>63.33</v>
+        <v>59</v>
       </c>
       <c r="N5" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="O5" t="n">
-        <v>3.78</v>
+        <v>3.4</v>
       </c>
       <c r="P5" t="n">
-        <v>13.44</v>
+        <v>13.7</v>
       </c>
       <c r="Q5" t="n">
-        <v>14.56</v>
+        <v>14.6</v>
       </c>
       <c r="R5" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="S5" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="T5" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="U5" t="n">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="V5" t="n">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>59</v>
+        <v>57.7</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="Z5" t="n">
-        <v>16.78</v>
+        <v>16.4</v>
       </c>
       <c r="AA5" t="n">
-        <v>11.11</v>
+        <v>10.5</v>
       </c>
       <c r="AB5" t="n">
-        <v>5.67</v>
+        <v>5.9</v>
       </c>
       <c r="AC5" t="n">
-        <v>18.78</v>
+        <v>18.3</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="AE5" t="n">
-        <v>3.44</v>
+        <v>3.2</v>
       </c>
       <c r="AF5" t="n">
         <v>0.1</v>
@@ -2759,70 +2759,70 @@
         <v>2.6</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.84</v>
+        <v>2.95</v>
       </c>
       <c r="BH5" t="n">
-        <v>10.53</v>
+        <v>10.2</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.84</v>
+        <v>2.95</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.47</v>
+        <v>0.6</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.63</v>
+        <v>0.6</v>
       </c>
       <c r="BL5" t="n">
         <v>1.05</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.68</v>
+        <v>0.7</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="BP5" t="n">
-        <v>5.21</v>
+        <v>5</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.32</v>
+        <v>5.2</v>
       </c>
       <c r="BR5" t="n">
-        <v>89.47</v>
+        <v>90</v>
       </c>
       <c r="BS5" t="n">
-        <v>63.16</v>
+        <v>65</v>
       </c>
       <c r="BT5" t="n">
-        <v>52.63</v>
+        <v>55</v>
       </c>
       <c r="BU5" t="n">
-        <v>42.11</v>
+        <v>45</v>
       </c>
       <c r="BV5" t="n">
-        <v>10.53</v>
+        <v>15</v>
       </c>
       <c r="BW5" t="n">
-        <v>10.53</v>
+        <v>10</v>
       </c>
       <c r="BX5" t="n">
-        <v>57.89</v>
+        <v>60</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="BZ5" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.58</v>
+        <v>3.59</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.86</v>
+        <v>3.88</v>
       </c>
       <c r="CC5" t="n">
         <v>2.77</v>
@@ -2834,154 +2834,154 @@
         <v>1.34</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.59</v>
+        <v>2.61</v>
       </c>
       <c r="CG5" t="n">
-        <v>3.08</v>
+        <v>3.06</v>
       </c>
       <c r="CH5" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CI5" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CL5" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CO5" t="n">
         <v>1.22</v>
       </c>
       <c r="CP5" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CQ5" t="n">
-        <v>2.87</v>
+        <v>2.89</v>
       </c>
       <c r="CR5" t="n">
         <v>1.38</v>
       </c>
       <c r="CS5" t="n">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="CT5" t="n">
-        <v>3.17</v>
+        <v>3.16</v>
       </c>
       <c r="CU5" t="n">
         <v>1.49</v>
       </c>
       <c r="CV5" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="CW5" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="CX5" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="CY5" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CZ5" t="n">
-        <v>2.37</v>
+        <v>2.39</v>
       </c>
       <c r="DA5" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="DB5" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="DC5" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="DD5" t="n">
-        <v>3.03</v>
+        <v>3.06</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.16</v>
+        <v>0.2</v>
       </c>
       <c r="DF5" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="DG5" t="n">
-        <v>3.37</v>
+        <v>3.25</v>
       </c>
       <c r="DH5" t="n">
-        <v>100.26</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DJ5" t="n">
-        <v>3.32</v>
+        <v>3.25</v>
       </c>
       <c r="DK5" t="n">
-        <v>6.79</v>
+        <v>6.5</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.58</v>
+        <v>0.55</v>
       </c>
       <c r="DM5" t="n">
-        <v>60.05</v>
+        <v>58.05</v>
       </c>
       <c r="DN5" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="DO5" t="n">
-        <v>3.42</v>
+        <v>3.25</v>
       </c>
       <c r="DP5" t="n">
-        <v>13.16</v>
+        <v>13.3</v>
       </c>
       <c r="DQ5" t="n">
-        <v>14.27</v>
+        <v>14.3</v>
       </c>
       <c r="DR5" t="n">
-        <v>5.53</v>
+        <v>5.45</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.16</v>
+        <v>0.2</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.16</v>
+        <v>0.2</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>55.84</v>
+        <v>55.35</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.21</v>
+        <v>0.25</v>
       </c>
       <c r="DX5" t="n">
-        <v>14.95</v>
+        <v>14.85</v>
       </c>
       <c r="DY5" t="n">
-        <v>10</v>
+        <v>9.75</v>
       </c>
       <c r="DZ5" t="n">
-        <v>4.95</v>
+        <v>5.1</v>
       </c>
       <c r="EA5" t="n">
-        <v>19.11</v>
+        <v>18.85</v>
       </c>
       <c r="EB5" t="n">
         <v>1.72</v>
       </c>
       <c r="EC5" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="6">
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D7" t="n">
         <v>10</v>
@@ -3406,82 +3406,82 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="G7" t="n">
-        <v>3.33</v>
+        <v>3.1</v>
       </c>
       <c r="H7" t="n">
-        <v>90.11</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="K7" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M7" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="P7" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="R7" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>53.1</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AD7" t="n">
         <v>1.22</v>
       </c>
-      <c r="K7" t="n">
-        <v>4.78</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="M7" t="n">
-        <v>41.11</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="P7" t="n">
-        <v>12.33</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>13.11</v>
-      </c>
-      <c r="R7" t="n">
-        <v>7.89</v>
-      </c>
-      <c r="S7" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" t="n">
-        <v>0</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" t="n">
-        <v>52.56</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>11.11</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>7.67</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>19.11</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.24</v>
-      </c>
       <c r="AE7" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AF7" t="n">
         <v>0.2</v>
@@ -3565,67 +3565,67 @@
         <v>1.8</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="BH7" t="n">
-        <v>9.050000000000001</v>
+        <v>9</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.74</v>
+        <v>0.7</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.74</v>
+        <v>0.7</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.58</v>
+        <v>0.6</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="BP7" t="n">
-        <v>3.89</v>
+        <v>3.85</v>
       </c>
       <c r="BQ7" t="n">
-        <v>5.16</v>
+        <v>5.15</v>
       </c>
       <c r="BR7" t="n">
-        <v>89.47</v>
+        <v>90</v>
       </c>
       <c r="BS7" t="n">
-        <v>52.63</v>
+        <v>55</v>
       </c>
       <c r="BT7" t="n">
-        <v>47.37</v>
+        <v>45</v>
       </c>
       <c r="BU7" t="n">
-        <v>31.58</v>
+        <v>30</v>
       </c>
       <c r="BV7" t="n">
-        <v>21.05</v>
+        <v>20</v>
       </c>
       <c r="BW7" t="n">
-        <v>10.53</v>
+        <v>10</v>
       </c>
       <c r="BX7" t="n">
-        <v>31.58</v>
+        <v>35</v>
       </c>
       <c r="BY7" t="n">
-        <v>2.62</v>
+        <v>2.55</v>
       </c>
       <c r="BZ7" t="n">
-        <v>2.74</v>
+        <v>2.65</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.37</v>
+        <v>3.36</v>
       </c>
       <c r="CB7" t="n">
         <v>3.51</v>
@@ -3643,13 +3643,13 @@
         <v>2.96</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CI7" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CJ7" t="n">
         <v>1.92</v>
@@ -3658,22 +3658,22 @@
         <v>1.58</v>
       </c>
       <c r="CL7" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="CN7" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CO7" t="n">
         <v>1.32</v>
       </c>
       <c r="CP7" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="CQ7" t="n">
-        <v>3.68</v>
+        <v>3.69</v>
       </c>
       <c r="CR7" t="n">
         <v>1.45</v>
@@ -3694,13 +3694,13 @@
         <v>1.95</v>
       </c>
       <c r="CX7" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CY7" t="n">
         <v>2.04</v>
       </c>
       <c r="CZ7" t="n">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="DA7" t="n">
         <v>1.78</v>
@@ -3709,85 +3709,85 @@
         <v>1.37</v>
       </c>
       <c r="DC7" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="DD7" t="n">
-        <v>3.91</v>
+        <v>3.89</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="DG7" t="n">
-        <v>2.84</v>
+        <v>2.75</v>
       </c>
       <c r="DH7" t="n">
-        <v>82.53</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DJ7" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="DK7" t="n">
-        <v>4.11</v>
+        <v>3.95</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="DM7" t="n">
-        <v>36.63</v>
+        <v>37.05</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.32</v>
+        <v>0.4</v>
       </c>
       <c r="DO7" t="n">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="DP7" t="n">
-        <v>12.37</v>
+        <v>12.05</v>
       </c>
       <c r="DQ7" t="n">
-        <v>12.53</v>
+        <v>12.75</v>
       </c>
       <c r="DR7" t="n">
-        <v>8.949999999999999</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>48.05</v>
+        <v>48.55</v>
       </c>
       <c r="DW7" t="n">
         <v>0.1</v>
       </c>
       <c r="DX7" t="n">
-        <v>11.63</v>
+        <v>11.5</v>
       </c>
       <c r="DY7" t="n">
-        <v>7.48</v>
+        <v>7.5</v>
       </c>
       <c r="DZ7" t="n">
-        <v>4.16</v>
+        <v>4</v>
       </c>
       <c r="EA7" t="n">
-        <v>18.47</v>
+        <v>18.7</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="EC7" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="8">
@@ -4200,94 +4200,94 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D9" t="n">
         <v>10</v>
       </c>
       <c r="E9" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="F9" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="G9" t="n">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="H9" t="n">
-        <v>102.56</v>
+        <v>101.8</v>
       </c>
       <c r="I9" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="J9" t="n">
-        <v>3.22</v>
+        <v>2.9</v>
       </c>
       <c r="K9" t="n">
-        <v>5.11</v>
+        <v>5.2</v>
       </c>
       <c r="L9" t="n">
-        <v>0.33</v>
+        <v>0.6</v>
       </c>
       <c r="M9" t="n">
-        <v>54.89</v>
+        <v>54.6</v>
       </c>
       <c r="N9" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="O9" t="n">
-        <v>2.44</v>
+        <v>2.7</v>
       </c>
       <c r="P9" t="n">
-        <v>15.78</v>
+        <v>16.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>15.22</v>
+        <v>15</v>
       </c>
       <c r="R9" t="n">
         <v>5</v>
       </c>
       <c r="S9" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="T9" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="U9" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="V9" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>59.56</v>
+        <v>59.1</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="Z9" t="n">
-        <v>16.33</v>
+        <v>16.1</v>
       </c>
       <c r="AA9" t="n">
-        <v>11.56</v>
+        <v>11.2</v>
       </c>
       <c r="AB9" t="n">
-        <v>4.78</v>
+        <v>4.9</v>
       </c>
       <c r="AC9" t="n">
-        <v>21.78</v>
+        <v>21.4</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AE9" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="AF9" t="n">
         <v>0.3</v>
@@ -4371,49 +4371,49 @@
         <v>3</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="BH9" t="n">
-        <v>9.529999999999999</v>
+        <v>9.65</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.68</v>
+        <v>0.7</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.84</v>
+        <v>0.8</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.63</v>
+        <v>4.8</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.89</v>
+        <v>4.85</v>
       </c>
       <c r="BR9" t="n">
-        <v>84.20999999999999</v>
+        <v>85</v>
       </c>
       <c r="BS9" t="n">
-        <v>73.68000000000001</v>
+        <v>75</v>
       </c>
       <c r="BT9" t="n">
-        <v>52.63</v>
+        <v>50</v>
       </c>
       <c r="BU9" t="n">
-        <v>31.58</v>
+        <v>30</v>
       </c>
       <c r="BV9" t="n">
         <v>0</v>
@@ -4422,19 +4422,19 @@
         <v>0</v>
       </c>
       <c r="BX9" t="n">
-        <v>68.42</v>
+        <v>65</v>
       </c>
       <c r="BY9" t="n">
         <v>2.1</v>
       </c>
       <c r="BZ9" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.26</v>
+        <v>3.25</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.4</v>
+        <v>3.39</v>
       </c>
       <c r="CC9" t="n">
         <v>2.97</v>
@@ -4443,22 +4443,22 @@
         <v>3.15</v>
       </c>
       <c r="CE9" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.77</v>
+        <v>2.8</v>
       </c>
       <c r="CG9" t="n">
-        <v>2.89</v>
+        <v>2.86</v>
       </c>
       <c r="CH9" t="n">
         <v>1.4</v>
       </c>
       <c r="CI9" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="CK9" t="n">
         <v>1.53</v>
@@ -4467,37 +4467,37 @@
         <v>1.94</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="CN9" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CO9" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="CP9" t="n">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="CQ9" t="n">
-        <v>3.24</v>
+        <v>3.31</v>
       </c>
       <c r="CR9" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CS9" t="n">
-        <v>3.03</v>
+        <v>3.06</v>
       </c>
       <c r="CT9" t="n">
-        <v>2.96</v>
+        <v>2.93</v>
       </c>
       <c r="CU9" t="n">
         <v>1.41</v>
       </c>
       <c r="CV9" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="CW9" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="CX9" t="n">
         <v>1.57</v>
@@ -4512,88 +4512,88 @@
         <v>1.87</v>
       </c>
       <c r="DB9" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="DC9" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="DD9" t="n">
-        <v>3.45</v>
+        <v>3.54</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.74</v>
+        <v>1.65</v>
       </c>
       <c r="DG9" t="n">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="DH9" t="n">
-        <v>97.05</v>
+        <v>96.95</v>
       </c>
       <c r="DI9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DJ9" t="n">
-        <v>3.21</v>
+        <v>3.05</v>
       </c>
       <c r="DK9" t="n">
-        <v>4.89</v>
+        <v>4.95</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.21</v>
+        <v>0.35</v>
       </c>
       <c r="DM9" t="n">
-        <v>47.68</v>
+        <v>47.9</v>
       </c>
       <c r="DN9" t="n">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="DO9" t="n">
-        <v>2.26</v>
+        <v>2.4</v>
       </c>
       <c r="DP9" t="n">
-        <v>16</v>
+        <v>16.15</v>
       </c>
       <c r="DQ9" t="n">
-        <v>15.16</v>
+        <v>15.05</v>
       </c>
       <c r="DR9" t="n">
-        <v>6</v>
+        <v>5.95</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>56.48</v>
+        <v>56.4</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DX9" t="n">
-        <v>14.68</v>
+        <v>14.65</v>
       </c>
       <c r="DY9" t="n">
-        <v>10</v>
+        <v>9.9</v>
       </c>
       <c r="DZ9" t="n">
-        <v>4.69</v>
+        <v>4.75</v>
       </c>
       <c r="EA9" t="n">
-        <v>22.32</v>
+        <v>22.1</v>
       </c>
       <c r="EB9" t="n">
         <v>1.6</v>
       </c>
       <c r="EC9" t="n">
-        <v>3</v>
+        <v>2.85</v>
       </c>
     </row>
     <row r="10">
@@ -5409,13 +5409,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
         <v>10</v>
       </c>
       <c r="D12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E12" t="n">
         <v>0.3</v>
@@ -5502,136 +5502,136 @@
         <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AH12" t="n">
-        <v>0.89</v>
+        <v>1</v>
       </c>
       <c r="AI12" t="n">
-        <v>90.56</v>
+        <v>89.8</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.89</v>
+        <v>3.1</v>
       </c>
       <c r="AL12" t="n">
-        <v>2.33</v>
+        <v>2.8</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="AN12" t="n">
-        <v>36.67</v>
+        <v>39.3</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.44</v>
+        <v>1.8</v>
       </c>
       <c r="AQ12" t="n">
-        <v>14.33</v>
+        <v>14.2</v>
       </c>
       <c r="AR12" t="n">
-        <v>14.56</v>
+        <v>14.4</v>
       </c>
       <c r="AS12" t="n">
-        <v>8.44</v>
+        <v>8.1</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.89</v>
+        <v>1</v>
       </c>
       <c r="AV12" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AW12" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AX12" t="n">
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>45.78</v>
+        <v>46.5</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="BA12" t="n">
-        <v>9.56</v>
+        <v>10.4</v>
       </c>
       <c r="BB12" t="n">
-        <v>6.33</v>
+        <v>7</v>
       </c>
       <c r="BC12" t="n">
-        <v>3.22</v>
+        <v>3.4</v>
       </c>
       <c r="BD12" t="n">
-        <v>21.22</v>
+        <v>21.5</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="BF12" t="n">
-        <v>2.56</v>
+        <v>2.8</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.37</v>
+        <v>2.5</v>
       </c>
       <c r="BH12" t="n">
-        <v>9</v>
+        <v>9.15</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.37</v>
+        <v>2.5</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.68</v>
+        <v>0.7</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.58</v>
+        <v>0.65</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="BP12" t="n">
-        <v>3.84</v>
+        <v>4.05</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.16</v>
+        <v>5.1</v>
       </c>
       <c r="BR12" t="n">
-        <v>84.20999999999999</v>
+        <v>85</v>
       </c>
       <c r="BS12" t="n">
-        <v>68.42</v>
+        <v>70</v>
       </c>
       <c r="BT12" t="n">
-        <v>42.11</v>
+        <v>45</v>
       </c>
       <c r="BU12" t="n">
-        <v>26.32</v>
+        <v>30</v>
       </c>
       <c r="BV12" t="n">
-        <v>5.26</v>
+        <v>10</v>
       </c>
       <c r="BW12" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BX12" t="n">
-        <v>57.89</v>
+        <v>60</v>
       </c>
       <c r="BY12" t="n">
         <v>2.08</v>
@@ -5640,28 +5640,28 @@
         <v>2.27</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.19</v>
+        <v>3.2</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.26</v>
+        <v>3.28</v>
       </c>
       <c r="CC12" t="n">
-        <v>3.46</v>
+        <v>3.52</v>
       </c>
       <c r="CD12" t="n">
-        <v>3.87</v>
+        <v>3.88</v>
       </c>
       <c r="CE12" t="n">
         <v>1.45</v>
       </c>
       <c r="CF12" t="n">
-        <v>3.15</v>
+        <v>3.12</v>
       </c>
       <c r="CG12" t="n">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="CH12" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="CI12" t="n">
         <v>1.84</v>
@@ -5673,10 +5673,10 @@
         <v>1.58</v>
       </c>
       <c r="CL12" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="CN12" t="n">
         <v>1.78</v>
@@ -5688,7 +5688,7 @@
         <v>2.2</v>
       </c>
       <c r="CQ12" t="n">
-        <v>3.95</v>
+        <v>3.92</v>
       </c>
       <c r="CR12" t="n">
         <v>1.5</v>
@@ -5703,19 +5703,19 @@
         <v>1.35</v>
       </c>
       <c r="CV12" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="CW12" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CX12" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CY12" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="CZ12" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="DA12" t="n">
         <v>1.75</v>
@@ -5724,85 +5724,85 @@
         <v>1.41</v>
       </c>
       <c r="DC12" t="n">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="DD12" t="n">
-        <v>4.27</v>
+        <v>4.23</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="DG12" t="n">
         <v>2.05</v>
       </c>
       <c r="DH12" t="n">
-        <v>91.27</v>
+        <v>90.84999999999999</v>
       </c>
       <c r="DI12" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.47</v>
+        <v>2.6</v>
       </c>
       <c r="DK12" t="n">
-        <v>4.21</v>
+        <v>4.35</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.42</v>
+        <v>0.45</v>
       </c>
       <c r="DM12" t="n">
-        <v>41.84</v>
+        <v>42.9</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="DO12" t="n">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="DP12" t="n">
-        <v>13.21</v>
+        <v>13.2</v>
       </c>
       <c r="DQ12" t="n">
-        <v>15</v>
+        <v>14.9</v>
       </c>
       <c r="DR12" t="n">
-        <v>8</v>
+        <v>7.85</v>
       </c>
       <c r="DS12" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="DT12" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>49.26</v>
+        <v>49.45</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DX12" t="n">
-        <v>12.48</v>
+        <v>12.75</v>
       </c>
       <c r="DY12" t="n">
-        <v>8.890000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="DZ12" t="n">
-        <v>3.58</v>
+        <v>3.65</v>
       </c>
       <c r="EA12" t="n">
-        <v>21.95</v>
+        <v>22.05</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.21</v>
+        <v>2.35</v>
       </c>
     </row>
     <row r="13">
@@ -6215,13 +6215,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C14" t="n">
         <v>9</v>
       </c>
       <c r="D14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -6305,139 +6305,139 @@
         <v>3.67</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AG14" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>81.45</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>28.82</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>14.27</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>13.73</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>10.55</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>37.18</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>9.82</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>6.73</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>17.55</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="BN14" t="n">
         <v>1.5</v>
       </c>
-      <c r="AH14" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>81.2</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>28.8</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>14</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>37.4</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="BG14" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="BH14" t="n">
-        <v>8.74</v>
-      </c>
-      <c r="BI14" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="BJ14" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="BK14" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="BL14" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="BM14" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="BN14" t="n">
-        <v>1.47</v>
-      </c>
       <c r="BO14" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="BP14" t="n">
-        <v>3.84</v>
+        <v>3.7</v>
       </c>
       <c r="BQ14" t="n">
-        <v>4.89</v>
+        <v>5</v>
       </c>
       <c r="BR14" t="n">
-        <v>89.47</v>
+        <v>90</v>
       </c>
       <c r="BS14" t="n">
-        <v>68.42</v>
+        <v>70</v>
       </c>
       <c r="BT14" t="n">
-        <v>47.37</v>
+        <v>50</v>
       </c>
       <c r="BU14" t="n">
-        <v>31.58</v>
+        <v>30</v>
       </c>
       <c r="BV14" t="n">
-        <v>21.05</v>
+        <v>20</v>
       </c>
       <c r="BW14" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BX14" t="n">
-        <v>57.89</v>
+        <v>60</v>
       </c>
       <c r="BY14" t="n">
         <v>2.96</v>
@@ -6446,25 +6446,25 @@
         <v>3.36</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.27</v>
+        <v>3.29</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.5</v>
+        <v>3.52</v>
       </c>
       <c r="CC14" t="n">
-        <v>5.18</v>
+        <v>5.3</v>
       </c>
       <c r="CD14" t="n">
-        <v>5.65</v>
+        <v>5.79</v>
       </c>
       <c r="CE14" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CF14" t="n">
         <v>3.17</v>
       </c>
       <c r="CG14" t="n">
-        <v>2.58</v>
+        <v>2.57</v>
       </c>
       <c r="CH14" t="n">
         <v>1.32</v>
@@ -6473,13 +6473,13 @@
         <v>1.74</v>
       </c>
       <c r="CJ14" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="CK14" t="n">
         <v>1.7</v>
       </c>
       <c r="CL14" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="CM14" t="n">
         <v>2.1</v>
@@ -6494,25 +6494,25 @@
         <v>2.25</v>
       </c>
       <c r="CQ14" t="n">
-        <v>4.19</v>
+        <v>4.17</v>
       </c>
       <c r="CR14" t="n">
         <v>1.51</v>
       </c>
       <c r="CS14" t="n">
-        <v>3.24</v>
+        <v>3.25</v>
       </c>
       <c r="CT14" t="n">
         <v>2.7</v>
       </c>
       <c r="CU14" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CV14" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CW14" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="CX14" t="n">
         <v>1.7</v>
@@ -6533,79 +6533,79 @@
         <v>2.35</v>
       </c>
       <c r="DD14" t="n">
-        <v>4.44</v>
+        <v>4.43</v>
       </c>
       <c r="DE14" t="n">
         <v>0.05</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="DG14" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="DH14" t="n">
-        <v>88.79000000000001</v>
+        <v>88.55</v>
       </c>
       <c r="DI14" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ14" t="n">
-        <v>3.26</v>
+        <v>3.35</v>
       </c>
       <c r="DK14" t="n">
-        <v>3.21</v>
+        <v>3.2</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DM14" t="n">
-        <v>34.74</v>
+        <v>34.45</v>
       </c>
       <c r="DN14" t="n">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="DO14" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="DP14" t="n">
-        <v>15.63</v>
+        <v>15.7</v>
       </c>
       <c r="DQ14" t="n">
-        <v>13</v>
+        <v>13.2</v>
       </c>
       <c r="DR14" t="n">
-        <v>9.26</v>
+        <v>9.25</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>41.95</v>
+        <v>41.6</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.16</v>
+        <v>0.2</v>
       </c>
       <c r="DX14" t="n">
-        <v>11.05</v>
+        <v>11</v>
       </c>
       <c r="DY14" t="n">
-        <v>7.53</v>
+        <v>7.55</v>
       </c>
       <c r="DZ14" t="n">
-        <v>3.53</v>
+        <v>3.45</v>
       </c>
       <c r="EA14" t="n">
-        <v>17.58</v>
+        <v>17.55</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="EC14" t="n">
         <v>3</v>
@@ -7021,13 +7021,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C16" t="n">
         <v>10</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E16" t="n">
         <v>0.2</v>
@@ -7114,97 +7114,97 @@
         <v>0</v>
       </c>
       <c r="AG16" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>92.09999999999999</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AP16" t="n">
         <v>2</v>
       </c>
-      <c r="AH16" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>91.11</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>4.67</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>37.44</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>2.22</v>
-      </c>
       <c r="AQ16" t="n">
-        <v>13.44</v>
+        <v>13.5</v>
       </c>
       <c r="AR16" t="n">
-        <v>16.67</v>
+        <v>16.8</v>
       </c>
       <c r="AS16" t="n">
-        <v>8.220000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AU16" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AV16" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AW16" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AX16" t="n">
         <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>52.44</v>
+        <v>52.8</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="BA16" t="n">
-        <v>12.22</v>
+        <v>11.6</v>
       </c>
       <c r="BB16" t="n">
-        <v>7.11</v>
+        <v>6.8</v>
       </c>
       <c r="BC16" t="n">
-        <v>5.11</v>
+        <v>4.8</v>
       </c>
       <c r="BD16" t="n">
-        <v>16.78</v>
+        <v>17.3</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="BF16" t="n">
-        <v>3.11</v>
+        <v>3</v>
       </c>
       <c r="BG16" t="n">
-        <v>3.63</v>
+        <v>3.55</v>
       </c>
       <c r="BH16" t="n">
-        <v>11.42</v>
+        <v>11.05</v>
       </c>
       <c r="BI16" t="n">
-        <v>3.63</v>
+        <v>3.55</v>
       </c>
       <c r="BJ16" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.58</v>
+        <v>0.55</v>
       </c>
       <c r="BL16" t="n">
         <v>1</v>
@@ -7216,34 +7216,34 @@
         <v>2.05</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="BP16" t="n">
-        <v>5.47</v>
+        <v>5.2</v>
       </c>
       <c r="BQ16" t="n">
-        <v>5.95</v>
+        <v>5.85</v>
       </c>
       <c r="BR16" t="n">
         <v>100</v>
       </c>
       <c r="BS16" t="n">
-        <v>94.73999999999999</v>
+        <v>95</v>
       </c>
       <c r="BT16" t="n">
-        <v>78.95</v>
+        <v>75</v>
       </c>
       <c r="BU16" t="n">
-        <v>57.89</v>
+        <v>55</v>
       </c>
       <c r="BV16" t="n">
-        <v>26.32</v>
+        <v>25</v>
       </c>
       <c r="BW16" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BX16" t="n">
-        <v>78.95</v>
+        <v>80</v>
       </c>
       <c r="BY16" t="n">
         <v>1.81</v>
@@ -7252,22 +7252,22 @@
         <v>1.82</v>
       </c>
       <c r="CA16" t="n">
-        <v>3.62</v>
+        <v>3.6</v>
       </c>
       <c r="CB16" t="n">
         <v>3.77</v>
       </c>
       <c r="CC16" t="n">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="CD16" t="n">
-        <v>3.39</v>
+        <v>3.43</v>
       </c>
       <c r="CE16" t="n">
         <v>1.34</v>
       </c>
       <c r="CF16" t="n">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="CG16" t="n">
         <v>3.08</v>
@@ -7285,13 +7285,13 @@
         <v>1.51</v>
       </c>
       <c r="CL16" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CM16" t="n">
         <v>2.44</v>
       </c>
       <c r="CN16" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CO16" t="n">
         <v>1.22</v>
@@ -7315,7 +7315,7 @@
         <v>1.5</v>
       </c>
       <c r="CV16" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="CW16" t="n">
         <v>1.67</v>
@@ -7342,79 +7342,79 @@
         <v>2.94</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DF16" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="DG16" t="n">
-        <v>3.26</v>
+        <v>3.1</v>
       </c>
       <c r="DH16" t="n">
-        <v>96</v>
+        <v>96.25</v>
       </c>
       <c r="DI16" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DJ16" t="n">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="DK16" t="n">
-        <v>6.05</v>
+        <v>5.75</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.63</v>
+        <v>0.6</v>
       </c>
       <c r="DM16" t="n">
-        <v>42.52</v>
+        <v>42.4</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="DO16" t="n">
-        <v>2.79</v>
+        <v>2.65</v>
       </c>
       <c r="DP16" t="n">
-        <v>13.05</v>
+        <v>13.1</v>
       </c>
       <c r="DQ16" t="n">
-        <v>15.42</v>
+        <v>15.55</v>
       </c>
       <c r="DR16" t="n">
-        <v>7.89</v>
+        <v>7.85</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.11</v>
+        <v>0.15</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.11</v>
+        <v>0.15</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>53.26</v>
+        <v>53.4</v>
       </c>
       <c r="DW16" t="n">
         <v>0.1</v>
       </c>
       <c r="DX16" t="n">
-        <v>14</v>
+        <v>13.6</v>
       </c>
       <c r="DY16" t="n">
-        <v>8.26</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="DZ16" t="n">
-        <v>5.74</v>
+        <v>5.55</v>
       </c>
       <c r="EA16" t="n">
-        <v>17.69</v>
+        <v>17.9</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="EC16" t="n">
-        <v>2.79</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="17">
@@ -7424,13 +7424,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C17" t="n">
         <v>10</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E17" t="n">
         <v>0.2</v>
@@ -7517,136 +7517,136 @@
         <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.22</v>
+        <v>2.4</v>
       </c>
       <c r="AI17" t="n">
-        <v>83.89</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="AK17" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>12</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>42.4</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>22</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BF17" t="n">
         <v>3</v>
       </c>
-      <c r="AL17" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>28.44</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>16.56</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>12.67</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>8.779999999999999</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>42.44</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>11.56</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>7.11</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>4.44</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>22.33</v>
-      </c>
-      <c r="BE17" t="n">
+      <c r="BG17" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>9</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BO17" t="n">
         <v>1.25</v>
       </c>
-      <c r="BF17" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="BG17" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="BH17" t="n">
-        <v>9.050000000000001</v>
-      </c>
-      <c r="BI17" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="BJ17" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="BK17" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="BL17" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="BM17" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="BN17" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="BO17" t="n">
-        <v>1.32</v>
-      </c>
       <c r="BP17" t="n">
-        <v>4.11</v>
+        <v>4.05</v>
       </c>
       <c r="BQ17" t="n">
-        <v>4.42</v>
+        <v>4.45</v>
       </c>
       <c r="BR17" t="n">
         <v>100</v>
       </c>
       <c r="BS17" t="n">
-        <v>63.16</v>
+        <v>65</v>
       </c>
       <c r="BT17" t="n">
-        <v>52.63</v>
+        <v>50</v>
       </c>
       <c r="BU17" t="n">
-        <v>26.32</v>
+        <v>25</v>
       </c>
       <c r="BV17" t="n">
-        <v>15.79</v>
+        <v>15</v>
       </c>
       <c r="BW17" t="n">
-        <v>15.79</v>
+        <v>15</v>
       </c>
       <c r="BX17" t="n">
-        <v>47.37</v>
+        <v>50</v>
       </c>
       <c r="BY17" t="n">
         <v>3.2</v>
@@ -7658,13 +7658,13 @@
         <v>3.44</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.67</v>
+        <v>3.66</v>
       </c>
       <c r="CC17" t="n">
-        <v>5.51</v>
+        <v>5.34</v>
       </c>
       <c r="CD17" t="n">
-        <v>6.59</v>
+        <v>6.43</v>
       </c>
       <c r="CE17" t="n">
         <v>1.42</v>
@@ -7685,13 +7685,13 @@
         <v>1.94</v>
       </c>
       <c r="CK17" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CL17" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="CN17" t="n">
         <v>1.78</v>
@@ -7700,7 +7700,7 @@
         <v>1.34</v>
       </c>
       <c r="CP17" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="CQ17" t="n">
         <v>3.7</v>
@@ -7712,25 +7712,25 @@
         <v>3.11</v>
       </c>
       <c r="CT17" t="n">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
       <c r="CU17" t="n">
         <v>1.4</v>
       </c>
       <c r="CV17" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CW17" t="n">
         <v>1.99</v>
       </c>
       <c r="CX17" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CY17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="CZ17" t="n">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="DA17" t="n">
         <v>1.77</v>
@@ -7739,85 +7739,85 @@
         <v>1.37</v>
       </c>
       <c r="DC17" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="DD17" t="n">
-        <v>3.97</v>
+        <v>3.95</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="DG17" t="n">
-        <v>1.58</v>
+        <v>1.7</v>
       </c>
       <c r="DH17" t="n">
-        <v>82.73999999999999</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="DI17" t="n">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="DJ17" t="n">
-        <v>3.11</v>
+        <v>3.2</v>
       </c>
       <c r="DK17" t="n">
-        <v>3.21</v>
+        <v>3.4</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.21</v>
+        <v>0.3</v>
       </c>
       <c r="DM17" t="n">
-        <v>30.52</v>
+        <v>32</v>
       </c>
       <c r="DN17" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="DO17" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="DP17" t="n">
-        <v>17.37</v>
+        <v>17.35</v>
       </c>
       <c r="DQ17" t="n">
-        <v>13</v>
+        <v>12.65</v>
       </c>
       <c r="DR17" t="n">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>43.95</v>
+        <v>43.85</v>
       </c>
       <c r="DW17" t="n">
         <v>0.05</v>
       </c>
       <c r="DX17" t="n">
-        <v>10.79</v>
+        <v>11</v>
       </c>
       <c r="DY17" t="n">
-        <v>6.74</v>
+        <v>6.95</v>
       </c>
       <c r="DZ17" t="n">
         <v>4.05</v>
       </c>
       <c r="EA17" t="n">
-        <v>21.31</v>
+        <v>21.2</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="EC17" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="18">
@@ -7827,94 +7827,94 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D18" t="n">
         <v>9</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="F18" t="n">
-        <v>1.4</v>
+        <v>1.73</v>
       </c>
       <c r="G18" t="n">
-        <v>4.5</v>
+        <v>4.45</v>
       </c>
       <c r="H18" t="n">
-        <v>113</v>
+        <v>111.27</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="J18" t="n">
-        <v>2.6</v>
+        <v>3.09</v>
       </c>
       <c r="K18" t="n">
-        <v>7</v>
+        <v>6.73</v>
       </c>
       <c r="L18" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="M18" t="n">
-        <v>65.7</v>
+        <v>63</v>
       </c>
       <c r="N18" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="O18" t="n">
-        <v>2.5</v>
+        <v>2.27</v>
       </c>
       <c r="P18" t="n">
-        <v>18</v>
+        <v>18.09</v>
       </c>
       <c r="Q18" t="n">
-        <v>12.9</v>
+        <v>13</v>
       </c>
       <c r="R18" t="n">
-        <v>5.2</v>
+        <v>5.36</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
       </c>
       <c r="T18" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="V18" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>52.5</v>
+        <v>51.73</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="Z18" t="n">
-        <v>17.4</v>
+        <v>16.55</v>
       </c>
       <c r="AA18" t="n">
-        <v>11.9</v>
+        <v>11.45</v>
       </c>
       <c r="AB18" t="n">
-        <v>5.5</v>
+        <v>5.09</v>
       </c>
       <c r="AC18" t="n">
-        <v>29.1</v>
+        <v>28.55</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.96</v>
+        <v>1.86</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.5</v>
+        <v>2.91</v>
       </c>
       <c r="AF18" t="n">
         <v>0.11</v>
@@ -8001,67 +8001,67 @@
         <v>2.05</v>
       </c>
       <c r="BH18" t="n">
-        <v>9.26</v>
+        <v>9</v>
       </c>
       <c r="BI18" t="n">
         <v>2.05</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.47</v>
+        <v>0.45</v>
       </c>
       <c r="BL18" t="n">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="BO18" t="n">
-        <v>0.84</v>
+        <v>0.8</v>
       </c>
       <c r="BP18" t="n">
-        <v>3.47</v>
+        <v>3.3</v>
       </c>
       <c r="BQ18" t="n">
-        <v>5.79</v>
+        <v>5.7</v>
       </c>
       <c r="BR18" t="n">
-        <v>89.47</v>
+        <v>90</v>
       </c>
       <c r="BS18" t="n">
-        <v>57.89</v>
+        <v>60</v>
       </c>
       <c r="BT18" t="n">
-        <v>31.58</v>
+        <v>30</v>
       </c>
       <c r="BU18" t="n">
-        <v>15.79</v>
+        <v>15</v>
       </c>
       <c r="BV18" t="n">
-        <v>10.53</v>
+        <v>10</v>
       </c>
       <c r="BW18" t="n">
         <v>0</v>
       </c>
       <c r="BX18" t="n">
-        <v>42.11</v>
+        <v>45</v>
       </c>
       <c r="BY18" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="BZ18" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CA18" t="n">
         <v>3.29</v>
       </c>
       <c r="CB18" t="n">
-        <v>3.41</v>
+        <v>3.42</v>
       </c>
       <c r="CC18" t="n">
         <v>2.76</v>
@@ -8070,43 +8070,43 @@
         <v>3.01</v>
       </c>
       <c r="CE18" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CF18" t="n">
-        <v>2.98</v>
+        <v>2.95</v>
       </c>
       <c r="CG18" t="n">
-        <v>2.71</v>
+        <v>2.73</v>
       </c>
       <c r="CH18" t="n">
         <v>1.37</v>
       </c>
       <c r="CI18" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="CJ18" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="CK18" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CL18" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="CM18" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="CN18" t="n">
         <v>1.73</v>
       </c>
       <c r="CO18" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="CP18" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="CQ18" t="n">
-        <v>3.84</v>
+        <v>3.78</v>
       </c>
       <c r="CR18" t="n">
         <v>1.47</v>
@@ -8121,106 +8121,106 @@
         <v>1.39</v>
       </c>
       <c r="CV18" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="CW18" t="n">
         <v>1.93</v>
       </c>
-      <c r="CW18" t="n">
-        <v>1.95</v>
-      </c>
       <c r="CX18" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="CY18" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="CZ18" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="DA18" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="DB18" t="n">
         <v>1.38</v>
       </c>
       <c r="DC18" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="DD18" t="n">
-        <v>4.07</v>
+        <v>4.01</v>
       </c>
       <c r="DE18" t="n">
         <v>0.1</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.79</v>
+        <v>1.95</v>
       </c>
       <c r="DG18" t="n">
         <v>4</v>
       </c>
       <c r="DH18" t="n">
-        <v>109.79</v>
+        <v>109</v>
       </c>
       <c r="DI18" t="n">
         <v>0.1</v>
       </c>
       <c r="DJ18" t="n">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="DK18" t="n">
-        <v>6.37</v>
+        <v>6.25</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.63</v>
+        <v>0.6</v>
       </c>
       <c r="DM18" t="n">
-        <v>55.79</v>
+        <v>54.8</v>
       </c>
       <c r="DN18" t="n">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="DO18" t="n">
-        <v>2.37</v>
+        <v>2.25</v>
       </c>
       <c r="DP18" t="n">
-        <v>17.68</v>
+        <v>17.75</v>
       </c>
       <c r="DQ18" t="n">
-        <v>13.53</v>
+        <v>13.55</v>
       </c>
       <c r="DR18" t="n">
-        <v>6.63</v>
+        <v>6.65</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DT18" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DU18" t="n">
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>52.53</v>
+        <v>52.1</v>
       </c>
       <c r="DW18" t="n">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="DX18" t="n">
-        <v>14.95</v>
+        <v>14.6</v>
       </c>
       <c r="DY18" t="n">
-        <v>10.32</v>
+        <v>10.15</v>
       </c>
       <c r="DZ18" t="n">
-        <v>4.63</v>
+        <v>4.45</v>
       </c>
       <c r="EA18" t="n">
-        <v>25.89</v>
+        <v>25.75</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="EC18" t="n">
-        <v>2.95</v>
+        <v>3.15</v>
       </c>
     </row>
     <row r="19">
@@ -8633,94 +8633,94 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D20" t="n">
         <v>9</v>
       </c>
       <c r="E20" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="F20" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="G20" t="n">
-        <v>2.7</v>
+        <v>2.91</v>
       </c>
       <c r="H20" t="n">
-        <v>115.1</v>
+        <v>115.55</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>2.6</v>
+        <v>2.73</v>
       </c>
       <c r="K20" t="n">
-        <v>5.4</v>
+        <v>5.36</v>
       </c>
       <c r="L20" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="M20" t="n">
-        <v>60.1</v>
+        <v>60.64</v>
       </c>
       <c r="N20" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="O20" t="n">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="P20" t="n">
-        <v>15.9</v>
+        <v>16</v>
       </c>
       <c r="Q20" t="n">
-        <v>11.3</v>
+        <v>11.73</v>
       </c>
       <c r="R20" t="n">
-        <v>6.4</v>
+        <v>6.45</v>
       </c>
       <c r="S20" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="T20" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="V20" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>53.3</v>
+        <v>54.36</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="Z20" t="n">
-        <v>16.3</v>
+        <v>16.09</v>
       </c>
       <c r="AA20" t="n">
-        <v>10.7</v>
+        <v>10.64</v>
       </c>
       <c r="AB20" t="n">
-        <v>5.6</v>
+        <v>5.45</v>
       </c>
       <c r="AC20" t="n">
-        <v>18</v>
+        <v>18.82</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="AF20" t="n">
         <v>0.11</v>
@@ -8804,70 +8804,70 @@
         <v>2.33</v>
       </c>
       <c r="BG20" t="n">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="BH20" t="n">
-        <v>8.949999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="BI20" t="n">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="BJ20" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="BK20" t="n">
-        <v>0.32</v>
+        <v>0.35</v>
       </c>
       <c r="BL20" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="BM20" t="n">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
       <c r="BN20" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="BO20" t="n">
         <v>1</v>
       </c>
       <c r="BP20" t="n">
-        <v>4.11</v>
+        <v>3.95</v>
       </c>
       <c r="BQ20" t="n">
-        <v>4.84</v>
+        <v>4.95</v>
       </c>
       <c r="BR20" t="n">
-        <v>84.20999999999999</v>
+        <v>85</v>
       </c>
       <c r="BS20" t="n">
-        <v>73.68000000000001</v>
+        <v>75</v>
       </c>
       <c r="BT20" t="n">
-        <v>52.63</v>
+        <v>55</v>
       </c>
       <c r="BU20" t="n">
-        <v>21.05</v>
+        <v>20</v>
       </c>
       <c r="BV20" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BW20" t="n">
         <v>0</v>
       </c>
       <c r="BX20" t="n">
-        <v>52.63</v>
+        <v>55</v>
       </c>
       <c r="BY20" t="n">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="BZ20" t="n">
-        <v>2.06</v>
+        <v>2.01</v>
       </c>
       <c r="CA20" t="n">
-        <v>3.19</v>
+        <v>3.21</v>
       </c>
       <c r="CB20" t="n">
-        <v>3.26</v>
+        <v>3.29</v>
       </c>
       <c r="CC20" t="n">
         <v>3.3</v>
@@ -8882,28 +8882,28 @@
         <v>3.24</v>
       </c>
       <c r="CG20" t="n">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="CH20" t="n">
         <v>1.32</v>
       </c>
       <c r="CI20" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CJ20" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="CK20" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CL20" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="CM20" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="CN20" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CO20" t="n">
         <v>1.42</v>
@@ -8912,28 +8912,28 @@
         <v>2.33</v>
       </c>
       <c r="CQ20" t="n">
-        <v>4.3</v>
+        <v>4.28</v>
       </c>
       <c r="CR20" t="n">
         <v>1.54</v>
       </c>
       <c r="CS20" t="n">
-        <v>3.25</v>
+        <v>3.26</v>
       </c>
       <c r="CT20" t="n">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="CU20" t="n">
         <v>1.36</v>
       </c>
       <c r="CV20" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CW20" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="CX20" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CY20" t="n">
         <v>2.12</v>
@@ -8948,85 +8948,85 @@
         <v>1.46</v>
       </c>
       <c r="DC20" t="n">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="DD20" t="n">
-        <v>4.65</v>
+        <v>4.63</v>
       </c>
       <c r="DE20" t="n">
         <v>0.1</v>
       </c>
       <c r="DF20" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="DG20" t="n">
-        <v>2.74</v>
+        <v>2.85</v>
       </c>
       <c r="DH20" t="n">
-        <v>106.9</v>
+        <v>107.55</v>
       </c>
       <c r="DI20" t="n">
         <v>0.1</v>
       </c>
       <c r="DJ20" t="n">
-        <v>2.69</v>
+        <v>2.75</v>
       </c>
       <c r="DK20" t="n">
-        <v>4.74</v>
+        <v>4.75</v>
       </c>
       <c r="DL20" t="n">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
       <c r="DM20" t="n">
-        <v>49.42</v>
+        <v>50.25</v>
       </c>
       <c r="DN20" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="DO20" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="DP20" t="n">
-        <v>14.58</v>
+        <v>14.7</v>
       </c>
       <c r="DQ20" t="n">
-        <v>12.58</v>
+        <v>12.75</v>
       </c>
       <c r="DR20" t="n">
-        <v>6.79</v>
+        <v>6.8</v>
       </c>
       <c r="DS20" t="n">
-        <v>0.11</v>
+        <v>0.15</v>
       </c>
       <c r="DT20" t="n">
-        <v>0.11</v>
+        <v>0.15</v>
       </c>
       <c r="DU20" t="n">
         <v>0</v>
       </c>
       <c r="DV20" t="n">
-        <v>50.47</v>
+        <v>51.2</v>
       </c>
       <c r="DW20" t="n">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="DX20" t="n">
-        <v>12.89</v>
+        <v>12.95</v>
       </c>
       <c r="DY20" t="n">
-        <v>8.529999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="DZ20" t="n">
-        <v>4.37</v>
+        <v>4.35</v>
       </c>
       <c r="EA20" t="n">
-        <v>18.68</v>
+        <v>19.1</v>
       </c>
       <c r="EB20" t="n">
         <v>1.49</v>
       </c>
       <c r="EC20" t="n">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
     </row>
     <row r="21">
@@ -9036,13 +9036,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
         <v>10</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -9129,49 +9129,49 @@
         <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="AI21" t="n">
-        <v>80.67</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="AJ21" t="n">
         <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="AL21" t="n">
-        <v>3.67</v>
+        <v>3.6</v>
       </c>
       <c r="AM21" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AN21" t="n">
-        <v>32.33</v>
+        <v>32.6</v>
       </c>
       <c r="AO21" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AQ21" t="n">
-        <v>10.56</v>
+        <v>11.1</v>
       </c>
       <c r="AR21" t="n">
-        <v>12.67</v>
+        <v>13</v>
       </c>
       <c r="AS21" t="n">
-        <v>8.779999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="AT21" t="n">
-        <v>1.33</v>
+        <v>1.6</v>
       </c>
       <c r="AU21" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="AV21" t="n">
         <v>0</v>
@@ -9183,82 +9183,82 @@
         <v>0</v>
       </c>
       <c r="AY21" t="n">
-        <v>45.89</v>
+        <v>46.7</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="BA21" t="n">
-        <v>8.779999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="BB21" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="BC21" t="n">
-        <v>1.78</v>
+        <v>2.2</v>
       </c>
       <c r="BD21" t="n">
-        <v>17.33</v>
+        <v>18.3</v>
       </c>
       <c r="BE21" t="n">
-        <v>0.92</v>
+        <v>0.97</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="BG21" t="n">
-        <v>2.21</v>
+        <v>2.35</v>
       </c>
       <c r="BH21" t="n">
-        <v>9.68</v>
+        <v>9.4</v>
       </c>
       <c r="BI21" t="n">
-        <v>2.21</v>
+        <v>2.35</v>
       </c>
       <c r="BJ21" t="n">
-        <v>0.53</v>
+        <v>0.65</v>
       </c>
       <c r="BK21" t="n">
-        <v>0.47</v>
+        <v>0.45</v>
       </c>
       <c r="BL21" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="BM21" t="n">
-        <v>0.42</v>
+        <v>0.45</v>
       </c>
       <c r="BN21" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="BO21" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="BP21" t="n">
-        <v>4.32</v>
+        <v>4.15</v>
       </c>
       <c r="BQ21" t="n">
-        <v>5.32</v>
+        <v>5.2</v>
       </c>
       <c r="BR21" t="n">
-        <v>94.73999999999999</v>
+        <v>95</v>
       </c>
       <c r="BS21" t="n">
-        <v>68.42</v>
+        <v>70</v>
       </c>
       <c r="BT21" t="n">
-        <v>36.84</v>
+        <v>40</v>
       </c>
       <c r="BU21" t="n">
-        <v>15.79</v>
+        <v>20</v>
       </c>
       <c r="BV21" t="n">
-        <v>5.26</v>
+        <v>10</v>
       </c>
       <c r="BW21" t="n">
         <v>0</v>
       </c>
       <c r="BX21" t="n">
-        <v>47.37</v>
+        <v>50</v>
       </c>
       <c r="BY21" t="n">
         <v>2.5</v>
@@ -9267,28 +9267,28 @@
         <v>2.67</v>
       </c>
       <c r="CA21" t="n">
-        <v>2.91</v>
+        <v>2.95</v>
       </c>
       <c r="CB21" t="n">
-        <v>3.02</v>
+        <v>3.09</v>
       </c>
       <c r="CC21" t="n">
-        <v>3.44</v>
+        <v>3.7</v>
       </c>
       <c r="CD21" t="n">
-        <v>3.96</v>
+        <v>4.32</v>
       </c>
       <c r="CE21" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CF21" t="n">
-        <v>3.68</v>
+        <v>3.65</v>
       </c>
       <c r="CG21" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="CH21" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="CI21" t="n">
         <v>1.67</v>
@@ -9297,37 +9297,37 @@
         <v>2.16</v>
       </c>
       <c r="CK21" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CL21" t="n">
-        <v>2.21</v>
+        <v>2.18</v>
       </c>
       <c r="CM21" t="n">
-        <v>2.08</v>
+        <v>2.11</v>
       </c>
       <c r="CN21" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="CO21" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CP21" t="n">
-        <v>2.59</v>
+        <v>2.56</v>
       </c>
       <c r="CQ21" t="n">
-        <v>5.04</v>
+        <v>4.96</v>
       </c>
       <c r="CR21" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="CS21" t="n">
-        <v>3.28</v>
+        <v>3.22</v>
       </c>
       <c r="CT21" t="n">
-        <v>2.41</v>
+        <v>2.45</v>
       </c>
       <c r="CU21" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CV21" t="n">
         <v>1.7</v>
@@ -9336,97 +9336,97 @@
         <v>2.25</v>
       </c>
       <c r="CX21" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CY21" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="CZ21" t="n">
-        <v>2.09</v>
+        <v>2.12</v>
       </c>
       <c r="DA21" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="DB21" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="DC21" t="n">
-        <v>2.81</v>
+        <v>2.78</v>
       </c>
       <c r="DD21" t="n">
-        <v>5.66</v>
+        <v>5.56</v>
       </c>
       <c r="DE21" t="n">
         <v>0</v>
       </c>
       <c r="DF21" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="DG21" t="n">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="DH21" t="n">
-        <v>90.42</v>
+        <v>91.65000000000001</v>
       </c>
       <c r="DI21" t="n">
         <v>0</v>
       </c>
       <c r="DJ21" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="DK21" t="n">
-        <v>4.63</v>
+        <v>4.55</v>
       </c>
       <c r="DL21" t="n">
-        <v>0.74</v>
+        <v>0.7</v>
       </c>
       <c r="DM21" t="n">
-        <v>39.63</v>
+        <v>39.4</v>
       </c>
       <c r="DN21" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="DO21" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="DP21" t="n">
-        <v>12.42</v>
+        <v>12.6</v>
       </c>
       <c r="DQ21" t="n">
-        <v>12.84</v>
+        <v>13</v>
       </c>
       <c r="DR21" t="n">
-        <v>8.949999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="DS21" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DT21" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DU21" t="n">
         <v>0</v>
       </c>
       <c r="DV21" t="n">
-        <v>46.37</v>
+        <v>46.75</v>
       </c>
       <c r="DW21" t="n">
         <v>0.05</v>
       </c>
       <c r="DX21" t="n">
-        <v>10.69</v>
+        <v>10.75</v>
       </c>
       <c r="DY21" t="n">
-        <v>7.84</v>
+        <v>7.75</v>
       </c>
       <c r="DZ21" t="n">
-        <v>2.84</v>
+        <v>3</v>
       </c>
       <c r="EA21" t="n">
-        <v>20.95</v>
+        <v>21.25</v>
       </c>
       <c r="EB21" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="EC21" t="n">
         <v>2.05</v>

--- a/data/teams/leagues/Averages_Spain_Segunda_División_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Spain_Segunda_División_2025-2026.xlsx
@@ -645,7 +645,7 @@
     <col width="9.6" customWidth="1" min="73" max="73"/>
     <col width="9.6" customWidth="1" min="74" max="74"/>
     <col width="9.6" customWidth="1" min="75" max="75"/>
-    <col width="8.4" customWidth="1" min="76" max="76"/>
+    <col width="7.199999999999999" customWidth="1" min="76" max="76"/>
     <col width="18" customWidth="1" min="77" max="77"/>
     <col width="27.6" customWidth="1" min="78" max="78"/>
     <col width="18" customWidth="1" min="79" max="79"/>
@@ -1379,10 +1379,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D2" t="n">
         <v>10</v>
@@ -1391,49 +1391,49 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="G2" t="n">
-        <v>2.89</v>
+        <v>2.7</v>
       </c>
       <c r="H2" t="n">
-        <v>91.89</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.11</v>
+        <v>-0.1</v>
       </c>
       <c r="J2" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="K2" t="n">
-        <v>5.56</v>
+        <v>5.5</v>
       </c>
       <c r="L2" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="M2" t="n">
-        <v>45.67</v>
+        <v>44.9</v>
       </c>
       <c r="N2" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="O2" t="n">
-        <v>2.67</v>
+        <v>2.8</v>
       </c>
       <c r="P2" t="n">
-        <v>9.779999999999999</v>
+        <v>9.9</v>
       </c>
       <c r="Q2" t="n">
-        <v>8.44</v>
+        <v>8.4</v>
       </c>
       <c r="R2" t="n">
-        <v>6.44</v>
+        <v>6.2</v>
       </c>
       <c r="S2" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="T2" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -1445,28 +1445,28 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>43.56</v>
+        <v>43.4</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="Z2" t="n">
         <v>15</v>
       </c>
       <c r="AA2" t="n">
-        <v>10.22</v>
+        <v>10.3</v>
       </c>
       <c r="AB2" t="n">
-        <v>4.78</v>
+        <v>4.7</v>
       </c>
       <c r="AC2" t="n">
-        <v>25.22</v>
+        <v>25.1</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AF2" t="n">
         <v>0.3</v>
@@ -1550,70 +1550,70 @@
         <v>2.6</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="BH2" t="n">
-        <v>10.58</v>
+        <v>10.55</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.84</v>
+        <v>0.8</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="BN2" t="n">
         <v>2</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="BP2" t="n">
-        <v>4.95</v>
+        <v>5.1</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.58</v>
+        <v>5.4</v>
       </c>
       <c r="BR2" t="n">
-        <v>84.20999999999999</v>
+        <v>85</v>
       </c>
       <c r="BS2" t="n">
-        <v>68.42</v>
+        <v>70</v>
       </c>
       <c r="BT2" t="n">
-        <v>52.63</v>
+        <v>55</v>
       </c>
       <c r="BU2" t="n">
-        <v>36.84</v>
+        <v>40</v>
       </c>
       <c r="BV2" t="n">
-        <v>26.32</v>
+        <v>25</v>
       </c>
       <c r="BW2" t="n">
-        <v>10.53</v>
+        <v>10</v>
       </c>
       <c r="BX2" t="n">
-        <v>57.89</v>
+        <v>60</v>
       </c>
       <c r="BY2" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="BZ2" t="n">
-        <v>2.16</v>
+        <v>2.19</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.3</v>
+        <v>3.29</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.51</v>
+        <v>3.49</v>
       </c>
       <c r="CC2" t="n">
         <v>3.83</v>
@@ -1625,16 +1625,16 @@
         <v>1.39</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.87</v>
+        <v>2.85</v>
       </c>
       <c r="CH2" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CI2" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CJ2" t="n">
         <v>1.76</v>
@@ -1646,7 +1646,7 @@
         <v>1.94</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="CN2" t="n">
         <v>1.89</v>
@@ -1658,19 +1658,19 @@
         <v>1.95</v>
       </c>
       <c r="CQ2" t="n">
-        <v>3.3</v>
+        <v>3.32</v>
       </c>
       <c r="CR2" t="n">
         <v>1.42</v>
       </c>
       <c r="CS2" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="CT2" t="n">
         <v>2.98</v>
       </c>
       <c r="CU2" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CV2" t="n">
         <v>2.1</v>
@@ -1685,94 +1685,94 @@
         <v>1.87</v>
       </c>
       <c r="CZ2" t="n">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="DA2" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="DB2" t="n">
         <v>1.31</v>
       </c>
       <c r="DC2" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="DD2" t="n">
-        <v>3.45</v>
+        <v>3.46</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.42</v>
+        <v>2.35</v>
       </c>
       <c r="DH2" t="n">
-        <v>88.95</v>
+        <v>88.7</v>
       </c>
       <c r="DI2" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="DK2" t="n">
         <v>4.9</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.47</v>
+        <v>0.45</v>
       </c>
       <c r="DM2" t="n">
-        <v>42.26</v>
+        <v>42.05</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.48</v>
+        <v>2.55</v>
       </c>
       <c r="DP2" t="n">
-        <v>11.32</v>
+        <v>11.3</v>
       </c>
       <c r="DQ2" t="n">
-        <v>10.89</v>
+        <v>10.75</v>
       </c>
       <c r="DR2" t="n">
-        <v>7.84</v>
+        <v>7.65</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>43.16</v>
+        <v>43.1</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DX2" t="n">
-        <v>13.16</v>
+        <v>13.25</v>
       </c>
       <c r="DY2" t="n">
-        <v>8.470000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="DZ2" t="n">
-        <v>4.69</v>
+        <v>4.65</v>
       </c>
       <c r="EA2" t="n">
-        <v>24.31</v>
+        <v>24.3</v>
       </c>
       <c r="EB2" t="n">
         <v>1.46</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="3">
@@ -2197,7 +2197,7 @@
         <v>0.1</v>
       </c>
       <c r="F4" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="G4" t="n">
         <v>2.3</v>
@@ -2209,7 +2209,7 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="K4" t="n">
         <v>4</v>
@@ -2272,7 +2272,7 @@
         <v>1.21</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="AF4" t="n">
         <v>0.1</v>
@@ -2290,7 +2290,7 @@
         <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AL4" t="n">
         <v>4.1</v>
@@ -2302,13 +2302,13 @@
         <v>37</v>
       </c>
       <c r="AO4" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="AP4" t="n">
         <v>1.8</v>
       </c>
       <c r="AQ4" t="n">
-        <v>14</v>
+        <v>14.1</v>
       </c>
       <c r="AR4" t="n">
         <v>15.5</v>
@@ -2353,7 +2353,7 @@
         <v>1.06</v>
       </c>
       <c r="BF4" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="BG4" t="n">
         <v>2.2</v>
@@ -2509,7 +2509,7 @@
         <v>0.1</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="DG4" t="n">
         <v>2.3</v>
@@ -2521,7 +2521,7 @@
         <v>0</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="DK4" t="n">
         <v>4.05</v>
@@ -2533,13 +2533,13 @@
         <v>41.6</v>
       </c>
       <c r="DN4" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="DO4" t="n">
         <v>1.75</v>
       </c>
       <c r="DP4" t="n">
-        <v>13.9</v>
+        <v>13.95</v>
       </c>
       <c r="DQ4" t="n">
         <v>15</v>
@@ -2578,7 +2578,7 @@
         <v>1.14</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="5">
@@ -2711,7 +2711,7 @@
         <v>3.1</v>
       </c>
       <c r="AQ5" t="n">
-        <v>12.9</v>
+        <v>13.1</v>
       </c>
       <c r="AR5" t="n">
         <v>14</v>
@@ -2942,7 +2942,7 @@
         <v>3.25</v>
       </c>
       <c r="DP5" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="DQ5" t="n">
         <v>14.3</v>
@@ -2991,94 +2991,94 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D6" t="n">
         <v>10</v>
       </c>
       <c r="E6" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="F6" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="G6" t="n">
-        <v>3.11</v>
+        <v>2.9</v>
       </c>
       <c r="H6" t="n">
-        <v>99.22</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="J6" t="n">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="K6" t="n">
-        <v>5.44</v>
+        <v>5.3</v>
       </c>
       <c r="L6" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="M6" t="n">
-        <v>54.56</v>
+        <v>52.8</v>
       </c>
       <c r="N6" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="O6" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="P6" t="n">
-        <v>14.78</v>
+        <v>14.8</v>
       </c>
       <c r="Q6" t="n">
-        <v>13.22</v>
+        <v>13.1</v>
       </c>
       <c r="R6" t="n">
-        <v>5.33</v>
+        <v>5.3</v>
       </c>
       <c r="S6" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="T6" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="U6" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="V6" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>54.33</v>
+        <v>52.2</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>12.11</v>
+        <v>11.6</v>
       </c>
       <c r="AA6" t="n">
-        <v>7.78</v>
+        <v>7.2</v>
       </c>
       <c r="AB6" t="n">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="AC6" t="n">
-        <v>21.22</v>
+        <v>21.3</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="AF6" t="n">
         <v>0.1</v>
@@ -3162,70 +3162,70 @@
         <v>2.4</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="BH6" t="n">
-        <v>8.84</v>
+        <v>9</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.58</v>
+        <v>0.6</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="BP6" t="n">
-        <v>3.79</v>
+        <v>3.8</v>
       </c>
       <c r="BQ6" t="n">
-        <v>4.74</v>
+        <v>4.9</v>
       </c>
       <c r="BR6" t="n">
-        <v>89.47</v>
+        <v>90</v>
       </c>
       <c r="BS6" t="n">
-        <v>63.16</v>
+        <v>65</v>
       </c>
       <c r="BT6" t="n">
-        <v>42.11</v>
+        <v>45</v>
       </c>
       <c r="BU6" t="n">
-        <v>21.05</v>
+        <v>20</v>
       </c>
       <c r="BV6" t="n">
-        <v>15.79</v>
+        <v>15</v>
       </c>
       <c r="BW6" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BX6" t="n">
-        <v>47.37</v>
+        <v>50</v>
       </c>
       <c r="BY6" t="n">
-        <v>2.43</v>
+        <v>2.38</v>
       </c>
       <c r="BZ6" t="n">
-        <v>2.63</v>
+        <v>2.57</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.2</v>
+        <v>3.21</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.31</v>
+        <v>3.32</v>
       </c>
       <c r="CC6" t="n">
         <v>4.06</v>
@@ -3246,31 +3246,31 @@
         <v>1.34</v>
       </c>
       <c r="CI6" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CJ6" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CK6" t="n">
         <v>1.67</v>
       </c>
       <c r="CL6" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="CM6" t="n">
         <v>2.1</v>
       </c>
       <c r="CN6" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CO6" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CP6" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="CQ6" t="n">
-        <v>4.02</v>
+        <v>3.99</v>
       </c>
       <c r="CR6" t="n">
         <v>1.48</v>
@@ -3312,79 +3312,79 @@
         <v>4.15</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="DH6" t="n">
-        <v>89.31</v>
+        <v>88.65000000000001</v>
       </c>
       <c r="DI6" t="n">
         <v>0.1</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="DK6" t="n">
-        <v>4.37</v>
+        <v>4.35</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.31</v>
+        <v>0.35</v>
       </c>
       <c r="DM6" t="n">
-        <v>44.69</v>
+        <v>44.3</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="DO6" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="DP6" t="n">
-        <v>13.69</v>
+        <v>13.75</v>
       </c>
       <c r="DQ6" t="n">
-        <v>13.37</v>
+        <v>13.3</v>
       </c>
       <c r="DR6" t="n">
-        <v>7.31</v>
+        <v>7.2</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>51</v>
+        <v>50.1</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DX6" t="n">
-        <v>10.89</v>
+        <v>10.7</v>
       </c>
       <c r="DY6" t="n">
-        <v>7.42</v>
+        <v>7.15</v>
       </c>
       <c r="DZ6" t="n">
-        <v>3.47</v>
+        <v>3.55</v>
       </c>
       <c r="EA6" t="n">
-        <v>20.74</v>
+        <v>20.8</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.58</v>
+        <v>2.55</v>
       </c>
     </row>
     <row r="7">
@@ -3797,13 +3797,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C8" t="n">
         <v>10</v>
       </c>
       <c r="D8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E8" t="n">
         <v>0.1</v>
@@ -3839,7 +3839,7 @@
         <v>2.5</v>
       </c>
       <c r="P8" t="n">
-        <v>14</v>
+        <v>14.1</v>
       </c>
       <c r="Q8" t="n">
         <v>13.4</v>
@@ -3887,34 +3887,34 @@
         <v>3.3</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="AI8" t="n">
-        <v>84</v>
+        <v>85.5</v>
       </c>
       <c r="AJ8" t="n">
         <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.67</v>
+        <v>2.6</v>
       </c>
       <c r="AL8" t="n">
-        <v>4.11</v>
+        <v>4.1</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AN8" t="n">
-        <v>28.89</v>
+        <v>30.1</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="AP8" t="n">
         <v>2</v>
@@ -3923,16 +3923,16 @@
         <v>16</v>
       </c>
       <c r="AR8" t="n">
-        <v>13.33</v>
+        <v>12.9</v>
       </c>
       <c r="AS8" t="n">
-        <v>10.44</v>
+        <v>10</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="AU8" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="AV8" t="n">
         <v>0</v>
@@ -3944,82 +3944,82 @@
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>41.33</v>
+        <v>41</v>
       </c>
       <c r="AZ8" t="n">
         <v>0</v>
       </c>
       <c r="BA8" t="n">
-        <v>8.109999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="BB8" t="n">
-        <v>5.22</v>
+        <v>5.7</v>
       </c>
       <c r="BC8" t="n">
-        <v>2.89</v>
+        <v>2.8</v>
       </c>
       <c r="BD8" t="n">
-        <v>19.22</v>
+        <v>18.8</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.93</v>
+        <v>0.96</v>
       </c>
       <c r="BF8" t="n">
-        <v>2.67</v>
+        <v>2.6</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="BH8" t="n">
-        <v>10.58</v>
+        <v>10.65</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.47</v>
+        <v>0.55</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.37</v>
+        <v>0.4</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.63</v>
+        <v>0.6</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.58</v>
+        <v>0.6</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.84</v>
+        <v>0.95</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.68</v>
+        <v>4.8</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.89</v>
+        <v>5.85</v>
       </c>
       <c r="BR8" t="n">
-        <v>78.95</v>
+        <v>80</v>
       </c>
       <c r="BS8" t="n">
-        <v>52.63</v>
+        <v>55</v>
       </c>
       <c r="BT8" t="n">
-        <v>42.11</v>
+        <v>45</v>
       </c>
       <c r="BU8" t="n">
-        <v>15.79</v>
+        <v>20</v>
       </c>
       <c r="BV8" t="n">
-        <v>10.53</v>
+        <v>10</v>
       </c>
       <c r="BW8" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BX8" t="n">
-        <v>42.11</v>
+        <v>45</v>
       </c>
       <c r="BY8" t="n">
         <v>2.33</v>
@@ -4028,25 +4028,25 @@
         <v>2.54</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.11</v>
+        <v>3.13</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.28</v>
+        <v>3.29</v>
       </c>
       <c r="CC8" t="n">
-        <v>3.7</v>
+        <v>3.83</v>
       </c>
       <c r="CD8" t="n">
-        <v>4.12</v>
+        <v>4.24</v>
       </c>
       <c r="CE8" t="n">
         <v>1.47</v>
       </c>
       <c r="CF8" t="n">
-        <v>3.17</v>
+        <v>3.16</v>
       </c>
       <c r="CG8" t="n">
-        <v>2.54</v>
+        <v>2.55</v>
       </c>
       <c r="CH8" t="n">
         <v>1.32</v>
@@ -4055,16 +4055,16 @@
         <v>1.78</v>
       </c>
       <c r="CJ8" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CK8" t="n">
         <v>1.64</v>
       </c>
       <c r="CL8" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="CN8" t="n">
         <v>1.72</v>
@@ -4073,10 +4073,10 @@
         <v>1.39</v>
       </c>
       <c r="CP8" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="CQ8" t="n">
-        <v>4.17</v>
+        <v>4.16</v>
       </c>
       <c r="CR8" t="n">
         <v>1.51</v>
@@ -4097,67 +4097,67 @@
         <v>2</v>
       </c>
       <c r="CX8" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CY8" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="CZ8" t="n">
         <v>2.25</v>
       </c>
       <c r="DA8" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="DB8" t="n">
         <v>1.42</v>
       </c>
       <c r="DC8" t="n">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="DD8" t="n">
-        <v>4.36</v>
+        <v>4.34</v>
       </c>
       <c r="DE8" t="n">
         <v>0.1</v>
       </c>
       <c r="DF8" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="DH8" t="n">
-        <v>89.05</v>
+        <v>89.55</v>
       </c>
       <c r="DI8" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ8" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="DK8" t="n">
-        <v>5</v>
+        <v>4.95</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DM8" t="n">
-        <v>39</v>
+        <v>39.1</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="DP8" t="n">
-        <v>14.95</v>
+        <v>15.05</v>
       </c>
       <c r="DQ8" t="n">
-        <v>13.37</v>
+        <v>13.15</v>
       </c>
       <c r="DR8" t="n">
-        <v>8.890000000000001</v>
+        <v>8.75</v>
       </c>
       <c r="DS8" t="n">
         <v>0</v>
@@ -4169,28 +4169,28 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>45.37</v>
+        <v>45</v>
       </c>
       <c r="DW8" t="n">
         <v>0</v>
       </c>
       <c r="DX8" t="n">
-        <v>10</v>
+        <v>10.1</v>
       </c>
       <c r="DY8" t="n">
-        <v>6.79</v>
+        <v>6.95</v>
       </c>
       <c r="DZ8" t="n">
-        <v>3.21</v>
+        <v>3.15</v>
       </c>
       <c r="EA8" t="n">
-        <v>19.31</v>
+        <v>19.1</v>
       </c>
       <c r="EB8" t="n">
         <v>1.14</v>
       </c>
       <c r="EC8" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
     </row>
     <row r="9">
@@ -4224,7 +4224,7 @@
         <v>0.1</v>
       </c>
       <c r="J9" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="K9" t="n">
         <v>5.2</v>
@@ -4236,7 +4236,7 @@
         <v>54.6</v>
       </c>
       <c r="N9" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="O9" t="n">
         <v>2.7</v>
@@ -4287,7 +4287,7 @@
         <v>1.75</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="AF9" t="n">
         <v>0.3</v>
@@ -4536,7 +4536,7 @@
         <v>0</v>
       </c>
       <c r="DJ9" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="DK9" t="n">
         <v>4.95</v>
@@ -4548,7 +4548,7 @@
         <v>47.9</v>
       </c>
       <c r="DN9" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="DO9" t="n">
         <v>2.4</v>
@@ -4593,7 +4593,7 @@
         <v>1.6</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="10">
@@ -4603,94 +4603,94 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D10" t="n">
         <v>10</v>
       </c>
       <c r="E10" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="F10" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="G10" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="H10" t="n">
-        <v>95.22</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="K10" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="L10" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="M10" t="n">
-        <v>44.22</v>
+        <v>44.4</v>
       </c>
       <c r="N10" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="O10" t="n">
-        <v>1.56</v>
+        <v>1.9</v>
       </c>
       <c r="P10" t="n">
-        <v>12</v>
+        <v>11.7</v>
       </c>
       <c r="Q10" t="n">
-        <v>13.33</v>
+        <v>13.6</v>
       </c>
       <c r="R10" t="n">
-        <v>7.22</v>
+        <v>7.3</v>
       </c>
       <c r="S10" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="T10" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="U10" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="V10" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>53.44</v>
+        <v>54.3</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="Z10" t="n">
-        <v>12.56</v>
+        <v>13.2</v>
       </c>
       <c r="AA10" t="n">
-        <v>7.67</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AB10" t="n">
-        <v>4.89</v>
+        <v>4.9</v>
       </c>
       <c r="AC10" t="n">
-        <v>19.67</v>
+        <v>19.2</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.11</v>
+        <v>2.3</v>
       </c>
       <c r="AF10" t="n">
         <v>0</v>
@@ -4774,67 +4774,67 @@
         <v>2.8</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.79</v>
+        <v>2.85</v>
       </c>
       <c r="BH10" t="n">
-        <v>8.630000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.79</v>
+        <v>2.85</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.63</v>
+        <v>0.7</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="BM10" t="n">
         <v>1</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="BP10" t="n">
-        <v>4.11</v>
+        <v>4.25</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.53</v>
+        <v>4.55</v>
       </c>
       <c r="BR10" t="n">
-        <v>94.73999999999999</v>
+        <v>95</v>
       </c>
       <c r="BS10" t="n">
-        <v>84.20999999999999</v>
+        <v>85</v>
       </c>
       <c r="BT10" t="n">
-        <v>57.89</v>
+        <v>60</v>
       </c>
       <c r="BU10" t="n">
-        <v>31.58</v>
+        <v>35</v>
       </c>
       <c r="BV10" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BW10" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BX10" t="n">
-        <v>52.63</v>
+        <v>55</v>
       </c>
       <c r="BY10" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="BZ10" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.28</v>
+        <v>3.29</v>
       </c>
       <c r="CB10" t="n">
         <v>3.42</v>
@@ -4852,25 +4852,25 @@
         <v>2.89</v>
       </c>
       <c r="CG10" t="n">
-        <v>2.85</v>
+        <v>2.84</v>
       </c>
       <c r="CH10" t="n">
         <v>1.38</v>
       </c>
       <c r="CI10" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CJ10" t="n">
         <v>1.82</v>
       </c>
       <c r="CK10" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CL10" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="CN10" t="n">
         <v>1.74</v>
@@ -4882,7 +4882,7 @@
         <v>2.02</v>
       </c>
       <c r="CQ10" t="n">
-        <v>3.46</v>
+        <v>3.49</v>
       </c>
       <c r="CR10" t="n">
         <v>1.45</v>
@@ -4891,112 +4891,112 @@
         <v>3.12</v>
       </c>
       <c r="CT10" t="n">
-        <v>2.88</v>
+        <v>2.87</v>
       </c>
       <c r="CU10" t="n">
         <v>1.39</v>
       </c>
       <c r="CV10" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="CW10" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="CX10" t="n">
         <v>1.64</v>
       </c>
       <c r="CY10" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="CZ10" t="n">
         <v>2.23</v>
       </c>
       <c r="DA10" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="DB10" t="n">
         <v>1.34</v>
       </c>
       <c r="DC10" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="DD10" t="n">
-        <v>3.67</v>
+        <v>3.68</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="DG10" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="DH10" t="n">
-        <v>86.31</v>
+        <v>86.95</v>
       </c>
       <c r="DI10" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.58</v>
+        <v>2.65</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.47</v>
+        <v>4.65</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="DM10" t="n">
-        <v>40.1</v>
+        <v>40.4</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.89</v>
+        <v>0.95</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.42</v>
+        <v>2.55</v>
       </c>
       <c r="DP10" t="n">
-        <v>11.58</v>
+        <v>11.45</v>
       </c>
       <c r="DQ10" t="n">
-        <v>12.68</v>
+        <v>12.85</v>
       </c>
       <c r="DR10" t="n">
         <v>8.050000000000001</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>50.58</v>
+        <v>51.15</v>
       </c>
       <c r="DW10" t="n">
         <v>0.05</v>
       </c>
       <c r="DX10" t="n">
-        <v>12.37</v>
+        <v>12.7</v>
       </c>
       <c r="DY10" t="n">
-        <v>7.58</v>
+        <v>7.9</v>
       </c>
       <c r="DZ10" t="n">
-        <v>4.79</v>
+        <v>4.8</v>
       </c>
       <c r="EA10" t="n">
-        <v>17.26</v>
+        <v>17.15</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="EC10" t="n">
-        <v>2.47</v>
+        <v>2.55</v>
       </c>
     </row>
     <row r="11">
@@ -5006,13 +5006,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C11" t="n">
         <v>9</v>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -5078,10 +5078,10 @@
         <v>0.11</v>
       </c>
       <c r="Z11" t="n">
-        <v>13.67</v>
+        <v>13.44</v>
       </c>
       <c r="AA11" t="n">
-        <v>8.779999999999999</v>
+        <v>8.56</v>
       </c>
       <c r="AB11" t="n">
         <v>4.89</v>
@@ -5090,145 +5090,145 @@
         <v>19.44</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AE11" t="n">
         <v>2</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AH11" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>98.36</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>40.55</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>13.64</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>15.09</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>7.18</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>57.64</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>13.64</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>9.09</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>18.09</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="BG11" t="n">
         <v>2.5</v>
       </c>
-      <c r="AI11" t="n">
-        <v>96.5</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>3</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>39.6</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>56.7</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>18</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>2.47</v>
-      </c>
       <c r="BH11" t="n">
-        <v>9.630000000000001</v>
+        <v>9.75</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.37</v>
+        <v>0.4</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="BL11" t="n">
         <v>1</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="BO11" t="n">
-        <v>0.68</v>
+        <v>0.7</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.42</v>
+        <v>4.4</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.16</v>
+        <v>5.3</v>
       </c>
       <c r="BR11" t="n">
-        <v>89.47</v>
+        <v>90</v>
       </c>
       <c r="BS11" t="n">
-        <v>73.68000000000001</v>
+        <v>75</v>
       </c>
       <c r="BT11" t="n">
-        <v>52.63</v>
+        <v>55</v>
       </c>
       <c r="BU11" t="n">
-        <v>26.32</v>
+        <v>25</v>
       </c>
       <c r="BV11" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BW11" t="n">
         <v>0</v>
       </c>
       <c r="BX11" t="n">
-        <v>63.16</v>
+        <v>65</v>
       </c>
       <c r="BY11" t="n">
         <v>2.32</v>
@@ -5240,13 +5240,13 @@
         <v>3.3</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.46</v>
+        <v>3.47</v>
       </c>
       <c r="CC11" t="n">
-        <v>3.95</v>
+        <v>3.89</v>
       </c>
       <c r="CD11" t="n">
-        <v>4.21</v>
+        <v>4.19</v>
       </c>
       <c r="CE11" t="n">
         <v>1.42</v>
@@ -5264,19 +5264,19 @@
         <v>1.94</v>
       </c>
       <c r="CJ11" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CK11" t="n">
         <v>1.64</v>
       </c>
       <c r="CL11" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="CN11" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CO11" t="n">
         <v>1.32</v>
@@ -5330,76 +5330,76 @@
         <v>0.05</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="DG11" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="DH11" t="n">
-        <v>100.37</v>
+        <v>101.2</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.58</v>
+        <v>2.55</v>
       </c>
       <c r="DK11" t="n">
-        <v>4.84</v>
+        <v>5</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DM11" t="n">
-        <v>44.73</v>
+        <v>45</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="DO11" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="DP11" t="n">
-        <v>13.89</v>
+        <v>13.8</v>
       </c>
       <c r="DQ11" t="n">
-        <v>14.9</v>
+        <v>14.85</v>
       </c>
       <c r="DR11" t="n">
-        <v>7.95</v>
+        <v>7.8</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>57.42</v>
+        <v>57.9</v>
       </c>
       <c r="DW11" t="n">
         <v>0.1</v>
       </c>
       <c r="DX11" t="n">
-        <v>13.74</v>
+        <v>13.55</v>
       </c>
       <c r="DY11" t="n">
-        <v>9.210000000000001</v>
+        <v>8.85</v>
       </c>
       <c r="DZ11" t="n">
-        <v>4.53</v>
+        <v>4.7</v>
       </c>
       <c r="EA11" t="n">
-        <v>18.68</v>
+        <v>18.7</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="12">
@@ -5812,19 +5812,19 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C13" t="n">
         <v>9</v>
       </c>
       <c r="D13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E13" t="n">
         <v>0.33</v>
       </c>
       <c r="F13" t="n">
-        <v>2.11</v>
+        <v>2.22</v>
       </c>
       <c r="G13" t="n">
         <v>2.44</v>
@@ -5836,7 +5836,7 @@
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>3</v>
+        <v>3.11</v>
       </c>
       <c r="K13" t="n">
         <v>5.56</v>
@@ -5899,142 +5899,142 @@
         <v>1.41</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.89</v>
+        <v>3</v>
       </c>
       <c r="AF13" t="n">
         <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AI13" t="n">
-        <v>82.09999999999999</v>
+        <v>83.73</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AK13" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="AL13" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AM13" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>34.64</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>13.55</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>8.550000000000001</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>49.64</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>10.27</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>6.09</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>19.73</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BJ13" t="n">
         <v>0.4</v>
       </c>
-      <c r="AN13" t="n">
-        <v>33.1</v>
-      </c>
-      <c r="AO13" t="n">
+      <c r="BK13" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="BN13" t="n">
         <v>1.2</v>
       </c>
-      <c r="AP13" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>48.8</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>6</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="BH13" t="n">
-        <v>9.470000000000001</v>
-      </c>
-      <c r="BI13" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="BJ13" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="BK13" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="BL13" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="BM13" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="BN13" t="n">
-        <v>1.16</v>
-      </c>
       <c r="BO13" t="n">
-        <v>0.79</v>
+        <v>0.85</v>
       </c>
       <c r="BP13" t="n">
-        <v>4.26</v>
+        <v>4.45</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4.68</v>
+        <v>4.55</v>
       </c>
       <c r="BR13" t="n">
-        <v>78.95</v>
+        <v>80</v>
       </c>
       <c r="BS13" t="n">
-        <v>63.16</v>
+        <v>65</v>
       </c>
       <c r="BT13" t="n">
-        <v>36.84</v>
+        <v>40</v>
       </c>
       <c r="BU13" t="n">
-        <v>10.53</v>
+        <v>15</v>
       </c>
       <c r="BV13" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BW13" t="n">
         <v>0</v>
       </c>
       <c r="BX13" t="n">
-        <v>47.37</v>
+        <v>50</v>
       </c>
       <c r="BY13" t="n">
         <v>2.3</v>
@@ -6049,19 +6049,19 @@
         <v>3.15</v>
       </c>
       <c r="CC13" t="n">
-        <v>3.02</v>
+        <v>3</v>
       </c>
       <c r="CD13" t="n">
-        <v>3.22</v>
+        <v>3.23</v>
       </c>
       <c r="CE13" t="n">
         <v>1.49</v>
       </c>
       <c r="CF13" t="n">
-        <v>3.26</v>
+        <v>3.25</v>
       </c>
       <c r="CG13" t="n">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="CH13" t="n">
         <v>1.31</v>
@@ -6070,142 +6070,142 @@
         <v>1.8</v>
       </c>
       <c r="CJ13" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CK13" t="n">
         <v>1.6</v>
       </c>
       <c r="CL13" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="CN13" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CO13" t="n">
         <v>1.42</v>
       </c>
       <c r="CP13" t="n">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="CQ13" t="n">
-        <v>4.28</v>
+        <v>4.25</v>
       </c>
       <c r="CR13" t="n">
         <v>1.53</v>
       </c>
       <c r="CS13" t="n">
-        <v>3.2</v>
+        <v>3.19</v>
       </c>
       <c r="CT13" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="CU13" t="n">
         <v>1.37</v>
       </c>
       <c r="CV13" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="CW13" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CX13" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CY13" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="CZ13" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="DA13" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="DB13" t="n">
         <v>1.45</v>
       </c>
       <c r="DC13" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="DD13" t="n">
-        <v>4.65</v>
+        <v>4.6</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DF13" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="DG13" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="DH13" t="n">
-        <v>85.31999999999999</v>
+        <v>86.05</v>
       </c>
       <c r="DI13" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ13" t="n">
-        <v>3.32</v>
+        <v>3.35</v>
       </c>
       <c r="DK13" t="n">
-        <v>4.69</v>
+        <v>4.7</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.26</v>
+        <v>0.3</v>
       </c>
       <c r="DM13" t="n">
-        <v>38.26</v>
+        <v>38.85</v>
       </c>
       <c r="DN13" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="DO13" t="n">
-        <v>2.26</v>
+        <v>2.35</v>
       </c>
       <c r="DP13" t="n">
-        <v>12.89</v>
+        <v>12.65</v>
       </c>
       <c r="DQ13" t="n">
-        <v>14.47</v>
+        <v>14.3</v>
       </c>
       <c r="DR13" t="n">
-        <v>8.27</v>
+        <v>8.1</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>50.11</v>
+        <v>50.5</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DX13" t="n">
-        <v>11.1</v>
+        <v>11.15</v>
       </c>
       <c r="DY13" t="n">
-        <v>6.79</v>
+        <v>6.8</v>
       </c>
       <c r="DZ13" t="n">
-        <v>4.32</v>
+        <v>4.35</v>
       </c>
       <c r="EA13" t="n">
-        <v>21.21</v>
+        <v>21.25</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="EC13" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
     </row>
     <row r="14">
@@ -6618,13 +6618,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C15" t="n">
         <v>10</v>
       </c>
       <c r="D15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E15" t="n">
         <v>0.1</v>
@@ -6642,7 +6642,7 @@
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="K15" t="n">
         <v>3.7</v>
@@ -6654,7 +6654,7 @@
         <v>46.9</v>
       </c>
       <c r="N15" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="O15" t="n">
         <v>1.7</v>
@@ -6705,142 +6705,142 @@
         <v>1.72</v>
       </c>
       <c r="AE15" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AH15" t="n">
         <v>2.3</v>
       </c>
-      <c r="AF15" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>2.67</v>
-      </c>
       <c r="AI15" t="n">
-        <v>90.56</v>
+        <v>90.3</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.44</v>
+        <v>2.6</v>
       </c>
       <c r="AL15" t="n">
-        <v>4.11</v>
+        <v>4.2</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.22</v>
+        <v>0.1</v>
       </c>
       <c r="AN15" t="n">
-        <v>46.33</v>
+        <v>45.4</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.44</v>
+        <v>1.2</v>
       </c>
       <c r="AQ15" t="n">
-        <v>12.33</v>
+        <v>12</v>
       </c>
       <c r="AR15" t="n">
-        <v>12.33</v>
+        <v>12.2</v>
       </c>
       <c r="AS15" t="n">
-        <v>8.220000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AX15" t="n">
         <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>51.22</v>
+        <v>50.8</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="BA15" t="n">
-        <v>9.779999999999999</v>
+        <v>10.1</v>
       </c>
       <c r="BB15" t="n">
-        <v>6.67</v>
+        <v>6.6</v>
       </c>
       <c r="BC15" t="n">
-        <v>3.11</v>
+        <v>3.5</v>
       </c>
       <c r="BD15" t="n">
-        <v>23.89</v>
+        <v>22.8</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.89</v>
+        <v>2.1</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="BH15" t="n">
-        <v>8.26</v>
+        <v>8.35</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.74</v>
+        <v>0.7</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.21</v>
+        <v>0.25</v>
       </c>
       <c r="BL15" t="n">
         <v>0.95</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.74</v>
+        <v>0.8</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="BO15" t="n">
         <v>0.95</v>
       </c>
       <c r="BP15" t="n">
-        <v>3.58</v>
+        <v>3.35</v>
       </c>
       <c r="BQ15" t="n">
-        <v>4.68</v>
+        <v>4.4</v>
       </c>
       <c r="BR15" t="n">
         <v>100</v>
       </c>
       <c r="BS15" t="n">
-        <v>73.68000000000001</v>
+        <v>75</v>
       </c>
       <c r="BT15" t="n">
-        <v>52.63</v>
+        <v>55</v>
       </c>
       <c r="BU15" t="n">
-        <v>26.32</v>
+        <v>30</v>
       </c>
       <c r="BV15" t="n">
-        <v>10.53</v>
+        <v>10</v>
       </c>
       <c r="BW15" t="n">
         <v>0</v>
       </c>
       <c r="BX15" t="n">
-        <v>57.89</v>
+        <v>60</v>
       </c>
       <c r="BY15" t="n">
         <v>2.29</v>
@@ -6849,37 +6849,37 @@
         <v>2.3</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.21</v>
+        <v>3.22</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.35</v>
+        <v>3.36</v>
       </c>
       <c r="CC15" t="n">
-        <v>4.06</v>
+        <v>4.08</v>
       </c>
       <c r="CD15" t="n">
-        <v>4.47</v>
+        <v>4.45</v>
       </c>
       <c r="CE15" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CF15" t="n">
-        <v>3.11</v>
+        <v>3.1</v>
       </c>
       <c r="CG15" t="n">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="CH15" t="n">
         <v>1.33</v>
       </c>
       <c r="CI15" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CJ15" t="n">
         <v>1.95</v>
       </c>
       <c r="CK15" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CL15" t="n">
         <v>2.16</v>
@@ -6903,7 +6903,7 @@
         <v>1.48</v>
       </c>
       <c r="CS15" t="n">
-        <v>3.2</v>
+        <v>3.21</v>
       </c>
       <c r="CT15" t="n">
         <v>2.76</v>
@@ -6942,40 +6942,40 @@
         <v>0.1</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="DG15" t="n">
-        <v>2.32</v>
+        <v>2.15</v>
       </c>
       <c r="DH15" t="n">
-        <v>88.63</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="DI15" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ15" t="n">
-        <v>2.47</v>
+        <v>2.6</v>
       </c>
       <c r="DK15" t="n">
-        <v>3.89</v>
+        <v>3.95</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.26</v>
+        <v>0.2</v>
       </c>
       <c r="DM15" t="n">
-        <v>46.63</v>
+        <v>46.15</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.74</v>
+        <v>0.8</v>
       </c>
       <c r="DO15" t="n">
-        <v>1.58</v>
+        <v>1.45</v>
       </c>
       <c r="DP15" t="n">
-        <v>13.31</v>
+        <v>13.1</v>
       </c>
       <c r="DQ15" t="n">
-        <v>12.37</v>
+        <v>12.3</v>
       </c>
       <c r="DR15" t="n">
         <v>8.050000000000001</v>
@@ -6990,28 +6990,28 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>51.31</v>
+        <v>51.1</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DX15" t="n">
-        <v>12.58</v>
+        <v>12.6</v>
       </c>
       <c r="DY15" t="n">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="DZ15" t="n">
-        <v>4.68</v>
+        <v>4.8</v>
       </c>
       <c r="EA15" t="n">
-        <v>22.84</v>
+        <v>22.35</v>
       </c>
       <c r="EB15" t="n">
         <v>1.46</v>
       </c>
       <c r="EC15" t="n">
-        <v>2.11</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="16">
@@ -7174,10 +7174,10 @@
         <v>0.2</v>
       </c>
       <c r="BA16" t="n">
-        <v>11.6</v>
+        <v>11.5</v>
       </c>
       <c r="BB16" t="n">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="BC16" t="n">
         <v>4.8</v>
@@ -7186,7 +7186,7 @@
         <v>17.3</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="BF16" t="n">
         <v>3</v>
@@ -7399,10 +7399,10 @@
         <v>0.1</v>
       </c>
       <c r="DX16" t="n">
-        <v>13.6</v>
+        <v>13.55</v>
       </c>
       <c r="DY16" t="n">
-        <v>8.050000000000001</v>
+        <v>8</v>
       </c>
       <c r="DZ16" t="n">
         <v>5.55</v>
@@ -7436,7 +7436,7 @@
         <v>0.2</v>
       </c>
       <c r="F17" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="G17" t="n">
         <v>1</v>
@@ -7448,7 +7448,7 @@
         <v>0.1</v>
       </c>
       <c r="J17" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="K17" t="n">
         <v>3.1</v>
@@ -7460,7 +7460,7 @@
         <v>32.4</v>
       </c>
       <c r="N17" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="O17" t="n">
         <v>1.7</v>
@@ -7511,7 +7511,7 @@
         <v>1.14</v>
       </c>
       <c r="AE17" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="AF17" t="n">
         <v>0</v>
@@ -7529,7 +7529,7 @@
         <v>0.2</v>
       </c>
       <c r="AK17" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="AL17" t="n">
         <v>3.7</v>
@@ -7541,7 +7541,7 @@
         <v>31.6</v>
       </c>
       <c r="AO17" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AP17" t="n">
         <v>1.3</v>
@@ -7592,7 +7592,7 @@
         <v>1.29</v>
       </c>
       <c r="BF17" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="BG17" t="n">
         <v>2.9</v>
@@ -7748,7 +7748,7 @@
         <v>0.1</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="DG17" t="n">
         <v>1.7</v>
@@ -7760,7 +7760,7 @@
         <v>0.15</v>
       </c>
       <c r="DJ17" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="DK17" t="n">
         <v>3.4</v>
@@ -7817,7 +7817,7 @@
         <v>1.21</v>
       </c>
       <c r="EC17" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
     </row>
     <row r="18">
@@ -8230,10 +8230,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D19" t="n">
         <v>10</v>
@@ -8242,49 +8242,49 @@
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="G19" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="H19" t="n">
-        <v>94.67</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="J19" t="n">
-        <v>3.67</v>
+        <v>3.6</v>
       </c>
       <c r="K19" t="n">
-        <v>4.44</v>
+        <v>4.1</v>
       </c>
       <c r="L19" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="M19" t="n">
-        <v>43.33</v>
+        <v>42.1</v>
       </c>
       <c r="N19" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="O19" t="n">
-        <v>2.78</v>
+        <v>2.6</v>
       </c>
       <c r="P19" t="n">
-        <v>12.89</v>
+        <v>13.6</v>
       </c>
       <c r="Q19" t="n">
-        <v>15.56</v>
+        <v>15.8</v>
       </c>
       <c r="R19" t="n">
-        <v>7.22</v>
+        <v>7.4</v>
       </c>
       <c r="S19" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="T19" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
@@ -8296,34 +8296,34 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>52.22</v>
+        <v>51.7</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="Z19" t="n">
-        <v>11.56</v>
+        <v>11.2</v>
       </c>
       <c r="AA19" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AB19" t="n">
-        <v>3.56</v>
+        <v>3.4</v>
       </c>
       <c r="AC19" t="n">
-        <v>23</v>
+        <v>22.8</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="AF19" t="n">
         <v>0.1</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AH19" t="n">
         <v>3.3</v>
@@ -8335,7 +8335,7 @@
         <v>0.1</v>
       </c>
       <c r="AK19" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="AL19" t="n">
         <v>5.6</v>
@@ -8398,73 +8398,73 @@
         <v>1.39</v>
       </c>
       <c r="BF19" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.42</v>
+        <v>2.45</v>
       </c>
       <c r="BH19" t="n">
-        <v>10.26</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.42</v>
+        <v>2.45</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.37</v>
+        <v>0.4</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.68</v>
+        <v>0.7</v>
       </c>
       <c r="BM19" t="n">
         <v>0.95</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="BO19" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="BP19" t="n">
-        <v>5.21</v>
+        <v>5.15</v>
       </c>
       <c r="BQ19" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="BR19" t="n">
+        <v>95</v>
+      </c>
+      <c r="BS19" t="n">
+        <v>65</v>
+      </c>
+      <c r="BT19" t="n">
+        <v>40</v>
+      </c>
+      <c r="BU19" t="n">
+        <v>25</v>
+      </c>
+      <c r="BV19" t="n">
+        <v>15</v>
+      </c>
+      <c r="BW19" t="n">
         <v>5</v>
       </c>
-      <c r="BR19" t="n">
-        <v>94.73999999999999</v>
-      </c>
-      <c r="BS19" t="n">
-        <v>63.16</v>
-      </c>
-      <c r="BT19" t="n">
-        <v>36.84</v>
-      </c>
-      <c r="BU19" t="n">
-        <v>26.32</v>
-      </c>
-      <c r="BV19" t="n">
-        <v>15.79</v>
-      </c>
-      <c r="BW19" t="n">
-        <v>5.26</v>
-      </c>
       <c r="BX19" t="n">
-        <v>52.63</v>
+        <v>55</v>
       </c>
       <c r="BY19" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="BZ19" t="n">
-        <v>2.43</v>
+        <v>2.52</v>
       </c>
       <c r="CA19" t="n">
-        <v>3.16</v>
+        <v>3.14</v>
       </c>
       <c r="CB19" t="n">
-        <v>3.29</v>
+        <v>3.27</v>
       </c>
       <c r="CC19" t="n">
         <v>3.76</v>
@@ -8473,43 +8473,43 @@
         <v>4.39</v>
       </c>
       <c r="CE19" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="CF19" t="n">
-        <v>3.17</v>
+        <v>3.18</v>
       </c>
       <c r="CG19" t="n">
-        <v>2.59</v>
+        <v>2.57</v>
       </c>
       <c r="CH19" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="CI19" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CJ19" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="CK19" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="CL19" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="CM19" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="CN19" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CO19" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CP19" t="n">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="CQ19" t="n">
-        <v>4.17</v>
+        <v>4.21</v>
       </c>
       <c r="CR19" t="n">
         <v>1.51</v>
@@ -8524,10 +8524,10 @@
         <v>1.37</v>
       </c>
       <c r="CV19" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="CW19" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="CX19" t="n">
         <v>1.6</v>
@@ -8542,88 +8542,88 @@
         <v>1.81</v>
       </c>
       <c r="DB19" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="DC19" t="n">
-        <v>2.29</v>
+        <v>2.32</v>
       </c>
       <c r="DD19" t="n">
-        <v>4.21</v>
+        <v>4.3</v>
       </c>
       <c r="DE19" t="n">
         <v>0.05</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="DG19" t="n">
-        <v>2.53</v>
+        <v>2.4</v>
       </c>
       <c r="DH19" t="n">
-        <v>92.11</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="DI19" t="n">
         <v>0.1</v>
       </c>
       <c r="DJ19" t="n">
-        <v>3.32</v>
+        <v>3.35</v>
       </c>
       <c r="DK19" t="n">
-        <v>5.05</v>
+        <v>4.85</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="DM19" t="n">
-        <v>42.89</v>
+        <v>42.3</v>
       </c>
       <c r="DN19" t="n">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="DO19" t="n">
-        <v>2.47</v>
+        <v>2.4</v>
       </c>
       <c r="DP19" t="n">
-        <v>13.16</v>
+        <v>13.5</v>
       </c>
       <c r="DQ19" t="n">
-        <v>15.53</v>
+        <v>15.65</v>
       </c>
       <c r="DR19" t="n">
-        <v>6.95</v>
+        <v>7.05</v>
       </c>
       <c r="DS19" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DT19" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DU19" t="n">
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>51.16</v>
+        <v>50.95</v>
       </c>
       <c r="DW19" t="n">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
       <c r="DX19" t="n">
-        <v>12.48</v>
+        <v>12.25</v>
       </c>
       <c r="DY19" t="n">
-        <v>9</v>
+        <v>8.85</v>
       </c>
       <c r="DZ19" t="n">
-        <v>3.48</v>
+        <v>3.4</v>
       </c>
       <c r="EA19" t="n">
-        <v>20.47</v>
+        <v>20.5</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="EC19" t="n">
-        <v>2.79</v>
+        <v>2.85</v>
       </c>
     </row>
     <row r="20">
@@ -9108,10 +9108,10 @@
         <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>12.4</v>
+        <v>12.5</v>
       </c>
       <c r="AA21" t="n">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AB21" t="n">
         <v>3.8</v>
@@ -9414,10 +9414,10 @@
         <v>0.05</v>
       </c>
       <c r="DX21" t="n">
-        <v>10.75</v>
+        <v>10.8</v>
       </c>
       <c r="DY21" t="n">
-        <v>7.75</v>
+        <v>7.8</v>
       </c>
       <c r="DZ21" t="n">
         <v>3</v>
@@ -9439,10 +9439,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C22" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D22" t="n">
         <v>9</v>
@@ -9451,79 +9451,79 @@
         <v>0</v>
       </c>
       <c r="F22" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="G22" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="H22" t="n">
+        <v>112.27</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="K22" t="n">
+        <v>5.36</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="M22" t="n">
+        <v>51.45</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="O22" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="P22" t="n">
+        <v>12.82</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>10.64</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="S22" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" t="n">
+        <v>46.45</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>13.55</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>8.359999999999999</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>5.18</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>19.55</v>
+      </c>
+      <c r="AD22" t="n">
         <v>1.6</v>
-      </c>
-      <c r="G22" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="H22" t="n">
-        <v>111</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="K22" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="M22" t="n">
-        <v>47.8</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="O22" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="P22" t="n">
-        <v>13</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="R22" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="S22" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="T22" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="V22" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="W22" t="n">
-        <v>0</v>
-      </c>
-      <c r="X22" t="n">
-        <v>45.8</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.58</v>
       </c>
       <c r="AE22" t="n">
         <v>2</v>
@@ -9610,70 +9610,70 @@
         <v>3.33</v>
       </c>
       <c r="BG22" t="n">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="BH22" t="n">
-        <v>9.58</v>
+        <v>9.6</v>
       </c>
       <c r="BI22" t="n">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="BJ22" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BK22" t="n">
-        <v>0.53</v>
+        <v>0.55</v>
       </c>
       <c r="BL22" t="n">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="BM22" t="n">
-        <v>0.53</v>
+        <v>0.6</v>
       </c>
       <c r="BN22" t="n">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="BO22" t="n">
         <v>1.05</v>
       </c>
       <c r="BP22" t="n">
-        <v>4.63</v>
+        <v>4.35</v>
       </c>
       <c r="BQ22" t="n">
-        <v>4.89</v>
+        <v>4.6</v>
       </c>
       <c r="BR22" t="n">
-        <v>94.73999999999999</v>
+        <v>95</v>
       </c>
       <c r="BS22" t="n">
-        <v>57.89</v>
+        <v>60</v>
       </c>
       <c r="BT22" t="n">
-        <v>42.11</v>
+        <v>45</v>
       </c>
       <c r="BU22" t="n">
-        <v>21.05</v>
+        <v>25</v>
       </c>
       <c r="BV22" t="n">
-        <v>15.79</v>
+        <v>15</v>
       </c>
       <c r="BW22" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BX22" t="n">
-        <v>52.63</v>
+        <v>55</v>
       </c>
       <c r="BY22" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BZ22" t="n">
         <v>2.11</v>
       </c>
-      <c r="BZ22" t="n">
-        <v>2.13</v>
-      </c>
       <c r="CA22" t="n">
-        <v>3.2</v>
+        <v>3.21</v>
       </c>
       <c r="CB22" t="n">
-        <v>3.29</v>
+        <v>3.3</v>
       </c>
       <c r="CC22" t="n">
         <v>3.22</v>
@@ -9694,7 +9694,7 @@
         <v>1.34</v>
       </c>
       <c r="CI22" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CJ22" t="n">
         <v>1.88</v>
@@ -9703,46 +9703,46 @@
         <v>1.62</v>
       </c>
       <c r="CL22" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="CM22" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="CN22" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CO22" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CP22" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="CQ22" t="n">
-        <v>3.92</v>
+        <v>3.91</v>
       </c>
       <c r="CR22" t="n">
         <v>1.48</v>
       </c>
       <c r="CS22" t="n">
-        <v>3.11</v>
+        <v>3.12</v>
       </c>
       <c r="CT22" t="n">
         <v>2.79</v>
       </c>
       <c r="CU22" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CV22" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CW22" t="n">
         <v>1.97</v>
       </c>
       <c r="CX22" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CY22" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="CZ22" t="n">
         <v>2.22</v>
@@ -9763,76 +9763,76 @@
         <v>0.1</v>
       </c>
       <c r="DF22" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="DG22" t="n">
-        <v>2.26</v>
+        <v>2.1</v>
       </c>
       <c r="DH22" t="n">
-        <v>99.48</v>
+        <v>100.75</v>
       </c>
       <c r="DI22" t="n">
         <v>0</v>
       </c>
       <c r="DJ22" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="DK22" t="n">
-        <v>4.47</v>
+        <v>4.5</v>
       </c>
       <c r="DL22" t="n">
-        <v>0.47</v>
+        <v>0.4</v>
       </c>
       <c r="DM22" t="n">
-        <v>41.53</v>
+        <v>43.85</v>
       </c>
       <c r="DN22" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="DO22" t="n">
-        <v>2.21</v>
+        <v>2.05</v>
       </c>
       <c r="DP22" t="n">
-        <v>12.47</v>
+        <v>12.4</v>
       </c>
       <c r="DQ22" t="n">
-        <v>10.79</v>
+        <v>10.65</v>
       </c>
       <c r="DR22" t="n">
-        <v>7.89</v>
+        <v>7.65</v>
       </c>
       <c r="DS22" t="n">
-        <v>0.21</v>
+        <v>0.25</v>
       </c>
       <c r="DT22" t="n">
-        <v>0.21</v>
+        <v>0.25</v>
       </c>
       <c r="DU22" t="n">
         <v>0</v>
       </c>
       <c r="DV22" t="n">
-        <v>44.21</v>
+        <v>44.65</v>
       </c>
       <c r="DW22" t="n">
-        <v>0.21</v>
+        <v>0.25</v>
       </c>
       <c r="DX22" t="n">
-        <v>11.1</v>
+        <v>11.25</v>
       </c>
       <c r="DY22" t="n">
-        <v>6.58</v>
+        <v>6.8</v>
       </c>
       <c r="DZ22" t="n">
-        <v>4.53</v>
+        <v>4.45</v>
       </c>
       <c r="EA22" t="n">
-        <v>19.74</v>
+        <v>19.6</v>
       </c>
       <c r="EB22" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="EC22" t="n">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="23">
@@ -9842,13 +9842,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C23" t="n">
         <v>10</v>
       </c>
       <c r="D23" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E23" t="n">
         <v>0.2</v>
@@ -9935,49 +9935,49 @@
         <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AI23" t="n">
-        <v>91.33</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AK23" t="n">
         <v>2</v>
       </c>
       <c r="AL23" t="n">
-        <v>3.89</v>
+        <v>3.8</v>
       </c>
       <c r="AM23" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AN23" t="n">
-        <v>37.22</v>
+        <v>37.2</v>
       </c>
       <c r="AO23" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="AP23" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AQ23" t="n">
-        <v>11.78</v>
+        <v>12.4</v>
       </c>
       <c r="AR23" t="n">
-        <v>18.89</v>
+        <v>19</v>
       </c>
       <c r="AS23" t="n">
-        <v>9.33</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT23" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="AU23" t="n">
-        <v>0.78</v>
+        <v>0.9</v>
       </c>
       <c r="AV23" t="n">
         <v>0</v>
@@ -9989,73 +9989,73 @@
         <v>0</v>
       </c>
       <c r="AY23" t="n">
-        <v>56.89</v>
+        <v>56.5</v>
       </c>
       <c r="AZ23" t="n">
         <v>0</v>
       </c>
       <c r="BA23" t="n">
-        <v>9.890000000000001</v>
+        <v>10.1</v>
       </c>
       <c r="BB23" t="n">
-        <v>7.22</v>
+        <v>7.2</v>
       </c>
       <c r="BC23" t="n">
-        <v>2.67</v>
+        <v>2.9</v>
       </c>
       <c r="BD23" t="n">
-        <v>18</v>
+        <v>18.2</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="BF23" t="n">
         <v>2</v>
       </c>
       <c r="BG23" t="n">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="BH23" t="n">
-        <v>7.58</v>
+        <v>7.4</v>
       </c>
       <c r="BI23" t="n">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="BJ23" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="BK23" t="n">
-        <v>0.26</v>
+        <v>0.3</v>
       </c>
       <c r="BL23" t="n">
-        <v>0.37</v>
+        <v>0.4</v>
       </c>
       <c r="BM23" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="BN23" t="n">
-        <v>0.84</v>
+        <v>0.9</v>
       </c>
       <c r="BO23" t="n">
         <v>0.95</v>
       </c>
       <c r="BP23" t="n">
-        <v>3.63</v>
+        <v>3.65</v>
       </c>
       <c r="BQ23" t="n">
-        <v>3.95</v>
+        <v>3.75</v>
       </c>
       <c r="BR23" t="n">
-        <v>78.95</v>
+        <v>80</v>
       </c>
       <c r="BS23" t="n">
-        <v>47.37</v>
+        <v>50</v>
       </c>
       <c r="BT23" t="n">
-        <v>31.58</v>
+        <v>35</v>
       </c>
       <c r="BU23" t="n">
-        <v>21.05</v>
+        <v>20</v>
       </c>
       <c r="BV23" t="n">
         <v>0</v>
@@ -10064,7 +10064,7 @@
         <v>0</v>
       </c>
       <c r="BX23" t="n">
-        <v>42.11</v>
+        <v>45</v>
       </c>
       <c r="BY23" t="n">
         <v>1.79</v>
@@ -10073,55 +10073,55 @@
         <v>1.84</v>
       </c>
       <c r="CA23" t="n">
-        <v>3.23</v>
+        <v>3.22</v>
       </c>
       <c r="CB23" t="n">
-        <v>3.36</v>
+        <v>3.33</v>
       </c>
       <c r="CC23" t="n">
-        <v>3.05</v>
+        <v>2.99</v>
       </c>
       <c r="CD23" t="n">
-        <v>3.38</v>
+        <v>3.3</v>
       </c>
       <c r="CE23" t="n">
         <v>1.47</v>
       </c>
       <c r="CF23" t="n">
-        <v>3.21</v>
+        <v>3.22</v>
       </c>
       <c r="CG23" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="CH23" t="n">
         <v>1.31</v>
       </c>
       <c r="CI23" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CJ23" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="CK23" t="n">
         <v>1.7</v>
       </c>
       <c r="CL23" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="CM23" t="n">
         <v>2.07</v>
       </c>
       <c r="CN23" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CO23" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CP23" t="n">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="CQ23" t="n">
-        <v>4.16</v>
+        <v>4.2</v>
       </c>
       <c r="CR23" t="n">
         <v>1.51</v>
@@ -10136,10 +10136,10 @@
         <v>1.37</v>
       </c>
       <c r="CV23" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CW23" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="CX23" t="n">
         <v>1.77</v>
@@ -10154,55 +10154,55 @@
         <v>1.65</v>
       </c>
       <c r="DB23" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="DC23" t="n">
-        <v>2.39</v>
+        <v>2.41</v>
       </c>
       <c r="DD23" t="n">
-        <v>4.53</v>
+        <v>4.6</v>
       </c>
       <c r="DE23" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DF23" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="DG23" t="n">
-        <v>1.79</v>
+        <v>1.7</v>
       </c>
       <c r="DH23" t="n">
-        <v>93.52</v>
+        <v>92.95</v>
       </c>
       <c r="DI23" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ23" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="DK23" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="DL23" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DM23" t="n">
-        <v>37.42</v>
+        <v>37.4</v>
       </c>
       <c r="DN23" t="n">
-        <v>0.48</v>
+        <v>0.5</v>
       </c>
       <c r="DO23" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="DP23" t="n">
-        <v>12.69</v>
+        <v>12.95</v>
       </c>
       <c r="DQ23" t="n">
-        <v>17.37</v>
+        <v>17.5</v>
       </c>
       <c r="DR23" t="n">
-        <v>7.79</v>
+        <v>7.8</v>
       </c>
       <c r="DS23" t="n">
         <v>0</v>
@@ -10214,28 +10214,28 @@
         <v>0</v>
       </c>
       <c r="DV23" t="n">
-        <v>55.63</v>
+        <v>55.5</v>
       </c>
       <c r="DW23" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DX23" t="n">
-        <v>11</v>
+        <v>11.05</v>
       </c>
       <c r="DY23" t="n">
-        <v>7.47</v>
+        <v>7.45</v>
       </c>
       <c r="DZ23" t="n">
-        <v>3.53</v>
+        <v>3.6</v>
       </c>
       <c r="EA23" t="n">
-        <v>18.32</v>
+        <v>18.4</v>
       </c>
       <c r="EB23" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="EC23" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Spain_Segunda_División_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Spain_Segunda_División_2025-2026.xlsx
@@ -645,7 +645,7 @@
     <col width="9.6" customWidth="1" min="73" max="73"/>
     <col width="9.6" customWidth="1" min="74" max="74"/>
     <col width="9.6" customWidth="1" min="75" max="75"/>
-    <col width="7.199999999999999" customWidth="1" min="76" max="76"/>
+    <col width="8.4" customWidth="1" min="76" max="76"/>
     <col width="18" customWidth="1" min="77" max="77"/>
     <col width="27.6" customWidth="1" min="78" max="78"/>
     <col width="18" customWidth="1" min="79" max="79"/>
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C2" t="n">
         <v>10</v>
       </c>
       <c r="D2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -1421,7 +1421,7 @@
         <v>2.8</v>
       </c>
       <c r="P2" t="n">
-        <v>9.9</v>
+        <v>10</v>
       </c>
       <c r="Q2" t="n">
         <v>8.4</v>
@@ -1445,7 +1445,7 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>43.4</v>
+        <v>43.3</v>
       </c>
       <c r="Y2" t="n">
         <v>0.1</v>
@@ -1469,139 +1469,139 @@
         <v>1.6</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AH2" t="n">
-        <v>2</v>
+        <v>2.18</v>
       </c>
       <c r="AI2" t="n">
-        <v>86.3</v>
+        <v>85.91</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AK2" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="AL2" t="n">
-        <v>4.3</v>
+        <v>4.64</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.6</v>
+        <v>0.73</v>
       </c>
       <c r="AN2" t="n">
-        <v>39.2</v>
+        <v>41.45</v>
       </c>
       <c r="AO2" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AP2" t="n">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="AQ2" t="n">
-        <v>12.7</v>
+        <v>12.64</v>
       </c>
       <c r="AR2" t="n">
-        <v>13.1</v>
+        <v>13.73</v>
       </c>
       <c r="AS2" t="n">
-        <v>9.1</v>
+        <v>8.82</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AX2" t="n">
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>42.8</v>
+        <v>43.82</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="BA2" t="n">
-        <v>11.5</v>
+        <v>12.27</v>
       </c>
       <c r="BB2" t="n">
-        <v>6.9</v>
+        <v>7.55</v>
       </c>
       <c r="BC2" t="n">
-        <v>4.6</v>
+        <v>4.73</v>
       </c>
       <c r="BD2" t="n">
-        <v>23.5</v>
+        <v>23.36</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="BF2" t="n">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="BG2" t="n">
-        <v>3</v>
+        <v>2.86</v>
       </c>
       <c r="BH2" t="n">
-        <v>10.55</v>
+        <v>10.52</v>
       </c>
       <c r="BI2" t="n">
-        <v>3</v>
+        <v>2.86</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.8</v>
+        <v>0.76</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="BN2" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="BO2" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="BP2" t="n">
         <v>5.1</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.4</v>
+        <v>5.38</v>
       </c>
       <c r="BR2" t="n">
-        <v>85</v>
+        <v>80.95</v>
       </c>
       <c r="BS2" t="n">
-        <v>70</v>
+        <v>66.67</v>
       </c>
       <c r="BT2" t="n">
-        <v>55</v>
+        <v>52.38</v>
       </c>
       <c r="BU2" t="n">
-        <v>40</v>
+        <v>38.1</v>
       </c>
       <c r="BV2" t="n">
-        <v>25</v>
+        <v>23.81</v>
       </c>
       <c r="BW2" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BX2" t="n">
-        <v>60</v>
+        <v>57.14</v>
       </c>
       <c r="BY2" t="n">
         <v>2.17</v>
@@ -1610,16 +1610,16 @@
         <v>2.19</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.29</v>
+        <v>3.28</v>
       </c>
       <c r="CB2" t="n">
         <v>3.49</v>
       </c>
       <c r="CC2" t="n">
-        <v>3.83</v>
+        <v>3.7</v>
       </c>
       <c r="CD2" t="n">
-        <v>4.35</v>
+        <v>4.19</v>
       </c>
       <c r="CE2" t="n">
         <v>1.39</v>
@@ -1634,7 +1634,7 @@
         <v>1.4</v>
       </c>
       <c r="CI2" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="CJ2" t="n">
         <v>1.76</v>
@@ -1661,7 +1661,7 @@
         <v>3.32</v>
       </c>
       <c r="CR2" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CS2" t="n">
         <v>2.96</v>
@@ -1673,10 +1673,10 @@
         <v>1.43</v>
       </c>
       <c r="CV2" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="CW2" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CX2" t="n">
         <v>1.52</v>
@@ -1685,7 +1685,7 @@
         <v>1.87</v>
       </c>
       <c r="CZ2" t="n">
-        <v>2.43</v>
+        <v>2.44</v>
       </c>
       <c r="DA2" t="n">
         <v>1.93</v>
@@ -1694,85 +1694,85 @@
         <v>1.31</v>
       </c>
       <c r="DC2" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="DD2" t="n">
-        <v>3.46</v>
+        <v>3.44</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.35</v>
+        <v>2.43</v>
       </c>
       <c r="DH2" t="n">
-        <v>88.7</v>
+        <v>88.38</v>
       </c>
       <c r="DI2" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="DK2" t="n">
-        <v>4.9</v>
+        <v>5.05</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.45</v>
+        <v>0.53</v>
       </c>
       <c r="DM2" t="n">
-        <v>42.05</v>
+        <v>43.09</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.55</v>
+        <v>2.62</v>
       </c>
       <c r="DP2" t="n">
-        <v>11.3</v>
+        <v>11.38</v>
       </c>
       <c r="DQ2" t="n">
-        <v>10.75</v>
+        <v>11.19</v>
       </c>
       <c r="DR2" t="n">
-        <v>7.65</v>
+        <v>7.57</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>43.1</v>
+        <v>43.57</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DX2" t="n">
-        <v>13.25</v>
+        <v>13.57</v>
       </c>
       <c r="DY2" t="n">
-        <v>8.6</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="DZ2" t="n">
-        <v>4.65</v>
+        <v>4.72</v>
       </c>
       <c r="EA2" t="n">
-        <v>24.3</v>
+        <v>24.19</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="3">
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C3" t="n">
         <v>10</v>
       </c>
       <c r="D3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E3" t="n">
         <v>0.1</v>
@@ -1848,7 +1848,7 @@
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>56.5</v>
+        <v>56.4</v>
       </c>
       <c r="Y3" t="n">
         <v>0.1</v>
@@ -1875,97 +1875,97 @@
         <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.4</v>
+        <v>1.73</v>
       </c>
       <c r="AI3" t="n">
-        <v>86</v>
+        <v>88.73</v>
       </c>
       <c r="AJ3" t="n">
         <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>3.5</v>
+        <v>3.27</v>
       </c>
       <c r="AL3" t="n">
-        <v>2.9</v>
+        <v>3.27</v>
       </c>
       <c r="AM3" t="n">
-        <v>-0.1</v>
+        <v>-0.09</v>
       </c>
       <c r="AN3" t="n">
-        <v>38.3</v>
+        <v>40.27</v>
       </c>
       <c r="AO3" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ3" t="n">
-        <v>13.8</v>
+        <v>13.45</v>
       </c>
       <c r="AR3" t="n">
-        <v>14.8</v>
+        <v>14.82</v>
       </c>
       <c r="AS3" t="n">
-        <v>7.8</v>
+        <v>7.55</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="AX3" t="n">
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>52.1</v>
+        <v>53.09</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="BA3" t="n">
-        <v>13.2</v>
+        <v>13.64</v>
       </c>
       <c r="BB3" t="n">
-        <v>8.9</v>
+        <v>9.09</v>
       </c>
       <c r="BC3" t="n">
-        <v>4.3</v>
+        <v>4.55</v>
       </c>
       <c r="BD3" t="n">
-        <v>21.8</v>
+        <v>21.36</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="BF3" t="n">
-        <v>3.4</v>
+        <v>3.18</v>
       </c>
       <c r="BG3" t="n">
-        <v>3.3</v>
+        <v>3.33</v>
       </c>
       <c r="BH3" t="n">
-        <v>9.4</v>
+        <v>9.48</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.3</v>
+        <v>3.33</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="BL3" t="n">
         <v>1.1</v>
@@ -1977,34 +1977,34 @@
         <v>2.1</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="BP3" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BQ3" t="n">
-        <v>4.95</v>
+        <v>5.14</v>
       </c>
       <c r="BR3" t="n">
-        <v>95</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="BS3" t="n">
-        <v>80</v>
+        <v>80.95</v>
       </c>
       <c r="BT3" t="n">
-        <v>70</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BU3" t="n">
-        <v>40</v>
+        <v>42.86</v>
       </c>
       <c r="BV3" t="n">
-        <v>25</v>
+        <v>23.81</v>
       </c>
       <c r="BW3" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BX3" t="n">
-        <v>70</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BY3" t="n">
         <v>1.71</v>
@@ -2016,22 +2016,22 @@
         <v>3.43</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.61</v>
+        <v>3.6</v>
       </c>
       <c r="CC3" t="n">
-        <v>2.55</v>
+        <v>2.51</v>
       </c>
       <c r="CD3" t="n">
-        <v>2.83</v>
+        <v>2.79</v>
       </c>
       <c r="CE3" t="n">
         <v>1.37</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.71</v>
+        <v>2.72</v>
       </c>
       <c r="CG3" t="n">
-        <v>2.91</v>
+        <v>2.92</v>
       </c>
       <c r="CH3" t="n">
         <v>1.43</v>
@@ -2043,16 +2043,16 @@
         <v>1.76</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="CL3" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CO3" t="n">
         <v>1.26</v>
@@ -2061,121 +2061,121 @@
         <v>1.89</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.16</v>
+        <v>3.18</v>
       </c>
       <c r="CR3" t="n">
         <v>1.4</v>
       </c>
       <c r="CS3" t="n">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="CT3" t="n">
-        <v>3.07</v>
+        <v>3.06</v>
       </c>
       <c r="CU3" t="n">
         <v>1.44</v>
       </c>
       <c r="CV3" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="CW3" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CX3" t="n">
         <v>1.55</v>
       </c>
       <c r="CY3" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="CZ3" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="DA3" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="DB3" t="n">
         <v>1.29</v>
       </c>
       <c r="DC3" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="DD3" t="n">
-        <v>3.31</v>
+        <v>3.33</v>
       </c>
       <c r="DE3" t="n">
         <v>0.05</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="DG3" t="n">
-        <v>2.65</v>
+        <v>2.76</v>
       </c>
       <c r="DH3" t="n">
-        <v>93.8</v>
+        <v>94.86</v>
       </c>
       <c r="DI3" t="n">
         <v>0</v>
       </c>
       <c r="DJ3" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="DK3" t="n">
-        <v>5.35</v>
+        <v>5.43</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
       <c r="DM3" t="n">
-        <v>46.6</v>
+        <v>47.24</v>
       </c>
       <c r="DN3" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="DO3" t="n">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="DP3" t="n">
-        <v>14</v>
+        <v>13.81</v>
       </c>
       <c r="DQ3" t="n">
-        <v>12.9</v>
+        <v>13</v>
       </c>
       <c r="DR3" t="n">
-        <v>7.55</v>
+        <v>7.43</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.25</v>
+        <v>0.28</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.25</v>
+        <v>0.28</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>54.3</v>
+        <v>54.67</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DX3" t="n">
-        <v>15.6</v>
+        <v>15.72</v>
       </c>
       <c r="DY3" t="n">
-        <v>9.75</v>
+        <v>9.81</v>
       </c>
       <c r="DZ3" t="n">
-        <v>5.85</v>
+        <v>5.91</v>
       </c>
       <c r="EA3" t="n">
-        <v>20.15</v>
+        <v>20</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.95</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="4">
@@ -2185,94 +2185,94 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D4" t="n">
         <v>10</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="F4" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="G4" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="H4" t="n">
-        <v>93.40000000000001</v>
+        <v>95.45</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>-0.09</v>
       </c>
       <c r="J4" t="n">
-        <v>3</v>
+        <v>2.73</v>
       </c>
       <c r="K4" t="n">
-        <v>4</v>
+        <v>3.82</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="M4" t="n">
-        <v>46.2</v>
+        <v>46.27</v>
       </c>
       <c r="N4" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="O4" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="P4" t="n">
-        <v>13.8</v>
+        <v>13.55</v>
       </c>
       <c r="Q4" t="n">
-        <v>14.5</v>
+        <v>14.18</v>
       </c>
       <c r="R4" t="n">
-        <v>9</v>
+        <v>8.82</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="V4" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>49.2</v>
+        <v>49.45</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>10.5</v>
+        <v>10.55</v>
       </c>
       <c r="AA4" t="n">
-        <v>7.5</v>
+        <v>7.45</v>
       </c>
       <c r="AB4" t="n">
-        <v>3</v>
+        <v>3.09</v>
       </c>
       <c r="AC4" t="n">
-        <v>25.7</v>
+        <v>25.82</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AE4" t="n">
-        <v>3</v>
+        <v>2.73</v>
       </c>
       <c r="AF4" t="n">
         <v>0.1</v>
@@ -2356,70 +2356,70 @@
         <v>2.4</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="BH4" t="n">
-        <v>8.6</v>
+        <v>8.43</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="BP4" t="n">
-        <v>4.05</v>
+        <v>3.9</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.55</v>
+        <v>4.52</v>
       </c>
       <c r="BR4" t="n">
-        <v>85</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BS4" t="n">
-        <v>65</v>
+        <v>61.9</v>
       </c>
       <c r="BT4" t="n">
-        <v>40</v>
+        <v>38.1</v>
       </c>
       <c r="BU4" t="n">
-        <v>15</v>
+        <v>14.29</v>
       </c>
       <c r="BV4" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BW4" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BX4" t="n">
-        <v>50</v>
+        <v>47.62</v>
       </c>
       <c r="BY4" t="n">
-        <v>2.23</v>
+        <v>2.27</v>
       </c>
       <c r="BZ4" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.01</v>
+        <v>3</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.11</v>
+        <v>3.1</v>
       </c>
       <c r="CC4" t="n">
         <v>3.71</v>
@@ -2428,13 +2428,13 @@
         <v>4.09</v>
       </c>
       <c r="CE4" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="CF4" t="n">
-        <v>3.45</v>
+        <v>3.47</v>
       </c>
       <c r="CG4" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="CH4" t="n">
         <v>1.26</v>
@@ -2443,28 +2443,28 @@
         <v>1.67</v>
       </c>
       <c r="CJ4" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="CK4" t="n">
         <v>1.71</v>
       </c>
       <c r="CL4" t="n">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="CN4" t="n">
         <v>1.66</v>
       </c>
       <c r="CO4" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="CP4" t="n">
-        <v>2.52</v>
+        <v>2.55</v>
       </c>
       <c r="CQ4" t="n">
-        <v>4.84</v>
+        <v>4.95</v>
       </c>
       <c r="CR4" t="n">
         <v>1.59</v>
@@ -2479,106 +2479,106 @@
         <v>1.33</v>
       </c>
       <c r="CV4" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="CW4" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="CX4" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="CY4" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="CZ4" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="DA4" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="DB4" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="DC4" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="DD4" t="n">
+        <v>5.51</v>
+      </c>
+      <c r="DE4" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="DF4" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="DG4" t="n">
         <v>2.24</v>
       </c>
-      <c r="CX4" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="CY4" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="CZ4" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="DA4" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="DB4" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="DC4" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="DD4" t="n">
-        <v>5.41</v>
-      </c>
-      <c r="DE4" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="DF4" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="DG4" t="n">
-        <v>2.3</v>
-      </c>
       <c r="DH4" t="n">
-        <v>90.40000000000001</v>
+        <v>91.62</v>
       </c>
       <c r="DI4" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.7</v>
+        <v>2.57</v>
       </c>
       <c r="DK4" t="n">
-        <v>4.05</v>
+        <v>3.95</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DM4" t="n">
-        <v>41.6</v>
+        <v>41.86</v>
       </c>
       <c r="DN4" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="DO4" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="DP4" t="n">
-        <v>13.95</v>
+        <v>13.81</v>
       </c>
       <c r="DQ4" t="n">
-        <v>15</v>
+        <v>14.81</v>
       </c>
       <c r="DR4" t="n">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>47.1</v>
+        <v>47.33</v>
       </c>
       <c r="DW4" t="n">
         <v>0</v>
       </c>
       <c r="DX4" t="n">
-        <v>9.85</v>
+        <v>9.91</v>
       </c>
       <c r="DY4" t="n">
         <v>6.9</v>
       </c>
       <c r="DZ4" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="EA4" t="n">
-        <v>23.6</v>
+        <v>23.76</v>
       </c>
       <c r="EB4" t="n">
         <v>1.14</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.7</v>
+        <v>2.57</v>
       </c>
     </row>
     <row r="5">
@@ -2654,7 +2654,7 @@
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>57.7</v>
+        <v>57.6</v>
       </c>
       <c r="Y5" t="n">
         <v>0.4</v>
@@ -2960,7 +2960,7 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>55.35</v>
+        <v>55.3</v>
       </c>
       <c r="DW5" t="n">
         <v>0.25</v>
@@ -3273,31 +3273,31 @@
         <v>3.99</v>
       </c>
       <c r="CR6" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CS6" t="n">
-        <v>3.15</v>
+        <v>3.14</v>
       </c>
       <c r="CT6" t="n">
-        <v>2.79</v>
+        <v>2.81</v>
       </c>
       <c r="CU6" t="n">
         <v>1.39</v>
       </c>
       <c r="CV6" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="CW6" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CX6" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="CY6" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="CZ6" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="DA6" t="n">
         <v>1.71</v>
@@ -3306,10 +3306,10 @@
         <v>1.39</v>
       </c>
       <c r="DC6" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="DD6" t="n">
-        <v>4.15</v>
+        <v>4.1</v>
       </c>
       <c r="DE6" t="n">
         <v>0.15</v>
@@ -3394,13 +3394,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C7" t="n">
         <v>10</v>
       </c>
       <c r="D7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -3484,139 +3484,139 @@
         <v>1.2</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AH7" t="n">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="AI7" t="n">
-        <v>75.7</v>
+        <v>74.45</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AK7" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>31.55</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>12.45</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>11.45</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>10.09</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>42.55</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>11.18</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>6.64</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>17.27</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BF7" t="n">
         <v>2</v>
       </c>
-      <c r="AL7" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>32.6</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>12</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>44</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>1.8</v>
-      </c>
       <c r="BG7" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="BH7" t="n">
-        <v>9</v>
+        <v>9.1</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="BN7" t="n">
         <v>1.1</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="BP7" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="BQ7" t="n">
-        <v>5.15</v>
+        <v>5.14</v>
       </c>
       <c r="BR7" t="n">
-        <v>90</v>
+        <v>90.48</v>
       </c>
       <c r="BS7" t="n">
-        <v>55</v>
+        <v>57.14</v>
       </c>
       <c r="BT7" t="n">
-        <v>45</v>
+        <v>42.86</v>
       </c>
       <c r="BU7" t="n">
-        <v>30</v>
+        <v>28.57</v>
       </c>
       <c r="BV7" t="n">
-        <v>20</v>
+        <v>19.05</v>
       </c>
       <c r="BW7" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BX7" t="n">
-        <v>35</v>
+        <v>38.1</v>
       </c>
       <c r="BY7" t="n">
         <v>2.55</v>
@@ -3625,37 +3625,37 @@
         <v>2.65</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.36</v>
+        <v>3.38</v>
       </c>
       <c r="CB7" t="n">
         <v>3.51</v>
       </c>
       <c r="CC7" t="n">
-        <v>5</v>
+        <v>4.85</v>
       </c>
       <c r="CD7" t="n">
-        <v>5.57</v>
+        <v>5.43</v>
       </c>
       <c r="CE7" t="n">
         <v>1.43</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.96</v>
+        <v>2.95</v>
       </c>
       <c r="CG7" t="n">
         <v>2.75</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CI7" t="n">
         <v>1.86</v>
       </c>
       <c r="CJ7" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CK7" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CL7" t="n">
         <v>2.03</v>
@@ -3670,19 +3670,19 @@
         <v>1.32</v>
       </c>
       <c r="CP7" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="CQ7" t="n">
-        <v>3.69</v>
+        <v>3.66</v>
       </c>
       <c r="CR7" t="n">
         <v>1.45</v>
       </c>
       <c r="CS7" t="n">
-        <v>3.14</v>
+        <v>3.13</v>
       </c>
       <c r="CT7" t="n">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="CU7" t="n">
         <v>1.39</v>
@@ -3691,103 +3691,103 @@
         <v>1.94</v>
       </c>
       <c r="CW7" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CX7" t="n">
         <v>1.63</v>
       </c>
       <c r="CY7" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="CZ7" t="n">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="DA7" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="DB7" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="DC7" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="DD7" t="n">
-        <v>3.89</v>
+        <v>3.86</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="DG7" t="n">
-        <v>2.75</v>
+        <v>2.67</v>
       </c>
       <c r="DH7" t="n">
-        <v>82.40000000000001</v>
+        <v>81.43000000000001</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DJ7" t="n">
-        <v>1.7</v>
+        <v>1.81</v>
       </c>
       <c r="DK7" t="n">
-        <v>3.95</v>
+        <v>3.81</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.3</v>
+        <v>0.28</v>
       </c>
       <c r="DM7" t="n">
-        <v>37.05</v>
+        <v>36.29</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.4</v>
+        <v>0.43</v>
       </c>
       <c r="DO7" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="DP7" t="n">
-        <v>12.05</v>
+        <v>12.09</v>
       </c>
       <c r="DQ7" t="n">
-        <v>12.75</v>
+        <v>12.43</v>
       </c>
       <c r="DR7" t="n">
-        <v>9.050000000000001</v>
+        <v>9.19</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>48.55</v>
+        <v>47.57</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DX7" t="n">
-        <v>11.5</v>
+        <v>11.05</v>
       </c>
       <c r="DY7" t="n">
-        <v>7.5</v>
+        <v>7.14</v>
       </c>
       <c r="DZ7" t="n">
-        <v>4</v>
+        <v>3.91</v>
       </c>
       <c r="EA7" t="n">
-        <v>18.7</v>
+        <v>18.33</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="EC7" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="8">
@@ -3797,94 +3797,94 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D8" t="n">
         <v>10</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="F8" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="G8" t="n">
-        <v>3.3</v>
+        <v>3.09</v>
       </c>
       <c r="H8" t="n">
-        <v>93.59999999999999</v>
+        <v>91.55</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="J8" t="n">
-        <v>3.3</v>
+        <v>3.36</v>
       </c>
       <c r="K8" t="n">
-        <v>5.8</v>
+        <v>5.73</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="M8" t="n">
-        <v>48.1</v>
+        <v>47.45</v>
       </c>
       <c r="N8" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="O8" t="n">
-        <v>2.5</v>
+        <v>2.64</v>
       </c>
       <c r="P8" t="n">
-        <v>14.1</v>
+        <v>13.45</v>
       </c>
       <c r="Q8" t="n">
-        <v>13.4</v>
+        <v>13</v>
       </c>
       <c r="R8" t="n">
-        <v>7.5</v>
+        <v>7.45</v>
       </c>
       <c r="S8" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="T8" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Y8" t="n">
         <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>11.7</v>
+        <v>11.55</v>
       </c>
       <c r="AA8" t="n">
-        <v>8.199999999999999</v>
+        <v>7.91</v>
       </c>
       <c r="AB8" t="n">
-        <v>3.5</v>
+        <v>3.64</v>
       </c>
       <c r="AC8" t="n">
-        <v>19.4</v>
+        <v>19.09</v>
       </c>
       <c r="AD8" t="n">
         <v>1.33</v>
       </c>
       <c r="AE8" t="n">
-        <v>3.3</v>
+        <v>3.36</v>
       </c>
       <c r="AF8" t="n">
         <v>0.1</v>
@@ -3968,67 +3968,67 @@
         <v>2.6</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.15</v>
+        <v>2.29</v>
       </c>
       <c r="BH8" t="n">
-        <v>10.65</v>
+        <v>11.1</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.15</v>
+        <v>2.29</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.55</v>
+        <v>0.57</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="BO8" t="n">
         <v>0.95</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.8</v>
+        <v>4.95</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.85</v>
+        <v>6.14</v>
       </c>
       <c r="BR8" t="n">
-        <v>80</v>
+        <v>80.95</v>
       </c>
       <c r="BS8" t="n">
-        <v>55</v>
+        <v>57.14</v>
       </c>
       <c r="BT8" t="n">
-        <v>45</v>
+        <v>47.62</v>
       </c>
       <c r="BU8" t="n">
-        <v>20</v>
+        <v>23.81</v>
       </c>
       <c r="BV8" t="n">
-        <v>10</v>
+        <v>14.29</v>
       </c>
       <c r="BW8" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BX8" t="n">
-        <v>45</v>
+        <v>47.62</v>
       </c>
       <c r="BY8" t="n">
-        <v>2.33</v>
+        <v>2.36</v>
       </c>
       <c r="BZ8" t="n">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.13</v>
+        <v>3.12</v>
       </c>
       <c r="CB8" t="n">
         <v>3.29</v>
@@ -4037,13 +4037,13 @@
         <v>3.83</v>
       </c>
       <c r="CD8" t="n">
-        <v>4.24</v>
+        <v>4.25</v>
       </c>
       <c r="CE8" t="n">
         <v>1.47</v>
       </c>
       <c r="CF8" t="n">
-        <v>3.16</v>
+        <v>3.17</v>
       </c>
       <c r="CG8" t="n">
         <v>2.55</v>
@@ -4058,34 +4058,34 @@
         <v>1.97</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CL8" t="n">
         <v>2.18</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="CN8" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CO8" t="n">
         <v>1.39</v>
       </c>
       <c r="CP8" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="CQ8" t="n">
-        <v>4.16</v>
+        <v>4.17</v>
       </c>
       <c r="CR8" t="n">
         <v>1.51</v>
       </c>
       <c r="CS8" t="n">
-        <v>3.2</v>
+        <v>3.19</v>
       </c>
       <c r="CT8" t="n">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="CU8" t="n">
         <v>1.37</v>
@@ -4115,61 +4115,61 @@
         <v>2.33</v>
       </c>
       <c r="DD8" t="n">
-        <v>4.34</v>
+        <v>4.33</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DF8" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="DH8" t="n">
-        <v>89.55</v>
+        <v>88.67</v>
       </c>
       <c r="DI8" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="DK8" t="n">
         <v>4.95</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.15</v>
+        <v>0.19</v>
       </c>
       <c r="DM8" t="n">
-        <v>39.1</v>
+        <v>39.19</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.25</v>
+        <v>2.34</v>
       </c>
       <c r="DP8" t="n">
-        <v>15.05</v>
+        <v>14.66</v>
       </c>
       <c r="DQ8" t="n">
-        <v>13.15</v>
+        <v>12.95</v>
       </c>
       <c r="DR8" t="n">
-        <v>8.75</v>
+        <v>8.66</v>
       </c>
       <c r="DS8" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="DT8" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>45</v>
+        <v>44.67</v>
       </c>
       <c r="DW8" t="n">
         <v>0</v>
@@ -4178,19 +4178,19 @@
         <v>10.1</v>
       </c>
       <c r="DY8" t="n">
-        <v>6.95</v>
+        <v>6.86</v>
       </c>
       <c r="DZ8" t="n">
-        <v>3.15</v>
+        <v>3.24</v>
       </c>
       <c r="EA8" t="n">
-        <v>19.1</v>
+        <v>18.95</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="EC8" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -4245,7 +4245,7 @@
         <v>16.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>15</v>
+        <v>15.1</v>
       </c>
       <c r="R9" t="n">
         <v>5</v>
@@ -4281,7 +4281,7 @@
         <v>4.9</v>
       </c>
       <c r="AC9" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="AD9" t="n">
         <v>1.75</v>
@@ -4557,7 +4557,7 @@
         <v>16.15</v>
       </c>
       <c r="DQ9" t="n">
-        <v>15.05</v>
+        <v>15.1</v>
       </c>
       <c r="DR9" t="n">
         <v>5.95</v>
@@ -4587,7 +4587,7 @@
         <v>4.75</v>
       </c>
       <c r="EA9" t="n">
-        <v>22.1</v>
+        <v>22.05</v>
       </c>
       <c r="EB9" t="n">
         <v>1.6</v>
@@ -4603,13 +4603,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C10" t="n">
         <v>10</v>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E10" t="n">
         <v>0.2</v>
@@ -4696,136 +4696,136 @@
         <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AI10" t="n">
-        <v>78.3</v>
+        <v>75</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.8</v>
+        <v>2.64</v>
       </c>
       <c r="AL10" t="n">
-        <v>4.9</v>
+        <v>4.73</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AN10" t="n">
-        <v>36.4</v>
+        <v>34</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AP10" t="n">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="AQ10" t="n">
-        <v>11.2</v>
+        <v>11.27</v>
       </c>
       <c r="AR10" t="n">
-        <v>12.1</v>
+        <v>12.27</v>
       </c>
       <c r="AS10" t="n">
-        <v>8.800000000000001</v>
+        <v>8.73</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AX10" t="n">
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>48</v>
+        <v>47.09</v>
       </c>
       <c r="AZ10" t="n">
         <v>0</v>
       </c>
       <c r="BA10" t="n">
-        <v>12.2</v>
+        <v>11.73</v>
       </c>
       <c r="BB10" t="n">
-        <v>7.5</v>
+        <v>7.18</v>
       </c>
       <c r="BC10" t="n">
-        <v>4.7</v>
+        <v>4.55</v>
       </c>
       <c r="BD10" t="n">
-        <v>15.1</v>
+        <v>14.73</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.37</v>
+        <v>1.31</v>
       </c>
       <c r="BF10" t="n">
-        <v>2.8</v>
+        <v>2.64</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.85</v>
+        <v>2.81</v>
       </c>
       <c r="BH10" t="n">
-        <v>8.800000000000001</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.85</v>
+        <v>2.81</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="BM10" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="BP10" t="n">
-        <v>4.25</v>
+        <v>4.43</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.55</v>
+        <v>4.43</v>
       </c>
       <c r="BR10" t="n">
-        <v>95</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="BS10" t="n">
-        <v>85</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BT10" t="n">
-        <v>60</v>
+        <v>57.14</v>
       </c>
       <c r="BU10" t="n">
-        <v>35</v>
+        <v>33.33</v>
       </c>
       <c r="BV10" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BW10" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BX10" t="n">
-        <v>55</v>
+        <v>57.14</v>
       </c>
       <c r="BY10" t="n">
         <v>1.88</v>
@@ -4837,31 +4837,31 @@
         <v>3.29</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.42</v>
+        <v>3.43</v>
       </c>
       <c r="CC10" t="n">
-        <v>2.74</v>
+        <v>2.83</v>
       </c>
       <c r="CD10" t="n">
-        <v>2.84</v>
+        <v>2.97</v>
       </c>
       <c r="CE10" t="n">
         <v>1.41</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.89</v>
+        <v>2.92</v>
       </c>
       <c r="CG10" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CI10" t="n">
         <v>1.95</v>
       </c>
       <c r="CJ10" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CK10" t="n">
         <v>1.63</v>
@@ -4870,19 +4870,19 @@
         <v>2.07</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="CN10" t="n">
         <v>1.74</v>
       </c>
       <c r="CO10" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="CP10" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="CQ10" t="n">
-        <v>3.49</v>
+        <v>3.52</v>
       </c>
       <c r="CR10" t="n">
         <v>1.45</v>
@@ -4891,7 +4891,7 @@
         <v>3.12</v>
       </c>
       <c r="CT10" t="n">
-        <v>2.87</v>
+        <v>2.88</v>
       </c>
       <c r="CU10" t="n">
         <v>1.39</v>
@@ -4900,19 +4900,19 @@
         <v>2.02</v>
       </c>
       <c r="CW10" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CX10" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CY10" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="CZ10" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="DA10" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="DB10" t="n">
         <v>1.34</v>
@@ -4927,76 +4927,76 @@
         <v>0.1</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="DG10" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="DH10" t="n">
-        <v>86.95</v>
+        <v>84.81</v>
       </c>
       <c r="DI10" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.65</v>
+        <v>2.57</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.65</v>
+        <v>4.57</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="DM10" t="n">
-        <v>40.4</v>
+        <v>38.95</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.55</v>
+        <v>2.57</v>
       </c>
       <c r="DP10" t="n">
-        <v>11.45</v>
+        <v>11.47</v>
       </c>
       <c r="DQ10" t="n">
-        <v>12.85</v>
+        <v>12.9</v>
       </c>
       <c r="DR10" t="n">
         <v>8.050000000000001</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>51.15</v>
+        <v>50.52</v>
       </c>
       <c r="DW10" t="n">
         <v>0.05</v>
       </c>
       <c r="DX10" t="n">
-        <v>12.7</v>
+        <v>12.43</v>
       </c>
       <c r="DY10" t="n">
-        <v>7.9</v>
+        <v>7.71</v>
       </c>
       <c r="DZ10" t="n">
-        <v>4.8</v>
+        <v>4.72</v>
       </c>
       <c r="EA10" t="n">
-        <v>17.15</v>
+        <v>16.86</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="EC10" t="n">
-        <v>2.55</v>
+        <v>2.48</v>
       </c>
     </row>
     <row r="11">
@@ -5006,10 +5006,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D11" t="n">
         <v>11</v>
@@ -5018,49 +5018,49 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="G11" t="n">
-        <v>3.67</v>
+        <v>3.7</v>
       </c>
       <c r="H11" t="n">
-        <v>104.67</v>
+        <v>109.4</v>
       </c>
       <c r="I11" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="J11" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="K11" t="n">
-        <v>5.56</v>
+        <v>6</v>
       </c>
       <c r="L11" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="M11" t="n">
-        <v>50.44</v>
+        <v>52.6</v>
       </c>
       <c r="N11" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="O11" t="n">
-        <v>1.89</v>
+        <v>2.3</v>
       </c>
       <c r="P11" t="n">
-        <v>14</v>
+        <v>13.2</v>
       </c>
       <c r="Q11" t="n">
-        <v>14.56</v>
+        <v>14.4</v>
       </c>
       <c r="R11" t="n">
-        <v>8.56</v>
+        <v>7.8</v>
       </c>
       <c r="S11" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="T11" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
@@ -5072,28 +5072,28 @@
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>58.22</v>
+        <v>59.6</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="Z11" t="n">
-        <v>13.44</v>
+        <v>13.9</v>
       </c>
       <c r="AA11" t="n">
-        <v>8.56</v>
+        <v>9</v>
       </c>
       <c r="AB11" t="n">
-        <v>4.89</v>
+        <v>4.9</v>
       </c>
       <c r="AC11" t="n">
-        <v>19.44</v>
+        <v>19.7</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="AE11" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AF11" t="n">
         <v>0.09</v>
@@ -5177,82 +5177,82 @@
         <v>2.73</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="BH11" t="n">
-        <v>9.75</v>
+        <v>9.81</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.3</v>
+        <v>0.33</v>
       </c>
       <c r="BL11" t="n">
         <v>1</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.8</v>
+        <v>0.76</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="BO11" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.4</v>
+        <v>4.48</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.3</v>
+        <v>5.29</v>
       </c>
       <c r="BR11" t="n">
-        <v>90</v>
+        <v>90.48</v>
       </c>
       <c r="BS11" t="n">
-        <v>75</v>
+        <v>76.19</v>
       </c>
       <c r="BT11" t="n">
-        <v>55</v>
+        <v>52.38</v>
       </c>
       <c r="BU11" t="n">
-        <v>25</v>
+        <v>23.81</v>
       </c>
       <c r="BV11" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BW11" t="n">
         <v>0</v>
       </c>
       <c r="BX11" t="n">
-        <v>65</v>
+        <v>66.67</v>
       </c>
       <c r="BY11" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="BZ11" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.3</v>
+        <v>3.32</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.47</v>
+        <v>3.46</v>
       </c>
       <c r="CC11" t="n">
         <v>3.89</v>
       </c>
       <c r="CD11" t="n">
-        <v>4.19</v>
+        <v>4.18</v>
       </c>
       <c r="CE11" t="n">
         <v>1.42</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="CG11" t="n">
         <v>2.78</v>
@@ -5270,22 +5270,22 @@
         <v>1.64</v>
       </c>
       <c r="CL11" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="CN11" t="n">
         <v>1.73</v>
       </c>
       <c r="CO11" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="CP11" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="CQ11" t="n">
-        <v>3.55</v>
+        <v>3.53</v>
       </c>
       <c r="CR11" t="n">
         <v>1.44</v>
@@ -5294,112 +5294,112 @@
         <v>3.04</v>
       </c>
       <c r="CT11" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="CU11" t="n">
         <v>1.41</v>
       </c>
       <c r="CV11" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="CW11" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CX11" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CY11" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="CZ11" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="DA11" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="DB11" t="n">
         <v>1.34</v>
       </c>
       <c r="DC11" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="DD11" t="n">
-        <v>3.71</v>
+        <v>3.68</v>
       </c>
       <c r="DE11" t="n">
         <v>0.05</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="DG11" t="n">
-        <v>3.25</v>
+        <v>3.29</v>
       </c>
       <c r="DH11" t="n">
-        <v>101.2</v>
+        <v>103.62</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.55</v>
+        <v>2.48</v>
       </c>
       <c r="DK11" t="n">
-        <v>5</v>
+        <v>5.24</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.15</v>
+        <v>0.19</v>
       </c>
       <c r="DM11" t="n">
-        <v>45</v>
+        <v>46.29</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="DO11" t="n">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="DP11" t="n">
-        <v>13.8</v>
+        <v>13.43</v>
       </c>
       <c r="DQ11" t="n">
-        <v>14.85</v>
+        <v>14.76</v>
       </c>
       <c r="DR11" t="n">
-        <v>7.8</v>
+        <v>7.48</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>57.9</v>
+        <v>58.57</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DX11" t="n">
-        <v>13.55</v>
+        <v>13.76</v>
       </c>
       <c r="DY11" t="n">
-        <v>8.85</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="DZ11" t="n">
-        <v>4.7</v>
+        <v>4.72</v>
       </c>
       <c r="EA11" t="n">
-        <v>18.7</v>
+        <v>18.86</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="12">
@@ -5556,16 +5556,16 @@
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>46.5</v>
+        <v>46.6</v>
       </c>
       <c r="AZ12" t="n">
         <v>0.2</v>
       </c>
       <c r="BA12" t="n">
-        <v>10.4</v>
+        <v>10.5</v>
       </c>
       <c r="BB12" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="BC12" t="n">
         <v>3.4</v>
@@ -5574,7 +5574,7 @@
         <v>21.5</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="BF12" t="n">
         <v>2.8</v>
@@ -5781,16 +5781,16 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>49.45</v>
+        <v>49.5</v>
       </c>
       <c r="DW12" t="n">
         <v>0.2</v>
       </c>
       <c r="DX12" t="n">
-        <v>12.75</v>
+        <v>12.8</v>
       </c>
       <c r="DY12" t="n">
-        <v>9.1</v>
+        <v>9.15</v>
       </c>
       <c r="DZ12" t="n">
         <v>3.65</v>
@@ -5799,7 +5799,7 @@
         <v>22.05</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="EC12" t="n">
         <v>2.35</v>
@@ -5938,7 +5938,7 @@
         <v>12</v>
       </c>
       <c r="AR13" t="n">
-        <v>13.55</v>
+        <v>13.64</v>
       </c>
       <c r="AS13" t="n">
         <v>8.550000000000001</v>
@@ -5959,7 +5959,7 @@
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>49.64</v>
+        <v>49.73</v>
       </c>
       <c r="AZ13" t="n">
         <v>0.27</v>
@@ -6052,7 +6052,7 @@
         <v>3</v>
       </c>
       <c r="CD13" t="n">
-        <v>3.23</v>
+        <v>3.22</v>
       </c>
       <c r="CE13" t="n">
         <v>1.49</v>
@@ -6097,7 +6097,7 @@
         <v>1.53</v>
       </c>
       <c r="CS13" t="n">
-        <v>3.19</v>
+        <v>3.2</v>
       </c>
       <c r="CT13" t="n">
         <v>2.64</v>
@@ -6118,7 +6118,7 @@
         <v>2.11</v>
       </c>
       <c r="CZ13" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="DA13" t="n">
         <v>1.72</v>
@@ -6169,7 +6169,7 @@
         <v>12.65</v>
       </c>
       <c r="DQ13" t="n">
-        <v>14.3</v>
+        <v>14.35</v>
       </c>
       <c r="DR13" t="n">
         <v>8.1</v>
@@ -6184,7 +6184,7 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>50.5</v>
+        <v>50.55</v>
       </c>
       <c r="DW13" t="n">
         <v>0.2</v>
@@ -6215,61 +6215,61 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D14" t="n">
         <v>11</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="F14" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="G14" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="H14" t="n">
-        <v>97.22</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>3.78</v>
+        <v>3.7</v>
       </c>
       <c r="K14" t="n">
-        <v>4.11</v>
+        <v>4.1</v>
       </c>
       <c r="L14" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="M14" t="n">
-        <v>41.33</v>
+        <v>41.1</v>
       </c>
       <c r="N14" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="O14" t="n">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="P14" t="n">
-        <v>17.44</v>
+        <v>17.3</v>
       </c>
       <c r="Q14" t="n">
-        <v>12.56</v>
+        <v>12.3</v>
       </c>
       <c r="R14" t="n">
-        <v>7.67</v>
+        <v>7.8</v>
       </c>
       <c r="S14" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="T14" t="n">
-        <v>0.67</v>
+        <v>0.8</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
@@ -6281,28 +6281,28 @@
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="Z14" t="n">
-        <v>12.44</v>
+        <v>12.1</v>
       </c>
       <c r="AA14" t="n">
-        <v>8.56</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AB14" t="n">
-        <v>3.89</v>
+        <v>3.8</v>
       </c>
       <c r="AC14" t="n">
-        <v>17.56</v>
+        <v>17.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AE14" t="n">
-        <v>3.67</v>
+        <v>3.6</v>
       </c>
       <c r="AF14" t="n">
         <v>0.09</v>
@@ -6386,70 +6386,70 @@
         <v>2.45</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.65</v>
+        <v>2.71</v>
       </c>
       <c r="BH14" t="n">
-        <v>8.699999999999999</v>
+        <v>8.81</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.65</v>
+        <v>2.71</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="BP14" t="n">
-        <v>3.7</v>
+        <v>3.62</v>
       </c>
       <c r="BQ14" t="n">
-        <v>5</v>
+        <v>5.19</v>
       </c>
       <c r="BR14" t="n">
-        <v>90</v>
+        <v>90.48</v>
       </c>
       <c r="BS14" t="n">
-        <v>70</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BT14" t="n">
-        <v>50</v>
+        <v>52.38</v>
       </c>
       <c r="BU14" t="n">
-        <v>30</v>
+        <v>33.33</v>
       </c>
       <c r="BV14" t="n">
-        <v>20</v>
+        <v>19.05</v>
       </c>
       <c r="BW14" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BX14" t="n">
-        <v>60</v>
+        <v>61.9</v>
       </c>
       <c r="BY14" t="n">
-        <v>2.96</v>
+        <v>2.99</v>
       </c>
       <c r="BZ14" t="n">
-        <v>3.36</v>
+        <v>3.35</v>
       </c>
       <c r="CA14" t="n">
         <v>3.29</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.52</v>
+        <v>3.51</v>
       </c>
       <c r="CC14" t="n">
         <v>5.3</v>
@@ -6461,19 +6461,19 @@
         <v>1.47</v>
       </c>
       <c r="CF14" t="n">
-        <v>3.17</v>
+        <v>3.16</v>
       </c>
       <c r="CG14" t="n">
-        <v>2.57</v>
+        <v>2.59</v>
       </c>
       <c r="CH14" t="n">
         <v>1.32</v>
       </c>
       <c r="CI14" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CJ14" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="CK14" t="n">
         <v>1.7</v>
@@ -6488,37 +6488,37 @@
         <v>1.68</v>
       </c>
       <c r="CO14" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CP14" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="CQ14" t="n">
-        <v>4.17</v>
+        <v>4.15</v>
       </c>
       <c r="CR14" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CS14" t="n">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="CT14" t="n">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="CU14" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CV14" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="CW14" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="CX14" t="n">
         <v>1.7</v>
       </c>
       <c r="CY14" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="CZ14" t="n">
         <v>2.13</v>
@@ -6530,82 +6530,82 @@
         <v>1.43</v>
       </c>
       <c r="DC14" t="n">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="DD14" t="n">
-        <v>4.43</v>
+        <v>4.39</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="DG14" t="n">
-        <v>1.65</v>
+        <v>1.76</v>
       </c>
       <c r="DH14" t="n">
-        <v>88.55</v>
+        <v>87.62</v>
       </c>
       <c r="DI14" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ14" t="n">
-        <v>3.35</v>
+        <v>3.33</v>
       </c>
       <c r="DK14" t="n">
-        <v>3.2</v>
+        <v>3.24</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DM14" t="n">
-        <v>34.45</v>
+        <v>34.67</v>
       </c>
       <c r="DN14" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="DO14" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="DP14" t="n">
-        <v>15.7</v>
+        <v>15.71</v>
       </c>
       <c r="DQ14" t="n">
-        <v>13.2</v>
+        <v>13.05</v>
       </c>
       <c r="DR14" t="n">
-        <v>9.25</v>
+        <v>9.24</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>41.6</v>
+        <v>41.38</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DX14" t="n">
-        <v>11</v>
+        <v>10.91</v>
       </c>
       <c r="DY14" t="n">
-        <v>7.55</v>
+        <v>7.48</v>
       </c>
       <c r="DZ14" t="n">
-        <v>3.45</v>
+        <v>3.43</v>
       </c>
       <c r="EA14" t="n">
-        <v>17.55</v>
+        <v>17.53</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="EC14" t="n">
         <v>3</v>
@@ -6858,7 +6858,7 @@
         <v>4.08</v>
       </c>
       <c r="CD15" t="n">
-        <v>4.45</v>
+        <v>4.48</v>
       </c>
       <c r="CE15" t="n">
         <v>1.46</v>
@@ -6903,19 +6903,19 @@
         <v>1.48</v>
       </c>
       <c r="CS15" t="n">
-        <v>3.21</v>
+        <v>3.2</v>
       </c>
       <c r="CT15" t="n">
-        <v>2.76</v>
+        <v>2.77</v>
       </c>
       <c r="CU15" t="n">
         <v>1.37</v>
       </c>
       <c r="CV15" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CW15" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CX15" t="n">
         <v>1.63</v>
@@ -6927,16 +6927,16 @@
         <v>2.24</v>
       </c>
       <c r="DA15" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="DB15" t="n">
         <v>1.4</v>
       </c>
       <c r="DC15" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="DD15" t="n">
-        <v>4.22</v>
+        <v>4.19</v>
       </c>
       <c r="DE15" t="n">
         <v>0.1</v>
@@ -7424,94 +7424,94 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D17" t="n">
         <v>10</v>
       </c>
       <c r="E17" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="F17" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="G17" t="n">
         <v>1</v>
       </c>
       <c r="H17" t="n">
-        <v>81.7</v>
+        <v>81.18000000000001</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="J17" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K17" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="M17" t="n">
-        <v>32.4</v>
+        <v>31.73</v>
       </c>
       <c r="N17" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="O17" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="P17" t="n">
-        <v>18.1</v>
+        <v>18.27</v>
       </c>
       <c r="Q17" t="n">
-        <v>13.3</v>
+        <v>13.18</v>
       </c>
       <c r="R17" t="n">
-        <v>9.199999999999999</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="S17" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="T17" t="n">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="V17" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>45.3</v>
+        <v>45.36</v>
       </c>
       <c r="Y17" t="n">
         <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>10.1</v>
+        <v>10.36</v>
       </c>
       <c r="AA17" t="n">
-        <v>6.4</v>
+        <v>6.73</v>
       </c>
       <c r="AB17" t="n">
-        <v>3.7</v>
+        <v>3.64</v>
       </c>
       <c r="AC17" t="n">
-        <v>20.4</v>
+        <v>20.27</v>
       </c>
       <c r="AD17" t="n">
         <v>1.14</v>
       </c>
       <c r="AE17" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="AF17" t="n">
         <v>0</v>
@@ -7595,70 +7595,70 @@
         <v>2.9</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="BH17" t="n">
-        <v>9</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.85</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.8</v>
+        <v>0.76</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="BP17" t="n">
-        <v>4.05</v>
+        <v>4.1</v>
       </c>
       <c r="BQ17" t="n">
-        <v>4.45</v>
+        <v>4.48</v>
       </c>
       <c r="BR17" t="n">
-        <v>100</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="BS17" t="n">
-        <v>65</v>
+        <v>61.9</v>
       </c>
       <c r="BT17" t="n">
-        <v>50</v>
+        <v>47.62</v>
       </c>
       <c r="BU17" t="n">
-        <v>25</v>
+        <v>23.81</v>
       </c>
       <c r="BV17" t="n">
-        <v>15</v>
+        <v>14.29</v>
       </c>
       <c r="BW17" t="n">
-        <v>15</v>
+        <v>14.29</v>
       </c>
       <c r="BX17" t="n">
-        <v>50</v>
+        <v>47.62</v>
       </c>
       <c r="BY17" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="BZ17" t="n">
-        <v>3.49</v>
+        <v>3.42</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.44</v>
+        <v>3.42</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.66</v>
+        <v>3.65</v>
       </c>
       <c r="CC17" t="n">
         <v>5.34</v>
@@ -7679,31 +7679,31 @@
         <v>1.35</v>
       </c>
       <c r="CI17" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="CJ17" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="CK17" t="n">
         <v>1.59</v>
       </c>
       <c r="CL17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="CN17" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CO17" t="n">
         <v>1.34</v>
       </c>
       <c r="CP17" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="CQ17" t="n">
-        <v>3.7</v>
+        <v>3.68</v>
       </c>
       <c r="CR17" t="n">
         <v>1.47</v>
@@ -7718,106 +7718,106 @@
         <v>1.4</v>
       </c>
       <c r="CV17" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="CW17" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="CX17" t="n">
         <v>1.63</v>
       </c>
       <c r="CY17" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="CZ17" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="DA17" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="DB17" t="n">
         <v>1.37</v>
       </c>
       <c r="DC17" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="DD17" t="n">
-        <v>3.95</v>
+        <v>3.91</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="DG17" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="DH17" t="n">
-        <v>82.90000000000001</v>
+        <v>82.56999999999999</v>
       </c>
       <c r="DI17" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DJ17" t="n">
-        <v>3.25</v>
+        <v>3.28</v>
       </c>
       <c r="DK17" t="n">
-        <v>3.4</v>
+        <v>3.33</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.3</v>
+        <v>0.28</v>
       </c>
       <c r="DM17" t="n">
-        <v>32</v>
+        <v>31.67</v>
       </c>
       <c r="DN17" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="DO17" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="DP17" t="n">
-        <v>17.35</v>
+        <v>17.47</v>
       </c>
       <c r="DQ17" t="n">
-        <v>12.65</v>
+        <v>12.62</v>
       </c>
       <c r="DR17" t="n">
-        <v>8.9</v>
+        <v>9.1</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>43.85</v>
+        <v>43.95</v>
       </c>
       <c r="DW17" t="n">
         <v>0.05</v>
       </c>
       <c r="DX17" t="n">
-        <v>11</v>
+        <v>11.09</v>
       </c>
       <c r="DY17" t="n">
-        <v>6.95</v>
+        <v>7.1</v>
       </c>
       <c r="DZ17" t="n">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="EA17" t="n">
-        <v>21.2</v>
+        <v>21.09</v>
       </c>
       <c r="EB17" t="n">
         <v>1.21</v>
       </c>
       <c r="EC17" t="n">
-        <v>3.15</v>
+        <v>3.19</v>
       </c>
     </row>
     <row r="18">
@@ -8302,10 +8302,10 @@
         <v>0.5</v>
       </c>
       <c r="Z19" t="n">
-        <v>11.2</v>
+        <v>11.3</v>
       </c>
       <c r="AA19" t="n">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="AB19" t="n">
         <v>3.4</v>
@@ -8458,7 +8458,7 @@
         <v>2.36</v>
       </c>
       <c r="BZ19" t="n">
-        <v>2.52</v>
+        <v>2.49</v>
       </c>
       <c r="CA19" t="n">
         <v>3.14</v>
@@ -8518,37 +8518,37 @@
         <v>3.22</v>
       </c>
       <c r="CT19" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="CU19" t="n">
         <v>1.37</v>
       </c>
       <c r="CV19" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CW19" t="n">
         <v>2</v>
       </c>
       <c r="CX19" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CY19" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="CZ19" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="DA19" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="DB19" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="DC19" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="DD19" t="n">
-        <v>4.3</v>
+        <v>4.28</v>
       </c>
       <c r="DE19" t="n">
         <v>0.05</v>
@@ -8608,10 +8608,10 @@
         <v>0.35</v>
       </c>
       <c r="DX19" t="n">
-        <v>12.25</v>
+        <v>12.3</v>
       </c>
       <c r="DY19" t="n">
-        <v>8.85</v>
+        <v>8.9</v>
       </c>
       <c r="DZ19" t="n">
         <v>3.4</v>
@@ -8633,13 +8633,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C20" t="n">
         <v>11</v>
       </c>
       <c r="D20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E20" t="n">
         <v>0.09</v>
@@ -8723,139 +8723,139 @@
         <v>2.55</v>
       </c>
       <c r="AF20" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="AI20" t="n">
-        <v>97.78</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0.22</v>
+        <v>0.1</v>
       </c>
       <c r="AK20" t="n">
-        <v>2.78</v>
+        <v>2.5</v>
       </c>
       <c r="AL20" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="AM20" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>47.4</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BH20" t="n">
+        <v>8.710000000000001</v>
+      </c>
+      <c r="BI20" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BJ20" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="BK20" t="n">
         <v>0.33</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>37.56</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>13.11</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>14</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>7.22</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>47.33</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>9.109999999999999</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>6.11</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>3</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>19.44</v>
-      </c>
-      <c r="BE20" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="BF20" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="BG20" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="BH20" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="BI20" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="BJ20" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="BK20" t="n">
-        <v>0.35</v>
       </c>
       <c r="BL20" t="n">
         <v>1.05</v>
       </c>
       <c r="BM20" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="BN20" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="BO20" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="BP20" t="n">
-        <v>3.95</v>
+        <v>3.81</v>
       </c>
       <c r="BQ20" t="n">
-        <v>4.95</v>
+        <v>4.9</v>
       </c>
       <c r="BR20" t="n">
-        <v>85</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BS20" t="n">
-        <v>75</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BT20" t="n">
-        <v>55</v>
+        <v>52.38</v>
       </c>
       <c r="BU20" t="n">
-        <v>20</v>
+        <v>19.05</v>
       </c>
       <c r="BV20" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BW20" t="n">
         <v>0</v>
       </c>
       <c r="BX20" t="n">
-        <v>55</v>
+        <v>52.38</v>
       </c>
       <c r="BY20" t="n">
         <v>1.9</v>
@@ -8864,55 +8864,55 @@
         <v>2.01</v>
       </c>
       <c r="CA20" t="n">
-        <v>3.21</v>
+        <v>3.19</v>
       </c>
       <c r="CB20" t="n">
-        <v>3.29</v>
+        <v>3.27</v>
       </c>
       <c r="CC20" t="n">
-        <v>3.3</v>
+        <v>3.27</v>
       </c>
       <c r="CD20" t="n">
-        <v>3.62</v>
+        <v>3.56</v>
       </c>
       <c r="CE20" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="CF20" t="n">
-        <v>3.24</v>
+        <v>3.27</v>
       </c>
       <c r="CG20" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="CH20" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="CI20" t="n">
         <v>1.74</v>
       </c>
       <c r="CJ20" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="CK20" t="n">
         <v>1.64</v>
       </c>
       <c r="CL20" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="CM20" t="n">
         <v>2.12</v>
-      </c>
-      <c r="CM20" t="n">
-        <v>2.13</v>
       </c>
       <c r="CN20" t="n">
         <v>1.72</v>
       </c>
       <c r="CO20" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CP20" t="n">
-        <v>2.33</v>
+        <v>2.37</v>
       </c>
       <c r="CQ20" t="n">
-        <v>4.28</v>
+        <v>4.41</v>
       </c>
       <c r="CR20" t="n">
         <v>1.54</v>
@@ -8927,106 +8927,106 @@
         <v>1.36</v>
       </c>
       <c r="CV20" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CW20" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="CX20" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="CY20" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="CZ20" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="DA20" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="DB20" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="DC20" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="DD20" t="n">
+        <v>4.77</v>
+      </c>
+      <c r="DE20" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="DF20" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="DG20" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="DH20" t="n">
+        <v>107.38</v>
+      </c>
+      <c r="DI20" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="DJ20" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="DK20" t="n">
+        <v>4.66</v>
+      </c>
+      <c r="DL20" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="DM20" t="n">
+        <v>49.62</v>
+      </c>
+      <c r="DN20" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="DO20" t="n">
         <v>1.81</v>
       </c>
-      <c r="CW20" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="CX20" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="CY20" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="CZ20" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="DA20" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="DB20" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="DC20" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="DD20" t="n">
-        <v>4.63</v>
-      </c>
-      <c r="DE20" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="DF20" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="DG20" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="DH20" t="n">
-        <v>107.55</v>
-      </c>
-      <c r="DI20" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="DJ20" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="DK20" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="DL20" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="DM20" t="n">
-        <v>50.25</v>
-      </c>
-      <c r="DN20" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="DO20" t="n">
-        <v>1.9</v>
-      </c>
       <c r="DP20" t="n">
-        <v>14.7</v>
+        <v>14.52</v>
       </c>
       <c r="DQ20" t="n">
-        <v>12.75</v>
+        <v>12.67</v>
       </c>
       <c r="DR20" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="DS20" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DT20" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DU20" t="n">
         <v>0</v>
       </c>
       <c r="DV20" t="n">
-        <v>51.2</v>
+        <v>51.05</v>
       </c>
       <c r="DW20" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DX20" t="n">
-        <v>12.95</v>
+        <v>12.76</v>
       </c>
       <c r="DY20" t="n">
-        <v>8.6</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="DZ20" t="n">
-        <v>4.35</v>
+        <v>4.24</v>
       </c>
       <c r="EA20" t="n">
-        <v>19.1</v>
+        <v>19.19</v>
       </c>
       <c r="EB20" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="EC20" t="n">
-        <v>2.45</v>
+        <v>2.34</v>
       </c>
     </row>
     <row r="21">
@@ -9183,7 +9183,7 @@
         <v>0</v>
       </c>
       <c r="AY21" t="n">
-        <v>46.7</v>
+        <v>46.8</v>
       </c>
       <c r="AZ21" t="n">
         <v>0.1</v>
@@ -9408,7 +9408,7 @@
         <v>0</v>
       </c>
       <c r="DV21" t="n">
-        <v>46.75</v>
+        <v>46.8</v>
       </c>
       <c r="DW21" t="n">
         <v>0.05</v>
@@ -9439,13 +9439,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C22" t="n">
         <v>11</v>
       </c>
       <c r="D22" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -9529,139 +9529,139 @@
         <v>2</v>
       </c>
       <c r="AF22" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AG22" t="n">
-        <v>2.78</v>
+        <v>2.6</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.89</v>
+        <v>2.8</v>
       </c>
       <c r="AI22" t="n">
-        <v>86.67</v>
+        <v>88.5</v>
       </c>
       <c r="AJ22" t="n">
         <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>3.56</v>
+        <v>3.3</v>
       </c>
       <c r="AL22" t="n">
-        <v>3.44</v>
+        <v>4.6</v>
       </c>
       <c r="AM22" t="n">
-        <v>0.22</v>
+        <v>0.5</v>
       </c>
       <c r="AN22" t="n">
-        <v>34.56</v>
+        <v>38.6</v>
       </c>
       <c r="AO22" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.56</v>
+        <v>1.8</v>
       </c>
       <c r="AQ22" t="n">
-        <v>11.89</v>
+        <v>11.7</v>
       </c>
       <c r="AR22" t="n">
-        <v>10.67</v>
+        <v>10.2</v>
       </c>
       <c r="AS22" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="AT22" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AU22" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="AV22" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="AW22" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="AX22" t="n">
         <v>0</v>
       </c>
       <c r="AY22" t="n">
-        <v>42.44</v>
+        <v>44.4</v>
       </c>
       <c r="AZ22" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="BA22" t="n">
-        <v>8.44</v>
+        <v>10.2</v>
       </c>
       <c r="BB22" t="n">
-        <v>4.89</v>
+        <v>6</v>
       </c>
       <c r="BC22" t="n">
-        <v>3.56</v>
+        <v>4.2</v>
       </c>
       <c r="BD22" t="n">
-        <v>19.67</v>
+        <v>19.6</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.04</v>
+        <v>1.22</v>
       </c>
       <c r="BF22" t="n">
-        <v>3.33</v>
+        <v>3.1</v>
       </c>
       <c r="BG22" t="n">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="BH22" t="n">
-        <v>9.6</v>
+        <v>10.1</v>
       </c>
       <c r="BI22" t="n">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="BJ22" t="n">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="BK22" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="BL22" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="BM22" t="n">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="BN22" t="n">
-        <v>1.45</v>
+        <v>1.57</v>
       </c>
       <c r="BO22" t="n">
         <v>1.05</v>
       </c>
       <c r="BP22" t="n">
-        <v>4.35</v>
+        <v>4.52</v>
       </c>
       <c r="BQ22" t="n">
-        <v>4.6</v>
+        <v>4.95</v>
       </c>
       <c r="BR22" t="n">
-        <v>95</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="BS22" t="n">
-        <v>60</v>
+        <v>61.9</v>
       </c>
       <c r="BT22" t="n">
-        <v>45</v>
+        <v>47.62</v>
       </c>
       <c r="BU22" t="n">
-        <v>25</v>
+        <v>28.57</v>
       </c>
       <c r="BV22" t="n">
-        <v>15</v>
+        <v>19.05</v>
       </c>
       <c r="BW22" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BX22" t="n">
-        <v>55</v>
+        <v>57.14</v>
       </c>
       <c r="BY22" t="n">
         <v>2.1</v>
@@ -9670,40 +9670,40 @@
         <v>2.11</v>
       </c>
       <c r="CA22" t="n">
-        <v>3.21</v>
+        <v>3.19</v>
       </c>
       <c r="CB22" t="n">
-        <v>3.3</v>
+        <v>3.29</v>
       </c>
       <c r="CC22" t="n">
-        <v>3.22</v>
+        <v>3.18</v>
       </c>
       <c r="CD22" t="n">
-        <v>3.32</v>
+        <v>3.26</v>
       </c>
       <c r="CE22" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="CF22" t="n">
-        <v>3.1</v>
+        <v>3.11</v>
       </c>
       <c r="CG22" t="n">
-        <v>2.67</v>
+        <v>2.66</v>
       </c>
       <c r="CH22" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="CI22" t="n">
         <v>1.86</v>
       </c>
       <c r="CJ22" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CK22" t="n">
         <v>1.62</v>
       </c>
       <c r="CL22" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="CM22" t="n">
         <v>2.17</v>
@@ -9712,19 +9712,19 @@
         <v>1.73</v>
       </c>
       <c r="CO22" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CP22" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="CQ22" t="n">
-        <v>3.91</v>
+        <v>3.94</v>
       </c>
       <c r="CR22" t="n">
         <v>1.48</v>
       </c>
       <c r="CS22" t="n">
-        <v>3.12</v>
+        <v>3.11</v>
       </c>
       <c r="CT22" t="n">
         <v>2.79</v>
@@ -9745,7 +9745,7 @@
         <v>2.07</v>
       </c>
       <c r="CZ22" t="n">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="DA22" t="n">
         <v>1.75</v>
@@ -9754,85 +9754,85 @@
         <v>1.42</v>
       </c>
       <c r="DC22" t="n">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="DD22" t="n">
-        <v>4.36</v>
+        <v>4.34</v>
       </c>
       <c r="DE22" t="n">
         <v>0.1</v>
       </c>
       <c r="DF22" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="DG22" t="n">
-        <v>2.1</v>
+        <v>2.52</v>
       </c>
       <c r="DH22" t="n">
-        <v>100.75</v>
+        <v>100.95</v>
       </c>
       <c r="DI22" t="n">
         <v>0</v>
       </c>
       <c r="DJ22" t="n">
-        <v>3</v>
+        <v>2.91</v>
       </c>
       <c r="DK22" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="DL22" t="n">
-        <v>0.4</v>
+        <v>0.53</v>
       </c>
       <c r="DM22" t="n">
-        <v>43.85</v>
+        <v>45.33</v>
       </c>
       <c r="DN22" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="DO22" t="n">
-        <v>2.05</v>
+        <v>2.14</v>
       </c>
       <c r="DP22" t="n">
-        <v>12.4</v>
+        <v>12.29</v>
       </c>
       <c r="DQ22" t="n">
-        <v>10.65</v>
+        <v>10.43</v>
       </c>
       <c r="DR22" t="n">
-        <v>7.65</v>
+        <v>7.48</v>
       </c>
       <c r="DS22" t="n">
-        <v>0.25</v>
+        <v>0.28</v>
       </c>
       <c r="DT22" t="n">
-        <v>0.25</v>
+        <v>0.28</v>
       </c>
       <c r="DU22" t="n">
         <v>0</v>
       </c>
       <c r="DV22" t="n">
-        <v>44.65</v>
+        <v>45.47</v>
       </c>
       <c r="DW22" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DX22" t="n">
-        <v>11.25</v>
+        <v>11.95</v>
       </c>
       <c r="DY22" t="n">
-        <v>6.8</v>
+        <v>7.24</v>
       </c>
       <c r="DZ22" t="n">
-        <v>4.45</v>
+        <v>4.71</v>
       </c>
       <c r="EA22" t="n">
-        <v>19.6</v>
+        <v>19.57</v>
       </c>
       <c r="EB22" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="EC22" t="n">
-        <v>2.6</v>
+        <v>2.52</v>
       </c>
     </row>
     <row r="23">
@@ -9842,61 +9842,61 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C23" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D23" t="n">
         <v>10</v>
       </c>
       <c r="E23" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="F23" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="G23" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="H23" t="n">
-        <v>95.5</v>
+        <v>97.36</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="K23" t="n">
-        <v>4</v>
+        <v>4.27</v>
       </c>
       <c r="L23" t="n">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="M23" t="n">
-        <v>37.6</v>
+        <v>39.27</v>
       </c>
       <c r="N23" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="O23" t="n">
-        <v>2.1</v>
+        <v>2.36</v>
       </c>
       <c r="P23" t="n">
-        <v>13.5</v>
+        <v>13.55</v>
       </c>
       <c r="Q23" t="n">
-        <v>16</v>
+        <v>15.55</v>
       </c>
       <c r="R23" t="n">
-        <v>6.4</v>
+        <v>6.09</v>
       </c>
       <c r="S23" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="T23" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="U23" t="n">
         <v>0</v>
@@ -9908,28 +9908,28 @@
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>54.5</v>
+        <v>55.18</v>
       </c>
       <c r="Y23" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="Z23" t="n">
-        <v>12</v>
+        <v>12.18</v>
       </c>
       <c r="AA23" t="n">
-        <v>7.7</v>
+        <v>7.73</v>
       </c>
       <c r="AB23" t="n">
-        <v>4.3</v>
+        <v>4.45</v>
       </c>
       <c r="AC23" t="n">
-        <v>18.6</v>
+        <v>18.27</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AF23" t="n">
         <v>0</v>
@@ -10013,49 +10013,49 @@
         <v>2</v>
       </c>
       <c r="BG23" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="BH23" t="n">
-        <v>7.4</v>
+        <v>7.52</v>
       </c>
       <c r="BI23" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="BJ23" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="BK23" t="n">
-        <v>0.3</v>
+        <v>0.33</v>
       </c>
       <c r="BL23" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="BM23" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="BN23" t="n">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="BO23" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="BP23" t="n">
-        <v>3.65</v>
+        <v>3.86</v>
       </c>
       <c r="BQ23" t="n">
-        <v>3.75</v>
+        <v>3.67</v>
       </c>
       <c r="BR23" t="n">
-        <v>80</v>
+        <v>80.95</v>
       </c>
       <c r="BS23" t="n">
-        <v>50</v>
+        <v>52.38</v>
       </c>
       <c r="BT23" t="n">
-        <v>35</v>
+        <v>33.33</v>
       </c>
       <c r="BU23" t="n">
-        <v>20</v>
+        <v>19.05</v>
       </c>
       <c r="BV23" t="n">
         <v>0</v>
@@ -10064,13 +10064,13 @@
         <v>0</v>
       </c>
       <c r="BX23" t="n">
-        <v>45</v>
+        <v>47.62</v>
       </c>
       <c r="BY23" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="BZ23" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="CA23" t="n">
         <v>3.22</v>
@@ -10082,13 +10082,13 @@
         <v>2.99</v>
       </c>
       <c r="CD23" t="n">
-        <v>3.3</v>
+        <v>3.33</v>
       </c>
       <c r="CE23" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="CF23" t="n">
-        <v>3.22</v>
+        <v>3.23</v>
       </c>
       <c r="CG23" t="n">
         <v>2.52</v>
@@ -10106,7 +10106,7 @@
         <v>1.7</v>
       </c>
       <c r="CL23" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="CM23" t="n">
         <v>2.07</v>
@@ -10118,91 +10118,91 @@
         <v>1.4</v>
       </c>
       <c r="CP23" t="n">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="CQ23" t="n">
         <v>4.2</v>
       </c>
       <c r="CR23" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="CS23" t="n">
-        <v>3.2</v>
+        <v>3.21</v>
       </c>
       <c r="CT23" t="n">
-        <v>2.68</v>
+        <v>2.67</v>
       </c>
       <c r="CU23" t="n">
         <v>1.37</v>
       </c>
       <c r="CV23" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CW23" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="CX23" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CY23" t="n">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="CZ23" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="DA23" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="DB23" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="DC23" t="n">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="DD23" t="n">
-        <v>4.6</v>
+        <v>4.55</v>
       </c>
       <c r="DE23" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DF23" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="DG23" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="DH23" t="n">
-        <v>92.95</v>
+        <v>94.05</v>
       </c>
       <c r="DI23" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ23" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="DK23" t="n">
-        <v>3.9</v>
+        <v>4.05</v>
       </c>
       <c r="DL23" t="n">
-        <v>0.25</v>
+        <v>0.28</v>
       </c>
       <c r="DM23" t="n">
-        <v>37.4</v>
+        <v>38.28</v>
       </c>
       <c r="DN23" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="DO23" t="n">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="DP23" t="n">
-        <v>12.95</v>
+        <v>13</v>
       </c>
       <c r="DQ23" t="n">
-        <v>17.5</v>
+        <v>17.19</v>
       </c>
       <c r="DR23" t="n">
-        <v>7.8</v>
+        <v>7.57</v>
       </c>
       <c r="DS23" t="n">
         <v>0</v>
@@ -10214,28 +10214,28 @@
         <v>0</v>
       </c>
       <c r="DV23" t="n">
-        <v>55.5</v>
+        <v>55.81</v>
       </c>
       <c r="DW23" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DX23" t="n">
-        <v>11.05</v>
+        <v>11.19</v>
       </c>
       <c r="DY23" t="n">
-        <v>7.45</v>
+        <v>7.48</v>
       </c>
       <c r="DZ23" t="n">
-        <v>3.6</v>
+        <v>3.71</v>
       </c>
       <c r="EA23" t="n">
-        <v>18.4</v>
+        <v>18.24</v>
       </c>
       <c r="EB23" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="EC23" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Spain_Segunda_División_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Spain_Segunda_División_2025-2026.xlsx
@@ -1526,7 +1526,7 @@
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>43.82</v>
+        <v>43.91</v>
       </c>
       <c r="AZ2" t="n">
         <v>0.27</v>
@@ -1751,7 +1751,7 @@
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>43.57</v>
+        <v>43.62</v>
       </c>
       <c r="DW2" t="n">
         <v>0.19</v>
@@ -1875,7 +1875,7 @@
         <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AH3" t="n">
         <v>1.73</v>
@@ -1887,7 +1887,7 @@
         <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>3.27</v>
+        <v>3.36</v>
       </c>
       <c r="AL3" t="n">
         <v>3.27</v>
@@ -1950,7 +1950,7 @@
         <v>1.47</v>
       </c>
       <c r="BF3" t="n">
-        <v>3.18</v>
+        <v>3.27</v>
       </c>
       <c r="BG3" t="n">
         <v>3.33</v>
@@ -2106,7 +2106,7 @@
         <v>0.05</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="DG3" t="n">
         <v>2.76</v>
@@ -2118,7 +2118,7 @@
         <v>0</v>
       </c>
       <c r="DJ3" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="DK3" t="n">
         <v>5.43</v>
@@ -2175,7 +2175,7 @@
         <v>1.75</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="4">
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C5" t="n">
         <v>10</v>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E5" t="n">
         <v>0.3</v>
@@ -2678,52 +2678,52 @@
         <v>3.2</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AH5" t="n">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="AI5" t="n">
-        <v>92.7</v>
+        <v>91.73</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.3</v>
+        <v>0.18</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.8</v>
+        <v>2.55</v>
       </c>
       <c r="AL5" t="n">
-        <v>6.3</v>
+        <v>6.27</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AN5" t="n">
-        <v>57.1</v>
+        <v>56.09</v>
       </c>
       <c r="AO5" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>13.18</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>13.73</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>5.82</v>
+      </c>
+      <c r="AT5" t="n">
         <v>1</v>
       </c>
-      <c r="AP5" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>14</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>6</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>1.1</v>
-      </c>
       <c r="AU5" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AV5" t="n">
         <v>0</v>
@@ -2738,79 +2738,79 @@
         <v>53</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="BA5" t="n">
-        <v>13.3</v>
+        <v>12.82</v>
       </c>
       <c r="BB5" t="n">
-        <v>9</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="BC5" t="n">
-        <v>4.3</v>
+        <v>4.18</v>
       </c>
       <c r="BD5" t="n">
-        <v>19.4</v>
+        <v>19.82</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="BF5" t="n">
-        <v>2.6</v>
+        <v>2.36</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.95</v>
+        <v>2.81</v>
       </c>
       <c r="BH5" t="n">
-        <v>10.2</v>
+        <v>10.29</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.95</v>
+        <v>2.81</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="BL5" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="BP5" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.2</v>
+        <v>5.19</v>
       </c>
       <c r="BR5" t="n">
-        <v>90</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BS5" t="n">
-        <v>65</v>
+        <v>61.9</v>
       </c>
       <c r="BT5" t="n">
-        <v>55</v>
+        <v>52.38</v>
       </c>
       <c r="BU5" t="n">
-        <v>45</v>
+        <v>42.86</v>
       </c>
       <c r="BV5" t="n">
-        <v>15</v>
+        <v>14.29</v>
       </c>
       <c r="BW5" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BX5" t="n">
-        <v>60</v>
+        <v>57.14</v>
       </c>
       <c r="BY5" t="n">
         <v>1.67</v>
@@ -2819,16 +2819,16 @@
         <v>1.66</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.59</v>
+        <v>3.58</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.88</v>
+        <v>3.86</v>
       </c>
       <c r="CC5" t="n">
-        <v>2.77</v>
+        <v>2.74</v>
       </c>
       <c r="CD5" t="n">
-        <v>2.97</v>
+        <v>2.92</v>
       </c>
       <c r="CE5" t="n">
         <v>1.34</v>
@@ -2837,22 +2837,22 @@
         <v>2.61</v>
       </c>
       <c r="CG5" t="n">
-        <v>3.06</v>
+        <v>3.05</v>
       </c>
       <c r="CH5" t="n">
         <v>1.46</v>
       </c>
       <c r="CI5" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CK5" t="n">
         <v>1.53</v>
       </c>
       <c r="CL5" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CM5" t="n">
         <v>2.34</v>
@@ -2873,13 +2873,13 @@
         <v>1.38</v>
       </c>
       <c r="CS5" t="n">
-        <v>2.76</v>
+        <v>2.77</v>
       </c>
       <c r="CT5" t="n">
-        <v>3.16</v>
+        <v>3.15</v>
       </c>
       <c r="CU5" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CV5" t="n">
         <v>2.18</v>
@@ -2891,97 +2891,97 @@
         <v>1.55</v>
       </c>
       <c r="CY5" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CZ5" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="DA5" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="DB5" t="n">
         <v>1.26</v>
       </c>
       <c r="DC5" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="DD5" t="n">
-        <v>3.06</v>
+        <v>3.08</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DF5" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="DG5" t="n">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="DH5" t="n">
-        <v>98.59999999999999</v>
+        <v>97.81</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.15</v>
+        <v>0.09</v>
       </c>
       <c r="DJ5" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="DK5" t="n">
-        <v>6.5</v>
+        <v>6.47</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.55</v>
+        <v>0.53</v>
       </c>
       <c r="DM5" t="n">
-        <v>58.05</v>
+        <v>57.48</v>
       </c>
       <c r="DN5" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="DO5" t="n">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="DP5" t="n">
-        <v>13.4</v>
+        <v>13.43</v>
       </c>
       <c r="DQ5" t="n">
-        <v>14.3</v>
+        <v>14.14</v>
       </c>
       <c r="DR5" t="n">
-        <v>5.45</v>
+        <v>5.38</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>55.3</v>
+        <v>55.19</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DX5" t="n">
-        <v>14.85</v>
+        <v>14.52</v>
       </c>
       <c r="DY5" t="n">
-        <v>9.75</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="DZ5" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="EA5" t="n">
-        <v>18.85</v>
+        <v>19.1</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="EC5" t="n">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
     </row>
     <row r="6">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C6" t="n">
         <v>10</v>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E6" t="n">
         <v>0.2</v>
@@ -3081,139 +3081,139 @@
         <v>2.7</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="AG6" t="n">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="AI6" t="n">
-        <v>80.40000000000001</v>
+        <v>81.27</v>
       </c>
       <c r="AJ6" t="n">
         <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="AL6" t="n">
-        <v>3.4</v>
+        <v>3.64</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="AN6" t="n">
-        <v>35.8</v>
+        <v>36.73</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.6</v>
+        <v>0.73</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AQ6" t="n">
-        <v>12.7</v>
+        <v>12.55</v>
       </c>
       <c r="AR6" t="n">
-        <v>13.5</v>
+        <v>12.82</v>
       </c>
       <c r="AS6" t="n">
-        <v>9.1</v>
+        <v>8.73</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AU6" t="n">
         <v>1</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AX6" t="n">
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>48</v>
+        <v>48.18</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="BA6" t="n">
-        <v>9.800000000000001</v>
+        <v>9.18</v>
       </c>
       <c r="BB6" t="n">
-        <v>7.1</v>
+        <v>6.55</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="BD6" t="n">
-        <v>20.3</v>
+        <v>21.36</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="BF6" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.4</v>
+        <v>2.43</v>
       </c>
       <c r="BH6" t="n">
-        <v>9</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.4</v>
+        <v>2.43</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.4</v>
+        <v>0.43</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="BP6" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="BQ6" t="n">
-        <v>4.9</v>
+        <v>4.95</v>
       </c>
       <c r="BR6" t="n">
-        <v>90</v>
+        <v>90.48</v>
       </c>
       <c r="BS6" t="n">
-        <v>65</v>
+        <v>66.67</v>
       </c>
       <c r="BT6" t="n">
-        <v>45</v>
+        <v>47.62</v>
       </c>
       <c r="BU6" t="n">
-        <v>20</v>
+        <v>19.05</v>
       </c>
       <c r="BV6" t="n">
-        <v>15</v>
+        <v>14.29</v>
       </c>
       <c r="BW6" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BX6" t="n">
-        <v>50</v>
+        <v>52.38</v>
       </c>
       <c r="BY6" t="n">
         <v>2.38</v>
@@ -3222,22 +3222,22 @@
         <v>2.57</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.21</v>
+        <v>3.2</v>
       </c>
       <c r="CB6" t="n">
         <v>3.32</v>
       </c>
       <c r="CC6" t="n">
-        <v>4.06</v>
+        <v>3.99</v>
       </c>
       <c r="CD6" t="n">
-        <v>4.42</v>
+        <v>4.37</v>
       </c>
       <c r="CE6" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CF6" t="n">
-        <v>3.06</v>
+        <v>3.05</v>
       </c>
       <c r="CG6" t="n">
         <v>2.64</v>
@@ -3249,7 +3249,7 @@
         <v>1.84</v>
       </c>
       <c r="CJ6" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CK6" t="n">
         <v>1.67</v>
@@ -3270,7 +3270,7 @@
         <v>2.2</v>
       </c>
       <c r="CQ6" t="n">
-        <v>3.99</v>
+        <v>3.97</v>
       </c>
       <c r="CR6" t="n">
         <v>1.47</v>
@@ -3285,10 +3285,10 @@
         <v>1.39</v>
       </c>
       <c r="CV6" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="CW6" t="n">
         <v>1.93</v>
-      </c>
-      <c r="CW6" t="n">
-        <v>1.94</v>
       </c>
       <c r="CX6" t="n">
         <v>1.69</v>
@@ -3312,79 +3312,79 @@
         <v>4.1</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.15</v>
+        <v>0.19</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.2</v>
+        <v>2.29</v>
       </c>
       <c r="DH6" t="n">
-        <v>88.65000000000001</v>
+        <v>88.70999999999999</v>
       </c>
       <c r="DI6" t="n">
         <v>0.1</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.7</v>
+        <v>2.67</v>
       </c>
       <c r="DK6" t="n">
-        <v>4.35</v>
+        <v>4.43</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.35</v>
+        <v>0.38</v>
       </c>
       <c r="DM6" t="n">
-        <v>44.3</v>
+        <v>44.38</v>
       </c>
       <c r="DN6" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="DO6" t="n">
         <v>1.95</v>
       </c>
       <c r="DP6" t="n">
-        <v>13.75</v>
+        <v>13.62</v>
       </c>
       <c r="DQ6" t="n">
-        <v>13.3</v>
+        <v>12.95</v>
       </c>
       <c r="DR6" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>50.1</v>
+        <v>50.09</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DX6" t="n">
-        <v>10.7</v>
+        <v>10.33</v>
       </c>
       <c r="DY6" t="n">
-        <v>7.15</v>
+        <v>6.86</v>
       </c>
       <c r="DZ6" t="n">
-        <v>3.55</v>
+        <v>3.48</v>
       </c>
       <c r="EA6" t="n">
-        <v>20.8</v>
+        <v>21.33</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.55</v>
+        <v>2.52</v>
       </c>
     </row>
     <row r="7">
@@ -3706,13 +3706,13 @@
         <v>1.79</v>
       </c>
       <c r="DB7" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="DC7" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="DD7" t="n">
-        <v>3.86</v>
+        <v>3.89</v>
       </c>
       <c r="DE7" t="n">
         <v>0.09</v>
@@ -4200,13 +4200,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C9" t="n">
         <v>10</v>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E9" t="n">
         <v>0.1</v>
@@ -4290,52 +4290,52 @@
         <v>2.8</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.6</v>
+        <v>2.91</v>
       </c>
       <c r="AI9" t="n">
-        <v>92.09999999999999</v>
+        <v>93.81999999999999</v>
       </c>
       <c r="AJ9" t="n">
-        <v>-0.1</v>
+        <v>-0.09</v>
       </c>
       <c r="AK9" t="n">
-        <v>3.2</v>
+        <v>3.09</v>
       </c>
       <c r="AL9" t="n">
-        <v>4.7</v>
+        <v>4.91</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AN9" t="n">
-        <v>41.2</v>
+        <v>42.45</v>
       </c>
       <c r="AO9" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AP9" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AQ9" t="n">
-        <v>16.2</v>
+        <v>15.45</v>
       </c>
       <c r="AR9" t="n">
-        <v>15.1</v>
+        <v>15</v>
       </c>
       <c r="AS9" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="AV9" t="n">
         <v>0</v>
@@ -4347,73 +4347,73 @@
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>53.7</v>
+        <v>54.82</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="BA9" t="n">
-        <v>13.2</v>
+        <v>13.27</v>
       </c>
       <c r="BB9" t="n">
-        <v>8.6</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="BC9" t="n">
-        <v>4.6</v>
+        <v>4.64</v>
       </c>
       <c r="BD9" t="n">
-        <v>22.8</v>
+        <v>22.36</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="BF9" t="n">
-        <v>3</v>
+        <v>2.91</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.4</v>
+        <v>2.43</v>
       </c>
       <c r="BH9" t="n">
-        <v>9.65</v>
+        <v>9.76</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.4</v>
+        <v>2.43</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.4</v>
+        <v>0.43</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.8</v>
+        <v>4.81</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.85</v>
+        <v>4.95</v>
       </c>
       <c r="BR9" t="n">
-        <v>85</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BS9" t="n">
-        <v>75</v>
+        <v>76.19</v>
       </c>
       <c r="BT9" t="n">
-        <v>50</v>
+        <v>52.38</v>
       </c>
       <c r="BU9" t="n">
-        <v>30</v>
+        <v>28.57</v>
       </c>
       <c r="BV9" t="n">
         <v>0</v>
@@ -4422,7 +4422,7 @@
         <v>0</v>
       </c>
       <c r="BX9" t="n">
-        <v>65</v>
+        <v>66.67</v>
       </c>
       <c r="BY9" t="n">
         <v>2.1</v>
@@ -4431,34 +4431,34 @@
         <v>2.12</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.25</v>
+        <v>3.23</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.39</v>
+        <v>3.37</v>
       </c>
       <c r="CC9" t="n">
-        <v>2.97</v>
+        <v>2.95</v>
       </c>
       <c r="CD9" t="n">
-        <v>3.15</v>
+        <v>3.14</v>
       </c>
       <c r="CE9" t="n">
         <v>1.41</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="CG9" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="CH9" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CI9" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CK9" t="n">
         <v>1.53</v>
@@ -4470,16 +4470,16 @@
         <v>2.36</v>
       </c>
       <c r="CN9" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="CO9" t="n">
         <v>1.29</v>
       </c>
       <c r="CP9" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="CQ9" t="n">
-        <v>3.31</v>
+        <v>3.37</v>
       </c>
       <c r="CR9" t="n">
         <v>1.43</v>
@@ -4494,106 +4494,106 @@
         <v>1.41</v>
       </c>
       <c r="CV9" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="CW9" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CX9" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CY9" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CZ9" t="n">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="DA9" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="DB9" t="n">
         <v>1.32</v>
       </c>
       <c r="DC9" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="DD9" t="n">
-        <v>3.54</v>
+        <v>3.6</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="DG9" t="n">
-        <v>2.55</v>
+        <v>2.71</v>
       </c>
       <c r="DH9" t="n">
-        <v>96.95</v>
+        <v>97.62</v>
       </c>
       <c r="DI9" t="n">
         <v>0</v>
       </c>
       <c r="DJ9" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="DK9" t="n">
-        <v>4.95</v>
+        <v>5.05</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="DM9" t="n">
-        <v>47.9</v>
+        <v>48.24</v>
       </c>
       <c r="DN9" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="DO9" t="n">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="DP9" t="n">
-        <v>16.15</v>
+        <v>15.76</v>
       </c>
       <c r="DQ9" t="n">
-        <v>15.1</v>
+        <v>15.05</v>
       </c>
       <c r="DR9" t="n">
-        <v>5.95</v>
+        <v>6.05</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>56.4</v>
+        <v>56.86</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DX9" t="n">
-        <v>14.65</v>
+        <v>14.62</v>
       </c>
       <c r="DY9" t="n">
-        <v>9.9</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="DZ9" t="n">
-        <v>4.75</v>
+        <v>4.76</v>
       </c>
       <c r="EA9" t="n">
-        <v>22.05</v>
+        <v>21.86</v>
       </c>
       <c r="EB9" t="n">
         <v>1.6</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="10">
@@ -5324,7 +5324,7 @@
         <v>2.08</v>
       </c>
       <c r="DD11" t="n">
-        <v>3.68</v>
+        <v>3.69</v>
       </c>
       <c r="DE11" t="n">
         <v>0.05</v>
@@ -5409,61 +5409,61 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D12" t="n">
         <v>10</v>
       </c>
       <c r="E12" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="F12" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="G12" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="H12" t="n">
-        <v>91.90000000000001</v>
+        <v>92.36</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>-0.09</v>
       </c>
       <c r="J12" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="K12" t="n">
-        <v>5.9</v>
+        <v>5.91</v>
       </c>
       <c r="L12" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="M12" t="n">
-        <v>46.5</v>
+        <v>45.82</v>
       </c>
       <c r="N12" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="O12" t="n">
-        <v>2.8</v>
+        <v>2.91</v>
       </c>
       <c r="P12" t="n">
-        <v>12.2</v>
+        <v>12.09</v>
       </c>
       <c r="Q12" t="n">
-        <v>15.4</v>
+        <v>15.27</v>
       </c>
       <c r="R12" t="n">
-        <v>7.6</v>
+        <v>7.36</v>
       </c>
       <c r="S12" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="T12" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="U12" t="n">
         <v>0</v>
@@ -5475,28 +5475,28 @@
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>52.4</v>
+        <v>51.91</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="Z12" t="n">
-        <v>15.1</v>
+        <v>14.73</v>
       </c>
       <c r="AA12" t="n">
-        <v>11.2</v>
+        <v>10.82</v>
       </c>
       <c r="AB12" t="n">
-        <v>3.9</v>
+        <v>3.91</v>
       </c>
       <c r="AC12" t="n">
-        <v>22.6</v>
+        <v>23.27</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>
@@ -5580,67 +5580,67 @@
         <v>2.8</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.15</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.05</v>
+        <v>4.19</v>
       </c>
       <c r="BQ12" t="n">
         <v>5.1</v>
       </c>
       <c r="BR12" t="n">
-        <v>85</v>
+        <v>80.95</v>
       </c>
       <c r="BS12" t="n">
-        <v>70</v>
+        <v>66.67</v>
       </c>
       <c r="BT12" t="n">
-        <v>45</v>
+        <v>42.86</v>
       </c>
       <c r="BU12" t="n">
-        <v>30</v>
+        <v>28.57</v>
       </c>
       <c r="BV12" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BW12" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BX12" t="n">
-        <v>60</v>
+        <v>57.14</v>
       </c>
       <c r="BY12" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="BZ12" t="n">
-        <v>2.27</v>
+        <v>2.35</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.2</v>
+        <v>3.21</v>
       </c>
       <c r="CB12" t="n">
         <v>3.28</v>
@@ -5655,7 +5655,7 @@
         <v>1.45</v>
       </c>
       <c r="CF12" t="n">
-        <v>3.12</v>
+        <v>3.1</v>
       </c>
       <c r="CG12" t="n">
         <v>2.63</v>
@@ -5664,16 +5664,16 @@
         <v>1.33</v>
       </c>
       <c r="CI12" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="CJ12" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="CK12" t="n">
         <v>1.58</v>
       </c>
       <c r="CL12" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="CM12" t="n">
         <v>2.23</v>
@@ -5682,31 +5682,31 @@
         <v>1.78</v>
       </c>
       <c r="CO12" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CP12" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="CQ12" t="n">
-        <v>3.92</v>
+        <v>3.87</v>
       </c>
       <c r="CR12" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CS12" t="n">
-        <v>3.26</v>
+        <v>3.24</v>
       </c>
       <c r="CT12" t="n">
-        <v>2.71</v>
+        <v>2.73</v>
       </c>
       <c r="CU12" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CV12" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CW12" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CX12" t="n">
         <v>1.65</v>
@@ -5715,61 +5715,61 @@
         <v>2.08</v>
       </c>
       <c r="CZ12" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="DA12" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="DB12" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="DC12" t="n">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="DD12" t="n">
-        <v>4.23</v>
+        <v>4.18</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="DG12" t="n">
         <v>2.05</v>
       </c>
       <c r="DH12" t="n">
-        <v>90.84999999999999</v>
+        <v>91.14</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.6</v>
+        <v>2.48</v>
       </c>
       <c r="DK12" t="n">
-        <v>4.35</v>
+        <v>4.43</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.45</v>
+        <v>0.48</v>
       </c>
       <c r="DM12" t="n">
-        <v>42.9</v>
+        <v>42.72</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.8</v>
+        <v>0.76</v>
       </c>
       <c r="DO12" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="DP12" t="n">
-        <v>13.2</v>
+        <v>13.09</v>
       </c>
       <c r="DQ12" t="n">
-        <v>14.9</v>
+        <v>14.86</v>
       </c>
       <c r="DR12" t="n">
-        <v>7.85</v>
+        <v>7.71</v>
       </c>
       <c r="DS12" t="n">
         <v>0.05</v>
@@ -5781,28 +5781,28 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>49.5</v>
+        <v>49.38</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DX12" t="n">
-        <v>12.8</v>
+        <v>12.72</v>
       </c>
       <c r="DY12" t="n">
-        <v>9.15</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="DZ12" t="n">
-        <v>3.65</v>
+        <v>3.67</v>
       </c>
       <c r="EA12" t="n">
-        <v>22.05</v>
+        <v>22.43</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.35</v>
+        <v>2.24</v>
       </c>
     </row>
     <row r="13">
@@ -5812,94 +5812,94 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D13" t="n">
         <v>11</v>
       </c>
       <c r="E13" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="F13" t="n">
-        <v>2.22</v>
+        <v>2.4</v>
       </c>
       <c r="G13" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="H13" t="n">
-        <v>88.89</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>3.11</v>
+        <v>3.2</v>
       </c>
       <c r="K13" t="n">
-        <v>5.56</v>
+        <v>5.4</v>
       </c>
       <c r="L13" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="M13" t="n">
-        <v>44</v>
+        <v>42.5</v>
       </c>
       <c r="N13" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="O13" t="n">
-        <v>3.11</v>
+        <v>3</v>
       </c>
       <c r="P13" t="n">
-        <v>13.44</v>
+        <v>14.2</v>
       </c>
       <c r="Q13" t="n">
-        <v>15.22</v>
+        <v>14.9</v>
       </c>
       <c r="R13" t="n">
-        <v>7.56</v>
+        <v>7.8</v>
       </c>
       <c r="S13" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="T13" t="n">
-        <v>0.67</v>
+        <v>0.9</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>51.56</v>
+        <v>50.8</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="Z13" t="n">
-        <v>12.22</v>
+        <v>12.2</v>
       </c>
       <c r="AA13" t="n">
-        <v>7.67</v>
+        <v>7.7</v>
       </c>
       <c r="AB13" t="n">
-        <v>4.56</v>
+        <v>4.5</v>
       </c>
       <c r="AC13" t="n">
-        <v>23.11</v>
+        <v>22.9</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="AE13" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="AF13" t="n">
         <v>0</v>
@@ -5983,64 +5983,64 @@
         <v>3.09</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="BH13" t="n">
-        <v>9.5</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.4</v>
+        <v>0.48</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.4</v>
+        <v>0.43</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.8</v>
+        <v>0.76</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="BO13" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="BP13" t="n">
-        <v>4.45</v>
+        <v>4.43</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4.55</v>
+        <v>4.71</v>
       </c>
       <c r="BR13" t="n">
-        <v>80</v>
+        <v>80.95</v>
       </c>
       <c r="BS13" t="n">
-        <v>65</v>
+        <v>66.67</v>
       </c>
       <c r="BT13" t="n">
-        <v>40</v>
+        <v>42.86</v>
       </c>
       <c r="BU13" t="n">
-        <v>15</v>
+        <v>14.29</v>
       </c>
       <c r="BV13" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BW13" t="n">
         <v>0</v>
       </c>
       <c r="BX13" t="n">
-        <v>50</v>
+        <v>47.62</v>
       </c>
       <c r="BY13" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="BZ13" t="n">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="CA13" t="n">
         <v>3.03</v>
@@ -6058,7 +6058,7 @@
         <v>1.49</v>
       </c>
       <c r="CF13" t="n">
-        <v>3.25</v>
+        <v>3.26</v>
       </c>
       <c r="CG13" t="n">
         <v>2.54</v>
@@ -6076,16 +6076,16 @@
         <v>1.6</v>
       </c>
       <c r="CL13" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="CN13" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CO13" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CP13" t="n">
         <v>2.33</v>
@@ -6109,16 +6109,16 @@
         <v>1.87</v>
       </c>
       <c r="CW13" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="CX13" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CY13" t="n">
         <v>2.11</v>
       </c>
       <c r="CZ13" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="DA13" t="n">
         <v>1.72</v>
@@ -6130,82 +6130,82 @@
         <v>2.42</v>
       </c>
       <c r="DD13" t="n">
-        <v>4.6</v>
+        <v>4.61</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DF13" t="n">
-        <v>2.15</v>
+        <v>2.24</v>
       </c>
       <c r="DG13" t="n">
         <v>1.95</v>
       </c>
       <c r="DH13" t="n">
-        <v>86.05</v>
+        <v>84.62</v>
       </c>
       <c r="DI13" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ13" t="n">
-        <v>3.35</v>
+        <v>3.38</v>
       </c>
       <c r="DK13" t="n">
-        <v>4.7</v>
+        <v>4.67</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.3</v>
+        <v>0.33</v>
       </c>
       <c r="DM13" t="n">
-        <v>38.85</v>
+        <v>38.38</v>
       </c>
       <c r="DN13" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="DO13" t="n">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="DP13" t="n">
-        <v>12.65</v>
+        <v>13.05</v>
       </c>
       <c r="DQ13" t="n">
-        <v>14.35</v>
+        <v>14.24</v>
       </c>
       <c r="DR13" t="n">
-        <v>8.1</v>
+        <v>8.19</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.1</v>
+        <v>0.14</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.1</v>
+        <v>0.14</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>50.55</v>
+        <v>50.24</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DX13" t="n">
-        <v>11.15</v>
+        <v>11.19</v>
       </c>
       <c r="DY13" t="n">
-        <v>6.8</v>
+        <v>6.86</v>
       </c>
       <c r="DZ13" t="n">
-        <v>4.35</v>
+        <v>4.33</v>
       </c>
       <c r="EA13" t="n">
-        <v>21.25</v>
+        <v>21.24</v>
       </c>
       <c r="EB13" t="n">
         <v>1.29</v>
       </c>
       <c r="EC13" t="n">
-        <v>3.05</v>
+        <v>3.09</v>
       </c>
     </row>
     <row r="14">
@@ -6227,7 +6227,7 @@
         <v>0.1</v>
       </c>
       <c r="F14" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="G14" t="n">
         <v>2.2</v>
@@ -6239,7 +6239,7 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="K14" t="n">
         <v>4.1</v>
@@ -6302,7 +6302,7 @@
         <v>1.33</v>
       </c>
       <c r="AE14" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="AF14" t="n">
         <v>0.09</v>
@@ -6539,7 +6539,7 @@
         <v>0.09</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="DG14" t="n">
         <v>1.76</v>
@@ -6551,7 +6551,7 @@
         <v>0.05</v>
       </c>
       <c r="DJ14" t="n">
-        <v>3.33</v>
+        <v>3.38</v>
       </c>
       <c r="DK14" t="n">
         <v>3.24</v>
@@ -6608,7 +6608,7 @@
         <v>1.18</v>
       </c>
       <c r="EC14" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
     </row>
     <row r="15">
@@ -6618,94 +6618,94 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D15" t="n">
         <v>10</v>
       </c>
       <c r="E15" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="F15" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="G15" t="n">
         <v>2</v>
       </c>
       <c r="H15" t="n">
-        <v>86.90000000000001</v>
+        <v>88.81999999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="J15" t="n">
-        <v>2.6</v>
+        <v>2.73</v>
       </c>
       <c r="K15" t="n">
-        <v>3.7</v>
+        <v>3.91</v>
       </c>
       <c r="L15" t="n">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="M15" t="n">
-        <v>46.9</v>
+        <v>47.27</v>
       </c>
       <c r="N15" t="n">
-        <v>0.8</v>
+        <v>0.91</v>
       </c>
       <c r="O15" t="n">
-        <v>1.7</v>
+        <v>1.91</v>
       </c>
       <c r="P15" t="n">
-        <v>14.2</v>
+        <v>13.45</v>
       </c>
       <c r="Q15" t="n">
-        <v>12.4</v>
+        <v>12.09</v>
       </c>
       <c r="R15" t="n">
-        <v>7.9</v>
+        <v>7.73</v>
       </c>
       <c r="S15" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="T15" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>51.4</v>
+        <v>51.27</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="Z15" t="n">
-        <v>15.1</v>
+        <v>15.36</v>
       </c>
       <c r="AA15" t="n">
-        <v>9</v>
+        <v>9.09</v>
       </c>
       <c r="AB15" t="n">
-        <v>6.1</v>
+        <v>6.27</v>
       </c>
       <c r="AC15" t="n">
-        <v>21.9</v>
+        <v>21.55</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="AF15" t="n">
         <v>0.1</v>
@@ -6789,67 +6789,67 @@
         <v>2.1</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="BH15" t="n">
-        <v>8.35</v>
+        <v>8.52</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.7</v>
+        <v>0.76</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.25</v>
+        <v>0.29</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.8</v>
+        <v>0.76</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="BO15" t="n">
-        <v>0.95</v>
+        <v>1.05</v>
       </c>
       <c r="BP15" t="n">
-        <v>3.35</v>
+        <v>3.48</v>
       </c>
       <c r="BQ15" t="n">
-        <v>4.4</v>
+        <v>4.48</v>
       </c>
       <c r="BR15" t="n">
         <v>100</v>
       </c>
       <c r="BS15" t="n">
-        <v>75</v>
+        <v>76.19</v>
       </c>
       <c r="BT15" t="n">
-        <v>55</v>
+        <v>57.14</v>
       </c>
       <c r="BU15" t="n">
-        <v>30</v>
+        <v>28.57</v>
       </c>
       <c r="BV15" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BW15" t="n">
         <v>0</v>
       </c>
       <c r="BX15" t="n">
-        <v>60</v>
+        <v>61.9</v>
       </c>
       <c r="BY15" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="BZ15" t="n">
         <v>2.29</v>
       </c>
-      <c r="BZ15" t="n">
-        <v>2.3</v>
-      </c>
       <c r="CA15" t="n">
-        <v>3.22</v>
+        <v>3.21</v>
       </c>
       <c r="CB15" t="n">
         <v>3.36</v>
@@ -6876,10 +6876,10 @@
         <v>1.82</v>
       </c>
       <c r="CJ15" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CK15" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="CL15" t="n">
         <v>2.16</v>
@@ -6891,13 +6891,13 @@
         <v>1.76</v>
       </c>
       <c r="CO15" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CP15" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.9</v>
+        <v>3.88</v>
       </c>
       <c r="CR15" t="n">
         <v>1.48</v>
@@ -6939,79 +6939,79 @@
         <v>4.19</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="DG15" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="DH15" t="n">
-        <v>88.59999999999999</v>
+        <v>89.52</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="DJ15" t="n">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="DK15" t="n">
-        <v>3.95</v>
+        <v>4.05</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.2</v>
+        <v>0.24</v>
       </c>
       <c r="DM15" t="n">
-        <v>46.15</v>
+        <v>46.38</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.8</v>
+        <v>0.86</v>
       </c>
       <c r="DO15" t="n">
-        <v>1.45</v>
+        <v>1.57</v>
       </c>
       <c r="DP15" t="n">
-        <v>13.1</v>
+        <v>12.76</v>
       </c>
       <c r="DQ15" t="n">
-        <v>12.3</v>
+        <v>12.14</v>
       </c>
       <c r="DR15" t="n">
-        <v>8.050000000000001</v>
+        <v>7.95</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.1</v>
+        <v>0.14</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.1</v>
+        <v>0.14</v>
       </c>
       <c r="DU15" t="n">
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>51.1</v>
+        <v>51.05</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DX15" t="n">
-        <v>12.6</v>
+        <v>12.86</v>
       </c>
       <c r="DY15" t="n">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="DZ15" t="n">
-        <v>4.8</v>
+        <v>4.95</v>
       </c>
       <c r="EA15" t="n">
-        <v>22.35</v>
+        <v>22.15</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="EC15" t="n">
-        <v>2.25</v>
+        <v>2.34</v>
       </c>
     </row>
     <row r="16">
@@ -7021,94 +7021,94 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D16" t="n">
         <v>10</v>
       </c>
       <c r="E16" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="F16" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="G16" t="n">
-        <v>4</v>
+        <v>4.64</v>
       </c>
       <c r="H16" t="n">
-        <v>100.4</v>
+        <v>103.36</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="K16" t="n">
-        <v>7.3</v>
+        <v>7.82</v>
       </c>
       <c r="L16" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="M16" t="n">
-        <v>47.1</v>
+        <v>50.91</v>
       </c>
       <c r="N16" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="O16" t="n">
-        <v>3.3</v>
+        <v>3.18</v>
       </c>
       <c r="P16" t="n">
-        <v>12.7</v>
+        <v>12.64</v>
       </c>
       <c r="Q16" t="n">
-        <v>14.3</v>
+        <v>14.09</v>
       </c>
       <c r="R16" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="S16" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="T16" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="V16" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>54</v>
+        <v>55.45</v>
       </c>
       <c r="Y16" t="n">
         <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>15.6</v>
+        <v>16.36</v>
       </c>
       <c r="AA16" t="n">
-        <v>9.300000000000001</v>
+        <v>10.09</v>
       </c>
       <c r="AB16" t="n">
-        <v>6.3</v>
+        <v>6.27</v>
       </c>
       <c r="AC16" t="n">
-        <v>18.5</v>
+        <v>19.36</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.77</v>
+        <v>1.84</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AF16" t="n">
         <v>0</v>
@@ -7192,70 +7192,70 @@
         <v>3</v>
       </c>
       <c r="BG16" t="n">
-        <v>3.55</v>
+        <v>3.62</v>
       </c>
       <c r="BH16" t="n">
-        <v>11.05</v>
+        <v>11.29</v>
       </c>
       <c r="BI16" t="n">
-        <v>3.55</v>
+        <v>3.62</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.55</v>
+        <v>0.62</v>
       </c>
       <c r="BL16" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="BM16" t="n">
         <v>1.05</v>
       </c>
       <c r="BN16" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="BP16" t="n">
-        <v>5.2</v>
+        <v>5.05</v>
       </c>
       <c r="BQ16" t="n">
-        <v>5.85</v>
+        <v>6.24</v>
       </c>
       <c r="BR16" t="n">
         <v>100</v>
       </c>
       <c r="BS16" t="n">
-        <v>95</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="BT16" t="n">
-        <v>75</v>
+        <v>76.19</v>
       </c>
       <c r="BU16" t="n">
-        <v>55</v>
+        <v>57.14</v>
       </c>
       <c r="BV16" t="n">
-        <v>25</v>
+        <v>28.57</v>
       </c>
       <c r="BW16" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BX16" t="n">
-        <v>80</v>
+        <v>80.95</v>
       </c>
       <c r="BY16" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BZ16" t="n">
         <v>1.81</v>
-      </c>
-      <c r="BZ16" t="n">
-        <v>1.82</v>
       </c>
       <c r="CA16" t="n">
         <v>3.6</v>
       </c>
       <c r="CB16" t="n">
-        <v>3.77</v>
+        <v>3.78</v>
       </c>
       <c r="CC16" t="n">
         <v>3.04</v>
@@ -7270,7 +7270,7 @@
         <v>2.5</v>
       </c>
       <c r="CG16" t="n">
-        <v>3.08</v>
+        <v>3.09</v>
       </c>
       <c r="CH16" t="n">
         <v>1.47</v>
@@ -7282,25 +7282,25 @@
         <v>1.66</v>
       </c>
       <c r="CK16" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CL16" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CM16" t="n">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="CN16" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="CO16" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="CP16" t="n">
         <v>1.75</v>
       </c>
       <c r="CQ16" t="n">
-        <v>2.82</v>
+        <v>2.81</v>
       </c>
       <c r="CR16" t="n">
         <v>1.38</v>
@@ -7309,28 +7309,28 @@
         <v>2.72</v>
       </c>
       <c r="CT16" t="n">
-        <v>3.15</v>
+        <v>3.16</v>
       </c>
       <c r="CU16" t="n">
         <v>1.5</v>
       </c>
       <c r="CV16" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="CW16" t="n">
         <v>1.67</v>
       </c>
       <c r="CX16" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CY16" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CZ16" t="n">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="DA16" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="DB16" t="n">
         <v>1.24</v>
@@ -7339,82 +7339,82 @@
         <v>1.78</v>
       </c>
       <c r="DD16" t="n">
-        <v>2.94</v>
+        <v>2.95</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="DG16" t="n">
-        <v>3.1</v>
+        <v>3.48</v>
       </c>
       <c r="DH16" t="n">
-        <v>96.25</v>
+        <v>98</v>
       </c>
       <c r="DI16" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DJ16" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="DK16" t="n">
-        <v>5.75</v>
+        <v>6.1</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="DM16" t="n">
-        <v>42.4</v>
+        <v>44.62</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="DO16" t="n">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="DP16" t="n">
-        <v>13.1</v>
+        <v>13.05</v>
       </c>
       <c r="DQ16" t="n">
-        <v>15.55</v>
+        <v>15.38</v>
       </c>
       <c r="DR16" t="n">
-        <v>7.85</v>
+        <v>7.52</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>53.4</v>
+        <v>54.19</v>
       </c>
       <c r="DW16" t="n">
         <v>0.1</v>
       </c>
       <c r="DX16" t="n">
-        <v>13.55</v>
+        <v>14.05</v>
       </c>
       <c r="DY16" t="n">
-        <v>8</v>
+        <v>8.48</v>
       </c>
       <c r="DZ16" t="n">
-        <v>5.55</v>
+        <v>5.57</v>
       </c>
       <c r="EA16" t="n">
-        <v>17.9</v>
+        <v>18.38</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="EC16" t="n">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
     </row>
     <row r="17">
@@ -7490,7 +7490,7 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>45.36</v>
+        <v>45.27</v>
       </c>
       <c r="Y17" t="n">
         <v>0</v>
@@ -7796,7 +7796,7 @@
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>43.95</v>
+        <v>43.9</v>
       </c>
       <c r="DW17" t="n">
         <v>0.05</v>
@@ -7827,13 +7827,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C18" t="n">
         <v>11</v>
       </c>
       <c r="D18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E18" t="n">
         <v>0.09</v>
@@ -7917,139 +7917,139 @@
         <v>2.91</v>
       </c>
       <c r="AF18" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="AH18" t="n">
-        <v>3.44</v>
+        <v>3.7</v>
       </c>
       <c r="AI18" t="n">
-        <v>106.22</v>
+        <v>105.7</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AK18" t="n">
-        <v>3.56</v>
+        <v>3.4</v>
       </c>
       <c r="AL18" t="n">
-        <v>5.67</v>
+        <v>5.9</v>
       </c>
       <c r="AM18" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AN18" t="n">
-        <v>44.78</v>
+        <v>45.6</v>
       </c>
       <c r="AO18" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AP18" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="AQ18" t="n">
-        <v>17.33</v>
+        <v>17</v>
       </c>
       <c r="AR18" t="n">
-        <v>14.22</v>
+        <v>14.9</v>
       </c>
       <c r="AS18" t="n">
-        <v>8.220000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="AT18" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AU18" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AV18" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AW18" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AX18" t="n">
         <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>52.56</v>
+        <v>52.9</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="BA18" t="n">
-        <v>12.22</v>
+        <v>12.2</v>
       </c>
       <c r="BB18" t="n">
-        <v>8.56</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BC18" t="n">
-        <v>3.67</v>
+        <v>3.5</v>
       </c>
       <c r="BD18" t="n">
-        <v>22.33</v>
+        <v>22.1</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="BF18" t="n">
-        <v>3.44</v>
+        <v>3.3</v>
       </c>
       <c r="BG18" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="BH18" t="n">
-        <v>9</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.35</v>
+        <v>0.43</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="BL18" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="BO18" t="n">
-        <v>0.8</v>
+        <v>0.86</v>
       </c>
       <c r="BP18" t="n">
-        <v>3.3</v>
+        <v>3.33</v>
       </c>
       <c r="BQ18" t="n">
-        <v>5.7</v>
+        <v>5.81</v>
       </c>
       <c r="BR18" t="n">
-        <v>90</v>
+        <v>90.48</v>
       </c>
       <c r="BS18" t="n">
-        <v>60</v>
+        <v>61.9</v>
       </c>
       <c r="BT18" t="n">
-        <v>30</v>
+        <v>33.33</v>
       </c>
       <c r="BU18" t="n">
-        <v>15</v>
+        <v>14.29</v>
       </c>
       <c r="BV18" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BW18" t="n">
         <v>0</v>
       </c>
       <c r="BX18" t="n">
-        <v>45</v>
+        <v>42.86</v>
       </c>
       <c r="BY18" t="n">
         <v>1.89</v>
@@ -8058,40 +8058,40 @@
         <v>1.95</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.29</v>
+        <v>3.27</v>
       </c>
       <c r="CB18" t="n">
-        <v>3.42</v>
+        <v>3.4</v>
       </c>
       <c r="CC18" t="n">
-        <v>2.76</v>
+        <v>2.77</v>
       </c>
       <c r="CD18" t="n">
-        <v>3.01</v>
+        <v>3.09</v>
       </c>
       <c r="CE18" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CF18" t="n">
-        <v>2.95</v>
+        <v>2.97</v>
       </c>
       <c r="CG18" t="n">
-        <v>2.73</v>
+        <v>2.72</v>
       </c>
       <c r="CH18" t="n">
         <v>1.37</v>
       </c>
       <c r="CI18" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CJ18" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="CK18" t="n">
         <v>1.61</v>
       </c>
       <c r="CL18" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="CM18" t="n">
         <v>2.14</v>
@@ -8100,13 +8100,13 @@
         <v>1.73</v>
       </c>
       <c r="CO18" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CP18" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="CQ18" t="n">
-        <v>3.78</v>
+        <v>3.8</v>
       </c>
       <c r="CR18" t="n">
         <v>1.47</v>
@@ -8121,13 +8121,13 @@
         <v>1.39</v>
       </c>
       <c r="CV18" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CW18" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CX18" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CY18" t="n">
         <v>2.1</v>
@@ -8142,85 +8142,85 @@
         <v>1.38</v>
       </c>
       <c r="DC18" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="DD18" t="n">
-        <v>4.01</v>
+        <v>4.05</v>
       </c>
       <c r="DE18" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="DG18" t="n">
-        <v>4</v>
+        <v>4.09</v>
       </c>
       <c r="DH18" t="n">
-        <v>109</v>
+        <v>108.62</v>
       </c>
       <c r="DI18" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DJ18" t="n">
-        <v>3.3</v>
+        <v>3.24</v>
       </c>
       <c r="DK18" t="n">
-        <v>6.25</v>
+        <v>6.33</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="DM18" t="n">
-        <v>54.8</v>
+        <v>54.71</v>
       </c>
       <c r="DN18" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="DO18" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="DP18" t="n">
-        <v>17.75</v>
+        <v>17.57</v>
       </c>
       <c r="DQ18" t="n">
-        <v>13.55</v>
+        <v>13.9</v>
       </c>
       <c r="DR18" t="n">
-        <v>6.65</v>
+        <v>6.52</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DT18" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DU18" t="n">
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>52.1</v>
+        <v>52.29</v>
       </c>
       <c r="DW18" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DX18" t="n">
-        <v>14.6</v>
+        <v>14.48</v>
       </c>
       <c r="DY18" t="n">
-        <v>10.15</v>
+        <v>10.14</v>
       </c>
       <c r="DZ18" t="n">
-        <v>4.45</v>
+        <v>4.33</v>
       </c>
       <c r="EA18" t="n">
-        <v>25.75</v>
+        <v>25.48</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="EC18" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="19">
@@ -8230,13 +8230,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C19" t="n">
         <v>10</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -8320,139 +8320,139 @@
         <v>2.9</v>
       </c>
       <c r="AF19" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.4</v>
+        <v>1.73</v>
       </c>
       <c r="AH19" t="n">
-        <v>3.3</v>
+        <v>3.27</v>
       </c>
       <c r="AI19" t="n">
-        <v>89.8</v>
+        <v>86.55</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AK19" t="n">
-        <v>3.1</v>
+        <v>3.36</v>
       </c>
       <c r="AL19" t="n">
-        <v>5.6</v>
+        <v>5.36</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AN19" t="n">
-        <v>42.5</v>
+        <v>40.73</v>
       </c>
       <c r="AO19" t="n">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AP19" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AQ19" t="n">
-        <v>13.4</v>
+        <v>13.27</v>
       </c>
       <c r="AR19" t="n">
-        <v>15.5</v>
+        <v>15.18</v>
       </c>
       <c r="AS19" t="n">
-        <v>6.7</v>
+        <v>7.45</v>
       </c>
       <c r="AT19" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AU19" t="n">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AV19" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AW19" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AX19" t="n">
         <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>50.2</v>
+        <v>48.36</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="BA19" t="n">
-        <v>13.3</v>
+        <v>12.91</v>
       </c>
       <c r="BB19" t="n">
-        <v>9.9</v>
+        <v>9.09</v>
       </c>
       <c r="BC19" t="n">
-        <v>3.4</v>
+        <v>3.82</v>
       </c>
       <c r="BD19" t="n">
-        <v>18.2</v>
+        <v>17.55</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="BF19" t="n">
-        <v>2.8</v>
+        <v>2.91</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.45</v>
+        <v>2.57</v>
       </c>
       <c r="BH19" t="n">
-        <v>9.949999999999999</v>
+        <v>10.24</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.45</v>
+        <v>2.57</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.4</v>
+        <v>0.48</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.7</v>
+        <v>0.76</v>
       </c>
       <c r="BM19" t="n">
         <v>0.95</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="BO19" t="n">
-        <v>0.8</v>
+        <v>0.86</v>
       </c>
       <c r="BP19" t="n">
-        <v>5.15</v>
+        <v>5</v>
       </c>
       <c r="BQ19" t="n">
-        <v>4.75</v>
+        <v>5.19</v>
       </c>
       <c r="BR19" t="n">
-        <v>95</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="BS19" t="n">
-        <v>65</v>
+        <v>66.67</v>
       </c>
       <c r="BT19" t="n">
-        <v>40</v>
+        <v>42.86</v>
       </c>
       <c r="BU19" t="n">
-        <v>25</v>
+        <v>28.57</v>
       </c>
       <c r="BV19" t="n">
-        <v>15</v>
+        <v>19.05</v>
       </c>
       <c r="BW19" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BX19" t="n">
-        <v>55</v>
+        <v>57.14</v>
       </c>
       <c r="BY19" t="n">
         <v>2.36</v>
@@ -8461,169 +8461,169 @@
         <v>2.49</v>
       </c>
       <c r="CA19" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="CB19" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="CC19" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="CD19" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="CE19" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="CF19" t="n">
         <v>3.14</v>
       </c>
-      <c r="CB19" t="n">
-        <v>3.27</v>
-      </c>
-      <c r="CC19" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="CD19" t="n">
-        <v>4.39</v>
-      </c>
-      <c r="CE19" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="CF19" t="n">
+      <c r="CG19" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="CH19" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="CI19" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="CJ19" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="CK19" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="CL19" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="CM19" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="CN19" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CO19" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="CP19" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="CQ19" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="CR19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="CS19" t="n">
         <v>3.18</v>
       </c>
-      <c r="CG19" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="CH19" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="CI19" t="n">
+      <c r="CT19" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="CU19" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="CV19" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="CW19" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="CX19" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="CY19" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="CZ19" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="DA19" t="n">
         <v>1.81</v>
-      </c>
-      <c r="CJ19" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="CK19" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="CL19" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="CM19" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="CN19" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="CO19" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="CP19" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="CQ19" t="n">
-        <v>4.21</v>
-      </c>
-      <c r="CR19" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="CS19" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="CT19" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="CU19" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="CV19" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="CW19" t="n">
-        <v>2</v>
-      </c>
-      <c r="CX19" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="CY19" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="CZ19" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="DA19" t="n">
-        <v>1.8</v>
       </c>
       <c r="DB19" t="n">
         <v>1.41</v>
       </c>
       <c r="DC19" t="n">
-        <v>2.31</v>
+        <v>2.28</v>
       </c>
       <c r="DD19" t="n">
-        <v>4.28</v>
+        <v>4.21</v>
       </c>
       <c r="DE19" t="n">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="DG19" t="n">
-        <v>2.4</v>
+        <v>2.43</v>
       </c>
       <c r="DH19" t="n">
-        <v>92.59999999999999</v>
+        <v>90.76000000000001</v>
       </c>
       <c r="DI19" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DJ19" t="n">
-        <v>3.35</v>
+        <v>3.47</v>
       </c>
       <c r="DK19" t="n">
-        <v>4.85</v>
+        <v>4.76</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="DM19" t="n">
-        <v>42.3</v>
+        <v>41.38</v>
       </c>
       <c r="DN19" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="DO19" t="n">
-        <v>2.4</v>
+        <v>2.29</v>
       </c>
       <c r="DP19" t="n">
-        <v>13.5</v>
+        <v>13.43</v>
       </c>
       <c r="DQ19" t="n">
-        <v>15.65</v>
+        <v>15.48</v>
       </c>
       <c r="DR19" t="n">
-        <v>7.05</v>
+        <v>7.43</v>
       </c>
       <c r="DS19" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DT19" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DU19" t="n">
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>50.95</v>
+        <v>49.95</v>
       </c>
       <c r="DW19" t="n">
-        <v>0.35</v>
+        <v>0.38</v>
       </c>
       <c r="DX19" t="n">
-        <v>12.3</v>
+        <v>12.14</v>
       </c>
       <c r="DY19" t="n">
-        <v>8.9</v>
+        <v>8.52</v>
       </c>
       <c r="DZ19" t="n">
-        <v>3.4</v>
+        <v>3.62</v>
       </c>
       <c r="EA19" t="n">
-        <v>20.5</v>
+        <v>20.05</v>
       </c>
       <c r="EB19" t="n">
         <v>1.32</v>
       </c>
       <c r="EC19" t="n">
-        <v>2.85</v>
+        <v>2.91</v>
       </c>
     </row>
     <row r="20">
@@ -9036,94 +9036,94 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D21" t="n">
         <v>10</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="F21" t="n">
-        <v>1.6</v>
+        <v>2.09</v>
       </c>
       <c r="G21" t="n">
-        <v>3.1</v>
+        <v>2.91</v>
       </c>
       <c r="H21" t="n">
-        <v>99.2</v>
+        <v>97.64</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>2.2</v>
+        <v>2.73</v>
       </c>
       <c r="K21" t="n">
-        <v>5.5</v>
+        <v>5.45</v>
       </c>
       <c r="L21" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="M21" t="n">
-        <v>46.2</v>
+        <v>46.55</v>
       </c>
       <c r="N21" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="O21" t="n">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="P21" t="n">
-        <v>14.1</v>
+        <v>14.09</v>
       </c>
       <c r="Q21" t="n">
-        <v>13</v>
+        <v>12.55</v>
       </c>
       <c r="R21" t="n">
-        <v>9.1</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="S21" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="T21" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="V21" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>46.8</v>
+        <v>45.64</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="Z21" t="n">
-        <v>12.5</v>
+        <v>12.55</v>
       </c>
       <c r="AA21" t="n">
-        <v>8.699999999999999</v>
+        <v>9</v>
       </c>
       <c r="AB21" t="n">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="AC21" t="n">
-        <v>24.2</v>
+        <v>23.55</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.2</v>
+        <v>2.64</v>
       </c>
       <c r="AF21" t="n">
         <v>0</v>
@@ -9207,61 +9207,61 @@
         <v>1.9</v>
       </c>
       <c r="BG21" t="n">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="BH21" t="n">
-        <v>9.4</v>
+        <v>9.52</v>
       </c>
       <c r="BI21" t="n">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="BJ21" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="BK21" t="n">
-        <v>0.45</v>
+        <v>0.48</v>
       </c>
       <c r="BL21" t="n">
-        <v>0.8</v>
+        <v>0.76</v>
       </c>
       <c r="BM21" t="n">
-        <v>0.45</v>
+        <v>0.48</v>
       </c>
       <c r="BN21" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="BO21" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="BP21" t="n">
-        <v>4.15</v>
+        <v>4.19</v>
       </c>
       <c r="BQ21" t="n">
-        <v>5.2</v>
+        <v>5.29</v>
       </c>
       <c r="BR21" t="n">
-        <v>95</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="BS21" t="n">
-        <v>70</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BT21" t="n">
-        <v>40</v>
+        <v>42.86</v>
       </c>
       <c r="BU21" t="n">
-        <v>20</v>
+        <v>19.05</v>
       </c>
       <c r="BV21" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BW21" t="n">
         <v>0</v>
       </c>
       <c r="BX21" t="n">
-        <v>50</v>
+        <v>52.38</v>
       </c>
       <c r="BY21" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="BZ21" t="n">
         <v>2.67</v>
@@ -9270,7 +9270,7 @@
         <v>2.95</v>
       </c>
       <c r="CB21" t="n">
-        <v>3.09</v>
+        <v>3.08</v>
       </c>
       <c r="CC21" t="n">
         <v>3.7</v>
@@ -9282,7 +9282,7 @@
         <v>1.56</v>
       </c>
       <c r="CF21" t="n">
-        <v>3.65</v>
+        <v>3.63</v>
       </c>
       <c r="CG21" t="n">
         <v>2.34</v>
@@ -9294,28 +9294,28 @@
         <v>1.67</v>
       </c>
       <c r="CJ21" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="CK21" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CL21" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="CM21" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="CN21" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CO21" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CP21" t="n">
         <v>2.56</v>
       </c>
       <c r="CQ21" t="n">
-        <v>4.96</v>
+        <v>4.94</v>
       </c>
       <c r="CR21" t="n">
         <v>1.6</v>
@@ -9330,106 +9330,106 @@
         <v>1.37</v>
       </c>
       <c r="CV21" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="CW21" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="CX21" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="CY21" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="CZ21" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="DA21" t="n">
         <v>1.7</v>
       </c>
-      <c r="CW21" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="CX21" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="CY21" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="CZ21" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="DA21" t="n">
-        <v>1.69</v>
-      </c>
       <c r="DB21" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="DC21" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="DD21" t="n">
-        <v>5.56</v>
+        <v>5.52</v>
       </c>
       <c r="DE21" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="DF21" t="n">
-        <v>1.45</v>
+        <v>1.71</v>
       </c>
       <c r="DG21" t="n">
-        <v>2.6</v>
+        <v>2.52</v>
       </c>
       <c r="DH21" t="n">
-        <v>91.65000000000001</v>
+        <v>91.19</v>
       </c>
       <c r="DI21" t="n">
         <v>0</v>
       </c>
       <c r="DJ21" t="n">
-        <v>2.15</v>
+        <v>2.43</v>
       </c>
       <c r="DK21" t="n">
-        <v>4.55</v>
+        <v>4.57</v>
       </c>
       <c r="DL21" t="n">
-        <v>0.7</v>
+        <v>0.72</v>
       </c>
       <c r="DM21" t="n">
-        <v>39.4</v>
+        <v>39.91</v>
       </c>
       <c r="DN21" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="DO21" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="DP21" t="n">
-        <v>12.6</v>
+        <v>12.67</v>
       </c>
       <c r="DQ21" t="n">
-        <v>13</v>
+        <v>12.76</v>
       </c>
       <c r="DR21" t="n">
-        <v>8.800000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="DS21" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DT21" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DU21" t="n">
         <v>0</v>
       </c>
       <c r="DV21" t="n">
-        <v>46.8</v>
+        <v>46.19</v>
       </c>
       <c r="DW21" t="n">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="DX21" t="n">
-        <v>10.8</v>
+        <v>10.91</v>
       </c>
       <c r="DY21" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="DZ21" t="n">
-        <v>3</v>
+        <v>2.91</v>
       </c>
       <c r="EA21" t="n">
-        <v>21.25</v>
+        <v>21.05</v>
       </c>
       <c r="EB21" t="n">
         <v>1.18</v>
       </c>
       <c r="EC21" t="n">
-        <v>2.05</v>
+        <v>2.29</v>
       </c>
     </row>
     <row r="22">
@@ -9592,10 +9592,10 @@
         <v>0.2</v>
       </c>
       <c r="BA22" t="n">
-        <v>10.2</v>
+        <v>10.1</v>
       </c>
       <c r="BB22" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BC22" t="n">
         <v>4.2</v>
@@ -9817,10 +9817,10 @@
         <v>0.24</v>
       </c>
       <c r="DX22" t="n">
-        <v>11.95</v>
+        <v>11.91</v>
       </c>
       <c r="DY22" t="n">
-        <v>7.24</v>
+        <v>7.19</v>
       </c>
       <c r="DZ22" t="n">
         <v>4.71</v>

--- a/data/teams/leagues/Averages_Spain_Segunda_División_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Spain_Segunda_División_2025-2026.xlsx
@@ -4440,7 +4440,7 @@
         <v>2.95</v>
       </c>
       <c r="CD9" t="n">
-        <v>3.14</v>
+        <v>3.13</v>
       </c>
       <c r="CE9" t="n">
         <v>1.41</v>
@@ -9108,10 +9108,10 @@
         <v>0.09</v>
       </c>
       <c r="Z21" t="n">
-        <v>12.55</v>
+        <v>12.36</v>
       </c>
       <c r="AA21" t="n">
-        <v>9</v>
+        <v>8.82</v>
       </c>
       <c r="AB21" t="n">
         <v>3.55</v>
@@ -9120,7 +9120,7 @@
         <v>23.55</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="AE21" t="n">
         <v>2.64</v>
@@ -9264,7 +9264,7 @@
         <v>2.52</v>
       </c>
       <c r="BZ21" t="n">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
       <c r="CA21" t="n">
         <v>2.95</v>
@@ -9354,7 +9354,7 @@
         <v>2.76</v>
       </c>
       <c r="DD21" t="n">
-        <v>5.52</v>
+        <v>5.53</v>
       </c>
       <c r="DE21" t="n">
         <v>0.05</v>
@@ -9414,10 +9414,10 @@
         <v>0.09</v>
       </c>
       <c r="DX21" t="n">
-        <v>10.91</v>
+        <v>10.81</v>
       </c>
       <c r="DY21" t="n">
-        <v>8</v>
+        <v>7.91</v>
       </c>
       <c r="DZ21" t="n">
         <v>2.91</v>

--- a/data/teams/leagues/Averages_Spain_Segunda_División_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Spain_Segunda_División_2025-2026.xlsx
@@ -2588,94 +2588,94 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D5" t="n">
         <v>11</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="F5" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="G5" t="n">
-        <v>3.3</v>
+        <v>3.09</v>
       </c>
       <c r="H5" t="n">
-        <v>104.5</v>
+        <v>104.82</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>3.7</v>
+        <v>3.64</v>
       </c>
       <c r="K5" t="n">
-        <v>6.7</v>
+        <v>6.27</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="M5" t="n">
-        <v>59</v>
+        <v>59.73</v>
       </c>
       <c r="N5" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="O5" t="n">
-        <v>3.4</v>
+        <v>3.18</v>
       </c>
       <c r="P5" t="n">
-        <v>13.7</v>
+        <v>14.18</v>
       </c>
       <c r="Q5" t="n">
-        <v>14.6</v>
+        <v>14.09</v>
       </c>
       <c r="R5" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="S5" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="T5" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="V5" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>57.6</v>
+        <v>56.55</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="Z5" t="n">
-        <v>16.4</v>
+        <v>16.18</v>
       </c>
       <c r="AA5" t="n">
-        <v>10.5</v>
+        <v>10.45</v>
       </c>
       <c r="AB5" t="n">
-        <v>5.9</v>
+        <v>5.73</v>
       </c>
       <c r="AC5" t="n">
-        <v>18.3</v>
+        <v>18.18</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AE5" t="n">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="AF5" t="n">
         <v>0.09</v>
@@ -2759,70 +2759,70 @@
         <v>2.36</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.81</v>
+        <v>2.77</v>
       </c>
       <c r="BH5" t="n">
-        <v>10.29</v>
+        <v>10</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.81</v>
+        <v>2.77</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.57</v>
+        <v>0.59</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
       <c r="BL5" t="n">
         <v>1</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="BO5" t="n">
         <v>1.14</v>
       </c>
       <c r="BP5" t="n">
-        <v>5.1</v>
+        <v>4.95</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.19</v>
+        <v>5.05</v>
       </c>
       <c r="BR5" t="n">
-        <v>85.70999999999999</v>
+        <v>86.36</v>
       </c>
       <c r="BS5" t="n">
-        <v>61.9</v>
+        <v>63.64</v>
       </c>
       <c r="BT5" t="n">
-        <v>52.38</v>
+        <v>50</v>
       </c>
       <c r="BU5" t="n">
-        <v>42.86</v>
+        <v>40.91</v>
       </c>
       <c r="BV5" t="n">
-        <v>14.29</v>
+        <v>13.64</v>
       </c>
       <c r="BW5" t="n">
-        <v>9.52</v>
+        <v>9.09</v>
       </c>
       <c r="BX5" t="n">
-        <v>57.14</v>
+        <v>54.55</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="BZ5" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.58</v>
+        <v>3.59</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.86</v>
+        <v>3.88</v>
       </c>
       <c r="CC5" t="n">
         <v>2.74</v>
@@ -2843,19 +2843,19 @@
         <v>1.46</v>
       </c>
       <c r="CI5" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CK5" t="n">
         <v>1.53</v>
       </c>
       <c r="CL5" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="CN5" t="n">
         <v>1.85</v>
@@ -2882,7 +2882,7 @@
         <v>1.48</v>
       </c>
       <c r="CV5" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="CW5" t="n">
         <v>1.76</v>
@@ -2891,34 +2891,34 @@
         <v>1.55</v>
       </c>
       <c r="CY5" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="CZ5" t="n">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="DA5" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="DB5" t="n">
         <v>1.26</v>
       </c>
       <c r="DC5" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="DD5" t="n">
-        <v>3.08</v>
+        <v>3.07</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DF5" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="DG5" t="n">
-        <v>3.24</v>
+        <v>3.14</v>
       </c>
       <c r="DH5" t="n">
-        <v>97.81</v>
+        <v>98.28</v>
       </c>
       <c r="DI5" t="n">
         <v>0.09</v>
@@ -2927,61 +2927,61 @@
         <v>3.1</v>
       </c>
       <c r="DK5" t="n">
-        <v>6.47</v>
+        <v>6.27</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="DM5" t="n">
-        <v>57.48</v>
+        <v>57.91</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="DO5" t="n">
-        <v>3.24</v>
+        <v>3.14</v>
       </c>
       <c r="DP5" t="n">
-        <v>13.43</v>
+        <v>13.68</v>
       </c>
       <c r="DQ5" t="n">
-        <v>14.14</v>
+        <v>13.91</v>
       </c>
       <c r="DR5" t="n">
-        <v>5.38</v>
+        <v>5.41</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.19</v>
+        <v>0.22</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.19</v>
+        <v>0.22</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>55.19</v>
+        <v>54.78</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="DX5" t="n">
-        <v>14.52</v>
+        <v>14.5</v>
       </c>
       <c r="DY5" t="n">
-        <v>9.529999999999999</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="DZ5" t="n">
-        <v>5</v>
+        <v>4.95</v>
       </c>
       <c r="EA5" t="n">
-        <v>19.1</v>
+        <v>19</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="EC5" t="n">
-        <v>2.76</v>
+        <v>2.77</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C13" t="n">
         <v>10</v>
       </c>
       <c r="D13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E13" t="n">
         <v>0.3</v>
@@ -5905,136 +5905,136 @@
         <v>0</v>
       </c>
       <c r="AG13" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>84.33</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>33.83</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>11.83</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>14.08</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>8.42</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>50.08</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>9.92</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>20.17</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="BG13" t="n">
         <v>2.09</v>
       </c>
-      <c r="AH13" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>83.73</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>4</v>
-      </c>
-      <c r="AM13" t="n">
+      <c r="BH13" t="n">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="BL13" t="n">
         <v>0.45</v>
       </c>
-      <c r="AN13" t="n">
-        <v>34.64</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>12</v>
-      </c>
-      <c r="AR13" t="n">
+      <c r="BM13" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>4.32</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>4.59</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>81.81999999999999</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>68.18000000000001</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>40.91</v>
+      </c>
+      <c r="BU13" t="n">
         <v>13.64</v>
       </c>
-      <c r="AS13" t="n">
-        <v>8.550000000000001</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>49.73</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>10.27</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>6.09</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>4.18</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>19.73</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>3.09</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="BH13" t="n">
-        <v>9.619999999999999</v>
-      </c>
-      <c r="BI13" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="BJ13" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="BK13" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="BL13" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="BM13" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="BN13" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="BO13" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="BP13" t="n">
-        <v>4.43</v>
-      </c>
-      <c r="BQ13" t="n">
-        <v>4.71</v>
-      </c>
-      <c r="BR13" t="n">
-        <v>80.95</v>
-      </c>
-      <c r="BS13" t="n">
-        <v>66.67</v>
-      </c>
-      <c r="BT13" t="n">
-        <v>42.86</v>
-      </c>
-      <c r="BU13" t="n">
-        <v>14.29</v>
-      </c>
       <c r="BV13" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BW13" t="n">
         <v>0</v>
       </c>
       <c r="BX13" t="n">
-        <v>47.62</v>
+        <v>45.45</v>
       </c>
       <c r="BY13" t="n">
         <v>2.28</v>
@@ -6043,55 +6043,55 @@
         <v>2.4</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.03</v>
+        <v>3.07</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="CC13" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="CD13" t="n">
-        <v>3.22</v>
+        <v>3.47</v>
       </c>
       <c r="CE13" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CF13" t="n">
-        <v>3.26</v>
+        <v>3.23</v>
       </c>
       <c r="CG13" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="CH13" t="n">
         <v>1.31</v>
       </c>
       <c r="CI13" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CJ13" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CK13" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CL13" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="CN13" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CO13" t="n">
         <v>1.41</v>
       </c>
       <c r="CP13" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="CQ13" t="n">
-        <v>4.25</v>
+        <v>4.19</v>
       </c>
       <c r="CR13" t="n">
         <v>1.53</v>
@@ -6106,73 +6106,73 @@
         <v>1.37</v>
       </c>
       <c r="CV13" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="CW13" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CX13" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="CY13" t="n">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="CZ13" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="DA13" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="DB13" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="DC13" t="n">
-        <v>2.42</v>
+        <v>2.39</v>
       </c>
       <c r="DD13" t="n">
-        <v>4.61</v>
+        <v>4.53</v>
       </c>
       <c r="DE13" t="n">
         <v>0.14</v>
       </c>
       <c r="DF13" t="n">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="DG13" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="DH13" t="n">
-        <v>84.62</v>
+        <v>84.91</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DJ13" t="n">
-        <v>3.38</v>
+        <v>3.27</v>
       </c>
       <c r="DK13" t="n">
-        <v>4.67</v>
+        <v>4.54</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="DM13" t="n">
-        <v>38.38</v>
+        <v>37.77</v>
       </c>
       <c r="DN13" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="DO13" t="n">
-        <v>2.33</v>
+        <v>2.27</v>
       </c>
       <c r="DP13" t="n">
-        <v>13.05</v>
+        <v>12.91</v>
       </c>
       <c r="DQ13" t="n">
-        <v>14.24</v>
+        <v>14.45</v>
       </c>
       <c r="DR13" t="n">
-        <v>8.19</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="DS13" t="n">
         <v>0.14</v>
@@ -6184,28 +6184,28 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>50.24</v>
+        <v>50.41</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DX13" t="n">
-        <v>11.19</v>
+        <v>10.96</v>
       </c>
       <c r="DY13" t="n">
-        <v>6.86</v>
+        <v>6.77</v>
       </c>
       <c r="DZ13" t="n">
-        <v>4.33</v>
+        <v>4.18</v>
       </c>
       <c r="EA13" t="n">
-        <v>21.24</v>
+        <v>21.41</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="EC13" t="n">
-        <v>3.09</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">

--- a/data/teams/leagues/Averages_Spain_Segunda_División_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Spain_Segunda_División_2025-2026.xlsx
@@ -1379,10 +1379,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D2" t="n">
         <v>11</v>
@@ -1391,49 +1391,49 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="G2" t="n">
-        <v>2.7</v>
+        <v>2.82</v>
       </c>
       <c r="H2" t="n">
-        <v>91.09999999999999</v>
+        <v>92</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1</v>
+        <v>-0.09</v>
       </c>
       <c r="J2" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="K2" t="n">
-        <v>5.5</v>
+        <v>5.55</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="M2" t="n">
-        <v>44.9</v>
+        <v>45</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="O2" t="n">
-        <v>2.8</v>
+        <v>2.73</v>
       </c>
       <c r="P2" t="n">
-        <v>10</v>
+        <v>9.27</v>
       </c>
       <c r="Q2" t="n">
-        <v>8.4</v>
+        <v>8.18</v>
       </c>
       <c r="R2" t="n">
-        <v>6.2</v>
+        <v>6.27</v>
       </c>
       <c r="S2" t="n">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="T2" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -1445,28 +1445,28 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>43.3</v>
+        <v>43.64</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="Z2" t="n">
-        <v>15</v>
+        <v>14.91</v>
       </c>
       <c r="AA2" t="n">
-        <v>10.3</v>
+        <v>10.45</v>
       </c>
       <c r="AB2" t="n">
-        <v>4.7</v>
+        <v>4.45</v>
       </c>
       <c r="AC2" t="n">
-        <v>25.1</v>
+        <v>24.73</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AF2" t="n">
         <v>0.27</v>
@@ -1550,67 +1550,67 @@
         <v>2.45</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.86</v>
+        <v>2.77</v>
       </c>
       <c r="BH2" t="n">
-        <v>10.52</v>
+        <v>10.59</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.86</v>
+        <v>2.77</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.48</v>
+        <v>0.45</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.48</v>
+        <v>0.45</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="BP2" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.38</v>
+        <v>5.55</v>
       </c>
       <c r="BR2" t="n">
-        <v>80.95</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BS2" t="n">
-        <v>66.67</v>
+        <v>63.64</v>
       </c>
       <c r="BT2" t="n">
-        <v>52.38</v>
+        <v>50</v>
       </c>
       <c r="BU2" t="n">
-        <v>38.1</v>
+        <v>36.36</v>
       </c>
       <c r="BV2" t="n">
-        <v>23.81</v>
+        <v>22.73</v>
       </c>
       <c r="BW2" t="n">
-        <v>9.52</v>
+        <v>9.09</v>
       </c>
       <c r="BX2" t="n">
-        <v>57.14</v>
+        <v>54.55</v>
       </c>
       <c r="BY2" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="BZ2" t="n">
         <v>2.19</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.28</v>
+        <v>3.29</v>
       </c>
       <c r="CB2" t="n">
         <v>3.49</v>
@@ -1634,7 +1634,7 @@
         <v>1.4</v>
       </c>
       <c r="CI2" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="CJ2" t="n">
         <v>1.76</v>
@@ -1643,13 +1643,13 @@
         <v>1.5</v>
       </c>
       <c r="CL2" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="CN2" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CO2" t="n">
         <v>1.28</v>
@@ -1658,10 +1658,10 @@
         <v>1.95</v>
       </c>
       <c r="CQ2" t="n">
-        <v>3.32</v>
+        <v>3.31</v>
       </c>
       <c r="CR2" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="CS2" t="n">
         <v>2.96</v>
@@ -1703,43 +1703,43 @@
         <v>0.14</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="DH2" t="n">
-        <v>88.38</v>
+        <v>88.95999999999999</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.43</v>
+        <v>2.41</v>
       </c>
       <c r="DK2" t="n">
-        <v>5.05</v>
+        <v>5.1</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="DM2" t="n">
-        <v>43.09</v>
+        <v>43.22</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="DP2" t="n">
-        <v>11.38</v>
+        <v>10.96</v>
       </c>
       <c r="DQ2" t="n">
-        <v>11.19</v>
+        <v>10.96</v>
       </c>
       <c r="DR2" t="n">
-        <v>7.57</v>
+        <v>7.55</v>
       </c>
       <c r="DS2" t="n">
         <v>0.09</v>
@@ -1751,28 +1751,28 @@
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>43.62</v>
+        <v>43.78</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DX2" t="n">
-        <v>13.57</v>
+        <v>13.59</v>
       </c>
       <c r="DY2" t="n">
-        <v>8.859999999999999</v>
+        <v>9</v>
       </c>
       <c r="DZ2" t="n">
-        <v>4.72</v>
+        <v>4.59</v>
       </c>
       <c r="EA2" t="n">
-        <v>24.19</v>
+        <v>24.04</v>
       </c>
       <c r="EB2" t="n">
         <v>1.5</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="3">
@@ -1782,94 +1782,94 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D3" t="n">
         <v>11</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="F3" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="G3" t="n">
-        <v>3.9</v>
+        <v>3.64</v>
       </c>
       <c r="H3" t="n">
-        <v>101.6</v>
+        <v>100.64</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="J3" t="n">
-        <v>2.7</v>
+        <v>2.82</v>
       </c>
       <c r="K3" t="n">
-        <v>7.8</v>
+        <v>7.27</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="M3" t="n">
-        <v>54.9</v>
+        <v>52.64</v>
       </c>
       <c r="N3" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="O3" t="n">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="P3" t="n">
-        <v>14.2</v>
+        <v>14.36</v>
       </c>
       <c r="Q3" t="n">
-        <v>11</v>
+        <v>11.55</v>
       </c>
       <c r="R3" t="n">
-        <v>7.3</v>
+        <v>7.64</v>
       </c>
       <c r="S3" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="T3" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="V3" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>56.4</v>
+        <v>56</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="Z3" t="n">
-        <v>18</v>
+        <v>17.45</v>
       </c>
       <c r="AA3" t="n">
-        <v>10.6</v>
+        <v>10.45</v>
       </c>
       <c r="AB3" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AC3" t="n">
-        <v>18.5</v>
+        <v>17.82</v>
       </c>
       <c r="AD3" t="n">
-        <v>2.05</v>
+        <v>1.97</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.5</v>
+        <v>2.64</v>
       </c>
       <c r="AF3" t="n">
         <v>0</v>
@@ -1953,70 +1953,70 @@
         <v>3.27</v>
       </c>
       <c r="BG3" t="n">
-        <v>3.33</v>
+        <v>3.32</v>
       </c>
       <c r="BH3" t="n">
-        <v>9.48</v>
+        <v>9.23</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.33</v>
+        <v>3.32</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="BL3" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="BM3" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="BN3" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="BP3" t="n">
-        <v>4</v>
+        <v>3.86</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5.14</v>
+        <v>5.05</v>
       </c>
       <c r="BR3" t="n">
-        <v>95.23999999999999</v>
+        <v>95.45</v>
       </c>
       <c r="BS3" t="n">
-        <v>80.95</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BT3" t="n">
-        <v>71.43000000000001</v>
+        <v>72.73</v>
       </c>
       <c r="BU3" t="n">
-        <v>42.86</v>
+        <v>40.91</v>
       </c>
       <c r="BV3" t="n">
-        <v>23.81</v>
+        <v>22.73</v>
       </c>
       <c r="BW3" t="n">
-        <v>9.52</v>
+        <v>9.09</v>
       </c>
       <c r="BX3" t="n">
-        <v>71.43000000000001</v>
+        <v>72.73</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="BZ3" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="CA3" t="n">
         <v>3.43</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.6</v>
+        <v>3.59</v>
       </c>
       <c r="CC3" t="n">
         <v>2.51</v>
@@ -2028,7 +2028,7 @@
         <v>1.37</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.72</v>
+        <v>2.71</v>
       </c>
       <c r="CG3" t="n">
         <v>2.92</v>
@@ -2043,13 +2043,13 @@
         <v>1.76</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="CL3" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="CN3" t="n">
         <v>1.87</v>
@@ -2061,37 +2061,37 @@
         <v>1.89</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.18</v>
+        <v>3.16</v>
       </c>
       <c r="CR3" t="n">
         <v>1.4</v>
       </c>
       <c r="CS3" t="n">
-        <v>2.93</v>
+        <v>2.92</v>
       </c>
       <c r="CT3" t="n">
-        <v>3.06</v>
+        <v>3.07</v>
       </c>
       <c r="CU3" t="n">
         <v>1.44</v>
       </c>
       <c r="CV3" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="CW3" t="n">
         <v>1.75</v>
       </c>
       <c r="CX3" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="CY3" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CZ3" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="DA3" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="DB3" t="n">
         <v>1.29</v>
@@ -2100,82 +2100,82 @@
         <v>1.94</v>
       </c>
       <c r="DD3" t="n">
-        <v>3.33</v>
+        <v>3.32</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="DG3" t="n">
-        <v>2.76</v>
+        <v>2.68</v>
       </c>
       <c r="DH3" t="n">
-        <v>94.86</v>
+        <v>94.68000000000001</v>
       </c>
       <c r="DI3" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="DJ3" t="n">
-        <v>3.05</v>
+        <v>3.09</v>
       </c>
       <c r="DK3" t="n">
-        <v>5.43</v>
+        <v>5.27</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="DM3" t="n">
-        <v>47.24</v>
+        <v>46.46</v>
       </c>
       <c r="DN3" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="DO3" t="n">
-        <v>2.43</v>
+        <v>2.36</v>
       </c>
       <c r="DP3" t="n">
-        <v>13.81</v>
+        <v>13.9</v>
       </c>
       <c r="DQ3" t="n">
-        <v>13</v>
+        <v>13.19</v>
       </c>
       <c r="DR3" t="n">
-        <v>7.43</v>
+        <v>7.59</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>54.67</v>
+        <v>54.54</v>
       </c>
       <c r="DW3" t="n">
         <v>0.09</v>
       </c>
       <c r="DX3" t="n">
-        <v>15.72</v>
+        <v>15.54</v>
       </c>
       <c r="DY3" t="n">
-        <v>9.81</v>
+        <v>9.77</v>
       </c>
       <c r="DZ3" t="n">
-        <v>5.91</v>
+        <v>5.78</v>
       </c>
       <c r="EA3" t="n">
-        <v>20</v>
+        <v>19.59</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
     </row>
     <row r="4">
@@ -2185,94 +2185,94 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D4" t="n">
         <v>10</v>
       </c>
       <c r="E4" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="F4" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="G4" t="n">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="H4" t="n">
-        <v>95.45</v>
+        <v>97.33</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="J4" t="n">
-        <v>2.73</v>
+        <v>2.83</v>
       </c>
       <c r="K4" t="n">
-        <v>3.82</v>
+        <v>3.83</v>
       </c>
       <c r="L4" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="M4" t="n">
-        <v>46.27</v>
+        <v>47.67</v>
       </c>
       <c r="N4" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="O4" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="P4" t="n">
-        <v>13.55</v>
+        <v>13.67</v>
       </c>
       <c r="Q4" t="n">
-        <v>14.18</v>
+        <v>14.25</v>
       </c>
       <c r="R4" t="n">
-        <v>8.82</v>
+        <v>8.67</v>
       </c>
       <c r="S4" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="V4" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>49.45</v>
+        <v>50.58</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="Z4" t="n">
-        <v>10.55</v>
+        <v>10.75</v>
       </c>
       <c r="AA4" t="n">
-        <v>7.45</v>
+        <v>7.58</v>
       </c>
       <c r="AB4" t="n">
-        <v>3.09</v>
+        <v>3.17</v>
       </c>
       <c r="AC4" t="n">
-        <v>25.82</v>
+        <v>26.17</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="AF4" t="n">
         <v>0.1</v>
@@ -2356,70 +2356,70 @@
         <v>2.4</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.14</v>
+        <v>2.09</v>
       </c>
       <c r="BH4" t="n">
-        <v>8.43</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.14</v>
+        <v>2.09</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.43</v>
+        <v>0.41</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.52</v>
+        <v>0.55</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BN4" t="n">
         <v>1.14</v>
       </c>
       <c r="BO4" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="BP4" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.52</v>
+        <v>4.5</v>
       </c>
       <c r="BR4" t="n">
-        <v>85.70999999999999</v>
+        <v>86.36</v>
       </c>
       <c r="BS4" t="n">
-        <v>61.9</v>
+        <v>59.09</v>
       </c>
       <c r="BT4" t="n">
-        <v>38.1</v>
+        <v>36.36</v>
       </c>
       <c r="BU4" t="n">
-        <v>14.29</v>
+        <v>13.64</v>
       </c>
       <c r="BV4" t="n">
-        <v>9.52</v>
+        <v>9.09</v>
       </c>
       <c r="BW4" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BX4" t="n">
-        <v>47.62</v>
+        <v>45.45</v>
       </c>
       <c r="BY4" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="BZ4" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="CA4" t="n">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.1</v>
+        <v>3.09</v>
       </c>
       <c r="CC4" t="n">
         <v>3.71</v>
@@ -2428,43 +2428,43 @@
         <v>4.09</v>
       </c>
       <c r="CE4" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CF4" t="n">
-        <v>3.47</v>
+        <v>3.52</v>
       </c>
       <c r="CG4" t="n">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="CH4" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="CI4" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CJ4" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="CK4" t="n">
         <v>1.71</v>
       </c>
       <c r="CL4" t="n">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="CM4" t="n">
         <v>2.05</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CO4" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="CP4" t="n">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="CQ4" t="n">
-        <v>4.95</v>
+        <v>5.02</v>
       </c>
       <c r="CR4" t="n">
         <v>1.59</v>
@@ -2479,10 +2479,10 @@
         <v>1.33</v>
       </c>
       <c r="CV4" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CW4" t="n">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="CX4" t="n">
         <v>1.76</v>
@@ -2497,88 +2497,88 @@
         <v>1.65</v>
       </c>
       <c r="DB4" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="DC4" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="DD4" t="n">
-        <v>5.51</v>
+        <v>5.58</v>
       </c>
       <c r="DE4" t="n">
         <v>0.09</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="DH4" t="n">
-        <v>91.62</v>
+        <v>92.81999999999999</v>
       </c>
       <c r="DI4" t="n">
-        <v>-0.05</v>
+        <v>-0.04</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.57</v>
+        <v>2.63</v>
       </c>
       <c r="DK4" t="n">
         <v>3.95</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DM4" t="n">
-        <v>41.86</v>
+        <v>42.82</v>
       </c>
       <c r="DN4" t="n">
         <v>1.14</v>
       </c>
       <c r="DO4" t="n">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="DP4" t="n">
-        <v>13.81</v>
+        <v>13.87</v>
       </c>
       <c r="DQ4" t="n">
-        <v>14.81</v>
+        <v>14.82</v>
       </c>
       <c r="DR4" t="n">
-        <v>9.1</v>
+        <v>9</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>47.33</v>
+        <v>48.04</v>
       </c>
       <c r="DW4" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="DX4" t="n">
-        <v>9.91</v>
+        <v>10.05</v>
       </c>
       <c r="DY4" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="DZ4" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="EA4" t="n">
-        <v>23.76</v>
+        <v>24.05</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.57</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="5">
@@ -2991,94 +2991,94 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D6" t="n">
         <v>11</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="F6" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="G6" t="n">
-        <v>2.9</v>
+        <v>3.18</v>
       </c>
       <c r="H6" t="n">
-        <v>96.90000000000001</v>
+        <v>98.64</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="J6" t="n">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="K6" t="n">
-        <v>5.3</v>
+        <v>5.55</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="M6" t="n">
-        <v>52.8</v>
+        <v>55.45</v>
       </c>
       <c r="N6" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="O6" t="n">
         <v>2</v>
       </c>
       <c r="P6" t="n">
-        <v>14.8</v>
+        <v>14.91</v>
       </c>
       <c r="Q6" t="n">
-        <v>13.1</v>
+        <v>12.82</v>
       </c>
       <c r="R6" t="n">
-        <v>5.3</v>
+        <v>5.45</v>
       </c>
       <c r="S6" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="T6" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="V6" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>52.2</v>
+        <v>53</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>11.6</v>
+        <v>12.45</v>
       </c>
       <c r="AA6" t="n">
-        <v>7.2</v>
+        <v>7.91</v>
       </c>
       <c r="AB6" t="n">
-        <v>4.4</v>
+        <v>4.55</v>
       </c>
       <c r="AC6" t="n">
-        <v>21.3</v>
+        <v>21.18</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.43</v>
+        <v>1.51</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="AF6" t="n">
         <v>0.18</v>
@@ -3162,70 +3162,70 @@
         <v>2.36</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="BH6" t="n">
-        <v>9.140000000000001</v>
+        <v>9.23</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.43</v>
+        <v>0.45</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.48</v>
+        <v>0.55</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="BP6" t="n">
-        <v>3.9</v>
+        <v>3.86</v>
       </c>
       <c r="BQ6" t="n">
-        <v>4.95</v>
+        <v>5.09</v>
       </c>
       <c r="BR6" t="n">
-        <v>90.48</v>
+        <v>90.91</v>
       </c>
       <c r="BS6" t="n">
-        <v>66.67</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="BT6" t="n">
-        <v>47.62</v>
+        <v>50</v>
       </c>
       <c r="BU6" t="n">
-        <v>19.05</v>
+        <v>18.18</v>
       </c>
       <c r="BV6" t="n">
-        <v>14.29</v>
+        <v>13.64</v>
       </c>
       <c r="BW6" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BX6" t="n">
-        <v>52.38</v>
+        <v>50</v>
       </c>
       <c r="BY6" t="n">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="BZ6" t="n">
         <v>2.57</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.32</v>
+        <v>3.3</v>
       </c>
       <c r="CC6" t="n">
         <v>3.99</v>
@@ -3234,13 +3234,13 @@
         <v>4.37</v>
       </c>
       <c r="CE6" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="CF6" t="n">
-        <v>3.05</v>
+        <v>3.07</v>
       </c>
       <c r="CG6" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="CH6" t="n">
         <v>1.34</v>
@@ -3255,40 +3255,40 @@
         <v>1.67</v>
       </c>
       <c r="CL6" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="CN6" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CO6" t="n">
         <v>1.37</v>
       </c>
       <c r="CP6" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="CQ6" t="n">
-        <v>3.97</v>
+        <v>4.02</v>
       </c>
       <c r="CR6" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="CS6" t="n">
-        <v>3.14</v>
+        <v>3.15</v>
       </c>
       <c r="CT6" t="n">
-        <v>2.81</v>
+        <v>2.79</v>
       </c>
       <c r="CU6" t="n">
         <v>1.39</v>
       </c>
       <c r="CV6" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="CW6" t="n">
         <v>1.94</v>
-      </c>
-      <c r="CW6" t="n">
-        <v>1.93</v>
       </c>
       <c r="CX6" t="n">
         <v>1.69</v>
@@ -3300,91 +3300,91 @@
         <v>2.15</v>
       </c>
       <c r="DA6" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="DB6" t="n">
         <v>1.39</v>
       </c>
       <c r="DC6" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="DD6" t="n">
-        <v>4.1</v>
+        <v>4.12</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.29</v>
+        <v>2.46</v>
       </c>
       <c r="DH6" t="n">
-        <v>88.70999999999999</v>
+        <v>89.95</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.67</v>
+        <v>2.55</v>
       </c>
       <c r="DK6" t="n">
-        <v>4.43</v>
+        <v>4.6</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="DM6" t="n">
-        <v>44.38</v>
+        <v>46.09</v>
       </c>
       <c r="DN6" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="DO6" t="n">
         <v>1.95</v>
       </c>
       <c r="DP6" t="n">
-        <v>13.62</v>
+        <v>13.73</v>
       </c>
       <c r="DQ6" t="n">
-        <v>12.95</v>
+        <v>12.82</v>
       </c>
       <c r="DR6" t="n">
-        <v>7.1</v>
+        <v>7.09</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>50.09</v>
+        <v>50.59</v>
       </c>
       <c r="DW6" t="n">
         <v>0.09</v>
       </c>
       <c r="DX6" t="n">
-        <v>10.33</v>
+        <v>10.82</v>
       </c>
       <c r="DY6" t="n">
-        <v>6.86</v>
+        <v>7.23</v>
       </c>
       <c r="DZ6" t="n">
-        <v>3.48</v>
+        <v>3.6</v>
       </c>
       <c r="EA6" t="n">
-        <v>21.33</v>
+        <v>21.27</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.52</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="7">
@@ -3394,94 +3394,94 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D7" t="n">
         <v>11</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="F7" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="G7" t="n">
-        <v>3.1</v>
+        <v>3.36</v>
       </c>
       <c r="H7" t="n">
-        <v>89.09999999999999</v>
+        <v>93.09</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="K7" t="n">
-        <v>4.4</v>
+        <v>4.73</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="M7" t="n">
-        <v>41.5</v>
+        <v>43.73</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="O7" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="P7" t="n">
+        <v>11.36</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>13.18</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7.64</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>54.45</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>11.45</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>7.82</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>19.36</v>
+      </c>
+      <c r="AD7" t="n">
         <v>1.3</v>
       </c>
-      <c r="P7" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="R7" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="S7" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" t="n">
-        <v>0</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" t="n">
-        <v>53.1</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AE7" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AF7" t="n">
         <v>0.18</v>
@@ -3565,70 +3565,70 @@
         <v>2</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.48</v>
+        <v>2.64</v>
       </c>
       <c r="BH7" t="n">
-        <v>9.1</v>
+        <v>9.09</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.48</v>
+        <v>2.64</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.71</v>
+        <v>0.82</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.52</v>
+        <v>0.55</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.57</v>
+        <v>0.59</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="BP7" t="n">
-        <v>3.95</v>
+        <v>3.91</v>
       </c>
       <c r="BQ7" t="n">
-        <v>5.14</v>
+        <v>5.18</v>
       </c>
       <c r="BR7" t="n">
-        <v>90.48</v>
+        <v>90.91</v>
       </c>
       <c r="BS7" t="n">
-        <v>57.14</v>
+        <v>59.09</v>
       </c>
       <c r="BT7" t="n">
-        <v>42.86</v>
+        <v>45.45</v>
       </c>
       <c r="BU7" t="n">
-        <v>28.57</v>
+        <v>31.82</v>
       </c>
       <c r="BV7" t="n">
-        <v>19.05</v>
+        <v>22.73</v>
       </c>
       <c r="BW7" t="n">
-        <v>9.52</v>
+        <v>13.64</v>
       </c>
       <c r="BX7" t="n">
-        <v>38.1</v>
+        <v>40.91</v>
       </c>
       <c r="BY7" t="n">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="BZ7" t="n">
-        <v>2.65</v>
+        <v>2.72</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.38</v>
+        <v>3.36</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.51</v>
+        <v>3.49</v>
       </c>
       <c r="CC7" t="n">
         <v>4.85</v>
@@ -3643,10 +3643,10 @@
         <v>2.95</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CI7" t="n">
         <v>1.86</v>
@@ -3658,7 +3658,7 @@
         <v>1.57</v>
       </c>
       <c r="CL7" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="CM7" t="n">
         <v>2.26</v>
@@ -3670,19 +3670,19 @@
         <v>1.32</v>
       </c>
       <c r="CP7" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="CQ7" t="n">
-        <v>3.66</v>
+        <v>3.68</v>
       </c>
       <c r="CR7" t="n">
         <v>1.45</v>
       </c>
       <c r="CS7" t="n">
-        <v>3.13</v>
+        <v>3.14</v>
       </c>
       <c r="CT7" t="n">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="CU7" t="n">
         <v>1.39</v>
@@ -3694,67 +3694,67 @@
         <v>1.94</v>
       </c>
       <c r="CX7" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CY7" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="CZ7" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="DA7" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="DB7" t="n">
         <v>1.37</v>
       </c>
       <c r="DC7" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="DD7" t="n">
-        <v>3.89</v>
+        <v>3.9</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.09</v>
+        <v>0.13</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="DG7" t="n">
-        <v>2.67</v>
+        <v>2.82</v>
       </c>
       <c r="DH7" t="n">
-        <v>81.43000000000001</v>
+        <v>83.77</v>
       </c>
       <c r="DI7" t="n">
         <v>0.09</v>
       </c>
       <c r="DJ7" t="n">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="DK7" t="n">
-        <v>3.81</v>
+        <v>4</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="DM7" t="n">
-        <v>36.29</v>
+        <v>37.64</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.43</v>
+        <v>0.41</v>
       </c>
       <c r="DO7" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="DP7" t="n">
-        <v>12.09</v>
+        <v>11.9</v>
       </c>
       <c r="DQ7" t="n">
-        <v>12.43</v>
+        <v>12.31</v>
       </c>
       <c r="DR7" t="n">
-        <v>9.19</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="DS7" t="n">
         <v>0.09</v>
@@ -3766,28 +3766,28 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>47.57</v>
+        <v>48.5</v>
       </c>
       <c r="DW7" t="n">
         <v>0.09</v>
       </c>
       <c r="DX7" t="n">
-        <v>11.05</v>
+        <v>11.32</v>
       </c>
       <c r="DY7" t="n">
-        <v>7.14</v>
+        <v>7.23</v>
       </c>
       <c r="DZ7" t="n">
-        <v>3.91</v>
+        <v>4.1</v>
       </c>
       <c r="EA7" t="n">
-        <v>18.33</v>
+        <v>18.31</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="EC7" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
     </row>
     <row r="8">
@@ -3797,13 +3797,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C8" t="n">
         <v>11</v>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E8" t="n">
         <v>0.09</v>
@@ -3887,52 +3887,52 @@
         <v>3.36</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AG8" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.1</v>
+        <v>2.36</v>
       </c>
       <c r="AI8" t="n">
-        <v>85.5</v>
+        <v>86.73</v>
       </c>
       <c r="AJ8" t="n">
         <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="AL8" t="n">
-        <v>4.1</v>
+        <v>4.27</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AN8" t="n">
-        <v>30.1</v>
+        <v>31.82</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AP8" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AQ8" t="n">
-        <v>16</v>
+        <v>15.09</v>
       </c>
       <c r="AR8" t="n">
-        <v>12.9</v>
+        <v>11.91</v>
       </c>
       <c r="AS8" t="n">
         <v>10</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AV8" t="n">
         <v>0</v>
@@ -3944,82 +3944,82 @@
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>41</v>
+        <v>42.09</v>
       </c>
       <c r="AZ8" t="n">
         <v>0</v>
       </c>
       <c r="BA8" t="n">
-        <v>8.5</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="BB8" t="n">
-        <v>5.7</v>
+        <v>5.73</v>
       </c>
       <c r="BC8" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="BD8" t="n">
-        <v>18.8</v>
+        <v>19.27</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.96</v>
+        <v>0.98</v>
       </c>
       <c r="BF8" t="n">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.29</v>
+        <v>2.23</v>
       </c>
       <c r="BH8" t="n">
-        <v>11.1</v>
+        <v>11.14</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.29</v>
+        <v>2.23</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.95</v>
+        <v>4.86</v>
       </c>
       <c r="BQ8" t="n">
-        <v>6.14</v>
+        <v>6.27</v>
       </c>
       <c r="BR8" t="n">
-        <v>80.95</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BS8" t="n">
-        <v>57.14</v>
+        <v>54.55</v>
       </c>
       <c r="BT8" t="n">
-        <v>47.62</v>
+        <v>45.45</v>
       </c>
       <c r="BU8" t="n">
-        <v>23.81</v>
+        <v>22.73</v>
       </c>
       <c r="BV8" t="n">
-        <v>14.29</v>
+        <v>13.64</v>
       </c>
       <c r="BW8" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BX8" t="n">
-        <v>47.62</v>
+        <v>45.45</v>
       </c>
       <c r="BY8" t="n">
         <v>2.36</v>
@@ -4028,73 +4028,73 @@
         <v>2.57</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.12</v>
+        <v>3.13</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.29</v>
+        <v>3.3</v>
       </c>
       <c r="CC8" t="n">
-        <v>3.83</v>
+        <v>3.82</v>
       </c>
       <c r="CD8" t="n">
-        <v>4.25</v>
+        <v>4.18</v>
       </c>
       <c r="CE8" t="n">
         <v>1.47</v>
       </c>
       <c r="CF8" t="n">
-        <v>3.17</v>
+        <v>3.14</v>
       </c>
       <c r="CG8" t="n">
-        <v>2.55</v>
+        <v>2.56</v>
       </c>
       <c r="CH8" t="n">
         <v>1.32</v>
       </c>
       <c r="CI8" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CJ8" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CL8" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="CN8" t="n">
         <v>1.73</v>
       </c>
       <c r="CO8" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CP8" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="CQ8" t="n">
-        <v>4.17</v>
+        <v>4.12</v>
       </c>
       <c r="CR8" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CS8" t="n">
-        <v>3.19</v>
+        <v>3.17</v>
       </c>
       <c r="CT8" t="n">
-        <v>2.69</v>
+        <v>2.71</v>
       </c>
       <c r="CU8" t="n">
         <v>1.37</v>
       </c>
       <c r="CV8" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="CW8" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="CX8" t="n">
         <v>1.62</v>
@@ -4109,88 +4109,88 @@
         <v>1.79</v>
       </c>
       <c r="DB8" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="DC8" t="n">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="DD8" t="n">
-        <v>4.33</v>
+        <v>4.29</v>
       </c>
       <c r="DE8" t="n">
         <v>0.09</v>
       </c>
       <c r="DF8" t="n">
-        <v>2.14</v>
+        <v>2.09</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.62</v>
+        <v>2.72</v>
       </c>
       <c r="DH8" t="n">
-        <v>88.67</v>
+        <v>89.14</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DJ8" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="DK8" t="n">
-        <v>4.95</v>
+        <v>5</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DM8" t="n">
-        <v>39.19</v>
+        <v>39.64</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.86</v>
+        <v>0.82</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="DP8" t="n">
-        <v>14.66</v>
+        <v>14.27</v>
       </c>
       <c r="DQ8" t="n">
-        <v>12.95</v>
+        <v>12.46</v>
       </c>
       <c r="DR8" t="n">
-        <v>8.66</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>44.67</v>
+        <v>45.04</v>
       </c>
       <c r="DW8" t="n">
         <v>0</v>
       </c>
       <c r="DX8" t="n">
-        <v>10.1</v>
+        <v>10.05</v>
       </c>
       <c r="DY8" t="n">
-        <v>6.86</v>
+        <v>6.82</v>
       </c>
       <c r="DZ8" t="n">
-        <v>3.24</v>
+        <v>3.23</v>
       </c>
       <c r="EA8" t="n">
-        <v>18.95</v>
+        <v>19.18</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="EC8" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="9">
@@ -4200,94 +4200,94 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D9" t="n">
         <v>11</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="F9" t="n">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="G9" t="n">
-        <v>2.5</v>
+        <v>2.18</v>
       </c>
       <c r="H9" t="n">
-        <v>101.8</v>
+        <v>103.91</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="J9" t="n">
-        <v>3</v>
+        <v>2.82</v>
       </c>
       <c r="K9" t="n">
-        <v>5.2</v>
+        <v>5.45</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6</v>
+        <v>0.45</v>
       </c>
       <c r="M9" t="n">
-        <v>54.6</v>
+        <v>56.36</v>
       </c>
       <c r="N9" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="O9" t="n">
-        <v>2.7</v>
+        <v>2.36</v>
       </c>
       <c r="P9" t="n">
-        <v>16.1</v>
+        <v>15.73</v>
       </c>
       <c r="Q9" t="n">
-        <v>15.1</v>
+        <v>14.55</v>
       </c>
       <c r="R9" t="n">
         <v>5</v>
       </c>
       <c r="S9" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="T9" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="V9" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>59.1</v>
+        <v>59.27</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="Z9" t="n">
-        <v>16.1</v>
+        <v>16.36</v>
       </c>
       <c r="AA9" t="n">
-        <v>11.2</v>
+        <v>11.27</v>
       </c>
       <c r="AB9" t="n">
-        <v>4.9</v>
+        <v>5.09</v>
       </c>
       <c r="AC9" t="n">
-        <v>21.3</v>
+        <v>21.73</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.8</v>
+        <v>2.64</v>
       </c>
       <c r="AF9" t="n">
         <v>0.27</v>
@@ -4371,49 +4371,49 @@
         <v>2.91</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.43</v>
+        <v>2.36</v>
       </c>
       <c r="BH9" t="n">
-        <v>9.76</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.43</v>
+        <v>2.36</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.43</v>
+        <v>0.45</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.77</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="BO9" t="n">
         <v>0.95</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.81</v>
+        <v>4.55</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.95</v>
+        <v>4.68</v>
       </c>
       <c r="BR9" t="n">
-        <v>85.70999999999999</v>
+        <v>86.36</v>
       </c>
       <c r="BS9" t="n">
-        <v>76.19</v>
+        <v>72.73</v>
       </c>
       <c r="BT9" t="n">
-        <v>52.38</v>
+        <v>50</v>
       </c>
       <c r="BU9" t="n">
-        <v>28.57</v>
+        <v>27.27</v>
       </c>
       <c r="BV9" t="n">
         <v>0</v>
@@ -4422,7 +4422,7 @@
         <v>0</v>
       </c>
       <c r="BX9" t="n">
-        <v>66.67</v>
+        <v>63.64</v>
       </c>
       <c r="BY9" t="n">
         <v>2.1</v>
@@ -4431,7 +4431,7 @@
         <v>2.12</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.23</v>
+        <v>3.24</v>
       </c>
       <c r="CB9" t="n">
         <v>3.37</v>
@@ -4461,13 +4461,13 @@
         <v>1.77</v>
       </c>
       <c r="CK9" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CL9" t="n">
         <v>1.94</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="CN9" t="n">
         <v>1.87</v>
@@ -4485,16 +4485,16 @@
         <v>1.43</v>
       </c>
       <c r="CS9" t="n">
-        <v>3.06</v>
+        <v>3.05</v>
       </c>
       <c r="CT9" t="n">
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
       <c r="CU9" t="n">
         <v>1.41</v>
       </c>
       <c r="CV9" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="CW9" t="n">
         <v>1.79</v>
@@ -4506,7 +4506,7 @@
         <v>1.93</v>
       </c>
       <c r="CZ9" t="n">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="DA9" t="n">
         <v>1.88</v>
@@ -4521,46 +4521,46 @@
         <v>3.6</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.62</v>
+        <v>1.54</v>
       </c>
       <c r="DG9" t="n">
-        <v>2.71</v>
+        <v>2.55</v>
       </c>
       <c r="DH9" t="n">
-        <v>97.62</v>
+        <v>98.86</v>
       </c>
       <c r="DI9" t="n">
         <v>0</v>
       </c>
       <c r="DJ9" t="n">
-        <v>3.05</v>
+        <v>2.95</v>
       </c>
       <c r="DK9" t="n">
-        <v>5.05</v>
+        <v>5.18</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.33</v>
+        <v>0.27</v>
       </c>
       <c r="DM9" t="n">
-        <v>48.24</v>
+        <v>49.4</v>
       </c>
       <c r="DN9" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="DO9" t="n">
-        <v>2.33</v>
+        <v>2.18</v>
       </c>
       <c r="DP9" t="n">
-        <v>15.76</v>
+        <v>15.59</v>
       </c>
       <c r="DQ9" t="n">
-        <v>15.05</v>
+        <v>14.78</v>
       </c>
       <c r="DR9" t="n">
-        <v>6.05</v>
+        <v>6</v>
       </c>
       <c r="DS9" t="n">
         <v>0.14</v>
@@ -4572,28 +4572,28 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>56.86</v>
+        <v>57.04</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DX9" t="n">
-        <v>14.62</v>
+        <v>14.81</v>
       </c>
       <c r="DY9" t="n">
-        <v>9.859999999999999</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="DZ9" t="n">
-        <v>4.76</v>
+        <v>4.86</v>
       </c>
       <c r="EA9" t="n">
-        <v>21.86</v>
+        <v>22.04</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.86</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="10">
@@ -4603,13 +4603,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C10" t="n">
         <v>10</v>
       </c>
       <c r="D10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E10" t="n">
         <v>0.2</v>
@@ -4696,136 +4696,136 @@
         <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="AI10" t="n">
-        <v>75</v>
+        <v>75.25</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.64</v>
+        <v>2.67</v>
       </c>
       <c r="AL10" t="n">
-        <v>4.73</v>
+        <v>4.5</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AN10" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AP10" t="n">
-        <v>3.18</v>
+        <v>2.92</v>
       </c>
       <c r="AQ10" t="n">
-        <v>11.27</v>
+        <v>11.75</v>
       </c>
       <c r="AR10" t="n">
-        <v>12.27</v>
+        <v>12.58</v>
       </c>
       <c r="AS10" t="n">
-        <v>8.73</v>
+        <v>8.42</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AX10" t="n">
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>47.09</v>
+        <v>47.17</v>
       </c>
       <c r="AZ10" t="n">
         <v>0</v>
       </c>
       <c r="BA10" t="n">
-        <v>11.73</v>
+        <v>12.5</v>
       </c>
       <c r="BB10" t="n">
-        <v>7.18</v>
+        <v>7.83</v>
       </c>
       <c r="BC10" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>15</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>8.640000000000001</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>4.27</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>4.36</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>95.45</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>86.36</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>59.09</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>31.82</v>
+      </c>
+      <c r="BV10" t="n">
         <v>4.55</v>
       </c>
-      <c r="BD10" t="n">
-        <v>14.73</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="BH10" t="n">
-        <v>8.859999999999999</v>
-      </c>
-      <c r="BI10" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="BJ10" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="BK10" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="BM10" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="BN10" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="BO10" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="BP10" t="n">
-        <v>4.43</v>
-      </c>
-      <c r="BQ10" t="n">
-        <v>4.43</v>
-      </c>
-      <c r="BR10" t="n">
-        <v>95.23999999999999</v>
-      </c>
-      <c r="BS10" t="n">
-        <v>85.70999999999999</v>
-      </c>
-      <c r="BT10" t="n">
-        <v>57.14</v>
-      </c>
-      <c r="BU10" t="n">
-        <v>33.33</v>
-      </c>
-      <c r="BV10" t="n">
-        <v>4.76</v>
-      </c>
       <c r="BW10" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BX10" t="n">
-        <v>57.14</v>
+        <v>59.09</v>
       </c>
       <c r="BY10" t="n">
         <v>1.88</v>
@@ -4840,34 +4840,34 @@
         <v>3.43</v>
       </c>
       <c r="CC10" t="n">
-        <v>2.83</v>
+        <v>2.86</v>
       </c>
       <c r="CD10" t="n">
-        <v>2.97</v>
+        <v>3.04</v>
       </c>
       <c r="CE10" t="n">
         <v>1.41</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="CG10" t="n">
         <v>2.82</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CI10" t="n">
         <v>1.95</v>
       </c>
       <c r="CJ10" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CK10" t="n">
         <v>1.63</v>
       </c>
       <c r="CL10" t="n">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="CM10" t="n">
         <v>2.16</v>
@@ -4876,28 +4876,28 @@
         <v>1.74</v>
       </c>
       <c r="CO10" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="CP10" t="n">
         <v>2.03</v>
       </c>
       <c r="CQ10" t="n">
-        <v>3.52</v>
+        <v>3.48</v>
       </c>
       <c r="CR10" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CS10" t="n">
-        <v>3.12</v>
+        <v>3.11</v>
       </c>
       <c r="CT10" t="n">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="CU10" t="n">
         <v>1.39</v>
       </c>
       <c r="CV10" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="CW10" t="n">
         <v>1.86</v>
@@ -4906,97 +4906,97 @@
         <v>1.65</v>
       </c>
       <c r="CY10" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="CZ10" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="DA10" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="DB10" t="n">
         <v>1.34</v>
       </c>
       <c r="DC10" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="DD10" t="n">
-        <v>3.68</v>
+        <v>3.66</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="DG10" t="n">
         <v>2</v>
       </c>
       <c r="DH10" t="n">
-        <v>84.81</v>
+        <v>84.5</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.57</v>
+        <v>2.59</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.57</v>
+        <v>4.45</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="DM10" t="n">
-        <v>38.95</v>
+        <v>39.27</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.91</v>
+        <v>0.86</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.57</v>
+        <v>2.46</v>
       </c>
       <c r="DP10" t="n">
-        <v>11.47</v>
+        <v>11.73</v>
       </c>
       <c r="DQ10" t="n">
-        <v>12.9</v>
+        <v>13.04</v>
       </c>
       <c r="DR10" t="n">
-        <v>8.050000000000001</v>
+        <v>7.91</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>50.52</v>
+        <v>50.41</v>
       </c>
       <c r="DW10" t="n">
         <v>0.05</v>
       </c>
       <c r="DX10" t="n">
-        <v>12.43</v>
+        <v>12.82</v>
       </c>
       <c r="DY10" t="n">
-        <v>7.71</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="DZ10" t="n">
-        <v>4.72</v>
+        <v>4.77</v>
       </c>
       <c r="EA10" t="n">
-        <v>16.86</v>
+        <v>16.91</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="EC10" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="11">
@@ -5006,13 +5006,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C11" t="n">
         <v>10</v>
       </c>
       <c r="D11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -5096,139 +5096,139 @@
         <v>1.9</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.09</v>
+        <v>0.17</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.91</v>
+        <v>2.67</v>
       </c>
       <c r="AI11" t="n">
-        <v>98.36</v>
+        <v>98</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.91</v>
+        <v>3</v>
       </c>
       <c r="AL11" t="n">
-        <v>4.55</v>
+        <v>4.25</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AN11" t="n">
-        <v>40.55</v>
+        <v>39.92</v>
       </c>
       <c r="AO11" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AQ11" t="n">
-        <v>13.64</v>
+        <v>13.75</v>
       </c>
       <c r="AR11" t="n">
-        <v>15.09</v>
+        <v>15.75</v>
       </c>
       <c r="AS11" t="n">
-        <v>7.18</v>
+        <v>7.17</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AX11" t="n">
         <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>57.64</v>
+        <v>57.92</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="BA11" t="n">
-        <v>13.64</v>
+        <v>13.67</v>
       </c>
       <c r="BB11" t="n">
-        <v>9.09</v>
+        <v>9.25</v>
       </c>
       <c r="BC11" t="n">
-        <v>4.55</v>
+        <v>4.42</v>
       </c>
       <c r="BD11" t="n">
-        <v>18.09</v>
+        <v>17.58</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="BF11" t="n">
-        <v>2.73</v>
+        <v>2.83</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="BH11" t="n">
-        <v>9.81</v>
+        <v>9.73</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.33</v>
+        <v>0.36</v>
       </c>
       <c r="BL11" t="n">
         <v>1</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="BO11" t="n">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.48</v>
+        <v>4.41</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.29</v>
+        <v>5.27</v>
       </c>
       <c r="BR11" t="n">
-        <v>90.48</v>
+        <v>90.91</v>
       </c>
       <c r="BS11" t="n">
-        <v>76.19</v>
+        <v>77.27</v>
       </c>
       <c r="BT11" t="n">
-        <v>52.38</v>
+        <v>54.55</v>
       </c>
       <c r="BU11" t="n">
-        <v>23.81</v>
+        <v>22.73</v>
       </c>
       <c r="BV11" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BW11" t="n">
         <v>0</v>
       </c>
       <c r="BX11" t="n">
-        <v>66.67</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="BY11" t="n">
         <v>2.28</v>
@@ -5237,22 +5237,22 @@
         <v>2.36</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.32</v>
+        <v>3.31</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.46</v>
+        <v>3.45</v>
       </c>
       <c r="CC11" t="n">
-        <v>3.89</v>
+        <v>3.77</v>
       </c>
       <c r="CD11" t="n">
-        <v>4.18</v>
+        <v>4.06</v>
       </c>
       <c r="CE11" t="n">
         <v>1.42</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="CG11" t="n">
         <v>2.78</v>
@@ -5264,16 +5264,16 @@
         <v>1.94</v>
       </c>
       <c r="CJ11" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CK11" t="n">
         <v>1.64</v>
       </c>
       <c r="CL11" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="CN11" t="n">
         <v>1.73</v>
@@ -5285,7 +5285,7 @@
         <v>2.03</v>
       </c>
       <c r="CQ11" t="n">
-        <v>3.53</v>
+        <v>3.52</v>
       </c>
       <c r="CR11" t="n">
         <v>1.44</v>
@@ -5327,46 +5327,46 @@
         <v>3.69</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="DG11" t="n">
-        <v>3.29</v>
+        <v>3.14</v>
       </c>
       <c r="DH11" t="n">
-        <v>103.62</v>
+        <v>103.18</v>
       </c>
       <c r="DI11" t="n">
         <v>0.14</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.48</v>
+        <v>2.55</v>
       </c>
       <c r="DK11" t="n">
-        <v>5.24</v>
+        <v>5.05</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DM11" t="n">
-        <v>46.29</v>
+        <v>45.68</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.86</v>
+        <v>0.91</v>
       </c>
       <c r="DO11" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="DP11" t="n">
-        <v>13.43</v>
+        <v>13.5</v>
       </c>
       <c r="DQ11" t="n">
-        <v>14.76</v>
+        <v>15.14</v>
       </c>
       <c r="DR11" t="n">
-        <v>7.48</v>
+        <v>7.46</v>
       </c>
       <c r="DS11" t="n">
         <v>0.09</v>
@@ -5378,28 +5378,28 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>58.57</v>
+        <v>58.68</v>
       </c>
       <c r="DW11" t="n">
         <v>0.09</v>
       </c>
       <c r="DX11" t="n">
-        <v>13.76</v>
+        <v>13.77</v>
       </c>
       <c r="DY11" t="n">
-        <v>9.050000000000001</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="DZ11" t="n">
-        <v>4.72</v>
+        <v>4.64</v>
       </c>
       <c r="EA11" t="n">
-        <v>18.86</v>
+        <v>18.54</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
     </row>
     <row r="12">
@@ -6215,61 +6215,61 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D14" t="n">
         <v>11</v>
       </c>
       <c r="E14" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="F14" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="G14" t="n">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="H14" t="n">
-        <v>94.40000000000001</v>
+        <v>92.64</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="J14" t="n">
-        <v>3.8</v>
+        <v>3.64</v>
       </c>
       <c r="K14" t="n">
-        <v>4.1</v>
+        <v>4.36</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="M14" t="n">
-        <v>41.1</v>
+        <v>40.55</v>
       </c>
       <c r="N14" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="O14" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="P14" t="n">
-        <v>17.3</v>
+        <v>17.82</v>
       </c>
       <c r="Q14" t="n">
-        <v>12.3</v>
+        <v>12.55</v>
       </c>
       <c r="R14" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="S14" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="T14" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
@@ -6281,28 +6281,28 @@
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>46</v>
+        <v>45.36</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="Z14" t="n">
-        <v>12.1</v>
+        <v>12.45</v>
       </c>
       <c r="AA14" t="n">
-        <v>8.300000000000001</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="AB14" t="n">
-        <v>3.8</v>
+        <v>3.91</v>
       </c>
       <c r="AC14" t="n">
-        <v>17.5</v>
+        <v>17.91</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE14" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="AF14" t="n">
         <v>0.09</v>
@@ -6386,70 +6386,70 @@
         <v>2.45</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.71</v>
+        <v>2.73</v>
       </c>
       <c r="BH14" t="n">
-        <v>8.81</v>
+        <v>8.77</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.71</v>
+        <v>2.73</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="BP14" t="n">
-        <v>3.62</v>
+        <v>3.59</v>
       </c>
       <c r="BQ14" t="n">
-        <v>5.19</v>
+        <v>5.18</v>
       </c>
       <c r="BR14" t="n">
-        <v>90.48</v>
+        <v>90.91</v>
       </c>
       <c r="BS14" t="n">
-        <v>71.43000000000001</v>
+        <v>72.73</v>
       </c>
       <c r="BT14" t="n">
-        <v>52.38</v>
+        <v>54.55</v>
       </c>
       <c r="BU14" t="n">
-        <v>33.33</v>
+        <v>31.82</v>
       </c>
       <c r="BV14" t="n">
-        <v>19.05</v>
+        <v>18.18</v>
       </c>
       <c r="BW14" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BX14" t="n">
-        <v>61.9</v>
+        <v>63.64</v>
       </c>
       <c r="BY14" t="n">
-        <v>2.99</v>
+        <v>2.96</v>
       </c>
       <c r="BZ14" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.29</v>
+        <v>3.28</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.51</v>
+        <v>3.49</v>
       </c>
       <c r="CC14" t="n">
         <v>5.3</v>
@@ -6470,16 +6470,16 @@
         <v>1.32</v>
       </c>
       <c r="CI14" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CJ14" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="CK14" t="n">
         <v>1.7</v>
       </c>
       <c r="CL14" t="n">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="CM14" t="n">
         <v>2.1</v>
@@ -6491,28 +6491,28 @@
         <v>1.38</v>
       </c>
       <c r="CP14" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="CQ14" t="n">
-        <v>4.15</v>
+        <v>4.11</v>
       </c>
       <c r="CR14" t="n">
         <v>1.5</v>
       </c>
       <c r="CS14" t="n">
-        <v>3.24</v>
+        <v>3.23</v>
       </c>
       <c r="CT14" t="n">
-        <v>2.71</v>
+        <v>2.72</v>
       </c>
       <c r="CU14" t="n">
         <v>1.37</v>
       </c>
       <c r="CV14" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CW14" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="CX14" t="n">
         <v>1.7</v>
@@ -6527,55 +6527,55 @@
         <v>1.69</v>
       </c>
       <c r="DB14" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="DC14" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="DD14" t="n">
-        <v>4.39</v>
+        <v>4.36</v>
       </c>
       <c r="DE14" t="n">
         <v>0.09</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="DG14" t="n">
-        <v>1.76</v>
+        <v>1.91</v>
       </c>
       <c r="DH14" t="n">
-        <v>87.62</v>
+        <v>87.04000000000001</v>
       </c>
       <c r="DI14" t="n">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="DJ14" t="n">
-        <v>3.38</v>
+        <v>3.32</v>
       </c>
       <c r="DK14" t="n">
-        <v>3.24</v>
+        <v>3.4</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DM14" t="n">
-        <v>34.67</v>
+        <v>34.68</v>
       </c>
       <c r="DN14" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="DO14" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="DP14" t="n">
-        <v>15.71</v>
+        <v>16.05</v>
       </c>
       <c r="DQ14" t="n">
-        <v>13.05</v>
+        <v>13.14</v>
       </c>
       <c r="DR14" t="n">
-        <v>9.24</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="DS14" t="n">
         <v>0.14</v>
@@ -6587,28 +6587,28 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>41.38</v>
+        <v>41.27</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DX14" t="n">
-        <v>10.91</v>
+        <v>11.14</v>
       </c>
       <c r="DY14" t="n">
-        <v>7.48</v>
+        <v>7.64</v>
       </c>
       <c r="DZ14" t="n">
-        <v>3.43</v>
+        <v>3.5</v>
       </c>
       <c r="EA14" t="n">
-        <v>17.53</v>
+        <v>17.73</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="EC14" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -6618,13 +6618,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C15" t="n">
         <v>11</v>
       </c>
       <c r="D15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E15" t="n">
         <v>0.09</v>
@@ -6708,139 +6708,139 @@
         <v>2.55</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="AI15" t="n">
-        <v>90.3</v>
+        <v>89.73</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="AL15" t="n">
-        <v>4.2</v>
+        <v>4.18</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="AN15" t="n">
-        <v>45.4</v>
+        <v>43.36</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="AQ15" t="n">
-        <v>12</v>
+        <v>11.73</v>
       </c>
       <c r="AR15" t="n">
-        <v>12.2</v>
+        <v>12.18</v>
       </c>
       <c r="AS15" t="n">
-        <v>8.199999999999999</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AU15" t="n">
         <v>1</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AX15" t="n">
         <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>50.8</v>
+        <v>49.73</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="BA15" t="n">
-        <v>10.1</v>
+        <v>9.91</v>
       </c>
       <c r="BB15" t="n">
-        <v>6.6</v>
+        <v>6.27</v>
       </c>
       <c r="BC15" t="n">
-        <v>3.5</v>
+        <v>3.64</v>
       </c>
       <c r="BD15" t="n">
-        <v>22.8</v>
+        <v>23.18</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="BF15" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.71</v>
+        <v>2.64</v>
       </c>
       <c r="BH15" t="n">
-        <v>8.52</v>
+        <v>8.68</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.71</v>
+        <v>2.64</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.76</v>
+        <v>0.73</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.29</v>
+        <v>0.32</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.76</v>
+        <v>0.73</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.67</v>
+        <v>1.59</v>
       </c>
       <c r="BO15" t="n">
         <v>1.05</v>
       </c>
       <c r="BP15" t="n">
-        <v>3.48</v>
+        <v>3.27</v>
       </c>
       <c r="BQ15" t="n">
-        <v>4.48</v>
+        <v>4.23</v>
       </c>
       <c r="BR15" t="n">
         <v>100</v>
       </c>
       <c r="BS15" t="n">
-        <v>76.19</v>
+        <v>72.73</v>
       </c>
       <c r="BT15" t="n">
-        <v>57.14</v>
+        <v>54.55</v>
       </c>
       <c r="BU15" t="n">
-        <v>28.57</v>
+        <v>27.27</v>
       </c>
       <c r="BV15" t="n">
-        <v>9.52</v>
+        <v>9.09</v>
       </c>
       <c r="BW15" t="n">
         <v>0</v>
       </c>
       <c r="BX15" t="n">
-        <v>61.9</v>
+        <v>59.09</v>
       </c>
       <c r="BY15" t="n">
         <v>2.27</v>
@@ -6849,43 +6849,43 @@
         <v>2.29</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.21</v>
+        <v>3.22</v>
       </c>
       <c r="CB15" t="n">
         <v>3.36</v>
       </c>
       <c r="CC15" t="n">
-        <v>4.08</v>
+        <v>4.06</v>
       </c>
       <c r="CD15" t="n">
-        <v>4.48</v>
+        <v>4.4</v>
       </c>
       <c r="CE15" t="n">
         <v>1.46</v>
       </c>
       <c r="CF15" t="n">
-        <v>3.1</v>
+        <v>3.09</v>
       </c>
       <c r="CG15" t="n">
-        <v>2.61</v>
+        <v>2.63</v>
       </c>
       <c r="CH15" t="n">
         <v>1.33</v>
       </c>
       <c r="CI15" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CJ15" t="n">
         <v>1.94</v>
       </c>
       <c r="CK15" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CL15" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="CN15" t="n">
         <v>1.76</v>
@@ -6894,124 +6894,124 @@
         <v>1.36</v>
       </c>
       <c r="CP15" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.88</v>
+        <v>3.87</v>
       </c>
       <c r="CR15" t="n">
         <v>1.48</v>
       </c>
       <c r="CS15" t="n">
-        <v>3.2</v>
+        <v>3.19</v>
       </c>
       <c r="CT15" t="n">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
       <c r="CU15" t="n">
         <v>1.37</v>
       </c>
       <c r="CV15" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="CW15" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CX15" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CY15" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="CZ15" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="DA15" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="DB15" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="DC15" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="DD15" t="n">
-        <v>4.19</v>
+        <v>4.16</v>
       </c>
       <c r="DE15" t="n">
         <v>0.09</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="DG15" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="DH15" t="n">
-        <v>89.52</v>
+        <v>89.28</v>
       </c>
       <c r="DI15" t="n">
         <v>0.09</v>
       </c>
       <c r="DJ15" t="n">
-        <v>2.67</v>
+        <v>2.59</v>
       </c>
       <c r="DK15" t="n">
         <v>4.05</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.24</v>
+        <v>0.18</v>
       </c>
       <c r="DM15" t="n">
-        <v>46.38</v>
+        <v>45.32</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.86</v>
+        <v>0.82</v>
       </c>
       <c r="DO15" t="n">
-        <v>1.57</v>
+        <v>1.45</v>
       </c>
       <c r="DP15" t="n">
-        <v>12.76</v>
+        <v>12.59</v>
       </c>
       <c r="DQ15" t="n">
         <v>12.14</v>
       </c>
       <c r="DR15" t="n">
-        <v>7.95</v>
+        <v>8.09</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DU15" t="n">
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>51.05</v>
+        <v>50.5</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DX15" t="n">
-        <v>12.86</v>
+        <v>12.63</v>
       </c>
       <c r="DY15" t="n">
-        <v>7.9</v>
+        <v>7.68</v>
       </c>
       <c r="DZ15" t="n">
         <v>4.95</v>
       </c>
       <c r="EA15" t="n">
-        <v>22.15</v>
+        <v>22.36</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="EC15" t="n">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
     </row>
     <row r="16">
@@ -7021,94 +7021,94 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D16" t="n">
         <v>10</v>
       </c>
       <c r="E16" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="F16" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="G16" t="n">
-        <v>4.64</v>
+        <v>4.5</v>
       </c>
       <c r="H16" t="n">
-        <v>103.36</v>
+        <v>101</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="K16" t="n">
-        <v>7.82</v>
+        <v>7.5</v>
       </c>
       <c r="L16" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="M16" t="n">
-        <v>50.91</v>
+        <v>49.33</v>
       </c>
       <c r="N16" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="O16" t="n">
-        <v>3.18</v>
+        <v>3</v>
       </c>
       <c r="P16" t="n">
-        <v>12.64</v>
+        <v>12.92</v>
       </c>
       <c r="Q16" t="n">
-        <v>14.09</v>
+        <v>13.75</v>
       </c>
       <c r="R16" t="n">
-        <v>7</v>
+        <v>7.33</v>
       </c>
       <c r="S16" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T16" t="n">
-        <v>2.27</v>
+        <v>2.42</v>
       </c>
       <c r="U16" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="V16" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>55.45</v>
+        <v>54.17</v>
       </c>
       <c r="Y16" t="n">
         <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>16.36</v>
+        <v>16.42</v>
       </c>
       <c r="AA16" t="n">
-        <v>10.09</v>
+        <v>10.08</v>
       </c>
       <c r="AB16" t="n">
-        <v>6.27</v>
+        <v>6.33</v>
       </c>
       <c r="AC16" t="n">
-        <v>19.36</v>
+        <v>18.92</v>
       </c>
       <c r="AD16" t="n">
         <v>1.84</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="AF16" t="n">
         <v>0</v>
@@ -7192,70 +7192,70 @@
         <v>3</v>
       </c>
       <c r="BG16" t="n">
-        <v>3.62</v>
+        <v>3.68</v>
       </c>
       <c r="BH16" t="n">
-        <v>11.29</v>
+        <v>11.05</v>
       </c>
       <c r="BI16" t="n">
-        <v>3.62</v>
+        <v>3.68</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="BL16" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="BM16" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="BN16" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.52</v>
+        <v>1.59</v>
       </c>
       <c r="BP16" t="n">
-        <v>5.05</v>
+        <v>4.86</v>
       </c>
       <c r="BQ16" t="n">
-        <v>6.24</v>
+        <v>6.18</v>
       </c>
       <c r="BR16" t="n">
         <v>100</v>
       </c>
       <c r="BS16" t="n">
-        <v>95.23999999999999</v>
+        <v>95.45</v>
       </c>
       <c r="BT16" t="n">
-        <v>76.19</v>
+        <v>77.27</v>
       </c>
       <c r="BU16" t="n">
-        <v>57.14</v>
+        <v>59.09</v>
       </c>
       <c r="BV16" t="n">
-        <v>28.57</v>
+        <v>31.82</v>
       </c>
       <c r="BW16" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BX16" t="n">
-        <v>80.95</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BY16" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="BZ16" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="CA16" t="n">
-        <v>3.6</v>
+        <v>3.58</v>
       </c>
       <c r="CB16" t="n">
-        <v>3.78</v>
+        <v>3.75</v>
       </c>
       <c r="CC16" t="n">
         <v>3.04</v>
@@ -7267,37 +7267,37 @@
         <v>1.34</v>
       </c>
       <c r="CF16" t="n">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="CG16" t="n">
-        <v>3.09</v>
+        <v>3.07</v>
       </c>
       <c r="CH16" t="n">
         <v>1.47</v>
       </c>
       <c r="CI16" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="CJ16" t="n">
         <v>1.66</v>
       </c>
       <c r="CK16" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="CL16" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="CM16" t="n">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="CN16" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CO16" t="n">
         <v>1.23</v>
       </c>
       <c r="CP16" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CQ16" t="n">
         <v>2.81</v>
@@ -7321,67 +7321,67 @@
         <v>1.67</v>
       </c>
       <c r="CX16" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="CY16" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CZ16" t="n">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="DA16" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="DB16" t="n">
         <v>1.24</v>
       </c>
       <c r="DC16" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="DD16" t="n">
-        <v>2.95</v>
+        <v>2.96</v>
       </c>
       <c r="DE16" t="n">
         <v>0.09</v>
       </c>
       <c r="DF16" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="DG16" t="n">
-        <v>3.48</v>
+        <v>3.45</v>
       </c>
       <c r="DH16" t="n">
-        <v>98</v>
+        <v>96.95</v>
       </c>
       <c r="DI16" t="n">
         <v>0.14</v>
       </c>
       <c r="DJ16" t="n">
-        <v>2.91</v>
+        <v>2.86</v>
       </c>
       <c r="DK16" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
       <c r="DM16" t="n">
-        <v>44.62</v>
+        <v>44.04</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="DO16" t="n">
-        <v>2.62</v>
+        <v>2.55</v>
       </c>
       <c r="DP16" t="n">
-        <v>13.05</v>
+        <v>13.18</v>
       </c>
       <c r="DQ16" t="n">
-        <v>15.38</v>
+        <v>15.14</v>
       </c>
       <c r="DR16" t="n">
-        <v>7.52</v>
+        <v>7.68</v>
       </c>
       <c r="DS16" t="n">
         <v>0.14</v>
@@ -7393,28 +7393,28 @@
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>54.19</v>
+        <v>53.55</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DX16" t="n">
-        <v>14.05</v>
+        <v>14.18</v>
       </c>
       <c r="DY16" t="n">
-        <v>8.48</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="DZ16" t="n">
-        <v>5.57</v>
+        <v>5.63</v>
       </c>
       <c r="EA16" t="n">
-        <v>18.38</v>
+        <v>18.18</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="EC16" t="n">
-        <v>2.76</v>
+        <v>2.73</v>
       </c>
     </row>
     <row r="17">
@@ -7424,13 +7424,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C17" t="n">
         <v>11</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E17" t="n">
         <v>0.18</v>
@@ -7517,49 +7517,49 @@
         <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="AI17" t="n">
-        <v>84.09999999999999</v>
+        <v>86.45</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AK17" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="AL17" t="n">
-        <v>3.7</v>
+        <v>3.73</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="AN17" t="n">
-        <v>31.6</v>
+        <v>33.45</v>
       </c>
       <c r="AO17" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AQ17" t="n">
-        <v>16.6</v>
+        <v>16.45</v>
       </c>
       <c r="AR17" t="n">
-        <v>12</v>
+        <v>11.64</v>
       </c>
       <c r="AS17" t="n">
-        <v>8.6</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AV17" t="n">
         <v>0</v>
@@ -7571,82 +7571,82 @@
         <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>42.4</v>
+        <v>42.45</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="BA17" t="n">
-        <v>11.9</v>
+        <v>13.27</v>
       </c>
       <c r="BB17" t="n">
-        <v>7.5</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="BC17" t="n">
-        <v>4.4</v>
+        <v>4.64</v>
       </c>
       <c r="BD17" t="n">
-        <v>22</v>
+        <v>21.27</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.29</v>
+        <v>1.41</v>
       </c>
       <c r="BF17" t="n">
-        <v>2.9</v>
+        <v>2.82</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.76</v>
+        <v>2.73</v>
       </c>
       <c r="BH17" t="n">
-        <v>9.050000000000001</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.76</v>
+        <v>2.73</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.86</v>
+        <v>0.82</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="BP17" t="n">
-        <v>4.1</v>
+        <v>4.05</v>
       </c>
       <c r="BQ17" t="n">
-        <v>4.48</v>
+        <v>4.45</v>
       </c>
       <c r="BR17" t="n">
-        <v>95.23999999999999</v>
+        <v>95.45</v>
       </c>
       <c r="BS17" t="n">
-        <v>61.9</v>
+        <v>63.64</v>
       </c>
       <c r="BT17" t="n">
-        <v>47.62</v>
+        <v>45.45</v>
       </c>
       <c r="BU17" t="n">
-        <v>23.81</v>
+        <v>22.73</v>
       </c>
       <c r="BV17" t="n">
-        <v>14.29</v>
+        <v>13.64</v>
       </c>
       <c r="BW17" t="n">
-        <v>14.29</v>
+        <v>13.64</v>
       </c>
       <c r="BX17" t="n">
-        <v>47.62</v>
+        <v>50</v>
       </c>
       <c r="BY17" t="n">
         <v>3.15</v>
@@ -7655,16 +7655,16 @@
         <v>3.42</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.42</v>
+        <v>3.43</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.65</v>
+        <v>3.64</v>
       </c>
       <c r="CC17" t="n">
-        <v>5.34</v>
+        <v>5.28</v>
       </c>
       <c r="CD17" t="n">
-        <v>6.43</v>
+        <v>6.27</v>
       </c>
       <c r="CE17" t="n">
         <v>1.42</v>
@@ -7685,13 +7685,13 @@
         <v>1.92</v>
       </c>
       <c r="CK17" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CL17" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="CN17" t="n">
         <v>1.79</v>
@@ -7700,7 +7700,7 @@
         <v>1.34</v>
       </c>
       <c r="CP17" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="CQ17" t="n">
         <v>3.68</v>
@@ -7709,7 +7709,7 @@
         <v>1.47</v>
       </c>
       <c r="CS17" t="n">
-        <v>3.11</v>
+        <v>3.12</v>
       </c>
       <c r="CT17" t="n">
         <v>2.8</v>
@@ -7724,16 +7724,16 @@
         <v>1.97</v>
       </c>
       <c r="CX17" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CY17" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="CZ17" t="n">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="DA17" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="DB17" t="n">
         <v>1.37</v>
@@ -7748,43 +7748,43 @@
         <v>0.09</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.86</v>
+        <v>1.77</v>
       </c>
       <c r="DG17" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="DH17" t="n">
-        <v>82.56999999999999</v>
+        <v>83.81999999999999</v>
       </c>
       <c r="DI17" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DJ17" t="n">
-        <v>3.28</v>
+        <v>3.22</v>
       </c>
       <c r="DK17" t="n">
-        <v>3.33</v>
+        <v>3.36</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.28</v>
+        <v>0.32</v>
       </c>
       <c r="DM17" t="n">
-        <v>31.67</v>
+        <v>32.59</v>
       </c>
       <c r="DN17" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="DO17" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="DP17" t="n">
-        <v>17.47</v>
+        <v>17.36</v>
       </c>
       <c r="DQ17" t="n">
-        <v>12.62</v>
+        <v>12.41</v>
       </c>
       <c r="DR17" t="n">
-        <v>9.1</v>
+        <v>9</v>
       </c>
       <c r="DS17" t="n">
         <v>0.14</v>
@@ -7796,28 +7796,28 @@
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>43.9</v>
+        <v>43.86</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DX17" t="n">
-        <v>11.09</v>
+        <v>11.82</v>
       </c>
       <c r="DY17" t="n">
-        <v>7.1</v>
+        <v>7.68</v>
       </c>
       <c r="DZ17" t="n">
-        <v>4</v>
+        <v>4.14</v>
       </c>
       <c r="EA17" t="n">
-        <v>21.09</v>
+        <v>20.77</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="EC17" t="n">
-        <v>3.19</v>
+        <v>3.14</v>
       </c>
     </row>
     <row r="18">
@@ -7827,13 +7827,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C18" t="n">
         <v>11</v>
       </c>
       <c r="D18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E18" t="n">
         <v>0.09</v>
@@ -7917,139 +7917,139 @@
         <v>2.91</v>
       </c>
       <c r="AF18" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AG18" t="n">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AH18" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="AI18" t="n">
-        <v>105.7</v>
+        <v>103.82</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="AK18" t="n">
-        <v>3.4</v>
+        <v>3.18</v>
       </c>
       <c r="AL18" t="n">
-        <v>5.9</v>
+        <v>5.64</v>
       </c>
       <c r="AM18" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AN18" t="n">
-        <v>45.6</v>
+        <v>44.64</v>
       </c>
       <c r="AO18" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AP18" t="n">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ18" t="n">
-        <v>17</v>
+        <v>16.36</v>
       </c>
       <c r="AR18" t="n">
-        <v>14.9</v>
+        <v>15</v>
       </c>
       <c r="AS18" t="n">
-        <v>7.8</v>
+        <v>8.27</v>
       </c>
       <c r="AT18" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AU18" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AV18" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AW18" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AX18" t="n">
         <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>52.9</v>
+        <v>51.64</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="BA18" t="n">
-        <v>12.2</v>
+        <v>12.18</v>
       </c>
       <c r="BB18" t="n">
-        <v>8.699999999999999</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="BC18" t="n">
-        <v>3.5</v>
+        <v>3.73</v>
       </c>
       <c r="BD18" t="n">
-        <v>22.1</v>
+        <v>22.18</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="BF18" t="n">
-        <v>3.3</v>
+        <v>3.09</v>
       </c>
       <c r="BG18" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="BH18" t="n">
-        <v>9.140000000000001</v>
+        <v>9.23</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.43</v>
+        <v>0.41</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.43</v>
+        <v>0.45</v>
       </c>
       <c r="BL18" t="n">
-        <v>0.76</v>
+        <v>0.73</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.48</v>
+        <v>0.55</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="BO18" t="n">
         <v>0.86</v>
       </c>
       <c r="BP18" t="n">
-        <v>3.33</v>
+        <v>3.32</v>
       </c>
       <c r="BQ18" t="n">
-        <v>5.81</v>
+        <v>5.91</v>
       </c>
       <c r="BR18" t="n">
-        <v>90.48</v>
+        <v>90.91</v>
       </c>
       <c r="BS18" t="n">
-        <v>61.9</v>
+        <v>63.64</v>
       </c>
       <c r="BT18" t="n">
-        <v>33.33</v>
+        <v>36.36</v>
       </c>
       <c r="BU18" t="n">
-        <v>14.29</v>
+        <v>13.64</v>
       </c>
       <c r="BV18" t="n">
-        <v>9.52</v>
+        <v>9.09</v>
       </c>
       <c r="BW18" t="n">
         <v>0</v>
       </c>
       <c r="BX18" t="n">
-        <v>42.86</v>
+        <v>40.91</v>
       </c>
       <c r="BY18" t="n">
         <v>1.89</v>
@@ -8058,28 +8058,28 @@
         <v>1.95</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.27</v>
+        <v>3.25</v>
       </c>
       <c r="CB18" t="n">
-        <v>3.4</v>
+        <v>3.39</v>
       </c>
       <c r="CC18" t="n">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
       <c r="CD18" t="n">
-        <v>3.09</v>
+        <v>3.1</v>
       </c>
       <c r="CE18" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CF18" t="n">
-        <v>2.97</v>
+        <v>2.99</v>
       </c>
       <c r="CG18" t="n">
-        <v>2.72</v>
+        <v>2.69</v>
       </c>
       <c r="CH18" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CI18" t="n">
         <v>1.85</v>
@@ -8091,7 +8091,7 @@
         <v>1.61</v>
       </c>
       <c r="CL18" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="CM18" t="n">
         <v>2.14</v>
@@ -8103,19 +8103,19 @@
         <v>1.35</v>
       </c>
       <c r="CP18" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="CQ18" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="CR18" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="CS18" t="n">
-        <v>3.11</v>
+        <v>3.13</v>
       </c>
       <c r="CT18" t="n">
-        <v>2.8</v>
+        <v>2.79</v>
       </c>
       <c r="CU18" t="n">
         <v>1.39</v>
@@ -8127,7 +8127,7 @@
         <v>1.94</v>
       </c>
       <c r="CX18" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CY18" t="n">
         <v>2.1</v>
@@ -8142,85 +8142,85 @@
         <v>1.38</v>
       </c>
       <c r="DC18" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="DD18" t="n">
-        <v>4.05</v>
+        <v>4.07</v>
       </c>
       <c r="DE18" t="n">
         <v>0.09</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.86</v>
+        <v>1.78</v>
       </c>
       <c r="DG18" t="n">
-        <v>4.09</v>
+        <v>4</v>
       </c>
       <c r="DH18" t="n">
-        <v>108.62</v>
+        <v>107.54</v>
       </c>
       <c r="DI18" t="n">
-        <v>0.09</v>
+        <v>0.13</v>
       </c>
       <c r="DJ18" t="n">
-        <v>3.24</v>
+        <v>3.14</v>
       </c>
       <c r="DK18" t="n">
-        <v>6.33</v>
+        <v>6.18</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.57</v>
+        <v>0.54</v>
       </c>
       <c r="DM18" t="n">
-        <v>54.71</v>
+        <v>53.82</v>
       </c>
       <c r="DN18" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="DO18" t="n">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="DP18" t="n">
-        <v>17.57</v>
+        <v>17.22</v>
       </c>
       <c r="DQ18" t="n">
-        <v>13.9</v>
+        <v>14</v>
       </c>
       <c r="DR18" t="n">
-        <v>6.52</v>
+        <v>6.82</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DT18" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DU18" t="n">
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>52.29</v>
+        <v>51.68</v>
       </c>
       <c r="DW18" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DX18" t="n">
-        <v>14.48</v>
+        <v>14.36</v>
       </c>
       <c r="DY18" t="n">
-        <v>10.14</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="DZ18" t="n">
-        <v>4.33</v>
+        <v>4.41</v>
       </c>
       <c r="EA18" t="n">
-        <v>25.48</v>
+        <v>25.36</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="EC18" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -8230,10 +8230,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C19" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D19" t="n">
         <v>11</v>
@@ -8242,49 +8242,49 @@
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="G19" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="H19" t="n">
-        <v>95.40000000000001</v>
+        <v>94.36</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="J19" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="K19" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L19" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="M19" t="n">
-        <v>42.1</v>
+        <v>42.36</v>
       </c>
       <c r="N19" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="O19" t="n">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="P19" t="n">
-        <v>13.6</v>
+        <v>13.09</v>
       </c>
       <c r="Q19" t="n">
-        <v>15.8</v>
+        <v>15.73</v>
       </c>
       <c r="R19" t="n">
-        <v>7.4</v>
+        <v>7.73</v>
       </c>
       <c r="S19" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="T19" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
@@ -8296,28 +8296,28 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>51.7</v>
+        <v>52.18</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="Z19" t="n">
-        <v>11.3</v>
+        <v>11.73</v>
       </c>
       <c r="AA19" t="n">
-        <v>7.9</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="AB19" t="n">
-        <v>3.4</v>
+        <v>3.18</v>
       </c>
       <c r="AC19" t="n">
-        <v>22.8</v>
+        <v>23.18</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="AF19" t="n">
         <v>0.18</v>
@@ -8401,70 +8401,70 @@
         <v>2.91</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.57</v>
+        <v>2.55</v>
       </c>
       <c r="BH19" t="n">
-        <v>10.24</v>
+        <v>10.09</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.57</v>
+        <v>2.55</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.48</v>
+        <v>0.45</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="BM19" t="n">
         <v>0.95</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="BO19" t="n">
-        <v>0.86</v>
+        <v>0.82</v>
       </c>
       <c r="BP19" t="n">
-        <v>5</v>
+        <v>4.91</v>
       </c>
       <c r="BQ19" t="n">
-        <v>5.19</v>
+        <v>5.14</v>
       </c>
       <c r="BR19" t="n">
-        <v>95.23999999999999</v>
+        <v>95.45</v>
       </c>
       <c r="BS19" t="n">
-        <v>66.67</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="BT19" t="n">
-        <v>42.86</v>
+        <v>40.91</v>
       </c>
       <c r="BU19" t="n">
-        <v>28.57</v>
+        <v>27.27</v>
       </c>
       <c r="BV19" t="n">
-        <v>19.05</v>
+        <v>18.18</v>
       </c>
       <c r="BW19" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BX19" t="n">
-        <v>57.14</v>
+        <v>59.09</v>
       </c>
       <c r="BY19" t="n">
-        <v>2.36</v>
+        <v>2.31</v>
       </c>
       <c r="BZ19" t="n">
-        <v>2.49</v>
+        <v>2.43</v>
       </c>
       <c r="CA19" t="n">
-        <v>3.17</v>
+        <v>3.18</v>
       </c>
       <c r="CB19" t="n">
-        <v>3.3</v>
+        <v>3.31</v>
       </c>
       <c r="CC19" t="n">
         <v>3.82</v>
@@ -8485,22 +8485,22 @@
         <v>1.33</v>
       </c>
       <c r="CI19" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CJ19" t="n">
         <v>1.95</v>
       </c>
       <c r="CK19" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CL19" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CM19" t="n">
         <v>2.3</v>
       </c>
       <c r="CN19" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CO19" t="n">
         <v>1.39</v>
@@ -8509,16 +8509,16 @@
         <v>2.24</v>
       </c>
       <c r="CQ19" t="n">
-        <v>4.14</v>
+        <v>4.12</v>
       </c>
       <c r="CR19" t="n">
         <v>1.5</v>
       </c>
       <c r="CS19" t="n">
-        <v>3.18</v>
+        <v>3.19</v>
       </c>
       <c r="CT19" t="n">
-        <v>2.71</v>
+        <v>2.72</v>
       </c>
       <c r="CU19" t="n">
         <v>1.38</v>
@@ -8536,10 +8536,10 @@
         <v>1.99</v>
       </c>
       <c r="CZ19" t="n">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="DA19" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="DB19" t="n">
         <v>1.41</v>
@@ -8548,49 +8548,49 @@
         <v>2.28</v>
       </c>
       <c r="DD19" t="n">
-        <v>4.21</v>
+        <v>4.2</v>
       </c>
       <c r="DE19" t="n">
         <v>0.09</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="DG19" t="n">
-        <v>2.43</v>
+        <v>2.41</v>
       </c>
       <c r="DH19" t="n">
-        <v>90.76000000000001</v>
+        <v>90.45999999999999</v>
       </c>
       <c r="DI19" t="n">
         <v>0.09</v>
       </c>
       <c r="DJ19" t="n">
-        <v>3.47</v>
+        <v>3.45</v>
       </c>
       <c r="DK19" t="n">
-        <v>4.76</v>
+        <v>4.68</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="DM19" t="n">
-        <v>41.38</v>
+        <v>41.54</v>
       </c>
       <c r="DN19" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="DO19" t="n">
-        <v>2.29</v>
+        <v>2.22</v>
       </c>
       <c r="DP19" t="n">
-        <v>13.43</v>
+        <v>13.18</v>
       </c>
       <c r="DQ19" t="n">
-        <v>15.48</v>
+        <v>15.46</v>
       </c>
       <c r="DR19" t="n">
-        <v>7.43</v>
+        <v>7.59</v>
       </c>
       <c r="DS19" t="n">
         <v>0.09</v>
@@ -8602,22 +8602,22 @@
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>49.95</v>
+        <v>50.27</v>
       </c>
       <c r="DW19" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="DX19" t="n">
-        <v>12.14</v>
+        <v>12.32</v>
       </c>
       <c r="DY19" t="n">
-        <v>8.52</v>
+        <v>8.82</v>
       </c>
       <c r="DZ19" t="n">
-        <v>3.62</v>
+        <v>3.5</v>
       </c>
       <c r="EA19" t="n">
-        <v>20.05</v>
+        <v>20.36</v>
       </c>
       <c r="EB19" t="n">
         <v>1.32</v>
@@ -9036,13 +9036,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C21" t="n">
         <v>11</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E21" t="n">
         <v>0.09</v>
@@ -9129,49 +9129,49 @@
         <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AI21" t="n">
-        <v>84.09999999999999</v>
+        <v>83.09</v>
       </c>
       <c r="AJ21" t="n">
         <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AL21" t="n">
-        <v>3.6</v>
+        <v>3.73</v>
       </c>
       <c r="AM21" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AN21" t="n">
-        <v>32.6</v>
+        <v>33.09</v>
       </c>
       <c r="AO21" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AQ21" t="n">
-        <v>11.1</v>
+        <v>11.45</v>
       </c>
       <c r="AR21" t="n">
-        <v>13</v>
+        <v>13.18</v>
       </c>
       <c r="AS21" t="n">
-        <v>8.5</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="AT21" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AU21" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AV21" t="n">
         <v>0</v>
@@ -9183,82 +9183,82 @@
         <v>0</v>
       </c>
       <c r="AY21" t="n">
-        <v>46.8</v>
+        <v>45.91</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="BA21" t="n">
-        <v>9.1</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="BB21" t="n">
-        <v>6.9</v>
+        <v>7.36</v>
       </c>
       <c r="BC21" t="n">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="BD21" t="n">
-        <v>18.3</v>
+        <v>18.64</v>
       </c>
       <c r="BE21" t="n">
-        <v>0.97</v>
+        <v>0.99</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="BG21" t="n">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="BH21" t="n">
-        <v>9.52</v>
+        <v>9.5</v>
       </c>
       <c r="BI21" t="n">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="BJ21" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="BK21" t="n">
-        <v>0.48</v>
+        <v>0.45</v>
       </c>
       <c r="BL21" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="BM21" t="n">
-        <v>0.48</v>
+        <v>0.45</v>
       </c>
       <c r="BN21" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="BO21" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="BP21" t="n">
-        <v>4.19</v>
+        <v>4.23</v>
       </c>
       <c r="BQ21" t="n">
-        <v>5.29</v>
+        <v>5.23</v>
       </c>
       <c r="BR21" t="n">
-        <v>95.23999999999999</v>
+        <v>95.45</v>
       </c>
       <c r="BS21" t="n">
-        <v>71.43000000000001</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="BT21" t="n">
-        <v>42.86</v>
+        <v>40.91</v>
       </c>
       <c r="BU21" t="n">
-        <v>19.05</v>
+        <v>18.18</v>
       </c>
       <c r="BV21" t="n">
-        <v>9.52</v>
+        <v>9.09</v>
       </c>
       <c r="BW21" t="n">
         <v>0</v>
       </c>
       <c r="BX21" t="n">
-        <v>52.38</v>
+        <v>50</v>
       </c>
       <c r="BY21" t="n">
         <v>2.52</v>
@@ -9267,40 +9267,40 @@
         <v>2.68</v>
       </c>
       <c r="CA21" t="n">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="CB21" t="n">
         <v>3.08</v>
       </c>
       <c r="CC21" t="n">
-        <v>3.7</v>
+        <v>3.76</v>
       </c>
       <c r="CD21" t="n">
-        <v>4.32</v>
+        <v>4.36</v>
       </c>
       <c r="CE21" t="n">
         <v>1.56</v>
       </c>
       <c r="CF21" t="n">
-        <v>3.63</v>
+        <v>3.67</v>
       </c>
       <c r="CG21" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="CH21" t="n">
         <v>1.25</v>
       </c>
       <c r="CI21" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CJ21" t="n">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="CK21" t="n">
         <v>1.67</v>
       </c>
       <c r="CL21" t="n">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="CM21" t="n">
         <v>2.12</v>
@@ -9309,13 +9309,13 @@
         <v>1.72</v>
       </c>
       <c r="CO21" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="CP21" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="CQ21" t="n">
-        <v>4.94</v>
+        <v>5.01</v>
       </c>
       <c r="CR21" t="n">
         <v>1.6</v>
@@ -9330,10 +9330,10 @@
         <v>1.37</v>
       </c>
       <c r="CV21" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="CW21" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="CX21" t="n">
         <v>1.71</v>
@@ -9348,52 +9348,52 @@
         <v>1.7</v>
       </c>
       <c r="DB21" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="DC21" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="DD21" t="n">
-        <v>5.53</v>
+        <v>5.59</v>
       </c>
       <c r="DE21" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DF21" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="DG21" t="n">
-        <v>2.52</v>
+        <v>2.55</v>
       </c>
       <c r="DH21" t="n">
-        <v>91.19</v>
+        <v>90.36</v>
       </c>
       <c r="DI21" t="n">
         <v>0</v>
       </c>
       <c r="DJ21" t="n">
-        <v>2.43</v>
+        <v>2.37</v>
       </c>
       <c r="DK21" t="n">
-        <v>4.57</v>
+        <v>4.59</v>
       </c>
       <c r="DL21" t="n">
-        <v>0.72</v>
+        <v>0.68</v>
       </c>
       <c r="DM21" t="n">
-        <v>39.91</v>
+        <v>39.82</v>
       </c>
       <c r="DN21" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="DO21" t="n">
         <v>2</v>
       </c>
       <c r="DP21" t="n">
-        <v>12.67</v>
+        <v>12.77</v>
       </c>
       <c r="DQ21" t="n">
-        <v>12.76</v>
+        <v>12.86</v>
       </c>
       <c r="DR21" t="n">
         <v>9.1</v>
@@ -9408,28 +9408,28 @@
         <v>0</v>
       </c>
       <c r="DV21" t="n">
-        <v>46.19</v>
+        <v>45.78</v>
       </c>
       <c r="DW21" t="n">
         <v>0.09</v>
       </c>
       <c r="DX21" t="n">
-        <v>10.81</v>
+        <v>10.9</v>
       </c>
       <c r="DY21" t="n">
-        <v>7.91</v>
+        <v>8.09</v>
       </c>
       <c r="DZ21" t="n">
-        <v>2.91</v>
+        <v>2.82</v>
       </c>
       <c r="EA21" t="n">
-        <v>21.05</v>
+        <v>21.1</v>
       </c>
       <c r="EB21" t="n">
         <v>1.18</v>
       </c>
       <c r="EC21" t="n">
-        <v>2.29</v>
+        <v>2.23</v>
       </c>
     </row>
     <row r="22">
@@ -9439,13 +9439,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C22" t="n">
         <v>11</v>
       </c>
       <c r="D22" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -9529,139 +9529,139 @@
         <v>2</v>
       </c>
       <c r="AF22" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AG22" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="AH22" t="n">
-        <v>2.8</v>
+        <v>2.55</v>
       </c>
       <c r="AI22" t="n">
-        <v>88.5</v>
+        <v>86.27</v>
       </c>
       <c r="AJ22" t="n">
         <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>3.3</v>
+        <v>3.18</v>
       </c>
       <c r="AL22" t="n">
-        <v>4.6</v>
+        <v>4.27</v>
       </c>
       <c r="AM22" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AN22" t="n">
-        <v>38.6</v>
+        <v>37.27</v>
       </c>
       <c r="AO22" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AQ22" t="n">
-        <v>11.7</v>
+        <v>11.55</v>
       </c>
       <c r="AR22" t="n">
-        <v>10.2</v>
+        <v>10</v>
       </c>
       <c r="AS22" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="AT22" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AU22" t="n">
-        <v>1.1</v>
+        <v>1.36</v>
       </c>
       <c r="AV22" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AW22" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AX22" t="n">
         <v>0</v>
       </c>
       <c r="AY22" t="n">
-        <v>44.4</v>
+        <v>43.27</v>
       </c>
       <c r="AZ22" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="BA22" t="n">
-        <v>10.1</v>
+        <v>9.73</v>
       </c>
       <c r="BB22" t="n">
-        <v>5.9</v>
+        <v>5.45</v>
       </c>
       <c r="BC22" t="n">
-        <v>4.2</v>
+        <v>4.27</v>
       </c>
       <c r="BD22" t="n">
-        <v>19.6</v>
+        <v>19.36</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="BF22" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="BG22" t="n">
-        <v>2.62</v>
+        <v>2.77</v>
       </c>
       <c r="BH22" t="n">
-        <v>10.1</v>
+        <v>10.05</v>
       </c>
       <c r="BI22" t="n">
-        <v>2.62</v>
+        <v>2.77</v>
       </c>
       <c r="BJ22" t="n">
-        <v>0.52</v>
+        <v>0.55</v>
       </c>
       <c r="BK22" t="n">
-        <v>0.52</v>
+        <v>0.64</v>
       </c>
       <c r="BL22" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="BM22" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="BN22" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="BO22" t="n">
-        <v>1.05</v>
+        <v>1.18</v>
       </c>
       <c r="BP22" t="n">
-        <v>4.52</v>
+        <v>4.45</v>
       </c>
       <c r="BQ22" t="n">
-        <v>4.95</v>
+        <v>5</v>
       </c>
       <c r="BR22" t="n">
-        <v>95.23999999999999</v>
+        <v>95.45</v>
       </c>
       <c r="BS22" t="n">
-        <v>61.9</v>
+        <v>63.64</v>
       </c>
       <c r="BT22" t="n">
-        <v>47.62</v>
+        <v>50</v>
       </c>
       <c r="BU22" t="n">
-        <v>28.57</v>
+        <v>31.82</v>
       </c>
       <c r="BV22" t="n">
-        <v>19.05</v>
+        <v>22.73</v>
       </c>
       <c r="BW22" t="n">
-        <v>4.76</v>
+        <v>9.09</v>
       </c>
       <c r="BX22" t="n">
-        <v>57.14</v>
+        <v>59.09</v>
       </c>
       <c r="BY22" t="n">
         <v>2.1</v>
@@ -9673,13 +9673,13 @@
         <v>3.19</v>
       </c>
       <c r="CB22" t="n">
-        <v>3.29</v>
+        <v>3.28</v>
       </c>
       <c r="CC22" t="n">
-        <v>3.18</v>
+        <v>3.1</v>
       </c>
       <c r="CD22" t="n">
-        <v>3.26</v>
+        <v>3.19</v>
       </c>
       <c r="CE22" t="n">
         <v>1.45</v>
@@ -9688,7 +9688,7 @@
         <v>3.11</v>
       </c>
       <c r="CG22" t="n">
-        <v>2.66</v>
+        <v>2.65</v>
       </c>
       <c r="CH22" t="n">
         <v>1.33</v>
@@ -9703,13 +9703,13 @@
         <v>1.62</v>
       </c>
       <c r="CL22" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="CM22" t="n">
         <v>2.17</v>
       </c>
       <c r="CN22" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CO22" t="n">
         <v>1.37</v>
@@ -9724,7 +9724,7 @@
         <v>1.48</v>
       </c>
       <c r="CS22" t="n">
-        <v>3.11</v>
+        <v>3.13</v>
       </c>
       <c r="CT22" t="n">
         <v>2.79</v>
@@ -9739,16 +9739,16 @@
         <v>1.97</v>
       </c>
       <c r="CX22" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CY22" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CZ22" t="n">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="DA22" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="DB22" t="n">
         <v>1.42</v>
@@ -9757,82 +9757,82 @@
         <v>2.33</v>
       </c>
       <c r="DD22" t="n">
-        <v>4.34</v>
+        <v>4.33</v>
       </c>
       <c r="DE22" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DF22" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="DG22" t="n">
-        <v>2.52</v>
+        <v>2.41</v>
       </c>
       <c r="DH22" t="n">
-        <v>100.95</v>
+        <v>99.27</v>
       </c>
       <c r="DI22" t="n">
         <v>0</v>
       </c>
       <c r="DJ22" t="n">
-        <v>2.91</v>
+        <v>2.86</v>
       </c>
       <c r="DK22" t="n">
-        <v>5</v>
+        <v>4.82</v>
       </c>
       <c r="DL22" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="DM22" t="n">
-        <v>45.33</v>
+        <v>44.36</v>
       </c>
       <c r="DN22" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="DO22" t="n">
-        <v>2.14</v>
+        <v>2.09</v>
       </c>
       <c r="DP22" t="n">
-        <v>12.29</v>
+        <v>12.19</v>
       </c>
       <c r="DQ22" t="n">
-        <v>10.43</v>
+        <v>10.32</v>
       </c>
       <c r="DR22" t="n">
-        <v>7.48</v>
+        <v>7.78</v>
       </c>
       <c r="DS22" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="DT22" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="DU22" t="n">
         <v>0</v>
       </c>
       <c r="DV22" t="n">
-        <v>45.47</v>
+        <v>44.86</v>
       </c>
       <c r="DW22" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="DX22" t="n">
-        <v>11.91</v>
+        <v>11.64</v>
       </c>
       <c r="DY22" t="n">
-        <v>7.19</v>
+        <v>6.9</v>
       </c>
       <c r="DZ22" t="n">
-        <v>4.71</v>
+        <v>4.72</v>
       </c>
       <c r="EA22" t="n">
-        <v>19.57</v>
+        <v>19.45</v>
       </c>
       <c r="EB22" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="EC22" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="23">
@@ -9842,13 +9842,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C23" t="n">
         <v>11</v>
       </c>
       <c r="D23" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E23" t="n">
         <v>0.18</v>
@@ -9935,136 +9935,136 @@
         <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AI23" t="n">
-        <v>90.40000000000001</v>
+        <v>90.27</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AK23" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>37.64</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>12.18</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>18.73</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>9.18</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>56.82</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>10.36</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>7.27</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>18.36</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BG23" t="n">
         <v>2</v>
       </c>
-      <c r="AL23" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>37.2</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>19</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>56.5</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="BD23" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="BE23" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="BF23" t="n">
+      <c r="BH23" t="n">
+        <v>7.45</v>
+      </c>
+      <c r="BI23" t="n">
         <v>2</v>
       </c>
-      <c r="BG23" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="BH23" t="n">
-        <v>7.52</v>
-      </c>
-      <c r="BI23" t="n">
-        <v>1.86</v>
-      </c>
       <c r="BJ23" t="n">
-        <v>0.67</v>
+        <v>0.73</v>
       </c>
       <c r="BK23" t="n">
-        <v>0.33</v>
+        <v>0.36</v>
       </c>
       <c r="BL23" t="n">
-        <v>0.38</v>
+        <v>0.45</v>
       </c>
       <c r="BM23" t="n">
-        <v>0.48</v>
+        <v>0.45</v>
       </c>
       <c r="BN23" t="n">
-        <v>0.86</v>
+        <v>0.91</v>
       </c>
       <c r="BO23" t="n">
-        <v>1</v>
+        <v>1.09</v>
       </c>
       <c r="BP23" t="n">
-        <v>3.86</v>
+        <v>3.73</v>
       </c>
       <c r="BQ23" t="n">
-        <v>3.67</v>
+        <v>3.73</v>
       </c>
       <c r="BR23" t="n">
-        <v>80.95</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BS23" t="n">
-        <v>52.38</v>
+        <v>54.55</v>
       </c>
       <c r="BT23" t="n">
-        <v>33.33</v>
+        <v>36.36</v>
       </c>
       <c r="BU23" t="n">
-        <v>19.05</v>
+        <v>22.73</v>
       </c>
       <c r="BV23" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="BW23" t="n">
         <v>0</v>
       </c>
       <c r="BX23" t="n">
-        <v>47.62</v>
+        <v>50</v>
       </c>
       <c r="BY23" t="n">
         <v>1.82</v>
@@ -10073,7 +10073,7 @@
         <v>1.86</v>
       </c>
       <c r="CA23" t="n">
-        <v>3.22</v>
+        <v>3.21</v>
       </c>
       <c r="CB23" t="n">
         <v>3.33</v>
@@ -10082,25 +10082,25 @@
         <v>2.99</v>
       </c>
       <c r="CD23" t="n">
-        <v>3.33</v>
+        <v>3.34</v>
       </c>
       <c r="CE23" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CF23" t="n">
-        <v>3.23</v>
+        <v>3.21</v>
       </c>
       <c r="CG23" t="n">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="CH23" t="n">
         <v>1.31</v>
       </c>
       <c r="CI23" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="CJ23" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CK23" t="n">
         <v>1.7</v>
@@ -10118,10 +10118,10 @@
         <v>1.4</v>
       </c>
       <c r="CP23" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="CQ23" t="n">
-        <v>4.2</v>
+        <v>4.15</v>
       </c>
       <c r="CR23" t="n">
         <v>1.52</v>
@@ -10136,73 +10136,73 @@
         <v>1.37</v>
       </c>
       <c r="CV23" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="CW23" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="CX23" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CY23" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="CZ23" t="n">
         <v>2.06</v>
       </c>
       <c r="DA23" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="DB23" t="n">
         <v>1.44</v>
       </c>
       <c r="DC23" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="DD23" t="n">
-        <v>4.55</v>
+        <v>4.49</v>
       </c>
       <c r="DE23" t="n">
         <v>0.09</v>
       </c>
       <c r="DF23" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="DG23" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="DH23" t="n">
-        <v>94.05</v>
+        <v>93.81999999999999</v>
       </c>
       <c r="DI23" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DJ23" t="n">
-        <v>2.09</v>
+        <v>2.18</v>
       </c>
       <c r="DK23" t="n">
-        <v>4.05</v>
+        <v>3.95</v>
       </c>
       <c r="DL23" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="DM23" t="n">
-        <v>38.28</v>
+        <v>38.46</v>
       </c>
       <c r="DN23" t="n">
-        <v>0.47</v>
+        <v>0.54</v>
       </c>
       <c r="DO23" t="n">
-        <v>2.33</v>
+        <v>2.22</v>
       </c>
       <c r="DP23" t="n">
-        <v>13</v>
+        <v>12.86</v>
       </c>
       <c r="DQ23" t="n">
-        <v>17.19</v>
+        <v>17.14</v>
       </c>
       <c r="DR23" t="n">
-        <v>7.57</v>
+        <v>7.63</v>
       </c>
       <c r="DS23" t="n">
         <v>0</v>
@@ -10214,28 +10214,28 @@
         <v>0</v>
       </c>
       <c r="DV23" t="n">
-        <v>55.81</v>
+        <v>56</v>
       </c>
       <c r="DW23" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DX23" t="n">
-        <v>11.19</v>
+        <v>11.27</v>
       </c>
       <c r="DY23" t="n">
-        <v>7.48</v>
+        <v>7.5</v>
       </c>
       <c r="DZ23" t="n">
-        <v>3.71</v>
+        <v>3.77</v>
       </c>
       <c r="EA23" t="n">
-        <v>18.24</v>
+        <v>18.31</v>
       </c>
       <c r="EB23" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="EC23" t="n">
-        <v>1.81</v>
+        <v>1.91</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Spain_Segunda_División_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Spain_Segunda_División_2025-2026.xlsx
@@ -4215,7 +4215,7 @@
         <v>1.45</v>
       </c>
       <c r="G9" t="n">
-        <v>2.18</v>
+        <v>2.82</v>
       </c>
       <c r="H9" t="n">
         <v>103.91</v>
@@ -4230,7 +4230,7 @@
         <v>5.45</v>
       </c>
       <c r="L9" t="n">
-        <v>0.45</v>
+        <v>0.55</v>
       </c>
       <c r="M9" t="n">
         <v>56.36</v>
@@ -4239,7 +4239,7 @@
         <v>1.36</v>
       </c>
       <c r="O9" t="n">
-        <v>2.36</v>
+        <v>2.64</v>
       </c>
       <c r="P9" t="n">
         <v>15.73</v>
@@ -4266,7 +4266,7 @@
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>59.27</v>
+        <v>59.18</v>
       </c>
       <c r="Y9" t="n">
         <v>0.18</v>
@@ -4275,16 +4275,16 @@
         <v>16.36</v>
       </c>
       <c r="AA9" t="n">
-        <v>11.27</v>
+        <v>11.36</v>
       </c>
       <c r="AB9" t="n">
-        <v>5.09</v>
+        <v>5</v>
       </c>
       <c r="AC9" t="n">
         <v>21.73</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AE9" t="n">
         <v>2.64</v>
@@ -4398,10 +4398,10 @@
         <v>0.95</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.55</v>
+        <v>4.77</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.68</v>
+        <v>5.09</v>
       </c>
       <c r="BR9" t="n">
         <v>86.36</v>
@@ -4527,7 +4527,7 @@
         <v>1.54</v>
       </c>
       <c r="DG9" t="n">
-        <v>2.55</v>
+        <v>2.86</v>
       </c>
       <c r="DH9" t="n">
         <v>98.86</v>
@@ -4542,7 +4542,7 @@
         <v>5.18</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.27</v>
+        <v>0.32</v>
       </c>
       <c r="DM9" t="n">
         <v>49.4</v>
@@ -4551,7 +4551,7 @@
         <v>1.36</v>
       </c>
       <c r="DO9" t="n">
-        <v>2.18</v>
+        <v>2.32</v>
       </c>
       <c r="DP9" t="n">
         <v>15.59</v>
@@ -4572,7 +4572,7 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>57.04</v>
+        <v>57</v>
       </c>
       <c r="DW9" t="n">
         <v>0.13</v>
@@ -4581,16 +4581,16 @@
         <v>14.81</v>
       </c>
       <c r="DY9" t="n">
-        <v>9.960000000000001</v>
+        <v>10</v>
       </c>
       <c r="DZ9" t="n">
-        <v>4.86</v>
+        <v>4.82</v>
       </c>
       <c r="EA9" t="n">
         <v>22.04</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="EC9" t="n">
         <v>2.78</v>
@@ -5409,61 +5409,61 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D12" t="n">
         <v>10</v>
       </c>
       <c r="E12" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="F12" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="G12" t="n">
-        <v>3</v>
+        <v>3.08</v>
       </c>
       <c r="H12" t="n">
-        <v>92.36</v>
+        <v>92.42</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="J12" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="K12" t="n">
-        <v>5.91</v>
+        <v>5.92</v>
       </c>
       <c r="L12" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="M12" t="n">
-        <v>45.82</v>
+        <v>45.17</v>
       </c>
       <c r="N12" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="O12" t="n">
-        <v>2.91</v>
+        <v>2.83</v>
       </c>
       <c r="P12" t="n">
-        <v>12.09</v>
+        <v>11.92</v>
       </c>
       <c r="Q12" t="n">
-        <v>15.27</v>
+        <v>15.08</v>
       </c>
       <c r="R12" t="n">
-        <v>7.36</v>
+        <v>7.33</v>
       </c>
       <c r="S12" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="T12" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="U12" t="n">
         <v>0</v>
@@ -5475,28 +5475,28 @@
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>51.91</v>
+        <v>52.75</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="Z12" t="n">
-        <v>14.73</v>
+        <v>14.83</v>
       </c>
       <c r="AA12" t="n">
-        <v>10.82</v>
+        <v>11</v>
       </c>
       <c r="AB12" t="n">
-        <v>3.91</v>
+        <v>3.83</v>
       </c>
       <c r="AC12" t="n">
-        <v>23.27</v>
+        <v>24.08</v>
       </c>
       <c r="AD12" t="n">
         <v>1.53</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>
@@ -5580,70 +5580,70 @@
         <v>2.8</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.38</v>
+        <v>2.27</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.289999999999999</v>
+        <v>9.23</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.38</v>
+        <v>2.27</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.48</v>
+        <v>0.45</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.19</v>
+        <v>4.14</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.1</v>
+        <v>5.09</v>
       </c>
       <c r="BR12" t="n">
-        <v>80.95</v>
+        <v>77.27</v>
       </c>
       <c r="BS12" t="n">
-        <v>66.67</v>
+        <v>63.64</v>
       </c>
       <c r="BT12" t="n">
-        <v>42.86</v>
+        <v>40.91</v>
       </c>
       <c r="BU12" t="n">
-        <v>28.57</v>
+        <v>27.27</v>
       </c>
       <c r="BV12" t="n">
-        <v>9.52</v>
+        <v>9.09</v>
       </c>
       <c r="BW12" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BX12" t="n">
-        <v>57.14</v>
+        <v>54.55</v>
       </c>
       <c r="BY12" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="BZ12" t="n">
         <v>2.35</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.21</v>
+        <v>3.2</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.28</v>
+        <v>3.27</v>
       </c>
       <c r="CC12" t="n">
         <v>3.52</v>
@@ -5655,25 +5655,25 @@
         <v>1.45</v>
       </c>
       <c r="CF12" t="n">
-        <v>3.1</v>
+        <v>3.11</v>
       </c>
       <c r="CG12" t="n">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="CH12" t="n">
         <v>1.33</v>
       </c>
       <c r="CI12" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CJ12" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="CK12" t="n">
         <v>1.58</v>
       </c>
       <c r="CL12" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="CM12" t="n">
         <v>2.23</v>
@@ -5682,13 +5682,13 @@
         <v>1.78</v>
       </c>
       <c r="CO12" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CP12" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="CQ12" t="n">
-        <v>3.87</v>
+        <v>3.91</v>
       </c>
       <c r="CR12" t="n">
         <v>1.49</v>
@@ -5703,10 +5703,10 @@
         <v>1.36</v>
       </c>
       <c r="CV12" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CW12" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CX12" t="n">
         <v>1.65</v>
@@ -5715,61 +5715,61 @@
         <v>2.08</v>
       </c>
       <c r="CZ12" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="DA12" t="n">
         <v>1.76</v>
       </c>
       <c r="DB12" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="DC12" t="n">
-        <v>2.27</v>
+        <v>2.29</v>
       </c>
       <c r="DD12" t="n">
-        <v>4.18</v>
+        <v>4.23</v>
       </c>
       <c r="DE12" t="n">
         <v>0.14</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.05</v>
+        <v>2.13</v>
       </c>
       <c r="DH12" t="n">
-        <v>91.14</v>
+        <v>91.23</v>
       </c>
       <c r="DI12" t="n">
         <v>0</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="DK12" t="n">
-        <v>4.43</v>
+        <v>4.5</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.48</v>
+        <v>0.45</v>
       </c>
       <c r="DM12" t="n">
-        <v>42.72</v>
+        <v>42.5</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.76</v>
+        <v>0.73</v>
       </c>
       <c r="DO12" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="DP12" t="n">
-        <v>13.09</v>
+        <v>12.96</v>
       </c>
       <c r="DQ12" t="n">
-        <v>14.86</v>
+        <v>14.77</v>
       </c>
       <c r="DR12" t="n">
-        <v>7.71</v>
+        <v>7.68</v>
       </c>
       <c r="DS12" t="n">
         <v>0.05</v>
@@ -5781,28 +5781,28 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>49.38</v>
+        <v>49.95</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DX12" t="n">
-        <v>12.72</v>
+        <v>12.86</v>
       </c>
       <c r="DY12" t="n">
-        <v>9.050000000000001</v>
+        <v>9.23</v>
       </c>
       <c r="DZ12" t="n">
-        <v>3.67</v>
+        <v>3.63</v>
       </c>
       <c r="EA12" t="n">
-        <v>22.43</v>
+        <v>22.91</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
     </row>
     <row r="13">
@@ -6714,7 +6714,7 @@
         <v>1.55</v>
       </c>
       <c r="AH15" t="n">
-        <v>2</v>
+        <v>2.27</v>
       </c>
       <c r="AI15" t="n">
         <v>89.73</v>
@@ -6729,7 +6729,7 @@
         <v>4.18</v>
       </c>
       <c r="AM15" t="n">
-        <v>0</v>
+        <v>0.18</v>
       </c>
       <c r="AN15" t="n">
         <v>43.36</v>
@@ -6738,7 +6738,7 @@
         <v>0.73</v>
       </c>
       <c r="AP15" t="n">
-        <v>1</v>
+        <v>1.27</v>
       </c>
       <c r="AQ15" t="n">
         <v>11.73</v>
@@ -6765,7 +6765,7 @@
         <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>49.73</v>
+        <v>49.82</v>
       </c>
       <c r="AZ15" t="n">
         <v>0.27</v>
@@ -6816,10 +6816,10 @@
         <v>1.05</v>
       </c>
       <c r="BP15" t="n">
-        <v>3.27</v>
+        <v>3.5</v>
       </c>
       <c r="BQ15" t="n">
-        <v>4.23</v>
+        <v>4.64</v>
       </c>
       <c r="BR15" t="n">
         <v>100</v>
@@ -6945,7 +6945,7 @@
         <v>1.64</v>
       </c>
       <c r="DG15" t="n">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="DH15" t="n">
         <v>89.28</v>
@@ -6960,7 +6960,7 @@
         <v>4.05</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.18</v>
+        <v>0.27</v>
       </c>
       <c r="DM15" t="n">
         <v>45.32</v>
@@ -6969,7 +6969,7 @@
         <v>0.82</v>
       </c>
       <c r="DO15" t="n">
-        <v>1.45</v>
+        <v>1.59</v>
       </c>
       <c r="DP15" t="n">
         <v>12.59</v>
@@ -6990,7 +6990,7 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>50.5</v>
+        <v>50.54</v>
       </c>
       <c r="DW15" t="n">
         <v>0.18</v>
@@ -8633,13 +8633,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C20" t="n">
         <v>11</v>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E20" t="n">
         <v>0.09</v>
@@ -8723,52 +8723,52 @@
         <v>2.55</v>
       </c>
       <c r="AF20" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.8</v>
+        <v>2.64</v>
       </c>
       <c r="AI20" t="n">
-        <v>98.40000000000001</v>
+        <v>96.73</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AK20" t="n">
-        <v>2.5</v>
+        <v>2.73</v>
       </c>
       <c r="AL20" t="n">
-        <v>3.9</v>
+        <v>3.73</v>
       </c>
       <c r="AM20" t="n">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="AN20" t="n">
-        <v>37.5</v>
+        <v>37.55</v>
       </c>
       <c r="AO20" t="n">
-        <v>0.8</v>
+        <v>0.91</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ20" t="n">
-        <v>12.9</v>
+        <v>12.91</v>
       </c>
       <c r="AR20" t="n">
-        <v>13.7</v>
+        <v>13.36</v>
       </c>
       <c r="AS20" t="n">
-        <v>7.4</v>
+        <v>8.27</v>
       </c>
       <c r="AT20" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AU20" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AV20" t="n">
         <v>0</v>
@@ -8780,82 +8780,82 @@
         <v>0</v>
       </c>
       <c r="AY20" t="n">
-        <v>47.4</v>
+        <v>46.55</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="BA20" t="n">
-        <v>9.1</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="BB20" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BC20" t="n">
-        <v>2.9</v>
+        <v>2.64</v>
       </c>
       <c r="BD20" t="n">
-        <v>19.6</v>
+        <v>20.18</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="BF20" t="n">
-        <v>2.1</v>
+        <v>2.36</v>
       </c>
       <c r="BG20" t="n">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
       <c r="BH20" t="n">
-        <v>8.710000000000001</v>
+        <v>8.68</v>
       </c>
       <c r="BI20" t="n">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
       <c r="BJ20" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BK20" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="BL20" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="BM20" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="BN20" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="BO20" t="n">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="BP20" t="n">
-        <v>3.81</v>
+        <v>3.77</v>
       </c>
       <c r="BQ20" t="n">
-        <v>4.9</v>
+        <v>4.91</v>
       </c>
       <c r="BR20" t="n">
-        <v>85.70999999999999</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BS20" t="n">
-        <v>71.43000000000001</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="BT20" t="n">
-        <v>52.38</v>
+        <v>50</v>
       </c>
       <c r="BU20" t="n">
-        <v>19.05</v>
+        <v>18.18</v>
       </c>
       <c r="BV20" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BW20" t="n">
         <v>0</v>
       </c>
       <c r="BX20" t="n">
-        <v>52.38</v>
+        <v>50</v>
       </c>
       <c r="BY20" t="n">
         <v>1.9</v>
@@ -8864,16 +8864,16 @@
         <v>2.01</v>
       </c>
       <c r="CA20" t="n">
-        <v>3.19</v>
+        <v>3.18</v>
       </c>
       <c r="CB20" t="n">
-        <v>3.27</v>
+        <v>3.26</v>
       </c>
       <c r="CC20" t="n">
-        <v>3.27</v>
+        <v>3.26</v>
       </c>
       <c r="CD20" t="n">
-        <v>3.56</v>
+        <v>3.57</v>
       </c>
       <c r="CE20" t="n">
         <v>1.48</v>
@@ -8882,13 +8882,13 @@
         <v>3.27</v>
       </c>
       <c r="CG20" t="n">
-        <v>2.52</v>
+        <v>2.51</v>
       </c>
       <c r="CH20" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="CI20" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CJ20" t="n">
         <v>2.06</v>
@@ -8897,13 +8897,13 @@
         <v>1.64</v>
       </c>
       <c r="CL20" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="CM20" t="n">
         <v>2.12</v>
       </c>
       <c r="CN20" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CO20" t="n">
         <v>1.43</v>
@@ -8912,7 +8912,7 @@
         <v>2.37</v>
       </c>
       <c r="CQ20" t="n">
-        <v>4.41</v>
+        <v>4.42</v>
       </c>
       <c r="CR20" t="n">
         <v>1.54</v>
@@ -8930,13 +8930,13 @@
         <v>1.8</v>
       </c>
       <c r="CW20" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="CX20" t="n">
         <v>1.69</v>
       </c>
       <c r="CY20" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="CZ20" t="n">
         <v>2.16</v>
@@ -8945,55 +8945,55 @@
         <v>1.71</v>
       </c>
       <c r="DB20" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="DC20" t="n">
-        <v>2.48</v>
+        <v>2.49</v>
       </c>
       <c r="DD20" t="n">
-        <v>4.77</v>
+        <v>4.79</v>
       </c>
       <c r="DE20" t="n">
         <v>0.09</v>
       </c>
       <c r="DF20" t="n">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="DG20" t="n">
-        <v>2.86</v>
+        <v>2.78</v>
       </c>
       <c r="DH20" t="n">
-        <v>107.38</v>
+        <v>106.14</v>
       </c>
       <c r="DI20" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DJ20" t="n">
-        <v>2.62</v>
+        <v>2.73</v>
       </c>
       <c r="DK20" t="n">
-        <v>4.66</v>
+        <v>4.55</v>
       </c>
       <c r="DL20" t="n">
-        <v>0.33</v>
+        <v>0.36</v>
       </c>
       <c r="DM20" t="n">
-        <v>49.62</v>
+        <v>49.1</v>
       </c>
       <c r="DN20" t="n">
-        <v>0.86</v>
+        <v>0.91</v>
       </c>
       <c r="DO20" t="n">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="DP20" t="n">
-        <v>14.52</v>
+        <v>14.46</v>
       </c>
       <c r="DQ20" t="n">
-        <v>12.67</v>
+        <v>12.54</v>
       </c>
       <c r="DR20" t="n">
-        <v>6.9</v>
+        <v>7.36</v>
       </c>
       <c r="DS20" t="n">
         <v>0.14</v>
@@ -9005,28 +9005,28 @@
         <v>0</v>
       </c>
       <c r="DV20" t="n">
-        <v>51.05</v>
+        <v>50.46</v>
       </c>
       <c r="DW20" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DX20" t="n">
-        <v>12.76</v>
+        <v>12.37</v>
       </c>
       <c r="DY20" t="n">
-        <v>8.529999999999999</v>
+        <v>8.32</v>
       </c>
       <c r="DZ20" t="n">
-        <v>4.24</v>
+        <v>4.05</v>
       </c>
       <c r="EA20" t="n">
-        <v>19.19</v>
+        <v>19.5</v>
       </c>
       <c r="EB20" t="n">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="EC20" t="n">
-        <v>2.34</v>
+        <v>2.45</v>
       </c>
     </row>
     <row r="21">

--- a/data/teams/leagues/Averages_Spain_Segunda_División_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Spain_Segunda_División_2025-2026.xlsx
@@ -2185,13 +2185,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C4" t="n">
         <v>12</v>
       </c>
       <c r="D4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E4" t="n">
         <v>0.08</v>
@@ -2275,139 +2275,139 @@
         <v>2.75</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.3</v>
+        <v>2.09</v>
       </c>
       <c r="AI4" t="n">
-        <v>87.40000000000001</v>
+        <v>87.73</v>
       </c>
       <c r="AJ4" t="n">
         <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>2.4</v>
+        <v>2.64</v>
       </c>
       <c r="AL4" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="AN4" t="n">
-        <v>37</v>
+        <v>37.91</v>
       </c>
       <c r="AO4" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ4" t="n">
-        <v>14.1</v>
+        <v>13.82</v>
       </c>
       <c r="AR4" t="n">
-        <v>15.5</v>
+        <v>15.45</v>
       </c>
       <c r="AS4" t="n">
-        <v>9.4</v>
+        <v>9.09</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AX4" t="n">
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>45</v>
+        <v>44.73</v>
       </c>
       <c r="AZ4" t="n">
         <v>0</v>
       </c>
       <c r="BA4" t="n">
-        <v>9.199999999999999</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="BB4" t="n">
-        <v>6.3</v>
+        <v>6.82</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.9</v>
+        <v>2.82</v>
       </c>
       <c r="BD4" t="n">
-        <v>21.5</v>
+        <v>21.55</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="BF4" t="n">
-        <v>2.4</v>
+        <v>2.64</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.09</v>
+        <v>2.13</v>
       </c>
       <c r="BH4" t="n">
-        <v>8.449999999999999</v>
+        <v>8.26</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.09</v>
+        <v>2.13</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.55</v>
+        <v>0.61</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.55</v>
+        <v>0.57</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.59</v>
+        <v>0.57</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="BP4" t="n">
-        <v>3.95</v>
+        <v>3.96</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="BR4" t="n">
-        <v>86.36</v>
+        <v>86.95999999999999</v>
       </c>
       <c r="BS4" t="n">
-        <v>59.09</v>
+        <v>60.87</v>
       </c>
       <c r="BT4" t="n">
-        <v>36.36</v>
+        <v>39.13</v>
       </c>
       <c r="BU4" t="n">
-        <v>13.64</v>
+        <v>13.04</v>
       </c>
       <c r="BV4" t="n">
-        <v>9.09</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BW4" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BX4" t="n">
-        <v>45.45</v>
+        <v>43.48</v>
       </c>
       <c r="BY4" t="n">
         <v>2.26</v>
@@ -2422,10 +2422,10 @@
         <v>3.09</v>
       </c>
       <c r="CC4" t="n">
-        <v>3.71</v>
+        <v>3.76</v>
       </c>
       <c r="CD4" t="n">
-        <v>4.09</v>
+        <v>4.1</v>
       </c>
       <c r="CE4" t="n">
         <v>1.57</v>
@@ -2449,7 +2449,7 @@
         <v>1.71</v>
       </c>
       <c r="CL4" t="n">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="CM4" t="n">
         <v>2.05</v>
@@ -2461,10 +2461,10 @@
         <v>1.52</v>
       </c>
       <c r="CP4" t="n">
-        <v>2.58</v>
+        <v>2.57</v>
       </c>
       <c r="CQ4" t="n">
-        <v>5.02</v>
+        <v>5.04</v>
       </c>
       <c r="CR4" t="n">
         <v>1.59</v>
@@ -2503,82 +2503,82 @@
         <v>2.75</v>
       </c>
       <c r="DD4" t="n">
-        <v>5.58</v>
+        <v>5.57</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="DH4" t="n">
-        <v>92.81999999999999</v>
+        <v>92.73999999999999</v>
       </c>
       <c r="DI4" t="n">
         <v>-0.04</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.63</v>
+        <v>2.74</v>
       </c>
       <c r="DK4" t="n">
-        <v>3.95</v>
+        <v>3.91</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.13</v>
+        <v>0.17</v>
       </c>
       <c r="DM4" t="n">
-        <v>42.82</v>
+        <v>43</v>
       </c>
       <c r="DN4" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="DO4" t="n">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="DP4" t="n">
-        <v>13.87</v>
+        <v>13.74</v>
       </c>
       <c r="DQ4" t="n">
         <v>14.82</v>
       </c>
       <c r="DR4" t="n">
-        <v>9</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>48.04</v>
+        <v>47.78</v>
       </c>
       <c r="DW4" t="n">
         <v>0.04</v>
       </c>
       <c r="DX4" t="n">
-        <v>10.05</v>
+        <v>10.22</v>
       </c>
       <c r="DY4" t="n">
-        <v>7</v>
+        <v>7.22</v>
       </c>
       <c r="DZ4" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="EA4" t="n">
-        <v>24.05</v>
+        <v>23.96</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.59</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="5">
@@ -6618,94 +6618,94 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D15" t="n">
         <v>11</v>
       </c>
       <c r="E15" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="F15" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="G15" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="H15" t="n">
+        <v>89.17</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="K15" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="M15" t="n">
+        <v>45.58</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="P15" t="n">
+        <v>13.58</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>12</v>
+      </c>
+      <c r="R15" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
         <v>2</v>
       </c>
-      <c r="H15" t="n">
-        <v>88.81999999999999</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="J15" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="K15" t="n">
-        <v>3.91</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="M15" t="n">
-        <v>47.27</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="O15" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="P15" t="n">
-        <v>13.45</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>12.09</v>
-      </c>
-      <c r="R15" t="n">
-        <v>7.73</v>
-      </c>
-      <c r="S15" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1.91</v>
-      </c>
       <c r="U15" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="V15" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>51.27</v>
+        <v>51.83</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="Z15" t="n">
-        <v>15.36</v>
+        <v>15.08</v>
       </c>
       <c r="AA15" t="n">
-        <v>9.09</v>
+        <v>8.75</v>
       </c>
       <c r="AB15" t="n">
-        <v>6.27</v>
+        <v>6.33</v>
       </c>
       <c r="AC15" t="n">
-        <v>21.55</v>
+        <v>21.17</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="AF15" t="n">
         <v>0.09</v>
@@ -6789,70 +6789,70 @@
         <v>2</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.64</v>
+        <v>2.65</v>
       </c>
       <c r="BH15" t="n">
-        <v>8.68</v>
+        <v>8.48</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.64</v>
+        <v>2.65</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.73</v>
+        <v>0.78</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.73</v>
+        <v>0.7</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="BP15" t="n">
-        <v>3.5</v>
+        <v>3.52</v>
       </c>
       <c r="BQ15" t="n">
-        <v>4.64</v>
+        <v>4.43</v>
       </c>
       <c r="BR15" t="n">
         <v>100</v>
       </c>
       <c r="BS15" t="n">
-        <v>72.73</v>
+        <v>73.91</v>
       </c>
       <c r="BT15" t="n">
-        <v>54.55</v>
+        <v>56.52</v>
       </c>
       <c r="BU15" t="n">
-        <v>27.27</v>
+        <v>26.09</v>
       </c>
       <c r="BV15" t="n">
-        <v>9.09</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BW15" t="n">
         <v>0</v>
       </c>
       <c r="BX15" t="n">
-        <v>59.09</v>
+        <v>56.52</v>
       </c>
       <c r="BY15" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BZ15" t="n">
         <v>2.27</v>
       </c>
-      <c r="BZ15" t="n">
-        <v>2.29</v>
-      </c>
       <c r="CA15" t="n">
-        <v>3.22</v>
+        <v>3.21</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.36</v>
+        <v>3.35</v>
       </c>
       <c r="CC15" t="n">
         <v>4.06</v>
@@ -6861,43 +6861,43 @@
         <v>4.4</v>
       </c>
       <c r="CE15" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="CF15" t="n">
-        <v>3.09</v>
+        <v>3.11</v>
       </c>
       <c r="CG15" t="n">
-        <v>2.63</v>
+        <v>2.61</v>
       </c>
       <c r="CH15" t="n">
         <v>1.33</v>
       </c>
       <c r="CI15" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CJ15" t="n">
         <v>1.94</v>
       </c>
       <c r="CK15" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="CL15" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="CN15" t="n">
         <v>1.76</v>
       </c>
       <c r="CO15" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CP15" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.87</v>
+        <v>3.93</v>
       </c>
       <c r="CR15" t="n">
         <v>1.48</v>
@@ -6906,16 +6906,16 @@
         <v>3.19</v>
       </c>
       <c r="CT15" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="CU15" t="n">
         <v>1.37</v>
       </c>
       <c r="CV15" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CW15" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="CX15" t="n">
         <v>1.62</v>
@@ -6930,55 +6930,55 @@
         <v>1.78</v>
       </c>
       <c r="DB15" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="DC15" t="n">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="DD15" t="n">
-        <v>4.16</v>
+        <v>4.21</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="DG15" t="n">
-        <v>2.13</v>
+        <v>2.04</v>
       </c>
       <c r="DH15" t="n">
-        <v>89.28</v>
+        <v>89.44</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DJ15" t="n">
-        <v>2.59</v>
+        <v>2.61</v>
       </c>
       <c r="DK15" t="n">
-        <v>4.05</v>
+        <v>3.91</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="DM15" t="n">
-        <v>45.32</v>
+        <v>44.52</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="DO15" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="DP15" t="n">
-        <v>12.59</v>
+        <v>12.7</v>
       </c>
       <c r="DQ15" t="n">
-        <v>12.14</v>
+        <v>12.09</v>
       </c>
       <c r="DR15" t="n">
-        <v>8.09</v>
+        <v>8.35</v>
       </c>
       <c r="DS15" t="n">
         <v>0.13</v>
@@ -6990,28 +6990,28 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>50.54</v>
+        <v>50.87</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DX15" t="n">
-        <v>12.63</v>
+        <v>12.61</v>
       </c>
       <c r="DY15" t="n">
-        <v>7.68</v>
+        <v>7.56</v>
       </c>
       <c r="DZ15" t="n">
-        <v>4.95</v>
+        <v>5.04</v>
       </c>
       <c r="EA15" t="n">
-        <v>22.36</v>
+        <v>22.13</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="EC15" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="16">

--- a/data/teams/leagues/Averages_Spain_Segunda_División_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Spain_Segunda_División_2025-2026.xlsx
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C2" t="n">
         <v>11</v>
       </c>
       <c r="D2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -1469,139 +1469,139 @@
         <v>1.64</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.18</v>
+        <v>2.5</v>
       </c>
       <c r="AI2" t="n">
-        <v>85.91</v>
+        <v>85.92</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AK2" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="AL2" t="n">
-        <v>4.64</v>
+        <v>5</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AN2" t="n">
-        <v>41.45</v>
+        <v>42.33</v>
       </c>
       <c r="AO2" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AP2" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AQ2" t="n">
-        <v>12.64</v>
+        <v>12.42</v>
       </c>
       <c r="AR2" t="n">
-        <v>13.73</v>
+        <v>13.08</v>
       </c>
       <c r="AS2" t="n">
-        <v>8.82</v>
+        <v>8.92</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AX2" t="n">
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>43.91</v>
+        <v>43.42</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="BA2" t="n">
-        <v>12.27</v>
+        <v>12.33</v>
       </c>
       <c r="BB2" t="n">
-        <v>7.55</v>
+        <v>7.75</v>
       </c>
       <c r="BC2" t="n">
-        <v>4.73</v>
+        <v>4.58</v>
       </c>
       <c r="BD2" t="n">
-        <v>23.36</v>
+        <v>24.25</v>
       </c>
       <c r="BE2" t="n">
         <v>1.41</v>
       </c>
       <c r="BF2" t="n">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.77</v>
+        <v>2.7</v>
       </c>
       <c r="BH2" t="n">
-        <v>10.59</v>
+        <v>10.74</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.77</v>
+        <v>2.7</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.77</v>
+        <v>0.74</v>
       </c>
       <c r="BM2" t="n">
         <v>1.09</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.91</v>
+        <v>0.87</v>
       </c>
       <c r="BP2" t="n">
         <v>5</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.55</v>
+        <v>5.7</v>
       </c>
       <c r="BR2" t="n">
-        <v>81.81999999999999</v>
+        <v>82.61</v>
       </c>
       <c r="BS2" t="n">
-        <v>63.64</v>
+        <v>60.87</v>
       </c>
       <c r="BT2" t="n">
-        <v>50</v>
+        <v>47.83</v>
       </c>
       <c r="BU2" t="n">
-        <v>36.36</v>
+        <v>34.78</v>
       </c>
       <c r="BV2" t="n">
-        <v>22.73</v>
+        <v>21.74</v>
       </c>
       <c r="BW2" t="n">
-        <v>9.09</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BX2" t="n">
-        <v>54.55</v>
+        <v>52.17</v>
       </c>
       <c r="BY2" t="n">
         <v>2.15</v>
@@ -1613,22 +1613,22 @@
         <v>3.29</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.49</v>
+        <v>3.48</v>
       </c>
       <c r="CC2" t="n">
-        <v>3.7</v>
+        <v>3.68</v>
       </c>
       <c r="CD2" t="n">
-        <v>4.19</v>
+        <v>4.21</v>
       </c>
       <c r="CE2" t="n">
         <v>1.39</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.85</v>
+        <v>2.84</v>
       </c>
       <c r="CH2" t="n">
         <v>1.4</v>
@@ -1643,7 +1643,7 @@
         <v>1.5</v>
       </c>
       <c r="CL2" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CM2" t="n">
         <v>2.43</v>
@@ -1658,7 +1658,7 @@
         <v>1.95</v>
       </c>
       <c r="CQ2" t="n">
-        <v>3.31</v>
+        <v>3.3</v>
       </c>
       <c r="CR2" t="n">
         <v>1.42</v>
@@ -1673,10 +1673,10 @@
         <v>1.43</v>
       </c>
       <c r="CV2" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="CW2" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CX2" t="n">
         <v>1.52</v>
@@ -1694,52 +1694,52 @@
         <v>1.31</v>
       </c>
       <c r="DC2" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="DD2" t="n">
-        <v>3.44</v>
+        <v>3.47</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="DH2" t="n">
-        <v>88.95999999999999</v>
+        <v>88.83</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
       <c r="DK2" t="n">
-        <v>5.1</v>
+        <v>5.26</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="DM2" t="n">
-        <v>43.22</v>
+        <v>43.61</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.64</v>
+        <v>0.61</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.59</v>
+        <v>2.61</v>
       </c>
       <c r="DP2" t="n">
-        <v>10.96</v>
+        <v>10.91</v>
       </c>
       <c r="DQ2" t="n">
-        <v>10.96</v>
+        <v>10.74</v>
       </c>
       <c r="DR2" t="n">
-        <v>7.55</v>
+        <v>7.65</v>
       </c>
       <c r="DS2" t="n">
         <v>0.09</v>
@@ -1751,28 +1751,28 @@
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>43.78</v>
+        <v>43.53</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DX2" t="n">
-        <v>13.59</v>
+        <v>13.56</v>
       </c>
       <c r="DY2" t="n">
-        <v>9</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="DZ2" t="n">
-        <v>4.59</v>
+        <v>4.52</v>
       </c>
       <c r="EA2" t="n">
-        <v>24.04</v>
+        <v>24.48</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="3">
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C3" t="n">
         <v>11</v>
       </c>
       <c r="D3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E3" t="n">
         <v>0.09</v>
@@ -1875,136 +1875,136 @@
         <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AI3" t="n">
-        <v>88.73</v>
+        <v>88.5</v>
       </c>
       <c r="AJ3" t="n">
         <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>3.36</v>
+        <v>3.17</v>
       </c>
       <c r="AL3" t="n">
-        <v>3.27</v>
+        <v>3.08</v>
       </c>
       <c r="AM3" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="AN3" t="n">
-        <v>40.27</v>
+        <v>39</v>
       </c>
       <c r="AO3" t="n">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ3" t="n">
-        <v>13.45</v>
+        <v>13.92</v>
       </c>
       <c r="AR3" t="n">
-        <v>14.82</v>
+        <v>14.75</v>
       </c>
       <c r="AS3" t="n">
-        <v>7.55</v>
+        <v>7.75</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AX3" t="n">
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>53.09</v>
+        <v>52.92</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="BA3" t="n">
-        <v>13.64</v>
+        <v>13.75</v>
       </c>
       <c r="BB3" t="n">
-        <v>9.09</v>
+        <v>9.25</v>
       </c>
       <c r="BC3" t="n">
-        <v>4.55</v>
+        <v>4.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>21.36</v>
+        <v>21.08</v>
       </c>
       <c r="BE3" t="n">
         <v>1.47</v>
       </c>
       <c r="BF3" t="n">
-        <v>3.27</v>
+        <v>3.08</v>
       </c>
       <c r="BG3" t="n">
-        <v>3.32</v>
+        <v>3.22</v>
       </c>
       <c r="BH3" t="n">
-        <v>9.23</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.32</v>
+        <v>3.22</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.73</v>
+        <v>0.7</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="BL3" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="BM3" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="BN3" t="n">
-        <v>2.09</v>
+        <v>2.04</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="BP3" t="n">
-        <v>3.86</v>
+        <v>3.74</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5.05</v>
+        <v>5.09</v>
       </c>
       <c r="BR3" t="n">
-        <v>95.45</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="BS3" t="n">
-        <v>81.81999999999999</v>
+        <v>78.26000000000001</v>
       </c>
       <c r="BT3" t="n">
-        <v>72.73</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="BU3" t="n">
-        <v>40.91</v>
+        <v>39.13</v>
       </c>
       <c r="BV3" t="n">
-        <v>22.73</v>
+        <v>21.74</v>
       </c>
       <c r="BW3" t="n">
-        <v>9.09</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BX3" t="n">
-        <v>72.73</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="BY3" t="n">
         <v>1.73</v>
@@ -2013,25 +2013,25 @@
         <v>1.81</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.43</v>
+        <v>3.41</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.59</v>
+        <v>3.58</v>
       </c>
       <c r="CC3" t="n">
-        <v>2.51</v>
+        <v>2.56</v>
       </c>
       <c r="CD3" t="n">
-        <v>2.79</v>
+        <v>2.83</v>
       </c>
       <c r="CE3" t="n">
         <v>1.37</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.71</v>
+        <v>2.72</v>
       </c>
       <c r="CG3" t="n">
-        <v>2.92</v>
+        <v>2.91</v>
       </c>
       <c r="CH3" t="n">
         <v>1.43</v>
@@ -2046,31 +2046,31 @@
         <v>1.52</v>
       </c>
       <c r="CL3" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CO3" t="n">
         <v>1.26</v>
       </c>
       <c r="CP3" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.16</v>
+        <v>3.19</v>
       </c>
       <c r="CR3" t="n">
         <v>1.4</v>
       </c>
       <c r="CS3" t="n">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="CT3" t="n">
-        <v>3.07</v>
+        <v>3.06</v>
       </c>
       <c r="CU3" t="n">
         <v>1.44</v>
@@ -2088,7 +2088,7 @@
         <v>1.94</v>
       </c>
       <c r="CZ3" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="DA3" t="n">
         <v>1.87</v>
@@ -2100,82 +2100,82 @@
         <v>1.94</v>
       </c>
       <c r="DD3" t="n">
-        <v>3.32</v>
+        <v>3.33</v>
       </c>
       <c r="DE3" t="n">
         <v>0.04</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="DG3" t="n">
-        <v>2.68</v>
+        <v>2.61</v>
       </c>
       <c r="DH3" t="n">
-        <v>94.68000000000001</v>
+        <v>94.31</v>
       </c>
       <c r="DI3" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ3" t="n">
-        <v>3.09</v>
+        <v>3</v>
       </c>
       <c r="DK3" t="n">
-        <v>5.27</v>
+        <v>5.08</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="DM3" t="n">
-        <v>46.46</v>
+        <v>45.52</v>
       </c>
       <c r="DN3" t="n">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="DO3" t="n">
-        <v>2.36</v>
+        <v>2.26</v>
       </c>
       <c r="DP3" t="n">
-        <v>13.9</v>
+        <v>14.13</v>
       </c>
       <c r="DQ3" t="n">
-        <v>13.19</v>
+        <v>13.22</v>
       </c>
       <c r="DR3" t="n">
-        <v>7.59</v>
+        <v>7.7</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>54.54</v>
+        <v>54.39</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DX3" t="n">
-        <v>15.54</v>
+        <v>15.52</v>
       </c>
       <c r="DY3" t="n">
-        <v>9.77</v>
+        <v>9.82</v>
       </c>
       <c r="DZ3" t="n">
-        <v>5.78</v>
+        <v>5.7</v>
       </c>
       <c r="EA3" t="n">
-        <v>19.59</v>
+        <v>19.52</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.96</v>
+        <v>2.87</v>
       </c>
     </row>
     <row r="4">
@@ -2425,7 +2425,7 @@
         <v>3.76</v>
       </c>
       <c r="CD4" t="n">
-        <v>4.1</v>
+        <v>4.12</v>
       </c>
       <c r="CE4" t="n">
         <v>1.57</v>
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C5" t="n">
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E5" t="n">
         <v>0.27</v>
@@ -2678,139 +2678,139 @@
         <v>3.18</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="AH5" t="n">
-        <v>3.18</v>
+        <v>3.25</v>
       </c>
       <c r="AI5" t="n">
-        <v>91.73</v>
+        <v>93.17</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.55</v>
+        <v>2.67</v>
       </c>
       <c r="AL5" t="n">
-        <v>6.27</v>
+        <v>6.83</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="AN5" t="n">
-        <v>56.09</v>
+        <v>58</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.91</v>
+        <v>1</v>
       </c>
       <c r="AP5" t="n">
-        <v>3.09</v>
+        <v>3.58</v>
       </c>
       <c r="AQ5" t="n">
-        <v>13.18</v>
+        <v>13.25</v>
       </c>
       <c r="AR5" t="n">
-        <v>13.73</v>
+        <v>13.25</v>
       </c>
       <c r="AS5" t="n">
-        <v>5.82</v>
+        <v>5.92</v>
       </c>
       <c r="AT5" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AU5" t="n">
         <v>1</v>
       </c>
-      <c r="AU5" t="n">
+      <c r="AV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>54.33</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>12.92</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>8.83</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>19.75</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>10.26</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BO5" t="n">
         <v>1.09</v>
       </c>
-      <c r="AV5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>53</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>12.82</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>8.640000000000001</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>4.18</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>19.82</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>10</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>1</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>1.14</v>
-      </c>
       <c r="BP5" t="n">
-        <v>4.95</v>
+        <v>5.17</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.05</v>
+        <v>5.09</v>
       </c>
       <c r="BR5" t="n">
-        <v>86.36</v>
+        <v>82.61</v>
       </c>
       <c r="BS5" t="n">
-        <v>63.64</v>
+        <v>60.87</v>
       </c>
       <c r="BT5" t="n">
-        <v>50</v>
+        <v>47.83</v>
       </c>
       <c r="BU5" t="n">
-        <v>40.91</v>
+        <v>39.13</v>
       </c>
       <c r="BV5" t="n">
-        <v>13.64</v>
+        <v>13.04</v>
       </c>
       <c r="BW5" t="n">
-        <v>9.09</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BX5" t="n">
-        <v>54.55</v>
+        <v>52.17</v>
       </c>
       <c r="BY5" t="n">
         <v>1.66</v>
@@ -2819,16 +2819,16 @@
         <v>1.65</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.59</v>
+        <v>3.58</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.88</v>
+        <v>3.86</v>
       </c>
       <c r="CC5" t="n">
-        <v>2.74</v>
+        <v>2.66</v>
       </c>
       <c r="CD5" t="n">
-        <v>2.92</v>
+        <v>2.84</v>
       </c>
       <c r="CE5" t="n">
         <v>1.34</v>
@@ -2837,7 +2837,7 @@
         <v>2.61</v>
       </c>
       <c r="CG5" t="n">
-        <v>3.05</v>
+        <v>3.04</v>
       </c>
       <c r="CH5" t="n">
         <v>1.46</v>
@@ -2855,28 +2855,28 @@
         <v>1.95</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CO5" t="n">
         <v>1.22</v>
       </c>
       <c r="CP5" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CQ5" t="n">
-        <v>2.89</v>
+        <v>2.91</v>
       </c>
       <c r="CR5" t="n">
         <v>1.38</v>
       </c>
       <c r="CS5" t="n">
-        <v>2.77</v>
+        <v>2.79</v>
       </c>
       <c r="CT5" t="n">
-        <v>3.15</v>
+        <v>3.14</v>
       </c>
       <c r="CU5" t="n">
         <v>1.48</v>
@@ -2888,13 +2888,13 @@
         <v>1.76</v>
       </c>
       <c r="CX5" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CY5" t="n">
         <v>1.9</v>
       </c>
       <c r="CZ5" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="DA5" t="n">
         <v>1.91</v>
@@ -2903,52 +2903,52 @@
         <v>1.26</v>
       </c>
       <c r="DC5" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="DD5" t="n">
-        <v>3.07</v>
+        <v>3.09</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DF5" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="DG5" t="n">
-        <v>3.14</v>
+        <v>3.17</v>
       </c>
       <c r="DH5" t="n">
-        <v>98.28</v>
+        <v>98.73999999999999</v>
       </c>
       <c r="DI5" t="n">
         <v>0.09</v>
       </c>
       <c r="DJ5" t="n">
-        <v>3.1</v>
+        <v>3.13</v>
       </c>
       <c r="DK5" t="n">
-        <v>6.27</v>
+        <v>6.56</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="DM5" t="n">
-        <v>57.91</v>
+        <v>58.83</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.91</v>
+        <v>0.96</v>
       </c>
       <c r="DO5" t="n">
-        <v>3.14</v>
+        <v>3.39</v>
       </c>
       <c r="DP5" t="n">
-        <v>13.68</v>
+        <v>13.69</v>
       </c>
       <c r="DQ5" t="n">
-        <v>13.91</v>
+        <v>13.65</v>
       </c>
       <c r="DR5" t="n">
-        <v>5.41</v>
+        <v>5.48</v>
       </c>
       <c r="DS5" t="n">
         <v>0.22</v>
@@ -2960,19 +2960,19 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>54.78</v>
+        <v>55.39</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DX5" t="n">
-        <v>14.5</v>
+        <v>14.48</v>
       </c>
       <c r="DY5" t="n">
-        <v>9.539999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="DZ5" t="n">
-        <v>4.95</v>
+        <v>4.87</v>
       </c>
       <c r="EA5" t="n">
         <v>19</v>
@@ -2981,7 +2981,7 @@
         <v>1.68</v>
       </c>
       <c r="EC5" t="n">
-        <v>2.77</v>
+        <v>2.83</v>
       </c>
     </row>
     <row r="6">
@@ -3797,94 +3797,94 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D8" t="n">
         <v>11</v>
       </c>
       <c r="E8" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="F8" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="G8" t="n">
-        <v>3.09</v>
+        <v>3.08</v>
       </c>
       <c r="H8" t="n">
-        <v>91.55</v>
+        <v>93.92</v>
       </c>
       <c r="I8" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="J8" t="n">
-        <v>3.36</v>
+        <v>3.42</v>
       </c>
       <c r="K8" t="n">
-        <v>5.73</v>
+        <v>5.92</v>
       </c>
       <c r="L8" t="n">
-        <v>0.27</v>
+        <v>0.42</v>
       </c>
       <c r="M8" t="n">
-        <v>47.45</v>
+        <v>48.42</v>
       </c>
       <c r="N8" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="O8" t="n">
-        <v>2.64</v>
+        <v>2.83</v>
       </c>
       <c r="P8" t="n">
-        <v>13.45</v>
+        <v>13.83</v>
       </c>
       <c r="Q8" t="n">
-        <v>13</v>
+        <v>12.67</v>
       </c>
       <c r="R8" t="n">
-        <v>7.45</v>
+        <v>7.5</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="T8" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="U8" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="V8" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>48</v>
+        <v>49.08</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="Z8" t="n">
-        <v>11.55</v>
+        <v>12</v>
       </c>
       <c r="AA8" t="n">
-        <v>7.91</v>
+        <v>8.25</v>
       </c>
       <c r="AB8" t="n">
-        <v>3.64</v>
+        <v>3.75</v>
       </c>
       <c r="AC8" t="n">
-        <v>19.09</v>
+        <v>20.42</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="AE8" t="n">
-        <v>3.36</v>
+        <v>3.25</v>
       </c>
       <c r="AF8" t="n">
         <v>0.09</v>
@@ -3968,70 +3968,70 @@
         <v>2.45</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.23</v>
+        <v>2.26</v>
       </c>
       <c r="BH8" t="n">
-        <v>11.14</v>
+        <v>11.09</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.23</v>
+        <v>2.26</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.36</v>
+        <v>0.39</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.68</v>
+        <v>0.7</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="BO8" t="n">
         <v>0.91</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.86</v>
+        <v>4.91</v>
       </c>
       <c r="BQ8" t="n">
-        <v>6.27</v>
+        <v>6.17</v>
       </c>
       <c r="BR8" t="n">
-        <v>81.81999999999999</v>
+        <v>82.61</v>
       </c>
       <c r="BS8" t="n">
-        <v>54.55</v>
+        <v>56.52</v>
       </c>
       <c r="BT8" t="n">
-        <v>45.45</v>
+        <v>47.83</v>
       </c>
       <c r="BU8" t="n">
-        <v>22.73</v>
+        <v>21.74</v>
       </c>
       <c r="BV8" t="n">
-        <v>13.64</v>
+        <v>13.04</v>
       </c>
       <c r="BW8" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BX8" t="n">
-        <v>45.45</v>
+        <v>47.83</v>
       </c>
       <c r="BY8" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="BZ8" t="n">
-        <v>2.57</v>
+        <v>2.58</v>
       </c>
       <c r="CA8" t="n">
         <v>3.13</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="CC8" t="n">
         <v>3.82</v>
@@ -4043,10 +4043,10 @@
         <v>1.47</v>
       </c>
       <c r="CF8" t="n">
-        <v>3.14</v>
+        <v>3.15</v>
       </c>
       <c r="CG8" t="n">
-        <v>2.56</v>
+        <v>2.55</v>
       </c>
       <c r="CH8" t="n">
         <v>1.32</v>
@@ -4058,7 +4058,7 @@
         <v>1.96</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CL8" t="n">
         <v>2.17</v>
@@ -4076,22 +4076,22 @@
         <v>2.25</v>
       </c>
       <c r="CQ8" t="n">
-        <v>4.12</v>
+        <v>4.13</v>
       </c>
       <c r="CR8" t="n">
         <v>1.5</v>
       </c>
       <c r="CS8" t="n">
-        <v>3.17</v>
+        <v>3.19</v>
       </c>
       <c r="CT8" t="n">
-        <v>2.71</v>
+        <v>2.7</v>
       </c>
       <c r="CU8" t="n">
         <v>1.37</v>
       </c>
       <c r="CV8" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CW8" t="n">
         <v>1.98</v>
@@ -4112,52 +4112,52 @@
         <v>1.41</v>
       </c>
       <c r="DC8" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="DD8" t="n">
-        <v>4.29</v>
+        <v>4.3</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DF8" t="n">
         <v>2.09</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="DH8" t="n">
-        <v>89.14</v>
+        <v>90.48</v>
       </c>
       <c r="DI8" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="DK8" t="n">
-        <v>5</v>
+        <v>5.13</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.18</v>
+        <v>0.26</v>
       </c>
       <c r="DM8" t="n">
-        <v>39.64</v>
+        <v>40.48</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.28</v>
+        <v>2.39</v>
       </c>
       <c r="DP8" t="n">
-        <v>14.27</v>
+        <v>14.43</v>
       </c>
       <c r="DQ8" t="n">
-        <v>12.46</v>
+        <v>12.31</v>
       </c>
       <c r="DR8" t="n">
-        <v>8.720000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="DS8" t="n">
         <v>0.04</v>
@@ -4169,28 +4169,28 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>45.04</v>
+        <v>45.74</v>
       </c>
       <c r="DW8" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="DX8" t="n">
-        <v>10.05</v>
+        <v>10.35</v>
       </c>
       <c r="DY8" t="n">
-        <v>6.82</v>
+        <v>7.04</v>
       </c>
       <c r="DZ8" t="n">
-        <v>3.23</v>
+        <v>3.31</v>
       </c>
       <c r="EA8" t="n">
-        <v>19.18</v>
+        <v>19.87</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="EC8" t="n">
-        <v>2.9</v>
+        <v>2.87</v>
       </c>
     </row>
     <row r="9">
@@ -4200,13 +4200,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C9" t="n">
         <v>11</v>
       </c>
       <c r="D9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E9" t="n">
         <v>0.09</v>
@@ -4290,52 +4290,52 @@
         <v>2.64</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.91</v>
+        <v>3</v>
       </c>
       <c r="AI9" t="n">
-        <v>93.81999999999999</v>
+        <v>91.58</v>
       </c>
       <c r="AJ9" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="AK9" t="n">
-        <v>3.09</v>
+        <v>3.08</v>
       </c>
       <c r="AL9" t="n">
-        <v>4.91</v>
+        <v>4.92</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AN9" t="n">
-        <v>42.45</v>
+        <v>40.58</v>
       </c>
       <c r="AO9" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AP9" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ9" t="n">
-        <v>15.45</v>
+        <v>15.83</v>
       </c>
       <c r="AR9" t="n">
-        <v>15</v>
+        <v>14.75</v>
       </c>
       <c r="AS9" t="n">
-        <v>7</v>
+        <v>7.42</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AV9" t="n">
         <v>0</v>
@@ -4347,73 +4347,73 @@
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>54.82</v>
+        <v>53.67</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="BA9" t="n">
-        <v>13.27</v>
+        <v>13.33</v>
       </c>
       <c r="BB9" t="n">
-        <v>8.640000000000001</v>
+        <v>8.42</v>
       </c>
       <c r="BC9" t="n">
-        <v>4.64</v>
+        <v>4.92</v>
       </c>
       <c r="BD9" t="n">
-        <v>22.36</v>
+        <v>21.42</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="BF9" t="n">
-        <v>2.91</v>
+        <v>2.92</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.36</v>
+        <v>2.39</v>
       </c>
       <c r="BH9" t="n">
-        <v>9.859999999999999</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.36</v>
+        <v>2.39</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.45</v>
+        <v>0.52</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.64</v>
+        <v>0.61</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.77</v>
+        <v>0.74</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.95</v>
+        <v>1.04</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.77</v>
+        <v>4.65</v>
       </c>
       <c r="BQ9" t="n">
-        <v>5.09</v>
+        <v>5.13</v>
       </c>
       <c r="BR9" t="n">
-        <v>86.36</v>
+        <v>86.95999999999999</v>
       </c>
       <c r="BS9" t="n">
-        <v>72.73</v>
+        <v>73.91</v>
       </c>
       <c r="BT9" t="n">
-        <v>50</v>
+        <v>52.17</v>
       </c>
       <c r="BU9" t="n">
-        <v>27.27</v>
+        <v>26.09</v>
       </c>
       <c r="BV9" t="n">
         <v>0</v>
@@ -4422,7 +4422,7 @@
         <v>0</v>
       </c>
       <c r="BX9" t="n">
-        <v>63.64</v>
+        <v>65.22</v>
       </c>
       <c r="BY9" t="n">
         <v>2.1</v>
@@ -4437,16 +4437,16 @@
         <v>3.37</v>
       </c>
       <c r="CC9" t="n">
-        <v>2.95</v>
+        <v>3.05</v>
       </c>
       <c r="CD9" t="n">
-        <v>3.13</v>
+        <v>3.22</v>
       </c>
       <c r="CE9" t="n">
         <v>1.41</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="CG9" t="n">
         <v>2.84</v>
@@ -4455,25 +4455,25 @@
         <v>1.39</v>
       </c>
       <c r="CI9" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CJ9" t="n">
         <v>1.77</v>
       </c>
       <c r="CK9" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="CL9" t="n">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="CN9" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CO9" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="CP9" t="n">
         <v>2</v>
@@ -4485,10 +4485,10 @@
         <v>1.43</v>
       </c>
       <c r="CS9" t="n">
-        <v>3.05</v>
+        <v>3.06</v>
       </c>
       <c r="CT9" t="n">
-        <v>2.94</v>
+        <v>2.93</v>
       </c>
       <c r="CU9" t="n">
         <v>1.41</v>
@@ -4497,19 +4497,19 @@
         <v>2.1</v>
       </c>
       <c r="CW9" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CX9" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="CY9" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="CZ9" t="n">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="DA9" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="DB9" t="n">
         <v>1.32</v>
@@ -4521,79 +4521,79 @@
         <v>3.6</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.18</v>
+        <v>0.22</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="DG9" t="n">
-        <v>2.86</v>
+        <v>2.91</v>
       </c>
       <c r="DH9" t="n">
-        <v>98.86</v>
+        <v>97.48</v>
       </c>
       <c r="DI9" t="n">
         <v>0</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.95</v>
+        <v>2.96</v>
       </c>
       <c r="DK9" t="n">
-        <v>5.18</v>
+        <v>5.17</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="DM9" t="n">
-        <v>49.4</v>
+        <v>48.13</v>
       </c>
       <c r="DN9" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="DO9" t="n">
-        <v>2.32</v>
+        <v>2.26</v>
       </c>
       <c r="DP9" t="n">
-        <v>15.59</v>
+        <v>15.78</v>
       </c>
       <c r="DQ9" t="n">
-        <v>14.78</v>
+        <v>14.65</v>
       </c>
       <c r="DR9" t="n">
-        <v>6</v>
+        <v>6.26</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>57</v>
+        <v>56.31</v>
       </c>
       <c r="DW9" t="n">
         <v>0.13</v>
       </c>
       <c r="DX9" t="n">
-        <v>14.81</v>
+        <v>14.78</v>
       </c>
       <c r="DY9" t="n">
-        <v>10</v>
+        <v>9.83</v>
       </c>
       <c r="DZ9" t="n">
-        <v>4.82</v>
+        <v>4.96</v>
       </c>
       <c r="EA9" t="n">
-        <v>22.04</v>
+        <v>21.57</v>
       </c>
       <c r="EB9" t="n">
         <v>1.63</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.78</v>
+        <v>2.79</v>
       </c>
     </row>
     <row r="10">
@@ -4603,94 +4603,94 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D10" t="n">
         <v>12</v>
       </c>
       <c r="E10" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="F10" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="G10" t="n">
-        <v>2.5</v>
+        <v>2.64</v>
       </c>
       <c r="H10" t="n">
-        <v>95.59999999999999</v>
+        <v>95.09</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="K10" t="n">
-        <v>4.4</v>
+        <v>4.64</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="M10" t="n">
-        <v>44.4</v>
+        <v>45</v>
       </c>
       <c r="N10" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="O10" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="P10" t="n">
-        <v>11.7</v>
+        <v>11.82</v>
       </c>
       <c r="Q10" t="n">
-        <v>13.6</v>
+        <v>13.55</v>
       </c>
       <c r="R10" t="n">
-        <v>7.3</v>
+        <v>7.27</v>
       </c>
       <c r="S10" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="T10" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="V10" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>54.3</v>
+        <v>53.91</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="Z10" t="n">
-        <v>13.2</v>
+        <v>12.82</v>
       </c>
       <c r="AA10" t="n">
-        <v>8.300000000000001</v>
+        <v>8.27</v>
       </c>
       <c r="AB10" t="n">
-        <v>4.9</v>
+        <v>4.55</v>
       </c>
       <c r="AC10" t="n">
-        <v>19.2</v>
+        <v>18.73</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="AF10" t="n">
         <v>0</v>
@@ -4774,70 +4774,70 @@
         <v>2.67</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.82</v>
+        <v>2.74</v>
       </c>
       <c r="BH10" t="n">
-        <v>8.640000000000001</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.82</v>
+        <v>2.74</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.73</v>
+        <v>0.7</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.59</v>
+        <v>0.57</v>
       </c>
       <c r="BM10" t="n">
         <v>1</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="BP10" t="n">
-        <v>4.27</v>
+        <v>4.35</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.36</v>
+        <v>4.43</v>
       </c>
       <c r="BR10" t="n">
-        <v>95.45</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="BS10" t="n">
-        <v>86.36</v>
+        <v>82.61</v>
       </c>
       <c r="BT10" t="n">
-        <v>59.09</v>
+        <v>56.52</v>
       </c>
       <c r="BU10" t="n">
-        <v>31.82</v>
+        <v>30.43</v>
       </c>
       <c r="BV10" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BW10" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BX10" t="n">
-        <v>59.09</v>
+        <v>56.52</v>
       </c>
       <c r="BY10" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="BZ10" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CA10" t="n">
         <v>3.29</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.43</v>
+        <v>3.44</v>
       </c>
       <c r="CC10" t="n">
         <v>2.86</v>
@@ -4849,28 +4849,28 @@
         <v>1.41</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="CG10" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="CH10" t="n">
         <v>1.38</v>
       </c>
       <c r="CI10" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="CJ10" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CK10" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CL10" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="CN10" t="n">
         <v>1.74</v>
@@ -4879,10 +4879,10 @@
         <v>1.31</v>
       </c>
       <c r="CP10" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="CQ10" t="n">
-        <v>3.48</v>
+        <v>3.45</v>
       </c>
       <c r="CR10" t="n">
         <v>1.44</v>
@@ -4897,106 +4897,106 @@
         <v>1.39</v>
       </c>
       <c r="CV10" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="CW10" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CX10" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CY10" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="CZ10" t="n">
-        <v>2.21</v>
+        <v>2.23</v>
       </c>
       <c r="DA10" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="DB10" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="DC10" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="DD10" t="n">
-        <v>3.66</v>
+        <v>3.63</v>
       </c>
       <c r="DE10" t="n">
         <v>0.09</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.68</v>
+        <v>1.74</v>
       </c>
       <c r="DG10" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="DH10" t="n">
-        <v>84.5</v>
+        <v>84.73999999999999</v>
       </c>
       <c r="DI10" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.59</v>
+        <v>2.61</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.45</v>
+        <v>4.57</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.36</v>
+        <v>0.39</v>
       </c>
       <c r="DM10" t="n">
-        <v>39.27</v>
+        <v>39.78</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.86</v>
+        <v>0.82</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="DP10" t="n">
-        <v>11.73</v>
+        <v>11.78</v>
       </c>
       <c r="DQ10" t="n">
         <v>13.04</v>
       </c>
       <c r="DR10" t="n">
-        <v>7.91</v>
+        <v>7.87</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>50.41</v>
+        <v>50.39</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DX10" t="n">
-        <v>12.82</v>
+        <v>12.65</v>
       </c>
       <c r="DY10" t="n">
         <v>8.039999999999999</v>
       </c>
       <c r="DZ10" t="n">
-        <v>4.77</v>
+        <v>4.61</v>
       </c>
       <c r="EA10" t="n">
-        <v>16.91</v>
+        <v>16.78</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="EC10" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
     </row>
     <row r="11">
@@ -5006,10 +5006,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D11" t="n">
         <v>12</v>
@@ -5018,49 +5018,49 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="G11" t="n">
-        <v>3.7</v>
+        <v>3.36</v>
       </c>
       <c r="H11" t="n">
-        <v>109.4</v>
+        <v>110</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="J11" t="n">
         <v>2</v>
       </c>
       <c r="K11" t="n">
-        <v>6</v>
+        <v>5.73</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="M11" t="n">
-        <v>52.6</v>
+        <v>54.36</v>
       </c>
       <c r="N11" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="O11" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="P11" t="n">
-        <v>13.2</v>
+        <v>13.64</v>
       </c>
       <c r="Q11" t="n">
-        <v>14.4</v>
+        <v>14.55</v>
       </c>
       <c r="R11" t="n">
-        <v>7.8</v>
+        <v>7.64</v>
       </c>
       <c r="S11" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="T11" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
@@ -5072,28 +5072,28 @@
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>59.6</v>
+        <v>60.82</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="Z11" t="n">
-        <v>13.9</v>
+        <v>14.36</v>
       </c>
       <c r="AA11" t="n">
-        <v>9</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="AB11" t="n">
-        <v>4.9</v>
+        <v>4.91</v>
       </c>
       <c r="AC11" t="n">
-        <v>19.7</v>
+        <v>19.36</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AF11" t="n">
         <v>0.17</v>
@@ -5177,64 +5177,64 @@
         <v>2.83</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="BH11" t="n">
-        <v>9.73</v>
+        <v>9.48</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.36</v>
+        <v>0.39</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.36</v>
+        <v>0.39</v>
       </c>
       <c r="BL11" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.77</v>
+        <v>0.74</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="BO11" t="n">
-        <v>0.73</v>
+        <v>0.78</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.41</v>
+        <v>4.39</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.27</v>
+        <v>5.04</v>
       </c>
       <c r="BR11" t="n">
-        <v>90.91</v>
+        <v>91.3</v>
       </c>
       <c r="BS11" t="n">
-        <v>77.27</v>
+        <v>78.26000000000001</v>
       </c>
       <c r="BT11" t="n">
-        <v>54.55</v>
+        <v>52.17</v>
       </c>
       <c r="BU11" t="n">
-        <v>22.73</v>
+        <v>21.74</v>
       </c>
       <c r="BV11" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BW11" t="n">
         <v>0</v>
       </c>
       <c r="BX11" t="n">
-        <v>68.18000000000001</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="BY11" t="n">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="BZ11" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="CA11" t="n">
         <v>3.31</v>
@@ -5252,40 +5252,40 @@
         <v>1.42</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.91</v>
+        <v>2.92</v>
       </c>
       <c r="CG11" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="CH11" t="n">
         <v>1.37</v>
       </c>
       <c r="CI11" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CJ11" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CK11" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CL11" t="n">
         <v>2.14</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="CN11" t="n">
         <v>1.73</v>
       </c>
       <c r="CO11" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="CP11" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="CQ11" t="n">
-        <v>3.52</v>
+        <v>3.54</v>
       </c>
       <c r="CR11" t="n">
         <v>1.44</v>
@@ -5306,13 +5306,13 @@
         <v>1.85</v>
       </c>
       <c r="CX11" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CY11" t="n">
         <v>2.06</v>
       </c>
       <c r="CZ11" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="DA11" t="n">
         <v>1.76</v>
@@ -5324,49 +5324,49 @@
         <v>2.08</v>
       </c>
       <c r="DD11" t="n">
-        <v>3.69</v>
+        <v>3.7</v>
       </c>
       <c r="DE11" t="n">
         <v>0.09</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="DG11" t="n">
-        <v>3.14</v>
+        <v>3</v>
       </c>
       <c r="DH11" t="n">
-        <v>103.18</v>
+        <v>103.74</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.55</v>
+        <v>2.52</v>
       </c>
       <c r="DK11" t="n">
-        <v>5.05</v>
+        <v>4.96</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.18</v>
+        <v>0.22</v>
       </c>
       <c r="DM11" t="n">
-        <v>45.68</v>
+        <v>46.83</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="DO11" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="DP11" t="n">
-        <v>13.5</v>
+        <v>13.7</v>
       </c>
       <c r="DQ11" t="n">
-        <v>15.14</v>
+        <v>15.18</v>
       </c>
       <c r="DR11" t="n">
-        <v>7.46</v>
+        <v>7.39</v>
       </c>
       <c r="DS11" t="n">
         <v>0.09</v>
@@ -5378,28 +5378,28 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>58.68</v>
+        <v>59.31</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DX11" t="n">
-        <v>13.77</v>
+        <v>14</v>
       </c>
       <c r="DY11" t="n">
-        <v>9.140000000000001</v>
+        <v>9.35</v>
       </c>
       <c r="DZ11" t="n">
-        <v>4.64</v>
+        <v>4.65</v>
       </c>
       <c r="EA11" t="n">
-        <v>18.54</v>
+        <v>18.43</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="12">
@@ -5409,13 +5409,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C12" t="n">
         <v>12</v>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E12" t="n">
         <v>0.25</v>
@@ -5502,136 +5502,136 @@
         <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AH12" t="n">
         <v>1</v>
       </c>
       <c r="AI12" t="n">
-        <v>89.8</v>
+        <v>88.91</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AK12" t="n">
-        <v>3.1</v>
+        <v>2.82</v>
       </c>
       <c r="AL12" t="n">
-        <v>2.8</v>
+        <v>2.73</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AN12" t="n">
-        <v>39.3</v>
+        <v>38.45</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AQ12" t="n">
-        <v>14.2</v>
+        <v>13.73</v>
       </c>
       <c r="AR12" t="n">
-        <v>14.4</v>
+        <v>14.64</v>
       </c>
       <c r="AS12" t="n">
-        <v>8.1</v>
+        <v>8.09</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AU12" t="n">
-        <v>1</v>
+        <v>1.09</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="AX12" t="n">
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>46.6</v>
+        <v>45.91</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="BA12" t="n">
-        <v>10.5</v>
+        <v>10.73</v>
       </c>
       <c r="BB12" t="n">
-        <v>7.1</v>
+        <v>7.45</v>
       </c>
       <c r="BC12" t="n">
-        <v>3.4</v>
+        <v>3.27</v>
       </c>
       <c r="BD12" t="n">
-        <v>21.5</v>
+        <v>20.55</v>
       </c>
       <c r="BE12" t="n">
         <v>1.19</v>
       </c>
       <c r="BF12" t="n">
-        <v>2.8</v>
+        <v>2.55</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.23</v>
+        <v>9.26</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.64</v>
+        <v>0.61</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.45</v>
+        <v>0.48</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="BO12" t="n">
         <v>1.09</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.14</v>
+        <v>4.22</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.09</v>
+        <v>5.04</v>
       </c>
       <c r="BR12" t="n">
-        <v>77.27</v>
+        <v>78.26000000000001</v>
       </c>
       <c r="BS12" t="n">
-        <v>63.64</v>
+        <v>65.22</v>
       </c>
       <c r="BT12" t="n">
-        <v>40.91</v>
+        <v>43.48</v>
       </c>
       <c r="BU12" t="n">
-        <v>27.27</v>
+        <v>26.09</v>
       </c>
       <c r="BV12" t="n">
-        <v>9.09</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BW12" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BX12" t="n">
-        <v>54.55</v>
+        <v>56.52</v>
       </c>
       <c r="BY12" t="n">
         <v>2.16</v>
@@ -5640,25 +5640,25 @@
         <v>2.35</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.2</v>
+        <v>3.19</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.27</v>
+        <v>3.26</v>
       </c>
       <c r="CC12" t="n">
-        <v>3.52</v>
+        <v>3.45</v>
       </c>
       <c r="CD12" t="n">
-        <v>3.88</v>
+        <v>3.8</v>
       </c>
       <c r="CE12" t="n">
         <v>1.45</v>
       </c>
       <c r="CF12" t="n">
-        <v>3.11</v>
+        <v>3.12</v>
       </c>
       <c r="CG12" t="n">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="CH12" t="n">
         <v>1.33</v>
@@ -5673,7 +5673,7 @@
         <v>1.58</v>
       </c>
       <c r="CL12" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="CM12" t="n">
         <v>2.23</v>
@@ -5688,16 +5688,16 @@
         <v>2.19</v>
       </c>
       <c r="CQ12" t="n">
-        <v>3.91</v>
+        <v>3.92</v>
       </c>
       <c r="CR12" t="n">
         <v>1.49</v>
       </c>
       <c r="CS12" t="n">
-        <v>3.24</v>
+        <v>3.25</v>
       </c>
       <c r="CT12" t="n">
-        <v>2.73</v>
+        <v>2.72</v>
       </c>
       <c r="CU12" t="n">
         <v>1.36</v>
@@ -5712,10 +5712,10 @@
         <v>1.65</v>
       </c>
       <c r="CY12" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="CZ12" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="DA12" t="n">
         <v>1.76</v>
@@ -5724,85 +5724,85 @@
         <v>1.41</v>
       </c>
       <c r="DC12" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="DD12" t="n">
-        <v>4.23</v>
+        <v>4.24</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.68</v>
+        <v>1.61</v>
       </c>
       <c r="DG12" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="DH12" t="n">
+        <v>90.73999999999999</v>
+      </c>
+      <c r="DI12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ12" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="DK12" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="DL12" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="DM12" t="n">
+        <v>41.96</v>
+      </c>
+      <c r="DN12" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="DO12" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="DP12" t="n">
+        <v>12.79</v>
+      </c>
+      <c r="DQ12" t="n">
+        <v>14.87</v>
+      </c>
+      <c r="DR12" t="n">
+        <v>7.69</v>
+      </c>
+      <c r="DS12" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="DT12" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="DU12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV12" t="n">
+        <v>49.48</v>
+      </c>
+      <c r="DW12" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="DX12" t="n">
+        <v>12.87</v>
+      </c>
+      <c r="DY12" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="DZ12" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="EA12" t="n">
+        <v>22.39</v>
+      </c>
+      <c r="EB12" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="EC12" t="n">
         <v>2.13</v>
-      </c>
-      <c r="DH12" t="n">
-        <v>91.23</v>
-      </c>
-      <c r="DI12" t="n">
-        <v>0</v>
-      </c>
-      <c r="DJ12" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="DK12" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="DL12" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="DM12" t="n">
-        <v>42.5</v>
-      </c>
-      <c r="DN12" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="DO12" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="DP12" t="n">
-        <v>12.96</v>
-      </c>
-      <c r="DQ12" t="n">
-        <v>14.77</v>
-      </c>
-      <c r="DR12" t="n">
-        <v>7.68</v>
-      </c>
-      <c r="DS12" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="DT12" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="DU12" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV12" t="n">
-        <v>49.95</v>
-      </c>
-      <c r="DW12" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="DX12" t="n">
-        <v>12.86</v>
-      </c>
-      <c r="DY12" t="n">
-        <v>9.23</v>
-      </c>
-      <c r="DZ12" t="n">
-        <v>3.63</v>
-      </c>
-      <c r="EA12" t="n">
-        <v>22.91</v>
-      </c>
-      <c r="EB12" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="EC12" t="n">
-        <v>2.23</v>
       </c>
     </row>
     <row r="13">
@@ -5812,94 +5812,94 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D13" t="n">
         <v>12</v>
       </c>
       <c r="E13" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="F13" t="n">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="G13" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="H13" t="n">
-        <v>85.59999999999999</v>
+        <v>85.64</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>3.2</v>
+        <v>3.09</v>
       </c>
       <c r="K13" t="n">
-        <v>5.4</v>
+        <v>5.45</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="M13" t="n">
-        <v>42.5</v>
+        <v>41.91</v>
       </c>
       <c r="N13" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="O13" t="n">
         <v>3</v>
       </c>
       <c r="P13" t="n">
-        <v>14.2</v>
+        <v>13.91</v>
       </c>
       <c r="Q13" t="n">
-        <v>14.9</v>
+        <v>15.45</v>
       </c>
       <c r="R13" t="n">
-        <v>7.8</v>
+        <v>7.64</v>
       </c>
       <c r="S13" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="T13" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="V13" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>50.8</v>
+        <v>51.27</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="Z13" t="n">
-        <v>12.2</v>
+        <v>12.91</v>
       </c>
       <c r="AA13" t="n">
-        <v>7.7</v>
+        <v>8.18</v>
       </c>
       <c r="AB13" t="n">
-        <v>4.5</v>
+        <v>4.73</v>
       </c>
       <c r="AC13" t="n">
-        <v>22.9</v>
+        <v>23.09</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="AE13" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="AF13" t="n">
         <v>0</v>
@@ -5986,67 +5986,67 @@
         <v>2.09</v>
       </c>
       <c r="BH13" t="n">
-        <v>9.359999999999999</v>
+        <v>9.35</v>
       </c>
       <c r="BI13" t="n">
         <v>2.09</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.45</v>
+        <v>0.52</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.73</v>
+        <v>0.7</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="BO13" t="n">
-        <v>0.91</v>
+        <v>0.87</v>
       </c>
       <c r="BP13" t="n">
-        <v>4.32</v>
+        <v>4.3</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4.59</v>
+        <v>4.61</v>
       </c>
       <c r="BR13" t="n">
-        <v>81.81999999999999</v>
+        <v>82.61</v>
       </c>
       <c r="BS13" t="n">
-        <v>68.18000000000001</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="BT13" t="n">
-        <v>40.91</v>
+        <v>39.13</v>
       </c>
       <c r="BU13" t="n">
-        <v>13.64</v>
+        <v>13.04</v>
       </c>
       <c r="BV13" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BW13" t="n">
         <v>0</v>
       </c>
       <c r="BX13" t="n">
-        <v>45.45</v>
+        <v>43.48</v>
       </c>
       <c r="BY13" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="BZ13" t="n">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.07</v>
+        <v>3.08</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.2</v>
+        <v>3.21</v>
       </c>
       <c r="CC13" t="n">
         <v>3.25</v>
@@ -6058,7 +6058,7 @@
         <v>1.48</v>
       </c>
       <c r="CF13" t="n">
-        <v>3.23</v>
+        <v>3.21</v>
       </c>
       <c r="CG13" t="n">
         <v>2.56</v>
@@ -6076,43 +6076,43 @@
         <v>1.59</v>
       </c>
       <c r="CL13" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="CM13" t="n">
         <v>2.21</v>
       </c>
       <c r="CN13" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CO13" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CP13" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="CQ13" t="n">
-        <v>4.19</v>
+        <v>4.15</v>
       </c>
       <c r="CR13" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CS13" t="n">
-        <v>3.2</v>
+        <v>3.22</v>
       </c>
       <c r="CT13" t="n">
         <v>2.64</v>
       </c>
       <c r="CU13" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CV13" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CW13" t="n">
         <v>2.01</v>
       </c>
       <c r="CX13" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CY13" t="n">
         <v>2.09</v>
@@ -6130,82 +6130,82 @@
         <v>2.39</v>
       </c>
       <c r="DD13" t="n">
-        <v>4.53</v>
+        <v>4.52</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF13" t="n">
-        <v>2.18</v>
+        <v>2.13</v>
       </c>
       <c r="DG13" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="DH13" t="n">
-        <v>84.91</v>
+        <v>84.95999999999999</v>
       </c>
       <c r="DI13" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ13" t="n">
-        <v>3.27</v>
+        <v>3.22</v>
       </c>
       <c r="DK13" t="n">
-        <v>4.54</v>
+        <v>4.6</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.32</v>
+        <v>0.35</v>
       </c>
       <c r="DM13" t="n">
-        <v>37.77</v>
+        <v>37.69</v>
       </c>
       <c r="DN13" t="n">
         <v>1</v>
       </c>
       <c r="DO13" t="n">
-        <v>2.27</v>
+        <v>2.31</v>
       </c>
       <c r="DP13" t="n">
-        <v>12.91</v>
+        <v>12.82</v>
       </c>
       <c r="DQ13" t="n">
-        <v>14.45</v>
+        <v>14.74</v>
       </c>
       <c r="DR13" t="n">
-        <v>8.140000000000001</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>50.41</v>
+        <v>50.65</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DX13" t="n">
-        <v>10.96</v>
+        <v>11.35</v>
       </c>
       <c r="DY13" t="n">
-        <v>6.77</v>
+        <v>7.04</v>
       </c>
       <c r="DZ13" t="n">
-        <v>4.18</v>
+        <v>4.31</v>
       </c>
       <c r="EA13" t="n">
-        <v>21.41</v>
+        <v>21.57</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="EC13" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
     </row>
     <row r="14">
@@ -6215,13 +6215,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C14" t="n">
         <v>11</v>
       </c>
       <c r="D14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E14" t="n">
         <v>0.09</v>
@@ -6305,139 +6305,139 @@
         <v>3.55</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AI14" t="n">
-        <v>81.45</v>
+        <v>80.67</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AK14" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>28.67</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>14.25</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>13.17</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>10.25</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>37.42</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>9.92</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>6.92</v>
+      </c>
+      <c r="BC14" t="n">
         <v>3</v>
       </c>
-      <c r="AL14" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>28.82</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>14.27</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>13.73</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>10.55</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>37.18</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>9.82</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>6.73</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>3.09</v>
-      </c>
       <c r="BD14" t="n">
-        <v>17.55</v>
+        <v>17.67</v>
       </c>
       <c r="BE14" t="n">
         <v>1.05</v>
       </c>
       <c r="BF14" t="n">
-        <v>2.45</v>
+        <v>2.58</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.73</v>
+        <v>2.74</v>
       </c>
       <c r="BH14" t="n">
-        <v>8.77</v>
+        <v>8.91</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.73</v>
+        <v>2.74</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.73</v>
+        <v>0.78</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="BP14" t="n">
-        <v>3.59</v>
+        <v>3.78</v>
       </c>
       <c r="BQ14" t="n">
-        <v>5.18</v>
+        <v>5.13</v>
       </c>
       <c r="BR14" t="n">
-        <v>90.91</v>
+        <v>91.3</v>
       </c>
       <c r="BS14" t="n">
-        <v>72.73</v>
+        <v>73.91</v>
       </c>
       <c r="BT14" t="n">
-        <v>54.55</v>
+        <v>56.52</v>
       </c>
       <c r="BU14" t="n">
-        <v>31.82</v>
+        <v>30.43</v>
       </c>
       <c r="BV14" t="n">
-        <v>18.18</v>
+        <v>17.39</v>
       </c>
       <c r="BW14" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BX14" t="n">
-        <v>63.64</v>
+        <v>60.87</v>
       </c>
       <c r="BY14" t="n">
         <v>2.96</v>
@@ -6446,22 +6446,22 @@
         <v>3.3</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.28</v>
+        <v>3.31</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.49</v>
+        <v>3.51</v>
       </c>
       <c r="CC14" t="n">
-        <v>5.3</v>
+        <v>5.33</v>
       </c>
       <c r="CD14" t="n">
-        <v>5.79</v>
+        <v>5.78</v>
       </c>
       <c r="CE14" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CF14" t="n">
-        <v>3.16</v>
+        <v>3.15</v>
       </c>
       <c r="CG14" t="n">
         <v>2.59</v>
@@ -6470,31 +6470,31 @@
         <v>1.32</v>
       </c>
       <c r="CI14" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CJ14" t="n">
         <v>2.02</v>
       </c>
       <c r="CK14" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="CL14" t="n">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="CN14" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CO14" t="n">
         <v>1.38</v>
       </c>
       <c r="CP14" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="CQ14" t="n">
-        <v>4.11</v>
+        <v>4.09</v>
       </c>
       <c r="CR14" t="n">
         <v>1.5</v>
@@ -6515,100 +6515,100 @@
         <v>2.04</v>
       </c>
       <c r="CX14" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="CY14" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="CZ14" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="DA14" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="DB14" t="n">
         <v>1.42</v>
       </c>
       <c r="DC14" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="DD14" t="n">
-        <v>4.36</v>
+        <v>4.34</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="DG14" t="n">
         <v>1.91</v>
       </c>
       <c r="DH14" t="n">
-        <v>87.04000000000001</v>
+        <v>86.39</v>
       </c>
       <c r="DI14" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DJ14" t="n">
-        <v>3.32</v>
+        <v>3.39</v>
       </c>
       <c r="DK14" t="n">
-        <v>3.4</v>
+        <v>3.52</v>
       </c>
       <c r="DL14" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="DM14" t="n">
+        <v>34.35</v>
+      </c>
+      <c r="DN14" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="DO14" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="DP14" t="n">
+        <v>15.96</v>
+      </c>
+      <c r="DQ14" t="n">
+        <v>12.87</v>
+      </c>
+      <c r="DR14" t="n">
+        <v>9.17</v>
+      </c>
+      <c r="DS14" t="n">
         <v>0.13</v>
       </c>
-      <c r="DM14" t="n">
-        <v>34.68</v>
-      </c>
-      <c r="DN14" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="DO14" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="DP14" t="n">
-        <v>16.05</v>
-      </c>
-      <c r="DQ14" t="n">
-        <v>13.14</v>
-      </c>
-      <c r="DR14" t="n">
-        <v>9.279999999999999</v>
-      </c>
-      <c r="DS14" t="n">
-        <v>0.14</v>
-      </c>
       <c r="DT14" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>41.27</v>
+        <v>41.22</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.18</v>
+        <v>0.22</v>
       </c>
       <c r="DX14" t="n">
-        <v>11.14</v>
+        <v>11.13</v>
       </c>
       <c r="DY14" t="n">
-        <v>7.64</v>
+        <v>7.7</v>
       </c>
       <c r="DZ14" t="n">
-        <v>3.5</v>
+        <v>3.44</v>
       </c>
       <c r="EA14" t="n">
-        <v>17.73</v>
+        <v>17.78</v>
       </c>
       <c r="EB14" t="n">
         <v>1.2</v>
       </c>
       <c r="EC14" t="n">
-        <v>3</v>
+        <v>3.04</v>
       </c>
     </row>
     <row r="15">
@@ -6906,7 +6906,7 @@
         <v>3.19</v>
       </c>
       <c r="CT15" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="CU15" t="n">
         <v>1.37</v>
@@ -7021,13 +7021,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C16" t="n">
         <v>12</v>
       </c>
       <c r="D16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E16" t="n">
         <v>0.17</v>
@@ -7114,136 +7114,136 @@
         <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.9</v>
+        <v>2.09</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="AI16" t="n">
-        <v>92.09999999999999</v>
+        <v>92.45</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AK16" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="AL16" t="n">
-        <v>4.2</v>
+        <v>4.27</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AN16" t="n">
-        <v>37.7</v>
+        <v>38</v>
       </c>
       <c r="AO16" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>13.45</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>16.45</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>52.55</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>11.27</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>6.82</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>16.82</v>
+      </c>
+      <c r="BE16" t="n">
         <v>1.3</v>
       </c>
-      <c r="AP16" t="n">
-        <v>2</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>2</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>52.8</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>17.3</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>1.34</v>
-      </c>
       <c r="BF16" t="n">
-        <v>3</v>
+        <v>3.09</v>
       </c>
       <c r="BG16" t="n">
-        <v>3.68</v>
+        <v>3.57</v>
       </c>
       <c r="BH16" t="n">
-        <v>11.05</v>
+        <v>11.09</v>
       </c>
       <c r="BI16" t="n">
-        <v>3.68</v>
+        <v>3.57</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.64</v>
+        <v>0.61</v>
       </c>
       <c r="BL16" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="BM16" t="n">
         <v>1</v>
       </c>
       <c r="BN16" t="n">
-        <v>2.09</v>
+        <v>2.04</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.59</v>
+        <v>1.52</v>
       </c>
       <c r="BP16" t="n">
-        <v>4.86</v>
+        <v>4.91</v>
       </c>
       <c r="BQ16" t="n">
-        <v>6.18</v>
+        <v>6.17</v>
       </c>
       <c r="BR16" t="n">
         <v>100</v>
       </c>
       <c r="BS16" t="n">
-        <v>95.45</v>
+        <v>91.3</v>
       </c>
       <c r="BT16" t="n">
-        <v>77.27</v>
+        <v>73.91</v>
       </c>
       <c r="BU16" t="n">
-        <v>59.09</v>
+        <v>56.52</v>
       </c>
       <c r="BV16" t="n">
-        <v>31.82</v>
+        <v>30.43</v>
       </c>
       <c r="BW16" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BX16" t="n">
-        <v>81.81999999999999</v>
+        <v>78.26000000000001</v>
       </c>
       <c r="BY16" t="n">
         <v>1.84</v>
@@ -7252,37 +7252,37 @@
         <v>1.85</v>
       </c>
       <c r="CA16" t="n">
-        <v>3.58</v>
+        <v>3.57</v>
       </c>
       <c r="CB16" t="n">
-        <v>3.75</v>
+        <v>3.74</v>
       </c>
       <c r="CC16" t="n">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="CD16" t="n">
-        <v>3.43</v>
+        <v>3.46</v>
       </c>
       <c r="CE16" t="n">
         <v>1.34</v>
       </c>
       <c r="CF16" t="n">
-        <v>2.51</v>
+        <v>2.52</v>
       </c>
       <c r="CG16" t="n">
-        <v>3.07</v>
+        <v>3.08</v>
       </c>
       <c r="CH16" t="n">
         <v>1.47</v>
       </c>
       <c r="CI16" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="CJ16" t="n">
         <v>1.66</v>
       </c>
       <c r="CK16" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CL16" t="n">
         <v>1.93</v>
@@ -7345,76 +7345,76 @@
         <v>0.09</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.95</v>
+        <v>2.04</v>
       </c>
       <c r="DG16" t="n">
-        <v>3.45</v>
+        <v>3.39</v>
       </c>
       <c r="DH16" t="n">
-        <v>96.95</v>
+        <v>96.91</v>
       </c>
       <c r="DI16" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DJ16" t="n">
-        <v>2.86</v>
+        <v>3</v>
       </c>
       <c r="DK16" t="n">
-        <v>6</v>
+        <v>5.96</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="DM16" t="n">
-        <v>44.04</v>
+        <v>43.91</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="DO16" t="n">
-        <v>2.55</v>
+        <v>2.56</v>
       </c>
       <c r="DP16" t="n">
-        <v>13.18</v>
+        <v>13.17</v>
       </c>
       <c r="DQ16" t="n">
-        <v>15.14</v>
+        <v>15.04</v>
       </c>
       <c r="DR16" t="n">
-        <v>7.68</v>
+        <v>7.87</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>53.55</v>
+        <v>53.4</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.09</v>
+        <v>0.13</v>
       </c>
       <c r="DX16" t="n">
-        <v>14.18</v>
+        <v>13.96</v>
       </c>
       <c r="DY16" t="n">
-        <v>8.539999999999999</v>
+        <v>8.52</v>
       </c>
       <c r="DZ16" t="n">
-        <v>5.63</v>
+        <v>5.43</v>
       </c>
       <c r="EA16" t="n">
-        <v>18.18</v>
+        <v>17.92</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="EC16" t="n">
-        <v>2.73</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="17">
@@ -7424,13 +7424,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C17" t="n">
         <v>11</v>
       </c>
       <c r="D17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E17" t="n">
         <v>0.18</v>
@@ -7517,49 +7517,49 @@
         <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="AI17" t="n">
-        <v>86.45</v>
+        <v>85.5</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AK17" t="n">
-        <v>3</v>
+        <v>2.83</v>
       </c>
       <c r="AL17" t="n">
-        <v>3.73</v>
+        <v>3.67</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AN17" t="n">
-        <v>33.45</v>
+        <v>31.83</v>
       </c>
       <c r="AO17" t="n">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ17" t="n">
-        <v>16.45</v>
+        <v>16.92</v>
       </c>
       <c r="AR17" t="n">
-        <v>11.64</v>
+        <v>11.58</v>
       </c>
       <c r="AS17" t="n">
-        <v>8.449999999999999</v>
+        <v>8.75</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AV17" t="n">
         <v>0</v>
@@ -7571,82 +7571,82 @@
         <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>42.45</v>
+        <v>42.58</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="BA17" t="n">
-        <v>13.27</v>
+        <v>12.92</v>
       </c>
       <c r="BB17" t="n">
-        <v>8.640000000000001</v>
+        <v>8.33</v>
       </c>
       <c r="BC17" t="n">
-        <v>4.64</v>
+        <v>4.58</v>
       </c>
       <c r="BD17" t="n">
-        <v>21.27</v>
+        <v>20.92</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="BF17" t="n">
-        <v>2.82</v>
+        <v>2.67</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.73</v>
+        <v>2.7</v>
       </c>
       <c r="BH17" t="n">
-        <v>8.949999999999999</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.73</v>
+        <v>2.7</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.82</v>
+        <v>0.87</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.77</v>
+        <v>0.74</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="BP17" t="n">
-        <v>4.05</v>
+        <v>4.04</v>
       </c>
       <c r="BQ17" t="n">
-        <v>4.45</v>
+        <v>4.48</v>
       </c>
       <c r="BR17" t="n">
-        <v>95.45</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="BS17" t="n">
-        <v>63.64</v>
+        <v>65.22</v>
       </c>
       <c r="BT17" t="n">
-        <v>45.45</v>
+        <v>43.48</v>
       </c>
       <c r="BU17" t="n">
-        <v>22.73</v>
+        <v>21.74</v>
       </c>
       <c r="BV17" t="n">
-        <v>13.64</v>
+        <v>13.04</v>
       </c>
       <c r="BW17" t="n">
-        <v>13.64</v>
+        <v>13.04</v>
       </c>
       <c r="BX17" t="n">
-        <v>50</v>
+        <v>47.83</v>
       </c>
       <c r="BY17" t="n">
         <v>3.15</v>
@@ -7655,22 +7655,22 @@
         <v>3.42</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.43</v>
+        <v>3.42</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.64</v>
+        <v>3.63</v>
       </c>
       <c r="CC17" t="n">
-        <v>5.28</v>
+        <v>5.19</v>
       </c>
       <c r="CD17" t="n">
-        <v>6.27</v>
+        <v>6.12</v>
       </c>
       <c r="CE17" t="n">
         <v>1.42</v>
       </c>
       <c r="CF17" t="n">
-        <v>3.03</v>
+        <v>3.02</v>
       </c>
       <c r="CG17" t="n">
         <v>2.69</v>
@@ -7688,10 +7688,10 @@
         <v>1.58</v>
       </c>
       <c r="CL17" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="CN17" t="n">
         <v>1.79</v>
@@ -7700,25 +7700,25 @@
         <v>1.34</v>
       </c>
       <c r="CP17" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="CQ17" t="n">
-        <v>3.68</v>
+        <v>3.66</v>
       </c>
       <c r="CR17" t="n">
         <v>1.47</v>
       </c>
       <c r="CS17" t="n">
-        <v>3.12</v>
+        <v>3.14</v>
       </c>
       <c r="CT17" t="n">
         <v>2.8</v>
       </c>
       <c r="CU17" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CV17" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CW17" t="n">
         <v>1.97</v>
@@ -7739,85 +7739,85 @@
         <v>1.37</v>
       </c>
       <c r="DC17" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="DD17" t="n">
-        <v>3.91</v>
+        <v>3.93</v>
       </c>
       <c r="DE17" t="n">
         <v>0.09</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="DG17" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="DH17" t="n">
-        <v>83.81999999999999</v>
+        <v>83.43000000000001</v>
       </c>
       <c r="DI17" t="n">
         <v>0.13</v>
       </c>
       <c r="DJ17" t="n">
-        <v>3.22</v>
+        <v>3.13</v>
       </c>
       <c r="DK17" t="n">
-        <v>3.36</v>
+        <v>3.35</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.32</v>
+        <v>0.31</v>
       </c>
       <c r="DM17" t="n">
-        <v>32.59</v>
+        <v>31.78</v>
       </c>
       <c r="DN17" t="n">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="DO17" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="DP17" t="n">
-        <v>17.36</v>
+        <v>17.57</v>
       </c>
       <c r="DQ17" t="n">
-        <v>12.41</v>
+        <v>12.35</v>
       </c>
       <c r="DR17" t="n">
-        <v>9</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>43.86</v>
+        <v>43.87</v>
       </c>
       <c r="DW17" t="n">
         <v>0.04</v>
       </c>
       <c r="DX17" t="n">
-        <v>11.82</v>
+        <v>11.7</v>
       </c>
       <c r="DY17" t="n">
-        <v>7.68</v>
+        <v>7.56</v>
       </c>
       <c r="DZ17" t="n">
-        <v>4.14</v>
+        <v>4.13</v>
       </c>
       <c r="EA17" t="n">
-        <v>20.77</v>
+        <v>20.61</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="EC17" t="n">
-        <v>3.14</v>
+        <v>3.04</v>
       </c>
     </row>
     <row r="18">
@@ -7827,94 +7827,94 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C18" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D18" t="n">
         <v>11</v>
       </c>
       <c r="E18" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="F18" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="G18" t="n">
-        <v>4.45</v>
+        <v>4.33</v>
       </c>
       <c r="H18" t="n">
-        <v>111.27</v>
+        <v>110.42</v>
       </c>
       <c r="I18" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="J18" t="n">
-        <v>3.09</v>
+        <v>3.17</v>
       </c>
       <c r="K18" t="n">
-        <v>6.73</v>
+        <v>6.58</v>
       </c>
       <c r="L18" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="M18" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="N18" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="O18" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="P18" t="n">
-        <v>18.09</v>
+        <v>17.08</v>
       </c>
       <c r="Q18" t="n">
-        <v>13</v>
+        <v>12.75</v>
       </c>
       <c r="R18" t="n">
-        <v>5.36</v>
+        <v>5.5</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
       </c>
       <c r="T18" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="U18" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="V18" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>51.73</v>
+        <v>52.58</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="Z18" t="n">
-        <v>16.55</v>
+        <v>15.75</v>
       </c>
       <c r="AA18" t="n">
-        <v>11.45</v>
+        <v>11.08</v>
       </c>
       <c r="AB18" t="n">
-        <v>5.09</v>
+        <v>4.67</v>
       </c>
       <c r="AC18" t="n">
-        <v>28.55</v>
+        <v>27.5</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.86</v>
+        <v>1.76</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.91</v>
+        <v>2.92</v>
       </c>
       <c r="AF18" t="n">
         <v>0.09</v>
@@ -7998,61 +7998,61 @@
         <v>3.09</v>
       </c>
       <c r="BG18" t="n">
-        <v>2.14</v>
+        <v>2.09</v>
       </c>
       <c r="BH18" t="n">
-        <v>9.23</v>
+        <v>9.43</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.14</v>
+        <v>2.09</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="BL18" t="n">
-        <v>0.73</v>
+        <v>0.7</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.55</v>
+        <v>0.57</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="BO18" t="n">
-        <v>0.86</v>
+        <v>0.83</v>
       </c>
       <c r="BP18" t="n">
-        <v>3.32</v>
+        <v>3.39</v>
       </c>
       <c r="BQ18" t="n">
-        <v>5.91</v>
+        <v>6.04</v>
       </c>
       <c r="BR18" t="n">
-        <v>90.91</v>
+        <v>91.3</v>
       </c>
       <c r="BS18" t="n">
-        <v>63.64</v>
+        <v>60.87</v>
       </c>
       <c r="BT18" t="n">
-        <v>36.36</v>
+        <v>34.78</v>
       </c>
       <c r="BU18" t="n">
-        <v>13.64</v>
+        <v>13.04</v>
       </c>
       <c r="BV18" t="n">
-        <v>9.09</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BW18" t="n">
         <v>0</v>
       </c>
       <c r="BX18" t="n">
-        <v>40.91</v>
+        <v>39.13</v>
       </c>
       <c r="BY18" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="BZ18" t="n">
         <v>1.95</v>
@@ -8061,7 +8061,7 @@
         <v>3.25</v>
       </c>
       <c r="CB18" t="n">
-        <v>3.39</v>
+        <v>3.38</v>
       </c>
       <c r="CC18" t="n">
         <v>2.78</v>
@@ -8073,7 +8073,7 @@
         <v>1.43</v>
       </c>
       <c r="CF18" t="n">
-        <v>2.99</v>
+        <v>2.98</v>
       </c>
       <c r="CG18" t="n">
         <v>2.69</v>
@@ -8082,7 +8082,7 @@
         <v>1.36</v>
       </c>
       <c r="CI18" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CJ18" t="n">
         <v>1.91</v>
@@ -8091,13 +8091,13 @@
         <v>1.61</v>
       </c>
       <c r="CL18" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="CM18" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="CN18" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CO18" t="n">
         <v>1.35</v>
@@ -8106,7 +8106,7 @@
         <v>2.16</v>
       </c>
       <c r="CQ18" t="n">
-        <v>3.85</v>
+        <v>3.83</v>
       </c>
       <c r="CR18" t="n">
         <v>1.48</v>
@@ -8127,64 +8127,64 @@
         <v>1.94</v>
       </c>
       <c r="CX18" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CY18" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="CZ18" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="DA18" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="DB18" t="n">
         <v>1.38</v>
       </c>
       <c r="DC18" t="n">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="DD18" t="n">
         <v>4.07</v>
       </c>
       <c r="DE18" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="DG18" t="n">
-        <v>4</v>
+        <v>3.96</v>
       </c>
       <c r="DH18" t="n">
-        <v>107.54</v>
+        <v>107.26</v>
       </c>
       <c r="DI18" t="n">
         <v>0.13</v>
       </c>
       <c r="DJ18" t="n">
-        <v>3.14</v>
+        <v>3.17</v>
       </c>
       <c r="DK18" t="n">
-        <v>6.18</v>
+        <v>6.13</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.54</v>
+        <v>0.52</v>
       </c>
       <c r="DM18" t="n">
-        <v>53.82</v>
+        <v>53.18</v>
       </c>
       <c r="DN18" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="DO18" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="DP18" t="n">
-        <v>17.22</v>
+        <v>16.74</v>
       </c>
       <c r="DQ18" t="n">
-        <v>14</v>
+        <v>13.83</v>
       </c>
       <c r="DR18" t="n">
         <v>6.82</v>
@@ -8199,25 +8199,25 @@
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>51.68</v>
+        <v>52.13</v>
       </c>
       <c r="DW18" t="n">
-        <v>0.13</v>
+        <v>0.17</v>
       </c>
       <c r="DX18" t="n">
-        <v>14.36</v>
+        <v>14.04</v>
       </c>
       <c r="DY18" t="n">
-        <v>9.949999999999999</v>
+        <v>9.82</v>
       </c>
       <c r="DZ18" t="n">
-        <v>4.41</v>
+        <v>4.22</v>
       </c>
       <c r="EA18" t="n">
-        <v>25.36</v>
+        <v>24.96</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="EC18" t="n">
         <v>3</v>
@@ -8230,10 +8230,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C19" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D19" t="n">
         <v>11</v>
@@ -8242,49 +8242,49 @@
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="G19" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="H19" t="n">
-        <v>94.36</v>
+        <v>91.33</v>
       </c>
       <c r="I19" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="J19" t="n">
-        <v>3.55</v>
+        <v>3.67</v>
       </c>
       <c r="K19" t="n">
-        <v>4</v>
+        <v>3.92</v>
       </c>
       <c r="L19" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="M19" t="n">
-        <v>42.36</v>
+        <v>40.75</v>
       </c>
       <c r="N19" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="O19" t="n">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="P19" t="n">
-        <v>13.09</v>
+        <v>12.67</v>
       </c>
       <c r="Q19" t="n">
-        <v>15.73</v>
+        <v>15.58</v>
       </c>
       <c r="R19" t="n">
-        <v>7.73</v>
+        <v>8.33</v>
       </c>
       <c r="S19" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="T19" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
@@ -8296,28 +8296,28 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>52.18</v>
+        <v>50.42</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="Z19" t="n">
-        <v>11.73</v>
+        <v>11.25</v>
       </c>
       <c r="AA19" t="n">
-        <v>8.550000000000001</v>
+        <v>8.33</v>
       </c>
       <c r="AB19" t="n">
-        <v>3.18</v>
+        <v>2.92</v>
       </c>
       <c r="AC19" t="n">
-        <v>23.18</v>
+        <v>22.25</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.91</v>
+        <v>2.92</v>
       </c>
       <c r="AF19" t="n">
         <v>0.18</v>
@@ -8401,70 +8401,70 @@
         <v>2.91</v>
       </c>
       <c r="BG19" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>10.35</v>
+      </c>
+      <c r="BI19" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="BJ19" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="BK19" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="BL19" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="BM19" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="BN19" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BO19" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="BP19" t="n">
+        <v>5.13</v>
+      </c>
+      <c r="BQ19" t="n">
+        <v>5.17</v>
+      </c>
+      <c r="BR19" t="n">
+        <v>91.3</v>
+      </c>
+      <c r="BS19" t="n">
+        <v>65.22</v>
+      </c>
+      <c r="BT19" t="n">
+        <v>39.13</v>
+      </c>
+      <c r="BU19" t="n">
+        <v>26.09</v>
+      </c>
+      <c r="BV19" t="n">
+        <v>17.39</v>
+      </c>
+      <c r="BW19" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="BX19" t="n">
+        <v>56.52</v>
+      </c>
+      <c r="BY19" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="BZ19" t="n">
         <v>2.55</v>
       </c>
-      <c r="BH19" t="n">
-        <v>10.09</v>
-      </c>
-      <c r="BI19" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="BJ19" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="BK19" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="BL19" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="BM19" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="BN19" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="BO19" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="BP19" t="n">
-        <v>4.91</v>
-      </c>
-      <c r="BQ19" t="n">
-        <v>5.14</v>
-      </c>
-      <c r="BR19" t="n">
-        <v>95.45</v>
-      </c>
-      <c r="BS19" t="n">
-        <v>68.18000000000001</v>
-      </c>
-      <c r="BT19" t="n">
-        <v>40.91</v>
-      </c>
-      <c r="BU19" t="n">
-        <v>27.27</v>
-      </c>
-      <c r="BV19" t="n">
-        <v>18.18</v>
-      </c>
-      <c r="BW19" t="n">
-        <v>4.55</v>
-      </c>
-      <c r="BX19" t="n">
-        <v>59.09</v>
-      </c>
-      <c r="BY19" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="BZ19" t="n">
-        <v>2.43</v>
-      </c>
       <c r="CA19" t="n">
-        <v>3.18</v>
+        <v>3.19</v>
       </c>
       <c r="CB19" t="n">
-        <v>3.31</v>
+        <v>3.32</v>
       </c>
       <c r="CC19" t="n">
         <v>3.82</v>
@@ -8473,13 +8473,13 @@
         <v>4.45</v>
       </c>
       <c r="CE19" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CF19" t="n">
-        <v>3.14</v>
+        <v>3.12</v>
       </c>
       <c r="CG19" t="n">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="CH19" t="n">
         <v>1.33</v>
@@ -8488,7 +8488,7 @@
         <v>1.83</v>
       </c>
       <c r="CJ19" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CK19" t="n">
         <v>1.58</v>
@@ -8497,100 +8497,100 @@
         <v>2.01</v>
       </c>
       <c r="CM19" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="CN19" t="n">
         <v>1.81</v>
       </c>
       <c r="CO19" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CP19" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="CQ19" t="n">
-        <v>4.12</v>
+        <v>4.08</v>
       </c>
       <c r="CR19" t="n">
         <v>1.5</v>
       </c>
       <c r="CS19" t="n">
-        <v>3.19</v>
+        <v>3.18</v>
       </c>
       <c r="CT19" t="n">
-        <v>2.72</v>
+        <v>2.73</v>
       </c>
       <c r="CU19" t="n">
         <v>1.38</v>
       </c>
       <c r="CV19" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="CW19" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="CX19" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="CY19" t="n">
         <v>1.98</v>
       </c>
-      <c r="CX19" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="CY19" t="n">
-        <v>1.99</v>
-      </c>
       <c r="CZ19" t="n">
-        <v>2.29</v>
+        <v>2.31</v>
       </c>
       <c r="DA19" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="DB19" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="DC19" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="DD19" t="n">
-        <v>4.2</v>
+        <v>4.17</v>
       </c>
       <c r="DE19" t="n">
         <v>0.09</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.68</v>
+        <v>1.74</v>
       </c>
       <c r="DG19" t="n">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
       <c r="DH19" t="n">
-        <v>90.45999999999999</v>
+        <v>89.04000000000001</v>
       </c>
       <c r="DI19" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DJ19" t="n">
-        <v>3.45</v>
+        <v>3.52</v>
       </c>
       <c r="DK19" t="n">
-        <v>4.68</v>
+        <v>4.61</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.63</v>
+        <v>0.61</v>
       </c>
       <c r="DM19" t="n">
-        <v>41.54</v>
+        <v>40.74</v>
       </c>
       <c r="DN19" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="DO19" t="n">
-        <v>2.22</v>
+        <v>2.17</v>
       </c>
       <c r="DP19" t="n">
-        <v>13.18</v>
+        <v>12.96</v>
       </c>
       <c r="DQ19" t="n">
-        <v>15.46</v>
+        <v>15.39</v>
       </c>
       <c r="DR19" t="n">
-        <v>7.59</v>
+        <v>7.91</v>
       </c>
       <c r="DS19" t="n">
         <v>0.09</v>
@@ -8602,28 +8602,28 @@
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>50.27</v>
+        <v>49.43</v>
       </c>
       <c r="DW19" t="n">
-        <v>0.36</v>
+        <v>0.39</v>
       </c>
       <c r="DX19" t="n">
-        <v>12.32</v>
+        <v>12.04</v>
       </c>
       <c r="DY19" t="n">
-        <v>8.82</v>
+        <v>8.69</v>
       </c>
       <c r="DZ19" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="EA19" t="n">
-        <v>20.36</v>
+        <v>20</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="EC19" t="n">
-        <v>2.91</v>
+        <v>2.92</v>
       </c>
     </row>
     <row r="20">
@@ -8633,94 +8633,94 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C20" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D20" t="n">
         <v>11</v>
       </c>
       <c r="E20" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="F20" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="G20" t="n">
-        <v>2.91</v>
+        <v>3.08</v>
       </c>
       <c r="H20" t="n">
-        <v>115.55</v>
+        <v>114.83</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>2.73</v>
+        <v>2.58</v>
       </c>
       <c r="K20" t="n">
-        <v>5.36</v>
+        <v>5.42</v>
       </c>
       <c r="L20" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="M20" t="n">
-        <v>60.64</v>
+        <v>59.92</v>
       </c>
       <c r="N20" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="O20" t="n">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="P20" t="n">
-        <v>16</v>
+        <v>15.83</v>
       </c>
       <c r="Q20" t="n">
-        <v>11.73</v>
+        <v>12.33</v>
       </c>
       <c r="R20" t="n">
-        <v>6.45</v>
+        <v>6.42</v>
       </c>
       <c r="S20" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="T20" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="U20" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="V20" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>54.36</v>
+        <v>53.92</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="Z20" t="n">
-        <v>16.09</v>
+        <v>16.17</v>
       </c>
       <c r="AA20" t="n">
-        <v>10.64</v>
+        <v>10.67</v>
       </c>
       <c r="AB20" t="n">
-        <v>5.45</v>
+        <v>5.5</v>
       </c>
       <c r="AC20" t="n">
-        <v>18.82</v>
+        <v>18.67</v>
       </c>
       <c r="AD20" t="n">
         <v>1.84</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.55</v>
+        <v>2.42</v>
       </c>
       <c r="AF20" t="n">
         <v>0.09</v>
@@ -8804,67 +8804,67 @@
         <v>2.36</v>
       </c>
       <c r="BG20" t="n">
-        <v>2.23</v>
+        <v>2.17</v>
       </c>
       <c r="BH20" t="n">
-        <v>8.68</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="BI20" t="n">
-        <v>2.23</v>
+        <v>2.17</v>
       </c>
       <c r="BJ20" t="n">
-        <v>0.59</v>
+        <v>0.57</v>
       </c>
       <c r="BK20" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="BL20" t="n">
         <v>1</v>
       </c>
       <c r="BM20" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="BN20" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="BO20" t="n">
-        <v>0.91</v>
+        <v>0.87</v>
       </c>
       <c r="BP20" t="n">
-        <v>3.77</v>
+        <v>3.65</v>
       </c>
       <c r="BQ20" t="n">
-        <v>4.91</v>
+        <v>4.96</v>
       </c>
       <c r="BR20" t="n">
-        <v>81.81999999999999</v>
+        <v>82.61</v>
       </c>
       <c r="BS20" t="n">
-        <v>68.18000000000001</v>
+        <v>65.22</v>
       </c>
       <c r="BT20" t="n">
-        <v>50</v>
+        <v>47.83</v>
       </c>
       <c r="BU20" t="n">
-        <v>18.18</v>
+        <v>17.39</v>
       </c>
       <c r="BV20" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BW20" t="n">
         <v>0</v>
       </c>
       <c r="BX20" t="n">
-        <v>50</v>
+        <v>47.83</v>
       </c>
       <c r="BY20" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="BZ20" t="n">
-        <v>2.01</v>
+        <v>2.04</v>
       </c>
       <c r="CA20" t="n">
-        <v>3.18</v>
+        <v>3.17</v>
       </c>
       <c r="CB20" t="n">
         <v>3.26</v>
@@ -8879,61 +8879,61 @@
         <v>1.48</v>
       </c>
       <c r="CF20" t="n">
-        <v>3.27</v>
+        <v>3.26</v>
       </c>
       <c r="CG20" t="n">
-        <v>2.51</v>
+        <v>2.52</v>
       </c>
       <c r="CH20" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="CI20" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CJ20" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="CK20" t="n">
         <v>1.64</v>
       </c>
       <c r="CL20" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="CM20" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="CN20" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CO20" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="CP20" t="n">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="CQ20" t="n">
-        <v>4.42</v>
+        <v>4.39</v>
       </c>
       <c r="CR20" t="n">
         <v>1.54</v>
       </c>
       <c r="CS20" t="n">
-        <v>3.26</v>
+        <v>3.25</v>
       </c>
       <c r="CT20" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="CU20" t="n">
         <v>1.36</v>
       </c>
       <c r="CV20" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CW20" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="CX20" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CY20" t="n">
         <v>2.13</v>
@@ -8945,88 +8945,88 @@
         <v>1.71</v>
       </c>
       <c r="DB20" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="DC20" t="n">
-        <v>2.49</v>
+        <v>2.47</v>
       </c>
       <c r="DD20" t="n">
-        <v>4.79</v>
+        <v>4.74</v>
       </c>
       <c r="DE20" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DF20" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="DG20" t="n">
-        <v>2.78</v>
+        <v>2.87</v>
       </c>
       <c r="DH20" t="n">
-        <v>106.14</v>
+        <v>106.17</v>
       </c>
       <c r="DI20" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ20" t="n">
-        <v>2.73</v>
+        <v>2.65</v>
       </c>
       <c r="DK20" t="n">
-        <v>4.55</v>
+        <v>4.61</v>
       </c>
       <c r="DL20" t="n">
-        <v>0.36</v>
+        <v>0.34</v>
       </c>
       <c r="DM20" t="n">
-        <v>49.1</v>
+        <v>49.22</v>
       </c>
       <c r="DN20" t="n">
-        <v>0.91</v>
+        <v>0.87</v>
       </c>
       <c r="DO20" t="n">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="DP20" t="n">
-        <v>14.46</v>
+        <v>14.43</v>
       </c>
       <c r="DQ20" t="n">
-        <v>12.54</v>
+        <v>12.82</v>
       </c>
       <c r="DR20" t="n">
-        <v>7.36</v>
+        <v>7.3</v>
       </c>
       <c r="DS20" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DT20" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DU20" t="n">
         <v>0</v>
       </c>
       <c r="DV20" t="n">
-        <v>50.46</v>
+        <v>50.4</v>
       </c>
       <c r="DW20" t="n">
         <v>0.13</v>
       </c>
       <c r="DX20" t="n">
-        <v>12.37</v>
+        <v>12.57</v>
       </c>
       <c r="DY20" t="n">
-        <v>8.32</v>
+        <v>8.44</v>
       </c>
       <c r="DZ20" t="n">
-        <v>4.05</v>
+        <v>4.13</v>
       </c>
       <c r="EA20" t="n">
-        <v>19.5</v>
+        <v>19.39</v>
       </c>
       <c r="EB20" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="EC20" t="n">
-        <v>2.45</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="21">
@@ -9036,13 +9036,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C21" t="n">
         <v>11</v>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E21" t="n">
         <v>0.09</v>
@@ -9129,136 +9129,136 @@
         <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="AI21" t="n">
-        <v>83.09</v>
+        <v>81.25</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="AK21" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>32.83</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>11.83</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>13.58</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>44.33</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>9.17</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>7.17</v>
+      </c>
+      <c r="BC21" t="n">
         <v>2</v>
       </c>
-      <c r="AL21" t="n">
-        <v>3.73</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>33.09</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>11.45</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>13.18</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>8.550000000000001</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>45.91</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>9.449999999999999</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>7.36</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>2.09</v>
-      </c>
       <c r="BD21" t="n">
-        <v>18.64</v>
+        <v>18.33</v>
       </c>
       <c r="BE21" t="n">
-        <v>0.99</v>
+        <v>0.96</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="BG21" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="BH21" t="n">
-        <v>9.5</v>
+        <v>9.26</v>
       </c>
       <c r="BI21" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="BJ21" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="BK21" t="n">
-        <v>0.45</v>
+        <v>0.48</v>
       </c>
       <c r="BL21" t="n">
-        <v>0.77</v>
+        <v>0.74</v>
       </c>
       <c r="BM21" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="BN21" t="n">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="BO21" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="BP21" t="n">
-        <v>4.23</v>
+        <v>4.22</v>
       </c>
       <c r="BQ21" t="n">
-        <v>5.23</v>
+        <v>5</v>
       </c>
       <c r="BR21" t="n">
-        <v>95.45</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="BS21" t="n">
-        <v>68.18000000000001</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="BT21" t="n">
-        <v>40.91</v>
+        <v>39.13</v>
       </c>
       <c r="BU21" t="n">
-        <v>18.18</v>
+        <v>17.39</v>
       </c>
       <c r="BV21" t="n">
-        <v>9.09</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BW21" t="n">
         <v>0</v>
       </c>
       <c r="BX21" t="n">
-        <v>50</v>
+        <v>52.17</v>
       </c>
       <c r="BY21" t="n">
         <v>2.52</v>
@@ -9267,13 +9267,13 @@
         <v>2.68</v>
       </c>
       <c r="CA21" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="CB21" t="n">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="CC21" t="n">
-        <v>3.76</v>
+        <v>3.8</v>
       </c>
       <c r="CD21" t="n">
         <v>4.36</v>
@@ -9282,10 +9282,10 @@
         <v>1.56</v>
       </c>
       <c r="CF21" t="n">
-        <v>3.67</v>
+        <v>3.65</v>
       </c>
       <c r="CG21" t="n">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="CH21" t="n">
         <v>1.25</v>
@@ -9294,7 +9294,7 @@
         <v>1.66</v>
       </c>
       <c r="CJ21" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="CK21" t="n">
         <v>1.67</v>
@@ -9303,19 +9303,19 @@
         <v>2.19</v>
       </c>
       <c r="CM21" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="CN21" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CO21" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CP21" t="n">
-        <v>2.58</v>
+        <v>2.57</v>
       </c>
       <c r="CQ21" t="n">
-        <v>5.01</v>
+        <v>4.96</v>
       </c>
       <c r="CR21" t="n">
         <v>1.6</v>
@@ -9330,106 +9330,106 @@
         <v>1.37</v>
       </c>
       <c r="CV21" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="CW21" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="CX21" t="n">
         <v>1.71</v>
       </c>
       <c r="CY21" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="CZ21" t="n">
         <v>2.14</v>
       </c>
       <c r="DA21" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="DB21" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="DC21" t="n">
-        <v>2.78</v>
+        <v>2.75</v>
       </c>
       <c r="DD21" t="n">
-        <v>5.59</v>
+        <v>5.51</v>
       </c>
       <c r="DE21" t="n">
         <v>0.04</v>
       </c>
       <c r="DF21" t="n">
-        <v>1.68</v>
+        <v>1.74</v>
       </c>
       <c r="DG21" t="n">
-        <v>2.55</v>
+        <v>2.44</v>
       </c>
       <c r="DH21" t="n">
-        <v>90.36</v>
+        <v>89.09</v>
       </c>
       <c r="DI21" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="DJ21" t="n">
-        <v>2.37</v>
+        <v>2.44</v>
       </c>
       <c r="DK21" t="n">
-        <v>4.59</v>
+        <v>4.43</v>
       </c>
       <c r="DL21" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="DM21" t="n">
-        <v>39.82</v>
+        <v>39.39</v>
       </c>
       <c r="DN21" t="n">
-        <v>0.64</v>
+        <v>0.66</v>
       </c>
       <c r="DO21" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="DP21" t="n">
-        <v>12.77</v>
+        <v>12.91</v>
       </c>
       <c r="DQ21" t="n">
-        <v>12.86</v>
+        <v>13.09</v>
       </c>
       <c r="DR21" t="n">
-        <v>9.1</v>
+        <v>9.18</v>
       </c>
       <c r="DS21" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DT21" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DU21" t="n">
         <v>0</v>
       </c>
       <c r="DV21" t="n">
-        <v>45.78</v>
+        <v>44.96</v>
       </c>
       <c r="DW21" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DX21" t="n">
-        <v>10.9</v>
+        <v>10.7</v>
       </c>
       <c r="DY21" t="n">
-        <v>8.09</v>
+        <v>7.96</v>
       </c>
       <c r="DZ21" t="n">
-        <v>2.82</v>
+        <v>2.74</v>
       </c>
       <c r="EA21" t="n">
-        <v>21.1</v>
+        <v>20.83</v>
       </c>
       <c r="EB21" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="EC21" t="n">
-        <v>2.23</v>
+        <v>2.31</v>
       </c>
     </row>
     <row r="22">
@@ -9439,10 +9439,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C22" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D22" t="n">
         <v>11</v>
@@ -9451,82 +9451,82 @@
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="G22" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="H22" t="n">
-        <v>112.27</v>
+        <v>110.67</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>2.55</v>
+        <v>2.42</v>
       </c>
       <c r="K22" t="n">
-        <v>5.36</v>
+        <v>5.42</v>
       </c>
       <c r="L22" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="M22" t="n">
-        <v>51.45</v>
+        <v>52.42</v>
       </c>
       <c r="N22" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="O22" t="n">
-        <v>2.45</v>
+        <v>2.58</v>
       </c>
       <c r="P22" t="n">
-        <v>12.82</v>
+        <v>12.33</v>
       </c>
       <c r="Q22" t="n">
-        <v>10.64</v>
+        <v>10.75</v>
       </c>
       <c r="R22" t="n">
-        <v>6.55</v>
+        <v>6.67</v>
       </c>
       <c r="S22" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="T22" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="U22" t="n">
-        <v>0.27</v>
+        <v>0.42</v>
       </c>
       <c r="V22" t="n">
-        <v>0.27</v>
+        <v>0.42</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>46.45</v>
+        <v>47.58</v>
       </c>
       <c r="Y22" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="Z22" t="n">
-        <v>13.55</v>
+        <v>13.75</v>
       </c>
       <c r="AA22" t="n">
-        <v>8.359999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="AB22" t="n">
-        <v>5.18</v>
+        <v>5.25</v>
       </c>
       <c r="AC22" t="n">
-        <v>19.55</v>
+        <v>18.92</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AE22" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AF22" t="n">
         <v>0.18</v>
@@ -9610,70 +9610,70 @@
         <v>3</v>
       </c>
       <c r="BG22" t="n">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
       <c r="BH22" t="n">
-        <v>10.05</v>
+        <v>10.13</v>
       </c>
       <c r="BI22" t="n">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
       <c r="BJ22" t="n">
-        <v>0.55</v>
+        <v>0.57</v>
       </c>
       <c r="BK22" t="n">
-        <v>0.64</v>
+        <v>0.61</v>
       </c>
       <c r="BL22" t="n">
-        <v>0.91</v>
+        <v>0.96</v>
       </c>
       <c r="BM22" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="BN22" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="BO22" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="BP22" t="n">
-        <v>4.45</v>
+        <v>4.61</v>
       </c>
       <c r="BQ22" t="n">
-        <v>5</v>
+        <v>4.96</v>
       </c>
       <c r="BR22" t="n">
-        <v>95.45</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="BS22" t="n">
-        <v>63.64</v>
+        <v>65.22</v>
       </c>
       <c r="BT22" t="n">
-        <v>50</v>
+        <v>52.17</v>
       </c>
       <c r="BU22" t="n">
-        <v>31.82</v>
+        <v>30.43</v>
       </c>
       <c r="BV22" t="n">
-        <v>22.73</v>
+        <v>21.74</v>
       </c>
       <c r="BW22" t="n">
-        <v>9.09</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BX22" t="n">
-        <v>59.09</v>
+        <v>56.52</v>
       </c>
       <c r="BY22" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="BZ22" t="n">
-        <v>2.11</v>
+        <v>2.07</v>
       </c>
       <c r="CA22" t="n">
-        <v>3.19</v>
+        <v>3.21</v>
       </c>
       <c r="CB22" t="n">
-        <v>3.28</v>
+        <v>3.31</v>
       </c>
       <c r="CC22" t="n">
         <v>3.1</v>
@@ -9685,7 +9685,7 @@
         <v>1.45</v>
       </c>
       <c r="CF22" t="n">
-        <v>3.11</v>
+        <v>3.1</v>
       </c>
       <c r="CG22" t="n">
         <v>2.65</v>
@@ -9694,19 +9694,19 @@
         <v>1.33</v>
       </c>
       <c r="CI22" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CJ22" t="n">
         <v>1.89</v>
       </c>
       <c r="CK22" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CL22" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="CM22" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="CN22" t="n">
         <v>1.74</v>
@@ -9718,7 +9718,7 @@
         <v>2.18</v>
       </c>
       <c r="CQ22" t="n">
-        <v>3.94</v>
+        <v>3.92</v>
       </c>
       <c r="CR22" t="n">
         <v>1.48</v>
@@ -9742,97 +9742,97 @@
         <v>1.63</v>
       </c>
       <c r="CY22" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="CZ22" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="DA22" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="DB22" t="n">
         <v>1.42</v>
       </c>
       <c r="DC22" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="DD22" t="n">
-        <v>4.33</v>
+        <v>4.31</v>
       </c>
       <c r="DE22" t="n">
         <v>0.09</v>
       </c>
       <c r="DF22" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="DG22" t="n">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
       <c r="DH22" t="n">
-        <v>99.27</v>
+        <v>99</v>
       </c>
       <c r="DI22" t="n">
         <v>0</v>
       </c>
       <c r="DJ22" t="n">
-        <v>2.86</v>
+        <v>2.78</v>
       </c>
       <c r="DK22" t="n">
-        <v>4.82</v>
+        <v>4.87</v>
       </c>
       <c r="DL22" t="n">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="DM22" t="n">
-        <v>44.36</v>
+        <v>45.17</v>
       </c>
       <c r="DN22" t="n">
-        <v>0.64</v>
+        <v>0.66</v>
       </c>
       <c r="DO22" t="n">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="DP22" t="n">
-        <v>12.19</v>
+        <v>11.96</v>
       </c>
       <c r="DQ22" t="n">
-        <v>10.32</v>
+        <v>10.39</v>
       </c>
       <c r="DR22" t="n">
         <v>7.78</v>
       </c>
       <c r="DS22" t="n">
-        <v>0.27</v>
+        <v>0.35</v>
       </c>
       <c r="DT22" t="n">
-        <v>0.27</v>
+        <v>0.35</v>
       </c>
       <c r="DU22" t="n">
         <v>0</v>
       </c>
       <c r="DV22" t="n">
-        <v>44.86</v>
+        <v>45.52</v>
       </c>
       <c r="DW22" t="n">
         <v>0.22</v>
       </c>
       <c r="DX22" t="n">
-        <v>11.64</v>
+        <v>11.83</v>
       </c>
       <c r="DY22" t="n">
-        <v>6.9</v>
+        <v>7.04</v>
       </c>
       <c r="DZ22" t="n">
-        <v>4.72</v>
+        <v>4.78</v>
       </c>
       <c r="EA22" t="n">
-        <v>19.45</v>
+        <v>19.13</v>
       </c>
       <c r="EB22" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="EC22" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
     </row>
     <row r="23">
@@ -9842,61 +9842,61 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C23" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D23" t="n">
         <v>11</v>
       </c>
       <c r="E23" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="F23" t="n">
-        <v>1.64</v>
+        <v>1.83</v>
       </c>
       <c r="G23" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="H23" t="n">
-        <v>97.36</v>
+        <v>98.83</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>2.18</v>
+        <v>2.42</v>
       </c>
       <c r="K23" t="n">
-        <v>4.27</v>
+        <v>4.17</v>
       </c>
       <c r="L23" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="M23" t="n">
-        <v>39.27</v>
+        <v>39.92</v>
       </c>
       <c r="N23" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="O23" t="n">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="P23" t="n">
-        <v>13.55</v>
+        <v>13.5</v>
       </c>
       <c r="Q23" t="n">
-        <v>15.55</v>
+        <v>15.92</v>
       </c>
       <c r="R23" t="n">
-        <v>6.09</v>
+        <v>6.08</v>
       </c>
       <c r="S23" t="n">
-        <v>0.73</v>
+        <v>0.83</v>
       </c>
       <c r="T23" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="U23" t="n">
         <v>0</v>
@@ -9908,28 +9908,28 @@
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>55.18</v>
+        <v>55.5</v>
       </c>
       <c r="Y23" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="Z23" t="n">
-        <v>12.18</v>
+        <v>12.33</v>
       </c>
       <c r="AA23" t="n">
-        <v>7.73</v>
+        <v>7.75</v>
       </c>
       <c r="AB23" t="n">
-        <v>4.45</v>
+        <v>4.58</v>
       </c>
       <c r="AC23" t="n">
-        <v>18.27</v>
+        <v>19.25</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AF23" t="n">
         <v>0</v>
@@ -10013,64 +10013,64 @@
         <v>2.18</v>
       </c>
       <c r="BG23" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="BH23" t="n">
-        <v>7.45</v>
+        <v>7.48</v>
       </c>
       <c r="BI23" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="BJ23" t="n">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="BK23" t="n">
-        <v>0.36</v>
+        <v>0.43</v>
       </c>
       <c r="BL23" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="BM23" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="BN23" t="n">
-        <v>0.91</v>
+        <v>0.87</v>
       </c>
       <c r="BO23" t="n">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="BP23" t="n">
-        <v>3.73</v>
+        <v>3.65</v>
       </c>
       <c r="BQ23" t="n">
-        <v>3.73</v>
+        <v>3.83</v>
       </c>
       <c r="BR23" t="n">
-        <v>81.81999999999999</v>
+        <v>82.61</v>
       </c>
       <c r="BS23" t="n">
-        <v>54.55</v>
+        <v>56.52</v>
       </c>
       <c r="BT23" t="n">
-        <v>36.36</v>
+        <v>39.13</v>
       </c>
       <c r="BU23" t="n">
-        <v>22.73</v>
+        <v>21.74</v>
       </c>
       <c r="BV23" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BW23" t="n">
         <v>0</v>
       </c>
       <c r="BX23" t="n">
-        <v>50</v>
+        <v>52.17</v>
       </c>
       <c r="BY23" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="BZ23" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="CA23" t="n">
         <v>3.21</v>
@@ -10088,10 +10088,10 @@
         <v>1.47</v>
       </c>
       <c r="CF23" t="n">
-        <v>3.21</v>
+        <v>3.2</v>
       </c>
       <c r="CG23" t="n">
-        <v>2.53</v>
+        <v>2.54</v>
       </c>
       <c r="CH23" t="n">
         <v>1.31</v>
@@ -10100,109 +10100,109 @@
         <v>1.81</v>
       </c>
       <c r="CJ23" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CK23" t="n">
         <v>1.7</v>
       </c>
       <c r="CL23" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="CM23" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CN23" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CO23" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CP23" t="n">
         <v>2.22</v>
       </c>
       <c r="CQ23" t="n">
-        <v>4.15</v>
+        <v>4.11</v>
       </c>
       <c r="CR23" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CS23" t="n">
         <v>3.21</v>
       </c>
       <c r="CT23" t="n">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
       <c r="CU23" t="n">
         <v>1.37</v>
       </c>
       <c r="CV23" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CW23" t="n">
         <v>2.04</v>
       </c>
       <c r="CX23" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CY23" t="n">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="CZ23" t="n">
         <v>2.06</v>
       </c>
       <c r="DA23" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="DB23" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="DC23" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="DD23" t="n">
-        <v>4.49</v>
+        <v>4.46</v>
       </c>
       <c r="DE23" t="n">
         <v>0.09</v>
       </c>
       <c r="DF23" t="n">
-        <v>1.54</v>
+        <v>1.65</v>
       </c>
       <c r="DG23" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="DH23" t="n">
-        <v>93.81999999999999</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="DI23" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ23" t="n">
-        <v>2.18</v>
+        <v>2.31</v>
       </c>
       <c r="DK23" t="n">
-        <v>3.95</v>
+        <v>3.92</v>
       </c>
       <c r="DL23" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="DM23" t="n">
-        <v>38.46</v>
+        <v>38.83</v>
       </c>
       <c r="DN23" t="n">
-        <v>0.54</v>
+        <v>0.52</v>
       </c>
       <c r="DO23" t="n">
-        <v>2.22</v>
+        <v>2.17</v>
       </c>
       <c r="DP23" t="n">
-        <v>12.86</v>
+        <v>12.87</v>
       </c>
       <c r="DQ23" t="n">
-        <v>17.14</v>
+        <v>17.26</v>
       </c>
       <c r="DR23" t="n">
-        <v>7.63</v>
+        <v>7.56</v>
       </c>
       <c r="DS23" t="n">
         <v>0</v>
@@ -10214,28 +10214,28 @@
         <v>0</v>
       </c>
       <c r="DV23" t="n">
-        <v>56</v>
+        <v>56.13</v>
       </c>
       <c r="DW23" t="n">
-        <v>0.18</v>
+        <v>0.22</v>
       </c>
       <c r="DX23" t="n">
-        <v>11.27</v>
+        <v>11.39</v>
       </c>
       <c r="DY23" t="n">
-        <v>7.5</v>
+        <v>7.52</v>
       </c>
       <c r="DZ23" t="n">
-        <v>3.77</v>
+        <v>3.87</v>
       </c>
       <c r="EA23" t="n">
-        <v>18.31</v>
+        <v>18.82</v>
       </c>
       <c r="EB23" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="EC23" t="n">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Spain_Segunda_División_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Spain_Segunda_División_2025-2026.xlsx
@@ -1905,7 +1905,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ3" t="n">
-        <v>13.92</v>
+        <v>13.83</v>
       </c>
       <c r="AR3" t="n">
         <v>14.75</v>
@@ -2136,7 +2136,7 @@
         <v>2.26</v>
       </c>
       <c r="DP3" t="n">
-        <v>14.13</v>
+        <v>14.08</v>
       </c>
       <c r="DQ3" t="n">
         <v>13.22</v>
@@ -2991,94 +2991,94 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D6" t="n">
         <v>11</v>
       </c>
       <c r="E6" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="F6" t="n">
-        <v>1.18</v>
+        <v>1.42</v>
       </c>
       <c r="G6" t="n">
-        <v>3.18</v>
+        <v>3.08</v>
       </c>
       <c r="H6" t="n">
-        <v>98.64</v>
+        <v>97.17</v>
       </c>
       <c r="I6" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="J6" t="n">
-        <v>2.45</v>
+        <v>2.58</v>
       </c>
       <c r="K6" t="n">
-        <v>5.55</v>
+        <v>5.5</v>
       </c>
       <c r="L6" t="n">
-        <v>0.27</v>
+        <v>0.42</v>
       </c>
       <c r="M6" t="n">
-        <v>55.45</v>
+        <v>54.92</v>
       </c>
       <c r="N6" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="O6" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="P6" t="n">
-        <v>14.91</v>
+        <v>14.92</v>
       </c>
       <c r="Q6" t="n">
-        <v>12.82</v>
+        <v>13</v>
       </c>
       <c r="R6" t="n">
-        <v>5.45</v>
+        <v>5.58</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
       </c>
       <c r="T6" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="U6" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="V6" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>53</v>
+        <v>52.75</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>12.45</v>
+        <v>12.92</v>
       </c>
       <c r="AA6" t="n">
-        <v>7.91</v>
+        <v>7.92</v>
       </c>
       <c r="AB6" t="n">
-        <v>4.55</v>
+        <v>5</v>
       </c>
       <c r="AC6" t="n">
-        <v>21.18</v>
+        <v>20.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.51</v>
+        <v>1.56</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.45</v>
+        <v>2.58</v>
       </c>
       <c r="AF6" t="n">
         <v>0.18</v>
@@ -3162,67 +3162,67 @@
         <v>2.36</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.45</v>
+        <v>2.52</v>
       </c>
       <c r="BH6" t="n">
-        <v>9.23</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.45</v>
+        <v>2.52</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.91</v>
+        <v>0.96</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.45</v>
+        <v>0.48</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.55</v>
+        <v>0.57</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="BN6" t="n">
         <v>1.09</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="BP6" t="n">
-        <v>3.86</v>
+        <v>3.87</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.09</v>
+        <v>5.26</v>
       </c>
       <c r="BR6" t="n">
-        <v>90.91</v>
+        <v>91.3</v>
       </c>
       <c r="BS6" t="n">
-        <v>68.18000000000001</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="BT6" t="n">
-        <v>50</v>
+        <v>52.17</v>
       </c>
       <c r="BU6" t="n">
-        <v>18.18</v>
+        <v>21.74</v>
       </c>
       <c r="BV6" t="n">
-        <v>13.64</v>
+        <v>13.04</v>
       </c>
       <c r="BW6" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BX6" t="n">
-        <v>50</v>
+        <v>52.17</v>
       </c>
       <c r="BY6" t="n">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
       <c r="BZ6" t="n">
-        <v>2.57</v>
+        <v>2.54</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.18</v>
+        <v>3.19</v>
       </c>
       <c r="CB6" t="n">
         <v>3.3</v>
@@ -3237,10 +3237,10 @@
         <v>1.45</v>
       </c>
       <c r="CF6" t="n">
-        <v>3.07</v>
+        <v>3.06</v>
       </c>
       <c r="CG6" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="CH6" t="n">
         <v>1.34</v>
@@ -3255,10 +3255,10 @@
         <v>1.67</v>
       </c>
       <c r="CL6" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="CN6" t="n">
         <v>1.68</v>
@@ -3267,37 +3267,37 @@
         <v>1.37</v>
       </c>
       <c r="CP6" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="CQ6" t="n">
-        <v>4.02</v>
+        <v>4</v>
       </c>
       <c r="CR6" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CS6" t="n">
-        <v>3.15</v>
+        <v>3.16</v>
       </c>
       <c r="CT6" t="n">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
       <c r="CU6" t="n">
         <v>1.39</v>
       </c>
       <c r="CV6" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="CW6" t="n">
         <v>1.93</v>
-      </c>
-      <c r="CW6" t="n">
-        <v>1.94</v>
       </c>
       <c r="CX6" t="n">
         <v>1.69</v>
       </c>
       <c r="CY6" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="CZ6" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="DA6" t="n">
         <v>1.72</v>
@@ -3306,85 +3306,85 @@
         <v>1.39</v>
       </c>
       <c r="DC6" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="DD6" t="n">
-        <v>4.12</v>
+        <v>4.11</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.46</v>
+        <v>2.43</v>
       </c>
       <c r="DH6" t="n">
-        <v>89.95</v>
+        <v>89.56999999999999</v>
       </c>
       <c r="DI6" t="n">
         <v>0.09</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.55</v>
+        <v>2.61</v>
       </c>
       <c r="DK6" t="n">
-        <v>4.6</v>
+        <v>4.61</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.36</v>
+        <v>0.43</v>
       </c>
       <c r="DM6" t="n">
-        <v>46.09</v>
+        <v>46.22</v>
       </c>
       <c r="DN6" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="DO6" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="DP6" t="n">
-        <v>13.73</v>
+        <v>13.79</v>
       </c>
       <c r="DQ6" t="n">
-        <v>12.82</v>
+        <v>12.91</v>
       </c>
       <c r="DR6" t="n">
         <v>7.09</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>50.59</v>
+        <v>50.56</v>
       </c>
       <c r="DW6" t="n">
         <v>0.09</v>
       </c>
       <c r="DX6" t="n">
-        <v>10.82</v>
+        <v>11.13</v>
       </c>
       <c r="DY6" t="n">
-        <v>7.23</v>
+        <v>7.26</v>
       </c>
       <c r="DZ6" t="n">
-        <v>3.6</v>
+        <v>3.87</v>
       </c>
       <c r="EA6" t="n">
-        <v>21.27</v>
+        <v>20.91</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.4</v>
+        <v>2.47</v>
       </c>
     </row>
     <row r="7">
@@ -3394,13 +3394,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C7" t="n">
         <v>11</v>
       </c>
       <c r="D7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E7" t="n">
         <v>0.09</v>
@@ -3484,139 +3484,139 @@
         <v>1.18</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AH7" t="n">
-        <v>2.27</v>
+        <v>2.67</v>
       </c>
       <c r="AI7" t="n">
-        <v>74.45</v>
+        <v>76.33</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AL7" t="n">
-        <v>3.27</v>
+        <v>3.67</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="AN7" t="n">
-        <v>31.55</v>
+        <v>32.42</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.64</v>
+        <v>0.75</v>
       </c>
       <c r="AP7" t="n">
         <v>1</v>
       </c>
       <c r="AQ7" t="n">
-        <v>12.45</v>
+        <v>12.67</v>
       </c>
       <c r="AR7" t="n">
-        <v>11.45</v>
+        <v>11.75</v>
       </c>
       <c r="AS7" t="n">
-        <v>10.09</v>
+        <v>9.83</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AX7" t="n">
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>42.55</v>
+        <v>43.17</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.09</v>
+        <v>0.17</v>
       </c>
       <c r="BA7" t="n">
-        <v>11.18</v>
+        <v>11.42</v>
       </c>
       <c r="BB7" t="n">
-        <v>6.64</v>
+        <v>6.75</v>
       </c>
       <c r="BC7" t="n">
-        <v>4.55</v>
+        <v>4.67</v>
       </c>
       <c r="BD7" t="n">
-        <v>17.27</v>
+        <v>17.83</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="BF7" t="n">
         <v>2</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.64</v>
+        <v>2.7</v>
       </c>
       <c r="BH7" t="n">
-        <v>9.09</v>
+        <v>9.26</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.64</v>
+        <v>2.7</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.68</v>
+        <v>0.74</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.55</v>
+        <v>0.57</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.59</v>
+        <v>0.57</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="BP7" t="n">
         <v>3.91</v>
       </c>
       <c r="BQ7" t="n">
-        <v>5.18</v>
+        <v>5.35</v>
       </c>
       <c r="BR7" t="n">
-        <v>90.91</v>
+        <v>91.3</v>
       </c>
       <c r="BS7" t="n">
-        <v>59.09</v>
+        <v>60.87</v>
       </c>
       <c r="BT7" t="n">
-        <v>45.45</v>
+        <v>47.83</v>
       </c>
       <c r="BU7" t="n">
-        <v>31.82</v>
+        <v>34.78</v>
       </c>
       <c r="BV7" t="n">
-        <v>22.73</v>
+        <v>21.74</v>
       </c>
       <c r="BW7" t="n">
-        <v>13.64</v>
+        <v>13.04</v>
       </c>
       <c r="BX7" t="n">
-        <v>40.91</v>
+        <v>43.48</v>
       </c>
       <c r="BY7" t="n">
         <v>2.6</v>
@@ -3625,25 +3625,25 @@
         <v>2.72</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.36</v>
+        <v>3.35</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.49</v>
+        <v>3.48</v>
       </c>
       <c r="CC7" t="n">
-        <v>4.85</v>
+        <v>4.7</v>
       </c>
       <c r="CD7" t="n">
-        <v>5.43</v>
+        <v>5.28</v>
       </c>
       <c r="CE7" t="n">
         <v>1.43</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="CH7" t="n">
         <v>1.36</v>
@@ -3655,13 +3655,13 @@
         <v>1.91</v>
       </c>
       <c r="CK7" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CL7" t="n">
         <v>2.02</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="CN7" t="n">
         <v>1.79</v>
@@ -3670,7 +3670,7 @@
         <v>1.32</v>
       </c>
       <c r="CP7" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="CQ7" t="n">
         <v>3.68</v>
@@ -3679,7 +3679,7 @@
         <v>1.45</v>
       </c>
       <c r="CS7" t="n">
-        <v>3.14</v>
+        <v>3.15</v>
       </c>
       <c r="CT7" t="n">
         <v>2.88</v>
@@ -3688,10 +3688,10 @@
         <v>1.39</v>
       </c>
       <c r="CV7" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CW7" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CX7" t="n">
         <v>1.62</v>
@@ -3703,7 +3703,7 @@
         <v>2.25</v>
       </c>
       <c r="DA7" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="DB7" t="n">
         <v>1.37</v>
@@ -3718,43 +3718,43 @@
         <v>0.13</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="DG7" t="n">
-        <v>2.82</v>
+        <v>3</v>
       </c>
       <c r="DH7" t="n">
-        <v>83.77</v>
+        <v>84.34999999999999</v>
       </c>
       <c r="DI7" t="n">
         <v>0.09</v>
       </c>
       <c r="DJ7" t="n">
-        <v>1.77</v>
+        <v>1.82</v>
       </c>
       <c r="DK7" t="n">
-        <v>4</v>
+        <v>4.18</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.27</v>
+        <v>0.31</v>
       </c>
       <c r="DM7" t="n">
-        <v>37.64</v>
+        <v>37.83</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.41</v>
+        <v>0.48</v>
       </c>
       <c r="DO7" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="DP7" t="n">
-        <v>11.9</v>
+        <v>12.04</v>
       </c>
       <c r="DQ7" t="n">
-        <v>12.31</v>
+        <v>12.43</v>
       </c>
       <c r="DR7" t="n">
-        <v>8.859999999999999</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="DS7" t="n">
         <v>0.09</v>
@@ -3766,28 +3766,28 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>48.5</v>
+        <v>48.56</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.09</v>
+        <v>0.13</v>
       </c>
       <c r="DX7" t="n">
-        <v>11.32</v>
+        <v>11.43</v>
       </c>
       <c r="DY7" t="n">
-        <v>7.23</v>
+        <v>7.26</v>
       </c>
       <c r="DZ7" t="n">
-        <v>4.1</v>
+        <v>4.18</v>
       </c>
       <c r="EA7" t="n">
-        <v>18.31</v>
+        <v>18.56</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="EC7" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
     </row>
     <row r="8">
@@ -4669,7 +4669,7 @@
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>53.91</v>
+        <v>54</v>
       </c>
       <c r="Y10" t="n">
         <v>0.09</v>
@@ -4975,7 +4975,7 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>50.39</v>
+        <v>50.44</v>
       </c>
       <c r="DW10" t="n">
         <v>0.04</v>
@@ -5072,7 +5072,7 @@
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>60.82</v>
+        <v>60.73</v>
       </c>
       <c r="Y11" t="n">
         <v>0.09</v>
@@ -5378,7 +5378,7 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>59.31</v>
+        <v>59.26</v>
       </c>
       <c r="DW11" t="n">
         <v>0.08</v>
@@ -7114,7 +7114,7 @@
         <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.09</v>
+        <v>2.18</v>
       </c>
       <c r="AH16" t="n">
         <v>2.18</v>
@@ -7168,7 +7168,7 @@
         <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>52.55</v>
+        <v>52.45</v>
       </c>
       <c r="AZ16" t="n">
         <v>0.27</v>
@@ -7189,7 +7189,7 @@
         <v>1.3</v>
       </c>
       <c r="BF16" t="n">
-        <v>3.09</v>
+        <v>3.18</v>
       </c>
       <c r="BG16" t="n">
         <v>3.57</v>
@@ -7345,7 +7345,7 @@
         <v>0.09</v>
       </c>
       <c r="DF16" t="n">
-        <v>2.04</v>
+        <v>2.09</v>
       </c>
       <c r="DG16" t="n">
         <v>3.39</v>
@@ -7393,7 +7393,7 @@
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>53.4</v>
+        <v>53.35</v>
       </c>
       <c r="DW16" t="n">
         <v>0.13</v>
@@ -7414,7 +7414,7 @@
         <v>1.58</v>
       </c>
       <c r="EC16" t="n">
-        <v>2.78</v>
+        <v>2.83</v>
       </c>
     </row>
     <row r="17">
@@ -8242,7 +8242,7 @@
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="G19" t="n">
         <v>1.58</v>
@@ -8254,7 +8254,7 @@
         <v>0.08</v>
       </c>
       <c r="J19" t="n">
-        <v>3.67</v>
+        <v>3.83</v>
       </c>
       <c r="K19" t="n">
         <v>3.92</v>
@@ -8299,7 +8299,7 @@
         <v>50.42</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.5</v>
+        <v>0.58</v>
       </c>
       <c r="Z19" t="n">
         <v>11.25</v>
@@ -8554,7 +8554,7 @@
         <v>0.09</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="DG19" t="n">
         <v>2.39</v>
@@ -8566,7 +8566,7 @@
         <v>0.08</v>
       </c>
       <c r="DJ19" t="n">
-        <v>3.52</v>
+        <v>3.61</v>
       </c>
       <c r="DK19" t="n">
         <v>4.61</v>
@@ -8605,7 +8605,7 @@
         <v>49.43</v>
       </c>
       <c r="DW19" t="n">
-        <v>0.39</v>
+        <v>0.43</v>
       </c>
       <c r="DX19" t="n">
         <v>12.04</v>
@@ -8678,7 +8678,7 @@
         <v>15.83</v>
       </c>
       <c r="Q20" t="n">
-        <v>12.33</v>
+        <v>12.25</v>
       </c>
       <c r="R20" t="n">
         <v>6.42</v>
@@ -8990,7 +8990,7 @@
         <v>14.43</v>
       </c>
       <c r="DQ20" t="n">
-        <v>12.82</v>
+        <v>12.78</v>
       </c>
       <c r="DR20" t="n">
         <v>7.3</v>
@@ -9183,7 +9183,7 @@
         <v>0</v>
       </c>
       <c r="AY21" t="n">
-        <v>44.33</v>
+        <v>44.42</v>
       </c>
       <c r="AZ21" t="n">
         <v>0.08</v>
@@ -9408,7 +9408,7 @@
         <v>0</v>
       </c>
       <c r="DV21" t="n">
-        <v>44.96</v>
+        <v>45</v>
       </c>
       <c r="DW21" t="n">
         <v>0.08</v>

--- a/data/teams/leagues/Averages_Spain_Segunda_División_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Spain_Segunda_División_2025-2026.xlsx
@@ -7424,94 +7424,94 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D17" t="n">
         <v>12</v>
       </c>
       <c r="E17" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="F17" t="n">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="G17" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="H17" t="n">
-        <v>81.18000000000001</v>
+        <v>82.67</v>
       </c>
       <c r="I17" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="J17" t="n">
-        <v>3.45</v>
+        <v>3.33</v>
       </c>
       <c r="K17" t="n">
         <v>3</v>
       </c>
       <c r="L17" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="M17" t="n">
-        <v>31.73</v>
+        <v>32.08</v>
       </c>
       <c r="N17" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="O17" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="P17" t="n">
-        <v>18.27</v>
+        <v>17.75</v>
       </c>
       <c r="Q17" t="n">
-        <v>13.18</v>
+        <v>13.08</v>
       </c>
       <c r="R17" t="n">
-        <v>9.550000000000001</v>
+        <v>8.83</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
       </c>
       <c r="T17" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="U17" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="V17" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>45.27</v>
+        <v>44.33</v>
       </c>
       <c r="Y17" t="n">
         <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>10.36</v>
+        <v>10.5</v>
       </c>
       <c r="AA17" t="n">
-        <v>6.73</v>
+        <v>6.75</v>
       </c>
       <c r="AB17" t="n">
-        <v>3.64</v>
+        <v>3.75</v>
       </c>
       <c r="AC17" t="n">
-        <v>20.27</v>
+        <v>19.92</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AE17" t="n">
-        <v>3.45</v>
+        <v>3.33</v>
       </c>
       <c r="AF17" t="n">
         <v>0</v>
@@ -7595,70 +7595,70 @@
         <v>2.67</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.7</v>
+        <v>2.67</v>
       </c>
       <c r="BH17" t="n">
-        <v>8.960000000000001</v>
+        <v>8.83</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.7</v>
+        <v>2.67</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.78</v>
+        <v>0.75</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="BP17" t="n">
         <v>4.04</v>
       </c>
       <c r="BQ17" t="n">
-        <v>4.48</v>
+        <v>4.38</v>
       </c>
       <c r="BR17" t="n">
-        <v>95.65000000000001</v>
+        <v>95.83</v>
       </c>
       <c r="BS17" t="n">
-        <v>65.22</v>
+        <v>66.67</v>
       </c>
       <c r="BT17" t="n">
-        <v>43.48</v>
+        <v>41.67</v>
       </c>
       <c r="BU17" t="n">
-        <v>21.74</v>
+        <v>20.83</v>
       </c>
       <c r="BV17" t="n">
-        <v>13.04</v>
+        <v>12.5</v>
       </c>
       <c r="BW17" t="n">
-        <v>13.04</v>
+        <v>12.5</v>
       </c>
       <c r="BX17" t="n">
-        <v>47.83</v>
+        <v>50</v>
       </c>
       <c r="BY17" t="n">
-        <v>3.15</v>
+        <v>3.12</v>
       </c>
       <c r="BZ17" t="n">
-        <v>3.42</v>
+        <v>3.38</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.42</v>
+        <v>3.4</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.63</v>
+        <v>3.61</v>
       </c>
       <c r="CC17" t="n">
         <v>5.19</v>
@@ -7673,7 +7673,7 @@
         <v>3.02</v>
       </c>
       <c r="CG17" t="n">
-        <v>2.69</v>
+        <v>2.68</v>
       </c>
       <c r="CH17" t="n">
         <v>1.35</v>
@@ -7682,25 +7682,25 @@
         <v>1.84</v>
       </c>
       <c r="CJ17" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CK17" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CL17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="CN17" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CO17" t="n">
         <v>1.34</v>
       </c>
       <c r="CP17" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="CQ17" t="n">
         <v>3.66</v>
@@ -7709,31 +7709,31 @@
         <v>1.47</v>
       </c>
       <c r="CS17" t="n">
-        <v>3.14</v>
+        <v>3.15</v>
       </c>
       <c r="CT17" t="n">
-        <v>2.8</v>
+        <v>2.79</v>
       </c>
       <c r="CU17" t="n">
         <v>1.39</v>
       </c>
       <c r="CV17" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="CW17" t="n">
         <v>1.97</v>
       </c>
       <c r="CX17" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="CY17" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="CZ17" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="DA17" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="DB17" t="n">
         <v>1.37</v>
@@ -7745,79 +7745,79 @@
         <v>3.93</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="DG17" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="DH17" t="n">
-        <v>83.43000000000001</v>
+        <v>84.08</v>
       </c>
       <c r="DI17" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DJ17" t="n">
-        <v>3.13</v>
+        <v>3.08</v>
       </c>
       <c r="DK17" t="n">
-        <v>3.35</v>
+        <v>3.33</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="DM17" t="n">
-        <v>31.78</v>
+        <v>31.96</v>
       </c>
       <c r="DN17" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="DO17" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="DP17" t="n">
-        <v>17.57</v>
+        <v>17.34</v>
       </c>
       <c r="DQ17" t="n">
-        <v>12.35</v>
+        <v>12.33</v>
       </c>
       <c r="DR17" t="n">
-        <v>9.130000000000001</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>43.87</v>
+        <v>43.46</v>
       </c>
       <c r="DW17" t="n">
         <v>0.04</v>
       </c>
       <c r="DX17" t="n">
-        <v>11.7</v>
+        <v>11.71</v>
       </c>
       <c r="DY17" t="n">
-        <v>7.56</v>
+        <v>7.54</v>
       </c>
       <c r="DZ17" t="n">
-        <v>4.13</v>
+        <v>4.16</v>
       </c>
       <c r="EA17" t="n">
-        <v>20.61</v>
+        <v>20.42</v>
       </c>
       <c r="EB17" t="n">
         <v>1.26</v>
       </c>
       <c r="EC17" t="n">
-        <v>3.04</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -9842,13 +9842,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C23" t="n">
         <v>12</v>
       </c>
       <c r="D23" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E23" t="n">
         <v>0.17</v>
@@ -9935,49 +9935,49 @@
         <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AI23" t="n">
-        <v>90.27</v>
+        <v>89.75</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0.09</v>
+        <v>0.17</v>
       </c>
       <c r="AK23" t="n">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="AL23" t="n">
-        <v>3.64</v>
+        <v>3.58</v>
       </c>
       <c r="AM23" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AN23" t="n">
-        <v>37.64</v>
+        <v>37.67</v>
       </c>
       <c r="AO23" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AP23" t="n">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ23" t="n">
-        <v>12.18</v>
+        <v>12.17</v>
       </c>
       <c r="AR23" t="n">
-        <v>18.73</v>
+        <v>18.17</v>
       </c>
       <c r="AS23" t="n">
-        <v>9.18</v>
+        <v>9.17</v>
       </c>
       <c r="AT23" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AU23" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AV23" t="n">
         <v>0</v>
@@ -9989,82 +9989,82 @@
         <v>0</v>
       </c>
       <c r="AY23" t="n">
-        <v>56.82</v>
+        <v>57.58</v>
       </c>
       <c r="AZ23" t="n">
         <v>0</v>
       </c>
       <c r="BA23" t="n">
-        <v>10.36</v>
+        <v>10.42</v>
       </c>
       <c r="BB23" t="n">
-        <v>7.27</v>
+        <v>7.25</v>
       </c>
       <c r="BC23" t="n">
-        <v>3.09</v>
+        <v>3.17</v>
       </c>
       <c r="BD23" t="n">
-        <v>18.36</v>
+        <v>18.58</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="BF23" t="n">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="BG23" t="n">
         <v>2.04</v>
       </c>
       <c r="BH23" t="n">
-        <v>7.48</v>
+        <v>7.42</v>
       </c>
       <c r="BI23" t="n">
         <v>2.04</v>
       </c>
       <c r="BJ23" t="n">
-        <v>0.74</v>
+        <v>0.71</v>
       </c>
       <c r="BK23" t="n">
-        <v>0.43</v>
+        <v>0.42</v>
       </c>
       <c r="BL23" t="n">
-        <v>0.43</v>
+        <v>0.46</v>
       </c>
       <c r="BM23" t="n">
-        <v>0.43</v>
+        <v>0.46</v>
       </c>
       <c r="BN23" t="n">
-        <v>0.87</v>
+        <v>0.92</v>
       </c>
       <c r="BO23" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="BP23" t="n">
-        <v>3.65</v>
+        <v>3.67</v>
       </c>
       <c r="BQ23" t="n">
-        <v>3.83</v>
+        <v>3.75</v>
       </c>
       <c r="BR23" t="n">
-        <v>82.61</v>
+        <v>83.33</v>
       </c>
       <c r="BS23" t="n">
-        <v>56.52</v>
+        <v>58.33</v>
       </c>
       <c r="BT23" t="n">
-        <v>39.13</v>
+        <v>37.5</v>
       </c>
       <c r="BU23" t="n">
-        <v>21.74</v>
+        <v>20.83</v>
       </c>
       <c r="BV23" t="n">
-        <v>4.35</v>
+        <v>4.17</v>
       </c>
       <c r="BW23" t="n">
         <v>0</v>
       </c>
       <c r="BX23" t="n">
-        <v>52.17</v>
+        <v>54.17</v>
       </c>
       <c r="BY23" t="n">
         <v>1.83</v>
@@ -10073,22 +10073,22 @@
         <v>1.87</v>
       </c>
       <c r="CA23" t="n">
-        <v>3.21</v>
+        <v>3.2</v>
       </c>
       <c r="CB23" t="n">
-        <v>3.33</v>
+        <v>3.32</v>
       </c>
       <c r="CC23" t="n">
-        <v>2.99</v>
+        <v>2.96</v>
       </c>
       <c r="CD23" t="n">
-        <v>3.34</v>
+        <v>3.29</v>
       </c>
       <c r="CE23" t="n">
         <v>1.47</v>
       </c>
       <c r="CF23" t="n">
-        <v>3.2</v>
+        <v>3.19</v>
       </c>
       <c r="CG23" t="n">
         <v>2.54</v>
@@ -10100,16 +10100,16 @@
         <v>1.81</v>
       </c>
       <c r="CJ23" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="CK23" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="CL23" t="n">
         <v>2.3</v>
       </c>
       <c r="CM23" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="CN23" t="n">
         <v>1.65</v>
@@ -10118,40 +10118,40 @@
         <v>1.39</v>
       </c>
       <c r="CP23" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="CQ23" t="n">
-        <v>4.11</v>
+        <v>4.09</v>
       </c>
       <c r="CR23" t="n">
         <v>1.51</v>
       </c>
       <c r="CS23" t="n">
-        <v>3.21</v>
+        <v>3.22</v>
       </c>
       <c r="CT23" t="n">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="CU23" t="n">
         <v>1.37</v>
       </c>
       <c r="CV23" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CW23" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="CX23" t="n">
         <v>1.78</v>
       </c>
       <c r="CY23" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="CZ23" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="DA23" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="DB23" t="n">
         <v>1.43</v>
@@ -10160,49 +10160,49 @@
         <v>2.36</v>
       </c>
       <c r="DD23" t="n">
-        <v>4.46</v>
+        <v>4.43</v>
       </c>
       <c r="DE23" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DF23" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="DG23" t="n">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="DH23" t="n">
-        <v>94.73999999999999</v>
+        <v>94.29000000000001</v>
       </c>
       <c r="DI23" t="n">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="DJ23" t="n">
-        <v>2.31</v>
+        <v>2.25</v>
       </c>
       <c r="DK23" t="n">
-        <v>3.92</v>
+        <v>3.88</v>
       </c>
       <c r="DL23" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DM23" t="n">
-        <v>38.83</v>
+        <v>38.8</v>
       </c>
       <c r="DN23" t="n">
-        <v>0.52</v>
+        <v>0.54</v>
       </c>
       <c r="DO23" t="n">
-        <v>2.17</v>
+        <v>2.21</v>
       </c>
       <c r="DP23" t="n">
-        <v>12.87</v>
+        <v>12.84</v>
       </c>
       <c r="DQ23" t="n">
-        <v>17.26</v>
+        <v>17.05</v>
       </c>
       <c r="DR23" t="n">
-        <v>7.56</v>
+        <v>7.62</v>
       </c>
       <c r="DS23" t="n">
         <v>0</v>
@@ -10214,28 +10214,28 @@
         <v>0</v>
       </c>
       <c r="DV23" t="n">
-        <v>56.13</v>
+        <v>56.54</v>
       </c>
       <c r="DW23" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DX23" t="n">
-        <v>11.39</v>
+        <v>11.38</v>
       </c>
       <c r="DY23" t="n">
-        <v>7.52</v>
+        <v>7.5</v>
       </c>
       <c r="DZ23" t="n">
-        <v>3.87</v>
+        <v>3.88</v>
       </c>
       <c r="EA23" t="n">
-        <v>18.82</v>
+        <v>18.92</v>
       </c>
       <c r="EB23" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="EC23" t="n">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Spain_Segunda_División_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Spain_Segunda_División_2025-2026.xlsx
@@ -1379,94 +1379,94 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D2" t="n">
         <v>12</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="F2" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="G2" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="H2" t="n">
+        <v>90.33</v>
+      </c>
+      <c r="I2" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="K2" t="n">
+        <v>5.58</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M2" t="n">
+        <v>44.58</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="O2" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="P2" t="n">
+        <v>9.42</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>8.17</v>
+      </c>
+      <c r="R2" t="n">
+        <v>6.17</v>
+      </c>
+      <c r="S2" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="n">
+        <v>43.08</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>10.08</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>4.42</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>24.33</v>
+      </c>
+      <c r="AD2" t="n">
         <v>1.55</v>
       </c>
-      <c r="G2" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="H2" t="n">
-        <v>92</v>
-      </c>
-      <c r="I2" t="n">
-        <v>-0.09</v>
-      </c>
-      <c r="J2" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="K2" t="n">
-        <v>5.55</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="M2" t="n">
-        <v>45</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="O2" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="P2" t="n">
-        <v>9.27</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>8.18</v>
-      </c>
-      <c r="R2" t="n">
-        <v>6.27</v>
-      </c>
-      <c r="S2" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V2" t="n">
-        <v>0</v>
-      </c>
-      <c r="W2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X2" t="n">
-        <v>43.64</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>14.91</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>10.45</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>24.73</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>1.58</v>
-      </c>
       <c r="AE2" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AF2" t="n">
         <v>0.25</v>
@@ -1550,67 +1550,67 @@
         <v>2.42</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.7</v>
+        <v>2.67</v>
       </c>
       <c r="BH2" t="n">
-        <v>10.74</v>
+        <v>10.71</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.7</v>
+        <v>2.67</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.43</v>
+        <v>0.46</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.43</v>
+        <v>0.42</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="BP2" t="n">
-        <v>5</v>
+        <v>4.92</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.7</v>
+        <v>5.75</v>
       </c>
       <c r="BR2" t="n">
-        <v>82.61</v>
+        <v>83.33</v>
       </c>
       <c r="BS2" t="n">
-        <v>60.87</v>
+        <v>62.5</v>
       </c>
       <c r="BT2" t="n">
-        <v>47.83</v>
+        <v>45.83</v>
       </c>
       <c r="BU2" t="n">
-        <v>34.78</v>
+        <v>33.33</v>
       </c>
       <c r="BV2" t="n">
-        <v>21.74</v>
+        <v>20.83</v>
       </c>
       <c r="BW2" t="n">
-        <v>8.699999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="BX2" t="n">
-        <v>52.17</v>
+        <v>50</v>
       </c>
       <c r="BY2" t="n">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="BZ2" t="n">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.29</v>
+        <v>3.3</v>
       </c>
       <c r="CB2" t="n">
         <v>3.48</v>
@@ -1625,7 +1625,7 @@
         <v>1.39</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="CG2" t="n">
         <v>2.84</v>
@@ -1634,22 +1634,22 @@
         <v>1.4</v>
       </c>
       <c r="CI2" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CJ2" t="n">
         <v>1.76</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CL2" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.43</v>
+        <v>2.44</v>
       </c>
       <c r="CN2" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CO2" t="n">
         <v>1.28</v>
@@ -1658,22 +1658,22 @@
         <v>1.95</v>
       </c>
       <c r="CQ2" t="n">
-        <v>3.3</v>
+        <v>3.29</v>
       </c>
       <c r="CR2" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CS2" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="CT2" t="n">
-        <v>2.98</v>
+        <v>2.97</v>
       </c>
       <c r="CU2" t="n">
         <v>1.43</v>
       </c>
       <c r="CV2" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="CW2" t="n">
         <v>1.8</v>
@@ -1697,82 +1697,82 @@
         <v>2.01</v>
       </c>
       <c r="DD2" t="n">
-        <v>3.47</v>
+        <v>3.48</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.13</v>
+        <v>0.16</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.65</v>
+        <v>2.66</v>
       </c>
       <c r="DH2" t="n">
-        <v>88.83</v>
+        <v>88.12</v>
       </c>
       <c r="DI2" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="DK2" t="n">
-        <v>5.26</v>
+        <v>5.29</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="DM2" t="n">
-        <v>43.61</v>
+        <v>43.46</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="DP2" t="n">
-        <v>10.91</v>
+        <v>10.92</v>
       </c>
       <c r="DQ2" t="n">
-        <v>10.74</v>
+        <v>10.62</v>
       </c>
       <c r="DR2" t="n">
-        <v>7.65</v>
+        <v>7.54</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>43.53</v>
+        <v>43.25</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DX2" t="n">
-        <v>13.56</v>
+        <v>13.42</v>
       </c>
       <c r="DY2" t="n">
-        <v>9.039999999999999</v>
+        <v>8.92</v>
       </c>
       <c r="DZ2" t="n">
-        <v>4.52</v>
+        <v>4.5</v>
       </c>
       <c r="EA2" t="n">
-        <v>24.48</v>
+        <v>24.29</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="3">
@@ -1782,94 +1782,94 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D3" t="n">
         <v>12</v>
       </c>
       <c r="E3" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="G3" t="n">
-        <v>3.64</v>
+        <v>3.33</v>
       </c>
       <c r="H3" t="n">
-        <v>100.64</v>
+        <v>100.67</v>
       </c>
       <c r="I3" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="J3" t="n">
-        <v>2.82</v>
+        <v>2.75</v>
       </c>
       <c r="K3" t="n">
-        <v>7.27</v>
+        <v>7.08</v>
       </c>
       <c r="L3" t="n">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="M3" t="n">
-        <v>52.64</v>
+        <v>52.25</v>
       </c>
       <c r="N3" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="O3" t="n">
-        <v>3.55</v>
+        <v>3.67</v>
       </c>
       <c r="P3" t="n">
-        <v>14.36</v>
+        <v>14.92</v>
       </c>
       <c r="Q3" t="n">
-        <v>11.55</v>
+        <v>11.58</v>
       </c>
       <c r="R3" t="n">
-        <v>7.64</v>
+        <v>7.75</v>
       </c>
       <c r="S3" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="T3" t="n">
-        <v>2.18</v>
+        <v>2.33</v>
       </c>
       <c r="U3" t="n">
-        <v>0.27</v>
+        <v>0.42</v>
       </c>
       <c r="V3" t="n">
-        <v>0.27</v>
+        <v>0.42</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>56</v>
+        <v>55.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="Z3" t="n">
-        <v>17.45</v>
+        <v>17.33</v>
       </c>
       <c r="AA3" t="n">
-        <v>10.45</v>
+        <v>10.17</v>
       </c>
       <c r="AB3" t="n">
-        <v>7</v>
+        <v>7.17</v>
       </c>
       <c r="AC3" t="n">
-        <v>17.82</v>
+        <v>18.33</v>
       </c>
       <c r="AD3" t="n">
         <v>1.97</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="AF3" t="n">
         <v>0</v>
@@ -1953,19 +1953,19 @@
         <v>3.08</v>
       </c>
       <c r="BG3" t="n">
-        <v>3.22</v>
+        <v>3.33</v>
       </c>
       <c r="BH3" t="n">
-        <v>9.130000000000001</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.22</v>
+        <v>3.33</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.7</v>
+        <v>0.79</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.48</v>
+        <v>0.5</v>
       </c>
       <c r="BL3" t="n">
         <v>1.04</v>
@@ -1977,34 +1977,34 @@
         <v>2.04</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="BP3" t="n">
-        <v>3.74</v>
+        <v>3.79</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5.09</v>
+        <v>4.96</v>
       </c>
       <c r="BR3" t="n">
-        <v>95.65000000000001</v>
+        <v>95.83</v>
       </c>
       <c r="BS3" t="n">
-        <v>78.26000000000001</v>
+        <v>79.17</v>
       </c>
       <c r="BT3" t="n">
-        <v>69.56999999999999</v>
+        <v>70.83</v>
       </c>
       <c r="BU3" t="n">
-        <v>39.13</v>
+        <v>41.67</v>
       </c>
       <c r="BV3" t="n">
-        <v>21.74</v>
+        <v>25</v>
       </c>
       <c r="BW3" t="n">
-        <v>8.699999999999999</v>
+        <v>12.5</v>
       </c>
       <c r="BX3" t="n">
-        <v>69.56999999999999</v>
+        <v>70.83</v>
       </c>
       <c r="BY3" t="n">
         <v>1.73</v>
@@ -2016,7 +2016,7 @@
         <v>3.41</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.58</v>
+        <v>3.59</v>
       </c>
       <c r="CC3" t="n">
         <v>2.56</v>
@@ -2031,7 +2031,7 @@
         <v>2.72</v>
       </c>
       <c r="CG3" t="n">
-        <v>2.91</v>
+        <v>2.92</v>
       </c>
       <c r="CH3" t="n">
         <v>1.43</v>
@@ -2046,7 +2046,7 @@
         <v>1.52</v>
       </c>
       <c r="CL3" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="CM3" t="n">
         <v>2.34</v>
@@ -2061,7 +2061,7 @@
         <v>1.9</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.19</v>
+        <v>3.17</v>
       </c>
       <c r="CR3" t="n">
         <v>1.4</v>
@@ -2070,7 +2070,7 @@
         <v>2.93</v>
       </c>
       <c r="CT3" t="n">
-        <v>3.06</v>
+        <v>3.07</v>
       </c>
       <c r="CU3" t="n">
         <v>1.44</v>
@@ -2100,82 +2100,82 @@
         <v>1.94</v>
       </c>
       <c r="DD3" t="n">
-        <v>3.33</v>
+        <v>3.32</v>
       </c>
       <c r="DE3" t="n">
         <v>0.04</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="DG3" t="n">
-        <v>2.61</v>
+        <v>2.5</v>
       </c>
       <c r="DH3" t="n">
-        <v>94.31</v>
+        <v>94.58</v>
       </c>
       <c r="DI3" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ3" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="DK3" t="n">
         <v>5.08</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.26</v>
+        <v>0.38</v>
       </c>
       <c r="DM3" t="n">
-        <v>45.52</v>
+        <v>45.62</v>
       </c>
       <c r="DN3" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="DO3" t="n">
-        <v>2.26</v>
+        <v>2.38</v>
       </c>
       <c r="DP3" t="n">
-        <v>14.08</v>
+        <v>14.38</v>
       </c>
       <c r="DQ3" t="n">
-        <v>13.22</v>
+        <v>13.16</v>
       </c>
       <c r="DR3" t="n">
-        <v>7.7</v>
+        <v>7.75</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.26</v>
+        <v>0.34</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.26</v>
+        <v>0.34</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>54.39</v>
+        <v>54.21</v>
       </c>
       <c r="DW3" t="n">
         <v>0.08</v>
       </c>
       <c r="DX3" t="n">
-        <v>15.52</v>
+        <v>15.54</v>
       </c>
       <c r="DY3" t="n">
-        <v>9.82</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="DZ3" t="n">
-        <v>5.7</v>
+        <v>5.84</v>
       </c>
       <c r="EA3" t="n">
-        <v>19.52</v>
+        <v>19.7</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.87</v>
+        <v>2.83</v>
       </c>
     </row>
     <row r="4">
@@ -2185,10 +2185,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D4" t="n">
         <v>11</v>
@@ -2197,82 +2197,82 @@
         <v>0.08</v>
       </c>
       <c r="F4" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="G4" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>97.33</v>
+        <v>95.15000000000001</v>
       </c>
       <c r="I4" t="n">
         <v>-0.08</v>
       </c>
       <c r="J4" t="n">
-        <v>2.83</v>
+        <v>2.92</v>
       </c>
       <c r="K4" t="n">
-        <v>3.83</v>
+        <v>3.62</v>
       </c>
       <c r="L4" t="n">
         <v>0.08</v>
       </c>
       <c r="M4" t="n">
-        <v>47.67</v>
+        <v>45.77</v>
       </c>
       <c r="N4" t="n">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="O4" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="P4" t="n">
-        <v>13.67</v>
+        <v>14</v>
       </c>
       <c r="Q4" t="n">
-        <v>14.25</v>
+        <v>13.92</v>
       </c>
       <c r="R4" t="n">
-        <v>8.67</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="S4" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="T4" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="U4" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="V4" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>50.58</v>
+        <v>49.46</v>
       </c>
       <c r="Y4" t="n">
         <v>0.08</v>
       </c>
       <c r="Z4" t="n">
-        <v>10.75</v>
+        <v>10.54</v>
       </c>
       <c r="AA4" t="n">
-        <v>7.58</v>
+        <v>7.31</v>
       </c>
       <c r="AB4" t="n">
-        <v>3.17</v>
+        <v>3.23</v>
       </c>
       <c r="AC4" t="n">
-        <v>26.17</v>
+        <v>25.31</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="AF4" t="n">
         <v>0.09</v>
@@ -2356,58 +2356,58 @@
         <v>2.64</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.13</v>
+        <v>2.17</v>
       </c>
       <c r="BH4" t="n">
-        <v>8.26</v>
+        <v>8.17</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.13</v>
+        <v>2.17</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.39</v>
+        <v>0.38</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.57</v>
+        <v>0.58</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.13</v>
+        <v>1.21</v>
       </c>
       <c r="BO4" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="BP4" t="n">
         <v>3.96</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.3</v>
+        <v>4.21</v>
       </c>
       <c r="BR4" t="n">
-        <v>86.95999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="BS4" t="n">
-        <v>60.87</v>
+        <v>62.5</v>
       </c>
       <c r="BT4" t="n">
-        <v>39.13</v>
+        <v>41.67</v>
       </c>
       <c r="BU4" t="n">
-        <v>13.04</v>
+        <v>12.5</v>
       </c>
       <c r="BV4" t="n">
-        <v>8.699999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="BW4" t="n">
-        <v>4.35</v>
+        <v>4.17</v>
       </c>
       <c r="BX4" t="n">
-        <v>43.48</v>
+        <v>45.83</v>
       </c>
       <c r="BY4" t="n">
         <v>2.26</v>
@@ -2419,7 +2419,7 @@
         <v>2.99</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.09</v>
+        <v>3.08</v>
       </c>
       <c r="CC4" t="n">
         <v>3.76</v>
@@ -2434,22 +2434,22 @@
         <v>3.52</v>
       </c>
       <c r="CG4" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="CH4" t="n">
         <v>1.25</v>
       </c>
       <c r="CI4" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CJ4" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="CK4" t="n">
         <v>1.71</v>
       </c>
       <c r="CL4" t="n">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="CM4" t="n">
         <v>2.05</v>
@@ -2461,19 +2461,19 @@
         <v>1.52</v>
       </c>
       <c r="CP4" t="n">
-        <v>2.57</v>
+        <v>2.6</v>
       </c>
       <c r="CQ4" t="n">
-        <v>5.04</v>
+        <v>5.06</v>
       </c>
       <c r="CR4" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="CS4" t="n">
         <v>3.4</v>
       </c>
       <c r="CT4" t="n">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="CU4" t="n">
         <v>1.33</v>
@@ -2482,13 +2482,13 @@
         <v>1.68</v>
       </c>
       <c r="CW4" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="CX4" t="n">
         <v>1.76</v>
       </c>
       <c r="CY4" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="CZ4" t="n">
         <v>2.07</v>
@@ -2500,85 +2500,85 @@
         <v>1.56</v>
       </c>
       <c r="DC4" t="n">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="DD4" t="n">
-        <v>5.57</v>
+        <v>5.61</v>
       </c>
       <c r="DE4" t="n">
         <v>0.08</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="DH4" t="n">
-        <v>92.73999999999999</v>
+        <v>91.75</v>
       </c>
       <c r="DI4" t="n">
         <v>-0.04</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.74</v>
+        <v>2.79</v>
       </c>
       <c r="DK4" t="n">
-        <v>3.91</v>
+        <v>3.79</v>
       </c>
       <c r="DL4" t="n">
         <v>0.17</v>
       </c>
       <c r="DM4" t="n">
-        <v>43</v>
+        <v>42.17</v>
       </c>
       <c r="DN4" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="DO4" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="DP4" t="n">
-        <v>13.74</v>
+        <v>13.92</v>
       </c>
       <c r="DQ4" t="n">
-        <v>14.82</v>
+        <v>14.62</v>
       </c>
       <c r="DR4" t="n">
-        <v>8.869999999999999</v>
+        <v>8.84</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>47.78</v>
+        <v>47.29</v>
       </c>
       <c r="DW4" t="n">
         <v>0.04</v>
       </c>
       <c r="DX4" t="n">
-        <v>10.22</v>
+        <v>10.13</v>
       </c>
       <c r="DY4" t="n">
-        <v>7.22</v>
+        <v>7.09</v>
       </c>
       <c r="DZ4" t="n">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="EA4" t="n">
-        <v>23.96</v>
+        <v>23.59</v>
       </c>
       <c r="EB4" t="n">
         <v>1.17</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="5">
@@ -2588,94 +2588,94 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D5" t="n">
         <v>12</v>
       </c>
       <c r="E5" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="F5" t="n">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="G5" t="n">
-        <v>3.09</v>
+        <v>3.17</v>
       </c>
       <c r="H5" t="n">
-        <v>104.82</v>
+        <v>102.75</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>3.64</v>
+        <v>3.58</v>
       </c>
       <c r="K5" t="n">
-        <v>6.27</v>
+        <v>6.25</v>
       </c>
       <c r="L5" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="M5" t="n">
-        <v>59.73</v>
+        <v>58.67</v>
       </c>
       <c r="N5" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="O5" t="n">
-        <v>3.18</v>
+        <v>3.08</v>
       </c>
       <c r="P5" t="n">
-        <v>14.18</v>
+        <v>15.25</v>
       </c>
       <c r="Q5" t="n">
-        <v>14.09</v>
+        <v>13.92</v>
       </c>
       <c r="R5" t="n">
         <v>5</v>
       </c>
       <c r="S5" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="T5" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="U5" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="V5" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>56.55</v>
+        <v>55.08</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="Z5" t="n">
-        <v>16.18</v>
+        <v>16.33</v>
       </c>
       <c r="AA5" t="n">
-        <v>10.45</v>
+        <v>10.58</v>
       </c>
       <c r="AB5" t="n">
-        <v>5.73</v>
+        <v>5.75</v>
       </c>
       <c r="AC5" t="n">
-        <v>18.18</v>
+        <v>17.58</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AE5" t="n">
-        <v>3.18</v>
+        <v>3.17</v>
       </c>
       <c r="AF5" t="n">
         <v>0.08</v>
@@ -2759,70 +2759,70 @@
         <v>2.5</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="BH5" t="n">
-        <v>10.26</v>
+        <v>10.33</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.96</v>
+        <v>0.92</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="BP5" t="n">
-        <v>5.17</v>
+        <v>5.12</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.09</v>
+        <v>5.21</v>
       </c>
       <c r="BR5" t="n">
-        <v>82.61</v>
+        <v>83.33</v>
       </c>
       <c r="BS5" t="n">
-        <v>60.87</v>
+        <v>62.5</v>
       </c>
       <c r="BT5" t="n">
-        <v>47.83</v>
+        <v>45.83</v>
       </c>
       <c r="BU5" t="n">
-        <v>39.13</v>
+        <v>37.5</v>
       </c>
       <c r="BV5" t="n">
-        <v>13.04</v>
+        <v>12.5</v>
       </c>
       <c r="BW5" t="n">
-        <v>8.699999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="BX5" t="n">
-        <v>52.17</v>
+        <v>50</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="BZ5" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.58</v>
+        <v>3.62</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.86</v>
+        <v>3.9</v>
       </c>
       <c r="CC5" t="n">
         <v>2.66</v>
@@ -2834,10 +2834,10 @@
         <v>1.34</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="CG5" t="n">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="CH5" t="n">
         <v>1.46</v>
@@ -2852,7 +2852,7 @@
         <v>1.53</v>
       </c>
       <c r="CL5" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CM5" t="n">
         <v>2.36</v>
@@ -2864,16 +2864,16 @@
         <v>1.22</v>
       </c>
       <c r="CP5" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CQ5" t="n">
-        <v>2.91</v>
+        <v>2.89</v>
       </c>
       <c r="CR5" t="n">
         <v>1.38</v>
       </c>
       <c r="CS5" t="n">
-        <v>2.79</v>
+        <v>2.77</v>
       </c>
       <c r="CT5" t="n">
         <v>3.14</v>
@@ -2909,76 +2909,76 @@
         <v>3.09</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DF5" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="DG5" t="n">
-        <v>3.17</v>
+        <v>3.21</v>
       </c>
       <c r="DH5" t="n">
-        <v>98.73999999999999</v>
+        <v>97.95999999999999</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DJ5" t="n">
-        <v>3.13</v>
+        <v>3.12</v>
       </c>
       <c r="DK5" t="n">
-        <v>6.56</v>
+        <v>6.54</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="DM5" t="n">
-        <v>58.83</v>
+        <v>58.34</v>
       </c>
       <c r="DN5" t="n">
         <v>0.96</v>
       </c>
       <c r="DO5" t="n">
-        <v>3.39</v>
+        <v>3.33</v>
       </c>
       <c r="DP5" t="n">
-        <v>13.69</v>
+        <v>14.25</v>
       </c>
       <c r="DQ5" t="n">
-        <v>13.65</v>
+        <v>13.58</v>
       </c>
       <c r="DR5" t="n">
-        <v>5.48</v>
+        <v>5.46</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>55.39</v>
+        <v>54.71</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DX5" t="n">
-        <v>14.48</v>
+        <v>14.62</v>
       </c>
       <c r="DY5" t="n">
-        <v>9.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="DZ5" t="n">
-        <v>4.87</v>
+        <v>4.92</v>
       </c>
       <c r="EA5" t="n">
-        <v>19</v>
+        <v>18.66</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="EC5" t="n">
         <v>2.83</v>
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C6" t="n">
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E6" t="n">
         <v>0.17</v>
@@ -3081,139 +3081,139 @@
         <v>2.58</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AI6" t="n">
-        <v>81.27</v>
+        <v>79.92</v>
       </c>
       <c r="AJ6" t="n">
         <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.64</v>
+        <v>2.67</v>
       </c>
       <c r="AL6" t="n">
-        <v>3.64</v>
+        <v>3.5</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AN6" t="n">
-        <v>36.73</v>
+        <v>36.67</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.73</v>
+        <v>0.83</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AQ6" t="n">
-        <v>12.55</v>
+        <v>12.67</v>
       </c>
       <c r="AR6" t="n">
-        <v>12.82</v>
+        <v>13.42</v>
       </c>
       <c r="AS6" t="n">
-        <v>8.73</v>
+        <v>8.33</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.64</v>
+        <v>1.83</v>
       </c>
       <c r="AU6" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="AX6" t="n">
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>48.18</v>
+        <v>48.33</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="BA6" t="n">
-        <v>9.18</v>
+        <v>9.75</v>
       </c>
       <c r="BB6" t="n">
-        <v>6.55</v>
+        <v>7</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.64</v>
+        <v>2.75</v>
       </c>
       <c r="BD6" t="n">
-        <v>21.36</v>
+        <v>21.58</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="BF6" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.52</v>
+        <v>2.67</v>
       </c>
       <c r="BH6" t="n">
-        <v>9.390000000000001</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.52</v>
+        <v>2.67</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.96</v>
+        <v>1.04</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.48</v>
+        <v>0.5</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.57</v>
+        <v>0.58</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.52</v>
+        <v>0.54</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.43</v>
+        <v>1.54</v>
       </c>
       <c r="BP6" t="n">
-        <v>3.87</v>
+        <v>3.92</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.26</v>
+        <v>5.12</v>
       </c>
       <c r="BR6" t="n">
-        <v>91.3</v>
+        <v>91.67</v>
       </c>
       <c r="BS6" t="n">
-        <v>69.56999999999999</v>
+        <v>70.83</v>
       </c>
       <c r="BT6" t="n">
-        <v>52.17</v>
+        <v>54.17</v>
       </c>
       <c r="BU6" t="n">
-        <v>21.74</v>
+        <v>25</v>
       </c>
       <c r="BV6" t="n">
-        <v>13.04</v>
+        <v>16.67</v>
       </c>
       <c r="BW6" t="n">
-        <v>4.35</v>
+        <v>8.33</v>
       </c>
       <c r="BX6" t="n">
-        <v>52.17</v>
+        <v>54.17</v>
       </c>
       <c r="BY6" t="n">
         <v>2.39</v>
@@ -3222,13 +3222,13 @@
         <v>2.54</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.19</v>
+        <v>3.2</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.3</v>
+        <v>3.33</v>
       </c>
       <c r="CC6" t="n">
-        <v>3.99</v>
+        <v>4.03</v>
       </c>
       <c r="CD6" t="n">
         <v>4.37</v>
@@ -3237,154 +3237,154 @@
         <v>1.45</v>
       </c>
       <c r="CF6" t="n">
-        <v>3.06</v>
+        <v>3.04</v>
       </c>
       <c r="CG6" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="CH6" t="n">
         <v>1.34</v>
       </c>
       <c r="CI6" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CJ6" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CK6" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CL6" t="n">
         <v>2.2</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="CN6" t="n">
         <v>1.68</v>
       </c>
       <c r="CO6" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CP6" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="CQ6" t="n">
-        <v>4</v>
+        <v>3.96</v>
       </c>
       <c r="CR6" t="n">
         <v>1.47</v>
       </c>
       <c r="CS6" t="n">
-        <v>3.16</v>
+        <v>3.14</v>
       </c>
       <c r="CT6" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="CU6" t="n">
         <v>1.39</v>
       </c>
       <c r="CV6" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CW6" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CX6" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CY6" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="CZ6" t="n">
         <v>2.16</v>
       </c>
       <c r="DA6" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="DB6" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="DC6" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="DD6" t="n">
-        <v>4.11</v>
+        <v>4.07</v>
       </c>
       <c r="DE6" t="n">
         <v>0.17</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="DH6" t="n">
-        <v>89.56999999999999</v>
+        <v>88.54000000000001</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="DK6" t="n">
-        <v>4.61</v>
+        <v>4.5</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.43</v>
+        <v>0.42</v>
       </c>
       <c r="DM6" t="n">
-        <v>46.22</v>
+        <v>45.79</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.96</v>
+        <v>1</v>
       </c>
       <c r="DO6" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="DP6" t="n">
-        <v>13.79</v>
+        <v>13.8</v>
       </c>
       <c r="DQ6" t="n">
-        <v>12.91</v>
+        <v>13.21</v>
       </c>
       <c r="DR6" t="n">
-        <v>7.09</v>
+        <v>6.96</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.17</v>
+        <v>0.2</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.17</v>
+        <v>0.2</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>50.56</v>
+        <v>50.54</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DX6" t="n">
-        <v>11.13</v>
+        <v>11.34</v>
       </c>
       <c r="DY6" t="n">
-        <v>7.26</v>
+        <v>7.46</v>
       </c>
       <c r="DZ6" t="n">
-        <v>3.87</v>
+        <v>3.88</v>
       </c>
       <c r="EA6" t="n">
-        <v>20.91</v>
+        <v>21.04</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="7">
@@ -3394,61 +3394,61 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D7" t="n">
         <v>12</v>
       </c>
       <c r="E7" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="F7" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="G7" t="n">
-        <v>3.36</v>
+        <v>3.42</v>
       </c>
       <c r="H7" t="n">
-        <v>93.09</v>
+        <v>91.83</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>1.36</v>
+        <v>1.58</v>
       </c>
       <c r="K7" t="n">
-        <v>4.73</v>
+        <v>4.67</v>
       </c>
       <c r="L7" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="M7" t="n">
-        <v>43.73</v>
+        <v>43.83</v>
       </c>
       <c r="N7" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="O7" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="P7" t="n">
-        <v>11.36</v>
+        <v>11.42</v>
       </c>
       <c r="Q7" t="n">
-        <v>13.18</v>
+        <v>12.92</v>
       </c>
       <c r="R7" t="n">
-        <v>7.64</v>
+        <v>8</v>
       </c>
       <c r="S7" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T7" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -3460,28 +3460,28 @@
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>54.45</v>
+        <v>53.42</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="Z7" t="n">
-        <v>11.45</v>
+        <v>11.58</v>
       </c>
       <c r="AA7" t="n">
-        <v>7.82</v>
+        <v>8.08</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.64</v>
+        <v>3.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>19.36</v>
+        <v>19.25</v>
       </c>
       <c r="AD7" t="n">
         <v>1.3</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.18</v>
+        <v>1.42</v>
       </c>
       <c r="AF7" t="n">
         <v>0.17</v>
@@ -3565,70 +3565,70 @@
         <v>2</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="BH7" t="n">
-        <v>9.26</v>
+        <v>9.33</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.74</v>
+        <v>0.71</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.83</v>
+        <v>0.79</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.57</v>
+        <v>0.54</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.57</v>
+        <v>0.58</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="BP7" t="n">
-        <v>3.91</v>
+        <v>3.92</v>
       </c>
       <c r="BQ7" t="n">
-        <v>5.35</v>
+        <v>5.42</v>
       </c>
       <c r="BR7" t="n">
-        <v>91.3</v>
+        <v>91.67</v>
       </c>
       <c r="BS7" t="n">
-        <v>60.87</v>
+        <v>58.33</v>
       </c>
       <c r="BT7" t="n">
-        <v>47.83</v>
+        <v>45.83</v>
       </c>
       <c r="BU7" t="n">
-        <v>34.78</v>
+        <v>33.33</v>
       </c>
       <c r="BV7" t="n">
-        <v>21.74</v>
+        <v>20.83</v>
       </c>
       <c r="BW7" t="n">
-        <v>13.04</v>
+        <v>12.5</v>
       </c>
       <c r="BX7" t="n">
-        <v>43.48</v>
+        <v>41.67</v>
       </c>
       <c r="BY7" t="n">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="BZ7" t="n">
-        <v>2.72</v>
+        <v>2.77</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.35</v>
+        <v>3.34</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.48</v>
+        <v>3.47</v>
       </c>
       <c r="CC7" t="n">
         <v>4.7</v>
@@ -3643,16 +3643,16 @@
         <v>2.94</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="CH7" t="n">
         <v>1.36</v>
       </c>
       <c r="CI7" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="CJ7" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CK7" t="n">
         <v>1.58</v>
@@ -3670,22 +3670,22 @@
         <v>1.32</v>
       </c>
       <c r="CP7" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="CQ7" t="n">
-        <v>3.68</v>
+        <v>3.7</v>
       </c>
       <c r="CR7" t="n">
         <v>1.45</v>
       </c>
       <c r="CS7" t="n">
-        <v>3.15</v>
+        <v>3.16</v>
       </c>
       <c r="CT7" t="n">
-        <v>2.88</v>
+        <v>2.87</v>
       </c>
       <c r="CU7" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CV7" t="n">
         <v>1.95</v>
@@ -3703,7 +3703,7 @@
         <v>2.25</v>
       </c>
       <c r="DA7" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="DB7" t="n">
         <v>1.37</v>
@@ -3712,82 +3712,82 @@
         <v>2.17</v>
       </c>
       <c r="DD7" t="n">
-        <v>3.9</v>
+        <v>3.92</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.26</v>
+        <v>1.34</v>
       </c>
       <c r="DG7" t="n">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="DH7" t="n">
-        <v>84.34999999999999</v>
+        <v>84.08</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DJ7" t="n">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="DK7" t="n">
-        <v>4.18</v>
+        <v>4.17</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="DM7" t="n">
-        <v>37.83</v>
+        <v>38.12</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.48</v>
+        <v>0.5</v>
       </c>
       <c r="DO7" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="DP7" t="n">
         <v>12.04</v>
       </c>
       <c r="DQ7" t="n">
-        <v>12.43</v>
+        <v>12.34</v>
       </c>
       <c r="DR7" t="n">
-        <v>8.779999999999999</v>
+        <v>8.92</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>48.56</v>
+        <v>48.29</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DX7" t="n">
-        <v>11.43</v>
+        <v>11.5</v>
       </c>
       <c r="DY7" t="n">
-        <v>7.26</v>
+        <v>7.42</v>
       </c>
       <c r="DZ7" t="n">
-        <v>4.18</v>
+        <v>4.08</v>
       </c>
       <c r="EA7" t="n">
-        <v>18.56</v>
+        <v>18.54</v>
       </c>
       <c r="EB7" t="n">
         <v>1.29</v>
       </c>
       <c r="EC7" t="n">
-        <v>1.61</v>
+        <v>1.71</v>
       </c>
     </row>
     <row r="8">
@@ -3797,13 +3797,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C8" t="n">
         <v>12</v>
       </c>
       <c r="D8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E8" t="n">
         <v>0.08</v>
@@ -3887,52 +3887,52 @@
         <v>3.25</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.36</v>
+        <v>2.08</v>
       </c>
       <c r="AI8" t="n">
-        <v>86.73</v>
+        <v>87.08</v>
       </c>
       <c r="AJ8" t="n">
         <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AL8" t="n">
-        <v>4.27</v>
+        <v>4.25</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.09</v>
+        <v>0</v>
       </c>
       <c r="AN8" t="n">
-        <v>31.82</v>
+        <v>32.92</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.91</v>
+        <v>1.67</v>
       </c>
       <c r="AQ8" t="n">
-        <v>15.09</v>
+        <v>14.75</v>
       </c>
       <c r="AR8" t="n">
-        <v>11.91</v>
+        <v>12</v>
       </c>
       <c r="AS8" t="n">
-        <v>10</v>
+        <v>9.58</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AU8" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AV8" t="n">
         <v>0</v>
@@ -3944,82 +3944,82 @@
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>42.09</v>
+        <v>42.58</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="BA8" t="n">
-        <v>8.550000000000001</v>
+        <v>8.75</v>
       </c>
       <c r="BB8" t="n">
-        <v>5.73</v>
+        <v>6.08</v>
       </c>
       <c r="BC8" t="n">
-        <v>2.82</v>
+        <v>2.67</v>
       </c>
       <c r="BD8" t="n">
-        <v>19.27</v>
+        <v>19.17</v>
       </c>
       <c r="BE8" t="n">
         <v>0.98</v>
       </c>
       <c r="BF8" t="n">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.26</v>
+        <v>2.21</v>
       </c>
       <c r="BH8" t="n">
-        <v>11.09</v>
+        <v>11</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.26</v>
+        <v>2.21</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.52</v>
+        <v>0.54</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.39</v>
+        <v>0.38</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.91</v>
+        <v>4.67</v>
       </c>
       <c r="BQ8" t="n">
-        <v>6.17</v>
+        <v>5.88</v>
       </c>
       <c r="BR8" t="n">
-        <v>82.61</v>
+        <v>83.33</v>
       </c>
       <c r="BS8" t="n">
-        <v>56.52</v>
+        <v>54.17</v>
       </c>
       <c r="BT8" t="n">
-        <v>47.83</v>
+        <v>45.83</v>
       </c>
       <c r="BU8" t="n">
-        <v>21.74</v>
+        <v>20.83</v>
       </c>
       <c r="BV8" t="n">
-        <v>13.04</v>
+        <v>12.5</v>
       </c>
       <c r="BW8" t="n">
-        <v>4.35</v>
+        <v>4.17</v>
       </c>
       <c r="BX8" t="n">
-        <v>47.83</v>
+        <v>45.83</v>
       </c>
       <c r="BY8" t="n">
         <v>2.38</v>
@@ -4028,25 +4028,25 @@
         <v>2.58</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.13</v>
+        <v>3.12</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.28</v>
+        <v>3.27</v>
       </c>
       <c r="CC8" t="n">
-        <v>3.82</v>
+        <v>3.73</v>
       </c>
       <c r="CD8" t="n">
-        <v>4.18</v>
+        <v>4.11</v>
       </c>
       <c r="CE8" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="CF8" t="n">
-        <v>3.15</v>
+        <v>3.16</v>
       </c>
       <c r="CG8" t="n">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="CH8" t="n">
         <v>1.32</v>
@@ -4055,7 +4055,7 @@
         <v>1.79</v>
       </c>
       <c r="CJ8" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="CK8" t="n">
         <v>1.63</v>
@@ -4064,28 +4064,28 @@
         <v>2.17</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="CN8" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CO8" t="n">
         <v>1.38</v>
       </c>
       <c r="CP8" t="n">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="CQ8" t="n">
-        <v>4.13</v>
+        <v>4.14</v>
       </c>
       <c r="CR8" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="CS8" t="n">
         <v>3.19</v>
       </c>
       <c r="CT8" t="n">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="CU8" t="n">
         <v>1.37</v>
@@ -4094,7 +4094,7 @@
         <v>1.89</v>
       </c>
       <c r="CW8" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="CX8" t="n">
         <v>1.62</v>
@@ -4109,25 +4109,25 @@
         <v>1.79</v>
       </c>
       <c r="DB8" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="DC8" t="n">
         <v>2.32</v>
       </c>
       <c r="DD8" t="n">
-        <v>4.3</v>
+        <v>4.33</v>
       </c>
       <c r="DE8" t="n">
         <v>0.08</v>
       </c>
       <c r="DF8" t="n">
-        <v>2.09</v>
+        <v>2.12</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.74</v>
+        <v>2.58</v>
       </c>
       <c r="DH8" t="n">
-        <v>90.48</v>
+        <v>90.5</v>
       </c>
       <c r="DI8" t="n">
         <v>0.04</v>
@@ -4136,28 +4136,28 @@
         <v>2.96</v>
       </c>
       <c r="DK8" t="n">
-        <v>5.13</v>
+        <v>5.08</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.26</v>
+        <v>0.21</v>
       </c>
       <c r="DM8" t="n">
-        <v>40.48</v>
+        <v>40.67</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.83</v>
+        <v>0.79</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.39</v>
+        <v>2.25</v>
       </c>
       <c r="DP8" t="n">
-        <v>14.43</v>
+        <v>14.29</v>
       </c>
       <c r="DQ8" t="n">
-        <v>12.31</v>
+        <v>12.34</v>
       </c>
       <c r="DR8" t="n">
-        <v>8.699999999999999</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="DS8" t="n">
         <v>0.04</v>
@@ -4169,28 +4169,28 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>45.74</v>
+        <v>45.83</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="DX8" t="n">
-        <v>10.35</v>
+        <v>10.38</v>
       </c>
       <c r="DY8" t="n">
-        <v>7.04</v>
+        <v>7.16</v>
       </c>
       <c r="DZ8" t="n">
-        <v>3.31</v>
+        <v>3.21</v>
       </c>
       <c r="EA8" t="n">
-        <v>19.87</v>
+        <v>19.8</v>
       </c>
       <c r="EB8" t="n">
         <v>1.18</v>
       </c>
       <c r="EC8" t="n">
-        <v>2.87</v>
+        <v>2.83</v>
       </c>
     </row>
     <row r="9">
@@ -4200,94 +4200,94 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D9" t="n">
         <v>12</v>
       </c>
       <c r="E9" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="F9" t="n">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="G9" t="n">
-        <v>2.82</v>
+        <v>2.92</v>
       </c>
       <c r="H9" t="n">
-        <v>103.91</v>
+        <v>103.67</v>
       </c>
       <c r="I9" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="J9" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="K9" t="n">
-        <v>5.45</v>
+        <v>5.42</v>
       </c>
       <c r="L9" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="M9" t="n">
-        <v>56.36</v>
+        <v>57.33</v>
       </c>
       <c r="N9" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="O9" t="n">
-        <v>2.64</v>
+        <v>2.5</v>
       </c>
       <c r="P9" t="n">
-        <v>15.73</v>
+        <v>15.25</v>
       </c>
       <c r="Q9" t="n">
-        <v>14.55</v>
+        <v>14.25</v>
       </c>
       <c r="R9" t="n">
-        <v>5</v>
+        <v>4.83</v>
       </c>
       <c r="S9" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="T9" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="U9" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="V9" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>59.18</v>
+        <v>60.17</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="Z9" t="n">
-        <v>16.36</v>
+        <v>16.58</v>
       </c>
       <c r="AA9" t="n">
-        <v>11.36</v>
+        <v>11.25</v>
       </c>
       <c r="AB9" t="n">
-        <v>5</v>
+        <v>5.33</v>
       </c>
       <c r="AC9" t="n">
-        <v>21.73</v>
+        <v>21.58</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.64</v>
+        <v>2.67</v>
       </c>
       <c r="AF9" t="n">
         <v>0.33</v>
@@ -4371,49 +4371,49 @@
         <v>2.92</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.39</v>
+        <v>2.46</v>
       </c>
       <c r="BH9" t="n">
-        <v>9.779999999999999</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.39</v>
+        <v>2.46</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.52</v>
+        <v>0.54</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.52</v>
+        <v>0.54</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.61</v>
+        <v>0.67</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.74</v>
+        <v>0.71</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.65</v>
+        <v>4.54</v>
       </c>
       <c r="BQ9" t="n">
-        <v>5.13</v>
+        <v>5.08</v>
       </c>
       <c r="BR9" t="n">
-        <v>86.95999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="BS9" t="n">
-        <v>73.91</v>
+        <v>75</v>
       </c>
       <c r="BT9" t="n">
-        <v>52.17</v>
+        <v>54.17</v>
       </c>
       <c r="BU9" t="n">
-        <v>26.09</v>
+        <v>29.17</v>
       </c>
       <c r="BV9" t="n">
         <v>0</v>
@@ -4422,19 +4422,19 @@
         <v>0</v>
       </c>
       <c r="BX9" t="n">
-        <v>65.22</v>
+        <v>66.67</v>
       </c>
       <c r="BY9" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="BZ9" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="CA9" t="n">
         <v>3.24</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.37</v>
+        <v>3.38</v>
       </c>
       <c r="CC9" t="n">
         <v>3.05</v>
@@ -4455,25 +4455,25 @@
         <v>1.39</v>
       </c>
       <c r="CI9" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CK9" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CL9" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CM9" t="n">
         <v>2.35</v>
       </c>
       <c r="CN9" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CO9" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="CP9" t="n">
         <v>2</v>
@@ -4500,13 +4500,13 @@
         <v>1.8</v>
       </c>
       <c r="CX9" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CY9" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CZ9" t="n">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="DA9" t="n">
         <v>1.87</v>
@@ -4521,16 +4521,16 @@
         <v>3.6</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="DG9" t="n">
-        <v>2.91</v>
+        <v>2.96</v>
       </c>
       <c r="DH9" t="n">
-        <v>97.48</v>
+        <v>97.62</v>
       </c>
       <c r="DI9" t="n">
         <v>0</v>
@@ -4542,58 +4542,58 @@
         <v>5.17</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
       <c r="DM9" t="n">
-        <v>48.13</v>
+        <v>48.96</v>
       </c>
       <c r="DN9" t="n">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="DO9" t="n">
-        <v>2.26</v>
+        <v>2.21</v>
       </c>
       <c r="DP9" t="n">
-        <v>15.78</v>
+        <v>15.54</v>
       </c>
       <c r="DQ9" t="n">
-        <v>14.65</v>
+        <v>14.5</v>
       </c>
       <c r="DR9" t="n">
-        <v>6.26</v>
+        <v>6.12</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>56.31</v>
+        <v>56.92</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DX9" t="n">
-        <v>14.78</v>
+        <v>14.95</v>
       </c>
       <c r="DY9" t="n">
         <v>9.83</v>
       </c>
       <c r="DZ9" t="n">
-        <v>4.96</v>
+        <v>5.12</v>
       </c>
       <c r="EA9" t="n">
-        <v>21.57</v>
+        <v>21.5</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="10">
@@ -4603,13 +4603,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C10" t="n">
         <v>11</v>
       </c>
       <c r="D10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E10" t="n">
         <v>0.18</v>
@@ -4696,136 +4696,136 @@
         <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AI10" t="n">
-        <v>75.25</v>
+        <v>75.45999999999999</v>
       </c>
       <c r="AJ10" t="n">
         <v>0.08</v>
       </c>
       <c r="AK10" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>4.69</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>36.54</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>3</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>11.62</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>12.46</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>8.380000000000001</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>48</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>12.77</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>8.08</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>4.69</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>15.15</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="BG10" t="n">
         <v>2.67</v>
       </c>
-      <c r="AL10" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>35</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>11.75</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>12.58</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>8.42</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>47.17</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>7.83</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>4.67</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>15</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="BF10" t="n">
+      <c r="BH10" t="n">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="BI10" t="n">
         <v>2.67</v>
       </c>
-      <c r="BG10" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="BH10" t="n">
-        <v>8.779999999999999</v>
-      </c>
-      <c r="BI10" t="n">
-        <v>2.74</v>
-      </c>
       <c r="BJ10" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.48</v>
+        <v>0.46</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.57</v>
+        <v>0.54</v>
       </c>
       <c r="BM10" t="n">
         <v>1</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="BP10" t="n">
-        <v>4.35</v>
+        <v>4.33</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.43</v>
+        <v>4.54</v>
       </c>
       <c r="BR10" t="n">
-        <v>95.65000000000001</v>
+        <v>95.83</v>
       </c>
       <c r="BS10" t="n">
-        <v>82.61</v>
+        <v>79.17</v>
       </c>
       <c r="BT10" t="n">
-        <v>56.52</v>
+        <v>54.17</v>
       </c>
       <c r="BU10" t="n">
-        <v>30.43</v>
+        <v>29.17</v>
       </c>
       <c r="BV10" t="n">
-        <v>4.35</v>
+        <v>4.17</v>
       </c>
       <c r="BW10" t="n">
-        <v>4.35</v>
+        <v>4.17</v>
       </c>
       <c r="BX10" t="n">
-        <v>56.52</v>
+        <v>54.17</v>
       </c>
       <c r="BY10" t="n">
         <v>1.9</v>
@@ -4834,16 +4834,16 @@
         <v>1.89</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.29</v>
+        <v>3.28</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.44</v>
+        <v>3.42</v>
       </c>
       <c r="CC10" t="n">
-        <v>2.86</v>
+        <v>2.82</v>
       </c>
       <c r="CD10" t="n">
-        <v>3.04</v>
+        <v>2.99</v>
       </c>
       <c r="CE10" t="n">
         <v>1.41</v>
@@ -4852,7 +4852,7 @@
         <v>2.89</v>
       </c>
       <c r="CG10" t="n">
-        <v>2.84</v>
+        <v>2.83</v>
       </c>
       <c r="CH10" t="n">
         <v>1.38</v>
@@ -4867,10 +4867,10 @@
         <v>1.62</v>
       </c>
       <c r="CL10" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="CN10" t="n">
         <v>1.74</v>
@@ -4879,25 +4879,25 @@
         <v>1.31</v>
       </c>
       <c r="CP10" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="CQ10" t="n">
-        <v>3.45</v>
+        <v>3.48</v>
       </c>
       <c r="CR10" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="CS10" t="n">
-        <v>3.11</v>
+        <v>3.13</v>
       </c>
       <c r="CT10" t="n">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="CU10" t="n">
         <v>1.39</v>
       </c>
       <c r="CV10" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="CW10" t="n">
         <v>1.85</v>
@@ -4912,91 +4912,91 @@
         <v>2.23</v>
       </c>
       <c r="DA10" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="DB10" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="DC10" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="DD10" t="n">
-        <v>3.63</v>
+        <v>3.65</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="DG10" t="n">
-        <v>2.09</v>
+        <v>2.13</v>
       </c>
       <c r="DH10" t="n">
-        <v>84.73999999999999</v>
+        <v>84.45999999999999</v>
       </c>
       <c r="DI10" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.61</v>
+        <v>2.59</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.57</v>
+        <v>4.67</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.39</v>
+        <v>0.37</v>
       </c>
       <c r="DM10" t="n">
-        <v>39.78</v>
+        <v>40.42</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.82</v>
+        <v>0.84</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.48</v>
+        <v>2.54</v>
       </c>
       <c r="DP10" t="n">
-        <v>11.78</v>
+        <v>11.71</v>
       </c>
       <c r="DQ10" t="n">
-        <v>13.04</v>
+        <v>12.96</v>
       </c>
       <c r="DR10" t="n">
         <v>7.87</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.17</v>
+        <v>0.21</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.17</v>
+        <v>0.21</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>50.44</v>
+        <v>50.75</v>
       </c>
       <c r="DW10" t="n">
         <v>0.04</v>
       </c>
       <c r="DX10" t="n">
-        <v>12.65</v>
+        <v>12.79</v>
       </c>
       <c r="DY10" t="n">
-        <v>8.039999999999999</v>
+        <v>8.17</v>
       </c>
       <c r="DZ10" t="n">
-        <v>4.61</v>
+        <v>4.63</v>
       </c>
       <c r="EA10" t="n">
-        <v>16.78</v>
+        <v>16.79</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="EC10" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="11">
@@ -5006,13 +5006,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C11" t="n">
         <v>11</v>
       </c>
       <c r="D11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -5096,139 +5096,139 @@
         <v>1.91</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.67</v>
+        <v>2.77</v>
       </c>
       <c r="AI11" t="n">
-        <v>98</v>
+        <v>96.31</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="AK11" t="n">
-        <v>3</v>
+        <v>3.08</v>
       </c>
       <c r="AL11" t="n">
-        <v>4.25</v>
+        <v>4.38</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.17</v>
+        <v>0.23</v>
       </c>
       <c r="AN11" t="n">
-        <v>39.92</v>
+        <v>39.31</v>
       </c>
       <c r="AO11" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AQ11" t="n">
-        <v>13.75</v>
+        <v>13.62</v>
       </c>
       <c r="AR11" t="n">
-        <v>15.75</v>
+        <v>16.62</v>
       </c>
       <c r="AS11" t="n">
-        <v>7.17</v>
+        <v>6.85</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="AX11" t="n">
         <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>57.92</v>
+        <v>58.15</v>
       </c>
       <c r="AZ11" t="n">
         <v>0.08</v>
       </c>
       <c r="BA11" t="n">
-        <v>13.67</v>
+        <v>13.38</v>
       </c>
       <c r="BB11" t="n">
-        <v>9.25</v>
+        <v>8.92</v>
       </c>
       <c r="BC11" t="n">
-        <v>4.42</v>
+        <v>4.46</v>
       </c>
       <c r="BD11" t="n">
-        <v>17.58</v>
+        <v>18.23</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="BF11" t="n">
-        <v>2.83</v>
+        <v>2.92</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="BH11" t="n">
-        <v>9.48</v>
+        <v>9.58</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.39</v>
+        <v>0.46</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.39</v>
+        <v>0.38</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.96</v>
+        <v>0.92</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.74</v>
+        <v>0.71</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="BO11" t="n">
-        <v>0.78</v>
+        <v>0.83</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.39</v>
+        <v>4.38</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.04</v>
+        <v>5.17</v>
       </c>
       <c r="BR11" t="n">
-        <v>91.3</v>
+        <v>91.67</v>
       </c>
       <c r="BS11" t="n">
-        <v>78.26000000000001</v>
+        <v>79.17</v>
       </c>
       <c r="BT11" t="n">
-        <v>52.17</v>
+        <v>50</v>
       </c>
       <c r="BU11" t="n">
-        <v>21.74</v>
+        <v>20.83</v>
       </c>
       <c r="BV11" t="n">
-        <v>4.35</v>
+        <v>4.17</v>
       </c>
       <c r="BW11" t="n">
         <v>0</v>
       </c>
       <c r="BX11" t="n">
-        <v>69.56999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="BY11" t="n">
         <v>2.25</v>
@@ -5237,34 +5237,34 @@
         <v>2.32</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.31</v>
+        <v>3.35</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.45</v>
+        <v>3.51</v>
       </c>
       <c r="CC11" t="n">
-        <v>3.77</v>
+        <v>3.94</v>
       </c>
       <c r="CD11" t="n">
-        <v>4.06</v>
+        <v>4.27</v>
       </c>
       <c r="CE11" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="CG11" t="n">
-        <v>2.76</v>
+        <v>2.79</v>
       </c>
       <c r="CH11" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CI11" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CJ11" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CK11" t="n">
         <v>1.63</v>
@@ -5273,34 +5273,34 @@
         <v>2.14</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="CN11" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CO11" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="CP11" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="CQ11" t="n">
-        <v>3.54</v>
+        <v>3.49</v>
       </c>
       <c r="CR11" t="n">
         <v>1.44</v>
       </c>
       <c r="CS11" t="n">
-        <v>3.04</v>
+        <v>3.01</v>
       </c>
       <c r="CT11" t="n">
         <v>2.91</v>
       </c>
       <c r="CU11" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CV11" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="CW11" t="n">
         <v>1.85</v>
@@ -5309,97 +5309,97 @@
         <v>1.64</v>
       </c>
       <c r="CY11" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="CZ11" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="DA11" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="DB11" t="n">
         <v>1.34</v>
       </c>
       <c r="DC11" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="DD11" t="n">
         <v>3.7</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.56</v>
+        <v>1.67</v>
       </c>
       <c r="DG11" t="n">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="DH11" t="n">
-        <v>103.74</v>
+        <v>102.58</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="DK11" t="n">
-        <v>4.96</v>
+        <v>5</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.22</v>
+        <v>0.25</v>
       </c>
       <c r="DM11" t="n">
-        <v>46.83</v>
+        <v>46.21</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.92</v>
+        <v>0.88</v>
       </c>
       <c r="DO11" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="DP11" t="n">
-        <v>13.7</v>
+        <v>13.63</v>
       </c>
       <c r="DQ11" t="n">
-        <v>15.18</v>
+        <v>15.67</v>
       </c>
       <c r="DR11" t="n">
-        <v>7.39</v>
+        <v>7.21</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>59.26</v>
+        <v>59.33</v>
       </c>
       <c r="DW11" t="n">
         <v>0.08</v>
       </c>
       <c r="DX11" t="n">
-        <v>14</v>
+        <v>13.83</v>
       </c>
       <c r="DY11" t="n">
-        <v>9.35</v>
+        <v>9.16</v>
       </c>
       <c r="DZ11" t="n">
-        <v>4.65</v>
+        <v>4.67</v>
       </c>
       <c r="EA11" t="n">
-        <v>18.43</v>
+        <v>18.75</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.39</v>
+        <v>2.46</v>
       </c>
     </row>
     <row r="12">
@@ -5409,58 +5409,58 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D12" t="n">
         <v>11</v>
       </c>
       <c r="E12" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="F12" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="G12" t="n">
         <v>3.08</v>
       </c>
       <c r="H12" t="n">
-        <v>92.42</v>
+        <v>92</v>
       </c>
       <c r="I12" t="n">
         <v>-0.08</v>
       </c>
       <c r="J12" t="n">
-        <v>1.92</v>
+        <v>2.15</v>
       </c>
       <c r="K12" t="n">
-        <v>5.92</v>
+        <v>5.85</v>
       </c>
       <c r="L12" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="M12" t="n">
-        <v>45.17</v>
+        <v>45.23</v>
       </c>
       <c r="N12" t="n">
-        <v>0.67</v>
+        <v>0.77</v>
       </c>
       <c r="O12" t="n">
-        <v>2.83</v>
+        <v>2.77</v>
       </c>
       <c r="P12" t="n">
-        <v>11.92</v>
+        <v>12.31</v>
       </c>
       <c r="Q12" t="n">
-        <v>15.08</v>
+        <v>15.23</v>
       </c>
       <c r="R12" t="n">
-        <v>7.33</v>
+        <v>7.15</v>
       </c>
       <c r="S12" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="T12" t="n">
         <v>1.08</v>
@@ -5475,19 +5475,19 @@
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>52.75</v>
+        <v>51.77</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="Z12" t="n">
-        <v>14.83</v>
+        <v>14.69</v>
       </c>
       <c r="AA12" t="n">
-        <v>11</v>
+        <v>10.69</v>
       </c>
       <c r="AB12" t="n">
-        <v>3.83</v>
+        <v>4</v>
       </c>
       <c r="AC12" t="n">
         <v>24.08</v>
@@ -5496,7 +5496,7 @@
         <v>1.53</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>
@@ -5580,64 +5580,64 @@
         <v>2.55</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.26</v>
+        <v>9.25</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.48</v>
+        <v>0.46</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.22</v>
+        <v>4.17</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.04</v>
+        <v>5.08</v>
       </c>
       <c r="BR12" t="n">
-        <v>78.26000000000001</v>
+        <v>79.17</v>
       </c>
       <c r="BS12" t="n">
-        <v>65.22</v>
+        <v>62.5</v>
       </c>
       <c r="BT12" t="n">
-        <v>43.48</v>
+        <v>41.67</v>
       </c>
       <c r="BU12" t="n">
-        <v>26.09</v>
+        <v>25</v>
       </c>
       <c r="BV12" t="n">
-        <v>8.699999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="BW12" t="n">
-        <v>4.35</v>
+        <v>4.17</v>
       </c>
       <c r="BX12" t="n">
-        <v>56.52</v>
+        <v>54.17</v>
       </c>
       <c r="BY12" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="BZ12" t="n">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="CA12" t="n">
         <v>3.19</v>
@@ -5664,145 +5664,145 @@
         <v>1.33</v>
       </c>
       <c r="CI12" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CJ12" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CK12" t="n">
         <v>1.58</v>
       </c>
       <c r="CL12" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="CN12" t="n">
         <v>1.78</v>
       </c>
       <c r="CO12" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CP12" t="n">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="CQ12" t="n">
-        <v>3.92</v>
+        <v>3.89</v>
       </c>
       <c r="CR12" t="n">
         <v>1.49</v>
       </c>
       <c r="CS12" t="n">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="CT12" t="n">
-        <v>2.72</v>
+        <v>2.73</v>
       </c>
       <c r="CU12" t="n">
         <v>1.36</v>
       </c>
       <c r="CV12" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CW12" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CX12" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CY12" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CZ12" t="n">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="DA12" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="DB12" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="DC12" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="DD12" t="n">
-        <v>4.24</v>
+        <v>4.22</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.09</v>
+        <v>2.13</v>
       </c>
       <c r="DH12" t="n">
-        <v>90.73999999999999</v>
+        <v>90.58</v>
       </c>
       <c r="DI12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.35</v>
+        <v>2.46</v>
       </c>
       <c r="DK12" t="n">
-        <v>4.39</v>
+        <v>4.42</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.43</v>
+        <v>0.41</v>
       </c>
       <c r="DM12" t="n">
-        <v>41.96</v>
+        <v>42.12</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.7</v>
+        <v>0.75</v>
       </c>
       <c r="DO12" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="DP12" t="n">
-        <v>12.79</v>
+        <v>12.96</v>
       </c>
       <c r="DQ12" t="n">
-        <v>14.87</v>
+        <v>14.96</v>
       </c>
       <c r="DR12" t="n">
-        <v>7.69</v>
+        <v>7.58</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>49.48</v>
+        <v>49.08</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DX12" t="n">
-        <v>12.87</v>
+        <v>12.88</v>
       </c>
       <c r="DY12" t="n">
-        <v>9.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="DZ12" t="n">
-        <v>3.56</v>
+        <v>3.67</v>
       </c>
       <c r="EA12" t="n">
-        <v>22.39</v>
+        <v>22.46</v>
       </c>
       <c r="EB12" t="n">
         <v>1.37</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.13</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="13">
@@ -5812,13 +5812,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C13" t="n">
         <v>11</v>
       </c>
       <c r="D13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E13" t="n">
         <v>0.27</v>
@@ -5905,136 +5905,136 @@
         <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AI13" t="n">
-        <v>84.33</v>
+        <v>87.84999999999999</v>
       </c>
       <c r="AJ13" t="n">
         <v>0.08</v>
       </c>
       <c r="AK13" t="n">
-        <v>3.33</v>
+        <v>3.23</v>
       </c>
       <c r="AL13" t="n">
-        <v>3.83</v>
+        <v>3.92</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AN13" t="n">
-        <v>33.83</v>
+        <v>34.46</v>
       </c>
       <c r="AO13" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AQ13" t="n">
-        <v>11.83</v>
+        <v>11.69</v>
       </c>
       <c r="AR13" t="n">
-        <v>14.08</v>
+        <v>14.38</v>
       </c>
       <c r="AS13" t="n">
-        <v>8.42</v>
+        <v>8.08</v>
       </c>
       <c r="AT13" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="AX13" t="n">
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>50.08</v>
+        <v>51.15</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="BA13" t="n">
-        <v>9.92</v>
+        <v>10</v>
       </c>
       <c r="BB13" t="n">
-        <v>6</v>
+        <v>6.08</v>
       </c>
       <c r="BC13" t="n">
         <v>3.92</v>
       </c>
       <c r="BD13" t="n">
-        <v>20.17</v>
+        <v>20.31</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="BF13" t="n">
-        <v>2.92</v>
+        <v>2.85</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.09</v>
+        <v>2.12</v>
       </c>
       <c r="BH13" t="n">
-        <v>9.35</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.09</v>
+        <v>2.12</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.48</v>
+        <v>0.46</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.39</v>
+        <v>0.38</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.52</v>
+        <v>0.58</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="BO13" t="n">
-        <v>0.87</v>
+        <v>0.83</v>
       </c>
       <c r="BP13" t="n">
-        <v>4.3</v>
+        <v>4.29</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4.61</v>
+        <v>4.5</v>
       </c>
       <c r="BR13" t="n">
-        <v>82.61</v>
+        <v>83.33</v>
       </c>
       <c r="BS13" t="n">
-        <v>69.56999999999999</v>
+        <v>70.83</v>
       </c>
       <c r="BT13" t="n">
-        <v>39.13</v>
+        <v>41.67</v>
       </c>
       <c r="BU13" t="n">
-        <v>13.04</v>
+        <v>12.5</v>
       </c>
       <c r="BV13" t="n">
-        <v>4.35</v>
+        <v>4.17</v>
       </c>
       <c r="BW13" t="n">
         <v>0</v>
       </c>
       <c r="BX13" t="n">
-        <v>43.48</v>
+        <v>45.83</v>
       </c>
       <c r="BY13" t="n">
         <v>2.24</v>
@@ -6043,169 +6043,169 @@
         <v>2.35</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.08</v>
+        <v>3.07</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.21</v>
+        <v>3.19</v>
       </c>
       <c r="CC13" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="CD13" t="n">
-        <v>3.47</v>
+        <v>3.5</v>
       </c>
       <c r="CE13" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="CF13" t="n">
-        <v>3.21</v>
+        <v>3.22</v>
       </c>
       <c r="CG13" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="CH13" t="n">
         <v>1.31</v>
       </c>
       <c r="CI13" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CJ13" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="CK13" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="CL13" t="n">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="CN13" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CO13" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CP13" t="n">
-        <v>2.29</v>
+        <v>2.32</v>
       </c>
       <c r="CQ13" t="n">
-        <v>4.15</v>
+        <v>4.21</v>
       </c>
       <c r="CR13" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="CS13" t="n">
         <v>3.22</v>
       </c>
       <c r="CT13" t="n">
-        <v>2.64</v>
+        <v>2.61</v>
       </c>
       <c r="CU13" t="n">
         <v>1.36</v>
       </c>
       <c r="CV13" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CW13" t="n">
-        <v>2.01</v>
+        <v>2.03</v>
       </c>
       <c r="CX13" t="n">
         <v>1.67</v>
       </c>
       <c r="CY13" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="CZ13" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="DA13" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="DB13" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="DC13" t="n">
-        <v>2.39</v>
+        <v>2.42</v>
       </c>
       <c r="DD13" t="n">
-        <v>4.52</v>
+        <v>4.61</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DF13" t="n">
-        <v>2.13</v>
+        <v>2.08</v>
       </c>
       <c r="DG13" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="DH13" t="n">
-        <v>84.95999999999999</v>
+        <v>86.84</v>
       </c>
       <c r="DI13" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ13" t="n">
-        <v>3.22</v>
+        <v>3.17</v>
       </c>
       <c r="DK13" t="n">
-        <v>4.6</v>
+        <v>4.62</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="DM13" t="n">
-        <v>37.69</v>
+        <v>37.87</v>
       </c>
       <c r="DN13" t="n">
         <v>1</v>
       </c>
       <c r="DO13" t="n">
-        <v>2.31</v>
+        <v>2.38</v>
       </c>
       <c r="DP13" t="n">
-        <v>12.82</v>
+        <v>12.71</v>
       </c>
       <c r="DQ13" t="n">
-        <v>14.74</v>
+        <v>14.87</v>
       </c>
       <c r="DR13" t="n">
-        <v>8.050000000000001</v>
+        <v>7.88</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>50.65</v>
+        <v>51.21</v>
       </c>
       <c r="DW13" t="n">
         <v>0.17</v>
       </c>
       <c r="DX13" t="n">
-        <v>11.35</v>
+        <v>11.33</v>
       </c>
       <c r="DY13" t="n">
         <v>7.04</v>
       </c>
       <c r="DZ13" t="n">
-        <v>4.31</v>
+        <v>4.29</v>
       </c>
       <c r="EA13" t="n">
-        <v>21.57</v>
+        <v>21.58</v>
       </c>
       <c r="EB13" t="n">
         <v>1.29</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
     </row>
     <row r="14">
@@ -7021,13 +7021,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C16" t="n">
         <v>12</v>
       </c>
       <c r="D16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E16" t="n">
         <v>0.17</v>
@@ -7114,112 +7114,112 @@
         <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AI16" t="n">
-        <v>92.45</v>
+        <v>93.33</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AK16" t="n">
-        <v>3.55</v>
+        <v>3.58</v>
       </c>
       <c r="AL16" t="n">
-        <v>4.27</v>
+        <v>4.25</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AN16" t="n">
-        <v>38</v>
+        <v>38.17</v>
       </c>
       <c r="AO16" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AP16" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AQ16" t="n">
-        <v>13.45</v>
+        <v>13.75</v>
       </c>
       <c r="AR16" t="n">
-        <v>16.45</v>
+        <v>16.5</v>
       </c>
       <c r="AS16" t="n">
-        <v>8.449999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AW16" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AX16" t="n">
         <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>52.45</v>
+        <v>53.08</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="BA16" t="n">
-        <v>11.27</v>
+        <v>10.83</v>
       </c>
       <c r="BB16" t="n">
-        <v>6.82</v>
+        <v>6.58</v>
       </c>
       <c r="BC16" t="n">
-        <v>4.45</v>
+        <v>4.25</v>
       </c>
       <c r="BD16" t="n">
-        <v>16.82</v>
+        <v>17.75</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="BF16" t="n">
-        <v>3.18</v>
+        <v>3.25</v>
       </c>
       <c r="BG16" t="n">
-        <v>3.57</v>
+        <v>3.46</v>
       </c>
       <c r="BH16" t="n">
-        <v>11.09</v>
+        <v>11</v>
       </c>
       <c r="BI16" t="n">
-        <v>3.57</v>
+        <v>3.46</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="BL16" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="BM16" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="BN16" t="n">
-        <v>2.04</v>
+        <v>1.96</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="BP16" t="n">
-        <v>4.91</v>
+        <v>4.83</v>
       </c>
       <c r="BQ16" t="n">
         <v>6.17</v>
@@ -7228,22 +7228,22 @@
         <v>100</v>
       </c>
       <c r="BS16" t="n">
-        <v>91.3</v>
+        <v>87.5</v>
       </c>
       <c r="BT16" t="n">
-        <v>73.91</v>
+        <v>70.83</v>
       </c>
       <c r="BU16" t="n">
-        <v>56.52</v>
+        <v>54.17</v>
       </c>
       <c r="BV16" t="n">
-        <v>30.43</v>
+        <v>29.17</v>
       </c>
       <c r="BW16" t="n">
-        <v>4.35</v>
+        <v>4.17</v>
       </c>
       <c r="BX16" t="n">
-        <v>78.26000000000001</v>
+        <v>75</v>
       </c>
       <c r="BY16" t="n">
         <v>1.84</v>
@@ -7252,31 +7252,31 @@
         <v>1.85</v>
       </c>
       <c r="CA16" t="n">
-        <v>3.57</v>
+        <v>3.55</v>
       </c>
       <c r="CB16" t="n">
-        <v>3.74</v>
+        <v>3.72</v>
       </c>
       <c r="CC16" t="n">
-        <v>3.05</v>
+        <v>3.03</v>
       </c>
       <c r="CD16" t="n">
-        <v>3.46</v>
+        <v>3.43</v>
       </c>
       <c r="CE16" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CF16" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="CG16" t="n">
-        <v>3.08</v>
+        <v>3.06</v>
       </c>
       <c r="CH16" t="n">
         <v>1.47</v>
       </c>
       <c r="CI16" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="CJ16" t="n">
         <v>1.66</v>
@@ -7291,7 +7291,7 @@
         <v>2.43</v>
       </c>
       <c r="CN16" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CO16" t="n">
         <v>1.23</v>
@@ -7300,19 +7300,19 @@
         <v>1.76</v>
       </c>
       <c r="CQ16" t="n">
-        <v>2.81</v>
+        <v>2.82</v>
       </c>
       <c r="CR16" t="n">
         <v>1.38</v>
       </c>
       <c r="CS16" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="CT16" t="n">
-        <v>3.16</v>
+        <v>3.14</v>
       </c>
       <c r="CU16" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CV16" t="n">
         <v>2.29</v>
@@ -7336,85 +7336,85 @@
         <v>1.24</v>
       </c>
       <c r="DC16" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="DD16" t="n">
-        <v>2.96</v>
+        <v>2.99</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DF16" t="n">
-        <v>2.09</v>
+        <v>2.12</v>
       </c>
       <c r="DG16" t="n">
-        <v>3.39</v>
+        <v>3.38</v>
       </c>
       <c r="DH16" t="n">
-        <v>96.91</v>
+        <v>97.16</v>
       </c>
       <c r="DI16" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DJ16" t="n">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="DK16" t="n">
-        <v>5.96</v>
+        <v>5.88</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="DM16" t="n">
-        <v>43.91</v>
+        <v>43.75</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="DO16" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="DP16" t="n">
-        <v>13.17</v>
+        <v>13.34</v>
       </c>
       <c r="DQ16" t="n">
-        <v>15.04</v>
+        <v>15.12</v>
       </c>
       <c r="DR16" t="n">
-        <v>7.87</v>
+        <v>7.83</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>53.35</v>
+        <v>53.62</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DX16" t="n">
-        <v>13.96</v>
+        <v>13.62</v>
       </c>
       <c r="DY16" t="n">
-        <v>8.52</v>
+        <v>8.33</v>
       </c>
       <c r="DZ16" t="n">
-        <v>5.43</v>
+        <v>5.29</v>
       </c>
       <c r="EA16" t="n">
-        <v>17.92</v>
+        <v>18.34</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="EC16" t="n">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
     </row>
     <row r="17">
@@ -7709,10 +7709,10 @@
         <v>1.47</v>
       </c>
       <c r="CS17" t="n">
-        <v>3.15</v>
+        <v>3.14</v>
       </c>
       <c r="CT17" t="n">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
       <c r="CU17" t="n">
         <v>1.39</v>
@@ -7742,7 +7742,7 @@
         <v>2.17</v>
       </c>
       <c r="DD17" t="n">
-        <v>3.93</v>
+        <v>3.92</v>
       </c>
       <c r="DE17" t="n">
         <v>0.08</v>
@@ -7827,13 +7827,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C18" t="n">
         <v>12</v>
       </c>
       <c r="D18" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E18" t="n">
         <v>0.08</v>
@@ -7917,139 +7917,139 @@
         <v>2.92</v>
       </c>
       <c r="AF18" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AH18" t="n">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="AI18" t="n">
-        <v>103.82</v>
+        <v>103</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AK18" t="n">
-        <v>3.18</v>
+        <v>3.25</v>
       </c>
       <c r="AL18" t="n">
-        <v>5.64</v>
+        <v>5.25</v>
       </c>
       <c r="AM18" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AN18" t="n">
-        <v>44.64</v>
+        <v>44</v>
       </c>
       <c r="AO18" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AP18" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AQ18" t="n">
-        <v>16.36</v>
+        <v>15.92</v>
       </c>
       <c r="AR18" t="n">
-        <v>15</v>
+        <v>14.58</v>
       </c>
       <c r="AS18" t="n">
-        <v>8.27</v>
+        <v>8.67</v>
       </c>
       <c r="AT18" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AU18" t="n">
         <v>1</v>
       </c>
       <c r="AV18" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AW18" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AX18" t="n">
         <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>51.64</v>
+        <v>49.75</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0.09</v>
+        <v>0.17</v>
       </c>
       <c r="BA18" t="n">
-        <v>12.18</v>
+        <v>11.92</v>
       </c>
       <c r="BB18" t="n">
-        <v>8.449999999999999</v>
+        <v>8.17</v>
       </c>
       <c r="BC18" t="n">
-        <v>3.73</v>
+        <v>3.75</v>
       </c>
       <c r="BD18" t="n">
-        <v>22.18</v>
+        <v>21.33</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="BF18" t="n">
-        <v>3.09</v>
+        <v>3</v>
       </c>
       <c r="BG18" t="n">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="BH18" t="n">
-        <v>9.43</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.39</v>
+        <v>0.42</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.43</v>
+        <v>0.46</v>
       </c>
       <c r="BL18" t="n">
-        <v>0.7</v>
+        <v>0.75</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.57</v>
+        <v>0.54</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="BO18" t="n">
-        <v>0.83</v>
+        <v>0.88</v>
       </c>
       <c r="BP18" t="n">
-        <v>3.39</v>
+        <v>3.33</v>
       </c>
       <c r="BQ18" t="n">
-        <v>6.04</v>
+        <v>5.96</v>
       </c>
       <c r="BR18" t="n">
-        <v>91.3</v>
+        <v>91.67</v>
       </c>
       <c r="BS18" t="n">
-        <v>60.87</v>
+        <v>62.5</v>
       </c>
       <c r="BT18" t="n">
-        <v>34.78</v>
+        <v>37.5</v>
       </c>
       <c r="BU18" t="n">
-        <v>13.04</v>
+        <v>16.67</v>
       </c>
       <c r="BV18" t="n">
-        <v>8.699999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="BW18" t="n">
         <v>0</v>
       </c>
       <c r="BX18" t="n">
-        <v>39.13</v>
+        <v>41.67</v>
       </c>
       <c r="BY18" t="n">
         <v>1.88</v>
@@ -8058,22 +8058,22 @@
         <v>1.95</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.25</v>
+        <v>3.26</v>
       </c>
       <c r="CB18" t="n">
-        <v>3.38</v>
+        <v>3.39</v>
       </c>
       <c r="CC18" t="n">
-        <v>2.78</v>
+        <v>2.87</v>
       </c>
       <c r="CD18" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="CE18" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="CF18" t="n">
-        <v>2.98</v>
+        <v>2.97</v>
       </c>
       <c r="CG18" t="n">
         <v>2.69</v>
@@ -8088,13 +8088,13 @@
         <v>1.91</v>
       </c>
       <c r="CK18" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CL18" t="n">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="CM18" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="CN18" t="n">
         <v>1.74</v>
@@ -8103,19 +8103,19 @@
         <v>1.35</v>
       </c>
       <c r="CP18" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="CQ18" t="n">
-        <v>3.83</v>
+        <v>3.8</v>
       </c>
       <c r="CR18" t="n">
         <v>1.48</v>
       </c>
       <c r="CS18" t="n">
-        <v>3.13</v>
+        <v>3.12</v>
       </c>
       <c r="CT18" t="n">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
       <c r="CU18" t="n">
         <v>1.39</v>
@@ -8127,100 +8127,100 @@
         <v>1.94</v>
       </c>
       <c r="CX18" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CY18" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="CZ18" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="DA18" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="DB18" t="n">
         <v>1.38</v>
       </c>
       <c r="DC18" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="DD18" t="n">
-        <v>4.07</v>
+        <v>4.04</v>
       </c>
       <c r="DE18" t="n">
         <v>0.08</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="DG18" t="n">
-        <v>3.96</v>
+        <v>3.79</v>
       </c>
       <c r="DH18" t="n">
-        <v>107.26</v>
+        <v>106.71</v>
       </c>
       <c r="DI18" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DJ18" t="n">
-        <v>3.17</v>
+        <v>3.21</v>
       </c>
       <c r="DK18" t="n">
-        <v>6.13</v>
+        <v>5.92</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="DM18" t="n">
-        <v>53.18</v>
+        <v>52.5</v>
       </c>
       <c r="DN18" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="DO18" t="n">
-        <v>2.17</v>
+        <v>2.12</v>
       </c>
       <c r="DP18" t="n">
-        <v>16.74</v>
+        <v>16.5</v>
       </c>
       <c r="DQ18" t="n">
-        <v>13.83</v>
+        <v>13.66</v>
       </c>
       <c r="DR18" t="n">
-        <v>6.82</v>
+        <v>7.08</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DT18" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DU18" t="n">
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>52.13</v>
+        <v>51.16</v>
       </c>
       <c r="DW18" t="n">
-        <v>0.17</v>
+        <v>0.21</v>
       </c>
       <c r="DX18" t="n">
-        <v>14.04</v>
+        <v>13.84</v>
       </c>
       <c r="DY18" t="n">
-        <v>9.82</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="DZ18" t="n">
-        <v>4.22</v>
+        <v>4.21</v>
       </c>
       <c r="EA18" t="n">
-        <v>24.96</v>
+        <v>24.42</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="EC18" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
     </row>
     <row r="19">
@@ -8230,13 +8230,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C19" t="n">
         <v>12</v>
       </c>
       <c r="D19" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -8320,139 +8320,139 @@
         <v>2.92</v>
       </c>
       <c r="AF19" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AH19" t="n">
-        <v>3.27</v>
+        <v>3.33</v>
       </c>
       <c r="AI19" t="n">
-        <v>86.55</v>
+        <v>88.58</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AK19" t="n">
-        <v>3.36</v>
+        <v>3.33</v>
       </c>
       <c r="AL19" t="n">
-        <v>5.36</v>
+        <v>5.25</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AN19" t="n">
-        <v>40.73</v>
+        <v>42.08</v>
       </c>
       <c r="AO19" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AP19" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AQ19" t="n">
-        <v>13.27</v>
+        <v>12.83</v>
       </c>
       <c r="AR19" t="n">
-        <v>15.18</v>
+        <v>14.83</v>
       </c>
       <c r="AS19" t="n">
-        <v>7.45</v>
+        <v>7.33</v>
       </c>
       <c r="AT19" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AU19" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AV19" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AW19" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AX19" t="n">
         <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>48.36</v>
+        <v>49.58</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="BA19" t="n">
-        <v>12.91</v>
+        <v>12.5</v>
       </c>
       <c r="BB19" t="n">
-        <v>9.09</v>
+        <v>8.75</v>
       </c>
       <c r="BC19" t="n">
-        <v>3.82</v>
+        <v>3.75</v>
       </c>
       <c r="BD19" t="n">
-        <v>17.55</v>
+        <v>18.83</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="BF19" t="n">
-        <v>2.91</v>
+        <v>2.92</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="BH19" t="n">
-        <v>10.35</v>
+        <v>10.33</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.35</v>
+        <v>0.38</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.43</v>
+        <v>0.42</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.91</v>
+        <v>0.88</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="BO19" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="BP19" t="n">
-        <v>5.13</v>
+        <v>5.04</v>
       </c>
       <c r="BQ19" t="n">
-        <v>5.17</v>
+        <v>5.25</v>
       </c>
       <c r="BR19" t="n">
-        <v>91.3</v>
+        <v>91.67</v>
       </c>
       <c r="BS19" t="n">
-        <v>65.22</v>
+        <v>66.67</v>
       </c>
       <c r="BT19" t="n">
-        <v>39.13</v>
+        <v>37.5</v>
       </c>
       <c r="BU19" t="n">
-        <v>26.09</v>
+        <v>25</v>
       </c>
       <c r="BV19" t="n">
-        <v>17.39</v>
+        <v>16.67</v>
       </c>
       <c r="BW19" t="n">
-        <v>4.35</v>
+        <v>4.17</v>
       </c>
       <c r="BX19" t="n">
-        <v>56.52</v>
+        <v>54.17</v>
       </c>
       <c r="BY19" t="n">
         <v>2.41</v>
@@ -8464,19 +8464,19 @@
         <v>3.19</v>
       </c>
       <c r="CB19" t="n">
-        <v>3.32</v>
+        <v>3.33</v>
       </c>
       <c r="CC19" t="n">
-        <v>3.82</v>
+        <v>3.84</v>
       </c>
       <c r="CD19" t="n">
-        <v>4.45</v>
+        <v>4.46</v>
       </c>
       <c r="CE19" t="n">
         <v>1.47</v>
       </c>
       <c r="CF19" t="n">
-        <v>3.12</v>
+        <v>3.1</v>
       </c>
       <c r="CG19" t="n">
         <v>2.62</v>
@@ -8485,37 +8485,37 @@
         <v>1.33</v>
       </c>
       <c r="CI19" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="CJ19" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="CK19" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="CL19" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="CM19" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="CN19" t="n">
         <v>1.83</v>
-      </c>
-      <c r="CJ19" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="CK19" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="CL19" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="CM19" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="CN19" t="n">
-        <v>1.81</v>
       </c>
       <c r="CO19" t="n">
         <v>1.38</v>
       </c>
       <c r="CP19" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="CQ19" t="n">
-        <v>4.08</v>
+        <v>4.04</v>
       </c>
       <c r="CR19" t="n">
         <v>1.5</v>
       </c>
       <c r="CS19" t="n">
-        <v>3.18</v>
+        <v>3.19</v>
       </c>
       <c r="CT19" t="n">
         <v>2.73</v>
@@ -8545,82 +8545,82 @@
         <v>1.4</v>
       </c>
       <c r="DC19" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="DD19" t="n">
-        <v>4.17</v>
+        <v>4.15</v>
       </c>
       <c r="DE19" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="DG19" t="n">
-        <v>2.39</v>
+        <v>2.46</v>
       </c>
       <c r="DH19" t="n">
-        <v>89.04000000000001</v>
+        <v>89.95999999999999</v>
       </c>
       <c r="DI19" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ19" t="n">
-        <v>3.61</v>
+        <v>3.58</v>
       </c>
       <c r="DK19" t="n">
-        <v>4.61</v>
+        <v>4.58</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="DM19" t="n">
-        <v>40.74</v>
+        <v>41.42</v>
       </c>
       <c r="DN19" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="DO19" t="n">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="DP19" t="n">
-        <v>12.96</v>
+        <v>12.75</v>
       </c>
       <c r="DQ19" t="n">
-        <v>15.39</v>
+        <v>15.2</v>
       </c>
       <c r="DR19" t="n">
-        <v>7.91</v>
+        <v>7.83</v>
       </c>
       <c r="DS19" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DT19" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DU19" t="n">
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>49.43</v>
+        <v>50</v>
       </c>
       <c r="DW19" t="n">
-        <v>0.43</v>
+        <v>0.42</v>
       </c>
       <c r="DX19" t="n">
-        <v>12.04</v>
+        <v>11.88</v>
       </c>
       <c r="DY19" t="n">
-        <v>8.69</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="DZ19" t="n">
-        <v>3.35</v>
+        <v>3.33</v>
       </c>
       <c r="EA19" t="n">
-        <v>20</v>
+        <v>20.54</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="EC19" t="n">
         <v>2.92</v>
@@ -8633,10 +8633,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C20" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D20" t="n">
         <v>11</v>
@@ -8645,82 +8645,82 @@
         <v>0.08</v>
       </c>
       <c r="F20" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="G20" t="n">
-        <v>3.08</v>
+        <v>3.15</v>
       </c>
       <c r="H20" t="n">
-        <v>114.83</v>
+        <v>106.23</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="K20" t="n">
-        <v>5.42</v>
+        <v>5.62</v>
       </c>
       <c r="L20" t="n">
-        <v>0.33</v>
+        <v>0.46</v>
       </c>
       <c r="M20" t="n">
-        <v>59.92</v>
+        <v>59.31</v>
       </c>
       <c r="N20" t="n">
-        <v>0.83</v>
+        <v>0.92</v>
       </c>
       <c r="O20" t="n">
-        <v>2.33</v>
+        <v>2.46</v>
       </c>
       <c r="P20" t="n">
-        <v>15.83</v>
+        <v>15.69</v>
       </c>
       <c r="Q20" t="n">
-        <v>12.25</v>
+        <v>11.85</v>
       </c>
       <c r="R20" t="n">
-        <v>6.42</v>
+        <v>6.77</v>
       </c>
       <c r="S20" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="T20" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="U20" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="V20" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>53.92</v>
+        <v>53.77</v>
       </c>
       <c r="Y20" t="n">
         <v>0.08</v>
       </c>
       <c r="Z20" t="n">
-        <v>16.17</v>
+        <v>15.69</v>
       </c>
       <c r="AA20" t="n">
-        <v>10.67</v>
+        <v>10.23</v>
       </c>
       <c r="AB20" t="n">
-        <v>5.5</v>
+        <v>5.46</v>
       </c>
       <c r="AC20" t="n">
-        <v>18.67</v>
+        <v>18.77</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="AF20" t="n">
         <v>0.09</v>
@@ -8804,70 +8804,70 @@
         <v>2.36</v>
       </c>
       <c r="BG20" t="n">
-        <v>2.17</v>
+        <v>2.12</v>
       </c>
       <c r="BH20" t="n">
-        <v>8.609999999999999</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="BI20" t="n">
-        <v>2.17</v>
+        <v>2.12</v>
       </c>
       <c r="BJ20" t="n">
-        <v>0.57</v>
+        <v>0.54</v>
       </c>
       <c r="BK20" t="n">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
       <c r="BL20" t="n">
         <v>1</v>
       </c>
       <c r="BM20" t="n">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
       <c r="BN20" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="BO20" t="n">
-        <v>0.87</v>
+        <v>0.83</v>
       </c>
       <c r="BP20" t="n">
-        <v>3.65</v>
+        <v>3.71</v>
       </c>
       <c r="BQ20" t="n">
-        <v>4.96</v>
+        <v>5</v>
       </c>
       <c r="BR20" t="n">
-        <v>82.61</v>
+        <v>83.33</v>
       </c>
       <c r="BS20" t="n">
-        <v>65.22</v>
+        <v>62.5</v>
       </c>
       <c r="BT20" t="n">
-        <v>47.83</v>
+        <v>45.83</v>
       </c>
       <c r="BU20" t="n">
-        <v>17.39</v>
+        <v>16.67</v>
       </c>
       <c r="BV20" t="n">
-        <v>4.35</v>
+        <v>4.17</v>
       </c>
       <c r="BW20" t="n">
         <v>0</v>
       </c>
       <c r="BX20" t="n">
-        <v>47.83</v>
+        <v>45.83</v>
       </c>
       <c r="BY20" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="BZ20" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="CA20" t="n">
-        <v>3.17</v>
+        <v>3.16</v>
       </c>
       <c r="CB20" t="n">
-        <v>3.26</v>
+        <v>3.25</v>
       </c>
       <c r="CC20" t="n">
         <v>3.26</v>
@@ -8882,7 +8882,7 @@
         <v>3.26</v>
       </c>
       <c r="CG20" t="n">
-        <v>2.52</v>
+        <v>2.51</v>
       </c>
       <c r="CH20" t="n">
         <v>1.31</v>
@@ -8891,7 +8891,7 @@
         <v>1.74</v>
       </c>
       <c r="CJ20" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="CK20" t="n">
         <v>1.64</v>
@@ -8909,10 +8909,10 @@
         <v>1.42</v>
       </c>
       <c r="CP20" t="n">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="CQ20" t="n">
-        <v>4.39</v>
+        <v>4.41</v>
       </c>
       <c r="CR20" t="n">
         <v>1.54</v>
@@ -8936,10 +8936,10 @@
         <v>1.68</v>
       </c>
       <c r="CY20" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="CZ20" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="DA20" t="n">
         <v>1.71</v>
@@ -8957,76 +8957,76 @@
         <v>0.08</v>
       </c>
       <c r="DF20" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="DG20" t="n">
-        <v>2.87</v>
+        <v>2.92</v>
       </c>
       <c r="DH20" t="n">
-        <v>106.17</v>
+        <v>101.88</v>
       </c>
       <c r="DI20" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ20" t="n">
-        <v>2.65</v>
+        <v>2.67</v>
       </c>
       <c r="DK20" t="n">
-        <v>4.61</v>
+        <v>4.75</v>
       </c>
       <c r="DL20" t="n">
-        <v>0.34</v>
+        <v>0.41</v>
       </c>
       <c r="DM20" t="n">
-        <v>49.22</v>
+        <v>49.34</v>
       </c>
       <c r="DN20" t="n">
-        <v>0.87</v>
+        <v>0.92</v>
       </c>
       <c r="DO20" t="n">
-        <v>1.74</v>
+        <v>1.83</v>
       </c>
       <c r="DP20" t="n">
-        <v>14.43</v>
+        <v>14.42</v>
       </c>
       <c r="DQ20" t="n">
-        <v>12.78</v>
+        <v>12.54</v>
       </c>
       <c r="DR20" t="n">
-        <v>7.3</v>
+        <v>7.46</v>
       </c>
       <c r="DS20" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DT20" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DU20" t="n">
         <v>0</v>
       </c>
       <c r="DV20" t="n">
-        <v>50.4</v>
+        <v>50.46</v>
       </c>
       <c r="DW20" t="n">
         <v>0.13</v>
       </c>
       <c r="DX20" t="n">
-        <v>12.57</v>
+        <v>12.46</v>
       </c>
       <c r="DY20" t="n">
-        <v>8.44</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="DZ20" t="n">
-        <v>4.13</v>
+        <v>4.17</v>
       </c>
       <c r="EA20" t="n">
-        <v>19.39</v>
+        <v>19.42</v>
       </c>
       <c r="EB20" t="n">
         <v>1.44</v>
       </c>
       <c r="EC20" t="n">
-        <v>2.39</v>
+        <v>2.41</v>
       </c>
     </row>
     <row r="21">
@@ -9036,94 +9036,94 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C21" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D21" t="n">
         <v>12</v>
       </c>
       <c r="E21" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="F21" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="G21" t="n">
-        <v>2.91</v>
+        <v>2.58</v>
       </c>
       <c r="H21" t="n">
-        <v>97.64</v>
+        <v>97.25</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="K21" t="n">
-        <v>5.45</v>
+        <v>5.42</v>
       </c>
       <c r="L21" t="n">
-        <v>0.73</v>
+        <v>0.58</v>
       </c>
       <c r="M21" t="n">
-        <v>46.55</v>
+        <v>47.75</v>
       </c>
       <c r="N21" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="O21" t="n">
-        <v>2.45</v>
+        <v>2.17</v>
       </c>
       <c r="P21" t="n">
-        <v>14.09</v>
+        <v>14</v>
       </c>
       <c r="Q21" t="n">
-        <v>12.55</v>
+        <v>12.42</v>
       </c>
       <c r="R21" t="n">
-        <v>9.640000000000001</v>
+        <v>9.67</v>
       </c>
       <c r="S21" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="T21" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="U21" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="V21" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>45.64</v>
+        <v>46.17</v>
       </c>
       <c r="Y21" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="Z21" t="n">
-        <v>12.36</v>
+        <v>12.33</v>
       </c>
       <c r="AA21" t="n">
-        <v>8.82</v>
+        <v>8.75</v>
       </c>
       <c r="AB21" t="n">
-        <v>3.55</v>
+        <v>3.58</v>
       </c>
       <c r="AC21" t="n">
-        <v>23.55</v>
+        <v>23.33</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.64</v>
+        <v>2.67</v>
       </c>
       <c r="AF21" t="n">
         <v>0</v>
@@ -9207,70 +9207,70 @@
         <v>2</v>
       </c>
       <c r="BG21" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="BH21" t="n">
-        <v>9.26</v>
+        <v>9.25</v>
       </c>
       <c r="BI21" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="BJ21" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="BK21" t="n">
-        <v>0.48</v>
+        <v>0.46</v>
       </c>
       <c r="BL21" t="n">
-        <v>0.74</v>
+        <v>0.71</v>
       </c>
       <c r="BM21" t="n">
-        <v>0.43</v>
+        <v>0.42</v>
       </c>
       <c r="BN21" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="BO21" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="BP21" t="n">
-        <v>4.22</v>
+        <v>4</v>
       </c>
       <c r="BQ21" t="n">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="BR21" t="n">
-        <v>95.65000000000001</v>
+        <v>95.83</v>
       </c>
       <c r="BS21" t="n">
-        <v>69.56999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="BT21" t="n">
-        <v>39.13</v>
+        <v>37.5</v>
       </c>
       <c r="BU21" t="n">
-        <v>17.39</v>
+        <v>16.67</v>
       </c>
       <c r="BV21" t="n">
-        <v>8.699999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="BW21" t="n">
         <v>0</v>
       </c>
       <c r="BX21" t="n">
-        <v>52.17</v>
+        <v>50</v>
       </c>
       <c r="BY21" t="n">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="BZ21" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="CA21" t="n">
         <v>2.96</v>
       </c>
       <c r="CB21" t="n">
-        <v>3.1</v>
+        <v>3.09</v>
       </c>
       <c r="CC21" t="n">
         <v>3.8</v>
@@ -9282,28 +9282,28 @@
         <v>1.56</v>
       </c>
       <c r="CF21" t="n">
-        <v>3.65</v>
+        <v>3.63</v>
       </c>
       <c r="CG21" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="CH21" t="n">
         <v>1.25</v>
       </c>
       <c r="CI21" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CJ21" t="n">
         <v>2.16</v>
       </c>
       <c r="CK21" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CL21" t="n">
         <v>2.19</v>
       </c>
       <c r="CM21" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="CN21" t="n">
         <v>1.73</v>
@@ -9312,10 +9312,10 @@
         <v>1.51</v>
       </c>
       <c r="CP21" t="n">
-        <v>2.57</v>
+        <v>2.56</v>
       </c>
       <c r="CQ21" t="n">
-        <v>4.96</v>
+        <v>4.94</v>
       </c>
       <c r="CR21" t="n">
         <v>1.6</v>
@@ -9330,10 +9330,10 @@
         <v>1.37</v>
       </c>
       <c r="CV21" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CW21" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="CX21" t="n">
         <v>1.71</v>
@@ -9351,85 +9351,85 @@
         <v>1.56</v>
       </c>
       <c r="DC21" t="n">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="DD21" t="n">
-        <v>5.51</v>
+        <v>5.49</v>
       </c>
       <c r="DE21" t="n">
         <v>0.04</v>
       </c>
       <c r="DF21" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="DG21" t="n">
-        <v>2.44</v>
+        <v>2.29</v>
       </c>
       <c r="DH21" t="n">
-        <v>89.09</v>
+        <v>89.25</v>
       </c>
       <c r="DI21" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ21" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="DK21" t="n">
-        <v>4.43</v>
+        <v>4.46</v>
       </c>
       <c r="DL21" t="n">
-        <v>0.65</v>
+        <v>0.58</v>
       </c>
       <c r="DM21" t="n">
-        <v>39.39</v>
+        <v>40.29</v>
       </c>
       <c r="DN21" t="n">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="DO21" t="n">
-        <v>1.95</v>
+        <v>1.84</v>
       </c>
       <c r="DP21" t="n">
-        <v>12.91</v>
+        <v>12.92</v>
       </c>
       <c r="DQ21" t="n">
-        <v>13.09</v>
+        <v>13</v>
       </c>
       <c r="DR21" t="n">
-        <v>9.18</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="DS21" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DT21" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DU21" t="n">
         <v>0</v>
       </c>
       <c r="DV21" t="n">
-        <v>45</v>
+        <v>45.29</v>
       </c>
       <c r="DW21" t="n">
         <v>0.08</v>
       </c>
       <c r="DX21" t="n">
-        <v>10.7</v>
+        <v>10.75</v>
       </c>
       <c r="DY21" t="n">
         <v>7.96</v>
       </c>
       <c r="DZ21" t="n">
-        <v>2.74</v>
+        <v>2.79</v>
       </c>
       <c r="EA21" t="n">
         <v>20.83</v>
       </c>
       <c r="EB21" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="EC21" t="n">
-        <v>2.31</v>
+        <v>2.34</v>
       </c>
     </row>
     <row r="22">
@@ -9439,13 +9439,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C22" t="n">
         <v>12</v>
       </c>
       <c r="D22" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -9529,139 +9529,139 @@
         <v>1.92</v>
       </c>
       <c r="AF22" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AG22" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="AH22" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="AI22" t="n">
-        <v>86.27</v>
+        <v>79.75</v>
       </c>
       <c r="AJ22" t="n">
         <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>3.18</v>
+        <v>3.25</v>
       </c>
       <c r="AL22" t="n">
-        <v>4.27</v>
+        <v>4.17</v>
       </c>
       <c r="AM22" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AN22" t="n">
-        <v>37.27</v>
+        <v>37.58</v>
       </c>
       <c r="AO22" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AQ22" t="n">
-        <v>11.55</v>
+        <v>11.17</v>
       </c>
       <c r="AR22" t="n">
-        <v>10</v>
+        <v>10.33</v>
       </c>
       <c r="AS22" t="n">
-        <v>9</v>
+        <v>8.67</v>
       </c>
       <c r="AT22" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AU22" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AV22" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AW22" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AX22" t="n">
         <v>0</v>
       </c>
       <c r="AY22" t="n">
-        <v>43.27</v>
+        <v>43.67</v>
       </c>
       <c r="AZ22" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="BA22" t="n">
-        <v>9.73</v>
+        <v>9.67</v>
       </c>
       <c r="BB22" t="n">
-        <v>5.45</v>
+        <v>5.5</v>
       </c>
       <c r="BC22" t="n">
-        <v>4.27</v>
+        <v>4.17</v>
       </c>
       <c r="BD22" t="n">
-        <v>19.36</v>
+        <v>19.67</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="BF22" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="BG22" t="n">
-        <v>2.78</v>
+        <v>2.71</v>
       </c>
       <c r="BH22" t="n">
-        <v>10.13</v>
+        <v>10.17</v>
       </c>
       <c r="BI22" t="n">
-        <v>2.78</v>
+        <v>2.71</v>
       </c>
       <c r="BJ22" t="n">
-        <v>0.57</v>
+        <v>0.54</v>
       </c>
       <c r="BK22" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="BL22" t="n">
         <v>0.96</v>
       </c>
       <c r="BM22" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="BN22" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="BO22" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="BP22" t="n">
-        <v>4.61</v>
+        <v>4.62</v>
       </c>
       <c r="BQ22" t="n">
-        <v>4.96</v>
+        <v>5</v>
       </c>
       <c r="BR22" t="n">
-        <v>95.65000000000001</v>
+        <v>95.83</v>
       </c>
       <c r="BS22" t="n">
-        <v>65.22</v>
+        <v>62.5</v>
       </c>
       <c r="BT22" t="n">
-        <v>52.17</v>
+        <v>50</v>
       </c>
       <c r="BU22" t="n">
-        <v>30.43</v>
+        <v>29.17</v>
       </c>
       <c r="BV22" t="n">
-        <v>21.74</v>
+        <v>20.83</v>
       </c>
       <c r="BW22" t="n">
-        <v>8.699999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="BX22" t="n">
-        <v>56.52</v>
+        <v>54.17</v>
       </c>
       <c r="BY22" t="n">
         <v>2.05</v>
@@ -9670,25 +9670,25 @@
         <v>2.07</v>
       </c>
       <c r="CA22" t="n">
-        <v>3.21</v>
+        <v>3.2</v>
       </c>
       <c r="CB22" t="n">
-        <v>3.31</v>
+        <v>3.3</v>
       </c>
       <c r="CC22" t="n">
-        <v>3.1</v>
+        <v>3.13</v>
       </c>
       <c r="CD22" t="n">
-        <v>3.19</v>
+        <v>3.25</v>
       </c>
       <c r="CE22" t="n">
         <v>1.45</v>
       </c>
       <c r="CF22" t="n">
-        <v>3.1</v>
+        <v>3.11</v>
       </c>
       <c r="CG22" t="n">
-        <v>2.65</v>
+        <v>2.64</v>
       </c>
       <c r="CH22" t="n">
         <v>1.33</v>
@@ -9697,13 +9697,13 @@
         <v>1.85</v>
       </c>
       <c r="CJ22" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CK22" t="n">
         <v>1.61</v>
       </c>
       <c r="CL22" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="CM22" t="n">
         <v>2.18</v>
@@ -9715,10 +9715,10 @@
         <v>1.37</v>
       </c>
       <c r="CP22" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="CQ22" t="n">
-        <v>3.92</v>
+        <v>3.95</v>
       </c>
       <c r="CR22" t="n">
         <v>1.48</v>
@@ -9733,10 +9733,10 @@
         <v>1.39</v>
       </c>
       <c r="CV22" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CW22" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="CX22" t="n">
         <v>1.63</v>
@@ -9754,85 +9754,85 @@
         <v>1.42</v>
       </c>
       <c r="DC22" t="n">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="DD22" t="n">
-        <v>4.31</v>
+        <v>4.33</v>
       </c>
       <c r="DE22" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DF22" t="n">
         <v>2</v>
       </c>
       <c r="DG22" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="DH22" t="n">
-        <v>99</v>
+        <v>95.20999999999999</v>
       </c>
       <c r="DI22" t="n">
         <v>0</v>
       </c>
       <c r="DJ22" t="n">
-        <v>2.78</v>
+        <v>2.83</v>
       </c>
       <c r="DK22" t="n">
-        <v>4.87</v>
+        <v>4.79</v>
       </c>
       <c r="DL22" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="DM22" t="n">
-        <v>45.17</v>
+        <v>45</v>
       </c>
       <c r="DN22" t="n">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="DO22" t="n">
-        <v>2.17</v>
+        <v>2.12</v>
       </c>
       <c r="DP22" t="n">
-        <v>11.96</v>
+        <v>11.75</v>
       </c>
       <c r="DQ22" t="n">
-        <v>10.39</v>
+        <v>10.54</v>
       </c>
       <c r="DR22" t="n">
-        <v>7.78</v>
+        <v>7.67</v>
       </c>
       <c r="DS22" t="n">
-        <v>0.35</v>
+        <v>0.34</v>
       </c>
       <c r="DT22" t="n">
-        <v>0.35</v>
+        <v>0.34</v>
       </c>
       <c r="DU22" t="n">
         <v>0</v>
       </c>
       <c r="DV22" t="n">
-        <v>45.52</v>
+        <v>45.62</v>
       </c>
       <c r="DW22" t="n">
-        <v>0.22</v>
+        <v>0.25</v>
       </c>
       <c r="DX22" t="n">
-        <v>11.83</v>
+        <v>11.71</v>
       </c>
       <c r="DY22" t="n">
-        <v>7.04</v>
+        <v>7</v>
       </c>
       <c r="DZ22" t="n">
-        <v>4.78</v>
+        <v>4.71</v>
       </c>
       <c r="EA22" t="n">
-        <v>19.13</v>
+        <v>19.3</v>
       </c>
       <c r="EB22" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="EC22" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
     </row>
     <row r="23">
@@ -10076,13 +10076,13 @@
         <v>3.2</v>
       </c>
       <c r="CB23" t="n">
-        <v>3.32</v>
+        <v>3.33</v>
       </c>
       <c r="CC23" t="n">
         <v>2.96</v>
       </c>
       <c r="CD23" t="n">
-        <v>3.29</v>
+        <v>3.28</v>
       </c>
       <c r="CE23" t="n">
         <v>1.47</v>
@@ -10127,7 +10127,7 @@
         <v>1.51</v>
       </c>
       <c r="CS23" t="n">
-        <v>3.22</v>
+        <v>3.21</v>
       </c>
       <c r="CT23" t="n">
         <v>2.69</v>
@@ -10157,7 +10157,7 @@
         <v>1.43</v>
       </c>
       <c r="DC23" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="DD23" t="n">
         <v>4.43</v>

--- a/data/teams/leagues/Averages_Spain_Segunda_División_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Spain_Segunda_División_2025-2026.xlsx
@@ -1848,7 +1848,7 @@
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>55.5</v>
+        <v>55.58</v>
       </c>
       <c r="Y3" t="n">
         <v>0.08</v>
@@ -2154,7 +2154,7 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>54.21</v>
+        <v>54.25</v>
       </c>
       <c r="DW3" t="n">
         <v>0.08</v>
@@ -3138,7 +3138,7 @@
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>48.33</v>
+        <v>48.25</v>
       </c>
       <c r="AZ6" t="n">
         <v>0.17</v>
@@ -3363,7 +3363,7 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>50.54</v>
+        <v>50.5</v>
       </c>
       <c r="DW6" t="n">
         <v>0.08</v>
@@ -3893,7 +3893,7 @@
         <v>2</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.08</v>
+        <v>2.42</v>
       </c>
       <c r="AI8" t="n">
         <v>87.08</v>
@@ -3908,7 +3908,7 @@
         <v>4.25</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="AN8" t="n">
         <v>32.92</v>
@@ -3917,7 +3917,7 @@
         <v>0.5</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="AQ8" t="n">
         <v>14.75</v>
@@ -3995,10 +3995,10 @@
         <v>0.92</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.67</v>
+        <v>4.83</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.88</v>
+        <v>6.17</v>
       </c>
       <c r="BR8" t="n">
         <v>83.33</v>
@@ -4124,7 +4124,7 @@
         <v>2.12</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.58</v>
+        <v>2.75</v>
       </c>
       <c r="DH8" t="n">
         <v>90.5</v>
@@ -4139,7 +4139,7 @@
         <v>5.08</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.21</v>
+        <v>0.25</v>
       </c>
       <c r="DM8" t="n">
         <v>40.67</v>
@@ -4148,7 +4148,7 @@
         <v>0.79</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="DP8" t="n">
         <v>14.29</v>
@@ -5637,7 +5637,7 @@
         <v>2.18</v>
       </c>
       <c r="BZ12" t="n">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="CA12" t="n">
         <v>3.19</v>
@@ -6215,94 +6215,94 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D14" t="n">
         <v>12</v>
       </c>
       <c r="E14" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="F14" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="G14" t="n">
-        <v>2.45</v>
+        <v>2.58</v>
       </c>
       <c r="H14" t="n">
-        <v>92.64</v>
+        <v>91.17</v>
       </c>
       <c r="I14" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="J14" t="n">
-        <v>3.64</v>
+        <v>3.67</v>
       </c>
       <c r="K14" t="n">
-        <v>4.36</v>
+        <v>4.58</v>
       </c>
       <c r="L14" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="M14" t="n">
-        <v>40.55</v>
+        <v>40</v>
       </c>
       <c r="N14" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="O14" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="P14" t="n">
-        <v>17.82</v>
+        <v>17.25</v>
       </c>
       <c r="Q14" t="n">
-        <v>12.55</v>
+        <v>12.25</v>
       </c>
       <c r="R14" t="n">
         <v>8</v>
       </c>
       <c r="S14" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="T14" t="n">
-        <v>0.82</v>
+        <v>0.92</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>45.36</v>
+        <v>44.42</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="Z14" t="n">
-        <v>12.45</v>
+        <v>13.17</v>
       </c>
       <c r="AA14" t="n">
-        <v>8.550000000000001</v>
+        <v>9.17</v>
       </c>
       <c r="AB14" t="n">
-        <v>3.91</v>
+        <v>4</v>
       </c>
       <c r="AC14" t="n">
-        <v>17.91</v>
+        <v>17.83</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AE14" t="n">
-        <v>3.55</v>
+        <v>3.58</v>
       </c>
       <c r="AF14" t="n">
         <v>0.08</v>
@@ -6386,70 +6386,70 @@
         <v>2.58</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="BH14" t="n">
-        <v>8.91</v>
+        <v>9.08</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.52</v>
+        <v>0.54</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="BO14" t="n">
         <v>1.17</v>
       </c>
       <c r="BP14" t="n">
-        <v>3.78</v>
+        <v>3.83</v>
       </c>
       <c r="BQ14" t="n">
-        <v>5.13</v>
+        <v>5.25</v>
       </c>
       <c r="BR14" t="n">
-        <v>91.3</v>
+        <v>91.67</v>
       </c>
       <c r="BS14" t="n">
-        <v>73.91</v>
+        <v>75</v>
       </c>
       <c r="BT14" t="n">
-        <v>56.52</v>
+        <v>58.33</v>
       </c>
       <c r="BU14" t="n">
-        <v>30.43</v>
+        <v>29.17</v>
       </c>
       <c r="BV14" t="n">
-        <v>17.39</v>
+        <v>16.67</v>
       </c>
       <c r="BW14" t="n">
-        <v>4.35</v>
+        <v>4.17</v>
       </c>
       <c r="BX14" t="n">
-        <v>60.87</v>
+        <v>62.5</v>
       </c>
       <c r="BY14" t="n">
-        <v>2.96</v>
+        <v>2.95</v>
       </c>
       <c r="BZ14" t="n">
-        <v>3.3</v>
+        <v>3.29</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.31</v>
+        <v>3.29</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.51</v>
+        <v>3.49</v>
       </c>
       <c r="CC14" t="n">
         <v>5.33</v>
@@ -6458,31 +6458,31 @@
         <v>5.78</v>
       </c>
       <c r="CE14" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="CF14" t="n">
-        <v>3.15</v>
+        <v>3.14</v>
       </c>
       <c r="CG14" t="n">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="CH14" t="n">
         <v>1.32</v>
       </c>
       <c r="CI14" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CJ14" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CK14" t="n">
         <v>1.69</v>
       </c>
       <c r="CL14" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="CN14" t="n">
         <v>1.69</v>
@@ -6491,16 +6491,16 @@
         <v>1.38</v>
       </c>
       <c r="CP14" t="n">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="CQ14" t="n">
-        <v>4.09</v>
+        <v>4.1</v>
       </c>
       <c r="CR14" t="n">
         <v>1.5</v>
       </c>
       <c r="CS14" t="n">
-        <v>3.23</v>
+        <v>3.24</v>
       </c>
       <c r="CT14" t="n">
         <v>2.72</v>
@@ -6521,10 +6521,10 @@
         <v>2.13</v>
       </c>
       <c r="CZ14" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="DA14" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="DB14" t="n">
         <v>1.42</v>
@@ -6539,76 +6539,76 @@
         <v>0.08</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="DG14" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="DH14" t="n">
-        <v>86.39</v>
+        <v>85.92</v>
       </c>
       <c r="DI14" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ14" t="n">
-        <v>3.39</v>
+        <v>3.42</v>
       </c>
       <c r="DK14" t="n">
-        <v>3.52</v>
+        <v>3.67</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DM14" t="n">
-        <v>34.35</v>
+        <v>34.34</v>
       </c>
       <c r="DN14" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="DO14" t="n">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="DP14" t="n">
-        <v>15.96</v>
+        <v>15.75</v>
       </c>
       <c r="DQ14" t="n">
-        <v>12.87</v>
+        <v>12.71</v>
       </c>
       <c r="DR14" t="n">
-        <v>9.17</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.13</v>
+        <v>0.16</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.13</v>
+        <v>0.16</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>41.22</v>
+        <v>40.92</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DX14" t="n">
-        <v>11.13</v>
+        <v>11.54</v>
       </c>
       <c r="DY14" t="n">
-        <v>7.7</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="DZ14" t="n">
-        <v>3.44</v>
+        <v>3.5</v>
       </c>
       <c r="EA14" t="n">
-        <v>17.78</v>
+        <v>17.75</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="EC14" t="n">
-        <v>3.04</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="15">
@@ -6618,13 +6618,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C15" t="n">
         <v>12</v>
       </c>
       <c r="D15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E15" t="n">
         <v>0.08</v>
@@ -6708,139 +6708,139 @@
         <v>2.58</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.27</v>
+        <v>2.42</v>
       </c>
       <c r="AI15" t="n">
-        <v>89.73</v>
+        <v>91.75</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AL15" t="n">
-        <v>4.18</v>
+        <v>4.33</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AN15" t="n">
-        <v>43.36</v>
+        <v>45.42</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AQ15" t="n">
-        <v>11.73</v>
+        <v>11.58</v>
       </c>
       <c r="AR15" t="n">
-        <v>12.18</v>
+        <v>12.08</v>
       </c>
       <c r="AS15" t="n">
-        <v>8.449999999999999</v>
+        <v>8.75</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AU15" t="n">
         <v>1</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AX15" t="n">
         <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>49.82</v>
+        <v>51.17</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="BA15" t="n">
-        <v>9.91</v>
+        <v>10.42</v>
       </c>
       <c r="BB15" t="n">
-        <v>6.27</v>
+        <v>6.83</v>
       </c>
       <c r="BC15" t="n">
-        <v>3.64</v>
+        <v>3.58</v>
       </c>
       <c r="BD15" t="n">
-        <v>23.18</v>
+        <v>22.08</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="BF15" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.65</v>
+        <v>2.67</v>
       </c>
       <c r="BH15" t="n">
-        <v>8.48</v>
+        <v>8.67</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.65</v>
+        <v>2.67</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="BP15" t="n">
-        <v>3.52</v>
+        <v>3.58</v>
       </c>
       <c r="BQ15" t="n">
-        <v>4.43</v>
+        <v>4.58</v>
       </c>
       <c r="BR15" t="n">
         <v>100</v>
       </c>
       <c r="BS15" t="n">
-        <v>73.91</v>
+        <v>75</v>
       </c>
       <c r="BT15" t="n">
-        <v>56.52</v>
+        <v>58.33</v>
       </c>
       <c r="BU15" t="n">
-        <v>26.09</v>
+        <v>25</v>
       </c>
       <c r="BV15" t="n">
-        <v>8.699999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="BW15" t="n">
         <v>0</v>
       </c>
       <c r="BX15" t="n">
-        <v>56.52</v>
+        <v>58.33</v>
       </c>
       <c r="BY15" t="n">
         <v>2.25</v>
@@ -6849,25 +6849,25 @@
         <v>2.27</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.21</v>
+        <v>3.2</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.35</v>
+        <v>3.34</v>
       </c>
       <c r="CC15" t="n">
-        <v>4.06</v>
+        <v>3.92</v>
       </c>
       <c r="CD15" t="n">
-        <v>4.4</v>
+        <v>4.25</v>
       </c>
       <c r="CE15" t="n">
         <v>1.47</v>
       </c>
       <c r="CF15" t="n">
-        <v>3.11</v>
+        <v>3.1</v>
       </c>
       <c r="CG15" t="n">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="CH15" t="n">
         <v>1.33</v>
@@ -6879,34 +6879,34 @@
         <v>1.94</v>
       </c>
       <c r="CK15" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CL15" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="CN15" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CO15" t="n">
         <v>1.37</v>
       </c>
       <c r="CP15" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.93</v>
+        <v>3.95</v>
       </c>
       <c r="CR15" t="n">
         <v>1.48</v>
       </c>
       <c r="CS15" t="n">
-        <v>3.19</v>
+        <v>3.2</v>
       </c>
       <c r="CT15" t="n">
-        <v>2.78</v>
+        <v>2.77</v>
       </c>
       <c r="CU15" t="n">
         <v>1.37</v>
@@ -6918,16 +6918,16 @@
         <v>1.98</v>
       </c>
       <c r="CX15" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CY15" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="CZ15" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="DA15" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="DB15" t="n">
         <v>1.4</v>
@@ -6936,82 +6936,82 @@
         <v>2.27</v>
       </c>
       <c r="DD15" t="n">
-        <v>4.21</v>
+        <v>4.22</v>
       </c>
       <c r="DE15" t="n">
         <v>0.08</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="DG15" t="n">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="DH15" t="n">
-        <v>89.44</v>
+        <v>90.45999999999999</v>
       </c>
       <c r="DI15" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ15" t="n">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="DK15" t="n">
-        <v>3.91</v>
+        <v>4</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DM15" t="n">
-        <v>44.52</v>
+        <v>45.5</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.78</v>
+        <v>0.75</v>
       </c>
       <c r="DO15" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="DP15" t="n">
-        <v>12.7</v>
+        <v>12.58</v>
       </c>
       <c r="DQ15" t="n">
-        <v>12.09</v>
+        <v>12.04</v>
       </c>
       <c r="DR15" t="n">
-        <v>8.35</v>
+        <v>8.5</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DU15" t="n">
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>50.87</v>
+        <v>51.5</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DX15" t="n">
-        <v>12.61</v>
+        <v>12.75</v>
       </c>
       <c r="DY15" t="n">
-        <v>7.56</v>
+        <v>7.79</v>
       </c>
       <c r="DZ15" t="n">
-        <v>5.04</v>
+        <v>4.96</v>
       </c>
       <c r="EA15" t="n">
-        <v>22.13</v>
+        <v>21.62</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="EC15" t="n">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="16">
@@ -7309,7 +7309,7 @@
         <v>2.74</v>
       </c>
       <c r="CT16" t="n">
-        <v>3.14</v>
+        <v>3.15</v>
       </c>
       <c r="CU16" t="n">
         <v>1.49</v>
@@ -8383,10 +8383,10 @@
         <v>0.25</v>
       </c>
       <c r="BA19" t="n">
-        <v>12.5</v>
+        <v>12.42</v>
       </c>
       <c r="BB19" t="n">
-        <v>8.75</v>
+        <v>8.67</v>
       </c>
       <c r="BC19" t="n">
         <v>3.75</v>
@@ -8395,7 +8395,7 @@
         <v>18.83</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="BF19" t="n">
         <v>2.92</v>
@@ -8608,10 +8608,10 @@
         <v>0.42</v>
       </c>
       <c r="DX19" t="n">
-        <v>11.88</v>
+        <v>11.84</v>
       </c>
       <c r="DY19" t="n">
-        <v>8.539999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="DZ19" t="n">
         <v>3.33</v>
@@ -9051,7 +9051,7 @@
         <v>2.08</v>
       </c>
       <c r="G21" t="n">
-        <v>2.58</v>
+        <v>2.92</v>
       </c>
       <c r="H21" t="n">
         <v>97.25</v>
@@ -9066,7 +9066,7 @@
         <v>5.42</v>
       </c>
       <c r="L21" t="n">
-        <v>0.58</v>
+        <v>0.67</v>
       </c>
       <c r="M21" t="n">
         <v>47.75</v>
@@ -9075,7 +9075,7 @@
         <v>0.67</v>
       </c>
       <c r="O21" t="n">
-        <v>2.17</v>
+        <v>2.42</v>
       </c>
       <c r="P21" t="n">
         <v>14</v>
@@ -9234,10 +9234,10 @@
         <v>1.12</v>
       </c>
       <c r="BP21" t="n">
-        <v>4</v>
+        <v>4.17</v>
       </c>
       <c r="BQ21" t="n">
-        <v>4.75</v>
+        <v>5.04</v>
       </c>
       <c r="BR21" t="n">
         <v>95.83</v>
@@ -9363,7 +9363,7 @@
         <v>1.75</v>
       </c>
       <c r="DG21" t="n">
-        <v>2.29</v>
+        <v>2.46</v>
       </c>
       <c r="DH21" t="n">
         <v>89.25</v>
@@ -9378,7 +9378,7 @@
         <v>4.46</v>
       </c>
       <c r="DL21" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="DM21" t="n">
         <v>40.29</v>
@@ -9387,7 +9387,7 @@
         <v>0.67</v>
       </c>
       <c r="DO21" t="n">
-        <v>1.84</v>
+        <v>1.96</v>
       </c>
       <c r="DP21" t="n">
         <v>12.92</v>

--- a/data/teams/leagues/Averages_Spain_Segunda_División_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Spain_Segunda_División_2025-2026.xlsx
@@ -2185,13 +2185,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C4" t="n">
         <v>13</v>
       </c>
       <c r="D4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E4" t="n">
         <v>0.08</v>
@@ -2275,139 +2275,139 @@
         <v>2.85</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="AI4" t="n">
-        <v>87.73</v>
+        <v>86.5</v>
       </c>
       <c r="AJ4" t="n">
         <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>2.64</v>
+        <v>2.67</v>
       </c>
       <c r="AL4" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>37.67</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>13.58</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>15.25</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>9.33</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>43.83</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>6.58</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>21.17</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>8.24</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>4.36</v>
+      </c>
+